--- a/Data_Table/공용 스킬 테이블.xlsx
+++ b/Data_Table/공용 스킬 테이블.xlsx
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>시작 일반 쥐 +1마리</t>
+          <t>시작 일반 쥐 +2마리</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" s="1" t="n">
         <v>1</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>시작 일반 쥐 +1마리</t>
+          <t>시작 일반 쥐 +2마리</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>1</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +5초</t>
+          <t>층 제한시간 +4초</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N18" s="1" t="n">
         <v>0</v>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>일반→레어 승급 필요 쥐 -1</t>
+          <t>일반→레어 승급 때 3% 확률로 2마리</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
@@ -1636,11 +1636,11 @@
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>Promote_Need</t>
+          <t>Promote_Double</t>
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>1</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>시작 일반 쥐 +1마리</t>
+          <t>시작 일반 쥐 +3마리</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N20" s="1" t="n">
         <v>1</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>5층 보스 체력 -50%</t>
+          <t>보스에게 주는 피해 +10% · 보스 층 시간 +4초</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
@@ -2816,21 +2816,21 @@
       </c>
       <c r="L39" s="1" t="inlineStr">
         <is>
-          <t>Boss_Hp_Down</t>
+          <t>Boss_Dmg_Pct</t>
         </is>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O39" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_bosshp</t>
+          <t>SkillIcons/cs_bossd</t>
         </is>
       </c>
       <c r="Q39" s="1" t="inlineStr"/>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>시작 일반 쥐 +1마리</t>
+          <t>시작 일반 쥐 +3마리</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="M51" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N51" s="1" t="n">
         <v>1</v>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>시작 레어 쥐 +1마리</t>
+          <t>시작 레어 쥐 +2마리</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="M53" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N53" s="1" t="n">
         <v>2</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +8초</t>
+          <t>층 제한시간 +5초</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="M56" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N56" s="1" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>일반→레어 승급 필요 쥐 -1</t>
+          <t>일반→레어 승급 때 3% 확률로 2마리</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
@@ -3882,11 +3882,11 @@
       </c>
       <c r="L57" s="1" t="inlineStr">
         <is>
-          <t>Promote_Need</t>
+          <t>Promote_Double</t>
         </is>
       </c>
       <c r="M57" s="1" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="N57" s="1" t="n">
         <v>1</v>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>쥐 이동 속도 +10%</t>
+          <t>시작 일반 쥐 +4마리</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
@@ -3941,21 +3941,21 @@
       </c>
       <c r="L58" s="1" t="inlineStr">
         <is>
-          <t>Move_Speed_Pct</t>
+          <t>Start_Rat</t>
         </is>
       </c>
       <c r="M58" s="1" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_speed</t>
+          <t>SkillIcons/cs_startrat</t>
         </is>
       </c>
       <c r="Q58" s="1" t="inlineStr"/>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>10층 보스 체력 -30%</t>
+          <t>보스에게 주는 피해 +10% · 보스 층 시간 +4초</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
@@ -5062,21 +5062,21 @@
       </c>
       <c r="L77" s="1" t="inlineStr">
         <is>
-          <t>Boss_Hp_Down</t>
+          <t>Boss_Dmg_Pct</t>
         </is>
       </c>
       <c r="M77" s="1" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="N77" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O77" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_bosshp</t>
+          <t>SkillIcons/cs_bossd</t>
         </is>
       </c>
       <c r="Q77" s="1" t="inlineStr"/>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>콤보 유지 시간 +20%</t>
+          <t>총공격 쿨타임 -0.5초</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
@@ -5180,11 +5180,11 @@
       </c>
       <c r="L79" s="1" t="inlineStr">
         <is>
-          <t>Combo_Time_Pct</t>
+          <t>Rush_CD</t>
         </is>
       </c>
       <c r="M79" s="1" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="N79" s="1" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="P79" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_combo</t>
+          <t>SkillIcons/cs_rush</t>
         </is>
       </c>
       <c r="Q79" s="1" t="inlineStr"/>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>시작 레어 쥐 +1마리</t>
+          <t>시작 레어 쥐 +2마리</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="M89" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N89" s="1" t="n">
         <v>2</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +8초</t>
+          <t>층 제한시간 +6초</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="M90" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N90" s="1" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>시작 레어 쥐 +1마리</t>
+          <t>시작 레어 쥐 +2마리</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="M91" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N91" s="1" t="n">
         <v>2</v>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +10초</t>
+          <t>층 제한시간 +6초</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="M94" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N94" s="1" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>레어→에픽 승급 필요 쥐 -1</t>
+          <t>레어→에픽 승급 때 3% 확률로 2마리</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
@@ -6128,11 +6128,11 @@
       </c>
       <c r="L95" s="1" t="inlineStr">
         <is>
-          <t>Promote_Need</t>
+          <t>Promote_Double</t>
         </is>
       </c>
       <c r="M95" s="1" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="N95" s="1" t="n">
         <v>2</v>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>일반→레어 승급 필요 쥐 -1</t>
+          <t>일반→레어 승급 때 2% 확률로 2마리</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
@@ -6187,11 +6187,11 @@
       </c>
       <c r="L96" s="1" t="inlineStr">
         <is>
-          <t>Promote_Need</t>
+          <t>Promote_Double</t>
         </is>
       </c>
       <c r="M96" s="1" t="n">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="N96" s="1" t="n">
         <v>1</v>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>15층 보스 체력 -30%</t>
+          <t>보스에게 주는 피해 +15% · 보스 층 시간 +4초</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
@@ -7308,21 +7308,21 @@
       </c>
       <c r="L115" s="1" t="inlineStr">
         <is>
-          <t>Boss_Hp_Down</t>
+          <t>Boss_Dmg_Pct</t>
         </is>
       </c>
       <c r="M115" s="1" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="N115" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O115" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_bosshp</t>
+          <t>SkillIcons/cs_bossd</t>
         </is>
       </c>
       <c r="Q115" s="1" t="inlineStr"/>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>시작 에픽 쥐 +1마리</t>
+          <t>시작 에픽 쥐 +2마리</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="M127" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N127" s="1" t="n">
         <v>3</v>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +10초</t>
+          <t>층 제한시간 +7초</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="M128" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N128" s="1" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>시작 레어 쥐 +2마리</t>
+          <t>시작 레어 쥐 +3마리</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
@@ -8142,7 +8142,7 @@
         </is>
       </c>
       <c r="M129" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N129" s="1" t="n">
         <v>2</v>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +10초</t>
+          <t>층 제한시간 +7초</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
@@ -8319,7 +8319,7 @@
         </is>
       </c>
       <c r="M132" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N132" s="1" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>에픽→유니크 승급 필요 쥐 -1</t>
+          <t>에픽→유니크 승급 때 3% 확률로 2마리</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
@@ -8374,11 +8374,11 @@
       </c>
       <c r="L133" s="1" t="inlineStr">
         <is>
-          <t>Promote_Need</t>
+          <t>Promote_Double</t>
         </is>
       </c>
       <c r="M133" s="1" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="N133" s="1" t="n">
         <v>3</v>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>쥐 이동 속도 +10%</t>
+          <t>시작 일반 쥐 +6마리</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
@@ -8433,21 +8433,21 @@
       </c>
       <c r="L134" s="1" t="inlineStr">
         <is>
-          <t>Move_Speed_Pct</t>
+          <t>Start_Rat</t>
         </is>
       </c>
       <c r="M134" s="1" t="n">
-        <v>0.1</v>
+        <v>6</v>
       </c>
       <c r="N134" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O134" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_speed</t>
+          <t>SkillIcons/cs_startrat</t>
         </is>
       </c>
       <c r="Q134" s="1" t="inlineStr"/>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>필살기 게이지 충전 +20%</t>
+          <t>필살기 쿨타임 -3초</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
@@ -9436,11 +9436,11 @@
       </c>
       <c r="L151" s="1" t="inlineStr">
         <is>
-          <t>Ult_Gauge_Pct</t>
+          <t>Ult_CD</t>
         </is>
       </c>
       <c r="M151" s="1" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="N151" s="1" t="n">
         <v>0</v>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>20층 보스 체력 -25%</t>
+          <t>보스에게 주는 피해 +15% · 보스 층 시간 +4초</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
@@ -9554,21 +9554,21 @@
       </c>
       <c r="L153" s="1" t="inlineStr">
         <is>
-          <t>Boss_Hp_Down</t>
+          <t>Boss_Dmg_Pct</t>
         </is>
       </c>
       <c r="M153" s="1" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="N153" s="1" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="O153" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P153" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_bosshp</t>
+          <t>SkillIcons/cs_bossd</t>
         </is>
       </c>
       <c r="Q153" s="1" t="inlineStr"/>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>시작 에픽 쥐 +1마리</t>
+          <t>시작 에픽 쥐 +2마리</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
@@ -10270,7 +10270,7 @@
         </is>
       </c>
       <c r="M165" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N165" s="1" t="n">
         <v>3</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +12초</t>
+          <t>층 제한시간 +8초</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M166" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N166" s="1" t="n">
         <v>0</v>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +12초</t>
+          <t>층 제한시간 +8초</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
@@ -10565,7 +10565,7 @@
         </is>
       </c>
       <c r="M170" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N170" s="1" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
       </c>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t>유니크→전설 승급 필요 쥐 -1</t>
+          <t>유니크→전설 승급 때 3% 확률로 2마리</t>
         </is>
       </c>
       <c r="D171" s="1" t="inlineStr">
@@ -10620,11 +10620,11 @@
       </c>
       <c r="L171" s="1" t="inlineStr">
         <is>
-          <t>Promote_Need</t>
+          <t>Promote_Double</t>
         </is>
       </c>
       <c r="M171" s="1" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="N171" s="1" t="n">
         <v>4</v>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>25층 보스 체력 -25%</t>
+          <t>보스에게 주는 피해 +20% · 보스 층 시간 +4초</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr">
@@ -11800,21 +11800,21 @@
       </c>
       <c r="L191" s="1" t="inlineStr">
         <is>
-          <t>Boss_Hp_Down</t>
+          <t>Boss_Dmg_Pct</t>
         </is>
       </c>
       <c r="M191" s="1" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N191" s="1" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="O191" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P191" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_bosshp</t>
+          <t>SkillIcons/cs_bossd</t>
         </is>
       </c>
       <c r="Q191" s="1" t="inlineStr"/>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>벽 체력 -5%</t>
+          <t>총공격 쿨타임 -0.5초</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
@@ -11918,11 +11918,11 @@
       </c>
       <c r="L193" s="1" t="inlineStr">
         <is>
-          <t>Wall_Hp_Down</t>
+          <t>Rush_CD</t>
         </is>
       </c>
       <c r="M193" s="1" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="N193" s="1" t="n">
         <v>0</v>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="P193" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_wallcrack</t>
+          <t>SkillIcons/cs_rush</t>
         </is>
       </c>
       <c r="Q193" s="1" t="inlineStr"/>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>시작 유니크 쥐 +1마리</t>
+          <t>시작 유니크 쥐 +2마리</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
@@ -12516,7 +12516,7 @@
         </is>
       </c>
       <c r="M203" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N203" s="1" t="n">
         <v>4</v>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +15초</t>
+          <t>층 제한시간 +9초</t>
         </is>
       </c>
       <c r="D204" s="1" t="inlineStr">
@@ -12575,7 +12575,7 @@
         </is>
       </c>
       <c r="M204" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N204" s="1" t="n">
         <v>0</v>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>시작 에픽 쥐 +2마리</t>
+          <t>시작 에픽 쥐 +3마리</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="M205" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N205" s="1" t="n">
         <v>3</v>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +15초</t>
+          <t>층 제한시간 +9초</t>
         </is>
       </c>
       <c r="D208" s="1" t="inlineStr">
@@ -12811,7 +12811,7 @@
         </is>
       </c>
       <c r="M208" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N208" s="1" t="n">
         <v>0</v>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>전설→신화 승급 필요 쥐 -1</t>
+          <t>전설→신화 승급 때 3% 확률로 2마리</t>
         </is>
       </c>
       <c r="D209" s="1" t="inlineStr">
@@ -12866,11 +12866,11 @@
       </c>
       <c r="L209" s="1" t="inlineStr">
         <is>
-          <t>Promote_Need</t>
+          <t>Promote_Double</t>
         </is>
       </c>
       <c r="M209" s="1" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="N209" s="1" t="n">
         <v>5</v>
@@ -12894,7 +12894,7 @@
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>쥐 이동 속도 +10%</t>
+          <t>시작 레어 쥐 +6마리</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
@@ -12925,21 +12925,21 @@
       </c>
       <c r="L210" s="1" t="inlineStr">
         <is>
-          <t>Move_Speed_Pct</t>
+          <t>Start_Rat</t>
         </is>
       </c>
       <c r="M210" s="1" t="n">
-        <v>0.1</v>
+        <v>6</v>
       </c>
       <c r="N210" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O210" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P210" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_speed</t>
+          <t>SkillIcons/cs_startrat</t>
         </is>
       </c>
       <c r="Q210" s="1" t="inlineStr"/>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="C229" s="1" t="inlineStr">
         <is>
-          <t>30층 보스 체력 -25%</t>
+          <t>보스에게 주는 피해 +20% · 보스 층 시간 +4초</t>
         </is>
       </c>
       <c r="D229" s="1" t="inlineStr">
@@ -14046,21 +14046,21 @@
       </c>
       <c r="L229" s="1" t="inlineStr">
         <is>
-          <t>Boss_Hp_Down</t>
+          <t>Boss_Dmg_Pct</t>
         </is>
       </c>
       <c r="M229" s="1" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N229" s="1" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="O229" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P229" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_bosshp</t>
+          <t>SkillIcons/cs_bossd</t>
         </is>
       </c>
       <c r="Q229" s="1" t="inlineStr"/>
@@ -14133,7 +14133,7 @@
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t>필살기 게이지 충전 +20%</t>
+          <t>필살기 쿨타임 -3초</t>
         </is>
       </c>
       <c r="D231" s="1" t="inlineStr">
@@ -14164,11 +14164,11 @@
       </c>
       <c r="L231" s="1" t="inlineStr">
         <is>
-          <t>Ult_Gauge_Pct</t>
+          <t>Ult_CD</t>
         </is>
       </c>
       <c r="M231" s="1" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="N231" s="1" t="n">
         <v>0</v>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +15초</t>
+          <t>층 제한시간 +10초</t>
         </is>
       </c>
       <c r="D242" s="1" t="inlineStr">
@@ -14821,7 +14821,7 @@
         </is>
       </c>
       <c r="M242" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N242" s="1" t="n">
         <v>0</v>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t>시작 유니크 쥐 +1마리</t>
+          <t>시작 유니크 쥐 +2마리</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
@@ -14880,7 +14880,7 @@
         </is>
       </c>
       <c r="M243" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N243" s="1" t="n">
         <v>4</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +20초</t>
+          <t>층 제한시간 +10초</t>
         </is>
       </c>
       <c r="D246" s="1" t="inlineStr">
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="M246" s="1" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N246" s="1" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t>일반→레어 승급 필요 쥐 -1</t>
+          <t>승급 때 3% 확률로 2마리</t>
         </is>
       </c>
       <c r="D247" s="1" t="inlineStr">
@@ -15112,14 +15112,14 @@
       </c>
       <c r="L247" s="1" t="inlineStr">
         <is>
-          <t>Promote_Need</t>
+          <t>Promote_Double</t>
         </is>
       </c>
       <c r="M247" s="1" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="N247" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O247" s="1" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t>35층 보스 체력 -25%</t>
+          <t>보스에게 주는 피해 +25% · 보스 층 시간 +3초</t>
         </is>
       </c>
       <c r="D267" s="1" t="inlineStr">
@@ -16292,21 +16292,21 @@
       </c>
       <c r="L267" s="1" t="inlineStr">
         <is>
-          <t>Boss_Hp_Down</t>
+          <t>Boss_Dmg_Pct</t>
         </is>
       </c>
       <c r="M267" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="N267" s="1" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="O267" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P267" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_bosshp</t>
+          <t>SkillIcons/cs_bossd</t>
         </is>
       </c>
       <c r="Q267" s="1" t="inlineStr"/>
@@ -17032,7 +17032,7 @@
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +20초</t>
+          <t>층 제한시간 +11초</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr">
@@ -17067,7 +17067,7 @@
         </is>
       </c>
       <c r="M280" s="1" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="N280" s="1" t="n">
         <v>0</v>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t>시작 유니크 쥐 +2마리</t>
+          <t>시작 유니크 쥐 +3마리</t>
         </is>
       </c>
       <c r="D281" s="1" t="inlineStr">
@@ -17126,7 +17126,7 @@
         </is>
       </c>
       <c r="M281" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N281" s="1" t="n">
         <v>4</v>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +20초</t>
+          <t>층 제한시간 +12초</t>
         </is>
       </c>
       <c r="D284" s="1" t="inlineStr">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="M284" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="N284" s="1" t="n">
         <v>0</v>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t>레어→에픽 승급 필요 쥐 -1</t>
+          <t>승급 때 4% 확률로 2마리</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
@@ -17358,14 +17358,14 @@
       </c>
       <c r="L285" s="1" t="inlineStr">
         <is>
-          <t>Promote_Need</t>
+          <t>Promote_Double</t>
         </is>
       </c>
       <c r="M285" s="1" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="N285" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O285" s="1" t="n">
         <v>0</v>
@@ -18389,7 +18389,7 @@
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t>필살기 게이지 충전 +30%</t>
+          <t>필살기 쿨타임 -4초</t>
         </is>
       </c>
       <c r="D303" s="1" t="inlineStr">
@@ -18420,11 +18420,11 @@
       </c>
       <c r="L303" s="1" t="inlineStr">
         <is>
-          <t>Ult_Gauge_Pct</t>
+          <t>Ult_CD</t>
         </is>
       </c>
       <c r="M303" s="1" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="N303" s="1" t="n">
         <v>0</v>
@@ -18507,7 +18507,7 @@
       </c>
       <c r="C305" s="1" t="inlineStr">
         <is>
-          <t>40층 보스 체력 -25%</t>
+          <t>보스에게 주는 피해 +25% · 보스 층 시간 +3초</t>
         </is>
       </c>
       <c r="D305" s="1" t="inlineStr">
@@ -18538,21 +18538,21 @@
       </c>
       <c r="L305" s="1" t="inlineStr">
         <is>
-          <t>Boss_Hp_Down</t>
+          <t>Boss_Dmg_Pct</t>
         </is>
       </c>
       <c r="M305" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="N305" s="1" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="O305" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P305" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_bosshp</t>
+          <t>SkillIcons/cs_bossd</t>
         </is>
       </c>
       <c r="Q305" s="1" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
-          <t>슈퍼 점프 확률 +50%</t>
+          <t>총공격 쿨타임 -0.5초</t>
         </is>
       </c>
       <c r="D306" s="1" t="inlineStr">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="L306" s="1" t="inlineStr">
         <is>
-          <t>Super_Jump_Pct</t>
+          <t>Rush_CD</t>
         </is>
       </c>
       <c r="M306" s="1" t="n">
@@ -18611,7 +18611,7 @@
       </c>
       <c r="P306" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_sjump</t>
+          <t>SkillIcons/cs_rush</t>
         </is>
       </c>
       <c r="Q306" s="1" t="inlineStr"/>
@@ -18904,7 +18904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>보스에게 주는 피해 ×(1 + 합)</t>
+          <t>보스에게 주는 피해 ×(1 + 합) · 보스 층 제한시간 + 밸류_02 합 (초)</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -19229,7 +19229,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>보스 층 추가 시간 (초)</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -19268,22 +19268,22 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Promote_Need</t>
+          <t>Promote_Double</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>승급(같은 등급 N마리 → 윗등급 1마리)에 필요한 쥐 - 합 (최소 RatManager.promoteMin)</t>
+          <t>승급(같은 등급 N마리 → 윗등급 1마리) 때 확률 합으로 윗등급 쥐가 2마리 나옴. N = 올림(등급 테이블 promote_base × promote_grow^이번 판 승급 횟수)</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>줄어드는 수</t>
+          <t>확률</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>등급 (1 일반 ~ 5 전설)</t>
+          <t>승급하는 등급 (0 = 모든 승급, 1 일반 ~ 5 전설)</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 + 합 (초)</t>
+          <t>층 제한시간 + 합 (초). 기본 RunTimer.baseTime 180초 (모든 층 같음)</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -19862,22 +19862,22 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Boss_Hp_Down</t>
+          <t>Ult_Gauge_Pct</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>보스 체력 ×(1 - 합) (최소 0.3)</t>
+          <t>필살기 게이지 충전 ×(1 + 합)</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>감소율</t>
+          <t>증가율</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>보스 층 (0 = 모든 보스)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -19889,12 +19889,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Ult_Gauge_Pct</t>
+          <t>Ult_Power_Pct</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>필살기 게이지 충전 ×(1 + 합)</t>
+          <t>필살기 피해 ×(1 + 합)</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -19916,17 +19916,17 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Ult_Power_Pct</t>
+          <t>Ult_Auto</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>필살기 피해 ×(1 + 합)</t>
+          <t>필살기 자동 사용</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>증가율</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -19943,17 +19943,17 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Ult_Auto</t>
+          <t>Super_Jump_Pct</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>필살기 자동 사용</t>
+          <t>슈퍼 점프 확률 ×(1 + 합)</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>증가율</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
@@ -19970,76 +19970,76 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Super_Jump_Pct</t>
+          <t>Bite_Zap</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>슈퍼 점프 확률 ×(1 + 합)</t>
+          <t>물 때 확률 합으로 주변 물건 감전</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>증가율</t>
+          <t>확률</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>감전 개수 (가장 큰 값)</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>피해 배율 (가장 큰 값)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Bite_Zap</t>
+          <t>Chain_Blast</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>물 때 확률 합으로 주변 물건 감전</t>
+          <t>물건이 터질 때 연쇄 폭발 범위 + 합 · 피해 + 합</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>확률</t>
+          <t>범위</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>감전 개수 (가장 큰 값)</t>
+          <t>피해 증가</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>피해 배율 (가장 큰 값)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Chain_Blast</t>
+          <t>Cheese_Meteor</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>물건이 터질 때 연쇄 폭발 범위 + 합 · 피해 + 합</t>
+          <t>치즈 운석: 밸류_01 &gt; 0 인 노드가 있으면 켜짐 (간격 = 가장 작은 밸류_01). 위력 = 무리 평균 힘 × (1 + 밸류_02 합)</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>범위</t>
+          <t>간격 (초)</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>피해 증가</t>
+          <t>위력 증가</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -20051,22 +20051,22 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Cheese_Meteor</t>
+          <t>Twin_Chance</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>치즈 운석: 밸류_01 &gt; 0 인 노드가 있으면 켜짐 (간격 = 가장 작은 밸류_01). 위력 = 무리 평균 힘 × (1 + 밸류_02 합)</t>
+          <t>쌍둥이 확률 + 합</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>간격 (초)</t>
+          <t>확률</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>위력 증가</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -20078,17 +20078,17 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Twin_Chance</t>
+          <t>Mutation_Chance</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>쌍둥이 확률 + 합</t>
+          <t>탄생 등급 배율(티어 테이블 birth_grade_k) + 합</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>확률</t>
+          <t>배율 증가</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
@@ -20105,76 +20105,76 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Mutation_Chance</t>
+          <t>Birth_Frenzy</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>탄생 등급 배율(티어 테이블 birth_grade_k) + 합</t>
+          <t>탄생 축제: 새끼가 태어나면 주변 쥐 광란 (시간 합 · 반경·배율은 가장 큰 값)</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>배율 증가</t>
+          <t>시간 (초)</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>반경</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>배율</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Birth_Frenzy</t>
+          <t>Furniture_Pct</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>탄생 축제: 새끼가 태어나면 주변 쥐 광란 (시간 합 · 반경·배율은 가장 큰 값)</t>
+          <t>가구 피해 ×(1 + 밸류_01 합) · 가구 치즈 ×(1 + 밸류_02 합)</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>시간 (초)</t>
+          <t>피해 증가</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>반경</t>
+          <t>치즈 증가</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>배율</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Furniture_Pct</t>
+          <t>Air_Cheese_Pct</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>가구 피해 ×(1 + 밸류_01 합) · 가구 치즈 ×(1 + 밸류_02 합)</t>
+          <t>공중에서 부딪힌 물건 치즈 ×(1 + 합)</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>피해 증가</t>
+          <t>증가율</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>치즈 증가</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -20186,17 +20186,17 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Air_Cheese_Pct</t>
+          <t>Ult_CD</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>공중에서 부딪힌 물건 치즈 ×(1 + 합)</t>
+          <t>필살기 하나가 끝난 뒤 다음 필살기까지 쿨타임 - 합 (초, 기본 UltimateManager.ultCooldown, 최소 ultCooldownMin)</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>증가율</t>
+          <t>초</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -20213,12 +20213,12 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Rush_Up</t>
+          <t>Rush_CD</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>총공격 시간 + 밸류_01 합 · 배율 + 밸류_02 합</t>
+          <t>클릭 총공격 쿨타임 - 합 (초, 최소 RatManager.rushCooldownMin)</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>배율</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
@@ -20240,25 +20240,52 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
+          <t>Rush_Up</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>총공격 시간 + 밸류_01 합 · 배율 + 밸류_02 합</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>초</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>배율</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
           <t>Cat_Hp_Down</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
+      <c r="B51" s="1" t="inlineStr">
         <is>
           <t>고양이 체력 ×(1 - 밸류_01 합) · 쥐가 겁먹는 시간 ×(1 - 밸류_02 합)</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>감소율</t>
         </is>
       </c>
-      <c r="D50" s="1" t="inlineStr">
+      <c r="D51" s="1" t="inlineStr">
         <is>
           <t>감소율</t>
         </is>
       </c>
-      <c r="E50" s="1" t="inlineStr">
+      <c r="E51" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/Data_Table/공용 스킬 테이블.xlsx
+++ b/Data_Table/공용 스킬 테이블.xlsx
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>시작 일반 쥐 +2마리</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" s="1" t="n">
         <v>1</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>시작 일반 쥐 +2마리</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>1</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>시작 일반 쥐 +3마리</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N20" s="1" t="n">
         <v>1</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>시작 일반 쥐 +3마리</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="M51" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N51" s="1" t="n">
         <v>1</v>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>시작 레어 쥐 +2마리</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="M53" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N53" s="1" t="n">
         <v>2</v>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>시작 일반 쥐 +4마리</t>
+          <t>시작 쥐 +2마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="M58" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N58" s="1" t="n">
         <v>1</v>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>시작 레어 쥐 +2마리</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="M89" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N89" s="1" t="n">
         <v>2</v>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>시작 레어 쥐 +2마리</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="M91" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N91" s="1" t="n">
         <v>2</v>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>시작 에픽 쥐 +2마리</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="M127" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N127" s="1" t="n">
         <v>3</v>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>시작 레어 쥐 +3마리</t>
+          <t>시작 쥐 +2마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
@@ -8142,7 +8142,7 @@
         </is>
       </c>
       <c r="M129" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N129" s="1" t="n">
         <v>2</v>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>시작 일반 쥐 +6마리</t>
+          <t>시작 쥐 +3마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="M134" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N134" s="1" t="n">
         <v>1</v>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>시작 에픽 쥐 +2마리</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
@@ -10270,7 +10270,7 @@
         </is>
       </c>
       <c r="M165" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N165" s="1" t="n">
         <v>3</v>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>시작 유니크 쥐 +1마리</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>시작 유니크 쥐 +2마리</t>
+          <t>시작 쥐 +2마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>시작 에픽 쥐 +3마리</t>
+          <t>시작 쥐 +2마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="M205" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N205" s="1" t="n">
         <v>3</v>
@@ -12894,7 +12894,7 @@
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>시작 레어 쥐 +6마리</t>
+          <t>시작 쥐 +3마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="M210" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N210" s="1" t="n">
         <v>2</v>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="C241" s="1" t="inlineStr">
         <is>
-          <t>시작 전설 쥐 +1마리</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D241" s="1" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t>시작 유니크 쥐 +2마리</t>
+          <t>시작 쥐 +2마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t>시작 신화 쥐 +1마리</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D279" s="1" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t>시작 유니크 쥐 +3마리</t>
+          <t>시작 쥐 +2마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D281" s="1" t="inlineStr">
@@ -17126,7 +17126,7 @@
         </is>
       </c>
       <c r="M281" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N281" s="1" t="n">
         <v>4</v>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>판 시작 쥐 + 밸류_01 마리 (그 등급에서 해금된 종 하나씩)</t>
+          <t>판 시작 쥐 + 밸류_01 마리 (등급은 시작 쥐처럼 지금 훈장의 등급 확률로 뽑음)</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -19256,7 +19256,7 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>등급 (1 일반 ~ 6 신화)</t>
+          <t>안 씀 (예전 등급 칸)</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">

--- a/Data_Table/공용 스킬 테이블.xlsx
+++ b/Data_Table/공용 스킬 테이블.xlsx
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
+          <t>번식 확률 +5%</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -1400,21 +1400,21 @@
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
-          <t>Start_Rat</t>
+          <t>Breed_Chance</t>
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_startrat</t>
+          <t>SkillIcons/cs_breed</t>
         </is>
       </c>
       <c r="Q15" s="1" t="inlineStr"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
+          <t>번식 확률 +5%</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -1695,21 +1695,21 @@
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>Start_Rat</t>
+          <t>Breed_Chance</t>
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_startrat</t>
+          <t>SkillIcons/cs_breed</t>
         </is>
       </c>
       <c r="Q20" s="1" t="inlineStr"/>
@@ -3653,7 +3653,7 @@
         <v>1</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O53" s="1" t="n">
         <v>0</v>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>시작 쥐 +2마리 (등급은 훈장 확률)</t>
+          <t>번식 확률 +5%</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
@@ -3941,21 +3941,21 @@
       </c>
       <c r="L58" s="1" t="inlineStr">
         <is>
-          <t>Start_Rat</t>
+          <t>Breed_Chance</t>
         </is>
       </c>
       <c r="M58" s="1" t="n">
-        <v>2</v>
+        <v>0.05</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_startrat</t>
+          <t>SkillIcons/cs_breed</t>
         </is>
       </c>
       <c r="Q58" s="1" t="inlineStr"/>
@@ -5781,7 +5781,7 @@
         <v>1</v>
       </c>
       <c r="N89" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O89" s="1" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
+          <t>번식 확률 +5%</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
@@ -5892,21 +5892,21 @@
       </c>
       <c r="L91" s="1" t="inlineStr">
         <is>
-          <t>Start_Rat</t>
+          <t>Breed_Chance</t>
         </is>
       </c>
       <c r="M91" s="1" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="N91" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O91" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_startrat</t>
+          <t>SkillIcons/cs_breed</t>
         </is>
       </c>
       <c r="Q91" s="1" t="inlineStr"/>
@@ -8027,7 +8027,7 @@
         <v>1</v>
       </c>
       <c r="N127" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O127" s="1" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>시작 쥐 +2마리 (등급은 훈장 확률)</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="M129" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N129" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O129" s="1" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>시작 쥐 +3마리 (등급은 훈장 확률)</t>
+          <t>번식 확률 +5%</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
@@ -8433,21 +8433,21 @@
       </c>
       <c r="L134" s="1" t="inlineStr">
         <is>
-          <t>Start_Rat</t>
+          <t>Breed_Chance</t>
         </is>
       </c>
       <c r="M134" s="1" t="n">
-        <v>3</v>
+        <v>0.05</v>
       </c>
       <c r="N134" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O134" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_startrat</t>
+          <t>SkillIcons/cs_breed</t>
         </is>
       </c>
       <c r="Q134" s="1" t="inlineStr"/>
@@ -10273,7 +10273,7 @@
         <v>1</v>
       </c>
       <c r="N165" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O165" s="1" t="n">
         <v>0</v>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
+          <t>번식 확률 +5%</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
@@ -10384,21 +10384,21 @@
       </c>
       <c r="L167" s="1" t="inlineStr">
         <is>
-          <t>Start_Rat</t>
+          <t>Breed_Chance</t>
         </is>
       </c>
       <c r="M167" s="1" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="N167" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O167" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P167" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_startrat</t>
+          <t>SkillIcons/cs_breed</t>
         </is>
       </c>
       <c r="Q167" s="1" t="inlineStr"/>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>시작 쥐 +2마리 (등급은 훈장 확률)</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="M203" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N203" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O203" s="1" t="n">
         <v>0</v>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>시작 쥐 +2마리 (등급은 훈장 확률)</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
@@ -12634,10 +12634,10 @@
         </is>
       </c>
       <c r="M205" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N205" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O205" s="1" t="n">
         <v>0</v>
@@ -12894,7 +12894,7 @@
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>시작 쥐 +3마리 (등급은 훈장 확률)</t>
+          <t>번식 확률 +5%</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
@@ -12925,21 +12925,21 @@
       </c>
       <c r="L210" s="1" t="inlineStr">
         <is>
-          <t>Start_Rat</t>
+          <t>Breed_Chance</t>
         </is>
       </c>
       <c r="M210" s="1" t="n">
-        <v>3</v>
+        <v>0.05</v>
       </c>
       <c r="N210" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O210" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P210" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_startrat</t>
+          <t>SkillIcons/cs_breed</t>
         </is>
       </c>
       <c r="Q210" s="1" t="inlineStr"/>
@@ -14765,7 +14765,7 @@
         <v>1</v>
       </c>
       <c r="N241" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O241" s="1" t="n">
         <v>0</v>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t>시작 쥐 +2마리 (등급은 훈장 확률)</t>
+          <t>번식 확률 +5%</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
@@ -14876,21 +14876,21 @@
       </c>
       <c r="L243" s="1" t="inlineStr">
         <is>
-          <t>Start_Rat</t>
+          <t>Breed_Chance</t>
         </is>
       </c>
       <c r="M243" s="1" t="n">
-        <v>2</v>
+        <v>0.05</v>
       </c>
       <c r="N243" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O243" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P243" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_startrat</t>
+          <t>SkillIcons/cs_breed</t>
         </is>
       </c>
       <c r="Q243" s="1" t="inlineStr"/>
@@ -17011,7 +17011,7 @@
         <v>1</v>
       </c>
       <c r="N279" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O279" s="1" t="n">
         <v>0</v>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t>시작 쥐 +2마리 (등급은 훈장 확률)</t>
+          <t>시작 쥐 +1마리 (등급은 훈장 확률)</t>
         </is>
       </c>
       <c r="D281" s="1" t="inlineStr">
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="M281" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N281" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O281" s="1" t="n">
         <v>0</v>

--- a/Data_Table/공용 스킬 테이블.xlsx
+++ b/Data_Table/공용 스킬 테이블.xlsx
@@ -11179,7 +11179,7 @@
       </c>
       <c r="C181" s="1" t="inlineStr">
         <is>
-          <t>모든 묘기 확률 +1%</t>
+          <t>묘기 해금: 쳇바퀴 돌기</t>
         </is>
       </c>
       <c r="D181" s="1" t="inlineStr">
@@ -11188,7 +11188,7 @@
         </is>
       </c>
       <c r="E181" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" s="1" t="n">
         <v>0</v>
@@ -11203,28 +11203,28 @@
         <v>0</v>
       </c>
       <c r="J181" s="1" t="n">
-        <v>800000</v>
+        <v>1200000</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L181" s="1" t="inlineStr">
         <is>
-          <t>Trick_Chance</t>
+          <t>Trick_Unlock</t>
         </is>
       </c>
       <c r="M181" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N181" s="1" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O181" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P181" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_flip</t>
+          <t>SkillIcons/cs_wheelspin</t>
         </is>
       </c>
       <c r="Q181" s="1" t="inlineStr"/>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>모든 묘기 확률 +1%</t>
+          <t>쳇바퀴 돌기 확률 +2%</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
@@ -13814,17 +13814,17 @@
         </is>
       </c>
       <c r="M225" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N225" s="1" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O225" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P225" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_flip</t>
+          <t>SkillIcons/cs_wheelspin</t>
         </is>
       </c>
       <c r="Q225" s="1" t="inlineStr"/>
@@ -18035,7 +18035,7 @@
       </c>
       <c r="C297" s="1" t="inlineStr">
         <is>
-          <t>모든 묘기 확률 +1%</t>
+          <t>쳇바퀴 돌기 확률 +2%</t>
         </is>
       </c>
       <c r="D297" s="1" t="inlineStr">
@@ -18070,17 +18070,17 @@
         </is>
       </c>
       <c r="M297" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N297" s="1" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O297" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P297" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_flip</t>
+          <t>SkillIcons/cs_wheelspin</t>
         </is>
       </c>
       <c r="Q297" s="1" t="inlineStr"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>묘기 (1 백덤블링 · 2 윈드밀 · 3 트리플 악셀 · 4 쥐 대포알)</t>
+          <t>묘기 (1 백덤블링 · 2 윈드밀 · 3 트리플 악셀 · 4 쥐 대포알 · 5 쳇바퀴 돌기)</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">

--- a/Data_Table/공용 스킬 테이블.xlsx
+++ b/Data_Table/공용 스킬 테이블.xlsx
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>130</v>
+        <v>680</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>130</v>
+        <v>680</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>0</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>130</v>
+        <v>680</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>0</v>
@@ -1275,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>0</v>
@@ -1570,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>130</v>
+        <v>680</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>180</v>
+        <v>990</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>0</v>
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>130</v>
+        <v>680</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>0</v>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>0</v>
@@ -1924,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>130</v>
+        <v>680</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>190</v>
+        <v>1100</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>0</v>
@@ -2101,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>130</v>
+        <v>680</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>270</v>
+        <v>1500</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>60</v>
+        <v>340</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>0</v>
@@ -2337,7 +2337,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>0</v>
@@ -2396,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="K32" s="1" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>130</v>
+        <v>680</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>130</v>
+        <v>680</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>180</v>
+        <v>990</v>
       </c>
       <c r="K35" s="1" t="n">
         <v>0</v>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +1층</t>
+          <t>스테이지 스킵 +2층</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>87</v>
+        <v>490</v>
       </c>
       <c r="K36" s="1" t="n">
         <v>0</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N36" s="1" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +1층</t>
+          <t>총공격 범위 +15%</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>3</v>
@@ -2750,18 +2750,18 @@
         <v>0</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>190</v>
+        <v>680</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="1" t="inlineStr">
         <is>
-          <t>Stage_Skip</t>
+          <t>Rush_Range</t>
         </is>
       </c>
       <c r="M38" s="1" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="N38" s="1" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P38" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_skip</t>
+          <t>SkillIcons/cs_rush</t>
         </is>
       </c>
       <c r="Q38" s="1" t="inlineStr"/>
@@ -2809,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="K39" s="1" t="n">
         <v>0</v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>180</v>
+        <v>990</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>0</v>
@@ -2927,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>130</v>
+        <v>680</v>
       </c>
       <c r="K41" s="1" t="n">
         <v>0</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>500</v>
+        <v>2600</v>
       </c>
       <c r="K43" s="1" t="n">
         <v>1</v>
@@ -3108,10 +3108,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>730</v>
+        <v>2600</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="1" t="inlineStr">
         <is>
@@ -3167,10 +3167,10 @@
         <v>0</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>1600</v>
+        <v>7700</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L45" s="1" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>1100</v>
+        <v>5100</v>
       </c>
       <c r="K46" s="1" t="n">
         <v>2</v>
@@ -3285,10 +3285,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>1600</v>
+        <v>5100</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L47" s="1" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>1100</v>
+        <v>5100</v>
       </c>
       <c r="K48" s="1" t="n">
         <v>2</v>
@@ -3403,10 +3403,10 @@
         <v>0</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>1600</v>
+        <v>5100</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L49" s="1" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         <v>0</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>1600</v>
+        <v>5100</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L50" s="1" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>500</v>
+        <v>2600</v>
       </c>
       <c r="K51" s="1" t="n">
         <v>1</v>
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>730</v>
+        <v>2600</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L52" s="1" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>1100</v>
+        <v>5100</v>
       </c>
       <c r="K53" s="1" t="n">
         <v>2</v>
@@ -3698,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>1100</v>
+        <v>5100</v>
       </c>
       <c r="K54" s="1" t="n">
         <v>2</v>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>1100</v>
+        <v>5100</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>2</v>
@@ -3816,10 +3816,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>1600</v>
+        <v>5100</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L56" s="1" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>2300</v>
+        <v>7700</v>
       </c>
       <c r="K57" s="1" t="n">
         <v>3</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>1600</v>
+        <v>5100</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L58" s="1" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>500</v>
+        <v>2600</v>
       </c>
       <c r="K59" s="1" t="n">
         <v>1</v>
@@ -4052,10 +4052,10 @@
         <v>0</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>730</v>
+        <v>2600</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" s="1" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>1100</v>
+        <v>5100</v>
       </c>
       <c r="K61" s="1" t="n">
         <v>2</v>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>1100</v>
+        <v>5100</v>
       </c>
       <c r="K62" s="1" t="n">
         <v>2</v>
@@ -4229,10 +4229,10 @@
         <v>0</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>1600</v>
+        <v>5100</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L63" s="1" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
         <v>0</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>2300</v>
+        <v>11000</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L64" s="1" t="inlineStr">
         <is>
@@ -4347,10 +4347,10 @@
         <v>0</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>1600</v>
+        <v>5100</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L65" s="1" t="inlineStr">
         <is>
@@ -4406,10 +4406,10 @@
         <v>0</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>3400</v>
+        <v>13000</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L66" s="1" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>750</v>
+        <v>5100</v>
       </c>
       <c r="K67" s="1" t="n">
         <v>2</v>
@@ -4524,10 +4524,10 @@
         <v>0</v>
       </c>
       <c r="J68" s="1" t="n">
-        <v>730</v>
+        <v>2600</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L68" s="1" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="1" t="n">
-        <v>1100</v>
+        <v>5100</v>
       </c>
       <c r="K69" s="1" t="n">
         <v>2</v>
@@ -4642,7 +4642,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="1" t="n">
-        <v>1100</v>
+        <v>5100</v>
       </c>
       <c r="K70" s="1" t="n">
         <v>2</v>
@@ -4701,10 +4701,10 @@
         <v>0</v>
       </c>
       <c r="J71" s="1" t="n">
-        <v>1600</v>
+        <v>5100</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L71" s="1" t="inlineStr">
         <is>
@@ -4760,10 +4760,10 @@
         <v>0</v>
       </c>
       <c r="J72" s="1" t="n">
-        <v>1600</v>
+        <v>5100</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L72" s="1" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="1" t="n">
-        <v>2300</v>
+        <v>7700</v>
       </c>
       <c r="K73" s="1" t="n">
         <v>3</v>
@@ -4878,10 +4878,10 @@
         <v>0</v>
       </c>
       <c r="J74" s="1" t="n">
-        <v>1100</v>
+        <v>5100</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L74" s="1" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="1" t="n">
-        <v>1100</v>
+        <v>5100</v>
       </c>
       <c r="K75" s="1" t="n">
         <v>2</v>
@@ -4996,10 +4996,10 @@
         <v>0</v>
       </c>
       <c r="J76" s="1" t="n">
-        <v>2300</v>
+        <v>11000</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L76" s="1" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="J77" s="1" t="n">
-        <v>1100</v>
+        <v>5100</v>
       </c>
       <c r="K77" s="1" t="n">
         <v>2</v>
@@ -5114,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="J78" s="1" t="n">
-        <v>2300</v>
+        <v>7700</v>
       </c>
       <c r="K78" s="1" t="n">
         <v>3</v>
@@ -5173,10 +5173,10 @@
         <v>0</v>
       </c>
       <c r="J79" s="1" t="n">
-        <v>1600</v>
+        <v>5100</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L79" s="1" t="inlineStr">
         <is>
@@ -5295,10 +5295,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="1" t="n">
-        <v>6000</v>
+        <v>26000</v>
       </c>
       <c r="K81" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L81" s="1" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="1" t="n">
-        <v>8700</v>
+        <v>26000</v>
       </c>
       <c r="K82" s="1" t="n">
         <v>4</v>
@@ -5413,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="1" t="n">
-        <v>19000</v>
+        <v>70000</v>
       </c>
       <c r="K83" s="1" t="n">
         <v>11</v>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="1" t="n">
-        <v>13000</v>
+        <v>39000</v>
       </c>
       <c r="K84" s="1" t="n">
         <v>6</v>
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="1" t="n">
-        <v>19000</v>
+        <v>45000</v>
       </c>
       <c r="K85" s="1" t="n">
         <v>7</v>
@@ -5590,7 +5590,7 @@
         <v>0</v>
       </c>
       <c r="J86" s="1" t="n">
-        <v>13000</v>
+        <v>39000</v>
       </c>
       <c r="K86" s="1" t="n">
         <v>6</v>
@@ -5649,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="1" t="n">
-        <v>19000</v>
+        <v>45000</v>
       </c>
       <c r="K87" s="1" t="n">
         <v>7</v>
@@ -5708,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="1" t="n">
-        <v>19000</v>
+        <v>45000</v>
       </c>
       <c r="K88" s="1" t="n">
         <v>7</v>
@@ -5767,10 +5767,10 @@
         <v>0</v>
       </c>
       <c r="J89" s="1" t="n">
-        <v>6000</v>
+        <v>26000</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L89" s="1" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="J90" s="1" t="n">
-        <v>8700</v>
+        <v>26000</v>
       </c>
       <c r="K90" s="1" t="n">
         <v>4</v>
@@ -5885,7 +5885,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="1" t="n">
-        <v>13000</v>
+        <v>39000</v>
       </c>
       <c r="K91" s="1" t="n">
         <v>6</v>
@@ -5944,7 +5944,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="1" t="n">
-        <v>13000</v>
+        <v>39000</v>
       </c>
       <c r="K92" s="1" t="n">
         <v>6</v>
@@ -6003,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="1" t="n">
-        <v>13000</v>
+        <v>39000</v>
       </c>
       <c r="K93" s="1" t="n">
         <v>6</v>
@@ -6062,7 +6062,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="1" t="n">
-        <v>19000</v>
+        <v>45000</v>
       </c>
       <c r="K94" s="1" t="n">
         <v>7</v>
@@ -6121,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="1" t="n">
-        <v>27000</v>
+        <v>58000</v>
       </c>
       <c r="K95" s="1" t="n">
         <v>9</v>
@@ -6180,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="1" t="n">
-        <v>19000</v>
+        <v>45000</v>
       </c>
       <c r="K96" s="1" t="n">
         <v>7</v>
@@ -6239,10 +6239,10 @@
         <v>0</v>
       </c>
       <c r="J97" s="1" t="n">
-        <v>6000</v>
+        <v>26000</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L97" s="1" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="1" t="n">
-        <v>8700</v>
+        <v>26000</v>
       </c>
       <c r="K98" s="1" t="n">
         <v>4</v>
@@ -6357,7 +6357,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="1" t="n">
-        <v>13000</v>
+        <v>39000</v>
       </c>
       <c r="K99" s="1" t="n">
         <v>6</v>
@@ -6416,7 +6416,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="1" t="n">
-        <v>13000</v>
+        <v>39000</v>
       </c>
       <c r="K100" s="1" t="n">
         <v>6</v>
@@ -6475,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="1" t="n">
-        <v>19000</v>
+        <v>45000</v>
       </c>
       <c r="K101" s="1" t="n">
         <v>7</v>
@@ -6534,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="1" t="n">
-        <v>28000</v>
+        <v>89000</v>
       </c>
       <c r="K102" s="1" t="n">
         <v>14</v>
@@ -6593,7 +6593,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="1" t="n">
-        <v>19000</v>
+        <v>45000</v>
       </c>
       <c r="K103" s="1" t="n">
         <v>7</v>
@@ -6652,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="1" t="n">
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="K104" s="1" t="n">
         <v>18</v>
@@ -6711,10 +6711,10 @@
         <v>0</v>
       </c>
       <c r="J105" s="1" t="n">
-        <v>9000</v>
+        <v>45000</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L105" s="1" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>0</v>
       </c>
       <c r="J106" s="1" t="n">
-        <v>8700</v>
+        <v>26000</v>
       </c>
       <c r="K106" s="1" t="n">
         <v>4</v>
@@ -6829,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="J107" s="1" t="n">
-        <v>13000</v>
+        <v>39000</v>
       </c>
       <c r="K107" s="1" t="n">
         <v>6</v>
@@ -6888,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="J108" s="1" t="n">
-        <v>13000</v>
+        <v>39000</v>
       </c>
       <c r="K108" s="1" t="n">
         <v>6</v>
@@ -6947,7 +6947,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="1" t="n">
-        <v>19000</v>
+        <v>45000</v>
       </c>
       <c r="K109" s="1" t="n">
         <v>7</v>
@@ -7006,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="1" t="n">
-        <v>19000</v>
+        <v>45000</v>
       </c>
       <c r="K110" s="1" t="n">
         <v>7</v>
@@ -7065,7 +7065,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="1" t="n">
-        <v>27000</v>
+        <v>58000</v>
       </c>
       <c r="K111" s="1" t="n">
         <v>9</v>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="1" t="n">
-        <v>14000</v>
+        <v>51000</v>
       </c>
       <c r="K112" s="1" t="n">
         <v>8</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="M112" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N112" s="1" t="n">
         <v>0</v>
@@ -7183,7 +7183,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="1" t="n">
-        <v>19000</v>
+        <v>70000</v>
       </c>
       <c r="K113" s="1" t="n">
         <v>11</v>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +1층</t>
+          <t>총공격 범위 +15%</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr">
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="E114" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" s="1" t="n">
         <v>3</v>
@@ -7242,18 +7242,18 @@
         <v>0</v>
       </c>
       <c r="J114" s="1" t="n">
-        <v>28000</v>
+        <v>45000</v>
       </c>
       <c r="K114" s="1" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L114" s="1" t="inlineStr">
         <is>
-          <t>Stage_Skip</t>
+          <t>Rush_Range</t>
         </is>
       </c>
       <c r="M114" s="1" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="N114" s="1" t="n">
         <v>0</v>
@@ -7263,7 +7263,7 @@
       </c>
       <c r="P114" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_skip</t>
+          <t>SkillIcons/cs_rush</t>
         </is>
       </c>
       <c r="Q114" s="1" t="inlineStr"/>
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="1" t="n">
-        <v>13000</v>
+        <v>39000</v>
       </c>
       <c r="K115" s="1" t="n">
         <v>6</v>
@@ -7360,7 +7360,7 @@
         <v>0</v>
       </c>
       <c r="J116" s="1" t="n">
-        <v>27000</v>
+        <v>58000</v>
       </c>
       <c r="K116" s="1" t="n">
         <v>9</v>
@@ -7419,7 +7419,7 @@
         <v>0</v>
       </c>
       <c r="J117" s="1" t="n">
-        <v>19000</v>
+        <v>45000</v>
       </c>
       <c r="K117" s="1" t="n">
         <v>7</v>
@@ -7541,10 +7541,10 @@
         <v>0</v>
       </c>
       <c r="J119" s="1" t="n">
-        <v>70000</v>
+        <v>170000</v>
       </c>
       <c r="K119" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L119" s="1" t="inlineStr">
         <is>
@@ -7600,10 +7600,10 @@
         <v>0</v>
       </c>
       <c r="J120" s="1" t="n">
-        <v>110000</v>
+        <v>230000</v>
       </c>
       <c r="K120" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L120" s="1" t="inlineStr">
         <is>
@@ -7659,10 +7659,10 @@
         <v>0</v>
       </c>
       <c r="J121" s="1" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L121" s="1" t="inlineStr">
         <is>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="J122" s="1" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L122" s="1" t="inlineStr">
         <is>
@@ -7777,10 +7777,10 @@
         <v>0</v>
       </c>
       <c r="J123" s="1" t="n">
-        <v>220000</v>
+        <v>350000</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L123" s="1" t="inlineStr">
         <is>
@@ -7836,10 +7836,10 @@
         <v>0</v>
       </c>
       <c r="J124" s="1" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L124" s="1" t="inlineStr">
         <is>
@@ -7895,10 +7895,10 @@
         <v>0</v>
       </c>
       <c r="J125" s="1" t="n">
-        <v>220000</v>
+        <v>350000</v>
       </c>
       <c r="K125" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L125" s="1" t="inlineStr">
         <is>
@@ -7954,10 +7954,10 @@
         <v>0</v>
       </c>
       <c r="J126" s="1" t="n">
-        <v>220000</v>
+        <v>350000</v>
       </c>
       <c r="K126" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L126" s="1" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         <v>0</v>
       </c>
       <c r="J127" s="1" t="n">
-        <v>70000</v>
+        <v>170000</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L127" s="1" t="inlineStr">
         <is>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="J128" s="1" t="n">
-        <v>110000</v>
+        <v>230000</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L128" s="1" t="inlineStr">
         <is>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="J129" s="1" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L129" s="1" t="inlineStr">
         <is>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="J130" s="1" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K130" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L130" s="1" t="inlineStr">
         <is>
@@ -8249,10 +8249,10 @@
         <v>0</v>
       </c>
       <c r="J131" s="1" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K131" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L131" s="1" t="inlineStr">
         <is>
@@ -8308,10 +8308,10 @@
         <v>0</v>
       </c>
       <c r="J132" s="1" t="n">
-        <v>220000</v>
+        <v>350000</v>
       </c>
       <c r="K132" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L132" s="1" t="inlineStr">
         <is>
@@ -8367,10 +8367,10 @@
         <v>0</v>
       </c>
       <c r="J133" s="1" t="n">
-        <v>310000</v>
+        <v>470000</v>
       </c>
       <c r="K133" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L133" s="1" t="inlineStr">
         <is>
@@ -8426,10 +8426,10 @@
         <v>0</v>
       </c>
       <c r="J134" s="1" t="n">
-        <v>220000</v>
+        <v>350000</v>
       </c>
       <c r="K134" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L134" s="1" t="inlineStr">
         <is>
@@ -8485,10 +8485,10 @@
         <v>0</v>
       </c>
       <c r="J135" s="1" t="n">
-        <v>70000</v>
+        <v>170000</v>
       </c>
       <c r="K135" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L135" s="1" t="inlineStr">
         <is>
@@ -8544,10 +8544,10 @@
         <v>0</v>
       </c>
       <c r="J136" s="1" t="n">
-        <v>110000</v>
+        <v>230000</v>
       </c>
       <c r="K136" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L136" s="1" t="inlineStr">
         <is>
@@ -8603,10 +8603,10 @@
         <v>0</v>
       </c>
       <c r="J137" s="1" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L137" s="1" t="inlineStr">
         <is>
@@ -8662,10 +8662,10 @@
         <v>0</v>
       </c>
       <c r="J138" s="1" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L138" s="1" t="inlineStr">
         <is>
@@ -8721,10 +8721,10 @@
         <v>0</v>
       </c>
       <c r="J139" s="1" t="n">
-        <v>220000</v>
+        <v>350000</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L139" s="1" t="inlineStr">
         <is>
@@ -8780,10 +8780,10 @@
         <v>0</v>
       </c>
       <c r="J140" s="1" t="n">
-        <v>330000</v>
+        <v>700000</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L140" s="1" t="inlineStr">
         <is>
@@ -8839,10 +8839,10 @@
         <v>0</v>
       </c>
       <c r="J141" s="1" t="n">
-        <v>220000</v>
+        <v>350000</v>
       </c>
       <c r="K141" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L141" s="1" t="inlineStr">
         <is>
@@ -8898,10 +8898,10 @@
         <v>0</v>
       </c>
       <c r="J142" s="1" t="n">
-        <v>470000</v>
+        <v>920000</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L142" s="1" t="inlineStr">
         <is>
@@ -8957,10 +8957,10 @@
         <v>0</v>
       </c>
       <c r="J143" s="1" t="n">
-        <v>110000</v>
+        <v>330000</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L143" s="1" t="inlineStr">
         <is>
@@ -9016,10 +9016,10 @@
         <v>0</v>
       </c>
       <c r="J144" s="1" t="n">
-        <v>110000</v>
+        <v>230000</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L144" s="1" t="inlineStr">
         <is>
@@ -9075,10 +9075,10 @@
         <v>0</v>
       </c>
       <c r="J145" s="1" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L145" s="1" t="inlineStr">
         <is>
@@ -9134,10 +9134,10 @@
         <v>0</v>
       </c>
       <c r="J146" s="1" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L146" s="1" t="inlineStr">
         <is>
@@ -9193,10 +9193,10 @@
         <v>0</v>
       </c>
       <c r="J147" s="1" t="n">
-        <v>220000</v>
+        <v>350000</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L147" s="1" t="inlineStr">
         <is>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="J148" s="1" t="n">
-        <v>220000</v>
+        <v>350000</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L148" s="1" t="inlineStr">
         <is>
@@ -9311,10 +9311,10 @@
         <v>0</v>
       </c>
       <c r="J149" s="1" t="n">
-        <v>310000</v>
+        <v>470000</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L149" s="1" t="inlineStr">
         <is>
@@ -9370,10 +9370,10 @@
         <v>0</v>
       </c>
       <c r="J150" s="1" t="n">
-        <v>160000</v>
+        <v>430000</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L150" s="1" t="inlineStr">
         <is>
@@ -9429,10 +9429,10 @@
         <v>0</v>
       </c>
       <c r="J151" s="1" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L151" s="1" t="inlineStr">
         <is>
@@ -9488,10 +9488,10 @@
         <v>0</v>
       </c>
       <c r="J152" s="1" t="n">
-        <v>330000</v>
+        <v>700000</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L152" s="1" t="inlineStr">
         <is>
@@ -9547,10 +9547,10 @@
         <v>0</v>
       </c>
       <c r="J153" s="1" t="n">
-        <v>150000</v>
+        <v>290000</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L153" s="1" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         <v>0</v>
       </c>
       <c r="J154" s="1" t="n">
-        <v>310000</v>
+        <v>470000</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L154" s="1" t="inlineStr">
         <is>
@@ -9665,10 +9665,10 @@
         <v>0</v>
       </c>
       <c r="J155" s="1" t="n">
-        <v>220000</v>
+        <v>350000</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L155" s="1" t="inlineStr">
         <is>
@@ -9787,10 +9787,10 @@
         <v>0</v>
       </c>
       <c r="J157" s="1" t="n">
-        <v>800000</v>
+        <v>1400000</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L157" s="1" t="inlineStr">
         <is>
@@ -9846,10 +9846,10 @@
         <v>0</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>1200000</v>
+        <v>1800000</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L158" s="1" t="inlineStr">
         <is>
@@ -9905,10 +9905,10 @@
         <v>0</v>
       </c>
       <c r="J159" s="1" t="n">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L159" s="1" t="inlineStr">
         <is>
@@ -9964,10 +9964,10 @@
         <v>0</v>
       </c>
       <c r="J160" s="1" t="n">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L160" s="1" t="inlineStr">
         <is>
@@ -10023,10 +10023,10 @@
         <v>0</v>
       </c>
       <c r="J161" s="1" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L161" s="1" t="inlineStr">
         <is>
@@ -10082,10 +10082,10 @@
         <v>0</v>
       </c>
       <c r="J162" s="1" t="n">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L162" s="1" t="inlineStr">
         <is>
@@ -10141,10 +10141,10 @@
         <v>0</v>
       </c>
       <c r="J163" s="1" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L163" s="1" t="inlineStr">
         <is>
@@ -10200,10 +10200,10 @@
         <v>0</v>
       </c>
       <c r="J164" s="1" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L164" s="1" t="inlineStr">
         <is>
@@ -10259,10 +10259,10 @@
         <v>0</v>
       </c>
       <c r="J165" s="1" t="n">
-        <v>800000</v>
+        <v>1400000</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L165" s="1" t="inlineStr">
         <is>
@@ -10318,10 +10318,10 @@
         <v>0</v>
       </c>
       <c r="J166" s="1" t="n">
-        <v>1200000</v>
+        <v>1800000</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L166" s="1" t="inlineStr">
         <is>
@@ -10377,10 +10377,10 @@
         <v>0</v>
       </c>
       <c r="J167" s="1" t="n">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L167" s="1" t="inlineStr">
         <is>
@@ -10436,10 +10436,10 @@
         <v>0</v>
       </c>
       <c r="J168" s="1" t="n">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L168" s="1" t="inlineStr">
         <is>
@@ -10495,10 +10495,10 @@
         <v>0</v>
       </c>
       <c r="J169" s="1" t="n">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L169" s="1" t="inlineStr">
         <is>
@@ -10554,10 +10554,10 @@
         <v>0</v>
       </c>
       <c r="J170" s="1" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="K170" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L170" s="1" t="inlineStr">
         <is>
@@ -10613,10 +10613,10 @@
         <v>0</v>
       </c>
       <c r="J171" s="1" t="n">
-        <v>3600000</v>
+        <v>3800000</v>
       </c>
       <c r="K171" s="1" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L171" s="1" t="inlineStr">
         <is>
@@ -10672,10 +10672,10 @@
         <v>0</v>
       </c>
       <c r="J172" s="1" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L172" s="1" t="inlineStr">
         <is>
@@ -10731,10 +10731,10 @@
         <v>0</v>
       </c>
       <c r="J173" s="1" t="n">
-        <v>800000</v>
+        <v>1400000</v>
       </c>
       <c r="K173" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L173" s="1" t="inlineStr">
         <is>
@@ -10790,10 +10790,10 @@
         <v>0</v>
       </c>
       <c r="J174" s="1" t="n">
-        <v>1200000</v>
+        <v>1800000</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L174" s="1" t="inlineStr">
         <is>
@@ -10849,10 +10849,10 @@
         <v>0</v>
       </c>
       <c r="J175" s="1" t="n">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L175" s="1" t="inlineStr">
         <is>
@@ -10908,10 +10908,10 @@
         <v>0</v>
       </c>
       <c r="J176" s="1" t="n">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L176" s="1" t="inlineStr">
         <is>
@@ -10967,10 +10967,10 @@
         <v>0</v>
       </c>
       <c r="J177" s="1" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="K177" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L177" s="1" t="inlineStr">
         <is>
@@ -11026,10 +11026,10 @@
         <v>0</v>
       </c>
       <c r="J178" s="1" t="n">
-        <v>3700000</v>
+        <v>5800000</v>
       </c>
       <c r="K178" s="1" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="L178" s="1" t="inlineStr">
         <is>
@@ -11085,10 +11085,10 @@
         <v>0</v>
       </c>
       <c r="J179" s="1" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="K179" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L179" s="1" t="inlineStr">
         <is>
@@ -11144,10 +11144,10 @@
         <v>0</v>
       </c>
       <c r="J180" s="1" t="n">
-        <v>5400000</v>
+        <v>7500000</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L180" s="1" t="inlineStr">
         <is>
@@ -11203,10 +11203,10 @@
         <v>0</v>
       </c>
       <c r="J181" s="1" t="n">
-        <v>1200000</v>
+        <v>2700000</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L181" s="1" t="inlineStr">
         <is>
@@ -11262,10 +11262,10 @@
         <v>0</v>
       </c>
       <c r="J182" s="1" t="n">
-        <v>1200000</v>
+        <v>1800000</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L182" s="1" t="inlineStr">
         <is>
@@ -11321,10 +11321,10 @@
         <v>0</v>
       </c>
       <c r="J183" s="1" t="n">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L183" s="1" t="inlineStr">
         <is>
@@ -11380,10 +11380,10 @@
         <v>0</v>
       </c>
       <c r="J184" s="1" t="n">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L184" s="1" t="inlineStr">
         <is>
@@ -11439,10 +11439,10 @@
         <v>0</v>
       </c>
       <c r="J185" s="1" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L185" s="1" t="inlineStr">
         <is>
@@ -11498,10 +11498,10 @@
         <v>0</v>
       </c>
       <c r="J186" s="1" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L186" s="1" t="inlineStr">
         <is>
@@ -11557,10 +11557,10 @@
         <v>0</v>
       </c>
       <c r="J187" s="1" t="n">
-        <v>3600000</v>
+        <v>3800000</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L187" s="1" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D188" s="1" t="inlineStr">
@@ -11616,10 +11616,10 @@
         <v>0</v>
       </c>
       <c r="J188" s="1" t="n">
-        <v>1800000</v>
+        <v>3500000</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L188" s="1" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         </is>
       </c>
       <c r="M188" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N188" s="1" t="n">
         <v>0</v>
@@ -11675,10 +11675,10 @@
         <v>0</v>
       </c>
       <c r="J189" s="1" t="n">
-        <v>2600000</v>
+        <v>4500000</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L189" s="1" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +1층</t>
+          <t>총공격 범위 +20%</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="E190" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F190" s="1" t="n">
         <v>3</v>
@@ -11734,18 +11734,18 @@
         <v>0</v>
       </c>
       <c r="J190" s="1" t="n">
-        <v>3700000</v>
+        <v>3000000</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="L190" s="1" t="inlineStr">
         <is>
-          <t>Stage_Skip</t>
+          <t>Rush_Range</t>
         </is>
       </c>
       <c r="M190" s="1" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="N190" s="1" t="n">
         <v>0</v>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="P190" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_skip</t>
+          <t>SkillIcons/cs_rush</t>
         </is>
       </c>
       <c r="Q190" s="1" t="inlineStr"/>
@@ -11793,10 +11793,10 @@
         <v>0</v>
       </c>
       <c r="J191" s="1" t="n">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L191" s="1" t="inlineStr">
         <is>
@@ -11852,10 +11852,10 @@
         <v>0</v>
       </c>
       <c r="J192" s="1" t="n">
-        <v>3600000</v>
+        <v>3800000</v>
       </c>
       <c r="K192" s="1" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L192" s="1" t="inlineStr">
         <is>
@@ -11911,10 +11911,10 @@
         <v>0</v>
       </c>
       <c r="J193" s="1" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L193" s="1" t="inlineStr">
         <is>
@@ -12033,10 +12033,10 @@
         <v>0</v>
       </c>
       <c r="J195" s="1" t="n">
-        <v>9000000</v>
+        <v>13000000</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L195" s="1" t="inlineStr">
         <is>
@@ -12092,10 +12092,10 @@
         <v>0</v>
       </c>
       <c r="J196" s="1" t="n">
-        <v>14000000</v>
+        <v>17000000</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="L196" s="1" t="inlineStr">
         <is>
@@ -12151,10 +12151,10 @@
         <v>0</v>
       </c>
       <c r="J197" s="1" t="n">
-        <v>19000000</v>
+        <v>22000000</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L197" s="1" t="inlineStr">
         <is>
@@ -12210,10 +12210,10 @@
         <v>0</v>
       </c>
       <c r="J198" s="1" t="n">
-        <v>19000000</v>
+        <v>22000000</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L198" s="1" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>28000000</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="L199" s="1" t="inlineStr">
         <is>
@@ -12328,10 +12328,10 @@
         <v>0</v>
       </c>
       <c r="J200" s="1" t="n">
-        <v>19000000</v>
+        <v>22000000</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L200" s="1" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>28000000</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="L201" s="1" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>28000000</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="L202" s="1" t="inlineStr">
         <is>
@@ -12505,10 +12505,10 @@
         <v>0</v>
       </c>
       <c r="J203" s="1" t="n">
-        <v>9000000</v>
+        <v>13000000</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L203" s="1" t="inlineStr">
         <is>
@@ -12564,10 +12564,10 @@
         <v>0</v>
       </c>
       <c r="J204" s="1" t="n">
-        <v>14000000</v>
+        <v>17000000</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="L204" s="1" t="inlineStr">
         <is>
@@ -12623,10 +12623,10 @@
         <v>0</v>
       </c>
       <c r="J205" s="1" t="n">
-        <v>19000000</v>
+        <v>22000000</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L205" s="1" t="inlineStr">
         <is>
@@ -12682,10 +12682,10 @@
         <v>0</v>
       </c>
       <c r="J206" s="1" t="n">
-        <v>19000000</v>
+        <v>22000000</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L206" s="1" t="inlineStr">
         <is>
@@ -12741,10 +12741,10 @@
         <v>0</v>
       </c>
       <c r="J207" s="1" t="n">
-        <v>19000000</v>
+        <v>22000000</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L207" s="1" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>28000000</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="L208" s="1" t="inlineStr">
         <is>
@@ -12859,10 +12859,10 @@
         <v>0</v>
       </c>
       <c r="J209" s="1" t="n">
-        <v>40000000</v>
+        <v>37000000</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="L209" s="1" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>28000000</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="L210" s="1" t="inlineStr">
         <is>
@@ -12977,10 +12977,10 @@
         <v>0</v>
       </c>
       <c r="J211" s="1" t="n">
-        <v>9000000</v>
+        <v>13000000</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L211" s="1" t="inlineStr">
         <is>
@@ -13036,10 +13036,10 @@
         <v>0</v>
       </c>
       <c r="J212" s="1" t="n">
-        <v>14000000</v>
+        <v>17000000</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="L212" s="1" t="inlineStr">
         <is>
@@ -13095,10 +13095,10 @@
         <v>0</v>
       </c>
       <c r="J213" s="1" t="n">
-        <v>19000000</v>
+        <v>22000000</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L213" s="1" t="inlineStr">
         <is>
@@ -13154,10 +13154,10 @@
         <v>0</v>
       </c>
       <c r="J214" s="1" t="n">
-        <v>19000000</v>
+        <v>22000000</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L214" s="1" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>28000000</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="L215" s="1" t="inlineStr">
         <is>
@@ -13272,10 +13272,10 @@
         <v>0</v>
       </c>
       <c r="J216" s="1" t="n">
-        <v>42000000</v>
+        <v>56000000</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L216" s="1" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>28000000</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="L217" s="1" t="inlineStr">
         <is>
@@ -13390,10 +13390,10 @@
         <v>0</v>
       </c>
       <c r="J218" s="1" t="n">
-        <v>60000000</v>
+        <v>72000000</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="L218" s="1" t="inlineStr">
         <is>
@@ -13449,10 +13449,10 @@
         <v>0</v>
       </c>
       <c r="J219" s="1" t="n">
-        <v>9000000</v>
+        <v>13000000</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L219" s="1" t="inlineStr">
         <is>
@@ -13508,10 +13508,10 @@
         <v>0</v>
       </c>
       <c r="J220" s="1" t="n">
-        <v>14000000</v>
+        <v>17000000</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="L220" s="1" t="inlineStr">
         <is>
@@ -13567,10 +13567,10 @@
         <v>0</v>
       </c>
       <c r="J221" s="1" t="n">
-        <v>19000000</v>
+        <v>22000000</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L221" s="1" t="inlineStr">
         <is>
@@ -13626,10 +13626,10 @@
         <v>0</v>
       </c>
       <c r="J222" s="1" t="n">
-        <v>19000000</v>
+        <v>22000000</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L222" s="1" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>28000000</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="L223" s="1" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>28000000</v>
       </c>
       <c r="K224" s="1" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="L224" s="1" t="inlineStr">
         <is>
@@ -13803,10 +13803,10 @@
         <v>0</v>
       </c>
       <c r="J225" s="1" t="n">
-        <v>40000000</v>
+        <v>37000000</v>
       </c>
       <c r="K225" s="1" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="L225" s="1" t="inlineStr">
         <is>
@@ -13862,10 +13862,10 @@
         <v>0</v>
       </c>
       <c r="J226" s="1" t="n">
-        <v>20000000</v>
+        <v>33000000</v>
       </c>
       <c r="K226" s="1" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="L226" s="1" t="inlineStr">
         <is>
@@ -13921,10 +13921,10 @@
         <v>0</v>
       </c>
       <c r="J227" s="1" t="n">
-        <v>29000000</v>
+        <v>43000000</v>
       </c>
       <c r="K227" s="1" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="L227" s="1" t="inlineStr">
         <is>
@@ -13980,10 +13980,10 @@
         <v>0</v>
       </c>
       <c r="J228" s="1" t="n">
-        <v>42000000</v>
+        <v>56000000</v>
       </c>
       <c r="K228" s="1" t="n">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L228" s="1" t="inlineStr">
         <is>
@@ -14039,10 +14039,10 @@
         <v>0</v>
       </c>
       <c r="J229" s="1" t="n">
-        <v>19000000</v>
+        <v>22000000</v>
       </c>
       <c r="K229" s="1" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L229" s="1" t="inlineStr">
         <is>
@@ -14098,10 +14098,10 @@
         <v>0</v>
       </c>
       <c r="J230" s="1" t="n">
-        <v>40000000</v>
+        <v>37000000</v>
       </c>
       <c r="K230" s="1" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="L230" s="1" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>28000000</v>
       </c>
       <c r="K231" s="1" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="L231" s="1" t="inlineStr">
         <is>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="J233" s="1" t="n">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="K233" s="1" t="n">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="L233" s="1" t="inlineStr">
         <is>
@@ -14338,10 +14338,10 @@
         <v>0</v>
       </c>
       <c r="J234" s="1" t="n">
-        <v>150000000</v>
+        <v>260000000</v>
       </c>
       <c r="K234" s="1" t="n">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="L234" s="1" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         <v>0</v>
       </c>
       <c r="J235" s="1" t="n">
-        <v>220000000</v>
+        <v>340000000</v>
       </c>
       <c r="K235" s="1" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L235" s="1" t="inlineStr">
         <is>
@@ -14456,10 +14456,10 @@
         <v>0</v>
       </c>
       <c r="J236" s="1" t="n">
-        <v>220000000</v>
+        <v>340000000</v>
       </c>
       <c r="K236" s="1" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L236" s="1" t="inlineStr">
         <is>
@@ -14515,10 +14515,10 @@
         <v>0</v>
       </c>
       <c r="J237" s="1" t="n">
-        <v>310000000</v>
+        <v>440000000</v>
       </c>
       <c r="K237" s="1" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="L237" s="1" t="inlineStr">
         <is>
@@ -14574,10 +14574,10 @@
         <v>0</v>
       </c>
       <c r="J238" s="1" t="n">
-        <v>220000000</v>
+        <v>340000000</v>
       </c>
       <c r="K238" s="1" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L238" s="1" t="inlineStr">
         <is>
@@ -14633,10 +14633,10 @@
         <v>0</v>
       </c>
       <c r="J239" s="1" t="n">
-        <v>310000000</v>
+        <v>440000000</v>
       </c>
       <c r="K239" s="1" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="L239" s="1" t="inlineStr">
         <is>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="J240" s="1" t="n">
-        <v>310000000</v>
+        <v>440000000</v>
       </c>
       <c r="K240" s="1" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="L240" s="1" t="inlineStr">
         <is>
@@ -14751,10 +14751,10 @@
         <v>0</v>
       </c>
       <c r="J241" s="1" t="n">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="K241" s="1" t="n">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="L241" s="1" t="inlineStr">
         <is>
@@ -14810,10 +14810,10 @@
         <v>0</v>
       </c>
       <c r="J242" s="1" t="n">
-        <v>150000000</v>
+        <v>260000000</v>
       </c>
       <c r="K242" s="1" t="n">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="L242" s="1" t="inlineStr">
         <is>
@@ -14869,10 +14869,10 @@
         <v>0</v>
       </c>
       <c r="J243" s="1" t="n">
-        <v>220000000</v>
+        <v>340000000</v>
       </c>
       <c r="K243" s="1" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L243" s="1" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>0</v>
       </c>
       <c r="J244" s="1" t="n">
-        <v>220000000</v>
+        <v>340000000</v>
       </c>
       <c r="K244" s="1" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L244" s="1" t="inlineStr">
         <is>
@@ -14987,10 +14987,10 @@
         <v>0</v>
       </c>
       <c r="J245" s="1" t="n">
-        <v>220000000</v>
+        <v>340000000</v>
       </c>
       <c r="K245" s="1" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L245" s="1" t="inlineStr">
         <is>
@@ -15046,10 +15046,10 @@
         <v>0</v>
       </c>
       <c r="J246" s="1" t="n">
-        <v>310000000</v>
+        <v>440000000</v>
       </c>
       <c r="K246" s="1" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="L246" s="1" t="inlineStr">
         <is>
@@ -15105,10 +15105,10 @@
         <v>0</v>
       </c>
       <c r="J247" s="1" t="n">
-        <v>450000000</v>
+        <v>570000000</v>
       </c>
       <c r="K247" s="1" t="n">
-        <v>143</v>
+        <v>295</v>
       </c>
       <c r="L247" s="1" t="inlineStr">
         <is>
@@ -15164,10 +15164,10 @@
         <v>0</v>
       </c>
       <c r="J248" s="1" t="n">
-        <v>310000000</v>
+        <v>440000000</v>
       </c>
       <c r="K248" s="1" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="L248" s="1" t="inlineStr">
         <is>
@@ -15223,10 +15223,10 @@
         <v>0</v>
       </c>
       <c r="J249" s="1" t="n">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="K249" s="1" t="n">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="L249" s="1" t="inlineStr">
         <is>
@@ -15282,10 +15282,10 @@
         <v>0</v>
       </c>
       <c r="J250" s="1" t="n">
-        <v>150000000</v>
+        <v>260000000</v>
       </c>
       <c r="K250" s="1" t="n">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="L250" s="1" t="inlineStr">
         <is>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="J251" s="1" t="n">
-        <v>220000000</v>
+        <v>340000000</v>
       </c>
       <c r="K251" s="1" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L251" s="1" t="inlineStr">
         <is>
@@ -15400,10 +15400,10 @@
         <v>0</v>
       </c>
       <c r="J252" s="1" t="n">
-        <v>220000000</v>
+        <v>340000000</v>
       </c>
       <c r="K252" s="1" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L252" s="1" t="inlineStr">
         <is>
@@ -15459,10 +15459,10 @@
         <v>0</v>
       </c>
       <c r="J253" s="1" t="n">
-        <v>310000000</v>
+        <v>440000000</v>
       </c>
       <c r="K253" s="1" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="L253" s="1" t="inlineStr">
         <is>
@@ -15518,10 +15518,10 @@
         <v>0</v>
       </c>
       <c r="J254" s="1" t="n">
-        <v>310000000</v>
+        <v>440000000</v>
       </c>
       <c r="K254" s="1" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="L254" s="1" t="inlineStr">
         <is>
@@ -15577,10 +15577,10 @@
         <v>0</v>
       </c>
       <c r="J255" s="1" t="n">
-        <v>310000000</v>
+        <v>440000000</v>
       </c>
       <c r="K255" s="1" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="L255" s="1" t="inlineStr">
         <is>
@@ -15636,10 +15636,10 @@
         <v>0</v>
       </c>
       <c r="J256" s="1" t="n">
-        <v>670000000</v>
+        <v>1200000000</v>
       </c>
       <c r="K256" s="1" t="n">
-        <v>286</v>
+        <v>589</v>
       </c>
       <c r="L256" s="1" t="inlineStr">
         <is>
@@ -15695,10 +15695,10 @@
         <v>0</v>
       </c>
       <c r="J257" s="1" t="n">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="K257" s="1" t="n">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="L257" s="1" t="inlineStr">
         <is>
@@ -15754,10 +15754,10 @@
         <v>0</v>
       </c>
       <c r="J258" s="1" t="n">
-        <v>150000000</v>
+        <v>260000000</v>
       </c>
       <c r="K258" s="1" t="n">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="L258" s="1" t="inlineStr">
         <is>
@@ -15813,10 +15813,10 @@
         <v>0</v>
       </c>
       <c r="J259" s="1" t="n">
-        <v>220000000</v>
+        <v>340000000</v>
       </c>
       <c r="K259" s="1" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L259" s="1" t="inlineStr">
         <is>
@@ -15872,10 +15872,10 @@
         <v>0</v>
       </c>
       <c r="J260" s="1" t="n">
-        <v>220000000</v>
+        <v>340000000</v>
       </c>
       <c r="K260" s="1" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L260" s="1" t="inlineStr">
         <is>
@@ -15931,10 +15931,10 @@
         <v>0</v>
       </c>
       <c r="J261" s="1" t="n">
-        <v>310000000</v>
+        <v>440000000</v>
       </c>
       <c r="K261" s="1" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="L261" s="1" t="inlineStr">
         <is>
@@ -15990,10 +15990,10 @@
         <v>0</v>
       </c>
       <c r="J262" s="1" t="n">
-        <v>310000000</v>
+        <v>440000000</v>
       </c>
       <c r="K262" s="1" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="L262" s="1" t="inlineStr">
         <is>
@@ -16049,10 +16049,10 @@
         <v>0</v>
       </c>
       <c r="J263" s="1" t="n">
-        <v>450000000</v>
+        <v>570000000</v>
       </c>
       <c r="K263" s="1" t="n">
-        <v>143</v>
+        <v>295</v>
       </c>
       <c r="L263" s="1" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
       </c>
       <c r="C264" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +4층</t>
         </is>
       </c>
       <c r="D264" s="1" t="inlineStr">
@@ -16108,10 +16108,10 @@
         <v>0</v>
       </c>
       <c r="J264" s="1" t="n">
-        <v>220000000</v>
+        <v>520000000</v>
       </c>
       <c r="K264" s="1" t="n">
-        <v>130</v>
+        <v>268</v>
       </c>
       <c r="L264" s="1" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         </is>
       </c>
       <c r="M264" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N264" s="1" t="n">
         <v>0</v>
@@ -16167,10 +16167,10 @@
         <v>0</v>
       </c>
       <c r="J265" s="1" t="n">
-        <v>220000000</v>
+        <v>340000000</v>
       </c>
       <c r="K265" s="1" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L265" s="1" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="C266" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>총공격 범위 +20%</t>
         </is>
       </c>
       <c r="D266" s="1" t="inlineStr">
@@ -16211,7 +16211,7 @@
         </is>
       </c>
       <c r="E266" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F266" s="1" t="n">
         <v>3</v>
@@ -16226,18 +16226,18 @@
         <v>0</v>
       </c>
       <c r="J266" s="1" t="n">
-        <v>460000000</v>
+        <v>440000000</v>
       </c>
       <c r="K266" s="1" t="n">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="L266" s="1" t="inlineStr">
         <is>
-          <t>Stage_Skip</t>
+          <t>Rush_Range</t>
         </is>
       </c>
       <c r="M266" s="1" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="N266" s="1" t="n">
         <v>0</v>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="P266" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_skip</t>
+          <t>SkillIcons/cs_rush</t>
         </is>
       </c>
       <c r="Q266" s="1" t="inlineStr"/>
@@ -16285,10 +16285,10 @@
         <v>0</v>
       </c>
       <c r="J267" s="1" t="n">
-        <v>220000000</v>
+        <v>340000000</v>
       </c>
       <c r="K267" s="1" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="L267" s="1" t="inlineStr">
         <is>
@@ -16344,10 +16344,10 @@
         <v>0</v>
       </c>
       <c r="J268" s="1" t="n">
-        <v>450000000</v>
+        <v>570000000</v>
       </c>
       <c r="K268" s="1" t="n">
-        <v>143</v>
+        <v>295</v>
       </c>
       <c r="L268" s="1" t="inlineStr">
         <is>
@@ -16403,10 +16403,10 @@
         <v>0</v>
       </c>
       <c r="J269" s="1" t="n">
-        <v>310000000</v>
+        <v>440000000</v>
       </c>
       <c r="K269" s="1" t="n">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="L269" s="1" t="inlineStr">
         <is>
@@ -16525,10 +16525,10 @@
         <v>0</v>
       </c>
       <c r="J271" s="1" t="n">
-        <v>1100000000</v>
+        <v>1400000000</v>
       </c>
       <c r="K271" s="1" t="n">
-        <v>100</v>
+        <v>859</v>
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
@@ -16584,10 +16584,10 @@
         <v>0</v>
       </c>
       <c r="J272" s="1" t="n">
-        <v>1600000000</v>
+        <v>1800000000</v>
       </c>
       <c r="K272" s="1" t="n">
-        <v>130</v>
+        <v>1117</v>
       </c>
       <c r="L272" s="1" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>2400000000</v>
       </c>
       <c r="K273" s="1" t="n">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>2400000000</v>
       </c>
       <c r="K274" s="1" t="n">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
@@ -16761,10 +16761,10 @@
         <v>0</v>
       </c>
       <c r="J275" s="1" t="n">
-        <v>3400000000</v>
+        <v>3100000000</v>
       </c>
       <c r="K275" s="1" t="n">
-        <v>220</v>
+        <v>1887</v>
       </c>
       <c r="L275" s="1" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>2400000000</v>
       </c>
       <c r="K276" s="1" t="n">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="L276" s="1" t="inlineStr">
         <is>
@@ -16879,10 +16879,10 @@
         <v>0</v>
       </c>
       <c r="J277" s="1" t="n">
-        <v>3400000000</v>
+        <v>3100000000</v>
       </c>
       <c r="K277" s="1" t="n">
-        <v>220</v>
+        <v>1887</v>
       </c>
       <c r="L277" s="1" t="inlineStr">
         <is>
@@ -16938,10 +16938,10 @@
         <v>0</v>
       </c>
       <c r="J278" s="1" t="n">
-        <v>3400000000</v>
+        <v>3100000000</v>
       </c>
       <c r="K278" s="1" t="n">
-        <v>220</v>
+        <v>1887</v>
       </c>
       <c r="L278" s="1" t="inlineStr">
         <is>
@@ -16997,10 +16997,10 @@
         <v>0</v>
       </c>
       <c r="J279" s="1" t="n">
-        <v>1100000000</v>
+        <v>1400000000</v>
       </c>
       <c r="K279" s="1" t="n">
-        <v>100</v>
+        <v>859</v>
       </c>
       <c r="L279" s="1" t="inlineStr">
         <is>
@@ -17056,10 +17056,10 @@
         <v>0</v>
       </c>
       <c r="J280" s="1" t="n">
-        <v>1600000000</v>
+        <v>1800000000</v>
       </c>
       <c r="K280" s="1" t="n">
-        <v>130</v>
+        <v>1117</v>
       </c>
       <c r="L280" s="1" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>2400000000</v>
       </c>
       <c r="K281" s="1" t="n">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="L281" s="1" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>2400000000</v>
       </c>
       <c r="K282" s="1" t="n">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="L282" s="1" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>2400000000</v>
       </c>
       <c r="K283" s="1" t="n">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="L283" s="1" t="inlineStr">
         <is>
@@ -17292,10 +17292,10 @@
         <v>0</v>
       </c>
       <c r="J284" s="1" t="n">
-        <v>3400000000</v>
+        <v>3100000000</v>
       </c>
       <c r="K284" s="1" t="n">
-        <v>220</v>
+        <v>1887</v>
       </c>
       <c r="L284" s="1" t="inlineStr">
         <is>
@@ -17351,10 +17351,10 @@
         <v>0</v>
       </c>
       <c r="J285" s="1" t="n">
-        <v>4900000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K285" s="1" t="n">
-        <v>286</v>
+        <v>2453</v>
       </c>
       <c r="L285" s="1" t="inlineStr">
         <is>
@@ -17410,10 +17410,10 @@
         <v>0</v>
       </c>
       <c r="J286" s="1" t="n">
-        <v>3400000000</v>
+        <v>3100000000</v>
       </c>
       <c r="K286" s="1" t="n">
-        <v>220</v>
+        <v>1887</v>
       </c>
       <c r="L286" s="1" t="inlineStr">
         <is>
@@ -17469,10 +17469,10 @@
         <v>0</v>
       </c>
       <c r="J287" s="1" t="n">
-        <v>1100000000</v>
+        <v>1400000000</v>
       </c>
       <c r="K287" s="1" t="n">
-        <v>100</v>
+        <v>859</v>
       </c>
       <c r="L287" s="1" t="inlineStr">
         <is>
@@ -17528,10 +17528,10 @@
         <v>0</v>
       </c>
       <c r="J288" s="1" t="n">
-        <v>1600000000</v>
+        <v>1800000000</v>
       </c>
       <c r="K288" s="1" t="n">
-        <v>130</v>
+        <v>1117</v>
       </c>
       <c r="L288" s="1" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>2400000000</v>
       </c>
       <c r="K289" s="1" t="n">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="L289" s="1" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>2400000000</v>
       </c>
       <c r="K290" s="1" t="n">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="L290" s="1" t="inlineStr">
         <is>
@@ -17705,10 +17705,10 @@
         <v>0</v>
       </c>
       <c r="J291" s="1" t="n">
-        <v>3400000000</v>
+        <v>3100000000</v>
       </c>
       <c r="K291" s="1" t="n">
-        <v>220</v>
+        <v>1887</v>
       </c>
       <c r="L291" s="1" t="inlineStr">
         <is>
@@ -17764,10 +17764,10 @@
         <v>0</v>
       </c>
       <c r="J292" s="1" t="n">
-        <v>3400000000</v>
+        <v>3100000000</v>
       </c>
       <c r="K292" s="1" t="n">
-        <v>220</v>
+        <v>1887</v>
       </c>
       <c r="L292" s="1" t="inlineStr">
         <is>
@@ -17823,10 +17823,10 @@
         <v>0</v>
       </c>
       <c r="J293" s="1" t="n">
-        <v>3400000000</v>
+        <v>3100000000</v>
       </c>
       <c r="K293" s="1" t="n">
-        <v>220</v>
+        <v>1887</v>
       </c>
       <c r="L293" s="1" t="inlineStr">
         <is>
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="J294" s="1" t="n">
-        <v>7300000000</v>
+        <v>7900000000</v>
       </c>
       <c r="K294" s="1" t="n">
-        <v>572</v>
+        <v>4906</v>
       </c>
       <c r="L294" s="1" t="inlineStr">
         <is>
@@ -17941,10 +17941,10 @@
         <v>0</v>
       </c>
       <c r="J295" s="1" t="n">
-        <v>1100000000</v>
+        <v>1400000000</v>
       </c>
       <c r="K295" s="1" t="n">
-        <v>100</v>
+        <v>859</v>
       </c>
       <c r="L295" s="1" t="inlineStr">
         <is>
@@ -18000,10 +18000,10 @@
         <v>0</v>
       </c>
       <c r="J296" s="1" t="n">
-        <v>1600000000</v>
+        <v>1800000000</v>
       </c>
       <c r="K296" s="1" t="n">
-        <v>130</v>
+        <v>1117</v>
       </c>
       <c r="L296" s="1" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>2400000000</v>
       </c>
       <c r="K297" s="1" t="n">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="L297" s="1" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>2400000000</v>
       </c>
       <c r="K298" s="1" t="n">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="L298" s="1" t="inlineStr">
         <is>
@@ -18177,10 +18177,10 @@
         <v>0</v>
       </c>
       <c r="J299" s="1" t="n">
-        <v>3400000000</v>
+        <v>3100000000</v>
       </c>
       <c r="K299" s="1" t="n">
-        <v>220</v>
+        <v>1887</v>
       </c>
       <c r="L299" s="1" t="inlineStr">
         <is>
@@ -18236,10 +18236,10 @@
         <v>0</v>
       </c>
       <c r="J300" s="1" t="n">
-        <v>3400000000</v>
+        <v>3100000000</v>
       </c>
       <c r="K300" s="1" t="n">
-        <v>220</v>
+        <v>1887</v>
       </c>
       <c r="L300" s="1" t="inlineStr">
         <is>
@@ -18295,10 +18295,10 @@
         <v>0</v>
       </c>
       <c r="J301" s="1" t="n">
-        <v>4900000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K301" s="1" t="n">
-        <v>286</v>
+        <v>2453</v>
       </c>
       <c r="L301" s="1" t="inlineStr">
         <is>
@@ -18354,10 +18354,10 @@
         <v>0</v>
       </c>
       <c r="J302" s="1" t="n">
-        <v>2400000000</v>
+        <v>3600000000</v>
       </c>
       <c r="K302" s="1" t="n">
-        <v>260</v>
+        <v>2233</v>
       </c>
       <c r="L302" s="1" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>2400000000</v>
       </c>
       <c r="K303" s="1" t="n">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="L303" s="1" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         <v>0</v>
       </c>
       <c r="J304" s="1" t="n">
-        <v>5100000000</v>
+        <v>6100000000</v>
       </c>
       <c r="K304" s="1" t="n">
-        <v>440</v>
+        <v>3774</v>
       </c>
       <c r="L304" s="1" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>2400000000</v>
       </c>
       <c r="K305" s="1" t="n">
-        <v>170</v>
+        <v>1452</v>
       </c>
       <c r="L305" s="1" t="inlineStr">
         <is>
@@ -18590,10 +18590,10 @@
         <v>0</v>
       </c>
       <c r="J306" s="1" t="n">
-        <v>4900000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K306" s="1" t="n">
-        <v>286</v>
+        <v>2453</v>
       </c>
       <c r="L306" s="1" t="inlineStr">
         <is>
@@ -18649,10 +18649,10 @@
         <v>0</v>
       </c>
       <c r="J307" s="1" t="n">
-        <v>3400000000</v>
+        <v>3100000000</v>
       </c>
       <c r="K307" s="1" t="n">
-        <v>220</v>
+        <v>1887</v>
       </c>
       <c r="L307" s="1" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20240,22 +20240,22 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Rush_Up</t>
+          <t>Rush_Range</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>총공격 시간 + 밸류_01 합 · 배율 + 밸류_02 합</t>
+          <t>클릭 총공격에 모이는 범위: 화면 밖으로 화면 크기 × 합 만큼 더 (그 안의 쥐도 돌진)</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>초</t>
+          <t>비율</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>배율</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -20267,25 +20267,52 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
+          <t>Rush_Up</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>총공격 시간 + 밸류_01 합 · 배율 + 밸류_02 합</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>초</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>배율</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
           <t>Cat_Hp_Down</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
+      <c r="B52" s="1" t="inlineStr">
         <is>
           <t>고양이 체력 ×(1 - 밸류_01 합) · 쥐가 겁먹는 시간 ×(1 - 밸류_02 합)</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>감소율</t>
         </is>
       </c>
-      <c r="D51" s="1" t="inlineStr">
+      <c r="D52" s="1" t="inlineStr">
         <is>
           <t>감소율</t>
         </is>
       </c>
-      <c r="E51" s="1" t="inlineStr">
+      <c r="E52" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/Data_Table/공용 스킬 테이블.xlsx
+++ b/Data_Table/공용 스킬 테이블.xlsx
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>230</v>
+        <v>1500</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>330</v>
+        <v>2200</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>470</v>
+        <v>3100</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>470</v>
+        <v>3100</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>470</v>
+        <v>3100</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>0</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>0</v>
@@ -1275,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>230</v>
+        <v>1500</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>330</v>
+        <v>2200</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>470</v>
+        <v>3100</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>470</v>
+        <v>3100</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>470</v>
+        <v>3100</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>0</v>
@@ -1570,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>990</v>
+        <v>6500</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>0</v>
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>230</v>
+        <v>1500</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>330</v>
+        <v>2200</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>0</v>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>470</v>
+        <v>3100</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>0</v>
@@ -1924,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>470</v>
+        <v>3100</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>1100</v>
+        <v>6800</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>0</v>
@@ -2101,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>1500</v>
+        <v>9800</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>340</v>
+        <v>2200</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>330</v>
+        <v>2200</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>0</v>
@@ -2337,7 +2337,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>470</v>
+        <v>3100</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>0</v>
@@ -2396,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>470</v>
+        <v>3100</v>
       </c>
       <c r="K32" s="1" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>990</v>
+        <v>6500</v>
       </c>
       <c r="K35" s="1" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>490</v>
+        <v>3200</v>
       </c>
       <c r="K36" s="1" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>470</v>
+        <v>3100</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>470</v>
+        <v>3100</v>
       </c>
       <c r="K39" s="1" t="n">
         <v>0</v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>990</v>
+        <v>6500</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>0</v>
@@ -2927,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="K41" s="1" t="n">
         <v>0</v>
@@ -3049,10 +3049,10 @@
         <v>0</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>2600</v>
+        <v>16000</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L43" s="1" t="inlineStr">
         <is>
@@ -3108,10 +3108,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>2600</v>
+        <v>21000</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L44" s="1" t="inlineStr">
         <is>
@@ -3167,10 +3167,10 @@
         <v>0</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>7700</v>
+        <v>52000</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L45" s="1" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         <v>0</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>5100</v>
+        <v>26000</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L46" s="1" t="inlineStr">
         <is>
@@ -3285,10 +3285,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>5100</v>
+        <v>36000</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L47" s="1" t="inlineStr">
         <is>
@@ -3344,10 +3344,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>5100</v>
+        <v>26000</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -3403,10 +3403,10 @@
         <v>0</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>5100</v>
+        <v>36000</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L49" s="1" t="inlineStr">
         <is>
@@ -3462,10 +3462,10 @@
         <v>0</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>5100</v>
+        <v>36000</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L50" s="1" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
         <v>0</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>2600</v>
+        <v>16000</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L51" s="1" t="inlineStr">
         <is>
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>2600</v>
+        <v>21000</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L52" s="1" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         <v>0</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>5100</v>
+        <v>26000</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L53" s="1" t="inlineStr">
         <is>
@@ -3698,10 +3698,10 @@
         <v>0</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>5100</v>
+        <v>26000</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L54" s="1" t="inlineStr">
         <is>
@@ -3757,10 +3757,10 @@
         <v>0</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>5100</v>
+        <v>26000</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L55" s="1" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>5100</v>
+        <v>36000</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L56" s="1" t="inlineStr">
         <is>
@@ -3875,10 +3875,10 @@
         <v>0</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>7700</v>
+        <v>47000</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L57" s="1" t="inlineStr">
         <is>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>5100</v>
+        <v>36000</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L58" s="1" t="inlineStr">
         <is>
@@ -3993,10 +3993,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>2600</v>
+        <v>16000</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L59" s="1" t="inlineStr">
         <is>
@@ -4052,10 +4052,10 @@
         <v>0</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>2600</v>
+        <v>21000</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L60" s="1" t="inlineStr">
         <is>
@@ -4111,10 +4111,10 @@
         <v>0</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>5100</v>
+        <v>26000</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L61" s="1" t="inlineStr">
         <is>
@@ -4170,10 +4170,10 @@
         <v>0</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>5100</v>
+        <v>26000</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L62" s="1" t="inlineStr">
         <is>
@@ -4229,10 +4229,10 @@
         <v>0</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>5100</v>
+        <v>36000</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L63" s="1" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
         <v>0</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>11000</v>
+        <v>67000</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L64" s="1" t="inlineStr">
         <is>
@@ -4347,10 +4347,10 @@
         <v>0</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>5100</v>
+        <v>36000</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L65" s="1" t="inlineStr">
         <is>
@@ -4406,10 +4406,10 @@
         <v>0</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>13000</v>
+        <v>88000</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="L66" s="1" t="inlineStr">
         <is>
@@ -4465,10 +4465,10 @@
         <v>0</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>5100</v>
+        <v>31000</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L67" s="1" t="inlineStr">
         <is>
@@ -4524,10 +4524,10 @@
         <v>0</v>
       </c>
       <c r="J68" s="1" t="n">
-        <v>2600</v>
+        <v>21000</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L68" s="1" t="inlineStr">
         <is>
@@ -4583,10 +4583,10 @@
         <v>0</v>
       </c>
       <c r="J69" s="1" t="n">
-        <v>5100</v>
+        <v>26000</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L69" s="1" t="inlineStr">
         <is>
@@ -4642,10 +4642,10 @@
         <v>0</v>
       </c>
       <c r="J70" s="1" t="n">
-        <v>5100</v>
+        <v>26000</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L70" s="1" t="inlineStr">
         <is>
@@ -4701,10 +4701,10 @@
         <v>0</v>
       </c>
       <c r="J71" s="1" t="n">
-        <v>5100</v>
+        <v>36000</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L71" s="1" t="inlineStr">
         <is>
@@ -4760,10 +4760,10 @@
         <v>0</v>
       </c>
       <c r="J72" s="1" t="n">
-        <v>5100</v>
+        <v>36000</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L72" s="1" t="inlineStr">
         <is>
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="J73" s="1" t="n">
-        <v>7700</v>
+        <v>47000</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L73" s="1" t="inlineStr">
         <is>
@@ -4878,10 +4878,10 @@
         <v>0</v>
       </c>
       <c r="J74" s="1" t="n">
-        <v>5100</v>
+        <v>41000</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L74" s="1" t="inlineStr">
         <is>
@@ -4937,10 +4937,10 @@
         <v>0</v>
       </c>
       <c r="J75" s="1" t="n">
-        <v>5100</v>
+        <v>26000</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L75" s="1" t="inlineStr">
         <is>
@@ -4996,10 +4996,10 @@
         <v>0</v>
       </c>
       <c r="J76" s="1" t="n">
-        <v>11000</v>
+        <v>67000</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L76" s="1" t="inlineStr">
         <is>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="J77" s="1" t="n">
-        <v>5100</v>
+        <v>26000</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L77" s="1" t="inlineStr">
         <is>
@@ -5114,10 +5114,10 @@
         <v>0</v>
       </c>
       <c r="J78" s="1" t="n">
-        <v>7700</v>
+        <v>47000</v>
       </c>
       <c r="K78" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L78" s="1" t="inlineStr">
         <is>
@@ -5173,10 +5173,10 @@
         <v>0</v>
       </c>
       <c r="J79" s="1" t="n">
-        <v>5100</v>
+        <v>36000</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L79" s="1" t="inlineStr">
         <is>
@@ -5295,10 +5295,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="1" t="n">
-        <v>26000</v>
+        <v>61000</v>
       </c>
       <c r="K81" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L81" s="1" t="inlineStr">
         <is>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="J82" s="1" t="n">
-        <v>26000</v>
+        <v>73000</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L82" s="1" t="inlineStr">
         <is>
@@ -5413,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="J83" s="1" t="n">
-        <v>70000</v>
+        <v>190000</v>
       </c>
       <c r="K83" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L83" s="1" t="inlineStr">
         <is>
@@ -5472,10 +5472,10 @@
         <v>0</v>
       </c>
       <c r="J84" s="1" t="n">
-        <v>39000</v>
+        <v>97000</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L84" s="1" t="inlineStr">
         <is>
@@ -5531,10 +5531,10 @@
         <v>0</v>
       </c>
       <c r="J85" s="1" t="n">
-        <v>45000</v>
+        <v>130000</v>
       </c>
       <c r="K85" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L85" s="1" t="inlineStr">
         <is>
@@ -5590,10 +5590,10 @@
         <v>0</v>
       </c>
       <c r="J86" s="1" t="n">
-        <v>39000</v>
+        <v>97000</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L86" s="1" t="inlineStr">
         <is>
@@ -5649,10 +5649,10 @@
         <v>0</v>
       </c>
       <c r="J87" s="1" t="n">
-        <v>45000</v>
+        <v>130000</v>
       </c>
       <c r="K87" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L87" s="1" t="inlineStr">
         <is>
@@ -5708,10 +5708,10 @@
         <v>0</v>
       </c>
       <c r="J88" s="1" t="n">
-        <v>45000</v>
+        <v>130000</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L88" s="1" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         <v>0</v>
       </c>
       <c r="J89" s="1" t="n">
-        <v>26000</v>
+        <v>61000</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L89" s="1" t="inlineStr">
         <is>
@@ -5826,10 +5826,10 @@
         <v>0</v>
       </c>
       <c r="J90" s="1" t="n">
-        <v>26000</v>
+        <v>73000</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L90" s="1" t="inlineStr">
         <is>
@@ -5885,10 +5885,10 @@
         <v>0</v>
       </c>
       <c r="J91" s="1" t="n">
-        <v>39000</v>
+        <v>97000</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L91" s="1" t="inlineStr">
         <is>
@@ -5944,10 +5944,10 @@
         <v>0</v>
       </c>
       <c r="J92" s="1" t="n">
-        <v>39000</v>
+        <v>97000</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L92" s="1" t="inlineStr">
         <is>
@@ -6003,10 +6003,10 @@
         <v>0</v>
       </c>
       <c r="J93" s="1" t="n">
-        <v>39000</v>
+        <v>97000</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L93" s="1" t="inlineStr">
         <is>
@@ -6062,10 +6062,10 @@
         <v>0</v>
       </c>
       <c r="J94" s="1" t="n">
-        <v>45000</v>
+        <v>130000</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L94" s="1" t="inlineStr">
         <is>
@@ -6121,10 +6121,10 @@
         <v>0</v>
       </c>
       <c r="J95" s="1" t="n">
-        <v>58000</v>
+        <v>160000</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L95" s="1" t="inlineStr">
         <is>
@@ -6180,10 +6180,10 @@
         <v>0</v>
       </c>
       <c r="J96" s="1" t="n">
-        <v>45000</v>
+        <v>130000</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L96" s="1" t="inlineStr">
         <is>
@@ -6239,10 +6239,10 @@
         <v>0</v>
       </c>
       <c r="J97" s="1" t="n">
-        <v>26000</v>
+        <v>61000</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L97" s="1" t="inlineStr">
         <is>
@@ -6298,10 +6298,10 @@
         <v>0</v>
       </c>
       <c r="J98" s="1" t="n">
-        <v>26000</v>
+        <v>73000</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L98" s="1" t="inlineStr">
         <is>
@@ -6357,10 +6357,10 @@
         <v>0</v>
       </c>
       <c r="J99" s="1" t="n">
-        <v>39000</v>
+        <v>97000</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L99" s="1" t="inlineStr">
         <is>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="J100" s="1" t="n">
-        <v>39000</v>
+        <v>97000</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L100" s="1" t="inlineStr">
         <is>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="J101" s="1" t="n">
-        <v>45000</v>
+        <v>130000</v>
       </c>
       <c r="K101" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L101" s="1" t="inlineStr">
         <is>
@@ -6534,10 +6534,10 @@
         <v>0</v>
       </c>
       <c r="J102" s="1" t="n">
-        <v>89000</v>
+        <v>250000</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L102" s="1" t="inlineStr">
         <is>
@@ -6593,10 +6593,10 @@
         <v>0</v>
       </c>
       <c r="J103" s="1" t="n">
-        <v>45000</v>
+        <v>130000</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L103" s="1" t="inlineStr">
         <is>
@@ -6652,10 +6652,10 @@
         <v>0</v>
       </c>
       <c r="J104" s="1" t="n">
-        <v>120000</v>
+        <v>320000</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="L104" s="1" t="inlineStr">
         <is>
@@ -6711,10 +6711,10 @@
         <v>0</v>
       </c>
       <c r="J105" s="1" t="n">
-        <v>45000</v>
+        <v>110000</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L105" s="1" t="inlineStr">
         <is>
@@ -6770,10 +6770,10 @@
         <v>0</v>
       </c>
       <c r="J106" s="1" t="n">
-        <v>26000</v>
+        <v>73000</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L106" s="1" t="inlineStr">
         <is>
@@ -6829,10 +6829,10 @@
         <v>0</v>
       </c>
       <c r="J107" s="1" t="n">
-        <v>39000</v>
+        <v>97000</v>
       </c>
       <c r="K107" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L107" s="1" t="inlineStr">
         <is>
@@ -6888,10 +6888,10 @@
         <v>0</v>
       </c>
       <c r="J108" s="1" t="n">
-        <v>39000</v>
+        <v>97000</v>
       </c>
       <c r="K108" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L108" s="1" t="inlineStr">
         <is>
@@ -6947,10 +6947,10 @@
         <v>0</v>
       </c>
       <c r="J109" s="1" t="n">
-        <v>45000</v>
+        <v>130000</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L109" s="1" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
         <v>0</v>
       </c>
       <c r="J110" s="1" t="n">
-        <v>45000</v>
+        <v>130000</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L110" s="1" t="inlineStr">
         <is>
@@ -7065,10 +7065,10 @@
         <v>0</v>
       </c>
       <c r="J111" s="1" t="n">
-        <v>58000</v>
+        <v>160000</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L111" s="1" t="inlineStr">
         <is>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="J112" s="1" t="n">
-        <v>51000</v>
+        <v>150000</v>
       </c>
       <c r="K112" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L112" s="1" t="inlineStr">
         <is>
@@ -7183,10 +7183,10 @@
         <v>0</v>
       </c>
       <c r="J113" s="1" t="n">
-        <v>70000</v>
+        <v>190000</v>
       </c>
       <c r="K113" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L113" s="1" t="inlineStr">
         <is>
@@ -7242,10 +7242,10 @@
         <v>0</v>
       </c>
       <c r="J114" s="1" t="n">
-        <v>45000</v>
+        <v>130000</v>
       </c>
       <c r="K114" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L114" s="1" t="inlineStr">
         <is>
@@ -7301,10 +7301,10 @@
         <v>0</v>
       </c>
       <c r="J115" s="1" t="n">
-        <v>39000</v>
+        <v>97000</v>
       </c>
       <c r="K115" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L115" s="1" t="inlineStr">
         <is>
@@ -7360,10 +7360,10 @@
         <v>0</v>
       </c>
       <c r="J116" s="1" t="n">
-        <v>58000</v>
+        <v>160000</v>
       </c>
       <c r="K116" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L116" s="1" t="inlineStr">
         <is>
@@ -7419,10 +7419,10 @@
         <v>0</v>
       </c>
       <c r="J117" s="1" t="n">
-        <v>45000</v>
+        <v>130000</v>
       </c>
       <c r="K117" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L117" s="1" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="1" t="n">
-        <v>170000</v>
+        <v>210000</v>
       </c>
       <c r="K119" s="1" t="n">
         <v>8</v>
@@ -7600,10 +7600,10 @@
         <v>0</v>
       </c>
       <c r="J120" s="1" t="n">
-        <v>230000</v>
+        <v>260000</v>
       </c>
       <c r="K120" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L120" s="1" t="inlineStr">
         <is>
@@ -7659,10 +7659,10 @@
         <v>0</v>
       </c>
       <c r="J121" s="1" t="n">
-        <v>290000</v>
+        <v>340000</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L121" s="1" t="inlineStr">
         <is>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="J122" s="1" t="n">
-        <v>290000</v>
+        <v>340000</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L122" s="1" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="1" t="n">
-        <v>350000</v>
+        <v>450000</v>
       </c>
       <c r="K123" s="1" t="n">
         <v>17</v>
@@ -7836,10 +7836,10 @@
         <v>0</v>
       </c>
       <c r="J124" s="1" t="n">
-        <v>290000</v>
+        <v>340000</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L124" s="1" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="1" t="n">
-        <v>350000</v>
+        <v>450000</v>
       </c>
       <c r="K125" s="1" t="n">
         <v>17</v>
@@ -7954,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="J126" s="1" t="n">
-        <v>350000</v>
+        <v>450000</v>
       </c>
       <c r="K126" s="1" t="n">
         <v>17</v>
@@ -8013,7 +8013,7 @@
         <v>0</v>
       </c>
       <c r="J127" s="1" t="n">
-        <v>170000</v>
+        <v>210000</v>
       </c>
       <c r="K127" s="1" t="n">
         <v>8</v>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="J128" s="1" t="n">
-        <v>230000</v>
+        <v>260000</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L128" s="1" t="inlineStr">
         <is>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="J129" s="1" t="n">
-        <v>290000</v>
+        <v>340000</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L129" s="1" t="inlineStr">
         <is>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="J130" s="1" t="n">
-        <v>290000</v>
+        <v>340000</v>
       </c>
       <c r="K130" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L130" s="1" t="inlineStr">
         <is>
@@ -8249,10 +8249,10 @@
         <v>0</v>
       </c>
       <c r="J131" s="1" t="n">
-        <v>290000</v>
+        <v>340000</v>
       </c>
       <c r="K131" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L131" s="1" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="1" t="n">
-        <v>350000</v>
+        <v>450000</v>
       </c>
       <c r="K132" s="1" t="n">
         <v>17</v>
@@ -8367,10 +8367,10 @@
         <v>0</v>
       </c>
       <c r="J133" s="1" t="n">
-        <v>470000</v>
+        <v>550000</v>
       </c>
       <c r="K133" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L133" s="1" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="1" t="n">
-        <v>350000</v>
+        <v>450000</v>
       </c>
       <c r="K134" s="1" t="n">
         <v>17</v>
@@ -8485,7 +8485,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="1" t="n">
-        <v>170000</v>
+        <v>210000</v>
       </c>
       <c r="K135" s="1" t="n">
         <v>8</v>
@@ -8544,10 +8544,10 @@
         <v>0</v>
       </c>
       <c r="J136" s="1" t="n">
-        <v>230000</v>
+        <v>260000</v>
       </c>
       <c r="K136" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L136" s="1" t="inlineStr">
         <is>
@@ -8603,10 +8603,10 @@
         <v>0</v>
       </c>
       <c r="J137" s="1" t="n">
-        <v>290000</v>
+        <v>340000</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L137" s="1" t="inlineStr">
         <is>
@@ -8662,10 +8662,10 @@
         <v>0</v>
       </c>
       <c r="J138" s="1" t="n">
-        <v>290000</v>
+        <v>340000</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L138" s="1" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>0</v>
       </c>
       <c r="J139" s="1" t="n">
-        <v>350000</v>
+        <v>450000</v>
       </c>
       <c r="K139" s="1" t="n">
         <v>17</v>
@@ -8780,10 +8780,10 @@
         <v>0</v>
       </c>
       <c r="J140" s="1" t="n">
-        <v>700000</v>
+        <v>860000</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L140" s="1" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>0</v>
       </c>
       <c r="J141" s="1" t="n">
-        <v>350000</v>
+        <v>450000</v>
       </c>
       <c r="K141" s="1" t="n">
         <v>17</v>
@@ -8898,10 +8898,10 @@
         <v>0</v>
       </c>
       <c r="J142" s="1" t="n">
-        <v>920000</v>
+        <v>1100000</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L142" s="1" t="inlineStr">
         <is>
@@ -8957,10 +8957,10 @@
         <v>0</v>
       </c>
       <c r="J143" s="1" t="n">
-        <v>330000</v>
+        <v>390000</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L143" s="1" t="inlineStr">
         <is>
@@ -9016,10 +9016,10 @@
         <v>0</v>
       </c>
       <c r="J144" s="1" t="n">
-        <v>230000</v>
+        <v>260000</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L144" s="1" t="inlineStr">
         <is>
@@ -9075,10 +9075,10 @@
         <v>0</v>
       </c>
       <c r="J145" s="1" t="n">
-        <v>290000</v>
+        <v>340000</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L145" s="1" t="inlineStr">
         <is>
@@ -9134,10 +9134,10 @@
         <v>0</v>
       </c>
       <c r="J146" s="1" t="n">
-        <v>290000</v>
+        <v>340000</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L146" s="1" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>0</v>
       </c>
       <c r="J147" s="1" t="n">
-        <v>350000</v>
+        <v>450000</v>
       </c>
       <c r="K147" s="1" t="n">
         <v>17</v>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="J148" s="1" t="n">
-        <v>350000</v>
+        <v>450000</v>
       </c>
       <c r="K148" s="1" t="n">
         <v>17</v>
@@ -9311,10 +9311,10 @@
         <v>0</v>
       </c>
       <c r="J149" s="1" t="n">
-        <v>470000</v>
+        <v>550000</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L149" s="1" t="inlineStr">
         <is>
@@ -9370,10 +9370,10 @@
         <v>0</v>
       </c>
       <c r="J150" s="1" t="n">
-        <v>430000</v>
+        <v>520000</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L150" s="1" t="inlineStr">
         <is>
@@ -9429,10 +9429,10 @@
         <v>0</v>
       </c>
       <c r="J151" s="1" t="n">
-        <v>290000</v>
+        <v>340000</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L151" s="1" t="inlineStr">
         <is>
@@ -9488,10 +9488,10 @@
         <v>0</v>
       </c>
       <c r="J152" s="1" t="n">
-        <v>700000</v>
+        <v>860000</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L152" s="1" t="inlineStr">
         <is>
@@ -9547,10 +9547,10 @@
         <v>0</v>
       </c>
       <c r="J153" s="1" t="n">
-        <v>290000</v>
+        <v>340000</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L153" s="1" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         <v>0</v>
       </c>
       <c r="J154" s="1" t="n">
-        <v>470000</v>
+        <v>550000</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L154" s="1" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>0</v>
       </c>
       <c r="J155" s="1" t="n">
-        <v>350000</v>
+        <v>450000</v>
       </c>
       <c r="K155" s="1" t="n">
         <v>17</v>
@@ -9787,10 +9787,10 @@
         <v>0</v>
       </c>
       <c r="J157" s="1" t="n">
-        <v>1400000</v>
+        <v>710000</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L157" s="1" t="inlineStr">
         <is>
@@ -9846,10 +9846,10 @@
         <v>0</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>1800000</v>
+        <v>870000</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L158" s="1" t="inlineStr">
         <is>
@@ -9905,10 +9905,10 @@
         <v>0</v>
       </c>
       <c r="J159" s="1" t="n">
-        <v>2300000</v>
+        <v>1200000</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L159" s="1" t="inlineStr">
         <is>
@@ -9964,10 +9964,10 @@
         <v>0</v>
       </c>
       <c r="J160" s="1" t="n">
-        <v>2300000</v>
+        <v>1200000</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L160" s="1" t="inlineStr">
         <is>
@@ -10023,10 +10023,10 @@
         <v>0</v>
       </c>
       <c r="J161" s="1" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L161" s="1" t="inlineStr">
         <is>
@@ -10082,10 +10082,10 @@
         <v>0</v>
       </c>
       <c r="J162" s="1" t="n">
-        <v>2300000</v>
+        <v>1200000</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L162" s="1" t="inlineStr">
         <is>
@@ -10141,10 +10141,10 @@
         <v>0</v>
       </c>
       <c r="J163" s="1" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L163" s="1" t="inlineStr">
         <is>
@@ -10200,10 +10200,10 @@
         <v>0</v>
       </c>
       <c r="J164" s="1" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L164" s="1" t="inlineStr">
         <is>
@@ -10259,10 +10259,10 @@
         <v>0</v>
       </c>
       <c r="J165" s="1" t="n">
-        <v>1400000</v>
+        <v>710000</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L165" s="1" t="inlineStr">
         <is>
@@ -10318,10 +10318,10 @@
         <v>0</v>
       </c>
       <c r="J166" s="1" t="n">
-        <v>1800000</v>
+        <v>870000</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L166" s="1" t="inlineStr">
         <is>
@@ -10377,10 +10377,10 @@
         <v>0</v>
       </c>
       <c r="J167" s="1" t="n">
-        <v>2300000</v>
+        <v>1200000</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L167" s="1" t="inlineStr">
         <is>
@@ -10436,10 +10436,10 @@
         <v>0</v>
       </c>
       <c r="J168" s="1" t="n">
-        <v>2300000</v>
+        <v>1200000</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L168" s="1" t="inlineStr">
         <is>
@@ -10495,10 +10495,10 @@
         <v>0</v>
       </c>
       <c r="J169" s="1" t="n">
-        <v>2300000</v>
+        <v>1200000</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L169" s="1" t="inlineStr">
         <is>
@@ -10554,10 +10554,10 @@
         <v>0</v>
       </c>
       <c r="J170" s="1" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="K170" s="1" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L170" s="1" t="inlineStr">
         <is>
@@ -10613,10 +10613,10 @@
         <v>0</v>
       </c>
       <c r="J171" s="1" t="n">
-        <v>3800000</v>
+        <v>1900000</v>
       </c>
       <c r="K171" s="1" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L171" s="1" t="inlineStr">
         <is>
@@ -10672,10 +10672,10 @@
         <v>0</v>
       </c>
       <c r="J172" s="1" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L172" s="1" t="inlineStr">
         <is>
@@ -10731,10 +10731,10 @@
         <v>0</v>
       </c>
       <c r="J173" s="1" t="n">
-        <v>1400000</v>
+        <v>710000</v>
       </c>
       <c r="K173" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L173" s="1" t="inlineStr">
         <is>
@@ -10790,10 +10790,10 @@
         <v>0</v>
       </c>
       <c r="J174" s="1" t="n">
-        <v>1800000</v>
+        <v>870000</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L174" s="1" t="inlineStr">
         <is>
@@ -10849,10 +10849,10 @@
         <v>0</v>
       </c>
       <c r="J175" s="1" t="n">
-        <v>2300000</v>
+        <v>1200000</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L175" s="1" t="inlineStr">
         <is>
@@ -10908,10 +10908,10 @@
         <v>0</v>
       </c>
       <c r="J176" s="1" t="n">
-        <v>2300000</v>
+        <v>1200000</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L176" s="1" t="inlineStr">
         <is>
@@ -10967,10 +10967,10 @@
         <v>0</v>
       </c>
       <c r="J177" s="1" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="K177" s="1" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L177" s="1" t="inlineStr">
         <is>
@@ -11026,10 +11026,10 @@
         <v>0</v>
       </c>
       <c r="J178" s="1" t="n">
-        <v>5800000</v>
+        <v>3000000</v>
       </c>
       <c r="K178" s="1" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="L178" s="1" t="inlineStr">
         <is>
@@ -11085,10 +11085,10 @@
         <v>0</v>
       </c>
       <c r="J179" s="1" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="K179" s="1" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L179" s="1" t="inlineStr">
         <is>
@@ -11144,10 +11144,10 @@
         <v>0</v>
       </c>
       <c r="J180" s="1" t="n">
-        <v>7500000</v>
+        <v>3800000</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="L180" s="1" t="inlineStr">
         <is>
@@ -11203,10 +11203,10 @@
         <v>0</v>
       </c>
       <c r="J181" s="1" t="n">
-        <v>2700000</v>
+        <v>1400000</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L181" s="1" t="inlineStr">
         <is>
@@ -11262,10 +11262,10 @@
         <v>0</v>
       </c>
       <c r="J182" s="1" t="n">
-        <v>1800000</v>
+        <v>870000</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L182" s="1" t="inlineStr">
         <is>
@@ -11321,10 +11321,10 @@
         <v>0</v>
       </c>
       <c r="J183" s="1" t="n">
-        <v>2300000</v>
+        <v>1200000</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L183" s="1" t="inlineStr">
         <is>
@@ -11380,10 +11380,10 @@
         <v>0</v>
       </c>
       <c r="J184" s="1" t="n">
-        <v>2300000</v>
+        <v>1200000</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L184" s="1" t="inlineStr">
         <is>
@@ -11439,10 +11439,10 @@
         <v>0</v>
       </c>
       <c r="J185" s="1" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L185" s="1" t="inlineStr">
         <is>
@@ -11498,10 +11498,10 @@
         <v>0</v>
       </c>
       <c r="J186" s="1" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L186" s="1" t="inlineStr">
         <is>
@@ -11557,10 +11557,10 @@
         <v>0</v>
       </c>
       <c r="J187" s="1" t="n">
-        <v>3800000</v>
+        <v>1900000</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L187" s="1" t="inlineStr">
         <is>
@@ -11616,10 +11616,10 @@
         <v>0</v>
       </c>
       <c r="J188" s="1" t="n">
-        <v>3500000</v>
+        <v>1800000</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L188" s="1" t="inlineStr">
         <is>
@@ -11675,10 +11675,10 @@
         <v>0</v>
       </c>
       <c r="J189" s="1" t="n">
-        <v>4500000</v>
+        <v>2300000</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L189" s="1" t="inlineStr">
         <is>
@@ -11734,10 +11734,10 @@
         <v>0</v>
       </c>
       <c r="J190" s="1" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L190" s="1" t="inlineStr">
         <is>
@@ -11793,10 +11793,10 @@
         <v>0</v>
       </c>
       <c r="J191" s="1" t="n">
-        <v>2300000</v>
+        <v>1200000</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L191" s="1" t="inlineStr">
         <is>
@@ -11852,10 +11852,10 @@
         <v>0</v>
       </c>
       <c r="J192" s="1" t="n">
-        <v>3800000</v>
+        <v>1900000</v>
       </c>
       <c r="K192" s="1" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L192" s="1" t="inlineStr">
         <is>
@@ -11911,10 +11911,10 @@
         <v>0</v>
       </c>
       <c r="J193" s="1" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L193" s="1" t="inlineStr">
         <is>
@@ -12033,10 +12033,10 @@
         <v>0</v>
       </c>
       <c r="J195" s="1" t="n">
-        <v>13000000</v>
+        <v>3400000</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L195" s="1" t="inlineStr">
         <is>
@@ -12092,10 +12092,10 @@
         <v>0</v>
       </c>
       <c r="J196" s="1" t="n">
-        <v>17000000</v>
+        <v>4300000</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L196" s="1" t="inlineStr">
         <is>
@@ -12151,10 +12151,10 @@
         <v>0</v>
       </c>
       <c r="J197" s="1" t="n">
-        <v>22000000</v>
+        <v>5600000</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L197" s="1" t="inlineStr">
         <is>
@@ -12210,10 +12210,10 @@
         <v>0</v>
       </c>
       <c r="J198" s="1" t="n">
-        <v>22000000</v>
+        <v>5600000</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L198" s="1" t="inlineStr">
         <is>
@@ -12269,10 +12269,10 @@
         <v>0</v>
       </c>
       <c r="J199" s="1" t="n">
-        <v>28000000</v>
+        <v>7300000</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L199" s="1" t="inlineStr">
         <is>
@@ -12328,10 +12328,10 @@
         <v>0</v>
       </c>
       <c r="J200" s="1" t="n">
-        <v>22000000</v>
+        <v>5600000</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L200" s="1" t="inlineStr">
         <is>
@@ -12387,10 +12387,10 @@
         <v>0</v>
       </c>
       <c r="J201" s="1" t="n">
-        <v>28000000</v>
+        <v>7300000</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L201" s="1" t="inlineStr">
         <is>
@@ -12446,10 +12446,10 @@
         <v>0</v>
       </c>
       <c r="J202" s="1" t="n">
-        <v>28000000</v>
+        <v>7300000</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L202" s="1" t="inlineStr">
         <is>
@@ -12505,10 +12505,10 @@
         <v>0</v>
       </c>
       <c r="J203" s="1" t="n">
-        <v>13000000</v>
+        <v>3400000</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L203" s="1" t="inlineStr">
         <is>
@@ -12564,10 +12564,10 @@
         <v>0</v>
       </c>
       <c r="J204" s="1" t="n">
-        <v>17000000</v>
+        <v>4300000</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L204" s="1" t="inlineStr">
         <is>
@@ -12623,10 +12623,10 @@
         <v>0</v>
       </c>
       <c r="J205" s="1" t="n">
-        <v>22000000</v>
+        <v>5600000</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L205" s="1" t="inlineStr">
         <is>
@@ -12682,10 +12682,10 @@
         <v>0</v>
       </c>
       <c r="J206" s="1" t="n">
-        <v>22000000</v>
+        <v>5600000</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L206" s="1" t="inlineStr">
         <is>
@@ -12741,10 +12741,10 @@
         <v>0</v>
       </c>
       <c r="J207" s="1" t="n">
-        <v>22000000</v>
+        <v>5600000</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L207" s="1" t="inlineStr">
         <is>
@@ -12800,10 +12800,10 @@
         <v>0</v>
       </c>
       <c r="J208" s="1" t="n">
-        <v>28000000</v>
+        <v>7300000</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L208" s="1" t="inlineStr">
         <is>
@@ -12859,10 +12859,10 @@
         <v>0</v>
       </c>
       <c r="J209" s="1" t="n">
-        <v>37000000</v>
+        <v>9400000</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="L209" s="1" t="inlineStr">
         <is>
@@ -12918,10 +12918,10 @@
         <v>0</v>
       </c>
       <c r="J210" s="1" t="n">
-        <v>28000000</v>
+        <v>7300000</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L210" s="1" t="inlineStr">
         <is>
@@ -12977,10 +12977,10 @@
         <v>0</v>
       </c>
       <c r="J211" s="1" t="n">
-        <v>13000000</v>
+        <v>3400000</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L211" s="1" t="inlineStr">
         <is>
@@ -13036,10 +13036,10 @@
         <v>0</v>
       </c>
       <c r="J212" s="1" t="n">
-        <v>17000000</v>
+        <v>4300000</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L212" s="1" t="inlineStr">
         <is>
@@ -13095,10 +13095,10 @@
         <v>0</v>
       </c>
       <c r="J213" s="1" t="n">
-        <v>22000000</v>
+        <v>5600000</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L213" s="1" t="inlineStr">
         <is>
@@ -13154,10 +13154,10 @@
         <v>0</v>
       </c>
       <c r="J214" s="1" t="n">
-        <v>22000000</v>
+        <v>5600000</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L214" s="1" t="inlineStr">
         <is>
@@ -13213,10 +13213,10 @@
         <v>0</v>
       </c>
       <c r="J215" s="1" t="n">
-        <v>28000000</v>
+        <v>7300000</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L215" s="1" t="inlineStr">
         <is>
@@ -13272,10 +13272,10 @@
         <v>0</v>
       </c>
       <c r="J216" s="1" t="n">
-        <v>56000000</v>
+        <v>15000000</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="L216" s="1" t="inlineStr">
         <is>
@@ -13331,10 +13331,10 @@
         <v>0</v>
       </c>
       <c r="J217" s="1" t="n">
-        <v>28000000</v>
+        <v>7300000</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L217" s="1" t="inlineStr">
         <is>
@@ -13390,10 +13390,10 @@
         <v>0</v>
       </c>
       <c r="J218" s="1" t="n">
-        <v>72000000</v>
+        <v>19000000</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="L218" s="1" t="inlineStr">
         <is>
@@ -13449,10 +13449,10 @@
         <v>0</v>
       </c>
       <c r="J219" s="1" t="n">
-        <v>13000000</v>
+        <v>3400000</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L219" s="1" t="inlineStr">
         <is>
@@ -13508,10 +13508,10 @@
         <v>0</v>
       </c>
       <c r="J220" s="1" t="n">
-        <v>17000000</v>
+        <v>4300000</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L220" s="1" t="inlineStr">
         <is>
@@ -13567,10 +13567,10 @@
         <v>0</v>
       </c>
       <c r="J221" s="1" t="n">
-        <v>22000000</v>
+        <v>5600000</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L221" s="1" t="inlineStr">
         <is>
@@ -13626,10 +13626,10 @@
         <v>0</v>
       </c>
       <c r="J222" s="1" t="n">
-        <v>22000000</v>
+        <v>5600000</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L222" s="1" t="inlineStr">
         <is>
@@ -13685,10 +13685,10 @@
         <v>0</v>
       </c>
       <c r="J223" s="1" t="n">
-        <v>28000000</v>
+        <v>7300000</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L223" s="1" t="inlineStr">
         <is>
@@ -13744,10 +13744,10 @@
         <v>0</v>
       </c>
       <c r="J224" s="1" t="n">
-        <v>28000000</v>
+        <v>7300000</v>
       </c>
       <c r="K224" s="1" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L224" s="1" t="inlineStr">
         <is>
@@ -13803,10 +13803,10 @@
         <v>0</v>
       </c>
       <c r="J225" s="1" t="n">
-        <v>37000000</v>
+        <v>9400000</v>
       </c>
       <c r="K225" s="1" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="L225" s="1" t="inlineStr">
         <is>
@@ -13862,10 +13862,10 @@
         <v>0</v>
       </c>
       <c r="J226" s="1" t="n">
-        <v>33000000</v>
+        <v>8600000</v>
       </c>
       <c r="K226" s="1" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="L226" s="1" t="inlineStr">
         <is>
@@ -13921,10 +13921,10 @@
         <v>0</v>
       </c>
       <c r="J227" s="1" t="n">
-        <v>43000000</v>
+        <v>12000000</v>
       </c>
       <c r="K227" s="1" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L227" s="1" t="inlineStr">
         <is>
@@ -13980,10 +13980,10 @@
         <v>0</v>
       </c>
       <c r="J228" s="1" t="n">
-        <v>56000000</v>
+        <v>15000000</v>
       </c>
       <c r="K228" s="1" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="L228" s="1" t="inlineStr">
         <is>
@@ -14039,10 +14039,10 @@
         <v>0</v>
       </c>
       <c r="J229" s="1" t="n">
-        <v>22000000</v>
+        <v>5600000</v>
       </c>
       <c r="K229" s="1" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L229" s="1" t="inlineStr">
         <is>
@@ -14098,10 +14098,10 @@
         <v>0</v>
       </c>
       <c r="J230" s="1" t="n">
-        <v>37000000</v>
+        <v>9400000</v>
       </c>
       <c r="K230" s="1" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="L230" s="1" t="inlineStr">
         <is>
@@ -14157,10 +14157,10 @@
         <v>0</v>
       </c>
       <c r="J231" s="1" t="n">
-        <v>28000000</v>
+        <v>7300000</v>
       </c>
       <c r="K231" s="1" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L231" s="1" t="inlineStr">
         <is>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="J233" s="1" t="n">
-        <v>200000000</v>
+        <v>32000000</v>
       </c>
       <c r="K233" s="1" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L233" s="1" t="inlineStr">
         <is>
@@ -14338,10 +14338,10 @@
         <v>0</v>
       </c>
       <c r="J234" s="1" t="n">
-        <v>260000000</v>
+        <v>41000000</v>
       </c>
       <c r="K234" s="1" t="n">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="L234" s="1" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         <v>0</v>
       </c>
       <c r="J235" s="1" t="n">
-        <v>340000000</v>
+        <v>53000000</v>
       </c>
       <c r="K235" s="1" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="L235" s="1" t="inlineStr">
         <is>
@@ -14456,10 +14456,10 @@
         <v>0</v>
       </c>
       <c r="J236" s="1" t="n">
-        <v>340000000</v>
+        <v>53000000</v>
       </c>
       <c r="K236" s="1" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="L236" s="1" t="inlineStr">
         <is>
@@ -14515,10 +14515,10 @@
         <v>0</v>
       </c>
       <c r="J237" s="1" t="n">
-        <v>440000000</v>
+        <v>69000000</v>
       </c>
       <c r="K237" s="1" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="L237" s="1" t="inlineStr">
         <is>
@@ -14574,10 +14574,10 @@
         <v>0</v>
       </c>
       <c r="J238" s="1" t="n">
-        <v>340000000</v>
+        <v>53000000</v>
       </c>
       <c r="K238" s="1" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="L238" s="1" t="inlineStr">
         <is>
@@ -14633,10 +14633,10 @@
         <v>0</v>
       </c>
       <c r="J239" s="1" t="n">
-        <v>440000000</v>
+        <v>69000000</v>
       </c>
       <c r="K239" s="1" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="L239" s="1" t="inlineStr">
         <is>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="J240" s="1" t="n">
-        <v>440000000</v>
+        <v>69000000</v>
       </c>
       <c r="K240" s="1" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="L240" s="1" t="inlineStr">
         <is>
@@ -14751,10 +14751,10 @@
         <v>0</v>
       </c>
       <c r="J241" s="1" t="n">
-        <v>200000000</v>
+        <v>32000000</v>
       </c>
       <c r="K241" s="1" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L241" s="1" t="inlineStr">
         <is>
@@ -14810,10 +14810,10 @@
         <v>0</v>
       </c>
       <c r="J242" s="1" t="n">
-        <v>260000000</v>
+        <v>41000000</v>
       </c>
       <c r="K242" s="1" t="n">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="L242" s="1" t="inlineStr">
         <is>
@@ -14869,10 +14869,10 @@
         <v>0</v>
       </c>
       <c r="J243" s="1" t="n">
-        <v>340000000</v>
+        <v>53000000</v>
       </c>
       <c r="K243" s="1" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="L243" s="1" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>0</v>
       </c>
       <c r="J244" s="1" t="n">
-        <v>340000000</v>
+        <v>53000000</v>
       </c>
       <c r="K244" s="1" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="L244" s="1" t="inlineStr">
         <is>
@@ -14987,10 +14987,10 @@
         <v>0</v>
       </c>
       <c r="J245" s="1" t="n">
-        <v>340000000</v>
+        <v>53000000</v>
       </c>
       <c r="K245" s="1" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="L245" s="1" t="inlineStr">
         <is>
@@ -15046,10 +15046,10 @@
         <v>0</v>
       </c>
       <c r="J246" s="1" t="n">
-        <v>440000000</v>
+        <v>69000000</v>
       </c>
       <c r="K246" s="1" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="L246" s="1" t="inlineStr">
         <is>
@@ -15105,10 +15105,10 @@
         <v>0</v>
       </c>
       <c r="J247" s="1" t="n">
-        <v>570000000</v>
+        <v>89000000</v>
       </c>
       <c r="K247" s="1" t="n">
-        <v>295</v>
+        <v>375</v>
       </c>
       <c r="L247" s="1" t="inlineStr">
         <is>
@@ -15164,10 +15164,10 @@
         <v>0</v>
       </c>
       <c r="J248" s="1" t="n">
-        <v>440000000</v>
+        <v>69000000</v>
       </c>
       <c r="K248" s="1" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="L248" s="1" t="inlineStr">
         <is>
@@ -15223,10 +15223,10 @@
         <v>0</v>
       </c>
       <c r="J249" s="1" t="n">
-        <v>200000000</v>
+        <v>32000000</v>
       </c>
       <c r="K249" s="1" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L249" s="1" t="inlineStr">
         <is>
@@ -15282,10 +15282,10 @@
         <v>0</v>
       </c>
       <c r="J250" s="1" t="n">
-        <v>260000000</v>
+        <v>41000000</v>
       </c>
       <c r="K250" s="1" t="n">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="L250" s="1" t="inlineStr">
         <is>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="J251" s="1" t="n">
-        <v>340000000</v>
+        <v>53000000</v>
       </c>
       <c r="K251" s="1" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="L251" s="1" t="inlineStr">
         <is>
@@ -15400,10 +15400,10 @@
         <v>0</v>
       </c>
       <c r="J252" s="1" t="n">
-        <v>340000000</v>
+        <v>53000000</v>
       </c>
       <c r="K252" s="1" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="L252" s="1" t="inlineStr">
         <is>
@@ -15459,10 +15459,10 @@
         <v>0</v>
       </c>
       <c r="J253" s="1" t="n">
-        <v>440000000</v>
+        <v>69000000</v>
       </c>
       <c r="K253" s="1" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="L253" s="1" t="inlineStr">
         <is>
@@ -15518,10 +15518,10 @@
         <v>0</v>
       </c>
       <c r="J254" s="1" t="n">
-        <v>440000000</v>
+        <v>69000000</v>
       </c>
       <c r="K254" s="1" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="L254" s="1" t="inlineStr">
         <is>
@@ -15577,10 +15577,10 @@
         <v>0</v>
       </c>
       <c r="J255" s="1" t="n">
-        <v>440000000</v>
+        <v>69000000</v>
       </c>
       <c r="K255" s="1" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="L255" s="1" t="inlineStr">
         <is>
@@ -15636,10 +15636,10 @@
         <v>0</v>
       </c>
       <c r="J256" s="1" t="n">
-        <v>1200000000</v>
+        <v>180000000</v>
       </c>
       <c r="K256" s="1" t="n">
-        <v>589</v>
+        <v>750</v>
       </c>
       <c r="L256" s="1" t="inlineStr">
         <is>
@@ -15695,10 +15695,10 @@
         <v>0</v>
       </c>
       <c r="J257" s="1" t="n">
-        <v>200000000</v>
+        <v>32000000</v>
       </c>
       <c r="K257" s="1" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L257" s="1" t="inlineStr">
         <is>
@@ -15754,10 +15754,10 @@
         <v>0</v>
       </c>
       <c r="J258" s="1" t="n">
-        <v>260000000</v>
+        <v>41000000</v>
       </c>
       <c r="K258" s="1" t="n">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="L258" s="1" t="inlineStr">
         <is>
@@ -15813,10 +15813,10 @@
         <v>0</v>
       </c>
       <c r="J259" s="1" t="n">
-        <v>340000000</v>
+        <v>53000000</v>
       </c>
       <c r="K259" s="1" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="L259" s="1" t="inlineStr">
         <is>
@@ -15872,10 +15872,10 @@
         <v>0</v>
       </c>
       <c r="J260" s="1" t="n">
-        <v>340000000</v>
+        <v>53000000</v>
       </c>
       <c r="K260" s="1" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="L260" s="1" t="inlineStr">
         <is>
@@ -15931,10 +15931,10 @@
         <v>0</v>
       </c>
       <c r="J261" s="1" t="n">
-        <v>440000000</v>
+        <v>69000000</v>
       </c>
       <c r="K261" s="1" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="L261" s="1" t="inlineStr">
         <is>
@@ -15990,10 +15990,10 @@
         <v>0</v>
       </c>
       <c r="J262" s="1" t="n">
-        <v>440000000</v>
+        <v>69000000</v>
       </c>
       <c r="K262" s="1" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="L262" s="1" t="inlineStr">
         <is>
@@ -16049,10 +16049,10 @@
         <v>0</v>
       </c>
       <c r="J263" s="1" t="n">
-        <v>570000000</v>
+        <v>89000000</v>
       </c>
       <c r="K263" s="1" t="n">
-        <v>295</v>
+        <v>375</v>
       </c>
       <c r="L263" s="1" t="inlineStr">
         <is>
@@ -16108,10 +16108,10 @@
         <v>0</v>
       </c>
       <c r="J264" s="1" t="n">
-        <v>520000000</v>
+        <v>82000000</v>
       </c>
       <c r="K264" s="1" t="n">
-        <v>268</v>
+        <v>342</v>
       </c>
       <c r="L264" s="1" t="inlineStr">
         <is>
@@ -16167,10 +16167,10 @@
         <v>0</v>
       </c>
       <c r="J265" s="1" t="n">
-        <v>340000000</v>
+        <v>53000000</v>
       </c>
       <c r="K265" s="1" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="L265" s="1" t="inlineStr">
         <is>
@@ -16226,10 +16226,10 @@
         <v>0</v>
       </c>
       <c r="J266" s="1" t="n">
-        <v>440000000</v>
+        <v>69000000</v>
       </c>
       <c r="K266" s="1" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="L266" s="1" t="inlineStr">
         <is>
@@ -16285,10 +16285,10 @@
         <v>0</v>
       </c>
       <c r="J267" s="1" t="n">
-        <v>340000000</v>
+        <v>53000000</v>
       </c>
       <c r="K267" s="1" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="L267" s="1" t="inlineStr">
         <is>
@@ -16344,10 +16344,10 @@
         <v>0</v>
       </c>
       <c r="J268" s="1" t="n">
-        <v>570000000</v>
+        <v>89000000</v>
       </c>
       <c r="K268" s="1" t="n">
-        <v>295</v>
+        <v>375</v>
       </c>
       <c r="L268" s="1" t="inlineStr">
         <is>
@@ -16403,10 +16403,10 @@
         <v>0</v>
       </c>
       <c r="J269" s="1" t="n">
-        <v>440000000</v>
+        <v>69000000</v>
       </c>
       <c r="K269" s="1" t="n">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="L269" s="1" t="inlineStr">
         <is>
@@ -16525,10 +16525,10 @@
         <v>0</v>
       </c>
       <c r="J271" s="1" t="n">
-        <v>1400000000</v>
+        <v>2300000000</v>
       </c>
       <c r="K271" s="1" t="n">
-        <v>859</v>
+        <v>4510</v>
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
@@ -16584,10 +16584,10 @@
         <v>0</v>
       </c>
       <c r="J272" s="1" t="n">
-        <v>1800000000</v>
+        <v>3000000000</v>
       </c>
       <c r="K272" s="1" t="n">
-        <v>1117</v>
+        <v>5862</v>
       </c>
       <c r="L272" s="1" t="inlineStr">
         <is>
@@ -16643,10 +16643,10 @@
         <v>0</v>
       </c>
       <c r="J273" s="1" t="n">
-        <v>2400000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K273" s="1" t="n">
-        <v>1452</v>
+        <v>7621</v>
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
@@ -16702,10 +16702,10 @@
         <v>0</v>
       </c>
       <c r="J274" s="1" t="n">
-        <v>2400000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K274" s="1" t="n">
-        <v>1452</v>
+        <v>7621</v>
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
@@ -16761,10 +16761,10 @@
         <v>0</v>
       </c>
       <c r="J275" s="1" t="n">
-        <v>3100000000</v>
+        <v>5100000000</v>
       </c>
       <c r="K275" s="1" t="n">
-        <v>1887</v>
+        <v>9907</v>
       </c>
       <c r="L275" s="1" t="inlineStr">
         <is>
@@ -16820,10 +16820,10 @@
         <v>0</v>
       </c>
       <c r="J276" s="1" t="n">
-        <v>2400000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K276" s="1" t="n">
-        <v>1452</v>
+        <v>7621</v>
       </c>
       <c r="L276" s="1" t="inlineStr">
         <is>
@@ -16879,10 +16879,10 @@
         <v>0</v>
       </c>
       <c r="J277" s="1" t="n">
-        <v>3100000000</v>
+        <v>5100000000</v>
       </c>
       <c r="K277" s="1" t="n">
-        <v>1887</v>
+        <v>9907</v>
       </c>
       <c r="L277" s="1" t="inlineStr">
         <is>
@@ -16938,10 +16938,10 @@
         <v>0</v>
       </c>
       <c r="J278" s="1" t="n">
-        <v>3100000000</v>
+        <v>5100000000</v>
       </c>
       <c r="K278" s="1" t="n">
-        <v>1887</v>
+        <v>9907</v>
       </c>
       <c r="L278" s="1" t="inlineStr">
         <is>
@@ -16997,10 +16997,10 @@
         <v>0</v>
       </c>
       <c r="J279" s="1" t="n">
-        <v>1400000000</v>
+        <v>2300000000</v>
       </c>
       <c r="K279" s="1" t="n">
-        <v>859</v>
+        <v>4510</v>
       </c>
       <c r="L279" s="1" t="inlineStr">
         <is>
@@ -17056,10 +17056,10 @@
         <v>0</v>
       </c>
       <c r="J280" s="1" t="n">
-        <v>1800000000</v>
+        <v>3000000000</v>
       </c>
       <c r="K280" s="1" t="n">
-        <v>1117</v>
+        <v>5862</v>
       </c>
       <c r="L280" s="1" t="inlineStr">
         <is>
@@ -17115,10 +17115,10 @@
         <v>0</v>
       </c>
       <c r="J281" s="1" t="n">
-        <v>2400000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K281" s="1" t="n">
-        <v>1452</v>
+        <v>7621</v>
       </c>
       <c r="L281" s="1" t="inlineStr">
         <is>
@@ -17174,10 +17174,10 @@
         <v>0</v>
       </c>
       <c r="J282" s="1" t="n">
-        <v>2400000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K282" s="1" t="n">
-        <v>1452</v>
+        <v>7621</v>
       </c>
       <c r="L282" s="1" t="inlineStr">
         <is>
@@ -17233,10 +17233,10 @@
         <v>0</v>
       </c>
       <c r="J283" s="1" t="n">
-        <v>2400000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K283" s="1" t="n">
-        <v>1452</v>
+        <v>7621</v>
       </c>
       <c r="L283" s="1" t="inlineStr">
         <is>
@@ -17292,10 +17292,10 @@
         <v>0</v>
       </c>
       <c r="J284" s="1" t="n">
-        <v>3100000000</v>
+        <v>5100000000</v>
       </c>
       <c r="K284" s="1" t="n">
-        <v>1887</v>
+        <v>9907</v>
       </c>
       <c r="L284" s="1" t="inlineStr">
         <is>
@@ -17351,10 +17351,10 @@
         <v>0</v>
       </c>
       <c r="J285" s="1" t="n">
-        <v>4000000000</v>
+        <v>6600000000</v>
       </c>
       <c r="K285" s="1" t="n">
-        <v>2453</v>
+        <v>12879</v>
       </c>
       <c r="L285" s="1" t="inlineStr">
         <is>
@@ -17410,10 +17410,10 @@
         <v>0</v>
       </c>
       <c r="J286" s="1" t="n">
-        <v>3100000000</v>
+        <v>5100000000</v>
       </c>
       <c r="K286" s="1" t="n">
-        <v>1887</v>
+        <v>9907</v>
       </c>
       <c r="L286" s="1" t="inlineStr">
         <is>
@@ -17469,10 +17469,10 @@
         <v>0</v>
       </c>
       <c r="J287" s="1" t="n">
-        <v>1400000000</v>
+        <v>2300000000</v>
       </c>
       <c r="K287" s="1" t="n">
-        <v>859</v>
+        <v>4510</v>
       </c>
       <c r="L287" s="1" t="inlineStr">
         <is>
@@ -17528,10 +17528,10 @@
         <v>0</v>
       </c>
       <c r="J288" s="1" t="n">
-        <v>1800000000</v>
+        <v>3000000000</v>
       </c>
       <c r="K288" s="1" t="n">
-        <v>1117</v>
+        <v>5862</v>
       </c>
       <c r="L288" s="1" t="inlineStr">
         <is>
@@ -17587,10 +17587,10 @@
         <v>0</v>
       </c>
       <c r="J289" s="1" t="n">
-        <v>2400000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K289" s="1" t="n">
-        <v>1452</v>
+        <v>7621</v>
       </c>
       <c r="L289" s="1" t="inlineStr">
         <is>
@@ -17646,10 +17646,10 @@
         <v>0</v>
       </c>
       <c r="J290" s="1" t="n">
-        <v>2400000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K290" s="1" t="n">
-        <v>1452</v>
+        <v>7621</v>
       </c>
       <c r="L290" s="1" t="inlineStr">
         <is>
@@ -17705,10 +17705,10 @@
         <v>0</v>
       </c>
       <c r="J291" s="1" t="n">
-        <v>3100000000</v>
+        <v>5100000000</v>
       </c>
       <c r="K291" s="1" t="n">
-        <v>1887</v>
+        <v>9907</v>
       </c>
       <c r="L291" s="1" t="inlineStr">
         <is>
@@ -17764,10 +17764,10 @@
         <v>0</v>
       </c>
       <c r="J292" s="1" t="n">
-        <v>3100000000</v>
+        <v>5100000000</v>
       </c>
       <c r="K292" s="1" t="n">
-        <v>1887</v>
+        <v>9907</v>
       </c>
       <c r="L292" s="1" t="inlineStr">
         <is>
@@ -17823,10 +17823,10 @@
         <v>0</v>
       </c>
       <c r="J293" s="1" t="n">
-        <v>3100000000</v>
+        <v>5100000000</v>
       </c>
       <c r="K293" s="1" t="n">
-        <v>1887</v>
+        <v>9907</v>
       </c>
       <c r="L293" s="1" t="inlineStr">
         <is>
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="J294" s="1" t="n">
-        <v>7900000000</v>
+        <v>14000000000</v>
       </c>
       <c r="K294" s="1" t="n">
-        <v>4906</v>
+        <v>25757</v>
       </c>
       <c r="L294" s="1" t="inlineStr">
         <is>
@@ -17941,10 +17941,10 @@
         <v>0</v>
       </c>
       <c r="J295" s="1" t="n">
-        <v>1400000000</v>
+        <v>2300000000</v>
       </c>
       <c r="K295" s="1" t="n">
-        <v>859</v>
+        <v>4510</v>
       </c>
       <c r="L295" s="1" t="inlineStr">
         <is>
@@ -18000,10 +18000,10 @@
         <v>0</v>
       </c>
       <c r="J296" s="1" t="n">
-        <v>1800000000</v>
+        <v>3000000000</v>
       </c>
       <c r="K296" s="1" t="n">
-        <v>1117</v>
+        <v>5862</v>
       </c>
       <c r="L296" s="1" t="inlineStr">
         <is>
@@ -18059,10 +18059,10 @@
         <v>0</v>
       </c>
       <c r="J297" s="1" t="n">
-        <v>2400000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K297" s="1" t="n">
-        <v>1452</v>
+        <v>7621</v>
       </c>
       <c r="L297" s="1" t="inlineStr">
         <is>
@@ -18118,10 +18118,10 @@
         <v>0</v>
       </c>
       <c r="J298" s="1" t="n">
-        <v>2400000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K298" s="1" t="n">
-        <v>1452</v>
+        <v>7621</v>
       </c>
       <c r="L298" s="1" t="inlineStr">
         <is>
@@ -18177,10 +18177,10 @@
         <v>0</v>
       </c>
       <c r="J299" s="1" t="n">
-        <v>3100000000</v>
+        <v>5100000000</v>
       </c>
       <c r="K299" s="1" t="n">
-        <v>1887</v>
+        <v>9907</v>
       </c>
       <c r="L299" s="1" t="inlineStr">
         <is>
@@ -18236,10 +18236,10 @@
         <v>0</v>
       </c>
       <c r="J300" s="1" t="n">
-        <v>3100000000</v>
+        <v>5100000000</v>
       </c>
       <c r="K300" s="1" t="n">
-        <v>1887</v>
+        <v>9907</v>
       </c>
       <c r="L300" s="1" t="inlineStr">
         <is>
@@ -18295,10 +18295,10 @@
         <v>0</v>
       </c>
       <c r="J301" s="1" t="n">
-        <v>4000000000</v>
+        <v>6600000000</v>
       </c>
       <c r="K301" s="1" t="n">
-        <v>2453</v>
+        <v>12879</v>
       </c>
       <c r="L301" s="1" t="inlineStr">
         <is>
@@ -18354,10 +18354,10 @@
         <v>0</v>
       </c>
       <c r="J302" s="1" t="n">
-        <v>3600000000</v>
+        <v>6000000000</v>
       </c>
       <c r="K302" s="1" t="n">
-        <v>2233</v>
+        <v>11724</v>
       </c>
       <c r="L302" s="1" t="inlineStr">
         <is>
@@ -18413,10 +18413,10 @@
         <v>0</v>
       </c>
       <c r="J303" s="1" t="n">
-        <v>2400000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K303" s="1" t="n">
-        <v>1452</v>
+        <v>7621</v>
       </c>
       <c r="L303" s="1" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         <v>0</v>
       </c>
       <c r="J304" s="1" t="n">
-        <v>6100000000</v>
+        <v>11000000000</v>
       </c>
       <c r="K304" s="1" t="n">
-        <v>3774</v>
+        <v>19813</v>
       </c>
       <c r="L304" s="1" t="inlineStr">
         <is>
@@ -18531,10 +18531,10 @@
         <v>0</v>
       </c>
       <c r="J305" s="1" t="n">
-        <v>2400000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K305" s="1" t="n">
-        <v>1452</v>
+        <v>7621</v>
       </c>
       <c r="L305" s="1" t="inlineStr">
         <is>
@@ -18590,10 +18590,10 @@
         <v>0</v>
       </c>
       <c r="J306" s="1" t="n">
-        <v>4000000000</v>
+        <v>6600000000</v>
       </c>
       <c r="K306" s="1" t="n">
-        <v>2453</v>
+        <v>12879</v>
       </c>
       <c r="L306" s="1" t="inlineStr">
         <is>
@@ -18649,10 +18649,10 @@
         <v>0</v>
       </c>
       <c r="J307" s="1" t="n">
-        <v>3100000000</v>
+        <v>5100000000</v>
       </c>
       <c r="K307" s="1" t="n">
-        <v>1887</v>
+        <v>9907</v>
       </c>
       <c r="L307" s="1" t="inlineStr">
         <is>

--- a/Data_Table/공용 스킬 테이블.xlsx
+++ b/Data_Table/공용 스킬 테이블.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Common_Skill" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Branch" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Common_Effect_Type" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Column_Desc" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Common_Skill" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Common_Effect_Type" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1383,11 +1383,11 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +3초</t>
+          <t>층 제한시간 +2초</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2492110</v>
+        <v>2400001</v>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="N14" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>0</v>
@@ -1635,11 +1635,11 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +4초</t>
+          <t>층 제한시간 +2초</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2492114</v>
+        <v>2400001</v>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="N18" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>0</v>
@@ -3243,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M43" s="1" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         <v>0</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>21000</v>
+        <v>26000</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M44" s="1" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>52000</v>
+        <v>67000</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M45" s="1" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         <v>0</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M46" s="1" t="inlineStr">
         <is>
@@ -3495,10 +3495,10 @@
         <v>0</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>36000</v>
+        <v>47000</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M47" s="1" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -3621,10 +3621,10 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>36000</v>
+        <v>47000</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M49" s="1" t="inlineStr">
         <is>
@@ -3684,10 +3684,10 @@
         <v>0</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>36000</v>
+        <v>47000</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M50" s="1" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M51" s="1" t="inlineStr">
         <is>
@@ -3783,11 +3783,11 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +5초</t>
+          <t>층 제한시간 +2초</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>2492210</v>
+        <v>2400001</v>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>21000</v>
+        <v>26000</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M52" s="1" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="N52" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>0</v>
@@ -3873,10 +3873,10 @@
         <v>0</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M53" s="1" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         <v>0</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M54" s="1" t="inlineStr">
         <is>
@@ -3999,10 +3999,10 @@
         <v>0</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M55" s="1" t="inlineStr">
         <is>
@@ -4035,11 +4035,11 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +5초</t>
+          <t>층 제한시간 +2초</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>2492210</v>
+        <v>2400001</v>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>36000</v>
+        <v>47000</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M56" s="1" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="N56" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O56" s="1" t="n">
         <v>0</v>
@@ -4125,10 +4125,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>47000</v>
+        <v>57000</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M57" s="1" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>36000</v>
+        <v>47000</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M58" s="1" t="inlineStr">
         <is>
@@ -4251,10 +4251,10 @@
         <v>0</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M59" s="1" t="inlineStr">
         <is>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>21000</v>
+        <v>26000</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M60" s="1" t="inlineStr">
         <is>
@@ -4377,10 +4377,10 @@
         <v>0</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M61" s="1" t="inlineStr">
         <is>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M62" s="1" t="inlineStr">
         <is>
@@ -4503,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>36000</v>
+        <v>47000</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M63" s="1" t="inlineStr">
         <is>
@@ -4566,10 +4566,10 @@
         <v>0</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>67000</v>
+        <v>88000</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M64" s="1" t="inlineStr">
         <is>
@@ -4629,10 +4629,10 @@
         <v>0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>36000</v>
+        <v>47000</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M65" s="1" t="inlineStr">
         <is>
@@ -4692,10 +4692,10 @@
         <v>0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>88000</v>
+        <v>120000</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M66" s="1" t="inlineStr">
         <is>
@@ -4755,10 +4755,10 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>31000</v>
+        <v>41000</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M67" s="1" t="inlineStr">
         <is>
@@ -4818,10 +4818,10 @@
         <v>0</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>21000</v>
+        <v>26000</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M68" s="1" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         <v>0</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M69" s="1" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>0</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M70" s="1" t="inlineStr">
         <is>
@@ -5007,10 +5007,10 @@
         <v>0</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>36000</v>
+        <v>47000</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M71" s="1" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
         <v>0</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>36000</v>
+        <v>47000</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M72" s="1" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
         <v>0</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>47000</v>
+        <v>57000</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M73" s="1" t="inlineStr">
         <is>
@@ -5196,10 +5196,10 @@
         <v>0</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>41000</v>
+        <v>52000</v>
       </c>
       <c r="L74" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M74" s="1" t="inlineStr">
         <is>
@@ -5259,10 +5259,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="L75" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M75" s="1" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>67000</v>
+        <v>88000</v>
       </c>
       <c r="L76" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M76" s="1" t="inlineStr">
         <is>
@@ -5385,10 +5385,10 @@
         <v>0</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="L77" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M77" s="1" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
         <v>0</v>
       </c>
       <c r="K78" s="1" t="n">
-        <v>47000</v>
+        <v>57000</v>
       </c>
       <c r="L78" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M78" s="1" t="inlineStr">
         <is>
@@ -5511,10 +5511,10 @@
         <v>0</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>36000</v>
+        <v>47000</v>
       </c>
       <c r="L79" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M79" s="1" t="inlineStr">
         <is>
@@ -5643,10 +5643,10 @@
         <v>0</v>
       </c>
       <c r="K81" s="1" t="n">
-        <v>61000</v>
+        <v>73000</v>
       </c>
       <c r="L81" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M81" s="1" t="inlineStr">
         <is>
@@ -5706,10 +5706,10 @@
         <v>0</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>73000</v>
+        <v>97000</v>
       </c>
       <c r="L82" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M82" s="1" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
         <v>0</v>
       </c>
       <c r="K83" s="1" t="n">
-        <v>190000</v>
+        <v>250000</v>
       </c>
       <c r="L83" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M83" s="1" t="inlineStr">
         <is>
@@ -5832,10 +5832,10 @@
         <v>0</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>97000</v>
+        <v>130000</v>
       </c>
       <c r="L84" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M84" s="1" t="inlineStr">
         <is>
@@ -5895,10 +5895,10 @@
         <v>0</v>
       </c>
       <c r="K85" s="1" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="L85" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M85" s="1" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>97000</v>
+        <v>130000</v>
       </c>
       <c r="L86" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M86" s="1" t="inlineStr">
         <is>
@@ -6021,10 +6021,10 @@
         <v>0</v>
       </c>
       <c r="K87" s="1" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="L87" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M87" s="1" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>0</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="L88" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M88" s="1" t="inlineStr">
         <is>
@@ -6147,10 +6147,10 @@
         <v>0</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>61000</v>
+        <v>73000</v>
       </c>
       <c r="L89" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M89" s="1" t="inlineStr">
         <is>
@@ -6183,11 +6183,11 @@
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +6초</t>
+          <t>층 제한시간 +3초</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>2492310</v>
+        <v>2492110</v>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
@@ -6210,10 +6210,10 @@
         <v>0</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>73000</v>
+        <v>97000</v>
       </c>
       <c r="L90" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M90" s="1" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="N90" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O90" s="1" t="n">
         <v>0</v>
@@ -6273,10 +6273,10 @@
         <v>0</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>97000</v>
+        <v>130000</v>
       </c>
       <c r="L91" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M91" s="1" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         <v>0</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>97000</v>
+        <v>130000</v>
       </c>
       <c r="L92" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -6399,10 +6399,10 @@
         <v>0</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>97000</v>
+        <v>130000</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M93" s="1" t="inlineStr">
         <is>
@@ -6435,11 +6435,11 @@
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +6초</t>
+          <t>층 제한시간 +3초</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>2492310</v>
+        <v>2492110</v>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
@@ -6462,10 +6462,10 @@
         <v>0</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="L94" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M94" s="1" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="N94" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O94" s="1" t="n">
         <v>0</v>
@@ -6525,10 +6525,10 @@
         <v>0</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>160000</v>
+        <v>210000</v>
       </c>
       <c r="L95" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M95" s="1" t="inlineStr">
         <is>
@@ -6588,10 +6588,10 @@
         <v>0</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M96" s="1" t="inlineStr">
         <is>
@@ -6651,10 +6651,10 @@
         <v>0</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>61000</v>
+        <v>73000</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M97" s="1" t="inlineStr">
         <is>
@@ -6714,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>73000</v>
+        <v>97000</v>
       </c>
       <c r="L98" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M98" s="1" t="inlineStr">
         <is>
@@ -6777,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>97000</v>
+        <v>130000</v>
       </c>
       <c r="L99" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M99" s="1" t="inlineStr">
         <is>
@@ -6840,10 +6840,10 @@
         <v>0</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>97000</v>
+        <v>130000</v>
       </c>
       <c r="L100" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M100" s="1" t="inlineStr">
         <is>
@@ -6903,10 +6903,10 @@
         <v>0</v>
       </c>
       <c r="K101" s="1" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="L101" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M101" s="1" t="inlineStr">
         <is>
@@ -6966,10 +6966,10 @@
         <v>0</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>250000</v>
+        <v>310000</v>
       </c>
       <c r="L102" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M102" s="1" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="L103" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M103" s="1" t="inlineStr">
         <is>
@@ -7092,10 +7092,10 @@
         <v>0</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>320000</v>
+        <v>400000</v>
       </c>
       <c r="L104" s="1" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="M104" s="1" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         <v>0</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>110000</v>
+        <v>150000</v>
       </c>
       <c r="L105" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M105" s="1" t="inlineStr">
         <is>
@@ -7218,10 +7218,10 @@
         <v>0</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>73000</v>
+        <v>97000</v>
       </c>
       <c r="L106" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M106" s="1" t="inlineStr">
         <is>
@@ -7281,10 +7281,10 @@
         <v>0</v>
       </c>
       <c r="K107" s="1" t="n">
-        <v>97000</v>
+        <v>130000</v>
       </c>
       <c r="L107" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M107" s="1" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>0</v>
       </c>
       <c r="K108" s="1" t="n">
-        <v>97000</v>
+        <v>130000</v>
       </c>
       <c r="L108" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M108" s="1" t="inlineStr">
         <is>
@@ -7407,10 +7407,10 @@
         <v>0</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="L109" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M109" s="1" t="inlineStr">
         <is>
@@ -7470,10 +7470,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="L110" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M110" s="1" t="inlineStr">
         <is>
@@ -7533,10 +7533,10 @@
         <v>0</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>160000</v>
+        <v>210000</v>
       </c>
       <c r="L111" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M111" s="1" t="inlineStr">
         <is>
@@ -7596,10 +7596,10 @@
         <v>0</v>
       </c>
       <c r="K112" s="1" t="n">
-        <v>150000</v>
+        <v>190000</v>
       </c>
       <c r="L112" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M112" s="1" t="inlineStr">
         <is>
@@ -7659,10 +7659,10 @@
         <v>0</v>
       </c>
       <c r="K113" s="1" t="n">
-        <v>190000</v>
+        <v>250000</v>
       </c>
       <c r="L113" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M113" s="1" t="inlineStr">
         <is>
@@ -7722,10 +7722,10 @@
         <v>0</v>
       </c>
       <c r="K114" s="1" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="L114" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M114" s="1" t="inlineStr">
         <is>
@@ -7785,10 +7785,10 @@
         <v>0</v>
       </c>
       <c r="K115" s="1" t="n">
-        <v>97000</v>
+        <v>130000</v>
       </c>
       <c r="L115" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M115" s="1" t="inlineStr">
         <is>
@@ -7848,10 +7848,10 @@
         <v>0</v>
       </c>
       <c r="K116" s="1" t="n">
-        <v>160000</v>
+        <v>210000</v>
       </c>
       <c r="L116" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M116" s="1" t="inlineStr">
         <is>
@@ -7911,10 +7911,10 @@
         <v>0</v>
       </c>
       <c r="K117" s="1" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="L117" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M117" s="1" t="inlineStr">
         <is>
@@ -8043,10 +8043,10 @@
         <v>0</v>
       </c>
       <c r="K119" s="1" t="n">
-        <v>210000</v>
+        <v>260000</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M119" s="1" t="inlineStr">
         <is>
@@ -8106,10 +8106,10 @@
         <v>0</v>
       </c>
       <c r="K120" s="1" t="n">
-        <v>260000</v>
+        <v>340000</v>
       </c>
       <c r="L120" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M120" s="1" t="inlineStr">
         <is>
@@ -8169,10 +8169,10 @@
         <v>0</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M121" s="1" t="inlineStr">
         <is>
@@ -8232,10 +8232,10 @@
         <v>0</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M122" s="1" t="inlineStr">
         <is>
@@ -8295,10 +8295,10 @@
         <v>0</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>450000</v>
+        <v>550000</v>
       </c>
       <c r="L123" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M123" s="1" t="inlineStr">
         <is>
@@ -8358,10 +8358,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M124" s="1" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>0</v>
       </c>
       <c r="K125" s="1" t="n">
-        <v>450000</v>
+        <v>550000</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M125" s="1" t="inlineStr">
         <is>
@@ -8484,10 +8484,10 @@
         <v>0</v>
       </c>
       <c r="K126" s="1" t="n">
-        <v>450000</v>
+        <v>550000</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M126" s="1" t="inlineStr">
         <is>
@@ -8547,10 +8547,10 @@
         <v>0</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>210000</v>
+        <v>260000</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M127" s="1" t="inlineStr">
         <is>
@@ -8583,11 +8583,11 @@
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +7초</t>
+          <t>층 제한시간 +4초</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>2492410</v>
+        <v>2492114</v>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
@@ -8610,10 +8610,10 @@
         <v>0</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>260000</v>
+        <v>340000</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M128" s="1" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="N128" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O128" s="1" t="n">
         <v>0</v>
@@ -8673,10 +8673,10 @@
         <v>0</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M129" s="1" t="inlineStr">
         <is>
@@ -8736,10 +8736,10 @@
         <v>0</v>
       </c>
       <c r="K130" s="1" t="n">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="L130" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M130" s="1" t="inlineStr">
         <is>
@@ -8799,10 +8799,10 @@
         <v>0</v>
       </c>
       <c r="K131" s="1" t="n">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M131" s="1" t="inlineStr">
         <is>
@@ -8835,11 +8835,11 @@
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +7초</t>
+          <t>층 제한시간 +4초</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>2492410</v>
+        <v>2492114</v>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
@@ -8862,10 +8862,10 @@
         <v>0</v>
       </c>
       <c r="K132" s="1" t="n">
-        <v>450000</v>
+        <v>550000</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M132" s="1" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="N132" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O132" s="1" t="n">
         <v>0</v>
@@ -8925,10 +8925,10 @@
         <v>0</v>
       </c>
       <c r="K133" s="1" t="n">
-        <v>550000</v>
+        <v>730000</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="M133" s="1" t="inlineStr">
         <is>
@@ -8988,10 +8988,10 @@
         <v>0</v>
       </c>
       <c r="K134" s="1" t="n">
-        <v>450000</v>
+        <v>550000</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M134" s="1" t="inlineStr">
         <is>
@@ -9051,10 +9051,10 @@
         <v>0</v>
       </c>
       <c r="K135" s="1" t="n">
-        <v>210000</v>
+        <v>260000</v>
       </c>
       <c r="L135" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M135" s="1" t="inlineStr">
         <is>
@@ -9114,10 +9114,10 @@
         <v>0</v>
       </c>
       <c r="K136" s="1" t="n">
-        <v>260000</v>
+        <v>340000</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M136" s="1" t="inlineStr">
         <is>
@@ -9177,10 +9177,10 @@
         <v>0</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M137" s="1" t="inlineStr">
         <is>
@@ -9240,10 +9240,10 @@
         <v>0</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M138" s="1" t="inlineStr">
         <is>
@@ -9303,10 +9303,10 @@
         <v>0</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>450000</v>
+        <v>550000</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M139" s="1" t="inlineStr">
         <is>
@@ -9366,10 +9366,10 @@
         <v>0</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>860000</v>
+        <v>1100000</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="M140" s="1" t="inlineStr">
         <is>
@@ -9429,10 +9429,10 @@
         <v>0</v>
       </c>
       <c r="K141" s="1" t="n">
-        <v>450000</v>
+        <v>550000</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M141" s="1" t="inlineStr">
         <is>
@@ -9492,10 +9492,10 @@
         <v>0</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>1100000</v>
+        <v>1500000</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="M142" s="1" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         <v>0</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>390000</v>
+        <v>520000</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M143" s="1" t="inlineStr">
         <is>
@@ -9618,10 +9618,10 @@
         <v>0</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>260000</v>
+        <v>340000</v>
       </c>
       <c r="L144" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M144" s="1" t="inlineStr">
         <is>
@@ -9681,10 +9681,10 @@
         <v>0</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="L145" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M145" s="1" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>0</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M146" s="1" t="inlineStr">
         <is>
@@ -9807,10 +9807,10 @@
         <v>0</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>450000</v>
+        <v>550000</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M147" s="1" t="inlineStr">
         <is>
@@ -9870,10 +9870,10 @@
         <v>0</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>450000</v>
+        <v>550000</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M148" s="1" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>550000</v>
+        <v>730000</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="M149" s="1" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>520000</v>
+        <v>650000</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M150" s="1" t="inlineStr">
         <is>
@@ -10032,11 +10032,11 @@
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>필살기 쿨타임 -3초</t>
+          <t>필살기 게이지 충전 +15%</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>2492433</v>
+        <v>2492236</v>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
@@ -10059,18 +10059,18 @@
         <v>0</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M151" s="1" t="inlineStr">
         <is>
-          <t>Ult_CD</t>
+          <t>Ult_Gauge_Pct</t>
         </is>
       </c>
       <c r="N151" s="1" t="n">
-        <v>3</v>
+        <v>0.15</v>
       </c>
       <c r="O151" s="1" t="n">
         <v>0</v>
@@ -10122,10 +10122,10 @@
         <v>0</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>860000</v>
+        <v>1100000</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="M152" s="1" t="inlineStr">
         <is>
@@ -10185,10 +10185,10 @@
         <v>0</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M153" s="1" t="inlineStr">
         <is>
@@ -10248,10 +10248,10 @@
         <v>0</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>550000</v>
+        <v>730000</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="M154" s="1" t="inlineStr">
         <is>
@@ -10311,10 +10311,10 @@
         <v>0</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>450000</v>
+        <v>550000</v>
       </c>
       <c r="L155" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M155" s="1" t="inlineStr">
         <is>
@@ -10443,10 +10443,10 @@
         <v>0</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>710000</v>
+        <v>870000</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M157" s="1" t="inlineStr">
         <is>
@@ -10506,10 +10506,10 @@
         <v>0</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>870000</v>
+        <v>1200000</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M158" s="1" t="inlineStr">
         <is>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M159" s="1" t="inlineStr">
         <is>
@@ -10632,10 +10632,10 @@
         <v>0</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="L160" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M160" s="1" t="inlineStr">
         <is>
@@ -10695,10 +10695,10 @@
         <v>0</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="L161" s="1" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M161" s="1" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>0</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="L162" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M162" s="1" t="inlineStr">
         <is>
@@ -10821,10 +10821,10 @@
         <v>0</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="L163" s="1" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M163" s="1" t="inlineStr">
         <is>
@@ -10884,10 +10884,10 @@
         <v>0</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="L164" s="1" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M164" s="1" t="inlineStr">
         <is>
@@ -10947,10 +10947,10 @@
         <v>0</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>710000</v>
+        <v>870000</v>
       </c>
       <c r="L165" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M165" s="1" t="inlineStr">
         <is>
@@ -10983,11 +10983,11 @@
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +8초</t>
+          <t>층 제한시간 +4초</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>2492510</v>
+        <v>2492114</v>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         <v>0</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>870000</v>
+        <v>1200000</v>
       </c>
       <c r="L166" s="1" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M166" s="1" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="N166" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O166" s="1" t="n">
         <v>0</v>
@@ -11073,10 +11073,10 @@
         <v>0</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="L167" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M167" s="1" t="inlineStr">
         <is>
@@ -11136,10 +11136,10 @@
         <v>0</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="L168" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M168" s="1" t="inlineStr">
         <is>
@@ -11199,10 +11199,10 @@
         <v>0</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="L169" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M169" s="1" t="inlineStr">
         <is>
@@ -11235,11 +11235,11 @@
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +8초</t>
+          <t>층 제한시간 +4초</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>2492510</v>
+        <v>2492114</v>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
@@ -11262,10 +11262,10 @@
         <v>0</v>
       </c>
       <c r="K170" s="1" t="n">
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="L170" s="1" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M170" s="1" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         </is>
       </c>
       <c r="N170" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O170" s="1" t="n">
         <v>0</v>
@@ -11325,10 +11325,10 @@
         <v>0</v>
       </c>
       <c r="K171" s="1" t="n">
-        <v>1900000</v>
+        <v>2500000</v>
       </c>
       <c r="L171" s="1" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="M171" s="1" t="inlineStr">
         <is>
@@ -11388,10 +11388,10 @@
         <v>0</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="L172" s="1" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M172" s="1" t="inlineStr">
         <is>
@@ -11451,10 +11451,10 @@
         <v>0</v>
       </c>
       <c r="K173" s="1" t="n">
-        <v>710000</v>
+        <v>870000</v>
       </c>
       <c r="L173" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M173" s="1" t="inlineStr">
         <is>
@@ -11514,10 +11514,10 @@
         <v>0</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>870000</v>
+        <v>1200000</v>
       </c>
       <c r="L174" s="1" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M174" s="1" t="inlineStr">
         <is>
@@ -11577,10 +11577,10 @@
         <v>0</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="L175" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M175" s="1" t="inlineStr">
         <is>
@@ -11640,10 +11640,10 @@
         <v>0</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="L176" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M176" s="1" t="inlineStr">
         <is>
@@ -11703,10 +11703,10 @@
         <v>0</v>
       </c>
       <c r="K177" s="1" t="n">
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="L177" s="1" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M177" s="1" t="inlineStr">
         <is>
@@ -11766,10 +11766,10 @@
         <v>0</v>
       </c>
       <c r="K178" s="1" t="n">
-        <v>3000000</v>
+        <v>3800000</v>
       </c>
       <c r="L178" s="1" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="M178" s="1" t="inlineStr">
         <is>
@@ -11829,10 +11829,10 @@
         <v>0</v>
       </c>
       <c r="K179" s="1" t="n">
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="L179" s="1" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M179" s="1" t="inlineStr">
         <is>
@@ -11892,10 +11892,10 @@
         <v>0</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>3800000</v>
+        <v>4900000</v>
       </c>
       <c r="L180" s="1" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="M180" s="1" t="inlineStr">
         <is>
@@ -11955,10 +11955,10 @@
         <v>0</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>1400000</v>
+        <v>1800000</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M181" s="1" t="inlineStr">
         <is>
@@ -12018,10 +12018,10 @@
         <v>0</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>870000</v>
+        <v>1200000</v>
       </c>
       <c r="L182" s="1" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M182" s="1" t="inlineStr">
         <is>
@@ -12081,10 +12081,10 @@
         <v>0</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="L183" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M183" s="1" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>0</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="L184" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M184" s="1" t="inlineStr">
         <is>
@@ -12207,10 +12207,10 @@
         <v>0</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="L185" s="1" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M185" s="1" t="inlineStr">
         <is>
@@ -12270,10 +12270,10 @@
         <v>0</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="L186" s="1" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M186" s="1" t="inlineStr">
         <is>
@@ -12333,10 +12333,10 @@
         <v>0</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>1900000</v>
+        <v>2500000</v>
       </c>
       <c r="L187" s="1" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="M187" s="1" t="inlineStr">
         <is>
@@ -12396,10 +12396,10 @@
         <v>0</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>1800000</v>
+        <v>2300000</v>
       </c>
       <c r="L188" s="1" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="M188" s="1" t="inlineStr">
         <is>
@@ -12459,10 +12459,10 @@
         <v>0</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>2300000</v>
+        <v>3000000</v>
       </c>
       <c r="L189" s="1" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="M189" s="1" t="inlineStr">
         <is>
@@ -12522,10 +12522,10 @@
         <v>0</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="L190" s="1" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M190" s="1" t="inlineStr">
         <is>
@@ -12585,10 +12585,10 @@
         <v>0</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="L191" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M191" s="1" t="inlineStr">
         <is>
@@ -12648,10 +12648,10 @@
         <v>0</v>
       </c>
       <c r="K192" s="1" t="n">
-        <v>1900000</v>
+        <v>2500000</v>
       </c>
       <c r="L192" s="1" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="M192" s="1" t="inlineStr">
         <is>
@@ -12711,10 +12711,10 @@
         <v>0</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="L193" s="1" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M193" s="1" t="inlineStr">
         <is>
@@ -12843,10 +12843,10 @@
         <v>0</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>3400000</v>
+        <v>3000000</v>
       </c>
       <c r="L195" s="1" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M195" s="1" t="inlineStr">
         <is>
@@ -12906,10 +12906,10 @@
         <v>0</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>4300000</v>
+        <v>3900000</v>
       </c>
       <c r="L196" s="1" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M196" s="1" t="inlineStr">
         <is>
@@ -12969,10 +12969,10 @@
         <v>0</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="L197" s="1" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M197" s="1" t="inlineStr">
         <is>
@@ -13032,10 +13032,10 @@
         <v>0</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="L198" s="1" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M198" s="1" t="inlineStr">
         <is>
@@ -13095,10 +13095,10 @@
         <v>0</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>7300000</v>
+        <v>6500000</v>
       </c>
       <c r="L199" s="1" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="M199" s="1" t="inlineStr">
         <is>
@@ -13158,10 +13158,10 @@
         <v>0</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="L200" s="1" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M200" s="1" t="inlineStr">
         <is>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>7300000</v>
+        <v>6500000</v>
       </c>
       <c r="L201" s="1" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="M201" s="1" t="inlineStr">
         <is>
@@ -13284,10 +13284,10 @@
         <v>0</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>7300000</v>
+        <v>6500000</v>
       </c>
       <c r="L202" s="1" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="M202" s="1" t="inlineStr">
         <is>
@@ -13347,10 +13347,10 @@
         <v>0</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>3400000</v>
+        <v>3000000</v>
       </c>
       <c r="L203" s="1" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M203" s="1" t="inlineStr">
         <is>
@@ -13383,11 +13383,11 @@
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +9초</t>
+          <t>층 제한시간 +4초</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>2492610</v>
+        <v>2492114</v>
       </c>
       <c r="E204" s="1" t="inlineStr">
         <is>
@@ -13410,10 +13410,10 @@
         <v>0</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>4300000</v>
+        <v>3900000</v>
       </c>
       <c r="L204" s="1" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M204" s="1" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="N204" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O204" s="1" t="n">
         <v>0</v>
@@ -13473,10 +13473,10 @@
         <v>0</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="L205" s="1" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M205" s="1" t="inlineStr">
         <is>
@@ -13536,10 +13536,10 @@
         <v>0</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="L206" s="1" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M206" s="1" t="inlineStr">
         <is>
@@ -13599,10 +13599,10 @@
         <v>0</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="L207" s="1" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M207" s="1" t="inlineStr">
         <is>
@@ -13635,11 +13635,11 @@
       </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +9초</t>
+          <t>층 제한시간 +4초</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>2492610</v>
+        <v>2492114</v>
       </c>
       <c r="E208" s="1" t="inlineStr">
         <is>
@@ -13662,10 +13662,10 @@
         <v>0</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>7300000</v>
+        <v>6500000</v>
       </c>
       <c r="L208" s="1" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="M208" s="1" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="N208" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O208" s="1" t="n">
         <v>0</v>
@@ -13725,10 +13725,10 @@
         <v>0</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>9400000</v>
+        <v>8500000</v>
       </c>
       <c r="L209" s="1" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="M209" s="1" t="inlineStr">
         <is>
@@ -13788,10 +13788,10 @@
         <v>0</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>7300000</v>
+        <v>6500000</v>
       </c>
       <c r="L210" s="1" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="M210" s="1" t="inlineStr">
         <is>
@@ -13851,10 +13851,10 @@
         <v>0</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>3400000</v>
+        <v>3000000</v>
       </c>
       <c r="L211" s="1" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M211" s="1" t="inlineStr">
         <is>
@@ -13914,10 +13914,10 @@
         <v>0</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>4300000</v>
+        <v>3900000</v>
       </c>
       <c r="L212" s="1" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M212" s="1" t="inlineStr">
         <is>
@@ -13977,10 +13977,10 @@
         <v>0</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="L213" s="1" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M213" s="1" t="inlineStr">
         <is>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="L214" s="1" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M214" s="1" t="inlineStr">
         <is>
@@ -14103,10 +14103,10 @@
         <v>0</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>7300000</v>
+        <v>6500000</v>
       </c>
       <c r="L215" s="1" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="M215" s="1" t="inlineStr">
         <is>
@@ -14166,10 +14166,10 @@
         <v>0</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>15000000</v>
+        <v>13000000</v>
       </c>
       <c r="L216" s="1" t="n">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="M216" s="1" t="inlineStr">
         <is>
@@ -14229,10 +14229,10 @@
         <v>0</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>7300000</v>
+        <v>6500000</v>
       </c>
       <c r="L217" s="1" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="M217" s="1" t="inlineStr">
         <is>
@@ -14292,10 +14292,10 @@
         <v>0</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>19000000</v>
+        <v>17000000</v>
       </c>
       <c r="L218" s="1" t="n">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="M218" s="1" t="inlineStr">
         <is>
@@ -14355,10 +14355,10 @@
         <v>0</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>3400000</v>
+        <v>3000000</v>
       </c>
       <c r="L219" s="1" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M219" s="1" t="inlineStr">
         <is>
@@ -14418,10 +14418,10 @@
         <v>0</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>4300000</v>
+        <v>3900000</v>
       </c>
       <c r="L220" s="1" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M220" s="1" t="inlineStr">
         <is>
@@ -14481,10 +14481,10 @@
         <v>0</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="L221" s="1" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M221" s="1" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>0</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="L222" s="1" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M222" s="1" t="inlineStr">
         <is>
@@ -14607,10 +14607,10 @@
         <v>0</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>7300000</v>
+        <v>6500000</v>
       </c>
       <c r="L223" s="1" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="M223" s="1" t="inlineStr">
         <is>
@@ -14670,10 +14670,10 @@
         <v>0</v>
       </c>
       <c r="K224" s="1" t="n">
-        <v>7300000</v>
+        <v>6500000</v>
       </c>
       <c r="L224" s="1" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="M224" s="1" t="inlineStr">
         <is>
@@ -14733,10 +14733,10 @@
         <v>0</v>
       </c>
       <c r="K225" s="1" t="n">
-        <v>9400000</v>
+        <v>8500000</v>
       </c>
       <c r="L225" s="1" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="M225" s="1" t="inlineStr">
         <is>
@@ -14796,10 +14796,10 @@
         <v>0</v>
       </c>
       <c r="K226" s="1" t="n">
-        <v>8600000</v>
+        <v>7700000</v>
       </c>
       <c r="L226" s="1" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M226" s="1" t="inlineStr">
         <is>
@@ -14859,10 +14859,10 @@
         <v>0</v>
       </c>
       <c r="K227" s="1" t="n">
-        <v>12000000</v>
+        <v>10000000</v>
       </c>
       <c r="L227" s="1" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="M227" s="1" t="inlineStr">
         <is>
@@ -14922,10 +14922,10 @@
         <v>0</v>
       </c>
       <c r="K228" s="1" t="n">
-        <v>15000000</v>
+        <v>13000000</v>
       </c>
       <c r="L228" s="1" t="n">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="M228" s="1" t="inlineStr">
         <is>
@@ -14985,10 +14985,10 @@
         <v>0</v>
       </c>
       <c r="K229" s="1" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="L229" s="1" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M229" s="1" t="inlineStr">
         <is>
@@ -15048,10 +15048,10 @@
         <v>0</v>
       </c>
       <c r="K230" s="1" t="n">
-        <v>9400000</v>
+        <v>8500000</v>
       </c>
       <c r="L230" s="1" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="M230" s="1" t="inlineStr">
         <is>
@@ -15084,11 +15084,11 @@
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t>필살기 쿨타임 -3초</t>
+          <t>필살기 게이지 충전 +20%</t>
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>2492433</v>
+        <v>2493037</v>
       </c>
       <c r="E231" s="1" t="inlineStr">
         <is>
@@ -15111,18 +15111,18 @@
         <v>0</v>
       </c>
       <c r="K231" s="1" t="n">
-        <v>7300000</v>
+        <v>6500000</v>
       </c>
       <c r="L231" s="1" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="M231" s="1" t="inlineStr">
         <is>
-          <t>Ult_CD</t>
+          <t>Ult_Gauge_Pct</t>
         </is>
       </c>
       <c r="N231" s="1" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="O231" s="1" t="n">
         <v>0</v>
@@ -15243,10 +15243,10 @@
         <v>0</v>
       </c>
       <c r="K233" s="1" t="n">
-        <v>32000000</v>
+        <v>48000000</v>
       </c>
       <c r="L233" s="1" t="n">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="M233" s="1" t="inlineStr">
         <is>
@@ -15306,10 +15306,10 @@
         <v>0</v>
       </c>
       <c r="K234" s="1" t="n">
-        <v>41000000</v>
+        <v>62000000</v>
       </c>
       <c r="L234" s="1" t="n">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="M234" s="1" t="inlineStr">
         <is>
@@ -15369,10 +15369,10 @@
         <v>0</v>
       </c>
       <c r="K235" s="1" t="n">
-        <v>53000000</v>
+        <v>80000000</v>
       </c>
       <c r="L235" s="1" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="M235" s="1" t="inlineStr">
         <is>
@@ -15432,10 +15432,10 @@
         <v>0</v>
       </c>
       <c r="K236" s="1" t="n">
-        <v>53000000</v>
+        <v>80000000</v>
       </c>
       <c r="L236" s="1" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="M236" s="1" t="inlineStr">
         <is>
@@ -15495,10 +15495,10 @@
         <v>0</v>
       </c>
       <c r="K237" s="1" t="n">
-        <v>69000000</v>
+        <v>110000000</v>
       </c>
       <c r="L237" s="1" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M237" s="1" t="inlineStr">
         <is>
@@ -15558,10 +15558,10 @@
         <v>0</v>
       </c>
       <c r="K238" s="1" t="n">
-        <v>53000000</v>
+        <v>80000000</v>
       </c>
       <c r="L238" s="1" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="M238" s="1" t="inlineStr">
         <is>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="K239" s="1" t="n">
-        <v>69000000</v>
+        <v>110000000</v>
       </c>
       <c r="L239" s="1" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M239" s="1" t="inlineStr">
         <is>
@@ -15684,10 +15684,10 @@
         <v>0</v>
       </c>
       <c r="K240" s="1" t="n">
-        <v>69000000</v>
+        <v>110000000</v>
       </c>
       <c r="L240" s="1" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M240" s="1" t="inlineStr">
         <is>
@@ -15747,10 +15747,10 @@
         <v>0</v>
       </c>
       <c r="K241" s="1" t="n">
-        <v>32000000</v>
+        <v>48000000</v>
       </c>
       <c r="L241" s="1" t="n">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="M241" s="1" t="inlineStr">
         <is>
@@ -15783,11 +15783,11 @@
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +10초</t>
+          <t>층 제한시간 +5초</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>2492710</v>
+        <v>2492210</v>
       </c>
       <c r="E242" s="1" t="inlineStr">
         <is>
@@ -15810,10 +15810,10 @@
         <v>0</v>
       </c>
       <c r="K242" s="1" t="n">
-        <v>41000000</v>
+        <v>62000000</v>
       </c>
       <c r="L242" s="1" t="n">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="M242" s="1" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         </is>
       </c>
       <c r="N242" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O242" s="1" t="n">
         <v>0</v>
@@ -15873,10 +15873,10 @@
         <v>0</v>
       </c>
       <c r="K243" s="1" t="n">
-        <v>53000000</v>
+        <v>80000000</v>
       </c>
       <c r="L243" s="1" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="M243" s="1" t="inlineStr">
         <is>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="K244" s="1" t="n">
-        <v>53000000</v>
+        <v>80000000</v>
       </c>
       <c r="L244" s="1" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="M244" s="1" t="inlineStr">
         <is>
@@ -15999,10 +15999,10 @@
         <v>0</v>
       </c>
       <c r="K245" s="1" t="n">
-        <v>53000000</v>
+        <v>80000000</v>
       </c>
       <c r="L245" s="1" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="M245" s="1" t="inlineStr">
         <is>
@@ -16035,11 +16035,11 @@
       </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +10초</t>
+          <t>층 제한시간 +5초</t>
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>2492710</v>
+        <v>2492210</v>
       </c>
       <c r="E246" s="1" t="inlineStr">
         <is>
@@ -16062,10 +16062,10 @@
         <v>0</v>
       </c>
       <c r="K246" s="1" t="n">
-        <v>69000000</v>
+        <v>110000000</v>
       </c>
       <c r="L246" s="1" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M246" s="1" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="N246" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O246" s="1" t="n">
         <v>0</v>
@@ -16125,10 +16125,10 @@
         <v>0</v>
       </c>
       <c r="K247" s="1" t="n">
-        <v>89000000</v>
+        <v>140000000</v>
       </c>
       <c r="L247" s="1" t="n">
-        <v>375</v>
+        <v>338</v>
       </c>
       <c r="M247" s="1" t="inlineStr">
         <is>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="K248" s="1" t="n">
-        <v>69000000</v>
+        <v>110000000</v>
       </c>
       <c r="L248" s="1" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M248" s="1" t="inlineStr">
         <is>
@@ -16251,10 +16251,10 @@
         <v>0</v>
       </c>
       <c r="K249" s="1" t="n">
-        <v>32000000</v>
+        <v>48000000</v>
       </c>
       <c r="L249" s="1" t="n">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="M249" s="1" t="inlineStr">
         <is>
@@ -16314,10 +16314,10 @@
         <v>0</v>
       </c>
       <c r="K250" s="1" t="n">
-        <v>41000000</v>
+        <v>62000000</v>
       </c>
       <c r="L250" s="1" t="n">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="M250" s="1" t="inlineStr">
         <is>
@@ -16377,10 +16377,10 @@
         <v>0</v>
       </c>
       <c r="K251" s="1" t="n">
-        <v>53000000</v>
+        <v>80000000</v>
       </c>
       <c r="L251" s="1" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="M251" s="1" t="inlineStr">
         <is>
@@ -16440,10 +16440,10 @@
         <v>0</v>
       </c>
       <c r="K252" s="1" t="n">
-        <v>53000000</v>
+        <v>80000000</v>
       </c>
       <c r="L252" s="1" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="M252" s="1" t="inlineStr">
         <is>
@@ -16503,10 +16503,10 @@
         <v>0</v>
       </c>
       <c r="K253" s="1" t="n">
-        <v>69000000</v>
+        <v>110000000</v>
       </c>
       <c r="L253" s="1" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M253" s="1" t="inlineStr">
         <is>
@@ -16566,10 +16566,10 @@
         <v>0</v>
       </c>
       <c r="K254" s="1" t="n">
-        <v>69000000</v>
+        <v>110000000</v>
       </c>
       <c r="L254" s="1" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M254" s="1" t="inlineStr">
         <is>
@@ -16629,10 +16629,10 @@
         <v>0</v>
       </c>
       <c r="K255" s="1" t="n">
-        <v>69000000</v>
+        <v>110000000</v>
       </c>
       <c r="L255" s="1" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M255" s="1" t="inlineStr">
         <is>
@@ -16692,10 +16692,10 @@
         <v>0</v>
       </c>
       <c r="K256" s="1" t="n">
-        <v>180000000</v>
+        <v>270000000</v>
       </c>
       <c r="L256" s="1" t="n">
-        <v>750</v>
+        <v>675</v>
       </c>
       <c r="M256" s="1" t="inlineStr">
         <is>
@@ -16755,10 +16755,10 @@
         <v>0</v>
       </c>
       <c r="K257" s="1" t="n">
-        <v>32000000</v>
+        <v>48000000</v>
       </c>
       <c r="L257" s="1" t="n">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="M257" s="1" t="inlineStr">
         <is>
@@ -16818,10 +16818,10 @@
         <v>0</v>
       </c>
       <c r="K258" s="1" t="n">
-        <v>41000000</v>
+        <v>62000000</v>
       </c>
       <c r="L258" s="1" t="n">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="M258" s="1" t="inlineStr">
         <is>
@@ -16881,10 +16881,10 @@
         <v>0</v>
       </c>
       <c r="K259" s="1" t="n">
-        <v>53000000</v>
+        <v>80000000</v>
       </c>
       <c r="L259" s="1" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="M259" s="1" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>0</v>
       </c>
       <c r="K260" s="1" t="n">
-        <v>53000000</v>
+        <v>80000000</v>
       </c>
       <c r="L260" s="1" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="M260" s="1" t="inlineStr">
         <is>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="K261" s="1" t="n">
-        <v>69000000</v>
+        <v>110000000</v>
       </c>
       <c r="L261" s="1" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M261" s="1" t="inlineStr">
         <is>
@@ -17070,10 +17070,10 @@
         <v>0</v>
       </c>
       <c r="K262" s="1" t="n">
-        <v>69000000</v>
+        <v>110000000</v>
       </c>
       <c r="L262" s="1" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M262" s="1" t="inlineStr">
         <is>
@@ -17133,10 +17133,10 @@
         <v>0</v>
       </c>
       <c r="K263" s="1" t="n">
-        <v>89000000</v>
+        <v>140000000</v>
       </c>
       <c r="L263" s="1" t="n">
-        <v>375</v>
+        <v>338</v>
       </c>
       <c r="M263" s="1" t="inlineStr">
         <is>
@@ -17196,10 +17196,10 @@
         <v>0</v>
       </c>
       <c r="K264" s="1" t="n">
-        <v>82000000</v>
+        <v>130000000</v>
       </c>
       <c r="L264" s="1" t="n">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="M264" s="1" t="inlineStr">
         <is>
@@ -17259,10 +17259,10 @@
         <v>0</v>
       </c>
       <c r="K265" s="1" t="n">
-        <v>53000000</v>
+        <v>80000000</v>
       </c>
       <c r="L265" s="1" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="M265" s="1" t="inlineStr">
         <is>
@@ -17322,10 +17322,10 @@
         <v>0</v>
       </c>
       <c r="K266" s="1" t="n">
-        <v>69000000</v>
+        <v>110000000</v>
       </c>
       <c r="L266" s="1" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M266" s="1" t="inlineStr">
         <is>
@@ -17385,10 +17385,10 @@
         <v>0</v>
       </c>
       <c r="K267" s="1" t="n">
-        <v>53000000</v>
+        <v>80000000</v>
       </c>
       <c r="L267" s="1" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="M267" s="1" t="inlineStr">
         <is>
@@ -17448,10 +17448,10 @@
         <v>0</v>
       </c>
       <c r="K268" s="1" t="n">
-        <v>89000000</v>
+        <v>140000000</v>
       </c>
       <c r="L268" s="1" t="n">
-        <v>375</v>
+        <v>338</v>
       </c>
       <c r="M268" s="1" t="inlineStr">
         <is>
@@ -17511,10 +17511,10 @@
         <v>0</v>
       </c>
       <c r="K269" s="1" t="n">
-        <v>69000000</v>
+        <v>110000000</v>
       </c>
       <c r="L269" s="1" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="M269" s="1" t="inlineStr">
         <is>
@@ -17643,10 +17643,10 @@
         <v>0</v>
       </c>
       <c r="K271" s="1" t="n">
-        <v>2300000000</v>
+        <v>2500000000</v>
       </c>
       <c r="L271" s="1" t="n">
-        <v>4510</v>
+        <v>1271</v>
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
@@ -17706,10 +17706,10 @@
         <v>0</v>
       </c>
       <c r="K272" s="1" t="n">
-        <v>3000000000</v>
+        <v>3200000000</v>
       </c>
       <c r="L272" s="1" t="n">
-        <v>5862</v>
+        <v>1652</v>
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
@@ -17769,10 +17769,10 @@
         <v>0</v>
       </c>
       <c r="K273" s="1" t="n">
-        <v>3900000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L273" s="1" t="n">
-        <v>7621</v>
+        <v>2148</v>
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
@@ -17832,10 +17832,10 @@
         <v>0</v>
       </c>
       <c r="K274" s="1" t="n">
-        <v>3900000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L274" s="1" t="n">
-        <v>7621</v>
+        <v>2148</v>
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
@@ -17895,10 +17895,10 @@
         <v>0</v>
       </c>
       <c r="K275" s="1" t="n">
-        <v>5100000000</v>
+        <v>5400000000</v>
       </c>
       <c r="L275" s="1" t="n">
-        <v>9907</v>
+        <v>2792</v>
       </c>
       <c r="M275" s="1" t="inlineStr">
         <is>
@@ -17958,10 +17958,10 @@
         <v>0</v>
       </c>
       <c r="K276" s="1" t="n">
-        <v>3900000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L276" s="1" t="n">
-        <v>7621</v>
+        <v>2148</v>
       </c>
       <c r="M276" s="1" t="inlineStr">
         <is>
@@ -18021,10 +18021,10 @@
         <v>0</v>
       </c>
       <c r="K277" s="1" t="n">
-        <v>5100000000</v>
+        <v>5400000000</v>
       </c>
       <c r="L277" s="1" t="n">
-        <v>9907</v>
+        <v>2792</v>
       </c>
       <c r="M277" s="1" t="inlineStr">
         <is>
@@ -18084,10 +18084,10 @@
         <v>0</v>
       </c>
       <c r="K278" s="1" t="n">
-        <v>5100000000</v>
+        <v>5400000000</v>
       </c>
       <c r="L278" s="1" t="n">
-        <v>9907</v>
+        <v>2792</v>
       </c>
       <c r="M278" s="1" t="inlineStr">
         <is>
@@ -18147,10 +18147,10 @@
         <v>0</v>
       </c>
       <c r="K279" s="1" t="n">
-        <v>2300000000</v>
+        <v>2500000000</v>
       </c>
       <c r="L279" s="1" t="n">
-        <v>4510</v>
+        <v>1271</v>
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
@@ -18183,11 +18183,11 @@
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +11초</t>
+          <t>층 제한시간 +6초</t>
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>2492810</v>
+        <v>2492310</v>
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
@@ -18210,10 +18210,10 @@
         <v>0</v>
       </c>
       <c r="K280" s="1" t="n">
-        <v>3000000000</v>
+        <v>3200000000</v>
       </c>
       <c r="L280" s="1" t="n">
-        <v>5862</v>
+        <v>1652</v>
       </c>
       <c r="M280" s="1" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         </is>
       </c>
       <c r="N280" s="1" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O280" s="1" t="n">
         <v>0</v>
@@ -18273,10 +18273,10 @@
         <v>0</v>
       </c>
       <c r="K281" s="1" t="n">
-        <v>3900000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L281" s="1" t="n">
-        <v>7621</v>
+        <v>2148</v>
       </c>
       <c r="M281" s="1" t="inlineStr">
         <is>
@@ -18336,10 +18336,10 @@
         <v>0</v>
       </c>
       <c r="K282" s="1" t="n">
-        <v>3900000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L282" s="1" t="n">
-        <v>7621</v>
+        <v>2148</v>
       </c>
       <c r="M282" s="1" t="inlineStr">
         <is>
@@ -18399,10 +18399,10 @@
         <v>0</v>
       </c>
       <c r="K283" s="1" t="n">
-        <v>3900000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L283" s="1" t="n">
-        <v>7621</v>
+        <v>2148</v>
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
@@ -18435,11 +18435,11 @@
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +12초</t>
+          <t>층 제한시간 +6초</t>
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>2492814</v>
+        <v>2492310</v>
       </c>
       <c r="E284" s="1" t="inlineStr">
         <is>
@@ -18462,10 +18462,10 @@
         <v>0</v>
       </c>
       <c r="K284" s="1" t="n">
-        <v>5100000000</v>
+        <v>5400000000</v>
       </c>
       <c r="L284" s="1" t="n">
-        <v>9907</v>
+        <v>2792</v>
       </c>
       <c r="M284" s="1" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         </is>
       </c>
       <c r="N284" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O284" s="1" t="n">
         <v>0</v>
@@ -18525,10 +18525,10 @@
         <v>0</v>
       </c>
       <c r="K285" s="1" t="n">
-        <v>6600000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L285" s="1" t="n">
-        <v>12879</v>
+        <v>3629</v>
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
@@ -18588,10 +18588,10 @@
         <v>0</v>
       </c>
       <c r="K286" s="1" t="n">
-        <v>5100000000</v>
+        <v>5400000000</v>
       </c>
       <c r="L286" s="1" t="n">
-        <v>9907</v>
+        <v>2792</v>
       </c>
       <c r="M286" s="1" t="inlineStr">
         <is>
@@ -18651,10 +18651,10 @@
         <v>0</v>
       </c>
       <c r="K287" s="1" t="n">
-        <v>2300000000</v>
+        <v>2500000000</v>
       </c>
       <c r="L287" s="1" t="n">
-        <v>4510</v>
+        <v>1271</v>
       </c>
       <c r="M287" s="1" t="inlineStr">
         <is>
@@ -18714,10 +18714,10 @@
         <v>0</v>
       </c>
       <c r="K288" s="1" t="n">
-        <v>3000000000</v>
+        <v>3200000000</v>
       </c>
       <c r="L288" s="1" t="n">
-        <v>5862</v>
+        <v>1652</v>
       </c>
       <c r="M288" s="1" t="inlineStr">
         <is>
@@ -18777,10 +18777,10 @@
         <v>0</v>
       </c>
       <c r="K289" s="1" t="n">
-        <v>3900000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L289" s="1" t="n">
-        <v>7621</v>
+        <v>2148</v>
       </c>
       <c r="M289" s="1" t="inlineStr">
         <is>
@@ -18840,10 +18840,10 @@
         <v>0</v>
       </c>
       <c r="K290" s="1" t="n">
-        <v>3900000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L290" s="1" t="n">
-        <v>7621</v>
+        <v>2148</v>
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
@@ -18903,10 +18903,10 @@
         <v>0</v>
       </c>
       <c r="K291" s="1" t="n">
-        <v>5100000000</v>
+        <v>5400000000</v>
       </c>
       <c r="L291" s="1" t="n">
-        <v>9907</v>
+        <v>2792</v>
       </c>
       <c r="M291" s="1" t="inlineStr">
         <is>
@@ -18966,10 +18966,10 @@
         <v>0</v>
       </c>
       <c r="K292" s="1" t="n">
-        <v>5100000000</v>
+        <v>5400000000</v>
       </c>
       <c r="L292" s="1" t="n">
-        <v>9907</v>
+        <v>2792</v>
       </c>
       <c r="M292" s="1" t="inlineStr">
         <is>
@@ -19029,10 +19029,10 @@
         <v>0</v>
       </c>
       <c r="K293" s="1" t="n">
-        <v>5100000000</v>
+        <v>5400000000</v>
       </c>
       <c r="L293" s="1" t="n">
-        <v>9907</v>
+        <v>2792</v>
       </c>
       <c r="M293" s="1" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>14000000000</v>
       </c>
       <c r="L294" s="1" t="n">
-        <v>25757</v>
+        <v>7258</v>
       </c>
       <c r="M294" s="1" t="inlineStr">
         <is>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="K295" s="1" t="n">
-        <v>2300000000</v>
+        <v>2500000000</v>
       </c>
       <c r="L295" s="1" t="n">
-        <v>4510</v>
+        <v>1271</v>
       </c>
       <c r="M295" s="1" t="inlineStr">
         <is>
@@ -19218,10 +19218,10 @@
         <v>0</v>
       </c>
       <c r="K296" s="1" t="n">
-        <v>3000000000</v>
+        <v>3200000000</v>
       </c>
       <c r="L296" s="1" t="n">
-        <v>5862</v>
+        <v>1652</v>
       </c>
       <c r="M296" s="1" t="inlineStr">
         <is>
@@ -19281,10 +19281,10 @@
         <v>0</v>
       </c>
       <c r="K297" s="1" t="n">
-        <v>3900000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L297" s="1" t="n">
-        <v>7621</v>
+        <v>2148</v>
       </c>
       <c r="M297" s="1" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>0</v>
       </c>
       <c r="K298" s="1" t="n">
-        <v>3900000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L298" s="1" t="n">
-        <v>7621</v>
+        <v>2148</v>
       </c>
       <c r="M298" s="1" t="inlineStr">
         <is>
@@ -19407,10 +19407,10 @@
         <v>0</v>
       </c>
       <c r="K299" s="1" t="n">
-        <v>5100000000</v>
+        <v>5400000000</v>
       </c>
       <c r="L299" s="1" t="n">
-        <v>9907</v>
+        <v>2792</v>
       </c>
       <c r="M299" s="1" t="inlineStr">
         <is>
@@ -19470,10 +19470,10 @@
         <v>0</v>
       </c>
       <c r="K300" s="1" t="n">
-        <v>5100000000</v>
+        <v>5400000000</v>
       </c>
       <c r="L300" s="1" t="n">
-        <v>9907</v>
+        <v>2792</v>
       </c>
       <c r="M300" s="1" t="inlineStr">
         <is>
@@ -19533,10 +19533,10 @@
         <v>0</v>
       </c>
       <c r="K301" s="1" t="n">
-        <v>6600000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L301" s="1" t="n">
-        <v>12879</v>
+        <v>3629</v>
       </c>
       <c r="M301" s="1" t="inlineStr">
         <is>
@@ -19596,10 +19596,10 @@
         <v>0</v>
       </c>
       <c r="K302" s="1" t="n">
-        <v>6000000000</v>
+        <v>6300000000</v>
       </c>
       <c r="L302" s="1" t="n">
-        <v>11724</v>
+        <v>3304</v>
       </c>
       <c r="M302" s="1" t="inlineStr">
         <is>
@@ -19632,11 +19632,11 @@
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t>필살기 쿨타임 -4초</t>
+          <t>필살기 게이지 충전 +20%</t>
         </is>
       </c>
       <c r="D303" s="1" t="n">
-        <v>2492833</v>
+        <v>2493037</v>
       </c>
       <c r="E303" s="1" t="inlineStr">
         <is>
@@ -19659,18 +19659,18 @@
         <v>0</v>
       </c>
       <c r="K303" s="1" t="n">
-        <v>3900000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L303" s="1" t="n">
-        <v>7621</v>
+        <v>2148</v>
       </c>
       <c r="M303" s="1" t="inlineStr">
         <is>
-          <t>Ult_CD</t>
+          <t>Ult_Gauge_Pct</t>
         </is>
       </c>
       <c r="N303" s="1" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="O303" s="1" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
         <v>11000000000</v>
       </c>
       <c r="L304" s="1" t="n">
-        <v>19813</v>
+        <v>5583</v>
       </c>
       <c r="M304" s="1" t="inlineStr">
         <is>
@@ -19785,10 +19785,10 @@
         <v>0</v>
       </c>
       <c r="K305" s="1" t="n">
-        <v>3900000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L305" s="1" t="n">
-        <v>7621</v>
+        <v>2148</v>
       </c>
       <c r="M305" s="1" t="inlineStr">
         <is>
@@ -19848,10 +19848,10 @@
         <v>0</v>
       </c>
       <c r="K306" s="1" t="n">
-        <v>6600000000</v>
+        <v>7000000000</v>
       </c>
       <c r="L306" s="1" t="n">
-        <v>12879</v>
+        <v>3629</v>
       </c>
       <c r="M306" s="1" t="inlineStr">
         <is>
@@ -19911,10 +19911,10 @@
         <v>0</v>
       </c>
       <c r="K307" s="1" t="n">
-        <v>5100000000</v>
+        <v>5400000000</v>
       </c>
       <c r="L307" s="1" t="n">
-        <v>9907</v>
+        <v>2792</v>
       </c>
       <c r="M307" s="1" t="inlineStr">
         <is>
@@ -20043,10 +20043,10 @@
         <v>0</v>
       </c>
       <c r="K309" s="1" t="n">
-        <v>1900000000000</v>
+        <v>5100000000</v>
       </c>
       <c r="L309" s="1" t="n">
-        <v>2890667</v>
+        <v>1160</v>
       </c>
       <c r="M309" s="1" t="inlineStr">
         <is>
@@ -20106,10 +20106,10 @@
         <v>0</v>
       </c>
       <c r="K310" s="1" t="n">
-        <v>2400000000000</v>
+        <v>6600000000</v>
       </c>
       <c r="L310" s="1" t="n">
-        <v>3757867</v>
+        <v>1508</v>
       </c>
       <c r="M310" s="1" t="inlineStr">
         <is>
@@ -20169,10 +20169,10 @@
         <v>0</v>
       </c>
       <c r="K311" s="1" t="n">
-        <v>3100000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="L311" s="1" t="n">
-        <v>4885227</v>
+        <v>1961</v>
       </c>
       <c r="M311" s="1" t="inlineStr">
         <is>
@@ -20232,10 +20232,10 @@
         <v>0</v>
       </c>
       <c r="K312" s="1" t="n">
-        <v>3100000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="L312" s="1" t="n">
-        <v>4885227</v>
+        <v>1961</v>
       </c>
       <c r="M312" s="1" t="inlineStr">
         <is>
@@ -20295,10 +20295,10 @@
         <v>0</v>
       </c>
       <c r="K313" s="1" t="n">
-        <v>4100000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="L313" s="1" t="n">
-        <v>6350795</v>
+        <v>2549</v>
       </c>
       <c r="M313" s="1" t="inlineStr">
         <is>
@@ -20358,10 +20358,10 @@
         <v>0</v>
       </c>
       <c r="K314" s="1" t="n">
-        <v>3100000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="L314" s="1" t="n">
-        <v>4885227</v>
+        <v>1961</v>
       </c>
       <c r="M314" s="1" t="inlineStr">
         <is>
@@ -20421,10 +20421,10 @@
         <v>0</v>
       </c>
       <c r="K315" s="1" t="n">
-        <v>4100000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="L315" s="1" t="n">
-        <v>6350795</v>
+        <v>2549</v>
       </c>
       <c r="M315" s="1" t="inlineStr">
         <is>
@@ -20484,10 +20484,10 @@
         <v>0</v>
       </c>
       <c r="K316" s="1" t="n">
-        <v>4100000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="L316" s="1" t="n">
-        <v>6350795</v>
+        <v>2549</v>
       </c>
       <c r="M316" s="1" t="inlineStr">
         <is>
@@ -20547,10 +20547,10 @@
         <v>0</v>
       </c>
       <c r="K317" s="1" t="n">
-        <v>3700000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="L317" s="1" t="n">
-        <v>5781334</v>
+        <v>2320</v>
       </c>
       <c r="M317" s="1" t="inlineStr">
         <is>
@@ -20583,11 +20583,11 @@
       </c>
       <c r="C318" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +12초</t>
+          <t>생명체 처치 치즈 +60%</t>
         </is>
       </c>
       <c r="D318" s="1" t="n">
-        <v>2492814</v>
+        <v>2492521</v>
       </c>
       <c r="E318" s="1" t="inlineStr">
         <is>
@@ -20610,28 +20610,28 @@
         <v>0</v>
       </c>
       <c r="K318" s="1" t="n">
-        <v>2400000000000</v>
+        <v>6600000000</v>
       </c>
       <c r="L318" s="1" t="n">
-        <v>3757867</v>
+        <v>1508</v>
       </c>
       <c r="M318" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Cheese_Pct</t>
         </is>
       </c>
       <c r="N318" s="1" t="n">
-        <v>12</v>
+        <v>0.6</v>
       </c>
       <c r="O318" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P318" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q318" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_cheesecreature</t>
         </is>
       </c>
       <c r="R318" s="1" t="inlineStr"/>
@@ -20673,10 +20673,10 @@
         <v>0</v>
       </c>
       <c r="K319" s="1" t="n">
-        <v>3100000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="L319" s="1" t="n">
-        <v>4885227</v>
+        <v>1961</v>
       </c>
       <c r="M319" s="1" t="inlineStr">
         <is>
@@ -20736,10 +20736,10 @@
         <v>0</v>
       </c>
       <c r="K320" s="1" t="n">
-        <v>3100000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="L320" s="1" t="n">
-        <v>4885227</v>
+        <v>1961</v>
       </c>
       <c r="M320" s="1" t="inlineStr">
         <is>
@@ -20799,10 +20799,10 @@
         <v>0</v>
       </c>
       <c r="K321" s="1" t="n">
-        <v>3100000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="L321" s="1" t="n">
-        <v>4885227</v>
+        <v>1961</v>
       </c>
       <c r="M321" s="1" t="inlineStr">
         <is>
@@ -20835,11 +20835,11 @@
       </c>
       <c r="C322" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +13초</t>
+          <t>황금 물건 확률 +3%</t>
         </is>
       </c>
       <c r="D322" s="1" t="n">
-        <v>2492914</v>
+        <v>2492423</v>
       </c>
       <c r="E322" s="1" t="inlineStr">
         <is>
@@ -20862,18 +20862,18 @@
         <v>0</v>
       </c>
       <c r="K322" s="1" t="n">
-        <v>4100000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="L322" s="1" t="n">
-        <v>6350795</v>
+        <v>2549</v>
       </c>
       <c r="M322" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Gold_Item</t>
         </is>
       </c>
       <c r="N322" s="1" t="n">
-        <v>13</v>
+        <v>0.03</v>
       </c>
       <c r="O322" s="1" t="n">
         <v>0</v>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="Q322" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_goldx</t>
         </is>
       </c>
       <c r="R322" s="1" t="inlineStr"/>
@@ -20925,10 +20925,10 @@
         <v>0</v>
       </c>
       <c r="K323" s="1" t="n">
-        <v>5300000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="L323" s="1" t="n">
-        <v>8256034</v>
+        <v>3314</v>
       </c>
       <c r="M323" s="1" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
         <v>0</v>
       </c>
       <c r="K324" s="1" t="n">
-        <v>4100000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="L324" s="1" t="n">
-        <v>6350795</v>
+        <v>2549</v>
       </c>
       <c r="M324" s="1" t="inlineStr">
         <is>
@@ -21051,10 +21051,10 @@
         <v>0</v>
       </c>
       <c r="K325" s="1" t="n">
-        <v>1900000000000</v>
+        <v>5100000000</v>
       </c>
       <c r="L325" s="1" t="n">
-        <v>2890667</v>
+        <v>1160</v>
       </c>
       <c r="M325" s="1" t="inlineStr">
         <is>
@@ -21114,10 +21114,10 @@
         <v>0</v>
       </c>
       <c r="K326" s="1" t="n">
-        <v>2400000000000</v>
+        <v>6600000000</v>
       </c>
       <c r="L326" s="1" t="n">
-        <v>3757867</v>
+        <v>1508</v>
       </c>
       <c r="M326" s="1" t="inlineStr">
         <is>
@@ -21177,10 +21177,10 @@
         <v>0</v>
       </c>
       <c r="K327" s="1" t="n">
-        <v>3100000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="L327" s="1" t="n">
-        <v>4885227</v>
+        <v>1961</v>
       </c>
       <c r="M327" s="1" t="inlineStr">
         <is>
@@ -21240,10 +21240,10 @@
         <v>0</v>
       </c>
       <c r="K328" s="1" t="n">
-        <v>3100000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="L328" s="1" t="n">
-        <v>4885227</v>
+        <v>1961</v>
       </c>
       <c r="M328" s="1" t="inlineStr">
         <is>
@@ -21303,10 +21303,10 @@
         <v>0</v>
       </c>
       <c r="K329" s="1" t="n">
-        <v>4100000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="L329" s="1" t="n">
-        <v>6350795</v>
+        <v>2549</v>
       </c>
       <c r="M329" s="1" t="inlineStr">
         <is>
@@ -21366,10 +21366,10 @@
         <v>0</v>
       </c>
       <c r="K330" s="1" t="n">
-        <v>4100000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="L330" s="1" t="n">
-        <v>6350795</v>
+        <v>2549</v>
       </c>
       <c r="M330" s="1" t="inlineStr">
         <is>
@@ -21429,10 +21429,10 @@
         <v>0</v>
       </c>
       <c r="K331" s="1" t="n">
-        <v>4100000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="L331" s="1" t="n">
-        <v>6350795</v>
+        <v>2549</v>
       </c>
       <c r="M331" s="1" t="inlineStr">
         <is>
@@ -21492,10 +21492,10 @@
         <v>0</v>
       </c>
       <c r="K332" s="1" t="n">
-        <v>5300000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="L332" s="1" t="n">
-        <v>8256034</v>
+        <v>3314</v>
       </c>
       <c r="M332" s="1" t="inlineStr">
         <is>
@@ -21555,10 +21555,10 @@
         <v>0</v>
       </c>
       <c r="K333" s="1" t="n">
-        <v>1900000000000</v>
+        <v>5100000000</v>
       </c>
       <c r="L333" s="1" t="n">
-        <v>2890667</v>
+        <v>1160</v>
       </c>
       <c r="M333" s="1" t="inlineStr">
         <is>
@@ -21618,10 +21618,10 @@
         <v>0</v>
       </c>
       <c r="K334" s="1" t="n">
-        <v>2400000000000</v>
+        <v>6600000000</v>
       </c>
       <c r="L334" s="1" t="n">
-        <v>3757867</v>
+        <v>1508</v>
       </c>
       <c r="M334" s="1" t="inlineStr">
         <is>
@@ -21681,10 +21681,10 @@
         <v>0</v>
       </c>
       <c r="K335" s="1" t="n">
-        <v>3100000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="L335" s="1" t="n">
-        <v>4885227</v>
+        <v>1961</v>
       </c>
       <c r="M335" s="1" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>0</v>
       </c>
       <c r="K336" s="1" t="n">
-        <v>3100000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="L336" s="1" t="n">
-        <v>4885227</v>
+        <v>1961</v>
       </c>
       <c r="M336" s="1" t="inlineStr">
         <is>
@@ -21807,10 +21807,10 @@
         <v>0</v>
       </c>
       <c r="K337" s="1" t="n">
-        <v>4100000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="L337" s="1" t="n">
-        <v>6350795</v>
+        <v>2549</v>
       </c>
       <c r="M337" s="1" t="inlineStr">
         <is>
@@ -21870,10 +21870,10 @@
         <v>0</v>
       </c>
       <c r="K338" s="1" t="n">
-        <v>4100000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="L338" s="1" t="n">
-        <v>6350795</v>
+        <v>2549</v>
       </c>
       <c r="M338" s="1" t="inlineStr">
         <is>
@@ -21933,10 +21933,10 @@
         <v>0</v>
       </c>
       <c r="K339" s="1" t="n">
-        <v>5300000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="L339" s="1" t="n">
-        <v>8256034</v>
+        <v>3314</v>
       </c>
       <c r="M339" s="1" t="inlineStr">
         <is>
@@ -21969,11 +21969,11 @@
       </c>
       <c r="C340" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +7층</t>
         </is>
       </c>
       <c r="D340" s="1" t="n">
-        <v>2492332</v>
+        <v>2493532</v>
       </c>
       <c r="E340" s="1" t="inlineStr">
         <is>
@@ -21996,10 +21996,10 @@
         <v>0</v>
       </c>
       <c r="K340" s="1" t="n">
-        <v>4800000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L340" s="1" t="n">
-        <v>7515734</v>
+        <v>3016</v>
       </c>
       <c r="M340" s="1" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         </is>
       </c>
       <c r="N340" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O340" s="1" t="n">
         <v>0</v>
@@ -22032,11 +22032,11 @@
       </c>
       <c r="C341" s="1" t="inlineStr">
         <is>
-          <t>필살기 쿨타임 -4초</t>
+          <t>필살기 게이지 충전 +20%</t>
         </is>
       </c>
       <c r="D341" s="1" t="n">
-        <v>2492833</v>
+        <v>2493037</v>
       </c>
       <c r="E341" s="1" t="inlineStr">
         <is>
@@ -22059,18 +22059,18 @@
         <v>0</v>
       </c>
       <c r="K341" s="1" t="n">
-        <v>3100000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="L341" s="1" t="n">
-        <v>4885227</v>
+        <v>1961</v>
       </c>
       <c r="M341" s="1" t="inlineStr">
         <is>
-          <t>Ult_CD</t>
+          <t>Ult_Gauge_Pct</t>
         </is>
       </c>
       <c r="N341" s="1" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="O341" s="1" t="n">
         <v>0</v>
@@ -22095,11 +22095,11 @@
       </c>
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +6층</t>
         </is>
       </c>
       <c r="D342" s="1" t="n">
-        <v>2492132</v>
+        <v>2492934</v>
       </c>
       <c r="E342" s="1" t="inlineStr">
         <is>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="K342" s="1" t="n">
-        <v>8100000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="L342" s="1" t="n">
-        <v>12701590</v>
+        <v>5098</v>
       </c>
       <c r="M342" s="1" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         </is>
       </c>
       <c r="N342" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O342" s="1" t="n">
         <v>0</v>
@@ -22185,10 +22185,10 @@
         <v>0</v>
       </c>
       <c r="K343" s="1" t="n">
-        <v>3100000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="L343" s="1" t="n">
-        <v>4885227</v>
+        <v>1961</v>
       </c>
       <c r="M343" s="1" t="inlineStr">
         <is>
@@ -22248,10 +22248,10 @@
         <v>0</v>
       </c>
       <c r="K344" s="1" t="n">
-        <v>5300000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="L344" s="1" t="n">
-        <v>8256034</v>
+        <v>3314</v>
       </c>
       <c r="M344" s="1" t="inlineStr">
         <is>
@@ -22311,10 +22311,10 @@
         <v>0</v>
       </c>
       <c r="K345" s="1" t="n">
-        <v>4100000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="L345" s="1" t="n">
-        <v>6350795</v>
+        <v>2549</v>
       </c>
       <c r="M345" s="1" t="inlineStr">
         <is>
@@ -22443,10 +22443,10 @@
         <v>0</v>
       </c>
       <c r="K347" s="1" t="n">
-        <v>6900000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="L347" s="1" t="n">
-        <v>8640000</v>
+        <v>4374</v>
       </c>
       <c r="M347" s="1" t="inlineStr">
         <is>
@@ -22506,10 +22506,10 @@
         <v>0</v>
       </c>
       <c r="K348" s="1" t="n">
-        <v>8900000000000</v>
+        <v>34000000000</v>
       </c>
       <c r="L348" s="1" t="n">
-        <v>11232000</v>
+        <v>5686</v>
       </c>
       <c r="M348" s="1" t="inlineStr">
         <is>
@@ -22569,10 +22569,10 @@
         <v>0</v>
       </c>
       <c r="K349" s="1" t="n">
-        <v>12000000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="L349" s="1" t="n">
-        <v>14601601</v>
+        <v>7391</v>
       </c>
       <c r="M349" s="1" t="inlineStr">
         <is>
@@ -22632,10 +22632,10 @@
         <v>0</v>
       </c>
       <c r="K350" s="1" t="n">
-        <v>12000000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="L350" s="1" t="n">
-        <v>14601601</v>
+        <v>7391</v>
       </c>
       <c r="M350" s="1" t="inlineStr">
         <is>
@@ -22695,10 +22695,10 @@
         <v>0</v>
       </c>
       <c r="K351" s="1" t="n">
-        <v>16000000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="L351" s="1" t="n">
-        <v>18982080</v>
+        <v>9609</v>
       </c>
       <c r="M351" s="1" t="inlineStr">
         <is>
@@ -22758,10 +22758,10 @@
         <v>0</v>
       </c>
       <c r="K352" s="1" t="n">
-        <v>12000000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="L352" s="1" t="n">
-        <v>14601601</v>
+        <v>7391</v>
       </c>
       <c r="M352" s="1" t="inlineStr">
         <is>
@@ -22821,10 +22821,10 @@
         <v>0</v>
       </c>
       <c r="K353" s="1" t="n">
-        <v>16000000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="L353" s="1" t="n">
-        <v>18982080</v>
+        <v>9609</v>
       </c>
       <c r="M353" s="1" t="inlineStr">
         <is>
@@ -22884,10 +22884,10 @@
         <v>0</v>
       </c>
       <c r="K354" s="1" t="n">
-        <v>16000000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="L354" s="1" t="n">
-        <v>18982080</v>
+        <v>9609</v>
       </c>
       <c r="M354" s="1" t="inlineStr">
         <is>
@@ -22947,10 +22947,10 @@
         <v>0</v>
       </c>
       <c r="K355" s="1" t="n">
-        <v>6900000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="L355" s="1" t="n">
-        <v>8640000</v>
+        <v>4374</v>
       </c>
       <c r="M355" s="1" t="inlineStr">
         <is>
@@ -22983,11 +22983,11 @@
       </c>
       <c r="C356" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +13초</t>
+          <t>생명체 처치 치즈 +70%</t>
         </is>
       </c>
       <c r="D356" s="1" t="n">
-        <v>2492914</v>
+        <v>2492621</v>
       </c>
       <c r="E356" s="1" t="inlineStr">
         <is>
@@ -23010,28 +23010,28 @@
         <v>0</v>
       </c>
       <c r="K356" s="1" t="n">
-        <v>8900000000000</v>
+        <v>34000000000</v>
       </c>
       <c r="L356" s="1" t="n">
-        <v>11232000</v>
+        <v>5686</v>
       </c>
       <c r="M356" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Cheese_Pct</t>
         </is>
       </c>
       <c r="N356" s="1" t="n">
-        <v>13</v>
+        <v>0.7</v>
       </c>
       <c r="O356" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P356" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q356" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_cheesecreature</t>
         </is>
       </c>
       <c r="R356" s="1" t="inlineStr"/>
@@ -23073,10 +23073,10 @@
         <v>0</v>
       </c>
       <c r="K357" s="1" t="n">
-        <v>12000000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="L357" s="1" t="n">
-        <v>14601601</v>
+        <v>7391</v>
       </c>
       <c r="M357" s="1" t="inlineStr">
         <is>
@@ -23136,10 +23136,10 @@
         <v>0</v>
       </c>
       <c r="K358" s="1" t="n">
-        <v>12000000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="L358" s="1" t="n">
-        <v>14601601</v>
+        <v>7391</v>
       </c>
       <c r="M358" s="1" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         <v>0</v>
       </c>
       <c r="K359" s="1" t="n">
-        <v>12000000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="L359" s="1" t="n">
-        <v>14601601</v>
+        <v>7391</v>
       </c>
       <c r="M359" s="1" t="inlineStr">
         <is>
@@ -23235,11 +23235,11 @@
       </c>
       <c r="C360" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +14초</t>
+          <t>황금 물건 확률 +3%</t>
         </is>
       </c>
       <c r="D360" s="1" t="n">
-        <v>2493014</v>
+        <v>2492423</v>
       </c>
       <c r="E360" s="1" t="inlineStr">
         <is>
@@ -23262,18 +23262,18 @@
         <v>0</v>
       </c>
       <c r="K360" s="1" t="n">
-        <v>16000000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="L360" s="1" t="n">
-        <v>18982080</v>
+        <v>9609</v>
       </c>
       <c r="M360" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Gold_Item</t>
         </is>
       </c>
       <c r="N360" s="1" t="n">
-        <v>14</v>
+        <v>0.03</v>
       </c>
       <c r="O360" s="1" t="n">
         <v>0</v>
@@ -23283,7 +23283,7 @@
       </c>
       <c r="Q360" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_goldx</t>
         </is>
       </c>
       <c r="R360" s="1" t="inlineStr"/>
@@ -23325,10 +23325,10 @@
         <v>0</v>
       </c>
       <c r="K361" s="1" t="n">
-        <v>20000000000000</v>
+        <v>74000000000</v>
       </c>
       <c r="L361" s="1" t="n">
-        <v>24676705</v>
+        <v>12491</v>
       </c>
       <c r="M361" s="1" t="inlineStr">
         <is>
@@ -23388,10 +23388,10 @@
         <v>0</v>
       </c>
       <c r="K362" s="1" t="n">
-        <v>16000000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="L362" s="1" t="n">
-        <v>18982080</v>
+        <v>9609</v>
       </c>
       <c r="M362" s="1" t="inlineStr">
         <is>
@@ -23451,10 +23451,10 @@
         <v>0</v>
       </c>
       <c r="K363" s="1" t="n">
-        <v>6900000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="L363" s="1" t="n">
-        <v>8640000</v>
+        <v>4374</v>
       </c>
       <c r="M363" s="1" t="inlineStr">
         <is>
@@ -23514,10 +23514,10 @@
         <v>0</v>
       </c>
       <c r="K364" s="1" t="n">
-        <v>8900000000000</v>
+        <v>34000000000</v>
       </c>
       <c r="L364" s="1" t="n">
-        <v>11232000</v>
+        <v>5686</v>
       </c>
       <c r="M364" s="1" t="inlineStr">
         <is>
@@ -23577,10 +23577,10 @@
         <v>0</v>
       </c>
       <c r="K365" s="1" t="n">
-        <v>12000000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="L365" s="1" t="n">
-        <v>14601601</v>
+        <v>7391</v>
       </c>
       <c r="M365" s="1" t="inlineStr">
         <is>
@@ -23640,10 +23640,10 @@
         <v>0</v>
       </c>
       <c r="K366" s="1" t="n">
-        <v>12000000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="L366" s="1" t="n">
-        <v>14601601</v>
+        <v>7391</v>
       </c>
       <c r="M366" s="1" t="inlineStr">
         <is>
@@ -23703,10 +23703,10 @@
         <v>0</v>
       </c>
       <c r="K367" s="1" t="n">
-        <v>16000000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="L367" s="1" t="n">
-        <v>18982080</v>
+        <v>9609</v>
       </c>
       <c r="M367" s="1" t="inlineStr">
         <is>
@@ -23766,10 +23766,10 @@
         <v>0</v>
       </c>
       <c r="K368" s="1" t="n">
-        <v>16000000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="L368" s="1" t="n">
-        <v>18982080</v>
+        <v>9609</v>
       </c>
       <c r="M368" s="1" t="inlineStr">
         <is>
@@ -23829,10 +23829,10 @@
         <v>0</v>
       </c>
       <c r="K369" s="1" t="n">
-        <v>16000000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="L369" s="1" t="n">
-        <v>18982080</v>
+        <v>9609</v>
       </c>
       <c r="M369" s="1" t="inlineStr">
         <is>
@@ -23892,10 +23892,10 @@
         <v>0</v>
       </c>
       <c r="K370" s="1" t="n">
-        <v>20000000000000</v>
+        <v>74000000000</v>
       </c>
       <c r="L370" s="1" t="n">
-        <v>24676705</v>
+        <v>12491</v>
       </c>
       <c r="M370" s="1" t="inlineStr">
         <is>
@@ -23955,10 +23955,10 @@
         <v>0</v>
       </c>
       <c r="K371" s="1" t="n">
-        <v>6900000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="L371" s="1" t="n">
-        <v>8640000</v>
+        <v>4374</v>
       </c>
       <c r="M371" s="1" t="inlineStr">
         <is>
@@ -24018,10 +24018,10 @@
         <v>0</v>
       </c>
       <c r="K372" s="1" t="n">
-        <v>8900000000000</v>
+        <v>34000000000</v>
       </c>
       <c r="L372" s="1" t="n">
-        <v>11232000</v>
+        <v>5686</v>
       </c>
       <c r="M372" s="1" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="K373" s="1" t="n">
-        <v>12000000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="L373" s="1" t="n">
-        <v>14601601</v>
+        <v>7391</v>
       </c>
       <c r="M373" s="1" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>0</v>
       </c>
       <c r="K374" s="1" t="n">
-        <v>12000000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="L374" s="1" t="n">
-        <v>14601601</v>
+        <v>7391</v>
       </c>
       <c r="M374" s="1" t="inlineStr">
         <is>
@@ -24207,10 +24207,10 @@
         <v>0</v>
       </c>
       <c r="K375" s="1" t="n">
-        <v>16000000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="L375" s="1" t="n">
-        <v>18982080</v>
+        <v>9609</v>
       </c>
       <c r="M375" s="1" t="inlineStr">
         <is>
@@ -24270,10 +24270,10 @@
         <v>0</v>
       </c>
       <c r="K376" s="1" t="n">
-        <v>16000000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="L376" s="1" t="n">
-        <v>18982080</v>
+        <v>9609</v>
       </c>
       <c r="M376" s="1" t="inlineStr">
         <is>
@@ -24333,10 +24333,10 @@
         <v>0</v>
       </c>
       <c r="K377" s="1" t="n">
-        <v>20000000000000</v>
+        <v>74000000000</v>
       </c>
       <c r="L377" s="1" t="n">
-        <v>24676705</v>
+        <v>12491</v>
       </c>
       <c r="M377" s="1" t="inlineStr">
         <is>
@@ -24369,11 +24369,11 @@
       </c>
       <c r="C378" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D378" s="1" t="n">
-        <v>2492332</v>
+        <v>2493332</v>
       </c>
       <c r="E378" s="1" t="inlineStr">
         <is>
@@ -24396,10 +24396,10 @@
         <v>0</v>
       </c>
       <c r="K378" s="1" t="n">
-        <v>18000000000000</v>
+        <v>68000000000</v>
       </c>
       <c r="L378" s="1" t="n">
-        <v>22464000</v>
+        <v>11371</v>
       </c>
       <c r="M378" s="1" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         </is>
       </c>
       <c r="N378" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O378" s="1" t="n">
         <v>0</v>
@@ -24432,11 +24432,11 @@
       </c>
       <c r="C379" s="1" t="inlineStr">
         <is>
-          <t>고양이 체력 -30% · 겁 -30%</t>
+          <t>증강 슬롯 +1</t>
         </is>
       </c>
       <c r="D379" s="1" t="n">
-        <v>2492733</v>
+        <v>2493033</v>
       </c>
       <c r="E379" s="1" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         </is>
       </c>
       <c r="F379" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G379" s="1" t="n">
         <v>2</v>
@@ -24459,28 +24459,28 @@
         <v>0</v>
       </c>
       <c r="K379" s="1" t="n">
-        <v>12000000000000</v>
+        <v>88000000000</v>
       </c>
       <c r="L379" s="1" t="n">
-        <v>14601601</v>
+        <v>14782</v>
       </c>
       <c r="M379" s="1" t="inlineStr">
         <is>
-          <t>Cat_Hp_Down</t>
+          <t>Aug_Slot</t>
         </is>
       </c>
       <c r="N379" s="1" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="O379" s="1" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="P379" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q379" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_catnip</t>
+          <t>SkillIcons/cs_stock</t>
         </is>
       </c>
       <c r="R379" s="1" t="inlineStr"/>
@@ -24495,11 +24495,11 @@
       </c>
       <c r="C380" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D380" s="1" t="n">
-        <v>2492132</v>
+        <v>2493332</v>
       </c>
       <c r="E380" s="1" t="inlineStr">
         <is>
@@ -24522,10 +24522,10 @@
         <v>0</v>
       </c>
       <c r="K380" s="1" t="n">
-        <v>31000000000000</v>
+        <v>120000000000</v>
       </c>
       <c r="L380" s="1" t="n">
-        <v>37964160</v>
+        <v>19217</v>
       </c>
       <c r="M380" s="1" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         </is>
       </c>
       <c r="N380" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O380" s="1" t="n">
         <v>0</v>
@@ -24585,10 +24585,10 @@
         <v>0</v>
       </c>
       <c r="K381" s="1" t="n">
-        <v>12000000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="L381" s="1" t="n">
-        <v>14601601</v>
+        <v>7391</v>
       </c>
       <c r="M381" s="1" t="inlineStr">
         <is>
@@ -24648,10 +24648,10 @@
         <v>0</v>
       </c>
       <c r="K382" s="1" t="n">
-        <v>20000000000000</v>
+        <v>74000000000</v>
       </c>
       <c r="L382" s="1" t="n">
-        <v>24676705</v>
+        <v>12491</v>
       </c>
       <c r="M382" s="1" t="inlineStr">
         <is>
@@ -24711,10 +24711,10 @@
         <v>0</v>
       </c>
       <c r="K383" s="1" t="n">
-        <v>16000000000000</v>
+        <v>57000000000</v>
       </c>
       <c r="L383" s="1" t="n">
-        <v>18982080</v>
+        <v>9609</v>
       </c>
       <c r="M383" s="1" t="inlineStr">
         <is>
@@ -24843,10 +24843,10 @@
         <v>0</v>
       </c>
       <c r="K385" s="1" t="n">
-        <v>26000000000000</v>
+        <v>74000000000</v>
       </c>
       <c r="L385" s="1" t="n">
-        <v>25760000</v>
+        <v>9894</v>
       </c>
       <c r="M385" s="1" t="inlineStr">
         <is>
@@ -24906,10 +24906,10 @@
         <v>0</v>
       </c>
       <c r="K386" s="1" t="n">
-        <v>34000000000000</v>
+        <v>96000000000</v>
       </c>
       <c r="L386" s="1" t="n">
-        <v>33488000</v>
+        <v>12862</v>
       </c>
       <c r="M386" s="1" t="inlineStr">
         <is>
@@ -24969,10 +24969,10 @@
         <v>0</v>
       </c>
       <c r="K387" s="1" t="n">
-        <v>44000000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L387" s="1" t="n">
-        <v>43534401</v>
+        <v>16720</v>
       </c>
       <c r="M387" s="1" t="inlineStr">
         <is>
@@ -25032,10 +25032,10 @@
         <v>0</v>
       </c>
       <c r="K388" s="1" t="n">
-        <v>44000000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L388" s="1" t="n">
-        <v>43534401</v>
+        <v>16720</v>
       </c>
       <c r="M388" s="1" t="inlineStr">
         <is>
@@ -25095,10 +25095,10 @@
         <v>0</v>
       </c>
       <c r="K389" s="1" t="n">
-        <v>56000000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L389" s="1" t="n">
-        <v>56594720</v>
+        <v>21736</v>
       </c>
       <c r="M389" s="1" t="inlineStr">
         <is>
@@ -25158,10 +25158,10 @@
         <v>0</v>
       </c>
       <c r="K390" s="1" t="n">
-        <v>44000000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L390" s="1" t="n">
-        <v>43534401</v>
+        <v>16720</v>
       </c>
       <c r="M390" s="1" t="inlineStr">
         <is>
@@ -25221,10 +25221,10 @@
         <v>0</v>
       </c>
       <c r="K391" s="1" t="n">
-        <v>56000000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L391" s="1" t="n">
-        <v>56594720</v>
+        <v>21736</v>
       </c>
       <c r="M391" s="1" t="inlineStr">
         <is>
@@ -25284,10 +25284,10 @@
         <v>0</v>
       </c>
       <c r="K392" s="1" t="n">
-        <v>56000000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L392" s="1" t="n">
-        <v>56594720</v>
+        <v>21736</v>
       </c>
       <c r="M392" s="1" t="inlineStr">
         <is>
@@ -25347,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="K393" s="1" t="n">
-        <v>26000000000000</v>
+        <v>74000000000</v>
       </c>
       <c r="L393" s="1" t="n">
-        <v>25760000</v>
+        <v>9894</v>
       </c>
       <c r="M393" s="1" t="inlineStr">
         <is>
@@ -25383,11 +25383,11 @@
       </c>
       <c r="C394" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +14초</t>
+          <t>생명체 처치 치즈 +80%</t>
         </is>
       </c>
       <c r="D394" s="1" t="n">
-        <v>2493014</v>
+        <v>2492721</v>
       </c>
       <c r="E394" s="1" t="inlineStr">
         <is>
@@ -25410,28 +25410,28 @@
         <v>0</v>
       </c>
       <c r="K394" s="1" t="n">
-        <v>34000000000000</v>
+        <v>96000000000</v>
       </c>
       <c r="L394" s="1" t="n">
-        <v>33488000</v>
+        <v>12862</v>
       </c>
       <c r="M394" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Cheese_Pct</t>
         </is>
       </c>
       <c r="N394" s="1" t="n">
-        <v>14</v>
+        <v>0.8</v>
       </c>
       <c r="O394" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P394" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q394" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_cheesecreature</t>
         </is>
       </c>
       <c r="R394" s="1" t="inlineStr"/>
@@ -25473,10 +25473,10 @@
         <v>0</v>
       </c>
       <c r="K395" s="1" t="n">
-        <v>44000000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L395" s="1" t="n">
-        <v>43534401</v>
+        <v>16720</v>
       </c>
       <c r="M395" s="1" t="inlineStr">
         <is>
@@ -25536,10 +25536,10 @@
         <v>0</v>
       </c>
       <c r="K396" s="1" t="n">
-        <v>44000000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L396" s="1" t="n">
-        <v>43534401</v>
+        <v>16720</v>
       </c>
       <c r="M396" s="1" t="inlineStr">
         <is>
@@ -25599,10 +25599,10 @@
         <v>0</v>
       </c>
       <c r="K397" s="1" t="n">
-        <v>44000000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L397" s="1" t="n">
-        <v>43534401</v>
+        <v>16720</v>
       </c>
       <c r="M397" s="1" t="inlineStr">
         <is>
@@ -25635,11 +25635,11 @@
       </c>
       <c r="C398" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +15초</t>
+          <t>황금 물건 확률 +3%</t>
         </is>
       </c>
       <c r="D398" s="1" t="n">
-        <v>2493114</v>
+        <v>2492423</v>
       </c>
       <c r="E398" s="1" t="inlineStr">
         <is>
@@ -25662,18 +25662,18 @@
         <v>0</v>
       </c>
       <c r="K398" s="1" t="n">
-        <v>56000000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L398" s="1" t="n">
-        <v>56594720</v>
+        <v>21736</v>
       </c>
       <c r="M398" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Gold_Item</t>
         </is>
       </c>
       <c r="N398" s="1" t="n">
-        <v>15</v>
+        <v>0.03</v>
       </c>
       <c r="O398" s="1" t="n">
         <v>0</v>
@@ -25683,7 +25683,7 @@
       </c>
       <c r="Q398" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_goldx</t>
         </is>
       </c>
       <c r="R398" s="1" t="inlineStr"/>
@@ -25725,10 +25725,10 @@
         <v>0</v>
       </c>
       <c r="K399" s="1" t="n">
-        <v>73000000000000</v>
+        <v>210000000000</v>
       </c>
       <c r="L399" s="1" t="n">
-        <v>73573137</v>
+        <v>28257</v>
       </c>
       <c r="M399" s="1" t="inlineStr">
         <is>
@@ -25788,10 +25788,10 @@
         <v>0</v>
       </c>
       <c r="K400" s="1" t="n">
-        <v>56000000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L400" s="1" t="n">
-        <v>56594720</v>
+        <v>21736</v>
       </c>
       <c r="M400" s="1" t="inlineStr">
         <is>
@@ -25851,10 +25851,10 @@
         <v>0</v>
       </c>
       <c r="K401" s="1" t="n">
-        <v>26000000000000</v>
+        <v>74000000000</v>
       </c>
       <c r="L401" s="1" t="n">
-        <v>25760000</v>
+        <v>9894</v>
       </c>
       <c r="M401" s="1" t="inlineStr">
         <is>
@@ -25914,10 +25914,10 @@
         <v>0</v>
       </c>
       <c r="K402" s="1" t="n">
-        <v>34000000000000</v>
+        <v>96000000000</v>
       </c>
       <c r="L402" s="1" t="n">
-        <v>33488000</v>
+        <v>12862</v>
       </c>
       <c r="M402" s="1" t="inlineStr">
         <is>
@@ -25977,10 +25977,10 @@
         <v>0</v>
       </c>
       <c r="K403" s="1" t="n">
-        <v>44000000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L403" s="1" t="n">
-        <v>43534401</v>
+        <v>16720</v>
       </c>
       <c r="M403" s="1" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>0</v>
       </c>
       <c r="K404" s="1" t="n">
-        <v>44000000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L404" s="1" t="n">
-        <v>43534401</v>
+        <v>16720</v>
       </c>
       <c r="M404" s="1" t="inlineStr">
         <is>
@@ -26103,10 +26103,10 @@
         <v>0</v>
       </c>
       <c r="K405" s="1" t="n">
-        <v>56000000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L405" s="1" t="n">
-        <v>56594720</v>
+        <v>21736</v>
       </c>
       <c r="M405" s="1" t="inlineStr">
         <is>
@@ -26166,10 +26166,10 @@
         <v>0</v>
       </c>
       <c r="K406" s="1" t="n">
-        <v>56000000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L406" s="1" t="n">
-        <v>56594720</v>
+        <v>21736</v>
       </c>
       <c r="M406" s="1" t="inlineStr">
         <is>
@@ -26229,10 +26229,10 @@
         <v>0</v>
       </c>
       <c r="K407" s="1" t="n">
-        <v>56000000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L407" s="1" t="n">
-        <v>56594720</v>
+        <v>21736</v>
       </c>
       <c r="M407" s="1" t="inlineStr">
         <is>
@@ -26292,10 +26292,10 @@
         <v>0</v>
       </c>
       <c r="K408" s="1" t="n">
-        <v>73000000000000</v>
+        <v>210000000000</v>
       </c>
       <c r="L408" s="1" t="n">
-        <v>73573137</v>
+        <v>28257</v>
       </c>
       <c r="M408" s="1" t="inlineStr">
         <is>
@@ -26355,10 +26355,10 @@
         <v>0</v>
       </c>
       <c r="K409" s="1" t="n">
-        <v>26000000000000</v>
+        <v>74000000000</v>
       </c>
       <c r="L409" s="1" t="n">
-        <v>25760000</v>
+        <v>9894</v>
       </c>
       <c r="M409" s="1" t="inlineStr">
         <is>
@@ -26418,10 +26418,10 @@
         <v>0</v>
       </c>
       <c r="K410" s="1" t="n">
-        <v>34000000000000</v>
+        <v>96000000000</v>
       </c>
       <c r="L410" s="1" t="n">
-        <v>33488000</v>
+        <v>12862</v>
       </c>
       <c r="M410" s="1" t="inlineStr">
         <is>
@@ -26481,10 +26481,10 @@
         <v>0</v>
       </c>
       <c r="K411" s="1" t="n">
-        <v>44000000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L411" s="1" t="n">
-        <v>43534401</v>
+        <v>16720</v>
       </c>
       <c r="M411" s="1" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>0</v>
       </c>
       <c r="K412" s="1" t="n">
-        <v>44000000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L412" s="1" t="n">
-        <v>43534401</v>
+        <v>16720</v>
       </c>
       <c r="M412" s="1" t="inlineStr">
         <is>
@@ -26607,10 +26607,10 @@
         <v>0</v>
       </c>
       <c r="K413" s="1" t="n">
-        <v>56000000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L413" s="1" t="n">
-        <v>56594720</v>
+        <v>21736</v>
       </c>
       <c r="M413" s="1" t="inlineStr">
         <is>
@@ -26670,10 +26670,10 @@
         <v>0</v>
       </c>
       <c r="K414" s="1" t="n">
-        <v>56000000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L414" s="1" t="n">
-        <v>56594720</v>
+        <v>21736</v>
       </c>
       <c r="M414" s="1" t="inlineStr">
         <is>
@@ -26733,10 +26733,10 @@
         <v>0</v>
       </c>
       <c r="K415" s="1" t="n">
-        <v>73000000000000</v>
+        <v>210000000000</v>
       </c>
       <c r="L415" s="1" t="n">
-        <v>73573137</v>
+        <v>28257</v>
       </c>
       <c r="M415" s="1" t="inlineStr">
         <is>
@@ -26769,11 +26769,11 @@
       </c>
       <c r="C416" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D416" s="1" t="n">
-        <v>2492332</v>
+        <v>2493332</v>
       </c>
       <c r="E416" s="1" t="inlineStr">
         <is>
@@ -26796,10 +26796,10 @@
         <v>0</v>
       </c>
       <c r="K416" s="1" t="n">
-        <v>67000000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="L416" s="1" t="n">
-        <v>66976000</v>
+        <v>25723</v>
       </c>
       <c r="M416" s="1" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         </is>
       </c>
       <c r="N416" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O416" s="1" t="n">
         <v>0</v>
@@ -26859,10 +26859,10 @@
         <v>0</v>
       </c>
       <c r="K417" s="1" t="n">
-        <v>44000000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L417" s="1" t="n">
-        <v>43534401</v>
+        <v>16720</v>
       </c>
       <c r="M417" s="1" t="inlineStr">
         <is>
@@ -26895,11 +26895,11 @@
       </c>
       <c r="C418" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D418" s="1" t="n">
-        <v>2492332</v>
+        <v>2493332</v>
       </c>
       <c r="E418" s="1" t="inlineStr">
         <is>
@@ -26922,10 +26922,10 @@
         <v>0</v>
       </c>
       <c r="K418" s="1" t="n">
-        <v>120000000000000</v>
+        <v>330000000000</v>
       </c>
       <c r="L418" s="1" t="n">
-        <v>113189440</v>
+        <v>43472</v>
       </c>
       <c r="M418" s="1" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         </is>
       </c>
       <c r="N418" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O418" s="1" t="n">
         <v>0</v>
@@ -26985,10 +26985,10 @@
         <v>0</v>
       </c>
       <c r="K419" s="1" t="n">
-        <v>44000000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L419" s="1" t="n">
-        <v>43534401</v>
+        <v>16720</v>
       </c>
       <c r="M419" s="1" t="inlineStr">
         <is>
@@ -27048,10 +27048,10 @@
         <v>0</v>
       </c>
       <c r="K420" s="1" t="n">
-        <v>73000000000000</v>
+        <v>210000000000</v>
       </c>
       <c r="L420" s="1" t="n">
-        <v>73573137</v>
+        <v>28257</v>
       </c>
       <c r="M420" s="1" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         <v>0</v>
       </c>
       <c r="K421" s="1" t="n">
-        <v>56000000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L421" s="1" t="n">
-        <v>56594720</v>
+        <v>21736</v>
       </c>
       <c r="M421" s="1" t="inlineStr">
         <is>
@@ -27243,10 +27243,10 @@
         <v>0</v>
       </c>
       <c r="K423" s="1" t="n">
-        <v>95000000000000</v>
+        <v>240000000000</v>
       </c>
       <c r="L423" s="1" t="n">
-        <v>76800000</v>
+        <v>24960</v>
       </c>
       <c r="M423" s="1" t="inlineStr">
         <is>
@@ -27306,10 +27306,10 @@
         <v>0</v>
       </c>
       <c r="K424" s="1" t="n">
-        <v>130000000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L424" s="1" t="n">
-        <v>99840000</v>
+        <v>32448</v>
       </c>
       <c r="M424" s="1" t="inlineStr">
         <is>
@@ -27369,10 +27369,10 @@
         <v>0</v>
       </c>
       <c r="K425" s="1" t="n">
-        <v>170000000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L425" s="1" t="n">
-        <v>129792001</v>
+        <v>42183</v>
       </c>
       <c r="M425" s="1" t="inlineStr">
         <is>
@@ -27432,10 +27432,10 @@
         <v>0</v>
       </c>
       <c r="K426" s="1" t="n">
-        <v>170000000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L426" s="1" t="n">
-        <v>129792001</v>
+        <v>42183</v>
       </c>
       <c r="M426" s="1" t="inlineStr">
         <is>
@@ -27495,10 +27495,10 @@
         <v>0</v>
       </c>
       <c r="K427" s="1" t="n">
-        <v>210000000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L427" s="1" t="n">
-        <v>168729600</v>
+        <v>54838</v>
       </c>
       <c r="M427" s="1" t="inlineStr">
         <is>
@@ -27558,10 +27558,10 @@
         <v>0</v>
       </c>
       <c r="K428" s="1" t="n">
-        <v>170000000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L428" s="1" t="n">
-        <v>129792001</v>
+        <v>42183</v>
       </c>
       <c r="M428" s="1" t="inlineStr">
         <is>
@@ -27621,10 +27621,10 @@
         <v>0</v>
       </c>
       <c r="K429" s="1" t="n">
-        <v>210000000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L429" s="1" t="n">
-        <v>168729600</v>
+        <v>54838</v>
       </c>
       <c r="M429" s="1" t="inlineStr">
         <is>
@@ -27684,10 +27684,10 @@
         <v>0</v>
       </c>
       <c r="K430" s="1" t="n">
-        <v>210000000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L430" s="1" t="n">
-        <v>168729600</v>
+        <v>54838</v>
       </c>
       <c r="M430" s="1" t="inlineStr">
         <is>
@@ -27747,10 +27747,10 @@
         <v>0</v>
       </c>
       <c r="K431" s="1" t="n">
-        <v>95000000000000</v>
+        <v>240000000000</v>
       </c>
       <c r="L431" s="1" t="n">
-        <v>76800000</v>
+        <v>24960</v>
       </c>
       <c r="M431" s="1" t="inlineStr">
         <is>
@@ -27783,11 +27783,11 @@
       </c>
       <c r="C432" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +15초</t>
+          <t>생명체 처치 치즈 +90%</t>
         </is>
       </c>
       <c r="D432" s="1" t="n">
-        <v>2493114</v>
+        <v>2493210</v>
       </c>
       <c r="E432" s="1" t="inlineStr">
         <is>
@@ -27810,28 +27810,28 @@
         <v>0</v>
       </c>
       <c r="K432" s="1" t="n">
-        <v>130000000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L432" s="1" t="n">
-        <v>99840000</v>
+        <v>32448</v>
       </c>
       <c r="M432" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Cheese_Pct</t>
         </is>
       </c>
       <c r="N432" s="1" t="n">
-        <v>15</v>
+        <v>0.9</v>
       </c>
       <c r="O432" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P432" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q432" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_cheesecreature</t>
         </is>
       </c>
       <c r="R432" s="1" t="inlineStr"/>
@@ -27873,10 +27873,10 @@
         <v>0</v>
       </c>
       <c r="K433" s="1" t="n">
-        <v>170000000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L433" s="1" t="n">
-        <v>129792001</v>
+        <v>42183</v>
       </c>
       <c r="M433" s="1" t="inlineStr">
         <is>
@@ -27936,10 +27936,10 @@
         <v>0</v>
       </c>
       <c r="K434" s="1" t="n">
-        <v>330000000000000</v>
+        <v>790000000000</v>
       </c>
       <c r="L434" s="1" t="n">
-        <v>259584001</v>
+        <v>84365</v>
       </c>
       <c r="M434" s="1" t="inlineStr">
         <is>
@@ -27999,10 +27999,10 @@
         <v>0</v>
       </c>
       <c r="K435" s="1" t="n">
-        <v>170000000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L435" s="1" t="n">
-        <v>129792001</v>
+        <v>42183</v>
       </c>
       <c r="M435" s="1" t="inlineStr">
         <is>
@@ -28062,10 +28062,10 @@
         <v>0</v>
       </c>
       <c r="K436" s="1" t="n">
-        <v>420000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L436" s="1" t="n">
-        <v>337459200</v>
+        <v>109675</v>
       </c>
       <c r="M436" s="1" t="inlineStr">
         <is>
@@ -28125,10 +28125,10 @@
         <v>0</v>
       </c>
       <c r="K437" s="1" t="n">
-        <v>280000000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L437" s="1" t="n">
-        <v>219348481</v>
+        <v>71289</v>
       </c>
       <c r="M437" s="1" t="inlineStr">
         <is>
@@ -28188,10 +28188,10 @@
         <v>0</v>
       </c>
       <c r="K438" s="1" t="n">
-        <v>420000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L438" s="1" t="n">
-        <v>337459200</v>
+        <v>109675</v>
       </c>
       <c r="M438" s="1" t="inlineStr">
         <is>
@@ -28251,10 +28251,10 @@
         <v>0</v>
       </c>
       <c r="K439" s="1" t="n">
-        <v>95000000000000</v>
+        <v>240000000000</v>
       </c>
       <c r="L439" s="1" t="n">
-        <v>76800000</v>
+        <v>24960</v>
       </c>
       <c r="M439" s="1" t="inlineStr">
         <is>
@@ -28314,10 +28314,10 @@
         <v>0</v>
       </c>
       <c r="K440" s="1" t="n">
-        <v>130000000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L440" s="1" t="n">
-        <v>99840000</v>
+        <v>32448</v>
       </c>
       <c r="M440" s="1" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>0</v>
       </c>
       <c r="K441" s="1" t="n">
-        <v>170000000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L441" s="1" t="n">
-        <v>129792001</v>
+        <v>42183</v>
       </c>
       <c r="M441" s="1" t="inlineStr">
         <is>
@@ -28440,10 +28440,10 @@
         <v>0</v>
       </c>
       <c r="K442" s="1" t="n">
-        <v>170000000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L442" s="1" t="n">
-        <v>129792001</v>
+        <v>42183</v>
       </c>
       <c r="M442" s="1" t="inlineStr">
         <is>
@@ -28503,10 +28503,10 @@
         <v>0</v>
       </c>
       <c r="K443" s="1" t="n">
-        <v>210000000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L443" s="1" t="n">
-        <v>168729600</v>
+        <v>54838</v>
       </c>
       <c r="M443" s="1" t="inlineStr">
         <is>
@@ -28566,10 +28566,10 @@
         <v>0</v>
       </c>
       <c r="K444" s="1" t="n">
-        <v>210000000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L444" s="1" t="n">
-        <v>168729600</v>
+        <v>54838</v>
       </c>
       <c r="M444" s="1" t="inlineStr">
         <is>
@@ -28629,10 +28629,10 @@
         <v>0</v>
       </c>
       <c r="K445" s="1" t="n">
-        <v>210000000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L445" s="1" t="n">
-        <v>168729600</v>
+        <v>54838</v>
       </c>
       <c r="M445" s="1" t="inlineStr">
         <is>
@@ -28692,10 +28692,10 @@
         <v>0</v>
       </c>
       <c r="K446" s="1" t="n">
-        <v>280000000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L446" s="1" t="n">
-        <v>219348481</v>
+        <v>71289</v>
       </c>
       <c r="M446" s="1" t="inlineStr">
         <is>
@@ -28755,10 +28755,10 @@
         <v>0</v>
       </c>
       <c r="K447" s="1" t="n">
-        <v>95000000000000</v>
+        <v>240000000000</v>
       </c>
       <c r="L447" s="1" t="n">
-        <v>76800000</v>
+        <v>24960</v>
       </c>
       <c r="M447" s="1" t="inlineStr">
         <is>
@@ -28818,10 +28818,10 @@
         <v>0</v>
       </c>
       <c r="K448" s="1" t="n">
-        <v>130000000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L448" s="1" t="n">
-        <v>99840000</v>
+        <v>32448</v>
       </c>
       <c r="M448" s="1" t="inlineStr">
         <is>
@@ -28881,10 +28881,10 @@
         <v>0</v>
       </c>
       <c r="K449" s="1" t="n">
-        <v>170000000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L449" s="1" t="n">
-        <v>129792001</v>
+        <v>42183</v>
       </c>
       <c r="M449" s="1" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>0</v>
       </c>
       <c r="K450" s="1" t="n">
-        <v>170000000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L450" s="1" t="n">
-        <v>129792001</v>
+        <v>42183</v>
       </c>
       <c r="M450" s="1" t="inlineStr">
         <is>
@@ -29007,10 +29007,10 @@
         <v>0</v>
       </c>
       <c r="K451" s="1" t="n">
-        <v>210000000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L451" s="1" t="n">
-        <v>168729600</v>
+        <v>54838</v>
       </c>
       <c r="M451" s="1" t="inlineStr">
         <is>
@@ -29070,10 +29070,10 @@
         <v>0</v>
       </c>
       <c r="K452" s="1" t="n">
-        <v>210000000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L452" s="1" t="n">
-        <v>168729600</v>
+        <v>54838</v>
       </c>
       <c r="M452" s="1" t="inlineStr">
         <is>
@@ -29133,10 +29133,10 @@
         <v>0</v>
       </c>
       <c r="K453" s="1" t="n">
-        <v>280000000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L453" s="1" t="n">
-        <v>219348481</v>
+        <v>71289</v>
       </c>
       <c r="M453" s="1" t="inlineStr">
         <is>
@@ -29169,11 +29169,11 @@
       </c>
       <c r="C454" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D454" s="1" t="n">
-        <v>2492332</v>
+        <v>2493332</v>
       </c>
       <c r="E454" s="1" t="inlineStr">
         <is>
@@ -29196,10 +29196,10 @@
         <v>0</v>
       </c>
       <c r="K454" s="1" t="n">
-        <v>250000000000000</v>
+        <v>610000000000</v>
       </c>
       <c r="L454" s="1" t="n">
-        <v>199680000</v>
+        <v>64896</v>
       </c>
       <c r="M454" s="1" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         </is>
       </c>
       <c r="N454" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O454" s="1" t="n">
         <v>0</v>
@@ -29259,10 +29259,10 @@
         <v>0</v>
       </c>
       <c r="K455" s="1" t="n">
-        <v>170000000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L455" s="1" t="n">
-        <v>129792001</v>
+        <v>42183</v>
       </c>
       <c r="M455" s="1" t="inlineStr">
         <is>
@@ -29295,11 +29295,11 @@
       </c>
       <c r="C456" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D456" s="1" t="n">
-        <v>2492332</v>
+        <v>2493332</v>
       </c>
       <c r="E456" s="1" t="inlineStr">
         <is>
@@ -29322,10 +29322,10 @@
         <v>0</v>
       </c>
       <c r="K456" s="1" t="n">
-        <v>420000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L456" s="1" t="n">
-        <v>337459200</v>
+        <v>109675</v>
       </c>
       <c r="M456" s="1" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         </is>
       </c>
       <c r="N456" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O456" s="1" t="n">
         <v>0</v>
@@ -29385,10 +29385,10 @@
         <v>0</v>
       </c>
       <c r="K457" s="1" t="n">
-        <v>170000000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L457" s="1" t="n">
-        <v>129792001</v>
+        <v>42183</v>
       </c>
       <c r="M457" s="1" t="inlineStr">
         <is>
@@ -29448,10 +29448,10 @@
         <v>0</v>
       </c>
       <c r="K458" s="1" t="n">
-        <v>280000000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L458" s="1" t="n">
-        <v>219348481</v>
+        <v>71289</v>
       </c>
       <c r="M458" s="1" t="inlineStr">
         <is>
@@ -29484,11 +29484,11 @@
       </c>
       <c r="C459" s="1" t="inlineStr">
         <is>
-          <t>필살기 쿨타임 -4초</t>
+          <t>증강 슬롯 +1</t>
         </is>
       </c>
       <c r="D459" s="1" t="n">
-        <v>2492833</v>
+        <v>2493033</v>
       </c>
       <c r="E459" s="1" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         </is>
       </c>
       <c r="F459" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G459" s="1" t="n">
         <v>2</v>
@@ -29511,18 +29511,18 @@
         <v>0</v>
       </c>
       <c r="K459" s="1" t="n">
-        <v>210000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L459" s="1" t="n">
-        <v>168729600</v>
+        <v>109675</v>
       </c>
       <c r="M459" s="1" t="inlineStr">
         <is>
-          <t>Ult_CD</t>
+          <t>Aug_Slot</t>
         </is>
       </c>
       <c r="N459" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O459" s="1" t="n">
         <v>0</v>
@@ -29532,7 +29532,7 @@
       </c>
       <c r="Q459" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_ultcd</t>
+          <t>SkillIcons/cs_stock</t>
         </is>
       </c>
       <c r="R459" s="1" t="inlineStr"/>
@@ -29643,10 +29643,10 @@
         <v>0</v>
       </c>
       <c r="K461" s="1" t="n">
-        <v>360000000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L461" s="1" t="n">
-        <v>229333334</v>
+        <v>43987</v>
       </c>
       <c r="M461" s="1" t="inlineStr">
         <is>
@@ -29706,10 +29706,10 @@
         <v>0</v>
       </c>
       <c r="K462" s="1" t="n">
-        <v>470000000000000</v>
+        <v>640000000000</v>
       </c>
       <c r="L462" s="1" t="n">
-        <v>298133334</v>
+        <v>57183</v>
       </c>
       <c r="M462" s="1" t="inlineStr">
         <is>
@@ -29769,10 +29769,10 @@
         <v>0</v>
       </c>
       <c r="K463" s="1" t="n">
-        <v>600000000000000</v>
+        <v>830000000000</v>
       </c>
       <c r="L463" s="1" t="n">
-        <v>387573334</v>
+        <v>74338</v>
       </c>
       <c r="M463" s="1" t="inlineStr">
         <is>
@@ -29832,10 +29832,10 @@
         <v>0</v>
       </c>
       <c r="K464" s="1" t="n">
-        <v>600000000000000</v>
+        <v>830000000000</v>
       </c>
       <c r="L464" s="1" t="n">
-        <v>387573334</v>
+        <v>74338</v>
       </c>
       <c r="M464" s="1" t="inlineStr">
         <is>
@@ -29895,10 +29895,10 @@
         <v>0</v>
       </c>
       <c r="K465" s="1" t="n">
-        <v>780000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L465" s="1" t="n">
-        <v>503845334</v>
+        <v>96639</v>
       </c>
       <c r="M465" s="1" t="inlineStr">
         <is>
@@ -29958,10 +29958,10 @@
         <v>0</v>
       </c>
       <c r="K466" s="1" t="n">
-        <v>600000000000000</v>
+        <v>830000000000</v>
       </c>
       <c r="L466" s="1" t="n">
-        <v>387573334</v>
+        <v>74338</v>
       </c>
       <c r="M466" s="1" t="inlineStr">
         <is>
@@ -30021,10 +30021,10 @@
         <v>0</v>
       </c>
       <c r="K467" s="1" t="n">
-        <v>780000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L467" s="1" t="n">
-        <v>503845334</v>
+        <v>96639</v>
       </c>
       <c r="M467" s="1" t="inlineStr">
         <is>
@@ -30084,10 +30084,10 @@
         <v>0</v>
       </c>
       <c r="K468" s="1" t="n">
-        <v>780000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L468" s="1" t="n">
-        <v>503845334</v>
+        <v>96639</v>
       </c>
       <c r="M468" s="1" t="inlineStr">
         <is>
@@ -30147,10 +30147,10 @@
         <v>0</v>
       </c>
       <c r="K469" s="1" t="n">
-        <v>360000000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L469" s="1" t="n">
-        <v>229333334</v>
+        <v>43987</v>
       </c>
       <c r="M469" s="1" t="inlineStr">
         <is>
@@ -30183,11 +30183,11 @@
       </c>
       <c r="C470" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +16초</t>
+          <t>생명체 처치 치즈 +100%</t>
         </is>
       </c>
       <c r="D470" s="1" t="n">
-        <v>2493310</v>
+        <v>2492821</v>
       </c>
       <c r="E470" s="1" t="inlineStr">
         <is>
@@ -30210,28 +30210,28 @@
         <v>0</v>
       </c>
       <c r="K470" s="1" t="n">
-        <v>470000000000000</v>
+        <v>640000000000</v>
       </c>
       <c r="L470" s="1" t="n">
-        <v>298133334</v>
+        <v>57183</v>
       </c>
       <c r="M470" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Cheese_Pct</t>
         </is>
       </c>
       <c r="N470" s="1" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O470" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P470" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q470" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_cheesecreature</t>
         </is>
       </c>
       <c r="R470" s="1" t="inlineStr"/>
@@ -30273,10 +30273,10 @@
         <v>0</v>
       </c>
       <c r="K471" s="1" t="n">
-        <v>600000000000000</v>
+        <v>830000000000</v>
       </c>
       <c r="L471" s="1" t="n">
-        <v>387573334</v>
+        <v>74338</v>
       </c>
       <c r="M471" s="1" t="inlineStr">
         <is>
@@ -30336,10 +30336,10 @@
         <v>0</v>
       </c>
       <c r="K472" s="1" t="n">
-        <v>600000000000000</v>
+        <v>830000000000</v>
       </c>
       <c r="L472" s="1" t="n">
-        <v>387573334</v>
+        <v>74338</v>
       </c>
       <c r="M472" s="1" t="inlineStr">
         <is>
@@ -30399,10 +30399,10 @@
         <v>0</v>
       </c>
       <c r="K473" s="1" t="n">
-        <v>600000000000000</v>
+        <v>830000000000</v>
       </c>
       <c r="L473" s="1" t="n">
-        <v>387573334</v>
+        <v>74338</v>
       </c>
       <c r="M473" s="1" t="inlineStr">
         <is>
@@ -30435,11 +30435,11 @@
       </c>
       <c r="C474" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +17초</t>
+          <t>황금 물건 확률 +3%</t>
         </is>
       </c>
       <c r="D474" s="1" t="n">
-        <v>2493314</v>
+        <v>2492423</v>
       </c>
       <c r="E474" s="1" t="inlineStr">
         <is>
@@ -30462,18 +30462,18 @@
         <v>0</v>
       </c>
       <c r="K474" s="1" t="n">
-        <v>780000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L474" s="1" t="n">
-        <v>503845334</v>
+        <v>96639</v>
       </c>
       <c r="M474" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Gold_Item</t>
         </is>
       </c>
       <c r="N474" s="1" t="n">
-        <v>17</v>
+        <v>0.03</v>
       </c>
       <c r="O474" s="1" t="n">
         <v>0</v>
@@ -30483,7 +30483,7 @@
       </c>
       <c r="Q474" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_goldx</t>
         </is>
       </c>
       <c r="R474" s="1" t="inlineStr"/>
@@ -30525,10 +30525,10 @@
         <v>0</v>
       </c>
       <c r="K475" s="1" t="n">
-        <v>1100000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L475" s="1" t="n">
-        <v>654998934</v>
+        <v>125631</v>
       </c>
       <c r="M475" s="1" t="inlineStr">
         <is>
@@ -30588,10 +30588,10 @@
         <v>0</v>
       </c>
       <c r="K476" s="1" t="n">
-        <v>780000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L476" s="1" t="n">
-        <v>503845334</v>
+        <v>96639</v>
       </c>
       <c r="M476" s="1" t="inlineStr">
         <is>
@@ -30651,10 +30651,10 @@
         <v>0</v>
       </c>
       <c r="K477" s="1" t="n">
-        <v>360000000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L477" s="1" t="n">
-        <v>229333334</v>
+        <v>43987</v>
       </c>
       <c r="M477" s="1" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>0</v>
       </c>
       <c r="K478" s="1" t="n">
-        <v>470000000000000</v>
+        <v>640000000000</v>
       </c>
       <c r="L478" s="1" t="n">
-        <v>298133334</v>
+        <v>57183</v>
       </c>
       <c r="M478" s="1" t="inlineStr">
         <is>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="K479" s="1" t="n">
-        <v>600000000000000</v>
+        <v>830000000000</v>
       </c>
       <c r="L479" s="1" t="n">
-        <v>387573334</v>
+        <v>74338</v>
       </c>
       <c r="M479" s="1" t="inlineStr">
         <is>
@@ -30840,10 +30840,10 @@
         <v>0</v>
       </c>
       <c r="K480" s="1" t="n">
-        <v>600000000000000</v>
+        <v>830000000000</v>
       </c>
       <c r="L480" s="1" t="n">
-        <v>387573334</v>
+        <v>74338</v>
       </c>
       <c r="M480" s="1" t="inlineStr">
         <is>
@@ -30903,10 +30903,10 @@
         <v>0</v>
       </c>
       <c r="K481" s="1" t="n">
-        <v>780000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L481" s="1" t="n">
-        <v>503845334</v>
+        <v>96639</v>
       </c>
       <c r="M481" s="1" t="inlineStr">
         <is>
@@ -30966,10 +30966,10 @@
         <v>0</v>
       </c>
       <c r="K482" s="1" t="n">
-        <v>780000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L482" s="1" t="n">
-        <v>503845334</v>
+        <v>96639</v>
       </c>
       <c r="M482" s="1" t="inlineStr">
         <is>
@@ -31029,10 +31029,10 @@
         <v>0</v>
       </c>
       <c r="K483" s="1" t="n">
-        <v>780000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L483" s="1" t="n">
-        <v>503845334</v>
+        <v>96639</v>
       </c>
       <c r="M483" s="1" t="inlineStr">
         <is>
@@ -31092,10 +31092,10 @@
         <v>0</v>
       </c>
       <c r="K484" s="1" t="n">
-        <v>1100000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L484" s="1" t="n">
-        <v>654998934</v>
+        <v>125631</v>
       </c>
       <c r="M484" s="1" t="inlineStr">
         <is>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="K485" s="1" t="n">
-        <v>360000000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L485" s="1" t="n">
-        <v>229333334</v>
+        <v>43987</v>
       </c>
       <c r="M485" s="1" t="inlineStr">
         <is>
@@ -31218,10 +31218,10 @@
         <v>0</v>
       </c>
       <c r="K486" s="1" t="n">
-        <v>470000000000000</v>
+        <v>640000000000</v>
       </c>
       <c r="L486" s="1" t="n">
-        <v>298133334</v>
+        <v>57183</v>
       </c>
       <c r="M486" s="1" t="inlineStr">
         <is>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="K487" s="1" t="n">
-        <v>600000000000000</v>
+        <v>830000000000</v>
       </c>
       <c r="L487" s="1" t="n">
-        <v>387573334</v>
+        <v>74338</v>
       </c>
       <c r="M487" s="1" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>0</v>
       </c>
       <c r="K488" s="1" t="n">
-        <v>600000000000000</v>
+        <v>830000000000</v>
       </c>
       <c r="L488" s="1" t="n">
-        <v>387573334</v>
+        <v>74338</v>
       </c>
       <c r="M488" s="1" t="inlineStr">
         <is>
@@ -31407,10 +31407,10 @@
         <v>0</v>
       </c>
       <c r="K489" s="1" t="n">
-        <v>780000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L489" s="1" t="n">
-        <v>503845334</v>
+        <v>96639</v>
       </c>
       <c r="M489" s="1" t="inlineStr">
         <is>
@@ -31470,10 +31470,10 @@
         <v>0</v>
       </c>
       <c r="K490" s="1" t="n">
-        <v>780000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L490" s="1" t="n">
-        <v>503845334</v>
+        <v>96639</v>
       </c>
       <c r="M490" s="1" t="inlineStr">
         <is>
@@ -31533,10 +31533,10 @@
         <v>0</v>
       </c>
       <c r="K491" s="1" t="n">
-        <v>1100000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L491" s="1" t="n">
-        <v>654998934</v>
+        <v>125631</v>
       </c>
       <c r="M491" s="1" t="inlineStr">
         <is>
@@ -31596,10 +31596,10 @@
         <v>0</v>
       </c>
       <c r="K492" s="1" t="n">
-        <v>930000000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="L492" s="1" t="n">
-        <v>596266667</v>
+        <v>114366</v>
       </c>
       <c r="M492" s="1" t="inlineStr">
         <is>
@@ -31659,10 +31659,10 @@
         <v>0</v>
       </c>
       <c r="K493" s="1" t="n">
-        <v>600000000000000</v>
+        <v>830000000000</v>
       </c>
       <c r="L493" s="1" t="n">
-        <v>387573334</v>
+        <v>74338</v>
       </c>
       <c r="M493" s="1" t="inlineStr">
         <is>
@@ -31722,10 +31722,10 @@
         <v>0</v>
       </c>
       <c r="K494" s="1" t="n">
-        <v>1600000000000000</v>
+        <v>2200000000000</v>
       </c>
       <c r="L494" s="1" t="n">
-        <v>1007690667</v>
+        <v>193278</v>
       </c>
       <c r="M494" s="1" t="inlineStr">
         <is>
@@ -31785,10 +31785,10 @@
         <v>0</v>
       </c>
       <c r="K495" s="1" t="n">
-        <v>600000000000000</v>
+        <v>830000000000</v>
       </c>
       <c r="L495" s="1" t="n">
-        <v>387573334</v>
+        <v>74338</v>
       </c>
       <c r="M495" s="1" t="inlineStr">
         <is>
@@ -31848,10 +31848,10 @@
         <v>0</v>
       </c>
       <c r="K496" s="1" t="n">
-        <v>1100000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L496" s="1" t="n">
-        <v>654998934</v>
+        <v>125631</v>
       </c>
       <c r="M496" s="1" t="inlineStr">
         <is>
@@ -31911,10 +31911,10 @@
         <v>0</v>
       </c>
       <c r="K497" s="1" t="n">
-        <v>780000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L497" s="1" t="n">
-        <v>503845334</v>
+        <v>96639</v>
       </c>
       <c r="M497" s="1" t="inlineStr">
         <is>
@@ -32043,10 +32043,10 @@
         <v>0</v>
       </c>
       <c r="K499" s="1" t="n">
-        <v>1400000000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L499" s="1" t="n">
-        <v>682666667</v>
+        <v>65934</v>
       </c>
       <c r="M499" s="1" t="inlineStr">
         <is>
@@ -32106,10 +32106,10 @@
         <v>0</v>
       </c>
       <c r="K500" s="1" t="n">
-        <v>1800000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L500" s="1" t="n">
-        <v>887466667</v>
+        <v>85714</v>
       </c>
       <c r="M500" s="1" t="inlineStr">
         <is>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="K501" s="1" t="n">
-        <v>2300000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L501" s="1" t="n">
-        <v>1153706667</v>
+        <v>111428</v>
       </c>
       <c r="M501" s="1" t="inlineStr">
         <is>
@@ -32232,10 +32232,10 @@
         <v>0</v>
       </c>
       <c r="K502" s="1" t="n">
-        <v>2300000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L502" s="1" t="n">
-        <v>1153706667</v>
+        <v>111428</v>
       </c>
       <c r="M502" s="1" t="inlineStr">
         <is>
@@ -32295,10 +32295,10 @@
         <v>0</v>
       </c>
       <c r="K503" s="1" t="n">
-        <v>2900000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L503" s="1" t="n">
-        <v>1499818667</v>
+        <v>144856</v>
       </c>
       <c r="M503" s="1" t="inlineStr">
         <is>
@@ -32358,10 +32358,10 @@
         <v>0</v>
       </c>
       <c r="K504" s="1" t="n">
-        <v>2300000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L504" s="1" t="n">
-        <v>1153706667</v>
+        <v>111428</v>
       </c>
       <c r="M504" s="1" t="inlineStr">
         <is>
@@ -32421,10 +32421,10 @@
         <v>0</v>
       </c>
       <c r="K505" s="1" t="n">
-        <v>2900000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L505" s="1" t="n">
-        <v>1499818667</v>
+        <v>144856</v>
       </c>
       <c r="M505" s="1" t="inlineStr">
         <is>
@@ -32484,10 +32484,10 @@
         <v>0</v>
       </c>
       <c r="K506" s="1" t="n">
-        <v>2900000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L506" s="1" t="n">
-        <v>1499818667</v>
+        <v>144856</v>
       </c>
       <c r="M506" s="1" t="inlineStr">
         <is>
@@ -32547,10 +32547,10 @@
         <v>0</v>
       </c>
       <c r="K507" s="1" t="n">
-        <v>1400000000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L507" s="1" t="n">
-        <v>682666667</v>
+        <v>65934</v>
       </c>
       <c r="M507" s="1" t="inlineStr">
         <is>
@@ -32583,11 +32583,11 @@
       </c>
       <c r="C508" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +17초</t>
+          <t>생명체 처치 치즈 +110%</t>
         </is>
       </c>
       <c r="D508" s="1" t="n">
-        <v>2493314</v>
+        <v>2493410</v>
       </c>
       <c r="E508" s="1" t="inlineStr">
         <is>
@@ -32610,28 +32610,28 @@
         <v>0</v>
       </c>
       <c r="K508" s="1" t="n">
-        <v>1800000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L508" s="1" t="n">
-        <v>887466667</v>
+        <v>85714</v>
       </c>
       <c r="M508" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Cheese_Pct</t>
         </is>
       </c>
       <c r="N508" s="1" t="n">
-        <v>17</v>
+        <v>1.1</v>
       </c>
       <c r="O508" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P508" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q508" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_cheesecreature</t>
         </is>
       </c>
       <c r="R508" s="1" t="inlineStr"/>
@@ -32673,10 +32673,10 @@
         <v>0</v>
       </c>
       <c r="K509" s="1" t="n">
-        <v>2300000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L509" s="1" t="n">
-        <v>1153706667</v>
+        <v>111428</v>
       </c>
       <c r="M509" s="1" t="inlineStr">
         <is>
@@ -32736,10 +32736,10 @@
         <v>0</v>
       </c>
       <c r="K510" s="1" t="n">
-        <v>2300000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>1153706667</v>
+        <v>111428</v>
       </c>
       <c r="M510" s="1" t="inlineStr">
         <is>
@@ -32799,10 +32799,10 @@
         <v>0</v>
       </c>
       <c r="K511" s="1" t="n">
-        <v>2300000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>1153706667</v>
+        <v>111428</v>
       </c>
       <c r="M511" s="1" t="inlineStr">
         <is>
@@ -32835,11 +32835,11 @@
       </c>
       <c r="C512" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +18초</t>
+          <t>황금 물건 확률 +3%</t>
         </is>
       </c>
       <c r="D512" s="1" t="n">
-        <v>2493414</v>
+        <v>2492423</v>
       </c>
       <c r="E512" s="1" t="inlineStr">
         <is>
@@ -32862,18 +32862,18 @@
         <v>0</v>
       </c>
       <c r="K512" s="1" t="n">
-        <v>2900000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>1499818667</v>
+        <v>144856</v>
       </c>
       <c r="M512" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Gold_Item</t>
         </is>
       </c>
       <c r="N512" s="1" t="n">
-        <v>18</v>
+        <v>0.03</v>
       </c>
       <c r="O512" s="1" t="n">
         <v>0</v>
@@ -32883,7 +32883,7 @@
       </c>
       <c r="Q512" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_goldx</t>
         </is>
       </c>
       <c r="R512" s="1" t="inlineStr"/>
@@ -32925,10 +32925,10 @@
         <v>0</v>
       </c>
       <c r="K513" s="1" t="n">
-        <v>3800000000000000</v>
+        <v>2400000000000</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>1949764267</v>
+        <v>188313</v>
       </c>
       <c r="M513" s="1" t="inlineStr">
         <is>
@@ -32988,10 +32988,10 @@
         <v>0</v>
       </c>
       <c r="K514" s="1" t="n">
-        <v>2900000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>1499818667</v>
+        <v>144856</v>
       </c>
       <c r="M514" s="1" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>0</v>
       </c>
       <c r="K515" s="1" t="n">
-        <v>1400000000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L515" s="1" t="n">
-        <v>682666667</v>
+        <v>65934</v>
       </c>
       <c r="M515" s="1" t="inlineStr">
         <is>
@@ -33114,10 +33114,10 @@
         <v>0</v>
       </c>
       <c r="K516" s="1" t="n">
-        <v>1800000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L516" s="1" t="n">
-        <v>887466667</v>
+        <v>85714</v>
       </c>
       <c r="M516" s="1" t="inlineStr">
         <is>
@@ -33177,10 +33177,10 @@
         <v>0</v>
       </c>
       <c r="K517" s="1" t="n">
-        <v>2300000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L517" s="1" t="n">
-        <v>1153706667</v>
+        <v>111428</v>
       </c>
       <c r="M517" s="1" t="inlineStr">
         <is>
@@ -33240,10 +33240,10 @@
         <v>0</v>
       </c>
       <c r="K518" s="1" t="n">
-        <v>2300000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L518" s="1" t="n">
-        <v>1153706667</v>
+        <v>111428</v>
       </c>
       <c r="M518" s="1" t="inlineStr">
         <is>
@@ -33303,10 +33303,10 @@
         <v>0</v>
       </c>
       <c r="K519" s="1" t="n">
-        <v>2900000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L519" s="1" t="n">
-        <v>1499818667</v>
+        <v>144856</v>
       </c>
       <c r="M519" s="1" t="inlineStr">
         <is>
@@ -33366,10 +33366,10 @@
         <v>0</v>
       </c>
       <c r="K520" s="1" t="n">
-        <v>2900000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L520" s="1" t="n">
-        <v>1499818667</v>
+        <v>144856</v>
       </c>
       <c r="M520" s="1" t="inlineStr">
         <is>
@@ -33429,10 +33429,10 @@
         <v>0</v>
       </c>
       <c r="K521" s="1" t="n">
-        <v>2900000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L521" s="1" t="n">
-        <v>1499818667</v>
+        <v>144856</v>
       </c>
       <c r="M521" s="1" t="inlineStr">
         <is>
@@ -33492,10 +33492,10 @@
         <v>0</v>
       </c>
       <c r="K522" s="1" t="n">
-        <v>3800000000000000</v>
+        <v>2400000000000</v>
       </c>
       <c r="L522" s="1" t="n">
-        <v>1949764267</v>
+        <v>188313</v>
       </c>
       <c r="M522" s="1" t="inlineStr">
         <is>
@@ -33555,10 +33555,10 @@
         <v>0</v>
       </c>
       <c r="K523" s="1" t="n">
-        <v>1400000000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L523" s="1" t="n">
-        <v>682666667</v>
+        <v>65934</v>
       </c>
       <c r="M523" s="1" t="inlineStr">
         <is>
@@ -33618,10 +33618,10 @@
         <v>0</v>
       </c>
       <c r="K524" s="1" t="n">
-        <v>1800000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L524" s="1" t="n">
-        <v>887466667</v>
+        <v>85714</v>
       </c>
       <c r="M524" s="1" t="inlineStr">
         <is>
@@ -33681,10 +33681,10 @@
         <v>0</v>
       </c>
       <c r="K525" s="1" t="n">
-        <v>2300000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L525" s="1" t="n">
-        <v>1153706667</v>
+        <v>111428</v>
       </c>
       <c r="M525" s="1" t="inlineStr">
         <is>
@@ -33744,10 +33744,10 @@
         <v>0</v>
       </c>
       <c r="K526" s="1" t="n">
-        <v>2300000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L526" s="1" t="n">
-        <v>1153706667</v>
+        <v>111428</v>
       </c>
       <c r="M526" s="1" t="inlineStr">
         <is>
@@ -33807,10 +33807,10 @@
         <v>0</v>
       </c>
       <c r="K527" s="1" t="n">
-        <v>2900000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L527" s="1" t="n">
-        <v>1499818667</v>
+        <v>144856</v>
       </c>
       <c r="M527" s="1" t="inlineStr">
         <is>
@@ -33870,10 +33870,10 @@
         <v>0</v>
       </c>
       <c r="K528" s="1" t="n">
-        <v>2900000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L528" s="1" t="n">
-        <v>1499818667</v>
+        <v>144856</v>
       </c>
       <c r="M528" s="1" t="inlineStr">
         <is>
@@ -33933,10 +33933,10 @@
         <v>0</v>
       </c>
       <c r="K529" s="1" t="n">
-        <v>3800000000000000</v>
+        <v>2400000000000</v>
       </c>
       <c r="L529" s="1" t="n">
-        <v>1949764267</v>
+        <v>188313</v>
       </c>
       <c r="M529" s="1" t="inlineStr">
         <is>
@@ -33969,11 +33969,11 @@
       </c>
       <c r="C530" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D530" s="1" t="n">
-        <v>2492332</v>
+        <v>2493332</v>
       </c>
       <c r="E530" s="1" t="inlineStr">
         <is>
@@ -33996,10 +33996,10 @@
         <v>0</v>
       </c>
       <c r="K530" s="1" t="n">
-        <v>3500000000000000</v>
+        <v>2200000000000</v>
       </c>
       <c r="L530" s="1" t="n">
-        <v>1774933334</v>
+        <v>171427</v>
       </c>
       <c r="M530" s="1" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         </is>
       </c>
       <c r="N530" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O530" s="1" t="n">
         <v>0</v>
@@ -34059,10 +34059,10 @@
         <v>0</v>
       </c>
       <c r="K531" s="1" t="n">
-        <v>2300000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L531" s="1" t="n">
-        <v>1153706667</v>
+        <v>111428</v>
       </c>
       <c r="M531" s="1" t="inlineStr">
         <is>
@@ -34095,11 +34095,11 @@
       </c>
       <c r="C532" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D532" s="1" t="n">
-        <v>2492332</v>
+        <v>2493332</v>
       </c>
       <c r="E532" s="1" t="inlineStr">
         <is>
@@ -34122,10 +34122,10 @@
         <v>0</v>
       </c>
       <c r="K532" s="1" t="n">
-        <v>5800000000000000</v>
+        <v>3600000000000</v>
       </c>
       <c r="L532" s="1" t="n">
-        <v>2999637334</v>
+        <v>289711</v>
       </c>
       <c r="M532" s="1" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         </is>
       </c>
       <c r="N532" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O532" s="1" t="n">
         <v>0</v>
@@ -34185,10 +34185,10 @@
         <v>0</v>
       </c>
       <c r="K533" s="1" t="n">
-        <v>2300000000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L533" s="1" t="n">
-        <v>1153706667</v>
+        <v>111428</v>
       </c>
       <c r="M533" s="1" t="inlineStr">
         <is>
@@ -34248,10 +34248,10 @@
         <v>0</v>
       </c>
       <c r="K534" s="1" t="n">
-        <v>3800000000000000</v>
+        <v>2400000000000</v>
       </c>
       <c r="L534" s="1" t="n">
-        <v>1949764267</v>
+        <v>188313</v>
       </c>
       <c r="M534" s="1" t="inlineStr">
         <is>
@@ -34311,10 +34311,10 @@
         <v>0</v>
       </c>
       <c r="K535" s="1" t="n">
-        <v>2900000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L535" s="1" t="n">
-        <v>1499818667</v>
+        <v>144856</v>
       </c>
       <c r="M535" s="1" t="inlineStr">
         <is>
@@ -34443,10 +34443,10 @@
         <v>0</v>
       </c>
       <c r="K537" s="1" t="n">
-        <v>4400000000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="L537" s="1" t="n">
-        <v>1824000000</v>
+        <v>148720</v>
       </c>
       <c r="M537" s="1" t="inlineStr">
         <is>
@@ -34506,10 +34506,10 @@
         <v>0</v>
       </c>
       <c r="K538" s="1" t="n">
-        <v>5800000000000000</v>
+        <v>2600000000000</v>
       </c>
       <c r="L538" s="1" t="n">
-        <v>2371200000</v>
+        <v>193336</v>
       </c>
       <c r="M538" s="1" t="inlineStr">
         <is>
@@ -34569,10 +34569,10 @@
         <v>0</v>
       </c>
       <c r="K539" s="1" t="n">
-        <v>7500000000000000</v>
+        <v>3400000000000</v>
       </c>
       <c r="L539" s="1" t="n">
-        <v>3082560001</v>
+        <v>251337</v>
       </c>
       <c r="M539" s="1" t="inlineStr">
         <is>
@@ -34632,10 +34632,10 @@
         <v>0</v>
       </c>
       <c r="K540" s="1" t="n">
-        <v>7500000000000000</v>
+        <v>3400000000000</v>
       </c>
       <c r="L540" s="1" t="n">
-        <v>3082560001</v>
+        <v>251337</v>
       </c>
       <c r="M540" s="1" t="inlineStr">
         <is>
@@ -34695,10 +34695,10 @@
         <v>0</v>
       </c>
       <c r="K541" s="1" t="n">
-        <v>9700000000000000</v>
+        <v>4400000000000</v>
       </c>
       <c r="L541" s="1" t="n">
-        <v>4007328000</v>
+        <v>326738</v>
       </c>
       <c r="M541" s="1" t="inlineStr">
         <is>
@@ -34758,10 +34758,10 @@
         <v>0</v>
       </c>
       <c r="K542" s="1" t="n">
-        <v>7500000000000000</v>
+        <v>3400000000000</v>
       </c>
       <c r="L542" s="1" t="n">
-        <v>3082560001</v>
+        <v>251337</v>
       </c>
       <c r="M542" s="1" t="inlineStr">
         <is>
@@ -34821,10 +34821,10 @@
         <v>0</v>
       </c>
       <c r="K543" s="1" t="n">
-        <v>9700000000000000</v>
+        <v>4400000000000</v>
       </c>
       <c r="L543" s="1" t="n">
-        <v>4007328000</v>
+        <v>326738</v>
       </c>
       <c r="M543" s="1" t="inlineStr">
         <is>
@@ -34884,10 +34884,10 @@
         <v>0</v>
       </c>
       <c r="K544" s="1" t="n">
-        <v>9700000000000000</v>
+        <v>4400000000000</v>
       </c>
       <c r="L544" s="1" t="n">
-        <v>4007328000</v>
+        <v>326738</v>
       </c>
       <c r="M544" s="1" t="inlineStr">
         <is>
@@ -34947,10 +34947,10 @@
         <v>0</v>
       </c>
       <c r="K545" s="1" t="n">
-        <v>4400000000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="L545" s="1" t="n">
-        <v>1824000000</v>
+        <v>148720</v>
       </c>
       <c r="M545" s="1" t="inlineStr">
         <is>
@@ -34983,11 +34983,11 @@
       </c>
       <c r="C546" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +18초</t>
+          <t>생명체 처치 치즈 +120%</t>
         </is>
       </c>
       <c r="D546" s="1" t="n">
-        <v>2493414</v>
+        <v>2493510</v>
       </c>
       <c r="E546" s="1" t="inlineStr">
         <is>
@@ -35010,28 +35010,28 @@
         <v>0</v>
       </c>
       <c r="K546" s="1" t="n">
-        <v>5800000000000000</v>
+        <v>2600000000000</v>
       </c>
       <c r="L546" s="1" t="n">
-        <v>2371200000</v>
+        <v>193336</v>
       </c>
       <c r="M546" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Cheese_Pct</t>
         </is>
       </c>
       <c r="N546" s="1" t="n">
-        <v>18</v>
+        <v>1.2</v>
       </c>
       <c r="O546" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P546" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q546" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_cheesecreature</t>
         </is>
       </c>
       <c r="R546" s="1" t="inlineStr"/>
@@ -35073,10 +35073,10 @@
         <v>0</v>
       </c>
       <c r="K547" s="1" t="n">
-        <v>7500000000000000</v>
+        <v>3400000000000</v>
       </c>
       <c r="L547" s="1" t="n">
-        <v>3082560001</v>
+        <v>251337</v>
       </c>
       <c r="M547" s="1" t="inlineStr">
         <is>
@@ -35136,10 +35136,10 @@
         <v>0</v>
       </c>
       <c r="K548" s="1" t="n">
-        <v>7500000000000000</v>
+        <v>3400000000000</v>
       </c>
       <c r="L548" s="1" t="n">
-        <v>3082560001</v>
+        <v>251337</v>
       </c>
       <c r="M548" s="1" t="inlineStr">
         <is>
@@ -35199,10 +35199,10 @@
         <v>0</v>
       </c>
       <c r="K549" s="1" t="n">
-        <v>7500000000000000</v>
+        <v>3400000000000</v>
       </c>
       <c r="L549" s="1" t="n">
-        <v>3082560001</v>
+        <v>251337</v>
       </c>
       <c r="M549" s="1" t="inlineStr">
         <is>
@@ -35235,11 +35235,11 @@
       </c>
       <c r="C550" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +19초</t>
+          <t>황금 물건 확률 +3%</t>
         </is>
       </c>
       <c r="D550" s="1" t="n">
-        <v>2493514</v>
+        <v>2492423</v>
       </c>
       <c r="E550" s="1" t="inlineStr">
         <is>
@@ -35262,18 +35262,18 @@
         <v>0</v>
       </c>
       <c r="K550" s="1" t="n">
-        <v>9700000000000000</v>
+        <v>4400000000000</v>
       </c>
       <c r="L550" s="1" t="n">
-        <v>4007328000</v>
+        <v>326738</v>
       </c>
       <c r="M550" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Gold_Item</t>
         </is>
       </c>
       <c r="N550" s="1" t="n">
-        <v>19</v>
+        <v>0.03</v>
       </c>
       <c r="O550" s="1" t="n">
         <v>0</v>
@@ -35283,7 +35283,7 @@
       </c>
       <c r="Q550" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_goldx</t>
         </is>
       </c>
       <c r="R550" s="1" t="inlineStr"/>
@@ -35325,10 +35325,10 @@
         <v>0</v>
       </c>
       <c r="K551" s="1" t="n">
-        <v>1.3e+16</v>
+        <v>5700000000000</v>
       </c>
       <c r="L551" s="1" t="n">
-        <v>5209526401</v>
+        <v>424760</v>
       </c>
       <c r="M551" s="1" t="inlineStr">
         <is>
@@ -35388,10 +35388,10 @@
         <v>0</v>
       </c>
       <c r="K552" s="1" t="n">
-        <v>9700000000000000</v>
+        <v>4400000000000</v>
       </c>
       <c r="L552" s="1" t="n">
-        <v>4007328000</v>
+        <v>326738</v>
       </c>
       <c r="M552" s="1" t="inlineStr">
         <is>
@@ -35451,10 +35451,10 @@
         <v>0</v>
       </c>
       <c r="K553" s="1" t="n">
-        <v>4400000000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="L553" s="1" t="n">
-        <v>1824000000</v>
+        <v>148720</v>
       </c>
       <c r="M553" s="1" t="inlineStr">
         <is>
@@ -35514,10 +35514,10 @@
         <v>0</v>
       </c>
       <c r="K554" s="1" t="n">
-        <v>5800000000000000</v>
+        <v>2600000000000</v>
       </c>
       <c r="L554" s="1" t="n">
-        <v>2371200000</v>
+        <v>193336</v>
       </c>
       <c r="M554" s="1" t="inlineStr">
         <is>
@@ -35577,10 +35577,10 @@
         <v>0</v>
       </c>
       <c r="K555" s="1" t="n">
-        <v>7500000000000000</v>
+        <v>3400000000000</v>
       </c>
       <c r="L555" s="1" t="n">
-        <v>3082560001</v>
+        <v>251337</v>
       </c>
       <c r="M555" s="1" t="inlineStr">
         <is>
@@ -35640,10 +35640,10 @@
         <v>0</v>
       </c>
       <c r="K556" s="1" t="n">
-        <v>7500000000000000</v>
+        <v>3400000000000</v>
       </c>
       <c r="L556" s="1" t="n">
-        <v>3082560001</v>
+        <v>251337</v>
       </c>
       <c r="M556" s="1" t="inlineStr">
         <is>
@@ -35703,10 +35703,10 @@
         <v>0</v>
       </c>
       <c r="K557" s="1" t="n">
-        <v>9700000000000000</v>
+        <v>4400000000000</v>
       </c>
       <c r="L557" s="1" t="n">
-        <v>4007328000</v>
+        <v>326738</v>
       </c>
       <c r="M557" s="1" t="inlineStr">
         <is>
@@ -35766,10 +35766,10 @@
         <v>0</v>
       </c>
       <c r="K558" s="1" t="n">
-        <v>9700000000000000</v>
+        <v>4400000000000</v>
       </c>
       <c r="L558" s="1" t="n">
-        <v>4007328000</v>
+        <v>326738</v>
       </c>
       <c r="M558" s="1" t="inlineStr">
         <is>
@@ -35829,10 +35829,10 @@
         <v>0</v>
       </c>
       <c r="K559" s="1" t="n">
-        <v>9700000000000000</v>
+        <v>4400000000000</v>
       </c>
       <c r="L559" s="1" t="n">
-        <v>4007328000</v>
+        <v>326738</v>
       </c>
       <c r="M559" s="1" t="inlineStr">
         <is>
@@ -35892,10 +35892,10 @@
         <v>0</v>
       </c>
       <c r="K560" s="1" t="n">
-        <v>1.3e+16</v>
+        <v>5700000000000</v>
       </c>
       <c r="L560" s="1" t="n">
-        <v>5209526401</v>
+        <v>424760</v>
       </c>
       <c r="M560" s="1" t="inlineStr">
         <is>
@@ -35955,10 +35955,10 @@
         <v>0</v>
       </c>
       <c r="K561" s="1" t="n">
-        <v>4400000000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="L561" s="1" t="n">
-        <v>1824000000</v>
+        <v>148720</v>
       </c>
       <c r="M561" s="1" t="inlineStr">
         <is>
@@ -36018,10 +36018,10 @@
         <v>0</v>
       </c>
       <c r="K562" s="1" t="n">
-        <v>5800000000000000</v>
+        <v>2600000000000</v>
       </c>
       <c r="L562" s="1" t="n">
-        <v>2371200000</v>
+        <v>193336</v>
       </c>
       <c r="M562" s="1" t="inlineStr">
         <is>
@@ -36081,10 +36081,10 @@
         <v>0</v>
       </c>
       <c r="K563" s="1" t="n">
-        <v>7500000000000000</v>
+        <v>3400000000000</v>
       </c>
       <c r="L563" s="1" t="n">
-        <v>3082560001</v>
+        <v>251337</v>
       </c>
       <c r="M563" s="1" t="inlineStr">
         <is>
@@ -36144,10 +36144,10 @@
         <v>0</v>
       </c>
       <c r="K564" s="1" t="n">
-        <v>7500000000000000</v>
+        <v>3400000000000</v>
       </c>
       <c r="L564" s="1" t="n">
-        <v>3082560001</v>
+        <v>251337</v>
       </c>
       <c r="M564" s="1" t="inlineStr">
         <is>
@@ -36207,10 +36207,10 @@
         <v>0</v>
       </c>
       <c r="K565" s="1" t="n">
-        <v>9700000000000000</v>
+        <v>4400000000000</v>
       </c>
       <c r="L565" s="1" t="n">
-        <v>4007328000</v>
+        <v>326738</v>
       </c>
       <c r="M565" s="1" t="inlineStr">
         <is>
@@ -36270,10 +36270,10 @@
         <v>0</v>
       </c>
       <c r="K566" s="1" t="n">
-        <v>9700000000000000</v>
+        <v>4400000000000</v>
       </c>
       <c r="L566" s="1" t="n">
-        <v>4007328000</v>
+        <v>326738</v>
       </c>
       <c r="M566" s="1" t="inlineStr">
         <is>
@@ -36333,10 +36333,10 @@
         <v>0</v>
       </c>
       <c r="K567" s="1" t="n">
-        <v>1.3e+16</v>
+        <v>5700000000000</v>
       </c>
       <c r="L567" s="1" t="n">
-        <v>5209526401</v>
+        <v>424760</v>
       </c>
       <c r="M567" s="1" t="inlineStr">
         <is>
@@ -36369,11 +36369,11 @@
       </c>
       <c r="C568" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +7층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D568" s="1" t="n">
-        <v>2493532</v>
+        <v>2493332</v>
       </c>
       <c r="E568" s="1" t="inlineStr">
         <is>
@@ -36396,10 +36396,10 @@
         <v>0</v>
       </c>
       <c r="K568" s="1" t="n">
-        <v>1.2e+16</v>
+        <v>5200000000000</v>
       </c>
       <c r="L568" s="1" t="n">
-        <v>4742400000</v>
+        <v>386672</v>
       </c>
       <c r="M568" s="1" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         </is>
       </c>
       <c r="N568" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O568" s="1" t="n">
         <v>0</v>
@@ -36459,10 +36459,10 @@
         <v>0</v>
       </c>
       <c r="K569" s="1" t="n">
-        <v>7500000000000000</v>
+        <v>3400000000000</v>
       </c>
       <c r="L569" s="1" t="n">
-        <v>3082560001</v>
+        <v>251337</v>
       </c>
       <c r="M569" s="1" t="inlineStr">
         <is>
@@ -36495,11 +36495,11 @@
       </c>
       <c r="C570" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +7층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D570" s="1" t="n">
-        <v>2493532</v>
+        <v>2493332</v>
       </c>
       <c r="E570" s="1" t="inlineStr">
         <is>
@@ -36522,10 +36522,10 @@
         <v>0</v>
       </c>
       <c r="K570" s="1" t="n">
-        <v>2e+16</v>
+        <v>8800000000000</v>
       </c>
       <c r="L570" s="1" t="n">
-        <v>8014656000</v>
+        <v>653476</v>
       </c>
       <c r="M570" s="1" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         </is>
       </c>
       <c r="N570" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O570" s="1" t="n">
         <v>0</v>
@@ -36585,10 +36585,10 @@
         <v>0</v>
       </c>
       <c r="K571" s="1" t="n">
-        <v>7500000000000000</v>
+        <v>3400000000000</v>
       </c>
       <c r="L571" s="1" t="n">
-        <v>3082560001</v>
+        <v>251337</v>
       </c>
       <c r="M571" s="1" t="inlineStr">
         <is>
@@ -36648,10 +36648,10 @@
         <v>0</v>
       </c>
       <c r="K572" s="1" t="n">
-        <v>1.3e+16</v>
+        <v>5700000000000</v>
       </c>
       <c r="L572" s="1" t="n">
-        <v>5209526401</v>
+        <v>424760</v>
       </c>
       <c r="M572" s="1" t="inlineStr">
         <is>
@@ -36711,10 +36711,10 @@
         <v>0</v>
       </c>
       <c r="K573" s="1" t="n">
-        <v>9700000000000000</v>
+        <v>4400000000000</v>
       </c>
       <c r="L573" s="1" t="n">
-        <v>4007328000</v>
+        <v>326738</v>
       </c>
       <c r="M573" s="1" t="inlineStr">
         <is>
@@ -36843,10 +36843,10 @@
         <v>0</v>
       </c>
       <c r="K575" s="1" t="n">
-        <v>1.4e+16</v>
+        <v>5800000000000</v>
       </c>
       <c r="L575" s="1" t="n">
-        <v>4560000000</v>
+        <v>371800</v>
       </c>
       <c r="M575" s="1" t="inlineStr">
         <is>
@@ -36906,10 +36906,10 @@
         <v>0</v>
       </c>
       <c r="K576" s="1" t="n">
-        <v>1.8e+16</v>
+        <v>7600000000000</v>
       </c>
       <c r="L576" s="1" t="n">
-        <v>5928000000</v>
+        <v>483340</v>
       </c>
       <c r="M576" s="1" t="inlineStr">
         <is>
@@ -36969,10 +36969,10 @@
         <v>0</v>
       </c>
       <c r="K577" s="1" t="n">
-        <v>2.4e+16</v>
+        <v>9800000000000</v>
       </c>
       <c r="L577" s="1" t="n">
-        <v>7706400001</v>
+        <v>628343</v>
       </c>
       <c r="M577" s="1" t="inlineStr">
         <is>
@@ -37032,10 +37032,10 @@
         <v>0</v>
       </c>
       <c r="K578" s="1" t="n">
-        <v>2.4e+16</v>
+        <v>9800000000000</v>
       </c>
       <c r="L578" s="1" t="n">
-        <v>7706400001</v>
+        <v>628343</v>
       </c>
       <c r="M578" s="1" t="inlineStr">
         <is>
@@ -37095,10 +37095,10 @@
         <v>0</v>
       </c>
       <c r="K579" s="1" t="n">
-        <v>3.1e+16</v>
+        <v>13000000000000</v>
       </c>
       <c r="L579" s="1" t="n">
-        <v>10018320000</v>
+        <v>816845</v>
       </c>
       <c r="M579" s="1" t="inlineStr">
         <is>
@@ -37158,10 +37158,10 @@
         <v>0</v>
       </c>
       <c r="K580" s="1" t="n">
-        <v>2.4e+16</v>
+        <v>9800000000000</v>
       </c>
       <c r="L580" s="1" t="n">
-        <v>7706400001</v>
+        <v>628343</v>
       </c>
       <c r="M580" s="1" t="inlineStr">
         <is>
@@ -37221,10 +37221,10 @@
         <v>0</v>
       </c>
       <c r="K581" s="1" t="n">
-        <v>3.1e+16</v>
+        <v>13000000000000</v>
       </c>
       <c r="L581" s="1" t="n">
-        <v>10018320000</v>
+        <v>816845</v>
       </c>
       <c r="M581" s="1" t="inlineStr">
         <is>
@@ -37284,10 +37284,10 @@
         <v>0</v>
       </c>
       <c r="K582" s="1" t="n">
-        <v>3.1e+16</v>
+        <v>13000000000000</v>
       </c>
       <c r="L582" s="1" t="n">
-        <v>10018320000</v>
+        <v>816845</v>
       </c>
       <c r="M582" s="1" t="inlineStr">
         <is>
@@ -37347,10 +37347,10 @@
         <v>0</v>
       </c>
       <c r="K583" s="1" t="n">
-        <v>1.4e+16</v>
+        <v>5800000000000</v>
       </c>
       <c r="L583" s="1" t="n">
-        <v>4560000000</v>
+        <v>371800</v>
       </c>
       <c r="M583" s="1" t="inlineStr">
         <is>
@@ -37383,11 +37383,11 @@
       </c>
       <c r="C584" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +19초</t>
+          <t>생명체 처치 치즈 +130%</t>
         </is>
       </c>
       <c r="D584" s="1" t="n">
-        <v>2493514</v>
+        <v>2493021</v>
       </c>
       <c r="E584" s="1" t="inlineStr">
         <is>
@@ -37410,28 +37410,28 @@
         <v>0</v>
       </c>
       <c r="K584" s="1" t="n">
-        <v>1.8e+16</v>
+        <v>7600000000000</v>
       </c>
       <c r="L584" s="1" t="n">
-        <v>5928000000</v>
+        <v>483340</v>
       </c>
       <c r="M584" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Cheese_Pct</t>
         </is>
       </c>
       <c r="N584" s="1" t="n">
-        <v>19</v>
+        <v>1.3</v>
       </c>
       <c r="O584" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P584" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Q584" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_cheesecreature</t>
         </is>
       </c>
       <c r="R584" s="1" t="inlineStr"/>
@@ -37473,10 +37473,10 @@
         <v>0</v>
       </c>
       <c r="K585" s="1" t="n">
-        <v>2.4e+16</v>
+        <v>9800000000000</v>
       </c>
       <c r="L585" s="1" t="n">
-        <v>7706400001</v>
+        <v>628343</v>
       </c>
       <c r="M585" s="1" t="inlineStr">
         <is>
@@ -37536,10 +37536,10 @@
         <v>0</v>
       </c>
       <c r="K586" s="1" t="n">
-        <v>2.4e+16</v>
+        <v>9800000000000</v>
       </c>
       <c r="L586" s="1" t="n">
-        <v>7706400001</v>
+        <v>628343</v>
       </c>
       <c r="M586" s="1" t="inlineStr">
         <is>
@@ -37599,10 +37599,10 @@
         <v>0</v>
       </c>
       <c r="K587" s="1" t="n">
-        <v>2.4e+16</v>
+        <v>9800000000000</v>
       </c>
       <c r="L587" s="1" t="n">
-        <v>7706400001</v>
+        <v>628343</v>
       </c>
       <c r="M587" s="1" t="inlineStr">
         <is>
@@ -37635,11 +37635,11 @@
       </c>
       <c r="C588" s="1" t="inlineStr">
         <is>
-          <t>층 제한시간 +20초</t>
+          <t>황금 물건 확률 +3%</t>
         </is>
       </c>
       <c r="D588" s="1" t="n">
-        <v>2493614</v>
+        <v>2492423</v>
       </c>
       <c r="E588" s="1" t="inlineStr">
         <is>
@@ -37662,18 +37662,18 @@
         <v>0</v>
       </c>
       <c r="K588" s="1" t="n">
-        <v>3.1e+16</v>
+        <v>13000000000000</v>
       </c>
       <c r="L588" s="1" t="n">
-        <v>10018320000</v>
+        <v>816845</v>
       </c>
       <c r="M588" s="1" t="inlineStr">
         <is>
-          <t>Time_Add</t>
+          <t>Gold_Item</t>
         </is>
       </c>
       <c r="N588" s="1" t="n">
-        <v>20</v>
+        <v>0.03</v>
       </c>
       <c r="O588" s="1" t="n">
         <v>0</v>
@@ -37683,7 +37683,7 @@
       </c>
       <c r="Q588" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_clock</t>
+          <t>SkillIcons/cs_goldx</t>
         </is>
       </c>
       <c r="R588" s="1" t="inlineStr"/>
@@ -37725,10 +37725,10 @@
         <v>0</v>
       </c>
       <c r="K589" s="1" t="n">
-        <v>4e+16</v>
+        <v>17000000000000</v>
       </c>
       <c r="L589" s="1" t="n">
-        <v>13023816001</v>
+        <v>1061898</v>
       </c>
       <c r="M589" s="1" t="inlineStr">
         <is>
@@ -37788,10 +37788,10 @@
         <v>0</v>
       </c>
       <c r="K590" s="1" t="n">
-        <v>3.1e+16</v>
+        <v>13000000000000</v>
       </c>
       <c r="L590" s="1" t="n">
-        <v>10018320000</v>
+        <v>816845</v>
       </c>
       <c r="M590" s="1" t="inlineStr">
         <is>
@@ -37851,10 +37851,10 @@
         <v>0</v>
       </c>
       <c r="K591" s="1" t="n">
-        <v>1.4e+16</v>
+        <v>5800000000000</v>
       </c>
       <c r="L591" s="1" t="n">
-        <v>4560000000</v>
+        <v>371800</v>
       </c>
       <c r="M591" s="1" t="inlineStr">
         <is>
@@ -37914,10 +37914,10 @@
         <v>0</v>
       </c>
       <c r="K592" s="1" t="n">
-        <v>1.8e+16</v>
+        <v>7600000000000</v>
       </c>
       <c r="L592" s="1" t="n">
-        <v>5928000000</v>
+        <v>483340</v>
       </c>
       <c r="M592" s="1" t="inlineStr">
         <is>
@@ -37977,10 +37977,10 @@
         <v>0</v>
       </c>
       <c r="K593" s="1" t="n">
-        <v>2.4e+16</v>
+        <v>9800000000000</v>
       </c>
       <c r="L593" s="1" t="n">
-        <v>7706400001</v>
+        <v>628343</v>
       </c>
       <c r="M593" s="1" t="inlineStr">
         <is>
@@ -38040,10 +38040,10 @@
         <v>0</v>
       </c>
       <c r="K594" s="1" t="n">
-        <v>2.4e+16</v>
+        <v>9800000000000</v>
       </c>
       <c r="L594" s="1" t="n">
-        <v>7706400001</v>
+        <v>628343</v>
       </c>
       <c r="M594" s="1" t="inlineStr">
         <is>
@@ -38103,10 +38103,10 @@
         <v>0</v>
       </c>
       <c r="K595" s="1" t="n">
-        <v>3.1e+16</v>
+        <v>13000000000000</v>
       </c>
       <c r="L595" s="1" t="n">
-        <v>10018320000</v>
+        <v>816845</v>
       </c>
       <c r="M595" s="1" t="inlineStr">
         <is>
@@ -38166,10 +38166,10 @@
         <v>0</v>
       </c>
       <c r="K596" s="1" t="n">
-        <v>3.1e+16</v>
+        <v>13000000000000</v>
       </c>
       <c r="L596" s="1" t="n">
-        <v>10018320000</v>
+        <v>816845</v>
       </c>
       <c r="M596" s="1" t="inlineStr">
         <is>
@@ -38229,10 +38229,10 @@
         <v>0</v>
       </c>
       <c r="K597" s="1" t="n">
-        <v>3.1e+16</v>
+        <v>13000000000000</v>
       </c>
       <c r="L597" s="1" t="n">
-        <v>10018320000</v>
+        <v>816845</v>
       </c>
       <c r="M597" s="1" t="inlineStr">
         <is>
@@ -38292,10 +38292,10 @@
         <v>0</v>
       </c>
       <c r="K598" s="1" t="n">
-        <v>4e+16</v>
+        <v>17000000000000</v>
       </c>
       <c r="L598" s="1" t="n">
-        <v>13023816001</v>
+        <v>1061898</v>
       </c>
       <c r="M598" s="1" t="inlineStr">
         <is>
@@ -38355,10 +38355,10 @@
         <v>0</v>
       </c>
       <c r="K599" s="1" t="n">
-        <v>1.4e+16</v>
+        <v>5800000000000</v>
       </c>
       <c r="L599" s="1" t="n">
-        <v>4560000000</v>
+        <v>371800</v>
       </c>
       <c r="M599" s="1" t="inlineStr">
         <is>
@@ -38418,10 +38418,10 @@
         <v>0</v>
       </c>
       <c r="K600" s="1" t="n">
-        <v>1.8e+16</v>
+        <v>7600000000000</v>
       </c>
       <c r="L600" s="1" t="n">
-        <v>5928000000</v>
+        <v>483340</v>
       </c>
       <c r="M600" s="1" t="inlineStr">
         <is>
@@ -38481,10 +38481,10 @@
         <v>0</v>
       </c>
       <c r="K601" s="1" t="n">
-        <v>2.4e+16</v>
+        <v>9800000000000</v>
       </c>
       <c r="L601" s="1" t="n">
-        <v>7706400001</v>
+        <v>628343</v>
       </c>
       <c r="M601" s="1" t="inlineStr">
         <is>
@@ -38544,10 +38544,10 @@
         <v>0</v>
       </c>
       <c r="K602" s="1" t="n">
-        <v>2.4e+16</v>
+        <v>9800000000000</v>
       </c>
       <c r="L602" s="1" t="n">
-        <v>7706400001</v>
+        <v>628343</v>
       </c>
       <c r="M602" s="1" t="inlineStr">
         <is>
@@ -38607,10 +38607,10 @@
         <v>0</v>
       </c>
       <c r="K603" s="1" t="n">
-        <v>3.1e+16</v>
+        <v>13000000000000</v>
       </c>
       <c r="L603" s="1" t="n">
-        <v>10018320000</v>
+        <v>816845</v>
       </c>
       <c r="M603" s="1" t="inlineStr">
         <is>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="K604" s="1" t="n">
-        <v>3.1e+16</v>
+        <v>13000000000000</v>
       </c>
       <c r="L604" s="1" t="n">
-        <v>10018320000</v>
+        <v>816845</v>
       </c>
       <c r="M604" s="1" t="inlineStr">
         <is>
@@ -38733,10 +38733,10 @@
         <v>0</v>
       </c>
       <c r="K605" s="1" t="n">
-        <v>4e+16</v>
+        <v>17000000000000</v>
       </c>
       <c r="L605" s="1" t="n">
-        <v>13023816001</v>
+        <v>1061898</v>
       </c>
       <c r="M605" s="1" t="inlineStr">
         <is>
@@ -38769,11 +38769,11 @@
       </c>
       <c r="C606" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D606" s="1" t="n">
-        <v>2492332</v>
+        <v>2493332</v>
       </c>
       <c r="E606" s="1" t="inlineStr">
         <is>
@@ -38796,10 +38796,10 @@
         <v>0</v>
       </c>
       <c r="K606" s="1" t="n">
-        <v>3.6e+16</v>
+        <v>16000000000000</v>
       </c>
       <c r="L606" s="1" t="n">
-        <v>11856000000</v>
+        <v>966680</v>
       </c>
       <c r="M606" s="1" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         </is>
       </c>
       <c r="N606" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O606" s="1" t="n">
         <v>0</v>
@@ -38859,10 +38859,10 @@
         <v>0</v>
       </c>
       <c r="K607" s="1" t="n">
-        <v>2.4e+16</v>
+        <v>9800000000000</v>
       </c>
       <c r="L607" s="1" t="n">
-        <v>7706400001</v>
+        <v>628343</v>
       </c>
       <c r="M607" s="1" t="inlineStr">
         <is>
@@ -38895,11 +38895,11 @@
       </c>
       <c r="C608" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D608" s="1" t="n">
-        <v>2492132</v>
+        <v>2493332</v>
       </c>
       <c r="E608" s="1" t="inlineStr">
         <is>
@@ -38922,10 +38922,10 @@
         <v>0</v>
       </c>
       <c r="K608" s="1" t="n">
-        <v>6.1e+16</v>
+        <v>26000000000000</v>
       </c>
       <c r="L608" s="1" t="n">
-        <v>20036640000</v>
+        <v>1633690</v>
       </c>
       <c r="M608" s="1" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         </is>
       </c>
       <c r="N608" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O608" s="1" t="n">
         <v>0</v>
@@ -38985,10 +38985,10 @@
         <v>0</v>
       </c>
       <c r="K609" s="1" t="n">
-        <v>2.4e+16</v>
+        <v>9800000000000</v>
       </c>
       <c r="L609" s="1" t="n">
-        <v>7706400001</v>
+        <v>628343</v>
       </c>
       <c r="M609" s="1" t="inlineStr">
         <is>
@@ -39048,10 +39048,10 @@
         <v>0</v>
       </c>
       <c r="K610" s="1" t="n">
-        <v>4e+16</v>
+        <v>17000000000000</v>
       </c>
       <c r="L610" s="1" t="n">
-        <v>13023816001</v>
+        <v>1061898</v>
       </c>
       <c r="M610" s="1" t="inlineStr">
         <is>
@@ -39084,11 +39084,11 @@
       </c>
       <c r="C611" s="1" t="inlineStr">
         <is>
-          <t>필살기 쿨타임 -5초</t>
+          <t>증강 슬롯 +1</t>
         </is>
       </c>
       <c r="D611" s="1" t="n">
-        <v>2493637</v>
+        <v>2493033</v>
       </c>
       <c r="E611" s="1" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         </is>
       </c>
       <c r="F611" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G611" s="1" t="n">
         <v>2</v>
@@ -39111,18 +39111,18 @@
         <v>0</v>
       </c>
       <c r="K611" s="1" t="n">
-        <v>3.1e+16</v>
+        <v>26000000000000</v>
       </c>
       <c r="L611" s="1" t="n">
-        <v>10018320000</v>
+        <v>1633690</v>
       </c>
       <c r="M611" s="1" t="inlineStr">
         <is>
-          <t>Ult_CD</t>
+          <t>Aug_Slot</t>
         </is>
       </c>
       <c r="N611" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O611" s="1" t="n">
         <v>0</v>
@@ -39132,7 +39132,7 @@
       </c>
       <c r="Q611" s="1" t="inlineStr">
         <is>
-          <t>SkillIcons/cs_ultcd</t>
+          <t>SkillIcons/cs_stock</t>
         </is>
       </c>
       <c r="R611" s="1" t="inlineStr"/>
@@ -39400,7 +39400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -40385,17 +40385,17 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Ult_Power_Pct</t>
+          <t>Aug_Slot</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>필살기 피해 ×(1 + 합)</t>
+          <t>증강 장착 슬롯 + 합 (기본 = 증강 테이블 Aug_Config slot_base 5)</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>증가율</t>
+          <t>칸 수</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
@@ -40412,17 +40412,17 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Ult_Auto</t>
+          <t>Research_Pct</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>필살기 자동 사용</t>
+          <t>층 클리어 연구자료 ×(1 + 합) (증강용)</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>증가율</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -40439,12 +40439,12 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Super_Jump_Pct</t>
+          <t>Ult_Power_Pct</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>슈퍼 점프 확률 ×(1 + 합)</t>
+          <t>필살기 피해 ×(1 + 합)</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -40466,49 +40466,49 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Bite_Zap</t>
+          <t>Ult_Auto</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>물 때 확률 합으로 주변 물건 감전</t>
+          <t>필살기 자동 사용</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>확률</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>감전 개수 (가장 큰 값)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>피해 배율 (가장 큰 값)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Chain_Blast</t>
+          <t>Super_Jump_Pct</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>물건이 터질 때 연쇄 폭발 범위 + 합 · 피해 + 합</t>
+          <t>슈퍼 점프 확률 ×(1 + 합)</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>범위</t>
+          <t>증가율</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>피해 증가</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -40520,49 +40520,49 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Cheese_Meteor</t>
+          <t>Bite_Zap</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>치즈 운석: 밸류_01 &gt; 0 인 노드가 있으면 켜짐 (간격 = 가장 작은 밸류_01). 위력 = 무리 평균 힘 × (1 + 밸류_02 합)</t>
+          <t>물 때 확률 합으로 주변 물건 감전</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>간격 (초)</t>
+          <t>확률</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>위력 증가</t>
+          <t>감전 개수 (가장 큰 값)</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>피해 배율 (가장 큰 값)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Twin_Chance</t>
+          <t>Chain_Blast</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>쌍둥이 확률 + 합</t>
+          <t>물건이 터질 때 연쇄 폭발 범위 + 합 · 피해 + 합</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>확률</t>
+          <t>범위</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>피해 증가</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -40574,22 +40574,22 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Mutation_Chance</t>
+          <t>Cheese_Meteor</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>탄생 등급 배율(티어 테이블 birth_grade_k) + 합</t>
+          <t>치즈 운석: 밸류_01 &gt; 0 인 노드가 있으면 켜짐 (간격 = 가장 작은 밸류_01). 위력 = 무리 평균 힘 × (1 + 밸류_02 합)</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>배율 증가</t>
+          <t>간격 (초)</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>위력 증가</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -40601,49 +40601,49 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Birth_Frenzy</t>
+          <t>Twin_Chance</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>탄생 축제: 새끼가 태어나면 주변 쥐 광란 (시간 합 · 반경·배율은 가장 큰 값)</t>
+          <t>쌍둥이 확률 + 합</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>시간 (초)</t>
+          <t>확률</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>반경</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>배율</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Furniture_Pct</t>
+          <t>Mutation_Chance</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>가구 피해 ×(1 + 밸류_01 합) · 가구 치즈 ×(1 + 밸류_02 합)</t>
+          <t>탄생 등급 배율(티어 테이블 birth_grade_k) + 합</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>피해 증가</t>
+          <t>배율 증가</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>치즈 증가</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -40655,49 +40655,49 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Air_Cheese_Pct</t>
+          <t>Birth_Frenzy</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>공중에서 부딪힌 물건 치즈 ×(1 + 합)</t>
+          <t>탄생 축제: 새끼가 태어나면 주변 쥐 광란 (시간 합 · 반경·배율은 가장 큰 값)</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>증가율</t>
+          <t>시간 (초)</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>반경</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>배율</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Ult_CD</t>
+          <t>Furniture_Pct</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>필살기 하나가 끝난 뒤 다음 필살기까지 쿨타임 - 합 (초, 기본 UltimateManager.ultCooldown, 최소 ultCooldownMin)</t>
+          <t>가구 피해 ×(1 + 밸류_01 합) · 가구 치즈 ×(1 + 밸류_02 합)</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>초</t>
+          <t>피해 증가</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>치즈 증가</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -40709,17 +40709,17 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Rush_CD</t>
+          <t>Air_Cheese_Pct</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>클릭 총공격 쿨타임 - 합 (초, 최소 RatManager.rushCooldownMin)</t>
+          <t>공중에서 부딪힌 물건 치즈 ×(1 + 합)</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>초</t>
+          <t>증가율</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
@@ -40736,17 +40736,17 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Rush_Range</t>
+          <t>Ult_CD</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>클릭 총공격에 모이는 범위: 화면 밖으로 화면 크기 × 합 만큼 더 (그 안의 쥐도 돌진)</t>
+          <t>필살기 하나가 끝난 뒤 다음 필살기까지 쿨타임 - 합 (초, 기본 UltimateManager.ultCooldown, 최소 ultCooldownMin)</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>비율</t>
+          <t>초</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
@@ -40763,12 +40763,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Rush_Up</t>
+          <t>Rush_CD</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>총공격 시간 + 밸류_01 합 · 배율 + 밸류_02 합</t>
+          <t>클릭 총공격 쿨타임 - 합 (초, 최소 RatManager.rushCooldownMin)</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -40778,7 +40778,7 @@
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>배율</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
@@ -40790,22 +40790,22 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Cat_Hp_Down</t>
+          <t>Rush_Range</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>고양이 체력 ×(1 - 밸류_01 합) · 쥐가 겁먹는 시간 ×(1 - 밸류_02 합)</t>
+          <t>클릭 총공격에 모이는 범위: 화면 밖으로 화면 크기 × 합 만큼 더 (그 안의 쥐도 돌진)</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>감소율</t>
+          <t>비율</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>감소율</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -40817,22 +40817,22 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Promote_Auto</t>
+          <t>Rush_Up</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>자동 승급: 판 중 밸류_01 초마다 일괄 승급 (승급 패널 토글로 끔, 9훈장 핵심)</t>
+          <t>총공격 시간 + 밸류_01 합 · 배율 + 밸류_02 합</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>간격 (초)</t>
+          <t>초</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>배율</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
@@ -40844,25 +40844,79 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
+          <t>Cat_Hp_Down</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>고양이 체력 ×(1 - 밸류_01 합) · 쥐가 겁먹는 시간 ×(1 - 밸류_02 합)</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>감소율</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>감소율</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>Promote_Auto</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>자동 승급: 판 중 밸류_01 초마다 일괄 승급 (승급 패널 토글로 끔, 9훈장 핵심)</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>간격 (초)</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
           <t>Promote_Need_Down</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
+      <c r="B56" s="1" t="inlineStr">
         <is>
           <t>승급 필요 마릿수 - 합 (최소 2마리, 12훈장)</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>마리 수</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
+      <c r="D56" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E54" s="1" t="inlineStr">
+      <c r="E56" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/Data_Table/공용 스킬 테이블.xlsx
+++ b/Data_Table/공용 스킬 테이블.xlsx
@@ -3243,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>21000</v>
+        <v>11000</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M43" s="1" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         <v>0</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M44" s="1" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>67000</v>
+        <v>33000</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M45" s="1" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         <v>0</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>36000</v>
+        <v>19000</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M46" s="1" t="inlineStr">
         <is>
@@ -3495,10 +3495,10 @@
         <v>0</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>47000</v>
+        <v>22000</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M47" s="1" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>36000</v>
+        <v>19000</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -3621,10 +3621,10 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>47000</v>
+        <v>22000</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M49" s="1" t="inlineStr">
         <is>
@@ -3684,10 +3684,10 @@
         <v>0</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>47000</v>
+        <v>22000</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M50" s="1" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>21000</v>
+        <v>11000</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M51" s="1" t="inlineStr">
         <is>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M52" s="1" t="inlineStr">
         <is>
@@ -3873,10 +3873,10 @@
         <v>0</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>36000</v>
+        <v>19000</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M53" s="1" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         <v>0</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>36000</v>
+        <v>19000</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M54" s="1" t="inlineStr">
         <is>
@@ -3999,10 +3999,10 @@
         <v>0</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>36000</v>
+        <v>19000</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M55" s="1" t="inlineStr">
         <is>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>47000</v>
+        <v>22000</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M56" s="1" t="inlineStr">
         <is>
@@ -4125,10 +4125,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>57000</v>
+        <v>26000</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M57" s="1" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>47000</v>
+        <v>22000</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M58" s="1" t="inlineStr">
         <is>
@@ -4251,10 +4251,10 @@
         <v>0</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>21000</v>
+        <v>11000</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M59" s="1" t="inlineStr">
         <is>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M60" s="1" t="inlineStr">
         <is>
@@ -4377,10 +4377,10 @@
         <v>0</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>36000</v>
+        <v>19000</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M61" s="1" t="inlineStr">
         <is>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>36000</v>
+        <v>19000</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M62" s="1" t="inlineStr">
         <is>
@@ -4503,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>47000</v>
+        <v>22000</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M63" s="1" t="inlineStr">
         <is>
@@ -4566,10 +4566,10 @@
         <v>0</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>88000</v>
+        <v>40000</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="M64" s="1" t="inlineStr">
         <is>
@@ -4629,10 +4629,10 @@
         <v>0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>47000</v>
+        <v>22000</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M65" s="1" t="inlineStr">
         <is>
@@ -4692,10 +4692,10 @@
         <v>0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>120000</v>
+        <v>51000</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M66" s="1" t="inlineStr">
         <is>
@@ -4755,10 +4755,10 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>41000</v>
+        <v>19000</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M67" s="1" t="inlineStr">
         <is>
@@ -4818,10 +4818,10 @@
         <v>0</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M68" s="1" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         <v>0</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>36000</v>
+        <v>19000</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M69" s="1" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>0</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>36000</v>
+        <v>19000</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M70" s="1" t="inlineStr">
         <is>
@@ -5007,10 +5007,10 @@
         <v>0</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>47000</v>
+        <v>22000</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M71" s="1" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
         <v>0</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>47000</v>
+        <v>22000</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M72" s="1" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
         <v>0</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>57000</v>
+        <v>26000</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M73" s="1" t="inlineStr">
         <is>
@@ -5196,10 +5196,10 @@
         <v>0</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>52000</v>
+        <v>26000</v>
       </c>
       <c r="L74" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M74" s="1" t="inlineStr">
         <is>
@@ -5259,10 +5259,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>36000</v>
+        <v>19000</v>
       </c>
       <c r="L75" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M75" s="1" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>88000</v>
+        <v>40000</v>
       </c>
       <c r="L76" s="1" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="M76" s="1" t="inlineStr">
         <is>
@@ -5385,10 +5385,10 @@
         <v>0</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>36000</v>
+        <v>19000</v>
       </c>
       <c r="L77" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M77" s="1" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
         <v>0</v>
       </c>
       <c r="K78" s="1" t="n">
-        <v>57000</v>
+        <v>26000</v>
       </c>
       <c r="L78" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M78" s="1" t="inlineStr">
         <is>
@@ -5511,10 +5511,10 @@
         <v>0</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>47000</v>
+        <v>22000</v>
       </c>
       <c r="L79" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M79" s="1" t="inlineStr">
         <is>
@@ -5643,10 +5643,10 @@
         <v>0</v>
       </c>
       <c r="K81" s="1" t="n">
-        <v>73000</v>
+        <v>39000</v>
       </c>
       <c r="L81" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M81" s="1" t="inlineStr">
         <is>
@@ -5706,10 +5706,10 @@
         <v>0</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>97000</v>
+        <v>48000</v>
       </c>
       <c r="L82" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M82" s="1" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
         <v>0</v>
       </c>
       <c r="K83" s="1" t="n">
-        <v>250000</v>
+        <v>120000</v>
       </c>
       <c r="L83" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="M83" s="1" t="inlineStr">
         <is>
@@ -5832,10 +5832,10 @@
         <v>0</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>130000</v>
+        <v>58000</v>
       </c>
       <c r="L84" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M84" s="1" t="inlineStr">
         <is>
@@ -5895,10 +5895,10 @@
         <v>0</v>
       </c>
       <c r="K85" s="1" t="n">
-        <v>160000</v>
+        <v>77000</v>
       </c>
       <c r="L85" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M85" s="1" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>130000</v>
+        <v>58000</v>
       </c>
       <c r="L86" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M86" s="1" t="inlineStr">
         <is>
@@ -6021,10 +6021,10 @@
         <v>0</v>
       </c>
       <c r="K87" s="1" t="n">
-        <v>160000</v>
+        <v>77000</v>
       </c>
       <c r="L87" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M87" s="1" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>0</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>160000</v>
+        <v>77000</v>
       </c>
       <c r="L88" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M88" s="1" t="inlineStr">
         <is>
@@ -6147,10 +6147,10 @@
         <v>0</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>73000</v>
+        <v>39000</v>
       </c>
       <c r="L89" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M89" s="1" t="inlineStr">
         <is>
@@ -6210,10 +6210,10 @@
         <v>0</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>97000</v>
+        <v>48000</v>
       </c>
       <c r="L90" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M90" s="1" t="inlineStr">
         <is>
@@ -6273,10 +6273,10 @@
         <v>0</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>130000</v>
+        <v>58000</v>
       </c>
       <c r="L91" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M91" s="1" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         <v>0</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>130000</v>
+        <v>58000</v>
       </c>
       <c r="L92" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -6399,10 +6399,10 @@
         <v>0</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>130000</v>
+        <v>58000</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M93" s="1" t="inlineStr">
         <is>
@@ -6462,10 +6462,10 @@
         <v>0</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>160000</v>
+        <v>77000</v>
       </c>
       <c r="L94" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M94" s="1" t="inlineStr">
         <is>
@@ -6525,10 +6525,10 @@
         <v>0</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>210000</v>
+        <v>96000</v>
       </c>
       <c r="L95" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M95" s="1" t="inlineStr">
         <is>
@@ -6588,10 +6588,10 @@
         <v>0</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>160000</v>
+        <v>77000</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M96" s="1" t="inlineStr">
         <is>
@@ -6651,10 +6651,10 @@
         <v>0</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>73000</v>
+        <v>39000</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M97" s="1" t="inlineStr">
         <is>
@@ -6714,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>97000</v>
+        <v>48000</v>
       </c>
       <c r="L98" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M98" s="1" t="inlineStr">
         <is>
@@ -6777,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>130000</v>
+        <v>58000</v>
       </c>
       <c r="L99" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M99" s="1" t="inlineStr">
         <is>
@@ -6840,10 +6840,10 @@
         <v>0</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>130000</v>
+        <v>58000</v>
       </c>
       <c r="L100" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M100" s="1" t="inlineStr">
         <is>
@@ -6903,10 +6903,10 @@
         <v>0</v>
       </c>
       <c r="K101" s="1" t="n">
-        <v>160000</v>
+        <v>77000</v>
       </c>
       <c r="L101" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M101" s="1" t="inlineStr">
         <is>
@@ -6966,10 +6966,10 @@
         <v>0</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>310000</v>
+        <v>150000</v>
       </c>
       <c r="L102" s="1" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M102" s="1" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>160000</v>
+        <v>77000</v>
       </c>
       <c r="L103" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M103" s="1" t="inlineStr">
         <is>
@@ -7092,10 +7092,10 @@
         <v>0</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="L104" s="1" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="M104" s="1" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         <v>0</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>150000</v>
+        <v>67000</v>
       </c>
       <c r="L105" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M105" s="1" t="inlineStr">
         <is>
@@ -7218,10 +7218,10 @@
         <v>0</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>97000</v>
+        <v>48000</v>
       </c>
       <c r="L106" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M106" s="1" t="inlineStr">
         <is>
@@ -7281,10 +7281,10 @@
         <v>0</v>
       </c>
       <c r="K107" s="1" t="n">
-        <v>130000</v>
+        <v>58000</v>
       </c>
       <c r="L107" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M107" s="1" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>0</v>
       </c>
       <c r="K108" s="1" t="n">
-        <v>130000</v>
+        <v>58000</v>
       </c>
       <c r="L108" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M108" s="1" t="inlineStr">
         <is>
@@ -7407,10 +7407,10 @@
         <v>0</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>160000</v>
+        <v>77000</v>
       </c>
       <c r="L109" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M109" s="1" t="inlineStr">
         <is>
@@ -7470,10 +7470,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>160000</v>
+        <v>77000</v>
       </c>
       <c r="L110" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M110" s="1" t="inlineStr">
         <is>
@@ -7533,10 +7533,10 @@
         <v>0</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>210000</v>
+        <v>96000</v>
       </c>
       <c r="L111" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M111" s="1" t="inlineStr">
         <is>
@@ -7596,10 +7596,10 @@
         <v>0</v>
       </c>
       <c r="K112" s="1" t="n">
-        <v>190000</v>
+        <v>87000</v>
       </c>
       <c r="L112" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M112" s="1" t="inlineStr">
         <is>
@@ -7659,10 +7659,10 @@
         <v>0</v>
       </c>
       <c r="K113" s="1" t="n">
-        <v>250000</v>
+        <v>120000</v>
       </c>
       <c r="L113" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="M113" s="1" t="inlineStr">
         <is>
@@ -7722,10 +7722,10 @@
         <v>0</v>
       </c>
       <c r="K114" s="1" t="n">
-        <v>160000</v>
+        <v>77000</v>
       </c>
       <c r="L114" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M114" s="1" t="inlineStr">
         <is>
@@ -7785,10 +7785,10 @@
         <v>0</v>
       </c>
       <c r="K115" s="1" t="n">
-        <v>130000</v>
+        <v>58000</v>
       </c>
       <c r="L115" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M115" s="1" t="inlineStr">
         <is>
@@ -7848,10 +7848,10 @@
         <v>0</v>
       </c>
       <c r="K116" s="1" t="n">
-        <v>210000</v>
+        <v>96000</v>
       </c>
       <c r="L116" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M116" s="1" t="inlineStr">
         <is>
@@ -7911,10 +7911,10 @@
         <v>0</v>
       </c>
       <c r="K117" s="1" t="n">
-        <v>160000</v>
+        <v>77000</v>
       </c>
       <c r="L117" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M117" s="1" t="inlineStr">
         <is>
@@ -8043,10 +8043,10 @@
         <v>0</v>
       </c>
       <c r="K119" s="1" t="n">
-        <v>260000</v>
+        <v>92000</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M119" s="1" t="inlineStr">
         <is>
@@ -8106,10 +8106,10 @@
         <v>0</v>
       </c>
       <c r="K120" s="1" t="n">
-        <v>340000</v>
+        <v>130000</v>
       </c>
       <c r="L120" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M120" s="1" t="inlineStr">
         <is>
@@ -8169,10 +8169,10 @@
         <v>0</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>450000</v>
+        <v>170000</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M121" s="1" t="inlineStr">
         <is>
@@ -8232,10 +8232,10 @@
         <v>0</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>450000</v>
+        <v>170000</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M122" s="1" t="inlineStr">
         <is>
@@ -8295,10 +8295,10 @@
         <v>0</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>550000</v>
+        <v>210000</v>
       </c>
       <c r="L123" s="1" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M123" s="1" t="inlineStr">
         <is>
@@ -8358,10 +8358,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>450000</v>
+        <v>170000</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M124" s="1" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>0</v>
       </c>
       <c r="K125" s="1" t="n">
-        <v>550000</v>
+        <v>210000</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M125" s="1" t="inlineStr">
         <is>
@@ -8484,10 +8484,10 @@
         <v>0</v>
       </c>
       <c r="K126" s="1" t="n">
-        <v>550000</v>
+        <v>210000</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M126" s="1" t="inlineStr">
         <is>
@@ -8547,10 +8547,10 @@
         <v>0</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>260000</v>
+        <v>92000</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M127" s="1" t="inlineStr">
         <is>
@@ -8610,10 +8610,10 @@
         <v>0</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>340000</v>
+        <v>130000</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M128" s="1" t="inlineStr">
         <is>
@@ -8673,10 +8673,10 @@
         <v>0</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>450000</v>
+        <v>170000</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M129" s="1" t="inlineStr">
         <is>
@@ -8736,10 +8736,10 @@
         <v>0</v>
       </c>
       <c r="K130" s="1" t="n">
-        <v>450000</v>
+        <v>170000</v>
       </c>
       <c r="L130" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M130" s="1" t="inlineStr">
         <is>
@@ -8799,10 +8799,10 @@
         <v>0</v>
       </c>
       <c r="K131" s="1" t="n">
-        <v>450000</v>
+        <v>170000</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M131" s="1" t="inlineStr">
         <is>
@@ -8862,10 +8862,10 @@
         <v>0</v>
       </c>
       <c r="K132" s="1" t="n">
-        <v>550000</v>
+        <v>210000</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M132" s="1" t="inlineStr">
         <is>
@@ -8925,10 +8925,10 @@
         <v>0</v>
       </c>
       <c r="K133" s="1" t="n">
-        <v>730000</v>
+        <v>260000</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="M133" s="1" t="inlineStr">
         <is>
@@ -8988,10 +8988,10 @@
         <v>0</v>
       </c>
       <c r="K134" s="1" t="n">
-        <v>550000</v>
+        <v>210000</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M134" s="1" t="inlineStr">
         <is>
@@ -9051,10 +9051,10 @@
         <v>0</v>
       </c>
       <c r="K135" s="1" t="n">
-        <v>260000</v>
+        <v>92000</v>
       </c>
       <c r="L135" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M135" s="1" t="inlineStr">
         <is>
@@ -9114,10 +9114,10 @@
         <v>0</v>
       </c>
       <c r="K136" s="1" t="n">
-        <v>340000</v>
+        <v>130000</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M136" s="1" t="inlineStr">
         <is>
@@ -9177,10 +9177,10 @@
         <v>0</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>450000</v>
+        <v>170000</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M137" s="1" t="inlineStr">
         <is>
@@ -9240,10 +9240,10 @@
         <v>0</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>450000</v>
+        <v>170000</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M138" s="1" t="inlineStr">
         <is>
@@ -9303,10 +9303,10 @@
         <v>0</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>550000</v>
+        <v>210000</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M139" s="1" t="inlineStr">
         <is>
@@ -9366,10 +9366,10 @@
         <v>0</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>1100000</v>
+        <v>410000</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="M140" s="1" t="inlineStr">
         <is>
@@ -9429,10 +9429,10 @@
         <v>0</v>
       </c>
       <c r="K141" s="1" t="n">
-        <v>550000</v>
+        <v>210000</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M141" s="1" t="inlineStr">
         <is>
@@ -9492,10 +9492,10 @@
         <v>0</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>1500000</v>
+        <v>520000</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="M142" s="1" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         <v>0</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>520000</v>
+        <v>190000</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M143" s="1" t="inlineStr">
         <is>
@@ -9618,10 +9618,10 @@
         <v>0</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>340000</v>
+        <v>130000</v>
       </c>
       <c r="L144" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M144" s="1" t="inlineStr">
         <is>
@@ -9681,10 +9681,10 @@
         <v>0</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>450000</v>
+        <v>170000</v>
       </c>
       <c r="L145" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M145" s="1" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>0</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>450000</v>
+        <v>170000</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M146" s="1" t="inlineStr">
         <is>
@@ -9807,10 +9807,10 @@
         <v>0</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>550000</v>
+        <v>210000</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M147" s="1" t="inlineStr">
         <is>
@@ -9870,10 +9870,10 @@
         <v>0</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>550000</v>
+        <v>210000</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M148" s="1" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>730000</v>
+        <v>260000</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="M149" s="1" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>650000</v>
+        <v>240000</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="M150" s="1" t="inlineStr">
         <is>
@@ -10059,10 +10059,10 @@
         <v>0</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>450000</v>
+        <v>170000</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M151" s="1" t="inlineStr">
         <is>
@@ -10122,10 +10122,10 @@
         <v>0</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>1100000</v>
+        <v>410000</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="M152" s="1" t="inlineStr">
         <is>
@@ -10185,10 +10185,10 @@
         <v>0</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>450000</v>
+        <v>170000</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M153" s="1" t="inlineStr">
         <is>
@@ -10248,10 +10248,10 @@
         <v>0</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>730000</v>
+        <v>260000</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="M154" s="1" t="inlineStr">
         <is>
@@ -10311,10 +10311,10 @@
         <v>0</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>550000</v>
+        <v>210000</v>
       </c>
       <c r="L155" s="1" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M155" s="1" t="inlineStr">
         <is>
@@ -10443,10 +10443,10 @@
         <v>0</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>870000</v>
+        <v>580000</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M157" s="1" t="inlineStr">
         <is>
@@ -10506,10 +10506,10 @@
         <v>0</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>1200000</v>
+        <v>750000</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M158" s="1" t="inlineStr">
         <is>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>1500000</v>
+        <v>980000</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M159" s="1" t="inlineStr">
         <is>
@@ -10632,10 +10632,10 @@
         <v>0</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>1500000</v>
+        <v>980000</v>
       </c>
       <c r="L160" s="1" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M160" s="1" t="inlineStr">
         <is>
@@ -10695,10 +10695,10 @@
         <v>0</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>1900000</v>
+        <v>1300000</v>
       </c>
       <c r="L161" s="1" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M161" s="1" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>0</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>1500000</v>
+        <v>980000</v>
       </c>
       <c r="L162" s="1" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M162" s="1" t="inlineStr">
         <is>
@@ -10821,10 +10821,10 @@
         <v>0</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>1900000</v>
+        <v>1300000</v>
       </c>
       <c r="L163" s="1" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M163" s="1" t="inlineStr">
         <is>
@@ -10884,10 +10884,10 @@
         <v>0</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>1900000</v>
+        <v>1300000</v>
       </c>
       <c r="L164" s="1" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M164" s="1" t="inlineStr">
         <is>
@@ -10947,10 +10947,10 @@
         <v>0</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>870000</v>
+        <v>580000</v>
       </c>
       <c r="L165" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M165" s="1" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         <v>0</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>1200000</v>
+        <v>750000</v>
       </c>
       <c r="L166" s="1" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M166" s="1" t="inlineStr">
         <is>
@@ -11073,10 +11073,10 @@
         <v>0</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>1500000</v>
+        <v>980000</v>
       </c>
       <c r="L167" s="1" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M167" s="1" t="inlineStr">
         <is>
@@ -11136,10 +11136,10 @@
         <v>0</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>1500000</v>
+        <v>980000</v>
       </c>
       <c r="L168" s="1" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M168" s="1" t="inlineStr">
         <is>
@@ -11199,10 +11199,10 @@
         <v>0</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>1500000</v>
+        <v>980000</v>
       </c>
       <c r="L169" s="1" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M169" s="1" t="inlineStr">
         <is>
@@ -11262,10 +11262,10 @@
         <v>0</v>
       </c>
       <c r="K170" s="1" t="n">
-        <v>1900000</v>
+        <v>1300000</v>
       </c>
       <c r="L170" s="1" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M170" s="1" t="inlineStr">
         <is>
@@ -11325,10 +11325,10 @@
         <v>0</v>
       </c>
       <c r="K171" s="1" t="n">
-        <v>2500000</v>
+        <v>1700000</v>
       </c>
       <c r="L171" s="1" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="M171" s="1" t="inlineStr">
         <is>
@@ -11388,10 +11388,10 @@
         <v>0</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>1900000</v>
+        <v>1300000</v>
       </c>
       <c r="L172" s="1" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M172" s="1" t="inlineStr">
         <is>
@@ -11451,10 +11451,10 @@
         <v>0</v>
       </c>
       <c r="K173" s="1" t="n">
-        <v>870000</v>
+        <v>580000</v>
       </c>
       <c r="L173" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M173" s="1" t="inlineStr">
         <is>
@@ -11514,10 +11514,10 @@
         <v>0</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>1200000</v>
+        <v>750000</v>
       </c>
       <c r="L174" s="1" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M174" s="1" t="inlineStr">
         <is>
@@ -11577,10 +11577,10 @@
         <v>0</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>1500000</v>
+        <v>980000</v>
       </c>
       <c r="L175" s="1" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M175" s="1" t="inlineStr">
         <is>
@@ -11640,10 +11640,10 @@
         <v>0</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>1500000</v>
+        <v>980000</v>
       </c>
       <c r="L176" s="1" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M176" s="1" t="inlineStr">
         <is>
@@ -11703,10 +11703,10 @@
         <v>0</v>
       </c>
       <c r="K177" s="1" t="n">
-        <v>1900000</v>
+        <v>1300000</v>
       </c>
       <c r="L177" s="1" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M177" s="1" t="inlineStr">
         <is>
@@ -11766,10 +11766,10 @@
         <v>0</v>
       </c>
       <c r="K178" s="1" t="n">
-        <v>3800000</v>
+        <v>2500000</v>
       </c>
       <c r="L178" s="1" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="M178" s="1" t="inlineStr">
         <is>
@@ -11829,10 +11829,10 @@
         <v>0</v>
       </c>
       <c r="K179" s="1" t="n">
-        <v>1900000</v>
+        <v>1300000</v>
       </c>
       <c r="L179" s="1" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M179" s="1" t="inlineStr">
         <is>
@@ -11892,10 +11892,10 @@
         <v>0</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>4900000</v>
+        <v>3300000</v>
       </c>
       <c r="L180" s="1" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="M180" s="1" t="inlineStr">
         <is>
@@ -11955,10 +11955,10 @@
         <v>0</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>1800000</v>
+        <v>1200000</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="M181" s="1" t="inlineStr">
         <is>
@@ -12018,10 +12018,10 @@
         <v>0</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>1200000</v>
+        <v>750000</v>
       </c>
       <c r="L182" s="1" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M182" s="1" t="inlineStr">
         <is>
@@ -12081,10 +12081,10 @@
         <v>0</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>1500000</v>
+        <v>980000</v>
       </c>
       <c r="L183" s="1" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M183" s="1" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>0</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>1500000</v>
+        <v>980000</v>
       </c>
       <c r="L184" s="1" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M184" s="1" t="inlineStr">
         <is>
@@ -12207,10 +12207,10 @@
         <v>0</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>1900000</v>
+        <v>1300000</v>
       </c>
       <c r="L185" s="1" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M185" s="1" t="inlineStr">
         <is>
@@ -12270,10 +12270,10 @@
         <v>0</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>1900000</v>
+        <v>1300000</v>
       </c>
       <c r="L186" s="1" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M186" s="1" t="inlineStr">
         <is>
@@ -12333,10 +12333,10 @@
         <v>0</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>2500000</v>
+        <v>1700000</v>
       </c>
       <c r="L187" s="1" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="M187" s="1" t="inlineStr">
         <is>
@@ -12396,10 +12396,10 @@
         <v>0</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>2300000</v>
+        <v>1500000</v>
       </c>
       <c r="L188" s="1" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M188" s="1" t="inlineStr">
         <is>
@@ -12459,10 +12459,10 @@
         <v>0</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="L189" s="1" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="M189" s="1" t="inlineStr">
         <is>
@@ -12522,10 +12522,10 @@
         <v>0</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>1900000</v>
+        <v>1300000</v>
       </c>
       <c r="L190" s="1" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M190" s="1" t="inlineStr">
         <is>
@@ -12585,10 +12585,10 @@
         <v>0</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>1500000</v>
+        <v>980000</v>
       </c>
       <c r="L191" s="1" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M191" s="1" t="inlineStr">
         <is>
@@ -12648,10 +12648,10 @@
         <v>0</v>
       </c>
       <c r="K192" s="1" t="n">
-        <v>2500000</v>
+        <v>1700000</v>
       </c>
       <c r="L192" s="1" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="M192" s="1" t="inlineStr">
         <is>
@@ -12711,10 +12711,10 @@
         <v>0</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>1900000</v>
+        <v>1300000</v>
       </c>
       <c r="L193" s="1" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M193" s="1" t="inlineStr">
         <is>
@@ -12843,10 +12843,10 @@
         <v>0</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>3000000</v>
+        <v>1100000</v>
       </c>
       <c r="L195" s="1" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="M195" s="1" t="inlineStr">
         <is>
@@ -12906,10 +12906,10 @@
         <v>0</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>3900000</v>
+        <v>1400000</v>
       </c>
       <c r="L196" s="1" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="M196" s="1" t="inlineStr">
         <is>
@@ -12969,10 +12969,10 @@
         <v>0</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>5000000</v>
+        <v>1800000</v>
       </c>
       <c r="L197" s="1" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M197" s="1" t="inlineStr">
         <is>
@@ -13032,10 +13032,10 @@
         <v>0</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>5000000</v>
+        <v>1800000</v>
       </c>
       <c r="L198" s="1" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M198" s="1" t="inlineStr">
         <is>
@@ -13095,10 +13095,10 @@
         <v>0</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>6500000</v>
+        <v>2400000</v>
       </c>
       <c r="L199" s="1" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M199" s="1" t="inlineStr">
         <is>
@@ -13158,10 +13158,10 @@
         <v>0</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>5000000</v>
+        <v>1800000</v>
       </c>
       <c r="L200" s="1" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M200" s="1" t="inlineStr">
         <is>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>6500000</v>
+        <v>2400000</v>
       </c>
       <c r="L201" s="1" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M201" s="1" t="inlineStr">
         <is>
@@ -13284,10 +13284,10 @@
         <v>0</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>6500000</v>
+        <v>2400000</v>
       </c>
       <c r="L202" s="1" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M202" s="1" t="inlineStr">
         <is>
@@ -13347,10 +13347,10 @@
         <v>0</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>3000000</v>
+        <v>1100000</v>
       </c>
       <c r="L203" s="1" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="M203" s="1" t="inlineStr">
         <is>
@@ -13410,10 +13410,10 @@
         <v>0</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>3900000</v>
+        <v>1400000</v>
       </c>
       <c r="L204" s="1" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="M204" s="1" t="inlineStr">
         <is>
@@ -13473,10 +13473,10 @@
         <v>0</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>5000000</v>
+        <v>1800000</v>
       </c>
       <c r="L205" s="1" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M205" s="1" t="inlineStr">
         <is>
@@ -13536,10 +13536,10 @@
         <v>0</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>5000000</v>
+        <v>1800000</v>
       </c>
       <c r="L206" s="1" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M206" s="1" t="inlineStr">
         <is>
@@ -13599,10 +13599,10 @@
         <v>0</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>5000000</v>
+        <v>1800000</v>
       </c>
       <c r="L207" s="1" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M207" s="1" t="inlineStr">
         <is>
@@ -13662,10 +13662,10 @@
         <v>0</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>6500000</v>
+        <v>2400000</v>
       </c>
       <c r="L208" s="1" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M208" s="1" t="inlineStr">
         <is>
@@ -13725,10 +13725,10 @@
         <v>0</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>8500000</v>
+        <v>3000000</v>
       </c>
       <c r="L209" s="1" t="n">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="M209" s="1" t="inlineStr">
         <is>
@@ -13788,10 +13788,10 @@
         <v>0</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>6500000</v>
+        <v>2400000</v>
       </c>
       <c r="L210" s="1" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M210" s="1" t="inlineStr">
         <is>
@@ -13851,10 +13851,10 @@
         <v>0</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>3000000</v>
+        <v>1100000</v>
       </c>
       <c r="L211" s="1" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="M211" s="1" t="inlineStr">
         <is>
@@ -13914,10 +13914,10 @@
         <v>0</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>3900000</v>
+        <v>1400000</v>
       </c>
       <c r="L212" s="1" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="M212" s="1" t="inlineStr">
         <is>
@@ -13977,10 +13977,10 @@
         <v>0</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>5000000</v>
+        <v>1800000</v>
       </c>
       <c r="L213" s="1" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M213" s="1" t="inlineStr">
         <is>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>5000000</v>
+        <v>1800000</v>
       </c>
       <c r="L214" s="1" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M214" s="1" t="inlineStr">
         <is>
@@ -14103,10 +14103,10 @@
         <v>0</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>6500000</v>
+        <v>2400000</v>
       </c>
       <c r="L215" s="1" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M215" s="1" t="inlineStr">
         <is>
@@ -14166,10 +14166,10 @@
         <v>0</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>13000000</v>
+        <v>4700000</v>
       </c>
       <c r="L216" s="1" t="n">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="M216" s="1" t="inlineStr">
         <is>
@@ -14229,10 +14229,10 @@
         <v>0</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>6500000</v>
+        <v>2400000</v>
       </c>
       <c r="L217" s="1" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M217" s="1" t="inlineStr">
         <is>
@@ -14292,10 +14292,10 @@
         <v>0</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>17000000</v>
+        <v>6000000</v>
       </c>
       <c r="L218" s="1" t="n">
-        <v>182</v>
+        <v>88</v>
       </c>
       <c r="M218" s="1" t="inlineStr">
         <is>
@@ -14355,10 +14355,10 @@
         <v>0</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>3000000</v>
+        <v>1100000</v>
       </c>
       <c r="L219" s="1" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="M219" s="1" t="inlineStr">
         <is>
@@ -14418,10 +14418,10 @@
         <v>0</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>3900000</v>
+        <v>1400000</v>
       </c>
       <c r="L220" s="1" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="M220" s="1" t="inlineStr">
         <is>
@@ -14481,10 +14481,10 @@
         <v>0</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>5000000</v>
+        <v>1800000</v>
       </c>
       <c r="L221" s="1" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M221" s="1" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>0</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>5000000</v>
+        <v>1800000</v>
       </c>
       <c r="L222" s="1" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M222" s="1" t="inlineStr">
         <is>
@@ -14607,10 +14607,10 @@
         <v>0</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>6500000</v>
+        <v>2400000</v>
       </c>
       <c r="L223" s="1" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M223" s="1" t="inlineStr">
         <is>
@@ -14670,10 +14670,10 @@
         <v>0</v>
       </c>
       <c r="K224" s="1" t="n">
-        <v>6500000</v>
+        <v>2400000</v>
       </c>
       <c r="L224" s="1" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M224" s="1" t="inlineStr">
         <is>
@@ -14733,10 +14733,10 @@
         <v>0</v>
       </c>
       <c r="K225" s="1" t="n">
-        <v>8500000</v>
+        <v>3000000</v>
       </c>
       <c r="L225" s="1" t="n">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="M225" s="1" t="inlineStr">
         <is>
@@ -14796,10 +14796,10 @@
         <v>0</v>
       </c>
       <c r="K226" s="1" t="n">
-        <v>7700000</v>
+        <v>2800000</v>
       </c>
       <c r="L226" s="1" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="M226" s="1" t="inlineStr">
         <is>
@@ -14859,10 +14859,10 @@
         <v>0</v>
       </c>
       <c r="K227" s="1" t="n">
-        <v>10000000</v>
+        <v>3600000</v>
       </c>
       <c r="L227" s="1" t="n">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="M227" s="1" t="inlineStr">
         <is>
@@ -14922,10 +14922,10 @@
         <v>0</v>
       </c>
       <c r="K228" s="1" t="n">
-        <v>13000000</v>
+        <v>4700000</v>
       </c>
       <c r="L228" s="1" t="n">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="M228" s="1" t="inlineStr">
         <is>
@@ -14985,10 +14985,10 @@
         <v>0</v>
       </c>
       <c r="K229" s="1" t="n">
-        <v>5000000</v>
+        <v>1800000</v>
       </c>
       <c r="L229" s="1" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M229" s="1" t="inlineStr">
         <is>
@@ -15048,10 +15048,10 @@
         <v>0</v>
       </c>
       <c r="K230" s="1" t="n">
-        <v>8500000</v>
+        <v>3000000</v>
       </c>
       <c r="L230" s="1" t="n">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="M230" s="1" t="inlineStr">
         <is>
@@ -15111,10 +15111,10 @@
         <v>0</v>
       </c>
       <c r="K231" s="1" t="n">
-        <v>6500000</v>
+        <v>2400000</v>
       </c>
       <c r="L231" s="1" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M231" s="1" t="inlineStr">
         <is>
@@ -15243,10 +15243,10 @@
         <v>0</v>
       </c>
       <c r="K233" s="1" t="n">
-        <v>48000000</v>
+        <v>9800000</v>
       </c>
       <c r="L233" s="1" t="n">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="M233" s="1" t="inlineStr">
         <is>
@@ -15306,10 +15306,10 @@
         <v>0</v>
       </c>
       <c r="K234" s="1" t="n">
-        <v>62000000</v>
+        <v>13000000</v>
       </c>
       <c r="L234" s="1" t="n">
-        <v>154</v>
+        <v>45</v>
       </c>
       <c r="M234" s="1" t="inlineStr">
         <is>
@@ -15369,10 +15369,10 @@
         <v>0</v>
       </c>
       <c r="K235" s="1" t="n">
-        <v>80000000</v>
+        <v>17000000</v>
       </c>
       <c r="L235" s="1" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M235" s="1" t="inlineStr">
         <is>
@@ -15432,10 +15432,10 @@
         <v>0</v>
       </c>
       <c r="K236" s="1" t="n">
-        <v>80000000</v>
+        <v>17000000</v>
       </c>
       <c r="L236" s="1" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M236" s="1" t="inlineStr">
         <is>
@@ -15495,10 +15495,10 @@
         <v>0</v>
       </c>
       <c r="K237" s="1" t="n">
-        <v>110000000</v>
+        <v>22000000</v>
       </c>
       <c r="L237" s="1" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="M237" s="1" t="inlineStr">
         <is>
@@ -15558,10 +15558,10 @@
         <v>0</v>
       </c>
       <c r="K238" s="1" t="n">
-        <v>80000000</v>
+        <v>17000000</v>
       </c>
       <c r="L238" s="1" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M238" s="1" t="inlineStr">
         <is>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="K239" s="1" t="n">
-        <v>110000000</v>
+        <v>22000000</v>
       </c>
       <c r="L239" s="1" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="M239" s="1" t="inlineStr">
         <is>
@@ -15684,10 +15684,10 @@
         <v>0</v>
       </c>
       <c r="K240" s="1" t="n">
-        <v>110000000</v>
+        <v>22000000</v>
       </c>
       <c r="L240" s="1" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="M240" s="1" t="inlineStr">
         <is>
@@ -15747,10 +15747,10 @@
         <v>0</v>
       </c>
       <c r="K241" s="1" t="n">
-        <v>48000000</v>
+        <v>9800000</v>
       </c>
       <c r="L241" s="1" t="n">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="M241" s="1" t="inlineStr">
         <is>
@@ -15810,10 +15810,10 @@
         <v>0</v>
       </c>
       <c r="K242" s="1" t="n">
-        <v>62000000</v>
+        <v>13000000</v>
       </c>
       <c r="L242" s="1" t="n">
-        <v>154</v>
+        <v>45</v>
       </c>
       <c r="M242" s="1" t="inlineStr">
         <is>
@@ -15873,10 +15873,10 @@
         <v>0</v>
       </c>
       <c r="K243" s="1" t="n">
-        <v>80000000</v>
+        <v>17000000</v>
       </c>
       <c r="L243" s="1" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M243" s="1" t="inlineStr">
         <is>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="K244" s="1" t="n">
-        <v>80000000</v>
+        <v>17000000</v>
       </c>
       <c r="L244" s="1" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M244" s="1" t="inlineStr">
         <is>
@@ -15999,10 +15999,10 @@
         <v>0</v>
       </c>
       <c r="K245" s="1" t="n">
-        <v>80000000</v>
+        <v>17000000</v>
       </c>
       <c r="L245" s="1" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M245" s="1" t="inlineStr">
         <is>
@@ -16062,10 +16062,10 @@
         <v>0</v>
       </c>
       <c r="K246" s="1" t="n">
-        <v>110000000</v>
+        <v>22000000</v>
       </c>
       <c r="L246" s="1" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="M246" s="1" t="inlineStr">
         <is>
@@ -16125,10 +16125,10 @@
         <v>0</v>
       </c>
       <c r="K247" s="1" t="n">
-        <v>140000000</v>
+        <v>28000000</v>
       </c>
       <c r="L247" s="1" t="n">
-        <v>338</v>
+        <v>99</v>
       </c>
       <c r="M247" s="1" t="inlineStr">
         <is>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="K248" s="1" t="n">
-        <v>110000000</v>
+        <v>22000000</v>
       </c>
       <c r="L248" s="1" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="M248" s="1" t="inlineStr">
         <is>
@@ -16251,10 +16251,10 @@
         <v>0</v>
       </c>
       <c r="K249" s="1" t="n">
-        <v>48000000</v>
+        <v>9800000</v>
       </c>
       <c r="L249" s="1" t="n">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="M249" s="1" t="inlineStr">
         <is>
@@ -16314,10 +16314,10 @@
         <v>0</v>
       </c>
       <c r="K250" s="1" t="n">
-        <v>62000000</v>
+        <v>13000000</v>
       </c>
       <c r="L250" s="1" t="n">
-        <v>154</v>
+        <v>45</v>
       </c>
       <c r="M250" s="1" t="inlineStr">
         <is>
@@ -16377,10 +16377,10 @@
         <v>0</v>
       </c>
       <c r="K251" s="1" t="n">
-        <v>80000000</v>
+        <v>17000000</v>
       </c>
       <c r="L251" s="1" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M251" s="1" t="inlineStr">
         <is>
@@ -16440,10 +16440,10 @@
         <v>0</v>
       </c>
       <c r="K252" s="1" t="n">
-        <v>80000000</v>
+        <v>17000000</v>
       </c>
       <c r="L252" s="1" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M252" s="1" t="inlineStr">
         <is>
@@ -16503,10 +16503,10 @@
         <v>0</v>
       </c>
       <c r="K253" s="1" t="n">
-        <v>110000000</v>
+        <v>22000000</v>
       </c>
       <c r="L253" s="1" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="M253" s="1" t="inlineStr">
         <is>
@@ -16566,10 +16566,10 @@
         <v>0</v>
       </c>
       <c r="K254" s="1" t="n">
-        <v>110000000</v>
+        <v>22000000</v>
       </c>
       <c r="L254" s="1" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="M254" s="1" t="inlineStr">
         <is>
@@ -16629,10 +16629,10 @@
         <v>0</v>
       </c>
       <c r="K255" s="1" t="n">
-        <v>110000000</v>
+        <v>22000000</v>
       </c>
       <c r="L255" s="1" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="M255" s="1" t="inlineStr">
         <is>
@@ -16692,10 +16692,10 @@
         <v>0</v>
       </c>
       <c r="K256" s="1" t="n">
-        <v>270000000</v>
+        <v>56000000</v>
       </c>
       <c r="L256" s="1" t="n">
-        <v>675</v>
+        <v>198</v>
       </c>
       <c r="M256" s="1" t="inlineStr">
         <is>
@@ -16755,10 +16755,10 @@
         <v>0</v>
       </c>
       <c r="K257" s="1" t="n">
-        <v>48000000</v>
+        <v>9800000</v>
       </c>
       <c r="L257" s="1" t="n">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="M257" s="1" t="inlineStr">
         <is>
@@ -16818,10 +16818,10 @@
         <v>0</v>
       </c>
       <c r="K258" s="1" t="n">
-        <v>62000000</v>
+        <v>13000000</v>
       </c>
       <c r="L258" s="1" t="n">
-        <v>154</v>
+        <v>45</v>
       </c>
       <c r="M258" s="1" t="inlineStr">
         <is>
@@ -16881,10 +16881,10 @@
         <v>0</v>
       </c>
       <c r="K259" s="1" t="n">
-        <v>80000000</v>
+        <v>17000000</v>
       </c>
       <c r="L259" s="1" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M259" s="1" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>0</v>
       </c>
       <c r="K260" s="1" t="n">
-        <v>80000000</v>
+        <v>17000000</v>
       </c>
       <c r="L260" s="1" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M260" s="1" t="inlineStr">
         <is>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="K261" s="1" t="n">
-        <v>110000000</v>
+        <v>22000000</v>
       </c>
       <c r="L261" s="1" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="M261" s="1" t="inlineStr">
         <is>
@@ -17070,10 +17070,10 @@
         <v>0</v>
       </c>
       <c r="K262" s="1" t="n">
-        <v>110000000</v>
+        <v>22000000</v>
       </c>
       <c r="L262" s="1" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="M262" s="1" t="inlineStr">
         <is>
@@ -17133,10 +17133,10 @@
         <v>0</v>
       </c>
       <c r="K263" s="1" t="n">
-        <v>140000000</v>
+        <v>28000000</v>
       </c>
       <c r="L263" s="1" t="n">
-        <v>338</v>
+        <v>99</v>
       </c>
       <c r="M263" s="1" t="inlineStr">
         <is>
@@ -17196,10 +17196,10 @@
         <v>0</v>
       </c>
       <c r="K264" s="1" t="n">
-        <v>130000000</v>
+        <v>26000000</v>
       </c>
       <c r="L264" s="1" t="n">
-        <v>308</v>
+        <v>90</v>
       </c>
       <c r="M264" s="1" t="inlineStr">
         <is>
@@ -17259,10 +17259,10 @@
         <v>0</v>
       </c>
       <c r="K265" s="1" t="n">
-        <v>80000000</v>
+        <v>17000000</v>
       </c>
       <c r="L265" s="1" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M265" s="1" t="inlineStr">
         <is>
@@ -17322,10 +17322,10 @@
         <v>0</v>
       </c>
       <c r="K266" s="1" t="n">
-        <v>110000000</v>
+        <v>22000000</v>
       </c>
       <c r="L266" s="1" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="M266" s="1" t="inlineStr">
         <is>
@@ -17385,10 +17385,10 @@
         <v>0</v>
       </c>
       <c r="K267" s="1" t="n">
-        <v>80000000</v>
+        <v>17000000</v>
       </c>
       <c r="L267" s="1" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="M267" s="1" t="inlineStr">
         <is>
@@ -17448,10 +17448,10 @@
         <v>0</v>
       </c>
       <c r="K268" s="1" t="n">
-        <v>140000000</v>
+        <v>28000000</v>
       </c>
       <c r="L268" s="1" t="n">
-        <v>338</v>
+        <v>99</v>
       </c>
       <c r="M268" s="1" t="inlineStr">
         <is>
@@ -17511,10 +17511,10 @@
         <v>0</v>
       </c>
       <c r="K269" s="1" t="n">
-        <v>110000000</v>
+        <v>22000000</v>
       </c>
       <c r="L269" s="1" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="M269" s="1" t="inlineStr">
         <is>
@@ -17643,10 +17643,10 @@
         <v>0</v>
       </c>
       <c r="K271" s="1" t="n">
-        <v>2500000000</v>
+        <v>690000000</v>
       </c>
       <c r="L271" s="1" t="n">
-        <v>1271</v>
+        <v>272</v>
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
@@ -17706,10 +17706,10 @@
         <v>0</v>
       </c>
       <c r="K272" s="1" t="n">
-        <v>3200000000</v>
+        <v>890000000</v>
       </c>
       <c r="L272" s="1" t="n">
-        <v>1652</v>
+        <v>354</v>
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
@@ -17769,10 +17769,10 @@
         <v>0</v>
       </c>
       <c r="K273" s="1" t="n">
-        <v>4100000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L273" s="1" t="n">
-        <v>2148</v>
+        <v>459</v>
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
@@ -17832,10 +17832,10 @@
         <v>0</v>
       </c>
       <c r="K274" s="1" t="n">
-        <v>4100000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L274" s="1" t="n">
-        <v>2148</v>
+        <v>459</v>
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
@@ -17895,10 +17895,10 @@
         <v>0</v>
       </c>
       <c r="K275" s="1" t="n">
-        <v>5400000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L275" s="1" t="n">
-        <v>2792</v>
+        <v>597</v>
       </c>
       <c r="M275" s="1" t="inlineStr">
         <is>
@@ -17958,10 +17958,10 @@
         <v>0</v>
       </c>
       <c r="K276" s="1" t="n">
-        <v>4100000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L276" s="1" t="n">
-        <v>2148</v>
+        <v>459</v>
       </c>
       <c r="M276" s="1" t="inlineStr">
         <is>
@@ -18021,10 +18021,10 @@
         <v>0</v>
       </c>
       <c r="K277" s="1" t="n">
-        <v>5400000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L277" s="1" t="n">
-        <v>2792</v>
+        <v>597</v>
       </c>
       <c r="M277" s="1" t="inlineStr">
         <is>
@@ -18084,10 +18084,10 @@
         <v>0</v>
       </c>
       <c r="K278" s="1" t="n">
-        <v>5400000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L278" s="1" t="n">
-        <v>2792</v>
+        <v>597</v>
       </c>
       <c r="M278" s="1" t="inlineStr">
         <is>
@@ -18147,10 +18147,10 @@
         <v>0</v>
       </c>
       <c r="K279" s="1" t="n">
-        <v>2500000000</v>
+        <v>690000000</v>
       </c>
       <c r="L279" s="1" t="n">
-        <v>1271</v>
+        <v>272</v>
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
@@ -18210,10 +18210,10 @@
         <v>0</v>
       </c>
       <c r="K280" s="1" t="n">
-        <v>3200000000</v>
+        <v>890000000</v>
       </c>
       <c r="L280" s="1" t="n">
-        <v>1652</v>
+        <v>354</v>
       </c>
       <c r="M280" s="1" t="inlineStr">
         <is>
@@ -18273,10 +18273,10 @@
         <v>0</v>
       </c>
       <c r="K281" s="1" t="n">
-        <v>4100000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L281" s="1" t="n">
-        <v>2148</v>
+        <v>459</v>
       </c>
       <c r="M281" s="1" t="inlineStr">
         <is>
@@ -18336,10 +18336,10 @@
         <v>0</v>
       </c>
       <c r="K282" s="1" t="n">
-        <v>4100000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L282" s="1" t="n">
-        <v>2148</v>
+        <v>459</v>
       </c>
       <c r="M282" s="1" t="inlineStr">
         <is>
@@ -18399,10 +18399,10 @@
         <v>0</v>
       </c>
       <c r="K283" s="1" t="n">
-        <v>4100000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L283" s="1" t="n">
-        <v>2148</v>
+        <v>459</v>
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
@@ -18462,10 +18462,10 @@
         <v>0</v>
       </c>
       <c r="K284" s="1" t="n">
-        <v>5400000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L284" s="1" t="n">
-        <v>2792</v>
+        <v>597</v>
       </c>
       <c r="M284" s="1" t="inlineStr">
         <is>
@@ -18525,10 +18525,10 @@
         <v>0</v>
       </c>
       <c r="K285" s="1" t="n">
-        <v>7000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="L285" s="1" t="n">
-        <v>3629</v>
+        <v>776</v>
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
@@ -18588,10 +18588,10 @@
         <v>0</v>
       </c>
       <c r="K286" s="1" t="n">
-        <v>5400000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L286" s="1" t="n">
-        <v>2792</v>
+        <v>597</v>
       </c>
       <c r="M286" s="1" t="inlineStr">
         <is>
@@ -18651,10 +18651,10 @@
         <v>0</v>
       </c>
       <c r="K287" s="1" t="n">
-        <v>2500000000</v>
+        <v>690000000</v>
       </c>
       <c r="L287" s="1" t="n">
-        <v>1271</v>
+        <v>272</v>
       </c>
       <c r="M287" s="1" t="inlineStr">
         <is>
@@ -18714,10 +18714,10 @@
         <v>0</v>
       </c>
       <c r="K288" s="1" t="n">
-        <v>3200000000</v>
+        <v>890000000</v>
       </c>
       <c r="L288" s="1" t="n">
-        <v>1652</v>
+        <v>354</v>
       </c>
       <c r="M288" s="1" t="inlineStr">
         <is>
@@ -18777,10 +18777,10 @@
         <v>0</v>
       </c>
       <c r="K289" s="1" t="n">
-        <v>4100000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L289" s="1" t="n">
-        <v>2148</v>
+        <v>459</v>
       </c>
       <c r="M289" s="1" t="inlineStr">
         <is>
@@ -18840,10 +18840,10 @@
         <v>0</v>
       </c>
       <c r="K290" s="1" t="n">
-        <v>4100000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L290" s="1" t="n">
-        <v>2148</v>
+        <v>459</v>
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
@@ -18903,10 +18903,10 @@
         <v>0</v>
       </c>
       <c r="K291" s="1" t="n">
-        <v>5400000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L291" s="1" t="n">
-        <v>2792</v>
+        <v>597</v>
       </c>
       <c r="M291" s="1" t="inlineStr">
         <is>
@@ -18966,10 +18966,10 @@
         <v>0</v>
       </c>
       <c r="K292" s="1" t="n">
-        <v>5400000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L292" s="1" t="n">
-        <v>2792</v>
+        <v>597</v>
       </c>
       <c r="M292" s="1" t="inlineStr">
         <is>
@@ -19029,10 +19029,10 @@
         <v>0</v>
       </c>
       <c r="K293" s="1" t="n">
-        <v>5400000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L293" s="1" t="n">
-        <v>2792</v>
+        <v>597</v>
       </c>
       <c r="M293" s="1" t="inlineStr">
         <is>
@@ -19092,10 +19092,10 @@
         <v>0</v>
       </c>
       <c r="K294" s="1" t="n">
-        <v>14000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="L294" s="1" t="n">
-        <v>7258</v>
+        <v>1552</v>
       </c>
       <c r="M294" s="1" t="inlineStr">
         <is>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="K295" s="1" t="n">
-        <v>2500000000</v>
+        <v>690000000</v>
       </c>
       <c r="L295" s="1" t="n">
-        <v>1271</v>
+        <v>272</v>
       </c>
       <c r="M295" s="1" t="inlineStr">
         <is>
@@ -19218,10 +19218,10 @@
         <v>0</v>
       </c>
       <c r="K296" s="1" t="n">
-        <v>3200000000</v>
+        <v>890000000</v>
       </c>
       <c r="L296" s="1" t="n">
-        <v>1652</v>
+        <v>354</v>
       </c>
       <c r="M296" s="1" t="inlineStr">
         <is>
@@ -19281,10 +19281,10 @@
         <v>0</v>
       </c>
       <c r="K297" s="1" t="n">
-        <v>4100000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L297" s="1" t="n">
-        <v>2148</v>
+        <v>459</v>
       </c>
       <c r="M297" s="1" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>0</v>
       </c>
       <c r="K298" s="1" t="n">
-        <v>4100000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L298" s="1" t="n">
-        <v>2148</v>
+        <v>459</v>
       </c>
       <c r="M298" s="1" t="inlineStr">
         <is>
@@ -19407,10 +19407,10 @@
         <v>0</v>
       </c>
       <c r="K299" s="1" t="n">
-        <v>5400000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L299" s="1" t="n">
-        <v>2792</v>
+        <v>597</v>
       </c>
       <c r="M299" s="1" t="inlineStr">
         <is>
@@ -19470,10 +19470,10 @@
         <v>0</v>
       </c>
       <c r="K300" s="1" t="n">
-        <v>5400000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L300" s="1" t="n">
-        <v>2792</v>
+        <v>597</v>
       </c>
       <c r="M300" s="1" t="inlineStr">
         <is>
@@ -19533,10 +19533,10 @@
         <v>0</v>
       </c>
       <c r="K301" s="1" t="n">
-        <v>7000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="L301" s="1" t="n">
-        <v>3629</v>
+        <v>776</v>
       </c>
       <c r="M301" s="1" t="inlineStr">
         <is>
@@ -19596,10 +19596,10 @@
         <v>0</v>
       </c>
       <c r="K302" s="1" t="n">
-        <v>6300000000</v>
+        <v>1800000000</v>
       </c>
       <c r="L302" s="1" t="n">
-        <v>3304</v>
+        <v>707</v>
       </c>
       <c r="M302" s="1" t="inlineStr">
         <is>
@@ -19659,10 +19659,10 @@
         <v>0</v>
       </c>
       <c r="K303" s="1" t="n">
-        <v>4100000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L303" s="1" t="n">
-        <v>2148</v>
+        <v>459</v>
       </c>
       <c r="M303" s="1" t="inlineStr">
         <is>
@@ -19722,10 +19722,10 @@
         <v>0</v>
       </c>
       <c r="K304" s="1" t="n">
-        <v>11000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="L304" s="1" t="n">
-        <v>5583</v>
+        <v>1194</v>
       </c>
       <c r="M304" s="1" t="inlineStr">
         <is>
@@ -19785,10 +19785,10 @@
         <v>0</v>
       </c>
       <c r="K305" s="1" t="n">
-        <v>4100000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L305" s="1" t="n">
-        <v>2148</v>
+        <v>459</v>
       </c>
       <c r="M305" s="1" t="inlineStr">
         <is>
@@ -19848,10 +19848,10 @@
         <v>0</v>
       </c>
       <c r="K306" s="1" t="n">
-        <v>7000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="L306" s="1" t="n">
-        <v>3629</v>
+        <v>776</v>
       </c>
       <c r="M306" s="1" t="inlineStr">
         <is>
@@ -19911,10 +19911,10 @@
         <v>0</v>
       </c>
       <c r="K307" s="1" t="n">
-        <v>5400000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L307" s="1" t="n">
-        <v>2792</v>
+        <v>597</v>
       </c>
       <c r="M307" s="1" t="inlineStr">
         <is>

--- a/Data_Table/공용 스킬 테이블.xlsx
+++ b/Data_Table/공용 스킬 테이블.xlsx
@@ -10443,10 +10443,10 @@
         <v>0</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>580000</v>
+        <v>430000</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M157" s="1" t="inlineStr">
         <is>
@@ -10506,10 +10506,10 @@
         <v>0</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>750000</v>
+        <v>530000</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M158" s="1" t="inlineStr">
         <is>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>980000</v>
+        <v>720000</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M159" s="1" t="inlineStr">
         <is>
@@ -10632,10 +10632,10 @@
         <v>0</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>980000</v>
+        <v>720000</v>
       </c>
       <c r="L160" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M160" s="1" t="inlineStr">
         <is>
@@ -10695,10 +10695,10 @@
         <v>0</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>1300000</v>
+        <v>910000</v>
       </c>
       <c r="L161" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M161" s="1" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>0</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>980000</v>
+        <v>720000</v>
       </c>
       <c r="L162" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M162" s="1" t="inlineStr">
         <is>
@@ -10821,10 +10821,10 @@
         <v>0</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>1300000</v>
+        <v>910000</v>
       </c>
       <c r="L163" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M163" s="1" t="inlineStr">
         <is>
@@ -10884,10 +10884,10 @@
         <v>0</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>1300000</v>
+        <v>910000</v>
       </c>
       <c r="L164" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M164" s="1" t="inlineStr">
         <is>
@@ -10947,10 +10947,10 @@
         <v>0</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>580000</v>
+        <v>430000</v>
       </c>
       <c r="L165" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M165" s="1" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         <v>0</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>750000</v>
+        <v>530000</v>
       </c>
       <c r="L166" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M166" s="1" t="inlineStr">
         <is>
@@ -11073,10 +11073,10 @@
         <v>0</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>980000</v>
+        <v>720000</v>
       </c>
       <c r="L167" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M167" s="1" t="inlineStr">
         <is>
@@ -11136,10 +11136,10 @@
         <v>0</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>980000</v>
+        <v>720000</v>
       </c>
       <c r="L168" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M168" s="1" t="inlineStr">
         <is>
@@ -11199,10 +11199,10 @@
         <v>0</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>980000</v>
+        <v>720000</v>
       </c>
       <c r="L169" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M169" s="1" t="inlineStr">
         <is>
@@ -11262,10 +11262,10 @@
         <v>0</v>
       </c>
       <c r="K170" s="1" t="n">
-        <v>1300000</v>
+        <v>910000</v>
       </c>
       <c r="L170" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M170" s="1" t="inlineStr">
         <is>
@@ -11325,10 +11325,10 @@
         <v>0</v>
       </c>
       <c r="K171" s="1" t="n">
-        <v>1700000</v>
+        <v>1200000</v>
       </c>
       <c r="L171" s="1" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M171" s="1" t="inlineStr">
         <is>
@@ -11388,10 +11388,10 @@
         <v>0</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>1300000</v>
+        <v>910000</v>
       </c>
       <c r="L172" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M172" s="1" t="inlineStr">
         <is>
@@ -11451,10 +11451,10 @@
         <v>0</v>
       </c>
       <c r="K173" s="1" t="n">
-        <v>580000</v>
+        <v>430000</v>
       </c>
       <c r="L173" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M173" s="1" t="inlineStr">
         <is>
@@ -11514,10 +11514,10 @@
         <v>0</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>750000</v>
+        <v>530000</v>
       </c>
       <c r="L174" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M174" s="1" t="inlineStr">
         <is>
@@ -11577,10 +11577,10 @@
         <v>0</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>980000</v>
+        <v>720000</v>
       </c>
       <c r="L175" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M175" s="1" t="inlineStr">
         <is>
@@ -11640,10 +11640,10 @@
         <v>0</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>980000</v>
+        <v>720000</v>
       </c>
       <c r="L176" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M176" s="1" t="inlineStr">
         <is>
@@ -11703,10 +11703,10 @@
         <v>0</v>
       </c>
       <c r="K177" s="1" t="n">
-        <v>1300000</v>
+        <v>910000</v>
       </c>
       <c r="L177" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M177" s="1" t="inlineStr">
         <is>
@@ -11766,10 +11766,10 @@
         <v>0</v>
       </c>
       <c r="K178" s="1" t="n">
-        <v>2500000</v>
+        <v>1800000</v>
       </c>
       <c r="L178" s="1" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M178" s="1" t="inlineStr">
         <is>
@@ -11829,10 +11829,10 @@
         <v>0</v>
       </c>
       <c r="K179" s="1" t="n">
-        <v>1300000</v>
+        <v>910000</v>
       </c>
       <c r="L179" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M179" s="1" t="inlineStr">
         <is>
@@ -11892,10 +11892,10 @@
         <v>0</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>3300000</v>
+        <v>2300000</v>
       </c>
       <c r="L180" s="1" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="M180" s="1" t="inlineStr">
         <is>
@@ -11955,10 +11955,10 @@
         <v>0</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>1200000</v>
+        <v>820000</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M181" s="1" t="inlineStr">
         <is>
@@ -12018,10 +12018,10 @@
         <v>0</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>750000</v>
+        <v>530000</v>
       </c>
       <c r="L182" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M182" s="1" t="inlineStr">
         <is>
@@ -12081,10 +12081,10 @@
         <v>0</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>980000</v>
+        <v>720000</v>
       </c>
       <c r="L183" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M183" s="1" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>0</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>980000</v>
+        <v>720000</v>
       </c>
       <c r="L184" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M184" s="1" t="inlineStr">
         <is>
@@ -12207,10 +12207,10 @@
         <v>0</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>1300000</v>
+        <v>910000</v>
       </c>
       <c r="L185" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M185" s="1" t="inlineStr">
         <is>
@@ -12270,10 +12270,10 @@
         <v>0</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>1300000</v>
+        <v>910000</v>
       </c>
       <c r="L186" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M186" s="1" t="inlineStr">
         <is>
@@ -12333,10 +12333,10 @@
         <v>0</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>1700000</v>
+        <v>1200000</v>
       </c>
       <c r="L187" s="1" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M187" s="1" t="inlineStr">
         <is>
@@ -12396,10 +12396,10 @@
         <v>0</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>1500000</v>
+        <v>1100000</v>
       </c>
       <c r="L188" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M188" s="1" t="inlineStr">
         <is>
@@ -12459,10 +12459,10 @@
         <v>0</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>2000000</v>
+        <v>1400000</v>
       </c>
       <c r="L189" s="1" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M189" s="1" t="inlineStr">
         <is>
@@ -12522,10 +12522,10 @@
         <v>0</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>1300000</v>
+        <v>910000</v>
       </c>
       <c r="L190" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M190" s="1" t="inlineStr">
         <is>
@@ -12585,10 +12585,10 @@
         <v>0</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>980000</v>
+        <v>720000</v>
       </c>
       <c r="L191" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M191" s="1" t="inlineStr">
         <is>
@@ -12648,10 +12648,10 @@
         <v>0</v>
       </c>
       <c r="K192" s="1" t="n">
-        <v>1700000</v>
+        <v>1200000</v>
       </c>
       <c r="L192" s="1" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M192" s="1" t="inlineStr">
         <is>
@@ -12711,10 +12711,10 @@
         <v>0</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>1300000</v>
+        <v>910000</v>
       </c>
       <c r="L193" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M193" s="1" t="inlineStr">
         <is>
@@ -12843,10 +12843,10 @@
         <v>0</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>1100000</v>
+        <v>850000</v>
       </c>
       <c r="L195" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M195" s="1" t="inlineStr">
         <is>
@@ -12906,10 +12906,10 @@
         <v>0</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>1400000</v>
+        <v>1100000</v>
       </c>
       <c r="L196" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M196" s="1" t="inlineStr">
         <is>
@@ -12969,10 +12969,10 @@
         <v>0</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>1800000</v>
+        <v>1400000</v>
       </c>
       <c r="L197" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M197" s="1" t="inlineStr">
         <is>
@@ -13032,10 +13032,10 @@
         <v>0</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>1800000</v>
+        <v>1400000</v>
       </c>
       <c r="L198" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M198" s="1" t="inlineStr">
         <is>
@@ -13095,10 +13095,10 @@
         <v>0</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>2400000</v>
+        <v>1900000</v>
       </c>
       <c r="L199" s="1" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M199" s="1" t="inlineStr">
         <is>
@@ -13158,10 +13158,10 @@
         <v>0</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>1800000</v>
+        <v>1400000</v>
       </c>
       <c r="L200" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M200" s="1" t="inlineStr">
         <is>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>2400000</v>
+        <v>1900000</v>
       </c>
       <c r="L201" s="1" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M201" s="1" t="inlineStr">
         <is>
@@ -13284,10 +13284,10 @@
         <v>0</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>2400000</v>
+        <v>1900000</v>
       </c>
       <c r="L202" s="1" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M202" s="1" t="inlineStr">
         <is>
@@ -13347,10 +13347,10 @@
         <v>0</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>1100000</v>
+        <v>850000</v>
       </c>
       <c r="L203" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M203" s="1" t="inlineStr">
         <is>
@@ -13410,10 +13410,10 @@
         <v>0</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>1400000</v>
+        <v>1100000</v>
       </c>
       <c r="L204" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M204" s="1" t="inlineStr">
         <is>
@@ -13473,10 +13473,10 @@
         <v>0</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>1800000</v>
+        <v>1400000</v>
       </c>
       <c r="L205" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M205" s="1" t="inlineStr">
         <is>
@@ -13536,10 +13536,10 @@
         <v>0</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>1800000</v>
+        <v>1400000</v>
       </c>
       <c r="L206" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M206" s="1" t="inlineStr">
         <is>
@@ -13599,10 +13599,10 @@
         <v>0</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>1800000</v>
+        <v>1400000</v>
       </c>
       <c r="L207" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M207" s="1" t="inlineStr">
         <is>
@@ -13662,10 +13662,10 @@
         <v>0</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>2400000</v>
+        <v>1900000</v>
       </c>
       <c r="L208" s="1" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M208" s="1" t="inlineStr">
         <is>
@@ -13725,10 +13725,10 @@
         <v>0</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>3000000</v>
+        <v>2400000</v>
       </c>
       <c r="L209" s="1" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M209" s="1" t="inlineStr">
         <is>
@@ -13788,10 +13788,10 @@
         <v>0</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>2400000</v>
+        <v>1900000</v>
       </c>
       <c r="L210" s="1" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M210" s="1" t="inlineStr">
         <is>
@@ -13851,10 +13851,10 @@
         <v>0</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>1100000</v>
+        <v>850000</v>
       </c>
       <c r="L211" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M211" s="1" t="inlineStr">
         <is>
@@ -13914,10 +13914,10 @@
         <v>0</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>1400000</v>
+        <v>1100000</v>
       </c>
       <c r="L212" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M212" s="1" t="inlineStr">
         <is>
@@ -13977,10 +13977,10 @@
         <v>0</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>1800000</v>
+        <v>1400000</v>
       </c>
       <c r="L213" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M213" s="1" t="inlineStr">
         <is>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>1800000</v>
+        <v>1400000</v>
       </c>
       <c r="L214" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M214" s="1" t="inlineStr">
         <is>
@@ -14103,10 +14103,10 @@
         <v>0</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>2400000</v>
+        <v>1900000</v>
       </c>
       <c r="L215" s="1" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M215" s="1" t="inlineStr">
         <is>
@@ -14166,10 +14166,10 @@
         <v>0</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>4700000</v>
+        <v>3700000</v>
       </c>
       <c r="L216" s="1" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="M216" s="1" t="inlineStr">
         <is>
@@ -14229,10 +14229,10 @@
         <v>0</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>2400000</v>
+        <v>1900000</v>
       </c>
       <c r="L217" s="1" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M217" s="1" t="inlineStr">
         <is>
@@ -14292,10 +14292,10 @@
         <v>0</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>6000000</v>
+        <v>4800000</v>
       </c>
       <c r="L218" s="1" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="M218" s="1" t="inlineStr">
         <is>
@@ -14355,10 +14355,10 @@
         <v>0</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>1100000</v>
+        <v>850000</v>
       </c>
       <c r="L219" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M219" s="1" t="inlineStr">
         <is>
@@ -14418,10 +14418,10 @@
         <v>0</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>1400000</v>
+        <v>1100000</v>
       </c>
       <c r="L220" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M220" s="1" t="inlineStr">
         <is>
@@ -14481,10 +14481,10 @@
         <v>0</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>1800000</v>
+        <v>1400000</v>
       </c>
       <c r="L221" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M221" s="1" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>0</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>1800000</v>
+        <v>1400000</v>
       </c>
       <c r="L222" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M222" s="1" t="inlineStr">
         <is>
@@ -14607,10 +14607,10 @@
         <v>0</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>2400000</v>
+        <v>1900000</v>
       </c>
       <c r="L223" s="1" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M223" s="1" t="inlineStr">
         <is>
@@ -14670,10 +14670,10 @@
         <v>0</v>
       </c>
       <c r="K224" s="1" t="n">
-        <v>2400000</v>
+        <v>1900000</v>
       </c>
       <c r="L224" s="1" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M224" s="1" t="inlineStr">
         <is>
@@ -14733,10 +14733,10 @@
         <v>0</v>
       </c>
       <c r="K225" s="1" t="n">
-        <v>3000000</v>
+        <v>2400000</v>
       </c>
       <c r="L225" s="1" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M225" s="1" t="inlineStr">
         <is>
@@ -14796,10 +14796,10 @@
         <v>0</v>
       </c>
       <c r="K226" s="1" t="n">
-        <v>2800000</v>
+        <v>2200000</v>
       </c>
       <c r="L226" s="1" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M226" s="1" t="inlineStr">
         <is>
@@ -14859,10 +14859,10 @@
         <v>0</v>
       </c>
       <c r="K227" s="1" t="n">
-        <v>3600000</v>
+        <v>2800000</v>
       </c>
       <c r="L227" s="1" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M227" s="1" t="inlineStr">
         <is>
@@ -14922,10 +14922,10 @@
         <v>0</v>
       </c>
       <c r="K228" s="1" t="n">
-        <v>4700000</v>
+        <v>3700000</v>
       </c>
       <c r="L228" s="1" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="M228" s="1" t="inlineStr">
         <is>
@@ -14985,10 +14985,10 @@
         <v>0</v>
       </c>
       <c r="K229" s="1" t="n">
-        <v>1800000</v>
+        <v>1400000</v>
       </c>
       <c r="L229" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M229" s="1" t="inlineStr">
         <is>
@@ -15048,10 +15048,10 @@
         <v>0</v>
       </c>
       <c r="K230" s="1" t="n">
-        <v>3000000</v>
+        <v>2400000</v>
       </c>
       <c r="L230" s="1" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M230" s="1" t="inlineStr">
         <is>
@@ -15111,10 +15111,10 @@
         <v>0</v>
       </c>
       <c r="K231" s="1" t="n">
-        <v>2400000</v>
+        <v>1900000</v>
       </c>
       <c r="L231" s="1" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M231" s="1" t="inlineStr">
         <is>
@@ -15243,10 +15243,10 @@
         <v>0</v>
       </c>
       <c r="K233" s="1" t="n">
-        <v>9800000</v>
+        <v>15000000</v>
       </c>
       <c r="L233" s="1" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="M233" s="1" t="inlineStr">
         <is>
@@ -15306,10 +15306,10 @@
         <v>0</v>
       </c>
       <c r="K234" s="1" t="n">
-        <v>13000000</v>
+        <v>19000000</v>
       </c>
       <c r="L234" s="1" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="M234" s="1" t="inlineStr">
         <is>
@@ -15369,10 +15369,10 @@
         <v>0</v>
       </c>
       <c r="K235" s="1" t="n">
-        <v>17000000</v>
+        <v>25000000</v>
       </c>
       <c r="L235" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M235" s="1" t="inlineStr">
         <is>
@@ -15432,10 +15432,10 @@
         <v>0</v>
       </c>
       <c r="K236" s="1" t="n">
-        <v>17000000</v>
+        <v>25000000</v>
       </c>
       <c r="L236" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M236" s="1" t="inlineStr">
         <is>
@@ -15495,10 +15495,10 @@
         <v>0</v>
       </c>
       <c r="K237" s="1" t="n">
-        <v>22000000</v>
+        <v>32000000</v>
       </c>
       <c r="L237" s="1" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="M237" s="1" t="inlineStr">
         <is>
@@ -15558,10 +15558,10 @@
         <v>0</v>
       </c>
       <c r="K238" s="1" t="n">
-        <v>17000000</v>
+        <v>25000000</v>
       </c>
       <c r="L238" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M238" s="1" t="inlineStr">
         <is>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="K239" s="1" t="n">
-        <v>22000000</v>
+        <v>32000000</v>
       </c>
       <c r="L239" s="1" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="M239" s="1" t="inlineStr">
         <is>
@@ -15684,10 +15684,10 @@
         <v>0</v>
       </c>
       <c r="K240" s="1" t="n">
-        <v>22000000</v>
+        <v>32000000</v>
       </c>
       <c r="L240" s="1" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="M240" s="1" t="inlineStr">
         <is>
@@ -15747,10 +15747,10 @@
         <v>0</v>
       </c>
       <c r="K241" s="1" t="n">
-        <v>9800000</v>
+        <v>15000000</v>
       </c>
       <c r="L241" s="1" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="M241" s="1" t="inlineStr">
         <is>
@@ -15810,10 +15810,10 @@
         <v>0</v>
       </c>
       <c r="K242" s="1" t="n">
-        <v>13000000</v>
+        <v>19000000</v>
       </c>
       <c r="L242" s="1" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="M242" s="1" t="inlineStr">
         <is>
@@ -15873,10 +15873,10 @@
         <v>0</v>
       </c>
       <c r="K243" s="1" t="n">
-        <v>17000000</v>
+        <v>25000000</v>
       </c>
       <c r="L243" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M243" s="1" t="inlineStr">
         <is>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="K244" s="1" t="n">
-        <v>17000000</v>
+        <v>25000000</v>
       </c>
       <c r="L244" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M244" s="1" t="inlineStr">
         <is>
@@ -15999,10 +15999,10 @@
         <v>0</v>
       </c>
       <c r="K245" s="1" t="n">
-        <v>17000000</v>
+        <v>25000000</v>
       </c>
       <c r="L245" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M245" s="1" t="inlineStr">
         <is>
@@ -16062,10 +16062,10 @@
         <v>0</v>
       </c>
       <c r="K246" s="1" t="n">
-        <v>22000000</v>
+        <v>32000000</v>
       </c>
       <c r="L246" s="1" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="M246" s="1" t="inlineStr">
         <is>
@@ -16125,10 +16125,10 @@
         <v>0</v>
       </c>
       <c r="K247" s="1" t="n">
-        <v>28000000</v>
+        <v>41000000</v>
       </c>
       <c r="L247" s="1" t="n">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="M247" s="1" t="inlineStr">
         <is>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="K248" s="1" t="n">
-        <v>22000000</v>
+        <v>32000000</v>
       </c>
       <c r="L248" s="1" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="M248" s="1" t="inlineStr">
         <is>
@@ -16251,10 +16251,10 @@
         <v>0</v>
       </c>
       <c r="K249" s="1" t="n">
-        <v>9800000</v>
+        <v>15000000</v>
       </c>
       <c r="L249" s="1" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="M249" s="1" t="inlineStr">
         <is>
@@ -16314,10 +16314,10 @@
         <v>0</v>
       </c>
       <c r="K250" s="1" t="n">
-        <v>13000000</v>
+        <v>19000000</v>
       </c>
       <c r="L250" s="1" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="M250" s="1" t="inlineStr">
         <is>
@@ -16377,10 +16377,10 @@
         <v>0</v>
       </c>
       <c r="K251" s="1" t="n">
-        <v>17000000</v>
+        <v>25000000</v>
       </c>
       <c r="L251" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M251" s="1" t="inlineStr">
         <is>
@@ -16440,10 +16440,10 @@
         <v>0</v>
       </c>
       <c r="K252" s="1" t="n">
-        <v>17000000</v>
+        <v>25000000</v>
       </c>
       <c r="L252" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M252" s="1" t="inlineStr">
         <is>
@@ -16503,10 +16503,10 @@
         <v>0</v>
       </c>
       <c r="K253" s="1" t="n">
-        <v>22000000</v>
+        <v>32000000</v>
       </c>
       <c r="L253" s="1" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="M253" s="1" t="inlineStr">
         <is>
@@ -16566,10 +16566,10 @@
         <v>0</v>
       </c>
       <c r="K254" s="1" t="n">
-        <v>22000000</v>
+        <v>32000000</v>
       </c>
       <c r="L254" s="1" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="M254" s="1" t="inlineStr">
         <is>
@@ -16629,10 +16629,10 @@
         <v>0</v>
       </c>
       <c r="K255" s="1" t="n">
-        <v>22000000</v>
+        <v>32000000</v>
       </c>
       <c r="L255" s="1" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="M255" s="1" t="inlineStr">
         <is>
@@ -16692,10 +16692,10 @@
         <v>0</v>
       </c>
       <c r="K256" s="1" t="n">
-        <v>56000000</v>
+        <v>82000000</v>
       </c>
       <c r="L256" s="1" t="n">
-        <v>198</v>
+        <v>287</v>
       </c>
       <c r="M256" s="1" t="inlineStr">
         <is>
@@ -16755,10 +16755,10 @@
         <v>0</v>
       </c>
       <c r="K257" s="1" t="n">
-        <v>9800000</v>
+        <v>15000000</v>
       </c>
       <c r="L257" s="1" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="M257" s="1" t="inlineStr">
         <is>
@@ -16818,10 +16818,10 @@
         <v>0</v>
       </c>
       <c r="K258" s="1" t="n">
-        <v>13000000</v>
+        <v>19000000</v>
       </c>
       <c r="L258" s="1" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="M258" s="1" t="inlineStr">
         <is>
@@ -16881,10 +16881,10 @@
         <v>0</v>
       </c>
       <c r="K259" s="1" t="n">
-        <v>17000000</v>
+        <v>25000000</v>
       </c>
       <c r="L259" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M259" s="1" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>0</v>
       </c>
       <c r="K260" s="1" t="n">
-        <v>17000000</v>
+        <v>25000000</v>
       </c>
       <c r="L260" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M260" s="1" t="inlineStr">
         <is>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="K261" s="1" t="n">
-        <v>22000000</v>
+        <v>32000000</v>
       </c>
       <c r="L261" s="1" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="M261" s="1" t="inlineStr">
         <is>
@@ -17070,10 +17070,10 @@
         <v>0</v>
       </c>
       <c r="K262" s="1" t="n">
-        <v>22000000</v>
+        <v>32000000</v>
       </c>
       <c r="L262" s="1" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="M262" s="1" t="inlineStr">
         <is>
@@ -17133,10 +17133,10 @@
         <v>0</v>
       </c>
       <c r="K263" s="1" t="n">
-        <v>28000000</v>
+        <v>41000000</v>
       </c>
       <c r="L263" s="1" t="n">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="M263" s="1" t="inlineStr">
         <is>
@@ -17196,10 +17196,10 @@
         <v>0</v>
       </c>
       <c r="K264" s="1" t="n">
-        <v>26000000</v>
+        <v>38000000</v>
       </c>
       <c r="L264" s="1" t="n">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="M264" s="1" t="inlineStr">
         <is>
@@ -17259,10 +17259,10 @@
         <v>0</v>
       </c>
       <c r="K265" s="1" t="n">
-        <v>17000000</v>
+        <v>25000000</v>
       </c>
       <c r="L265" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M265" s="1" t="inlineStr">
         <is>
@@ -17322,10 +17322,10 @@
         <v>0</v>
       </c>
       <c r="K266" s="1" t="n">
-        <v>22000000</v>
+        <v>32000000</v>
       </c>
       <c r="L266" s="1" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="M266" s="1" t="inlineStr">
         <is>
@@ -17385,10 +17385,10 @@
         <v>0</v>
       </c>
       <c r="K267" s="1" t="n">
-        <v>17000000</v>
+        <v>25000000</v>
       </c>
       <c r="L267" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M267" s="1" t="inlineStr">
         <is>
@@ -17448,10 +17448,10 @@
         <v>0</v>
       </c>
       <c r="K268" s="1" t="n">
-        <v>28000000</v>
+        <v>41000000</v>
       </c>
       <c r="L268" s="1" t="n">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="M268" s="1" t="inlineStr">
         <is>
@@ -17511,10 +17511,10 @@
         <v>0</v>
       </c>
       <c r="K269" s="1" t="n">
-        <v>22000000</v>
+        <v>32000000</v>
       </c>
       <c r="L269" s="1" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="M269" s="1" t="inlineStr">
         <is>
@@ -17643,10 +17643,10 @@
         <v>0</v>
       </c>
       <c r="K271" s="1" t="n">
-        <v>690000000</v>
+        <v>460000000</v>
       </c>
       <c r="L271" s="1" t="n">
-        <v>272</v>
+        <v>179</v>
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
@@ -17706,10 +17706,10 @@
         <v>0</v>
       </c>
       <c r="K272" s="1" t="n">
-        <v>890000000</v>
+        <v>600000000</v>
       </c>
       <c r="L272" s="1" t="n">
-        <v>354</v>
+        <v>233</v>
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
@@ -17769,10 +17769,10 @@
         <v>0</v>
       </c>
       <c r="K273" s="1" t="n">
-        <v>1200000000</v>
+        <v>780000000</v>
       </c>
       <c r="L273" s="1" t="n">
-        <v>459</v>
+        <v>302</v>
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
@@ -17832,10 +17832,10 @@
         <v>0</v>
       </c>
       <c r="K274" s="1" t="n">
-        <v>1200000000</v>
+        <v>780000000</v>
       </c>
       <c r="L274" s="1" t="n">
-        <v>459</v>
+        <v>302</v>
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
@@ -17895,10 +17895,10 @@
         <v>0</v>
       </c>
       <c r="K275" s="1" t="n">
-        <v>1500000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L275" s="1" t="n">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="M275" s="1" t="inlineStr">
         <is>
@@ -17958,10 +17958,10 @@
         <v>0</v>
       </c>
       <c r="K276" s="1" t="n">
-        <v>1200000000</v>
+        <v>780000000</v>
       </c>
       <c r="L276" s="1" t="n">
-        <v>459</v>
+        <v>302</v>
       </c>
       <c r="M276" s="1" t="inlineStr">
         <is>
@@ -18021,10 +18021,10 @@
         <v>0</v>
       </c>
       <c r="K277" s="1" t="n">
-        <v>1500000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L277" s="1" t="n">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="M277" s="1" t="inlineStr">
         <is>
@@ -18084,10 +18084,10 @@
         <v>0</v>
       </c>
       <c r="K278" s="1" t="n">
-        <v>1500000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L278" s="1" t="n">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="M278" s="1" t="inlineStr">
         <is>
@@ -18147,10 +18147,10 @@
         <v>0</v>
       </c>
       <c r="K279" s="1" t="n">
-        <v>690000000</v>
+        <v>460000000</v>
       </c>
       <c r="L279" s="1" t="n">
-        <v>272</v>
+        <v>179</v>
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
@@ -18210,10 +18210,10 @@
         <v>0</v>
       </c>
       <c r="K280" s="1" t="n">
-        <v>890000000</v>
+        <v>600000000</v>
       </c>
       <c r="L280" s="1" t="n">
-        <v>354</v>
+        <v>233</v>
       </c>
       <c r="M280" s="1" t="inlineStr">
         <is>
@@ -18273,10 +18273,10 @@
         <v>0</v>
       </c>
       <c r="K281" s="1" t="n">
-        <v>1200000000</v>
+        <v>780000000</v>
       </c>
       <c r="L281" s="1" t="n">
-        <v>459</v>
+        <v>302</v>
       </c>
       <c r="M281" s="1" t="inlineStr">
         <is>
@@ -18336,10 +18336,10 @@
         <v>0</v>
       </c>
       <c r="K282" s="1" t="n">
-        <v>1200000000</v>
+        <v>780000000</v>
       </c>
       <c r="L282" s="1" t="n">
-        <v>459</v>
+        <v>302</v>
       </c>
       <c r="M282" s="1" t="inlineStr">
         <is>
@@ -18399,10 +18399,10 @@
         <v>0</v>
       </c>
       <c r="K283" s="1" t="n">
-        <v>1200000000</v>
+        <v>780000000</v>
       </c>
       <c r="L283" s="1" t="n">
-        <v>459</v>
+        <v>302</v>
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
@@ -18462,10 +18462,10 @@
         <v>0</v>
       </c>
       <c r="K284" s="1" t="n">
-        <v>1500000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L284" s="1" t="n">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="M284" s="1" t="inlineStr">
         <is>
@@ -18525,10 +18525,10 @@
         <v>0</v>
       </c>
       <c r="K285" s="1" t="n">
-        <v>2000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="L285" s="1" t="n">
-        <v>776</v>
+        <v>511</v>
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
@@ -18588,10 +18588,10 @@
         <v>0</v>
       </c>
       <c r="K286" s="1" t="n">
-        <v>1500000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L286" s="1" t="n">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="M286" s="1" t="inlineStr">
         <is>
@@ -18651,10 +18651,10 @@
         <v>0</v>
       </c>
       <c r="K287" s="1" t="n">
-        <v>690000000</v>
+        <v>460000000</v>
       </c>
       <c r="L287" s="1" t="n">
-        <v>272</v>
+        <v>179</v>
       </c>
       <c r="M287" s="1" t="inlineStr">
         <is>
@@ -18714,10 +18714,10 @@
         <v>0</v>
       </c>
       <c r="K288" s="1" t="n">
-        <v>890000000</v>
+        <v>600000000</v>
       </c>
       <c r="L288" s="1" t="n">
-        <v>354</v>
+        <v>233</v>
       </c>
       <c r="M288" s="1" t="inlineStr">
         <is>
@@ -18777,10 +18777,10 @@
         <v>0</v>
       </c>
       <c r="K289" s="1" t="n">
-        <v>1200000000</v>
+        <v>780000000</v>
       </c>
       <c r="L289" s="1" t="n">
-        <v>459</v>
+        <v>302</v>
       </c>
       <c r="M289" s="1" t="inlineStr">
         <is>
@@ -18840,10 +18840,10 @@
         <v>0</v>
       </c>
       <c r="K290" s="1" t="n">
-        <v>1200000000</v>
+        <v>780000000</v>
       </c>
       <c r="L290" s="1" t="n">
-        <v>459</v>
+        <v>302</v>
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
@@ -18903,10 +18903,10 @@
         <v>0</v>
       </c>
       <c r="K291" s="1" t="n">
-        <v>1500000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L291" s="1" t="n">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="M291" s="1" t="inlineStr">
         <is>
@@ -18966,10 +18966,10 @@
         <v>0</v>
       </c>
       <c r="K292" s="1" t="n">
-        <v>1500000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L292" s="1" t="n">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="M292" s="1" t="inlineStr">
         <is>
@@ -19029,10 +19029,10 @@
         <v>0</v>
       </c>
       <c r="K293" s="1" t="n">
-        <v>1500000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L293" s="1" t="n">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="M293" s="1" t="inlineStr">
         <is>
@@ -19092,10 +19092,10 @@
         <v>0</v>
       </c>
       <c r="K294" s="1" t="n">
-        <v>3900000000</v>
+        <v>2700000000</v>
       </c>
       <c r="L294" s="1" t="n">
-        <v>1552</v>
+        <v>1021</v>
       </c>
       <c r="M294" s="1" t="inlineStr">
         <is>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="K295" s="1" t="n">
-        <v>690000000</v>
+        <v>460000000</v>
       </c>
       <c r="L295" s="1" t="n">
-        <v>272</v>
+        <v>179</v>
       </c>
       <c r="M295" s="1" t="inlineStr">
         <is>
@@ -19218,10 +19218,10 @@
         <v>0</v>
       </c>
       <c r="K296" s="1" t="n">
-        <v>890000000</v>
+        <v>600000000</v>
       </c>
       <c r="L296" s="1" t="n">
-        <v>354</v>
+        <v>233</v>
       </c>
       <c r="M296" s="1" t="inlineStr">
         <is>
@@ -19281,10 +19281,10 @@
         <v>0</v>
       </c>
       <c r="K297" s="1" t="n">
-        <v>1200000000</v>
+        <v>780000000</v>
       </c>
       <c r="L297" s="1" t="n">
-        <v>459</v>
+        <v>302</v>
       </c>
       <c r="M297" s="1" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>0</v>
       </c>
       <c r="K298" s="1" t="n">
-        <v>1200000000</v>
+        <v>780000000</v>
       </c>
       <c r="L298" s="1" t="n">
-        <v>459</v>
+        <v>302</v>
       </c>
       <c r="M298" s="1" t="inlineStr">
         <is>
@@ -19407,10 +19407,10 @@
         <v>0</v>
       </c>
       <c r="K299" s="1" t="n">
-        <v>1500000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L299" s="1" t="n">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="M299" s="1" t="inlineStr">
         <is>
@@ -19470,10 +19470,10 @@
         <v>0</v>
       </c>
       <c r="K300" s="1" t="n">
-        <v>1500000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L300" s="1" t="n">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="M300" s="1" t="inlineStr">
         <is>
@@ -19533,10 +19533,10 @@
         <v>0</v>
       </c>
       <c r="K301" s="1" t="n">
-        <v>2000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="L301" s="1" t="n">
-        <v>776</v>
+        <v>511</v>
       </c>
       <c r="M301" s="1" t="inlineStr">
         <is>
@@ -19596,10 +19596,10 @@
         <v>0</v>
       </c>
       <c r="K302" s="1" t="n">
-        <v>1800000000</v>
+        <v>1200000000</v>
       </c>
       <c r="L302" s="1" t="n">
-        <v>707</v>
+        <v>465</v>
       </c>
       <c r="M302" s="1" t="inlineStr">
         <is>
@@ -19659,10 +19659,10 @@
         <v>0</v>
       </c>
       <c r="K303" s="1" t="n">
-        <v>1200000000</v>
+        <v>780000000</v>
       </c>
       <c r="L303" s="1" t="n">
-        <v>459</v>
+        <v>302</v>
       </c>
       <c r="M303" s="1" t="inlineStr">
         <is>
@@ -19722,10 +19722,10 @@
         <v>0</v>
       </c>
       <c r="K304" s="1" t="n">
-        <v>3000000000</v>
+        <v>2100000000</v>
       </c>
       <c r="L304" s="1" t="n">
-        <v>1194</v>
+        <v>785</v>
       </c>
       <c r="M304" s="1" t="inlineStr">
         <is>
@@ -19785,10 +19785,10 @@
         <v>0</v>
       </c>
       <c r="K305" s="1" t="n">
-        <v>1200000000</v>
+        <v>780000000</v>
       </c>
       <c r="L305" s="1" t="n">
-        <v>459</v>
+        <v>302</v>
       </c>
       <c r="M305" s="1" t="inlineStr">
         <is>
@@ -19848,10 +19848,10 @@
         <v>0</v>
       </c>
       <c r="K306" s="1" t="n">
-        <v>2000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="L306" s="1" t="n">
-        <v>776</v>
+        <v>511</v>
       </c>
       <c r="M306" s="1" t="inlineStr">
         <is>
@@ -19911,10 +19911,10 @@
         <v>0</v>
       </c>
       <c r="K307" s="1" t="n">
-        <v>1500000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L307" s="1" t="n">
-        <v>597</v>
+        <v>393</v>
       </c>
       <c r="M307" s="1" t="inlineStr">
         <is>

--- a/Data_Table/공용 스킬 테이블.xlsx
+++ b/Data_Table/공용 스킬 테이블.xlsx
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>0</v>
@@ -969,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="L10" s="1" t="n">
         <v>0</v>
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>0</v>
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>0</v>
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="L14" s="1" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="L15" s="1" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="L16" s="1" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="L17" s="1" t="n">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="L18" s="1" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>6500</v>
+        <v>7100</v>
       </c>
       <c r="L19" s="1" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="L20" s="1" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="L21" s="1" t="n">
         <v>0</v>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="L22" s="1" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="L23" s="1" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="L24" s="1" t="n">
         <v>0</v>
@@ -2103,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="L25" s="1" t="n">
         <v>0</v>
@@ -2166,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>6800</v>
+        <v>7400</v>
       </c>
       <c r="L26" s="1" t="n">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>9800</v>
+        <v>11000</v>
       </c>
       <c r="L28" s="1" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="L29" s="1" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="L30" s="1" t="n">
         <v>0</v>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="L31" s="1" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="L32" s="1" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="L33" s="1" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="L34" s="1" t="n">
         <v>0</v>
@@ -2733,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>6500</v>
+        <v>7100</v>
       </c>
       <c r="L35" s="1" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>0</v>
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>0</v>
@@ -2922,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>6500</v>
+        <v>7100</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>0</v>
@@ -3111,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>11000</v>
+        <v>27000</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>3</v>
@@ -3306,10 +3306,10 @@
         <v>0</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M44" s="1" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>33000</v>
+        <v>72000</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M45" s="1" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         <v>0</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M46" s="1" t="inlineStr">
         <is>
@@ -3495,10 +3495,10 @@
         <v>0</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>22000</v>
+        <v>45000</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M47" s="1" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -3621,10 +3621,10 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>22000</v>
+        <v>45000</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M49" s="1" t="inlineStr">
         <is>
@@ -3684,10 +3684,10 @@
         <v>0</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>22000</v>
+        <v>45000</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M50" s="1" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>11000</v>
+        <v>27000</v>
       </c>
       <c r="L51" s="1" t="n">
         <v>3</v>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M52" s="1" t="inlineStr">
         <is>
@@ -3873,10 +3873,10 @@
         <v>0</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M53" s="1" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         <v>0</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M54" s="1" t="inlineStr">
         <is>
@@ -3999,10 +3999,10 @@
         <v>0</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M55" s="1" t="inlineStr">
         <is>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>22000</v>
+        <v>45000</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M56" s="1" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>26000</v>
+        <v>63000</v>
       </c>
       <c r="L57" s="1" t="n">
         <v>7</v>
@@ -4188,10 +4188,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>22000</v>
+        <v>45000</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M58" s="1" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>11000</v>
+        <v>27000</v>
       </c>
       <c r="L59" s="1" t="n">
         <v>3</v>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M60" s="1" t="inlineStr">
         <is>
@@ -4377,10 +4377,10 @@
         <v>0</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M61" s="1" t="inlineStr">
         <is>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M62" s="1" t="inlineStr">
         <is>
@@ -4503,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>22000</v>
+        <v>45000</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M63" s="1" t="inlineStr">
         <is>
@@ -4566,10 +4566,10 @@
         <v>0</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M64" s="1" t="inlineStr">
         <is>
@@ -4629,10 +4629,10 @@
         <v>0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>22000</v>
+        <v>45000</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M65" s="1" t="inlineStr">
         <is>
@@ -4692,10 +4692,10 @@
         <v>0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>51000</v>
+        <v>120000</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M66" s="1" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>19000</v>
+        <v>45000</v>
       </c>
       <c r="L67" s="1" t="n">
         <v>5</v>
@@ -4818,10 +4818,10 @@
         <v>0</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M68" s="1" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         <v>0</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M69" s="1" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>0</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M70" s="1" t="inlineStr">
         <is>
@@ -5007,10 +5007,10 @@
         <v>0</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>22000</v>
+        <v>45000</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M71" s="1" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
         <v>0</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>22000</v>
+        <v>45000</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M72" s="1" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>26000</v>
+        <v>63000</v>
       </c>
       <c r="L73" s="1" t="n">
         <v>7</v>
@@ -5196,10 +5196,10 @@
         <v>0</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>26000</v>
+        <v>54000</v>
       </c>
       <c r="L74" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M74" s="1" t="inlineStr">
         <is>
@@ -5259,10 +5259,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="L75" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M75" s="1" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="L76" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M76" s="1" t="inlineStr">
         <is>
@@ -5385,10 +5385,10 @@
         <v>0</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="L77" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M77" s="1" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="1" t="n">
-        <v>26000</v>
+        <v>63000</v>
       </c>
       <c r="L78" s="1" t="n">
         <v>7</v>
@@ -5511,10 +5511,10 @@
         <v>0</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>22000</v>
+        <v>45000</v>
       </c>
       <c r="L79" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M79" s="1" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="1" t="n">
-        <v>39000</v>
+        <v>130000</v>
       </c>
       <c r="L81" s="1" t="n">
         <v>4</v>
@@ -5706,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>48000</v>
+        <v>160000</v>
       </c>
       <c r="L82" s="1" t="n">
         <v>5</v>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="1" t="n">
-        <v>120000</v>
+        <v>380000</v>
       </c>
       <c r="L83" s="1" t="n">
         <v>12</v>
@@ -5832,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>58000</v>
+        <v>190000</v>
       </c>
       <c r="L84" s="1" t="n">
         <v>6</v>
@@ -5895,7 +5895,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="1" t="n">
-        <v>77000</v>
+        <v>260000</v>
       </c>
       <c r="L85" s="1" t="n">
         <v>8</v>
@@ -5958,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>58000</v>
+        <v>190000</v>
       </c>
       <c r="L86" s="1" t="n">
         <v>6</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="1" t="n">
-        <v>77000</v>
+        <v>260000</v>
       </c>
       <c r="L87" s="1" t="n">
         <v>8</v>
@@ -6084,7 +6084,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>77000</v>
+        <v>260000</v>
       </c>
       <c r="L88" s="1" t="n">
         <v>8</v>
@@ -6147,7 +6147,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>39000</v>
+        <v>130000</v>
       </c>
       <c r="L89" s="1" t="n">
         <v>4</v>
@@ -6210,7 +6210,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>48000</v>
+        <v>160000</v>
       </c>
       <c r="L90" s="1" t="n">
         <v>5</v>
@@ -6273,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>58000</v>
+        <v>190000</v>
       </c>
       <c r="L91" s="1" t="n">
         <v>6</v>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>58000</v>
+        <v>190000</v>
       </c>
       <c r="L92" s="1" t="n">
         <v>6</v>
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>58000</v>
+        <v>190000</v>
       </c>
       <c r="L93" s="1" t="n">
         <v>6</v>
@@ -6462,7 +6462,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>77000</v>
+        <v>260000</v>
       </c>
       <c r="L94" s="1" t="n">
         <v>8</v>
@@ -6525,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>96000</v>
+        <v>320000</v>
       </c>
       <c r="L95" s="1" t="n">
         <v>10</v>
@@ -6588,7 +6588,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>77000</v>
+        <v>260000</v>
       </c>
       <c r="L96" s="1" t="n">
         <v>8</v>
@@ -6651,7 +6651,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>39000</v>
+        <v>130000</v>
       </c>
       <c r="L97" s="1" t="n">
         <v>4</v>
@@ -6714,7 +6714,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>48000</v>
+        <v>160000</v>
       </c>
       <c r="L98" s="1" t="n">
         <v>5</v>
@@ -6777,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>58000</v>
+        <v>190000</v>
       </c>
       <c r="L99" s="1" t="n">
         <v>6</v>
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>58000</v>
+        <v>190000</v>
       </c>
       <c r="L100" s="1" t="n">
         <v>6</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="1" t="n">
-        <v>77000</v>
+        <v>260000</v>
       </c>
       <c r="L101" s="1" t="n">
         <v>8</v>
@@ -6966,10 +6966,10 @@
         <v>0</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>150000</v>
+        <v>510000</v>
       </c>
       <c r="L102" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M102" s="1" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>77000</v>
+        <v>260000</v>
       </c>
       <c r="L103" s="1" t="n">
         <v>8</v>
@@ -7092,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>200000</v>
+        <v>630000</v>
       </c>
       <c r="L104" s="1" t="n">
         <v>20</v>
@@ -7155,7 +7155,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>67000</v>
+        <v>220000</v>
       </c>
       <c r="L105" s="1" t="n">
         <v>7</v>
@@ -7218,7 +7218,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>48000</v>
+        <v>160000</v>
       </c>
       <c r="L106" s="1" t="n">
         <v>5</v>
@@ -7281,7 +7281,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="1" t="n">
-        <v>58000</v>
+        <v>190000</v>
       </c>
       <c r="L107" s="1" t="n">
         <v>6</v>
@@ -7344,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="1" t="n">
-        <v>58000</v>
+        <v>190000</v>
       </c>
       <c r="L108" s="1" t="n">
         <v>6</v>
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>77000</v>
+        <v>260000</v>
       </c>
       <c r="L109" s="1" t="n">
         <v>8</v>
@@ -7470,7 +7470,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>77000</v>
+        <v>260000</v>
       </c>
       <c r="L110" s="1" t="n">
         <v>8</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>96000</v>
+        <v>320000</v>
       </c>
       <c r="L111" s="1" t="n">
         <v>10</v>
@@ -7596,10 +7596,10 @@
         <v>0</v>
       </c>
       <c r="K112" s="1" t="n">
-        <v>87000</v>
+        <v>320000</v>
       </c>
       <c r="L112" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M112" s="1" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="1" t="n">
-        <v>120000</v>
+        <v>380000</v>
       </c>
       <c r="L113" s="1" t="n">
         <v>12</v>
@@ -7722,7 +7722,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="1" t="n">
-        <v>77000</v>
+        <v>260000</v>
       </c>
       <c r="L114" s="1" t="n">
         <v>8</v>
@@ -7785,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="1" t="n">
-        <v>58000</v>
+        <v>190000</v>
       </c>
       <c r="L115" s="1" t="n">
         <v>6</v>
@@ -7848,7 +7848,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="1" t="n">
-        <v>96000</v>
+        <v>320000</v>
       </c>
       <c r="L116" s="1" t="n">
         <v>10</v>
@@ -7911,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="1" t="n">
-        <v>77000</v>
+        <v>260000</v>
       </c>
       <c r="L117" s="1" t="n">
         <v>8</v>
@@ -8043,10 +8043,10 @@
         <v>0</v>
       </c>
       <c r="K119" s="1" t="n">
-        <v>92000</v>
+        <v>880000</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M119" s="1" t="inlineStr">
         <is>
@@ -8106,10 +8106,10 @@
         <v>0</v>
       </c>
       <c r="K120" s="1" t="n">
-        <v>130000</v>
+        <v>1100000</v>
       </c>
       <c r="L120" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M120" s="1" t="inlineStr">
         <is>
@@ -8169,10 +8169,10 @@
         <v>0</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>170000</v>
+        <v>1500000</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M121" s="1" t="inlineStr">
         <is>
@@ -8232,10 +8232,10 @@
         <v>0</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>170000</v>
+        <v>1500000</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M122" s="1" t="inlineStr">
         <is>
@@ -8295,10 +8295,10 @@
         <v>0</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>210000</v>
+        <v>1800000</v>
       </c>
       <c r="L123" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M123" s="1" t="inlineStr">
         <is>
@@ -8358,10 +8358,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>170000</v>
+        <v>1500000</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M124" s="1" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>0</v>
       </c>
       <c r="K125" s="1" t="n">
-        <v>210000</v>
+        <v>1800000</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M125" s="1" t="inlineStr">
         <is>
@@ -8484,10 +8484,10 @@
         <v>0</v>
       </c>
       <c r="K126" s="1" t="n">
-        <v>210000</v>
+        <v>1800000</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M126" s="1" t="inlineStr">
         <is>
@@ -8547,10 +8547,10 @@
         <v>0</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>92000</v>
+        <v>880000</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M127" s="1" t="inlineStr">
         <is>
@@ -8610,10 +8610,10 @@
         <v>0</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>130000</v>
+        <v>1100000</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M128" s="1" t="inlineStr">
         <is>
@@ -8673,10 +8673,10 @@
         <v>0</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>170000</v>
+        <v>1500000</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M129" s="1" t="inlineStr">
         <is>
@@ -8736,10 +8736,10 @@
         <v>0</v>
       </c>
       <c r="K130" s="1" t="n">
-        <v>170000</v>
+        <v>1500000</v>
       </c>
       <c r="L130" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M130" s="1" t="inlineStr">
         <is>
@@ -8799,10 +8799,10 @@
         <v>0</v>
       </c>
       <c r="K131" s="1" t="n">
-        <v>170000</v>
+        <v>1500000</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M131" s="1" t="inlineStr">
         <is>
@@ -8862,10 +8862,10 @@
         <v>0</v>
       </c>
       <c r="K132" s="1" t="n">
-        <v>210000</v>
+        <v>1800000</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M132" s="1" t="inlineStr">
         <is>
@@ -8925,10 +8925,10 @@
         <v>0</v>
       </c>
       <c r="K133" s="1" t="n">
-        <v>260000</v>
+        <v>2300000</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M133" s="1" t="inlineStr">
         <is>
@@ -8988,10 +8988,10 @@
         <v>0</v>
       </c>
       <c r="K134" s="1" t="n">
-        <v>210000</v>
+        <v>1800000</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M134" s="1" t="inlineStr">
         <is>
@@ -9051,10 +9051,10 @@
         <v>0</v>
       </c>
       <c r="K135" s="1" t="n">
-        <v>92000</v>
+        <v>880000</v>
       </c>
       <c r="L135" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M135" s="1" t="inlineStr">
         <is>
@@ -9114,10 +9114,10 @@
         <v>0</v>
       </c>
       <c r="K136" s="1" t="n">
-        <v>130000</v>
+        <v>1100000</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M136" s="1" t="inlineStr">
         <is>
@@ -9177,10 +9177,10 @@
         <v>0</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>170000</v>
+        <v>1500000</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M137" s="1" t="inlineStr">
         <is>
@@ -9240,10 +9240,10 @@
         <v>0</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>170000</v>
+        <v>1500000</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M138" s="1" t="inlineStr">
         <is>
@@ -9303,10 +9303,10 @@
         <v>0</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>210000</v>
+        <v>1800000</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M139" s="1" t="inlineStr">
         <is>
@@ -9366,10 +9366,10 @@
         <v>0</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>410000</v>
+        <v>3500000</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M140" s="1" t="inlineStr">
         <is>
@@ -9429,10 +9429,10 @@
         <v>0</v>
       </c>
       <c r="K141" s="1" t="n">
-        <v>210000</v>
+        <v>1800000</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M141" s="1" t="inlineStr">
         <is>
@@ -9492,10 +9492,10 @@
         <v>0</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>520000</v>
+        <v>4600000</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="M142" s="1" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         <v>0</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>190000</v>
+        <v>1700000</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M143" s="1" t="inlineStr">
         <is>
@@ -9618,10 +9618,10 @@
         <v>0</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>130000</v>
+        <v>1100000</v>
       </c>
       <c r="L144" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M144" s="1" t="inlineStr">
         <is>
@@ -9681,10 +9681,10 @@
         <v>0</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>170000</v>
+        <v>1500000</v>
       </c>
       <c r="L145" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M145" s="1" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>0</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>170000</v>
+        <v>1500000</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M146" s="1" t="inlineStr">
         <is>
@@ -9807,10 +9807,10 @@
         <v>0</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>210000</v>
+        <v>1800000</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M147" s="1" t="inlineStr">
         <is>
@@ -9870,10 +9870,10 @@
         <v>0</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>210000</v>
+        <v>1800000</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M148" s="1" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>260000</v>
+        <v>2300000</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M149" s="1" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>240000</v>
+        <v>2100000</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M150" s="1" t="inlineStr">
         <is>
@@ -10059,10 +10059,10 @@
         <v>0</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>170000</v>
+        <v>1500000</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M151" s="1" t="inlineStr">
         <is>
@@ -10122,10 +10122,10 @@
         <v>0</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>410000</v>
+        <v>3500000</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M152" s="1" t="inlineStr">
         <is>
@@ -10185,10 +10185,10 @@
         <v>0</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>170000</v>
+        <v>1500000</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M153" s="1" t="inlineStr">
         <is>
@@ -10248,10 +10248,10 @@
         <v>0</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>260000</v>
+        <v>2300000</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M154" s="1" t="inlineStr">
         <is>
@@ -10311,10 +10311,10 @@
         <v>0</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>210000</v>
+        <v>1800000</v>
       </c>
       <c r="L155" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M155" s="1" t="inlineStr">
         <is>
@@ -10443,10 +10443,10 @@
         <v>0</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>430000</v>
+        <v>6400000</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M157" s="1" t="inlineStr">
         <is>
@@ -10506,10 +10506,10 @@
         <v>0</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>530000</v>
+        <v>8600000</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M158" s="1" t="inlineStr">
         <is>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>720000</v>
+        <v>11000000</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M159" s="1" t="inlineStr">
         <is>
@@ -10632,10 +10632,10 @@
         <v>0</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>720000</v>
+        <v>11000000</v>
       </c>
       <c r="L160" s="1" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M160" s="1" t="inlineStr">
         <is>
@@ -10695,10 +10695,10 @@
         <v>0</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>910000</v>
+        <v>15000000</v>
       </c>
       <c r="L161" s="1" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M161" s="1" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>0</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>720000</v>
+        <v>11000000</v>
       </c>
       <c r="L162" s="1" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M162" s="1" t="inlineStr">
         <is>
@@ -10821,10 +10821,10 @@
         <v>0</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>910000</v>
+        <v>15000000</v>
       </c>
       <c r="L163" s="1" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M163" s="1" t="inlineStr">
         <is>
@@ -10884,10 +10884,10 @@
         <v>0</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>910000</v>
+        <v>15000000</v>
       </c>
       <c r="L164" s="1" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M164" s="1" t="inlineStr">
         <is>
@@ -10947,10 +10947,10 @@
         <v>0</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>430000</v>
+        <v>6400000</v>
       </c>
       <c r="L165" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M165" s="1" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         <v>0</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>530000</v>
+        <v>8600000</v>
       </c>
       <c r="L166" s="1" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M166" s="1" t="inlineStr">
         <is>
@@ -11073,10 +11073,10 @@
         <v>0</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>720000</v>
+        <v>11000000</v>
       </c>
       <c r="L167" s="1" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M167" s="1" t="inlineStr">
         <is>
@@ -11136,10 +11136,10 @@
         <v>0</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>720000</v>
+        <v>11000000</v>
       </c>
       <c r="L168" s="1" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M168" s="1" t="inlineStr">
         <is>
@@ -11199,10 +11199,10 @@
         <v>0</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>720000</v>
+        <v>11000000</v>
       </c>
       <c r="L169" s="1" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M169" s="1" t="inlineStr">
         <is>
@@ -11262,10 +11262,10 @@
         <v>0</v>
       </c>
       <c r="K170" s="1" t="n">
-        <v>910000</v>
+        <v>15000000</v>
       </c>
       <c r="L170" s="1" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M170" s="1" t="inlineStr">
         <is>
@@ -11325,10 +11325,10 @@
         <v>0</v>
       </c>
       <c r="K171" s="1" t="n">
-        <v>1200000</v>
+        <v>19000000</v>
       </c>
       <c r="L171" s="1" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="M171" s="1" t="inlineStr">
         <is>
@@ -11388,10 +11388,10 @@
         <v>0</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>910000</v>
+        <v>15000000</v>
       </c>
       <c r="L172" s="1" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M172" s="1" t="inlineStr">
         <is>
@@ -11451,10 +11451,10 @@
         <v>0</v>
       </c>
       <c r="K173" s="1" t="n">
-        <v>430000</v>
+        <v>6400000</v>
       </c>
       <c r="L173" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M173" s="1" t="inlineStr">
         <is>
@@ -11514,10 +11514,10 @@
         <v>0</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>530000</v>
+        <v>8600000</v>
       </c>
       <c r="L174" s="1" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M174" s="1" t="inlineStr">
         <is>
@@ -11577,10 +11577,10 @@
         <v>0</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>720000</v>
+        <v>11000000</v>
       </c>
       <c r="L175" s="1" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M175" s="1" t="inlineStr">
         <is>
@@ -11640,10 +11640,10 @@
         <v>0</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>720000</v>
+        <v>11000000</v>
       </c>
       <c r="L176" s="1" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M176" s="1" t="inlineStr">
         <is>
@@ -11703,10 +11703,10 @@
         <v>0</v>
       </c>
       <c r="K177" s="1" t="n">
-        <v>910000</v>
+        <v>15000000</v>
       </c>
       <c r="L177" s="1" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M177" s="1" t="inlineStr">
         <is>
@@ -11766,10 +11766,10 @@
         <v>0</v>
       </c>
       <c r="K178" s="1" t="n">
-        <v>1800000</v>
+        <v>28000000</v>
       </c>
       <c r="L178" s="1" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="M178" s="1" t="inlineStr">
         <is>
@@ -11829,10 +11829,10 @@
         <v>0</v>
       </c>
       <c r="K179" s="1" t="n">
-        <v>910000</v>
+        <v>15000000</v>
       </c>
       <c r="L179" s="1" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M179" s="1" t="inlineStr">
         <is>
@@ -11892,10 +11892,10 @@
         <v>0</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>2300000</v>
+        <v>37000000</v>
       </c>
       <c r="L180" s="1" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="M180" s="1" t="inlineStr">
         <is>
@@ -11955,10 +11955,10 @@
         <v>0</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>820000</v>
+        <v>13000000</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="M181" s="1" t="inlineStr">
         <is>
@@ -12018,10 +12018,10 @@
         <v>0</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>530000</v>
+        <v>8600000</v>
       </c>
       <c r="L182" s="1" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M182" s="1" t="inlineStr">
         <is>
@@ -12081,10 +12081,10 @@
         <v>0</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>720000</v>
+        <v>11000000</v>
       </c>
       <c r="L183" s="1" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M183" s="1" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>0</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>720000</v>
+        <v>11000000</v>
       </c>
       <c r="L184" s="1" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M184" s="1" t="inlineStr">
         <is>
@@ -12207,10 +12207,10 @@
         <v>0</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>910000</v>
+        <v>15000000</v>
       </c>
       <c r="L185" s="1" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M185" s="1" t="inlineStr">
         <is>
@@ -12270,10 +12270,10 @@
         <v>0</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>910000</v>
+        <v>15000000</v>
       </c>
       <c r="L186" s="1" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M186" s="1" t="inlineStr">
         <is>
@@ -12333,10 +12333,10 @@
         <v>0</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>1200000</v>
+        <v>19000000</v>
       </c>
       <c r="L187" s="1" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="M187" s="1" t="inlineStr">
         <is>
@@ -12396,10 +12396,10 @@
         <v>0</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>1100000</v>
+        <v>17000000</v>
       </c>
       <c r="L188" s="1" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="M188" s="1" t="inlineStr">
         <is>
@@ -12459,10 +12459,10 @@
         <v>0</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>1400000</v>
+        <v>22000000</v>
       </c>
       <c r="L189" s="1" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="M189" s="1" t="inlineStr">
         <is>
@@ -12522,10 +12522,10 @@
         <v>0</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>910000</v>
+        <v>15000000</v>
       </c>
       <c r="L190" s="1" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M190" s="1" t="inlineStr">
         <is>
@@ -12585,10 +12585,10 @@
         <v>0</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>720000</v>
+        <v>11000000</v>
       </c>
       <c r="L191" s="1" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M191" s="1" t="inlineStr">
         <is>
@@ -12648,10 +12648,10 @@
         <v>0</v>
       </c>
       <c r="K192" s="1" t="n">
-        <v>1200000</v>
+        <v>19000000</v>
       </c>
       <c r="L192" s="1" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="M192" s="1" t="inlineStr">
         <is>
@@ -12711,10 +12711,10 @@
         <v>0</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>910000</v>
+        <v>15000000</v>
       </c>
       <c r="L193" s="1" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M193" s="1" t="inlineStr">
         <is>
@@ -12843,10 +12843,10 @@
         <v>0</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>850000</v>
+        <v>53000000</v>
       </c>
       <c r="L195" s="1" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="M195" s="1" t="inlineStr">
         <is>
@@ -12906,10 +12906,10 @@
         <v>0</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>1100000</v>
+        <v>68000000</v>
       </c>
       <c r="L196" s="1" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="M196" s="1" t="inlineStr">
         <is>
@@ -12969,10 +12969,10 @@
         <v>0</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>1400000</v>
+        <v>89000000</v>
       </c>
       <c r="L197" s="1" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M197" s="1" t="inlineStr">
         <is>
@@ -13032,10 +13032,10 @@
         <v>0</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>1400000</v>
+        <v>89000000</v>
       </c>
       <c r="L198" s="1" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M198" s="1" t="inlineStr">
         <is>
@@ -13095,10 +13095,10 @@
         <v>0</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>1900000</v>
+        <v>120000000</v>
       </c>
       <c r="L199" s="1" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="M199" s="1" t="inlineStr">
         <is>
@@ -13158,10 +13158,10 @@
         <v>0</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>1400000</v>
+        <v>89000000</v>
       </c>
       <c r="L200" s="1" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M200" s="1" t="inlineStr">
         <is>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>1900000</v>
+        <v>120000000</v>
       </c>
       <c r="L201" s="1" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="M201" s="1" t="inlineStr">
         <is>
@@ -13284,10 +13284,10 @@
         <v>0</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>1900000</v>
+        <v>120000000</v>
       </c>
       <c r="L202" s="1" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="M202" s="1" t="inlineStr">
         <is>
@@ -13347,10 +13347,10 @@
         <v>0</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>850000</v>
+        <v>53000000</v>
       </c>
       <c r="L203" s="1" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="M203" s="1" t="inlineStr">
         <is>
@@ -13410,10 +13410,10 @@
         <v>0</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>1100000</v>
+        <v>68000000</v>
       </c>
       <c r="L204" s="1" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="M204" s="1" t="inlineStr">
         <is>
@@ -13473,10 +13473,10 @@
         <v>0</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>1400000</v>
+        <v>89000000</v>
       </c>
       <c r="L205" s="1" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M205" s="1" t="inlineStr">
         <is>
@@ -13536,10 +13536,10 @@
         <v>0</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>1400000</v>
+        <v>89000000</v>
       </c>
       <c r="L206" s="1" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M206" s="1" t="inlineStr">
         <is>
@@ -13599,10 +13599,10 @@
         <v>0</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>1400000</v>
+        <v>89000000</v>
       </c>
       <c r="L207" s="1" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M207" s="1" t="inlineStr">
         <is>
@@ -13662,10 +13662,10 @@
         <v>0</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>1900000</v>
+        <v>120000000</v>
       </c>
       <c r="L208" s="1" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="M208" s="1" t="inlineStr">
         <is>
@@ -13725,10 +13725,10 @@
         <v>0</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>2400000</v>
+        <v>150000000</v>
       </c>
       <c r="L209" s="1" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="M209" s="1" t="inlineStr">
         <is>
@@ -13788,10 +13788,10 @@
         <v>0</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>1900000</v>
+        <v>120000000</v>
       </c>
       <c r="L210" s="1" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="M210" s="1" t="inlineStr">
         <is>
@@ -13851,10 +13851,10 @@
         <v>0</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>850000</v>
+        <v>53000000</v>
       </c>
       <c r="L211" s="1" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="M211" s="1" t="inlineStr">
         <is>
@@ -13914,10 +13914,10 @@
         <v>0</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>1100000</v>
+        <v>68000000</v>
       </c>
       <c r="L212" s="1" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="M212" s="1" t="inlineStr">
         <is>
@@ -13977,10 +13977,10 @@
         <v>0</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>1400000</v>
+        <v>89000000</v>
       </c>
       <c r="L213" s="1" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M213" s="1" t="inlineStr">
         <is>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>1400000</v>
+        <v>89000000</v>
       </c>
       <c r="L214" s="1" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M214" s="1" t="inlineStr">
         <is>
@@ -14103,10 +14103,10 @@
         <v>0</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>1900000</v>
+        <v>120000000</v>
       </c>
       <c r="L215" s="1" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="M215" s="1" t="inlineStr">
         <is>
@@ -14166,10 +14166,10 @@
         <v>0</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>3700000</v>
+        <v>230000000</v>
       </c>
       <c r="L216" s="1" t="n">
-        <v>60</v>
+        <v>185</v>
       </c>
       <c r="M216" s="1" t="inlineStr">
         <is>
@@ -14229,10 +14229,10 @@
         <v>0</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>1900000</v>
+        <v>120000000</v>
       </c>
       <c r="L217" s="1" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="M217" s="1" t="inlineStr">
         <is>
@@ -14292,10 +14292,10 @@
         <v>0</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>4800000</v>
+        <v>300000000</v>
       </c>
       <c r="L218" s="1" t="n">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="M218" s="1" t="inlineStr">
         <is>
@@ -14355,10 +14355,10 @@
         <v>0</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>850000</v>
+        <v>53000000</v>
       </c>
       <c r="L219" s="1" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="M219" s="1" t="inlineStr">
         <is>
@@ -14418,10 +14418,10 @@
         <v>0</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>1100000</v>
+        <v>68000000</v>
       </c>
       <c r="L220" s="1" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="M220" s="1" t="inlineStr">
         <is>
@@ -14481,10 +14481,10 @@
         <v>0</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>1400000</v>
+        <v>89000000</v>
       </c>
       <c r="L221" s="1" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M221" s="1" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>0</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>1400000</v>
+        <v>89000000</v>
       </c>
       <c r="L222" s="1" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M222" s="1" t="inlineStr">
         <is>
@@ -14607,10 +14607,10 @@
         <v>0</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>1900000</v>
+        <v>120000000</v>
       </c>
       <c r="L223" s="1" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="M223" s="1" t="inlineStr">
         <is>
@@ -14670,10 +14670,10 @@
         <v>0</v>
       </c>
       <c r="K224" s="1" t="n">
-        <v>1900000</v>
+        <v>120000000</v>
       </c>
       <c r="L224" s="1" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="M224" s="1" t="inlineStr">
         <is>
@@ -14733,10 +14733,10 @@
         <v>0</v>
       </c>
       <c r="K225" s="1" t="n">
-        <v>2400000</v>
+        <v>150000000</v>
       </c>
       <c r="L225" s="1" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="M225" s="1" t="inlineStr">
         <is>
@@ -14796,10 +14796,10 @@
         <v>0</v>
       </c>
       <c r="K226" s="1" t="n">
-        <v>2200000</v>
+        <v>140000000</v>
       </c>
       <c r="L226" s="1" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="M226" s="1" t="inlineStr">
         <is>
@@ -14859,10 +14859,10 @@
         <v>0</v>
       </c>
       <c r="K227" s="1" t="n">
-        <v>2800000</v>
+        <v>180000000</v>
       </c>
       <c r="L227" s="1" t="n">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="M227" s="1" t="inlineStr">
         <is>
@@ -14922,10 +14922,10 @@
         <v>0</v>
       </c>
       <c r="K228" s="1" t="n">
-        <v>3700000</v>
+        <v>230000000</v>
       </c>
       <c r="L228" s="1" t="n">
-        <v>60</v>
+        <v>185</v>
       </c>
       <c r="M228" s="1" t="inlineStr">
         <is>
@@ -14985,10 +14985,10 @@
         <v>0</v>
       </c>
       <c r="K229" s="1" t="n">
-        <v>1400000</v>
+        <v>89000000</v>
       </c>
       <c r="L229" s="1" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M229" s="1" t="inlineStr">
         <is>
@@ -15048,10 +15048,10 @@
         <v>0</v>
       </c>
       <c r="K230" s="1" t="n">
-        <v>2400000</v>
+        <v>150000000</v>
       </c>
       <c r="L230" s="1" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="M230" s="1" t="inlineStr">
         <is>
@@ -15111,10 +15111,10 @@
         <v>0</v>
       </c>
       <c r="K231" s="1" t="n">
-        <v>1900000</v>
+        <v>120000000</v>
       </c>
       <c r="L231" s="1" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="M231" s="1" t="inlineStr">
         <is>
@@ -15243,10 +15243,10 @@
         <v>0</v>
       </c>
       <c r="K233" s="1" t="n">
-        <v>15000000</v>
+        <v>740000000</v>
       </c>
       <c r="L233" s="1" t="n">
-        <v>51</v>
+        <v>215</v>
       </c>
       <c r="M233" s="1" t="inlineStr">
         <is>
@@ -15306,10 +15306,10 @@
         <v>0</v>
       </c>
       <c r="K234" s="1" t="n">
-        <v>19000000</v>
+        <v>960000000</v>
       </c>
       <c r="L234" s="1" t="n">
-        <v>66</v>
+        <v>279</v>
       </c>
       <c r="M234" s="1" t="inlineStr">
         <is>
@@ -15369,10 +15369,10 @@
         <v>0</v>
       </c>
       <c r="K235" s="1" t="n">
-        <v>25000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L235" s="1" t="n">
-        <v>85</v>
+        <v>362</v>
       </c>
       <c r="M235" s="1" t="inlineStr">
         <is>
@@ -15432,10 +15432,10 @@
         <v>0</v>
       </c>
       <c r="K236" s="1" t="n">
-        <v>25000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L236" s="1" t="n">
-        <v>85</v>
+        <v>362</v>
       </c>
       <c r="M236" s="1" t="inlineStr">
         <is>
@@ -15495,10 +15495,10 @@
         <v>0</v>
       </c>
       <c r="K237" s="1" t="n">
-        <v>32000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L237" s="1" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="M237" s="1" t="inlineStr">
         <is>
@@ -15558,10 +15558,10 @@
         <v>0</v>
       </c>
       <c r="K238" s="1" t="n">
-        <v>25000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L238" s="1" t="n">
-        <v>85</v>
+        <v>362</v>
       </c>
       <c r="M238" s="1" t="inlineStr">
         <is>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="K239" s="1" t="n">
-        <v>32000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L239" s="1" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="M239" s="1" t="inlineStr">
         <is>
@@ -15684,10 +15684,10 @@
         <v>0</v>
       </c>
       <c r="K240" s="1" t="n">
-        <v>32000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L240" s="1" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="M240" s="1" t="inlineStr">
         <is>
@@ -15747,10 +15747,10 @@
         <v>0</v>
       </c>
       <c r="K241" s="1" t="n">
-        <v>15000000</v>
+        <v>740000000</v>
       </c>
       <c r="L241" s="1" t="n">
-        <v>51</v>
+        <v>215</v>
       </c>
       <c r="M241" s="1" t="inlineStr">
         <is>
@@ -15810,10 +15810,10 @@
         <v>0</v>
       </c>
       <c r="K242" s="1" t="n">
-        <v>19000000</v>
+        <v>960000000</v>
       </c>
       <c r="L242" s="1" t="n">
-        <v>66</v>
+        <v>279</v>
       </c>
       <c r="M242" s="1" t="inlineStr">
         <is>
@@ -15873,10 +15873,10 @@
         <v>0</v>
       </c>
       <c r="K243" s="1" t="n">
-        <v>25000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L243" s="1" t="n">
-        <v>85</v>
+        <v>362</v>
       </c>
       <c r="M243" s="1" t="inlineStr">
         <is>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="K244" s="1" t="n">
-        <v>25000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L244" s="1" t="n">
-        <v>85</v>
+        <v>362</v>
       </c>
       <c r="M244" s="1" t="inlineStr">
         <is>
@@ -15999,10 +15999,10 @@
         <v>0</v>
       </c>
       <c r="K245" s="1" t="n">
-        <v>25000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L245" s="1" t="n">
-        <v>85</v>
+        <v>362</v>
       </c>
       <c r="M245" s="1" t="inlineStr">
         <is>
@@ -16062,10 +16062,10 @@
         <v>0</v>
       </c>
       <c r="K246" s="1" t="n">
-        <v>32000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L246" s="1" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="M246" s="1" t="inlineStr">
         <is>
@@ -16125,10 +16125,10 @@
         <v>0</v>
       </c>
       <c r="K247" s="1" t="n">
-        <v>41000000</v>
+        <v>2100000000</v>
       </c>
       <c r="L247" s="1" t="n">
-        <v>144</v>
+        <v>612</v>
       </c>
       <c r="M247" s="1" t="inlineStr">
         <is>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="K248" s="1" t="n">
-        <v>32000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L248" s="1" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="M248" s="1" t="inlineStr">
         <is>
@@ -16251,10 +16251,10 @@
         <v>0</v>
       </c>
       <c r="K249" s="1" t="n">
-        <v>15000000</v>
+        <v>740000000</v>
       </c>
       <c r="L249" s="1" t="n">
-        <v>51</v>
+        <v>215</v>
       </c>
       <c r="M249" s="1" t="inlineStr">
         <is>
@@ -16314,10 +16314,10 @@
         <v>0</v>
       </c>
       <c r="K250" s="1" t="n">
-        <v>19000000</v>
+        <v>960000000</v>
       </c>
       <c r="L250" s="1" t="n">
-        <v>66</v>
+        <v>279</v>
       </c>
       <c r="M250" s="1" t="inlineStr">
         <is>
@@ -16377,10 +16377,10 @@
         <v>0</v>
       </c>
       <c r="K251" s="1" t="n">
-        <v>25000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L251" s="1" t="n">
-        <v>85</v>
+        <v>362</v>
       </c>
       <c r="M251" s="1" t="inlineStr">
         <is>
@@ -16440,10 +16440,10 @@
         <v>0</v>
       </c>
       <c r="K252" s="1" t="n">
-        <v>25000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L252" s="1" t="n">
-        <v>85</v>
+        <v>362</v>
       </c>
       <c r="M252" s="1" t="inlineStr">
         <is>
@@ -16503,10 +16503,10 @@
         <v>0</v>
       </c>
       <c r="K253" s="1" t="n">
-        <v>32000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L253" s="1" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="M253" s="1" t="inlineStr">
         <is>
@@ -16566,10 +16566,10 @@
         <v>0</v>
       </c>
       <c r="K254" s="1" t="n">
-        <v>32000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L254" s="1" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="M254" s="1" t="inlineStr">
         <is>
@@ -16629,10 +16629,10 @@
         <v>0</v>
       </c>
       <c r="K255" s="1" t="n">
-        <v>32000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L255" s="1" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="M255" s="1" t="inlineStr">
         <is>
@@ -16692,10 +16692,10 @@
         <v>0</v>
       </c>
       <c r="K256" s="1" t="n">
-        <v>82000000</v>
+        <v>4200000000</v>
       </c>
       <c r="L256" s="1" t="n">
-        <v>287</v>
+        <v>1224</v>
       </c>
       <c r="M256" s="1" t="inlineStr">
         <is>
@@ -16755,10 +16755,10 @@
         <v>0</v>
       </c>
       <c r="K257" s="1" t="n">
-        <v>15000000</v>
+        <v>740000000</v>
       </c>
       <c r="L257" s="1" t="n">
-        <v>51</v>
+        <v>215</v>
       </c>
       <c r="M257" s="1" t="inlineStr">
         <is>
@@ -16818,10 +16818,10 @@
         <v>0</v>
       </c>
       <c r="K258" s="1" t="n">
-        <v>19000000</v>
+        <v>960000000</v>
       </c>
       <c r="L258" s="1" t="n">
-        <v>66</v>
+        <v>279</v>
       </c>
       <c r="M258" s="1" t="inlineStr">
         <is>
@@ -16881,10 +16881,10 @@
         <v>0</v>
       </c>
       <c r="K259" s="1" t="n">
-        <v>25000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L259" s="1" t="n">
-        <v>85</v>
+        <v>362</v>
       </c>
       <c r="M259" s="1" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>0</v>
       </c>
       <c r="K260" s="1" t="n">
-        <v>25000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L260" s="1" t="n">
-        <v>85</v>
+        <v>362</v>
       </c>
       <c r="M260" s="1" t="inlineStr">
         <is>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="K261" s="1" t="n">
-        <v>32000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L261" s="1" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="M261" s="1" t="inlineStr">
         <is>
@@ -17070,10 +17070,10 @@
         <v>0</v>
       </c>
       <c r="K262" s="1" t="n">
-        <v>32000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L262" s="1" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="M262" s="1" t="inlineStr">
         <is>
@@ -17133,10 +17133,10 @@
         <v>0</v>
       </c>
       <c r="K263" s="1" t="n">
-        <v>41000000</v>
+        <v>2100000000</v>
       </c>
       <c r="L263" s="1" t="n">
-        <v>144</v>
+        <v>612</v>
       </c>
       <c r="M263" s="1" t="inlineStr">
         <is>
@@ -17196,10 +17196,10 @@
         <v>0</v>
       </c>
       <c r="K264" s="1" t="n">
-        <v>38000000</v>
+        <v>2000000000</v>
       </c>
       <c r="L264" s="1" t="n">
-        <v>131</v>
+        <v>557</v>
       </c>
       <c r="M264" s="1" t="inlineStr">
         <is>
@@ -17259,10 +17259,10 @@
         <v>0</v>
       </c>
       <c r="K265" s="1" t="n">
-        <v>25000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L265" s="1" t="n">
-        <v>85</v>
+        <v>362</v>
       </c>
       <c r="M265" s="1" t="inlineStr">
         <is>
@@ -17322,10 +17322,10 @@
         <v>0</v>
       </c>
       <c r="K266" s="1" t="n">
-        <v>32000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L266" s="1" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="M266" s="1" t="inlineStr">
         <is>
@@ -17385,10 +17385,10 @@
         <v>0</v>
       </c>
       <c r="K267" s="1" t="n">
-        <v>25000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L267" s="1" t="n">
-        <v>85</v>
+        <v>362</v>
       </c>
       <c r="M267" s="1" t="inlineStr">
         <is>
@@ -17448,10 +17448,10 @@
         <v>0</v>
       </c>
       <c r="K268" s="1" t="n">
-        <v>41000000</v>
+        <v>2100000000</v>
       </c>
       <c r="L268" s="1" t="n">
-        <v>144</v>
+        <v>612</v>
       </c>
       <c r="M268" s="1" t="inlineStr">
         <is>
@@ -17511,10 +17511,10 @@
         <v>0</v>
       </c>
       <c r="K269" s="1" t="n">
-        <v>32000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L269" s="1" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="M269" s="1" t="inlineStr">
         <is>
@@ -17643,10 +17643,10 @@
         <v>0</v>
       </c>
       <c r="K271" s="1" t="n">
-        <v>460000000</v>
+        <v>1400000000</v>
       </c>
       <c r="L271" s="1" t="n">
-        <v>179</v>
+        <v>330</v>
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
@@ -17706,10 +17706,10 @@
         <v>0</v>
       </c>
       <c r="K272" s="1" t="n">
-        <v>600000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L272" s="1" t="n">
-        <v>233</v>
+        <v>429</v>
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
@@ -17769,10 +17769,10 @@
         <v>0</v>
       </c>
       <c r="K273" s="1" t="n">
-        <v>780000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L273" s="1" t="n">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
@@ -17832,10 +17832,10 @@
         <v>0</v>
       </c>
       <c r="K274" s="1" t="n">
-        <v>780000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L274" s="1" t="n">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
@@ -17895,10 +17895,10 @@
         <v>0</v>
       </c>
       <c r="K275" s="1" t="n">
-        <v>1100000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L275" s="1" t="n">
-        <v>393</v>
+        <v>726</v>
       </c>
       <c r="M275" s="1" t="inlineStr">
         <is>
@@ -17958,10 +17958,10 @@
         <v>0</v>
       </c>
       <c r="K276" s="1" t="n">
-        <v>780000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L276" s="1" t="n">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="M276" s="1" t="inlineStr">
         <is>
@@ -18021,10 +18021,10 @@
         <v>0</v>
       </c>
       <c r="K277" s="1" t="n">
-        <v>1100000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L277" s="1" t="n">
-        <v>393</v>
+        <v>726</v>
       </c>
       <c r="M277" s="1" t="inlineStr">
         <is>
@@ -18084,10 +18084,10 @@
         <v>0</v>
       </c>
       <c r="K278" s="1" t="n">
-        <v>1100000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L278" s="1" t="n">
-        <v>393</v>
+        <v>726</v>
       </c>
       <c r="M278" s="1" t="inlineStr">
         <is>
@@ -18147,10 +18147,10 @@
         <v>0</v>
       </c>
       <c r="K279" s="1" t="n">
-        <v>460000000</v>
+        <v>1400000000</v>
       </c>
       <c r="L279" s="1" t="n">
-        <v>179</v>
+        <v>330</v>
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
@@ -18210,10 +18210,10 @@
         <v>0</v>
       </c>
       <c r="K280" s="1" t="n">
-        <v>600000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L280" s="1" t="n">
-        <v>233</v>
+        <v>429</v>
       </c>
       <c r="M280" s="1" t="inlineStr">
         <is>
@@ -18273,10 +18273,10 @@
         <v>0</v>
       </c>
       <c r="K281" s="1" t="n">
-        <v>780000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L281" s="1" t="n">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="M281" s="1" t="inlineStr">
         <is>
@@ -18336,10 +18336,10 @@
         <v>0</v>
       </c>
       <c r="K282" s="1" t="n">
-        <v>780000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L282" s="1" t="n">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="M282" s="1" t="inlineStr">
         <is>
@@ -18399,10 +18399,10 @@
         <v>0</v>
       </c>
       <c r="K283" s="1" t="n">
-        <v>780000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L283" s="1" t="n">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
@@ -18462,10 +18462,10 @@
         <v>0</v>
       </c>
       <c r="K284" s="1" t="n">
-        <v>1100000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L284" s="1" t="n">
-        <v>393</v>
+        <v>726</v>
       </c>
       <c r="M284" s="1" t="inlineStr">
         <is>
@@ -18525,10 +18525,10 @@
         <v>0</v>
       </c>
       <c r="K285" s="1" t="n">
-        <v>1400000000</v>
+        <v>4000000000</v>
       </c>
       <c r="L285" s="1" t="n">
-        <v>511</v>
+        <v>943</v>
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
@@ -18588,10 +18588,10 @@
         <v>0</v>
       </c>
       <c r="K286" s="1" t="n">
-        <v>1100000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L286" s="1" t="n">
-        <v>393</v>
+        <v>726</v>
       </c>
       <c r="M286" s="1" t="inlineStr">
         <is>
@@ -18651,10 +18651,10 @@
         <v>0</v>
       </c>
       <c r="K287" s="1" t="n">
-        <v>460000000</v>
+        <v>1400000000</v>
       </c>
       <c r="L287" s="1" t="n">
-        <v>179</v>
+        <v>330</v>
       </c>
       <c r="M287" s="1" t="inlineStr">
         <is>
@@ -18714,10 +18714,10 @@
         <v>0</v>
       </c>
       <c r="K288" s="1" t="n">
-        <v>600000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L288" s="1" t="n">
-        <v>233</v>
+        <v>429</v>
       </c>
       <c r="M288" s="1" t="inlineStr">
         <is>
@@ -18777,10 +18777,10 @@
         <v>0</v>
       </c>
       <c r="K289" s="1" t="n">
-        <v>780000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L289" s="1" t="n">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="M289" s="1" t="inlineStr">
         <is>
@@ -18840,10 +18840,10 @@
         <v>0</v>
       </c>
       <c r="K290" s="1" t="n">
-        <v>780000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L290" s="1" t="n">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
@@ -18903,10 +18903,10 @@
         <v>0</v>
       </c>
       <c r="K291" s="1" t="n">
-        <v>1100000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L291" s="1" t="n">
-        <v>393</v>
+        <v>726</v>
       </c>
       <c r="M291" s="1" t="inlineStr">
         <is>
@@ -18966,10 +18966,10 @@
         <v>0</v>
       </c>
       <c r="K292" s="1" t="n">
-        <v>1100000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L292" s="1" t="n">
-        <v>393</v>
+        <v>726</v>
       </c>
       <c r="M292" s="1" t="inlineStr">
         <is>
@@ -19029,10 +19029,10 @@
         <v>0</v>
       </c>
       <c r="K293" s="1" t="n">
-        <v>1100000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L293" s="1" t="n">
-        <v>393</v>
+        <v>726</v>
       </c>
       <c r="M293" s="1" t="inlineStr">
         <is>
@@ -19092,10 +19092,10 @@
         <v>0</v>
       </c>
       <c r="K294" s="1" t="n">
-        <v>2700000000</v>
+        <v>8000000000</v>
       </c>
       <c r="L294" s="1" t="n">
-        <v>1021</v>
+        <v>1886</v>
       </c>
       <c r="M294" s="1" t="inlineStr">
         <is>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="K295" s="1" t="n">
-        <v>460000000</v>
+        <v>1400000000</v>
       </c>
       <c r="L295" s="1" t="n">
-        <v>179</v>
+        <v>330</v>
       </c>
       <c r="M295" s="1" t="inlineStr">
         <is>
@@ -19218,10 +19218,10 @@
         <v>0</v>
       </c>
       <c r="K296" s="1" t="n">
-        <v>600000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L296" s="1" t="n">
-        <v>233</v>
+        <v>429</v>
       </c>
       <c r="M296" s="1" t="inlineStr">
         <is>
@@ -19281,10 +19281,10 @@
         <v>0</v>
       </c>
       <c r="K297" s="1" t="n">
-        <v>780000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L297" s="1" t="n">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="M297" s="1" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>0</v>
       </c>
       <c r="K298" s="1" t="n">
-        <v>780000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L298" s="1" t="n">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="M298" s="1" t="inlineStr">
         <is>
@@ -19407,10 +19407,10 @@
         <v>0</v>
       </c>
       <c r="K299" s="1" t="n">
-        <v>1100000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L299" s="1" t="n">
-        <v>393</v>
+        <v>726</v>
       </c>
       <c r="M299" s="1" t="inlineStr">
         <is>
@@ -19470,10 +19470,10 @@
         <v>0</v>
       </c>
       <c r="K300" s="1" t="n">
-        <v>1100000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L300" s="1" t="n">
-        <v>393</v>
+        <v>726</v>
       </c>
       <c r="M300" s="1" t="inlineStr">
         <is>
@@ -19533,10 +19533,10 @@
         <v>0</v>
       </c>
       <c r="K301" s="1" t="n">
-        <v>1400000000</v>
+        <v>4000000000</v>
       </c>
       <c r="L301" s="1" t="n">
-        <v>511</v>
+        <v>943</v>
       </c>
       <c r="M301" s="1" t="inlineStr">
         <is>
@@ -19596,10 +19596,10 @@
         <v>0</v>
       </c>
       <c r="K302" s="1" t="n">
-        <v>1200000000</v>
+        <v>3700000000</v>
       </c>
       <c r="L302" s="1" t="n">
-        <v>465</v>
+        <v>858</v>
       </c>
       <c r="M302" s="1" t="inlineStr">
         <is>
@@ -19659,10 +19659,10 @@
         <v>0</v>
       </c>
       <c r="K303" s="1" t="n">
-        <v>780000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L303" s="1" t="n">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="M303" s="1" t="inlineStr">
         <is>
@@ -19722,10 +19722,10 @@
         <v>0</v>
       </c>
       <c r="K304" s="1" t="n">
-        <v>2100000000</v>
+        <v>6200000000</v>
       </c>
       <c r="L304" s="1" t="n">
-        <v>785</v>
+        <v>1451</v>
       </c>
       <c r="M304" s="1" t="inlineStr">
         <is>
@@ -19785,10 +19785,10 @@
         <v>0</v>
       </c>
       <c r="K305" s="1" t="n">
-        <v>780000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L305" s="1" t="n">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="M305" s="1" t="inlineStr">
         <is>
@@ -19848,10 +19848,10 @@
         <v>0</v>
       </c>
       <c r="K306" s="1" t="n">
-        <v>1400000000</v>
+        <v>4000000000</v>
       </c>
       <c r="L306" s="1" t="n">
-        <v>511</v>
+        <v>943</v>
       </c>
       <c r="M306" s="1" t="inlineStr">
         <is>
@@ -19911,10 +19911,10 @@
         <v>0</v>
       </c>
       <c r="K307" s="1" t="n">
-        <v>1100000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L307" s="1" t="n">
-        <v>393</v>
+        <v>726</v>
       </c>
       <c r="M307" s="1" t="inlineStr">
         <is>
@@ -20043,10 +20043,10 @@
         <v>0</v>
       </c>
       <c r="K309" s="1" t="n">
-        <v>5100000000</v>
+        <v>2600000000</v>
       </c>
       <c r="L309" s="1" t="n">
-        <v>1160</v>
+        <v>550</v>
       </c>
       <c r="M309" s="1" t="inlineStr">
         <is>
@@ -20106,10 +20106,10 @@
         <v>0</v>
       </c>
       <c r="K310" s="1" t="n">
-        <v>6600000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L310" s="1" t="n">
-        <v>1508</v>
+        <v>715</v>
       </c>
       <c r="M310" s="1" t="inlineStr">
         <is>
@@ -20169,10 +20169,10 @@
         <v>0</v>
       </c>
       <c r="K311" s="1" t="n">
-        <v>8500000000</v>
+        <v>4400000000</v>
       </c>
       <c r="L311" s="1" t="n">
-        <v>1961</v>
+        <v>930</v>
       </c>
       <c r="M311" s="1" t="inlineStr">
         <is>
@@ -20232,10 +20232,10 @@
         <v>0</v>
       </c>
       <c r="K312" s="1" t="n">
-        <v>8500000000</v>
+        <v>4400000000</v>
       </c>
       <c r="L312" s="1" t="n">
-        <v>1961</v>
+        <v>930</v>
       </c>
       <c r="M312" s="1" t="inlineStr">
         <is>
@@ -20295,10 +20295,10 @@
         <v>0</v>
       </c>
       <c r="K313" s="1" t="n">
-        <v>12000000000</v>
+        <v>5700000000</v>
       </c>
       <c r="L313" s="1" t="n">
-        <v>2549</v>
+        <v>1209</v>
       </c>
       <c r="M313" s="1" t="inlineStr">
         <is>
@@ -20358,10 +20358,10 @@
         <v>0</v>
       </c>
       <c r="K314" s="1" t="n">
-        <v>8500000000</v>
+        <v>4400000000</v>
       </c>
       <c r="L314" s="1" t="n">
-        <v>1961</v>
+        <v>930</v>
       </c>
       <c r="M314" s="1" t="inlineStr">
         <is>
@@ -20421,10 +20421,10 @@
         <v>0</v>
       </c>
       <c r="K315" s="1" t="n">
-        <v>12000000000</v>
+        <v>5700000000</v>
       </c>
       <c r="L315" s="1" t="n">
-        <v>2549</v>
+        <v>1209</v>
       </c>
       <c r="M315" s="1" t="inlineStr">
         <is>
@@ -20484,10 +20484,10 @@
         <v>0</v>
       </c>
       <c r="K316" s="1" t="n">
-        <v>12000000000</v>
+        <v>5700000000</v>
       </c>
       <c r="L316" s="1" t="n">
-        <v>2549</v>
+        <v>1209</v>
       </c>
       <c r="M316" s="1" t="inlineStr">
         <is>
@@ -20547,10 +20547,10 @@
         <v>0</v>
       </c>
       <c r="K317" s="1" t="n">
-        <v>11000000000</v>
+        <v>5200000000</v>
       </c>
       <c r="L317" s="1" t="n">
-        <v>2320</v>
+        <v>1100</v>
       </c>
       <c r="M317" s="1" t="inlineStr">
         <is>
@@ -20610,10 +20610,10 @@
         <v>0</v>
       </c>
       <c r="K318" s="1" t="n">
-        <v>6600000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L318" s="1" t="n">
-        <v>1508</v>
+        <v>715</v>
       </c>
       <c r="M318" s="1" t="inlineStr">
         <is>
@@ -20673,10 +20673,10 @@
         <v>0</v>
       </c>
       <c r="K319" s="1" t="n">
-        <v>8500000000</v>
+        <v>4400000000</v>
       </c>
       <c r="L319" s="1" t="n">
-        <v>1961</v>
+        <v>930</v>
       </c>
       <c r="M319" s="1" t="inlineStr">
         <is>
@@ -20736,10 +20736,10 @@
         <v>0</v>
       </c>
       <c r="K320" s="1" t="n">
-        <v>8500000000</v>
+        <v>4400000000</v>
       </c>
       <c r="L320" s="1" t="n">
-        <v>1961</v>
+        <v>930</v>
       </c>
       <c r="M320" s="1" t="inlineStr">
         <is>
@@ -20799,10 +20799,10 @@
         <v>0</v>
       </c>
       <c r="K321" s="1" t="n">
-        <v>8500000000</v>
+        <v>4400000000</v>
       </c>
       <c r="L321" s="1" t="n">
-        <v>1961</v>
+        <v>930</v>
       </c>
       <c r="M321" s="1" t="inlineStr">
         <is>
@@ -20862,10 +20862,10 @@
         <v>0</v>
       </c>
       <c r="K322" s="1" t="n">
-        <v>12000000000</v>
+        <v>5700000000</v>
       </c>
       <c r="L322" s="1" t="n">
-        <v>2549</v>
+        <v>1209</v>
       </c>
       <c r="M322" s="1" t="inlineStr">
         <is>
@@ -20925,10 +20925,10 @@
         <v>0</v>
       </c>
       <c r="K323" s="1" t="n">
-        <v>15000000000</v>
+        <v>7400000000</v>
       </c>
       <c r="L323" s="1" t="n">
-        <v>3314</v>
+        <v>1571</v>
       </c>
       <c r="M323" s="1" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
         <v>0</v>
       </c>
       <c r="K324" s="1" t="n">
-        <v>12000000000</v>
+        <v>5700000000</v>
       </c>
       <c r="L324" s="1" t="n">
-        <v>2549</v>
+        <v>1209</v>
       </c>
       <c r="M324" s="1" t="inlineStr">
         <is>
@@ -21051,10 +21051,10 @@
         <v>0</v>
       </c>
       <c r="K325" s="1" t="n">
-        <v>5100000000</v>
+        <v>2600000000</v>
       </c>
       <c r="L325" s="1" t="n">
-        <v>1160</v>
+        <v>550</v>
       </c>
       <c r="M325" s="1" t="inlineStr">
         <is>
@@ -21114,10 +21114,10 @@
         <v>0</v>
       </c>
       <c r="K326" s="1" t="n">
-        <v>6600000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L326" s="1" t="n">
-        <v>1508</v>
+        <v>715</v>
       </c>
       <c r="M326" s="1" t="inlineStr">
         <is>
@@ -21177,10 +21177,10 @@
         <v>0</v>
       </c>
       <c r="K327" s="1" t="n">
-        <v>8500000000</v>
+        <v>4400000000</v>
       </c>
       <c r="L327" s="1" t="n">
-        <v>1961</v>
+        <v>930</v>
       </c>
       <c r="M327" s="1" t="inlineStr">
         <is>
@@ -21240,10 +21240,10 @@
         <v>0</v>
       </c>
       <c r="K328" s="1" t="n">
-        <v>8500000000</v>
+        <v>4400000000</v>
       </c>
       <c r="L328" s="1" t="n">
-        <v>1961</v>
+        <v>930</v>
       </c>
       <c r="M328" s="1" t="inlineStr">
         <is>
@@ -21303,10 +21303,10 @@
         <v>0</v>
       </c>
       <c r="K329" s="1" t="n">
-        <v>12000000000</v>
+        <v>5700000000</v>
       </c>
       <c r="L329" s="1" t="n">
-        <v>2549</v>
+        <v>1209</v>
       </c>
       <c r="M329" s="1" t="inlineStr">
         <is>
@@ -21366,10 +21366,10 @@
         <v>0</v>
       </c>
       <c r="K330" s="1" t="n">
-        <v>12000000000</v>
+        <v>5700000000</v>
       </c>
       <c r="L330" s="1" t="n">
-        <v>2549</v>
+        <v>1209</v>
       </c>
       <c r="M330" s="1" t="inlineStr">
         <is>
@@ -21429,10 +21429,10 @@
         <v>0</v>
       </c>
       <c r="K331" s="1" t="n">
-        <v>12000000000</v>
+        <v>5700000000</v>
       </c>
       <c r="L331" s="1" t="n">
-        <v>2549</v>
+        <v>1209</v>
       </c>
       <c r="M331" s="1" t="inlineStr">
         <is>
@@ -21492,10 +21492,10 @@
         <v>0</v>
       </c>
       <c r="K332" s="1" t="n">
-        <v>15000000000</v>
+        <v>7400000000</v>
       </c>
       <c r="L332" s="1" t="n">
-        <v>3314</v>
+        <v>1571</v>
       </c>
       <c r="M332" s="1" t="inlineStr">
         <is>
@@ -21555,10 +21555,10 @@
         <v>0</v>
       </c>
       <c r="K333" s="1" t="n">
-        <v>5100000000</v>
+        <v>2600000000</v>
       </c>
       <c r="L333" s="1" t="n">
-        <v>1160</v>
+        <v>550</v>
       </c>
       <c r="M333" s="1" t="inlineStr">
         <is>
@@ -21618,10 +21618,10 @@
         <v>0</v>
       </c>
       <c r="K334" s="1" t="n">
-        <v>6600000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L334" s="1" t="n">
-        <v>1508</v>
+        <v>715</v>
       </c>
       <c r="M334" s="1" t="inlineStr">
         <is>
@@ -21681,10 +21681,10 @@
         <v>0</v>
       </c>
       <c r="K335" s="1" t="n">
-        <v>8500000000</v>
+        <v>4400000000</v>
       </c>
       <c r="L335" s="1" t="n">
-        <v>1961</v>
+        <v>930</v>
       </c>
       <c r="M335" s="1" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>0</v>
       </c>
       <c r="K336" s="1" t="n">
-        <v>8500000000</v>
+        <v>4400000000</v>
       </c>
       <c r="L336" s="1" t="n">
-        <v>1961</v>
+        <v>930</v>
       </c>
       <c r="M336" s="1" t="inlineStr">
         <is>
@@ -21807,10 +21807,10 @@
         <v>0</v>
       </c>
       <c r="K337" s="1" t="n">
-        <v>12000000000</v>
+        <v>5700000000</v>
       </c>
       <c r="L337" s="1" t="n">
-        <v>2549</v>
+        <v>1209</v>
       </c>
       <c r="M337" s="1" t="inlineStr">
         <is>
@@ -21870,10 +21870,10 @@
         <v>0</v>
       </c>
       <c r="K338" s="1" t="n">
-        <v>12000000000</v>
+        <v>5700000000</v>
       </c>
       <c r="L338" s="1" t="n">
-        <v>2549</v>
+        <v>1209</v>
       </c>
       <c r="M338" s="1" t="inlineStr">
         <is>
@@ -21933,10 +21933,10 @@
         <v>0</v>
       </c>
       <c r="K339" s="1" t="n">
-        <v>15000000000</v>
+        <v>7400000000</v>
       </c>
       <c r="L339" s="1" t="n">
-        <v>3314</v>
+        <v>1571</v>
       </c>
       <c r="M339" s="1" t="inlineStr">
         <is>
@@ -21996,10 +21996,10 @@
         <v>0</v>
       </c>
       <c r="K340" s="1" t="n">
-        <v>14000000000</v>
+        <v>6700000000</v>
       </c>
       <c r="L340" s="1" t="n">
-        <v>3016</v>
+        <v>1430</v>
       </c>
       <c r="M340" s="1" t="inlineStr">
         <is>
@@ -22059,10 +22059,10 @@
         <v>0</v>
       </c>
       <c r="K341" s="1" t="n">
-        <v>8500000000</v>
+        <v>4400000000</v>
       </c>
       <c r="L341" s="1" t="n">
-        <v>1961</v>
+        <v>930</v>
       </c>
       <c r="M341" s="1" t="inlineStr">
         <is>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="K342" s="1" t="n">
-        <v>23000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="L342" s="1" t="n">
-        <v>5098</v>
+        <v>2417</v>
       </c>
       <c r="M342" s="1" t="inlineStr">
         <is>
@@ -22185,10 +22185,10 @@
         <v>0</v>
       </c>
       <c r="K343" s="1" t="n">
-        <v>8500000000</v>
+        <v>4400000000</v>
       </c>
       <c r="L343" s="1" t="n">
-        <v>1961</v>
+        <v>930</v>
       </c>
       <c r="M343" s="1" t="inlineStr">
         <is>
@@ -22248,10 +22248,10 @@
         <v>0</v>
       </c>
       <c r="K344" s="1" t="n">
-        <v>15000000000</v>
+        <v>7400000000</v>
       </c>
       <c r="L344" s="1" t="n">
-        <v>3314</v>
+        <v>1571</v>
       </c>
       <c r="M344" s="1" t="inlineStr">
         <is>
@@ -22311,10 +22311,10 @@
         <v>0</v>
       </c>
       <c r="K345" s="1" t="n">
-        <v>12000000000</v>
+        <v>5700000000</v>
       </c>
       <c r="L345" s="1" t="n">
-        <v>2549</v>
+        <v>1209</v>
       </c>
       <c r="M345" s="1" t="inlineStr">
         <is>
@@ -22443,10 +22443,10 @@
         <v>0</v>
       </c>
       <c r="K347" s="1" t="n">
-        <v>26000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="L347" s="1" t="n">
-        <v>4374</v>
+        <v>1970</v>
       </c>
       <c r="M347" s="1" t="inlineStr">
         <is>
@@ -22506,10 +22506,10 @@
         <v>0</v>
       </c>
       <c r="K348" s="1" t="n">
-        <v>34000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="L348" s="1" t="n">
-        <v>5686</v>
+        <v>2561</v>
       </c>
       <c r="M348" s="1" t="inlineStr">
         <is>
@@ -22569,10 +22569,10 @@
         <v>0</v>
       </c>
       <c r="K349" s="1" t="n">
-        <v>44000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="L349" s="1" t="n">
-        <v>7391</v>
+        <v>3330</v>
       </c>
       <c r="M349" s="1" t="inlineStr">
         <is>
@@ -22632,10 +22632,10 @@
         <v>0</v>
       </c>
       <c r="K350" s="1" t="n">
-        <v>44000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="L350" s="1" t="n">
-        <v>7391</v>
+        <v>3330</v>
       </c>
       <c r="M350" s="1" t="inlineStr">
         <is>
@@ -22695,10 +22695,10 @@
         <v>0</v>
       </c>
       <c r="K351" s="1" t="n">
-        <v>57000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="L351" s="1" t="n">
-        <v>9609</v>
+        <v>4329</v>
       </c>
       <c r="M351" s="1" t="inlineStr">
         <is>
@@ -22758,10 +22758,10 @@
         <v>0</v>
       </c>
       <c r="K352" s="1" t="n">
-        <v>44000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="L352" s="1" t="n">
-        <v>7391</v>
+        <v>3330</v>
       </c>
       <c r="M352" s="1" t="inlineStr">
         <is>
@@ -22821,10 +22821,10 @@
         <v>0</v>
       </c>
       <c r="K353" s="1" t="n">
-        <v>57000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="L353" s="1" t="n">
-        <v>9609</v>
+        <v>4329</v>
       </c>
       <c r="M353" s="1" t="inlineStr">
         <is>
@@ -22884,10 +22884,10 @@
         <v>0</v>
       </c>
       <c r="K354" s="1" t="n">
-        <v>57000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="L354" s="1" t="n">
-        <v>9609</v>
+        <v>4329</v>
       </c>
       <c r="M354" s="1" t="inlineStr">
         <is>
@@ -22947,10 +22947,10 @@
         <v>0</v>
       </c>
       <c r="K355" s="1" t="n">
-        <v>26000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="L355" s="1" t="n">
-        <v>4374</v>
+        <v>1970</v>
       </c>
       <c r="M355" s="1" t="inlineStr">
         <is>
@@ -23010,10 +23010,10 @@
         <v>0</v>
       </c>
       <c r="K356" s="1" t="n">
-        <v>34000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="L356" s="1" t="n">
-        <v>5686</v>
+        <v>2561</v>
       </c>
       <c r="M356" s="1" t="inlineStr">
         <is>
@@ -23073,10 +23073,10 @@
         <v>0</v>
       </c>
       <c r="K357" s="1" t="n">
-        <v>44000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="L357" s="1" t="n">
-        <v>7391</v>
+        <v>3330</v>
       </c>
       <c r="M357" s="1" t="inlineStr">
         <is>
@@ -23136,10 +23136,10 @@
         <v>0</v>
       </c>
       <c r="K358" s="1" t="n">
-        <v>44000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="L358" s="1" t="n">
-        <v>7391</v>
+        <v>3330</v>
       </c>
       <c r="M358" s="1" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         <v>0</v>
       </c>
       <c r="K359" s="1" t="n">
-        <v>44000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="L359" s="1" t="n">
-        <v>7391</v>
+        <v>3330</v>
       </c>
       <c r="M359" s="1" t="inlineStr">
         <is>
@@ -23262,10 +23262,10 @@
         <v>0</v>
       </c>
       <c r="K360" s="1" t="n">
-        <v>57000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="L360" s="1" t="n">
-        <v>9609</v>
+        <v>4329</v>
       </c>
       <c r="M360" s="1" t="inlineStr">
         <is>
@@ -23325,10 +23325,10 @@
         <v>0</v>
       </c>
       <c r="K361" s="1" t="n">
-        <v>74000000000</v>
+        <v>36000000000</v>
       </c>
       <c r="L361" s="1" t="n">
-        <v>12491</v>
+        <v>5627</v>
       </c>
       <c r="M361" s="1" t="inlineStr">
         <is>
@@ -23388,10 +23388,10 @@
         <v>0</v>
       </c>
       <c r="K362" s="1" t="n">
-        <v>57000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="L362" s="1" t="n">
-        <v>9609</v>
+        <v>4329</v>
       </c>
       <c r="M362" s="1" t="inlineStr">
         <is>
@@ -23451,10 +23451,10 @@
         <v>0</v>
       </c>
       <c r="K363" s="1" t="n">
-        <v>26000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="L363" s="1" t="n">
-        <v>4374</v>
+        <v>1970</v>
       </c>
       <c r="M363" s="1" t="inlineStr">
         <is>
@@ -23514,10 +23514,10 @@
         <v>0</v>
       </c>
       <c r="K364" s="1" t="n">
-        <v>34000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="L364" s="1" t="n">
-        <v>5686</v>
+        <v>2561</v>
       </c>
       <c r="M364" s="1" t="inlineStr">
         <is>
@@ -23577,10 +23577,10 @@
         <v>0</v>
       </c>
       <c r="K365" s="1" t="n">
-        <v>44000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="L365" s="1" t="n">
-        <v>7391</v>
+        <v>3330</v>
       </c>
       <c r="M365" s="1" t="inlineStr">
         <is>
@@ -23640,10 +23640,10 @@
         <v>0</v>
       </c>
       <c r="K366" s="1" t="n">
-        <v>44000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="L366" s="1" t="n">
-        <v>7391</v>
+        <v>3330</v>
       </c>
       <c r="M366" s="1" t="inlineStr">
         <is>
@@ -23703,10 +23703,10 @@
         <v>0</v>
       </c>
       <c r="K367" s="1" t="n">
-        <v>57000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="L367" s="1" t="n">
-        <v>9609</v>
+        <v>4329</v>
       </c>
       <c r="M367" s="1" t="inlineStr">
         <is>
@@ -23766,10 +23766,10 @@
         <v>0</v>
       </c>
       <c r="K368" s="1" t="n">
-        <v>57000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="L368" s="1" t="n">
-        <v>9609</v>
+        <v>4329</v>
       </c>
       <c r="M368" s="1" t="inlineStr">
         <is>
@@ -23829,10 +23829,10 @@
         <v>0</v>
       </c>
       <c r="K369" s="1" t="n">
-        <v>57000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="L369" s="1" t="n">
-        <v>9609</v>
+        <v>4329</v>
       </c>
       <c r="M369" s="1" t="inlineStr">
         <is>
@@ -23892,10 +23892,10 @@
         <v>0</v>
       </c>
       <c r="K370" s="1" t="n">
-        <v>74000000000</v>
+        <v>36000000000</v>
       </c>
       <c r="L370" s="1" t="n">
-        <v>12491</v>
+        <v>5627</v>
       </c>
       <c r="M370" s="1" t="inlineStr">
         <is>
@@ -23955,10 +23955,10 @@
         <v>0</v>
       </c>
       <c r="K371" s="1" t="n">
-        <v>26000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="L371" s="1" t="n">
-        <v>4374</v>
+        <v>1970</v>
       </c>
       <c r="M371" s="1" t="inlineStr">
         <is>
@@ -24018,10 +24018,10 @@
         <v>0</v>
       </c>
       <c r="K372" s="1" t="n">
-        <v>34000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="L372" s="1" t="n">
-        <v>5686</v>
+        <v>2561</v>
       </c>
       <c r="M372" s="1" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="K373" s="1" t="n">
-        <v>44000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="L373" s="1" t="n">
-        <v>7391</v>
+        <v>3330</v>
       </c>
       <c r="M373" s="1" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>0</v>
       </c>
       <c r="K374" s="1" t="n">
-        <v>44000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="L374" s="1" t="n">
-        <v>7391</v>
+        <v>3330</v>
       </c>
       <c r="M374" s="1" t="inlineStr">
         <is>
@@ -24207,10 +24207,10 @@
         <v>0</v>
       </c>
       <c r="K375" s="1" t="n">
-        <v>57000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="L375" s="1" t="n">
-        <v>9609</v>
+        <v>4329</v>
       </c>
       <c r="M375" s="1" t="inlineStr">
         <is>
@@ -24270,10 +24270,10 @@
         <v>0</v>
       </c>
       <c r="K376" s="1" t="n">
-        <v>57000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="L376" s="1" t="n">
-        <v>9609</v>
+        <v>4329</v>
       </c>
       <c r="M376" s="1" t="inlineStr">
         <is>
@@ -24333,10 +24333,10 @@
         <v>0</v>
       </c>
       <c r="K377" s="1" t="n">
-        <v>74000000000</v>
+        <v>36000000000</v>
       </c>
       <c r="L377" s="1" t="n">
-        <v>12491</v>
+        <v>5627</v>
       </c>
       <c r="M377" s="1" t="inlineStr">
         <is>
@@ -24396,10 +24396,10 @@
         <v>0</v>
       </c>
       <c r="K378" s="1" t="n">
-        <v>68000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="L378" s="1" t="n">
-        <v>11371</v>
+        <v>5122</v>
       </c>
       <c r="M378" s="1" t="inlineStr">
         <is>
@@ -24459,10 +24459,10 @@
         <v>0</v>
       </c>
       <c r="K379" s="1" t="n">
-        <v>88000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="L379" s="1" t="n">
-        <v>14782</v>
+        <v>6659</v>
       </c>
       <c r="M379" s="1" t="inlineStr">
         <is>
@@ -24522,10 +24522,10 @@
         <v>0</v>
       </c>
       <c r="K380" s="1" t="n">
-        <v>120000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="L380" s="1" t="n">
-        <v>19217</v>
+        <v>8657</v>
       </c>
       <c r="M380" s="1" t="inlineStr">
         <is>
@@ -24585,10 +24585,10 @@
         <v>0</v>
       </c>
       <c r="K381" s="1" t="n">
-        <v>44000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="L381" s="1" t="n">
-        <v>7391</v>
+        <v>3330</v>
       </c>
       <c r="M381" s="1" t="inlineStr">
         <is>
@@ -24648,10 +24648,10 @@
         <v>0</v>
       </c>
       <c r="K382" s="1" t="n">
-        <v>74000000000</v>
+        <v>36000000000</v>
       </c>
       <c r="L382" s="1" t="n">
-        <v>12491</v>
+        <v>5627</v>
       </c>
       <c r="M382" s="1" t="inlineStr">
         <is>
@@ -24711,10 +24711,10 @@
         <v>0</v>
       </c>
       <c r="K383" s="1" t="n">
-        <v>57000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="L383" s="1" t="n">
-        <v>9609</v>
+        <v>4329</v>
       </c>
       <c r="M383" s="1" t="inlineStr">
         <is>
@@ -24843,10 +24843,10 @@
         <v>0</v>
       </c>
       <c r="K385" s="1" t="n">
-        <v>74000000000</v>
+        <v>36000000000</v>
       </c>
       <c r="L385" s="1" t="n">
-        <v>9894</v>
+        <v>4500</v>
       </c>
       <c r="M385" s="1" t="inlineStr">
         <is>
@@ -24906,10 +24906,10 @@
         <v>0</v>
       </c>
       <c r="K386" s="1" t="n">
-        <v>96000000000</v>
+        <v>46000000000</v>
       </c>
       <c r="L386" s="1" t="n">
-        <v>12862</v>
+        <v>5850</v>
       </c>
       <c r="M386" s="1" t="inlineStr">
         <is>
@@ -24969,10 +24969,10 @@
         <v>0</v>
       </c>
       <c r="K387" s="1" t="n">
-        <v>130000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="L387" s="1" t="n">
-        <v>16720</v>
+        <v>7606</v>
       </c>
       <c r="M387" s="1" t="inlineStr">
         <is>
@@ -25032,10 +25032,10 @@
         <v>0</v>
       </c>
       <c r="K388" s="1" t="n">
-        <v>130000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="L388" s="1" t="n">
-        <v>16720</v>
+        <v>7606</v>
       </c>
       <c r="M388" s="1" t="inlineStr">
         <is>
@@ -25095,10 +25095,10 @@
         <v>0</v>
       </c>
       <c r="K389" s="1" t="n">
-        <v>170000000000</v>
+        <v>78000000000</v>
       </c>
       <c r="L389" s="1" t="n">
-        <v>21736</v>
+        <v>9887</v>
       </c>
       <c r="M389" s="1" t="inlineStr">
         <is>
@@ -25158,10 +25158,10 @@
         <v>0</v>
       </c>
       <c r="K390" s="1" t="n">
-        <v>130000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="L390" s="1" t="n">
-        <v>16720</v>
+        <v>7606</v>
       </c>
       <c r="M390" s="1" t="inlineStr">
         <is>
@@ -25221,10 +25221,10 @@
         <v>0</v>
       </c>
       <c r="K391" s="1" t="n">
-        <v>170000000000</v>
+        <v>78000000000</v>
       </c>
       <c r="L391" s="1" t="n">
-        <v>21736</v>
+        <v>9887</v>
       </c>
       <c r="M391" s="1" t="inlineStr">
         <is>
@@ -25284,10 +25284,10 @@
         <v>0</v>
       </c>
       <c r="K392" s="1" t="n">
-        <v>170000000000</v>
+        <v>78000000000</v>
       </c>
       <c r="L392" s="1" t="n">
-        <v>21736</v>
+        <v>9887</v>
       </c>
       <c r="M392" s="1" t="inlineStr">
         <is>
@@ -25347,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="K393" s="1" t="n">
-        <v>74000000000</v>
+        <v>36000000000</v>
       </c>
       <c r="L393" s="1" t="n">
-        <v>9894</v>
+        <v>4500</v>
       </c>
       <c r="M393" s="1" t="inlineStr">
         <is>
@@ -25410,10 +25410,10 @@
         <v>0</v>
       </c>
       <c r="K394" s="1" t="n">
-        <v>96000000000</v>
+        <v>46000000000</v>
       </c>
       <c r="L394" s="1" t="n">
-        <v>12862</v>
+        <v>5850</v>
       </c>
       <c r="M394" s="1" t="inlineStr">
         <is>
@@ -25473,10 +25473,10 @@
         <v>0</v>
       </c>
       <c r="K395" s="1" t="n">
-        <v>130000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="L395" s="1" t="n">
-        <v>16720</v>
+        <v>7606</v>
       </c>
       <c r="M395" s="1" t="inlineStr">
         <is>
@@ -25536,10 +25536,10 @@
         <v>0</v>
       </c>
       <c r="K396" s="1" t="n">
-        <v>130000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="L396" s="1" t="n">
-        <v>16720</v>
+        <v>7606</v>
       </c>
       <c r="M396" s="1" t="inlineStr">
         <is>
@@ -25599,10 +25599,10 @@
         <v>0</v>
       </c>
       <c r="K397" s="1" t="n">
-        <v>130000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="L397" s="1" t="n">
-        <v>16720</v>
+        <v>7606</v>
       </c>
       <c r="M397" s="1" t="inlineStr">
         <is>
@@ -25662,10 +25662,10 @@
         <v>0</v>
       </c>
       <c r="K398" s="1" t="n">
-        <v>170000000000</v>
+        <v>78000000000</v>
       </c>
       <c r="L398" s="1" t="n">
-        <v>21736</v>
+        <v>9887</v>
       </c>
       <c r="M398" s="1" t="inlineStr">
         <is>
@@ -25725,10 +25725,10 @@
         <v>0</v>
       </c>
       <c r="K399" s="1" t="n">
-        <v>210000000000</v>
+        <v>110000000000</v>
       </c>
       <c r="L399" s="1" t="n">
-        <v>28257</v>
+        <v>12853</v>
       </c>
       <c r="M399" s="1" t="inlineStr">
         <is>
@@ -25788,10 +25788,10 @@
         <v>0</v>
       </c>
       <c r="K400" s="1" t="n">
-        <v>170000000000</v>
+        <v>78000000000</v>
       </c>
       <c r="L400" s="1" t="n">
-        <v>21736</v>
+        <v>9887</v>
       </c>
       <c r="M400" s="1" t="inlineStr">
         <is>
@@ -25851,10 +25851,10 @@
         <v>0</v>
       </c>
       <c r="K401" s="1" t="n">
-        <v>74000000000</v>
+        <v>36000000000</v>
       </c>
       <c r="L401" s="1" t="n">
-        <v>9894</v>
+        <v>4500</v>
       </c>
       <c r="M401" s="1" t="inlineStr">
         <is>
@@ -25914,10 +25914,10 @@
         <v>0</v>
       </c>
       <c r="K402" s="1" t="n">
-        <v>96000000000</v>
+        <v>46000000000</v>
       </c>
       <c r="L402" s="1" t="n">
-        <v>12862</v>
+        <v>5850</v>
       </c>
       <c r="M402" s="1" t="inlineStr">
         <is>
@@ -25977,10 +25977,10 @@
         <v>0</v>
       </c>
       <c r="K403" s="1" t="n">
-        <v>130000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="L403" s="1" t="n">
-        <v>16720</v>
+        <v>7606</v>
       </c>
       <c r="M403" s="1" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>0</v>
       </c>
       <c r="K404" s="1" t="n">
-        <v>130000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="L404" s="1" t="n">
-        <v>16720</v>
+        <v>7606</v>
       </c>
       <c r="M404" s="1" t="inlineStr">
         <is>
@@ -26103,10 +26103,10 @@
         <v>0</v>
       </c>
       <c r="K405" s="1" t="n">
-        <v>170000000000</v>
+        <v>78000000000</v>
       </c>
       <c r="L405" s="1" t="n">
-        <v>21736</v>
+        <v>9887</v>
       </c>
       <c r="M405" s="1" t="inlineStr">
         <is>
@@ -26166,10 +26166,10 @@
         <v>0</v>
       </c>
       <c r="K406" s="1" t="n">
-        <v>170000000000</v>
+        <v>78000000000</v>
       </c>
       <c r="L406" s="1" t="n">
-        <v>21736</v>
+        <v>9887</v>
       </c>
       <c r="M406" s="1" t="inlineStr">
         <is>
@@ -26229,10 +26229,10 @@
         <v>0</v>
       </c>
       <c r="K407" s="1" t="n">
-        <v>170000000000</v>
+        <v>78000000000</v>
       </c>
       <c r="L407" s="1" t="n">
-        <v>21736</v>
+        <v>9887</v>
       </c>
       <c r="M407" s="1" t="inlineStr">
         <is>
@@ -26292,10 +26292,10 @@
         <v>0</v>
       </c>
       <c r="K408" s="1" t="n">
-        <v>210000000000</v>
+        <v>110000000000</v>
       </c>
       <c r="L408" s="1" t="n">
-        <v>28257</v>
+        <v>12853</v>
       </c>
       <c r="M408" s="1" t="inlineStr">
         <is>
@@ -26355,10 +26355,10 @@
         <v>0</v>
       </c>
       <c r="K409" s="1" t="n">
-        <v>74000000000</v>
+        <v>36000000000</v>
       </c>
       <c r="L409" s="1" t="n">
-        <v>9894</v>
+        <v>4500</v>
       </c>
       <c r="M409" s="1" t="inlineStr">
         <is>
@@ -26418,10 +26418,10 @@
         <v>0</v>
       </c>
       <c r="K410" s="1" t="n">
-        <v>96000000000</v>
+        <v>46000000000</v>
       </c>
       <c r="L410" s="1" t="n">
-        <v>12862</v>
+        <v>5850</v>
       </c>
       <c r="M410" s="1" t="inlineStr">
         <is>
@@ -26481,10 +26481,10 @@
         <v>0</v>
       </c>
       <c r="K411" s="1" t="n">
-        <v>130000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="L411" s="1" t="n">
-        <v>16720</v>
+        <v>7606</v>
       </c>
       <c r="M411" s="1" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>0</v>
       </c>
       <c r="K412" s="1" t="n">
-        <v>130000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="L412" s="1" t="n">
-        <v>16720</v>
+        <v>7606</v>
       </c>
       <c r="M412" s="1" t="inlineStr">
         <is>
@@ -26607,10 +26607,10 @@
         <v>0</v>
       </c>
       <c r="K413" s="1" t="n">
-        <v>170000000000</v>
+        <v>78000000000</v>
       </c>
       <c r="L413" s="1" t="n">
-        <v>21736</v>
+        <v>9887</v>
       </c>
       <c r="M413" s="1" t="inlineStr">
         <is>
@@ -26670,10 +26670,10 @@
         <v>0</v>
       </c>
       <c r="K414" s="1" t="n">
-        <v>170000000000</v>
+        <v>78000000000</v>
       </c>
       <c r="L414" s="1" t="n">
-        <v>21736</v>
+        <v>9887</v>
       </c>
       <c r="M414" s="1" t="inlineStr">
         <is>
@@ -26733,10 +26733,10 @@
         <v>0</v>
       </c>
       <c r="K415" s="1" t="n">
-        <v>210000000000</v>
+        <v>110000000000</v>
       </c>
       <c r="L415" s="1" t="n">
-        <v>28257</v>
+        <v>12853</v>
       </c>
       <c r="M415" s="1" t="inlineStr">
         <is>
@@ -26796,10 +26796,10 @@
         <v>0</v>
       </c>
       <c r="K416" s="1" t="n">
-        <v>200000000000</v>
+        <v>92000000000</v>
       </c>
       <c r="L416" s="1" t="n">
-        <v>25723</v>
+        <v>11700</v>
       </c>
       <c r="M416" s="1" t="inlineStr">
         <is>
@@ -26859,10 +26859,10 @@
         <v>0</v>
       </c>
       <c r="K417" s="1" t="n">
-        <v>130000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="L417" s="1" t="n">
-        <v>16720</v>
+        <v>7606</v>
       </c>
       <c r="M417" s="1" t="inlineStr">
         <is>
@@ -26922,10 +26922,10 @@
         <v>0</v>
       </c>
       <c r="K418" s="1" t="n">
-        <v>330000000000</v>
+        <v>160000000000</v>
       </c>
       <c r="L418" s="1" t="n">
-        <v>43472</v>
+        <v>19773</v>
       </c>
       <c r="M418" s="1" t="inlineStr">
         <is>
@@ -26985,10 +26985,10 @@
         <v>0</v>
       </c>
       <c r="K419" s="1" t="n">
-        <v>130000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="L419" s="1" t="n">
-        <v>16720</v>
+        <v>7606</v>
       </c>
       <c r="M419" s="1" t="inlineStr">
         <is>
@@ -27048,10 +27048,10 @@
         <v>0</v>
       </c>
       <c r="K420" s="1" t="n">
-        <v>210000000000</v>
+        <v>110000000000</v>
       </c>
       <c r="L420" s="1" t="n">
-        <v>28257</v>
+        <v>12853</v>
       </c>
       <c r="M420" s="1" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         <v>0</v>
       </c>
       <c r="K421" s="1" t="n">
-        <v>170000000000</v>
+        <v>78000000000</v>
       </c>
       <c r="L421" s="1" t="n">
-        <v>21736</v>
+        <v>9887</v>
       </c>
       <c r="M421" s="1" t="inlineStr">
         <is>
@@ -27243,10 +27243,10 @@
         <v>0</v>
       </c>
       <c r="K423" s="1" t="n">
-        <v>240000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L423" s="1" t="n">
-        <v>24960</v>
+        <v>12710</v>
       </c>
       <c r="M423" s="1" t="inlineStr">
         <is>
@@ -27306,10 +27306,10 @@
         <v>0</v>
       </c>
       <c r="K424" s="1" t="n">
-        <v>310000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L424" s="1" t="n">
-        <v>32448</v>
+        <v>16523</v>
       </c>
       <c r="M424" s="1" t="inlineStr">
         <is>
@@ -27369,10 +27369,10 @@
         <v>0</v>
       </c>
       <c r="K425" s="1" t="n">
-        <v>400000000000</v>
+        <v>220000000000</v>
       </c>
       <c r="L425" s="1" t="n">
-        <v>42183</v>
+        <v>21480</v>
       </c>
       <c r="M425" s="1" t="inlineStr">
         <is>
@@ -27432,10 +27432,10 @@
         <v>0</v>
       </c>
       <c r="K426" s="1" t="n">
-        <v>400000000000</v>
+        <v>220000000000</v>
       </c>
       <c r="L426" s="1" t="n">
-        <v>42183</v>
+        <v>21480</v>
       </c>
       <c r="M426" s="1" t="inlineStr">
         <is>
@@ -27495,10 +27495,10 @@
         <v>0</v>
       </c>
       <c r="K427" s="1" t="n">
-        <v>520000000000</v>
+        <v>280000000000</v>
       </c>
       <c r="L427" s="1" t="n">
-        <v>54838</v>
+        <v>27924</v>
       </c>
       <c r="M427" s="1" t="inlineStr">
         <is>
@@ -27558,10 +27558,10 @@
         <v>0</v>
       </c>
       <c r="K428" s="1" t="n">
-        <v>400000000000</v>
+        <v>220000000000</v>
       </c>
       <c r="L428" s="1" t="n">
-        <v>42183</v>
+        <v>21480</v>
       </c>
       <c r="M428" s="1" t="inlineStr">
         <is>
@@ -27621,10 +27621,10 @@
         <v>0</v>
       </c>
       <c r="K429" s="1" t="n">
-        <v>520000000000</v>
+        <v>280000000000</v>
       </c>
       <c r="L429" s="1" t="n">
-        <v>54838</v>
+        <v>27924</v>
       </c>
       <c r="M429" s="1" t="inlineStr">
         <is>
@@ -27684,10 +27684,10 @@
         <v>0</v>
       </c>
       <c r="K430" s="1" t="n">
-        <v>520000000000</v>
+        <v>280000000000</v>
       </c>
       <c r="L430" s="1" t="n">
-        <v>54838</v>
+        <v>27924</v>
       </c>
       <c r="M430" s="1" t="inlineStr">
         <is>
@@ -27747,10 +27747,10 @@
         <v>0</v>
       </c>
       <c r="K431" s="1" t="n">
-        <v>240000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L431" s="1" t="n">
-        <v>24960</v>
+        <v>12710</v>
       </c>
       <c r="M431" s="1" t="inlineStr">
         <is>
@@ -27810,10 +27810,10 @@
         <v>0</v>
       </c>
       <c r="K432" s="1" t="n">
-        <v>310000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L432" s="1" t="n">
-        <v>32448</v>
+        <v>16523</v>
       </c>
       <c r="M432" s="1" t="inlineStr">
         <is>
@@ -27873,10 +27873,10 @@
         <v>0</v>
       </c>
       <c r="K433" s="1" t="n">
-        <v>400000000000</v>
+        <v>220000000000</v>
       </c>
       <c r="L433" s="1" t="n">
-        <v>42183</v>
+        <v>21480</v>
       </c>
       <c r="M433" s="1" t="inlineStr">
         <is>
@@ -27936,10 +27936,10 @@
         <v>0</v>
       </c>
       <c r="K434" s="1" t="n">
-        <v>790000000000</v>
+        <v>430000000000</v>
       </c>
       <c r="L434" s="1" t="n">
-        <v>84365</v>
+        <v>42960</v>
       </c>
       <c r="M434" s="1" t="inlineStr">
         <is>
@@ -27999,10 +27999,10 @@
         <v>0</v>
       </c>
       <c r="K435" s="1" t="n">
-        <v>400000000000</v>
+        <v>220000000000</v>
       </c>
       <c r="L435" s="1" t="n">
-        <v>42183</v>
+        <v>21480</v>
       </c>
       <c r="M435" s="1" t="inlineStr">
         <is>
@@ -28062,10 +28062,10 @@
         <v>0</v>
       </c>
       <c r="K436" s="1" t="n">
-        <v>1100000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L436" s="1" t="n">
-        <v>109675</v>
+        <v>55848</v>
       </c>
       <c r="M436" s="1" t="inlineStr">
         <is>
@@ -28125,10 +28125,10 @@
         <v>0</v>
       </c>
       <c r="K437" s="1" t="n">
-        <v>670000000000</v>
+        <v>360000000000</v>
       </c>
       <c r="L437" s="1" t="n">
-        <v>71289</v>
+        <v>36302</v>
       </c>
       <c r="M437" s="1" t="inlineStr">
         <is>
@@ -28188,10 +28188,10 @@
         <v>0</v>
       </c>
       <c r="K438" s="1" t="n">
-        <v>1100000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L438" s="1" t="n">
-        <v>109675</v>
+        <v>55848</v>
       </c>
       <c r="M438" s="1" t="inlineStr">
         <is>
@@ -28251,10 +28251,10 @@
         <v>0</v>
       </c>
       <c r="K439" s="1" t="n">
-        <v>240000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L439" s="1" t="n">
-        <v>24960</v>
+        <v>12710</v>
       </c>
       <c r="M439" s="1" t="inlineStr">
         <is>
@@ -28314,10 +28314,10 @@
         <v>0</v>
       </c>
       <c r="K440" s="1" t="n">
-        <v>310000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L440" s="1" t="n">
-        <v>32448</v>
+        <v>16523</v>
       </c>
       <c r="M440" s="1" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>0</v>
       </c>
       <c r="K441" s="1" t="n">
-        <v>400000000000</v>
+        <v>220000000000</v>
       </c>
       <c r="L441" s="1" t="n">
-        <v>42183</v>
+        <v>21480</v>
       </c>
       <c r="M441" s="1" t="inlineStr">
         <is>
@@ -28440,10 +28440,10 @@
         <v>0</v>
       </c>
       <c r="K442" s="1" t="n">
-        <v>400000000000</v>
+        <v>220000000000</v>
       </c>
       <c r="L442" s="1" t="n">
-        <v>42183</v>
+        <v>21480</v>
       </c>
       <c r="M442" s="1" t="inlineStr">
         <is>
@@ -28503,10 +28503,10 @@
         <v>0</v>
       </c>
       <c r="K443" s="1" t="n">
-        <v>520000000000</v>
+        <v>280000000000</v>
       </c>
       <c r="L443" s="1" t="n">
-        <v>54838</v>
+        <v>27924</v>
       </c>
       <c r="M443" s="1" t="inlineStr">
         <is>
@@ -28566,10 +28566,10 @@
         <v>0</v>
       </c>
       <c r="K444" s="1" t="n">
-        <v>520000000000</v>
+        <v>280000000000</v>
       </c>
       <c r="L444" s="1" t="n">
-        <v>54838</v>
+        <v>27924</v>
       </c>
       <c r="M444" s="1" t="inlineStr">
         <is>
@@ -28629,10 +28629,10 @@
         <v>0</v>
       </c>
       <c r="K445" s="1" t="n">
-        <v>520000000000</v>
+        <v>280000000000</v>
       </c>
       <c r="L445" s="1" t="n">
-        <v>54838</v>
+        <v>27924</v>
       </c>
       <c r="M445" s="1" t="inlineStr">
         <is>
@@ -28692,10 +28692,10 @@
         <v>0</v>
       </c>
       <c r="K446" s="1" t="n">
-        <v>670000000000</v>
+        <v>360000000000</v>
       </c>
       <c r="L446" s="1" t="n">
-        <v>71289</v>
+        <v>36302</v>
       </c>
       <c r="M446" s="1" t="inlineStr">
         <is>
@@ -28755,10 +28755,10 @@
         <v>0</v>
       </c>
       <c r="K447" s="1" t="n">
-        <v>240000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L447" s="1" t="n">
-        <v>24960</v>
+        <v>12710</v>
       </c>
       <c r="M447" s="1" t="inlineStr">
         <is>
@@ -28818,10 +28818,10 @@
         <v>0</v>
       </c>
       <c r="K448" s="1" t="n">
-        <v>310000000000</v>
+        <v>170000000000</v>
       </c>
       <c r="L448" s="1" t="n">
-        <v>32448</v>
+        <v>16523</v>
       </c>
       <c r="M448" s="1" t="inlineStr">
         <is>
@@ -28881,10 +28881,10 @@
         <v>0</v>
       </c>
       <c r="K449" s="1" t="n">
-        <v>400000000000</v>
+        <v>220000000000</v>
       </c>
       <c r="L449" s="1" t="n">
-        <v>42183</v>
+        <v>21480</v>
       </c>
       <c r="M449" s="1" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>0</v>
       </c>
       <c r="K450" s="1" t="n">
-        <v>400000000000</v>
+        <v>220000000000</v>
       </c>
       <c r="L450" s="1" t="n">
-        <v>42183</v>
+        <v>21480</v>
       </c>
       <c r="M450" s="1" t="inlineStr">
         <is>
@@ -29007,10 +29007,10 @@
         <v>0</v>
       </c>
       <c r="K451" s="1" t="n">
-        <v>520000000000</v>
+        <v>280000000000</v>
       </c>
       <c r="L451" s="1" t="n">
-        <v>54838</v>
+        <v>27924</v>
       </c>
       <c r="M451" s="1" t="inlineStr">
         <is>
@@ -29070,10 +29070,10 @@
         <v>0</v>
       </c>
       <c r="K452" s="1" t="n">
-        <v>520000000000</v>
+        <v>280000000000</v>
       </c>
       <c r="L452" s="1" t="n">
-        <v>54838</v>
+        <v>27924</v>
       </c>
       <c r="M452" s="1" t="inlineStr">
         <is>
@@ -29133,10 +29133,10 @@
         <v>0</v>
       </c>
       <c r="K453" s="1" t="n">
-        <v>670000000000</v>
+        <v>360000000000</v>
       </c>
       <c r="L453" s="1" t="n">
-        <v>71289</v>
+        <v>36302</v>
       </c>
       <c r="M453" s="1" t="inlineStr">
         <is>
@@ -29196,10 +29196,10 @@
         <v>0</v>
       </c>
       <c r="K454" s="1" t="n">
-        <v>610000000000</v>
+        <v>330000000000</v>
       </c>
       <c r="L454" s="1" t="n">
-        <v>64896</v>
+        <v>33046</v>
       </c>
       <c r="M454" s="1" t="inlineStr">
         <is>
@@ -29259,10 +29259,10 @@
         <v>0</v>
       </c>
       <c r="K455" s="1" t="n">
-        <v>400000000000</v>
+        <v>220000000000</v>
       </c>
       <c r="L455" s="1" t="n">
-        <v>42183</v>
+        <v>21480</v>
       </c>
       <c r="M455" s="1" t="inlineStr">
         <is>
@@ -29322,10 +29322,10 @@
         <v>0</v>
       </c>
       <c r="K456" s="1" t="n">
-        <v>1100000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L456" s="1" t="n">
-        <v>109675</v>
+        <v>55848</v>
       </c>
       <c r="M456" s="1" t="inlineStr">
         <is>
@@ -29385,10 +29385,10 @@
         <v>0</v>
       </c>
       <c r="K457" s="1" t="n">
-        <v>400000000000</v>
+        <v>220000000000</v>
       </c>
       <c r="L457" s="1" t="n">
-        <v>42183</v>
+        <v>21480</v>
       </c>
       <c r="M457" s="1" t="inlineStr">
         <is>
@@ -29448,10 +29448,10 @@
         <v>0</v>
       </c>
       <c r="K458" s="1" t="n">
-        <v>670000000000</v>
+        <v>360000000000</v>
       </c>
       <c r="L458" s="1" t="n">
-        <v>71289</v>
+        <v>36302</v>
       </c>
       <c r="M458" s="1" t="inlineStr">
         <is>
@@ -29511,10 +29511,10 @@
         <v>0</v>
       </c>
       <c r="K459" s="1" t="n">
-        <v>1100000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L459" s="1" t="n">
-        <v>109675</v>
+        <v>55848</v>
       </c>
       <c r="M459" s="1" t="inlineStr">
         <is>
@@ -29643,10 +29643,10 @@
         <v>0</v>
       </c>
       <c r="K461" s="1" t="n">
-        <v>490000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="L461" s="1" t="n">
-        <v>43987</v>
+        <v>19040</v>
       </c>
       <c r="M461" s="1" t="inlineStr">
         <is>
@@ -29706,10 +29706,10 @@
         <v>0</v>
       </c>
       <c r="K462" s="1" t="n">
-        <v>640000000000</v>
+        <v>290000000000</v>
       </c>
       <c r="L462" s="1" t="n">
-        <v>57183</v>
+        <v>24752</v>
       </c>
       <c r="M462" s="1" t="inlineStr">
         <is>
@@ -29769,10 +29769,10 @@
         <v>0</v>
       </c>
       <c r="K463" s="1" t="n">
-        <v>830000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L463" s="1" t="n">
-        <v>74338</v>
+        <v>32178</v>
       </c>
       <c r="M463" s="1" t="inlineStr">
         <is>
@@ -29832,10 +29832,10 @@
         <v>0</v>
       </c>
       <c r="K464" s="1" t="n">
-        <v>830000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L464" s="1" t="n">
-        <v>74338</v>
+        <v>32178</v>
       </c>
       <c r="M464" s="1" t="inlineStr">
         <is>
@@ -29895,10 +29895,10 @@
         <v>0</v>
       </c>
       <c r="K465" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L465" s="1" t="n">
-        <v>96639</v>
+        <v>41831</v>
       </c>
       <c r="M465" s="1" t="inlineStr">
         <is>
@@ -29958,10 +29958,10 @@
         <v>0</v>
       </c>
       <c r="K466" s="1" t="n">
-        <v>830000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L466" s="1" t="n">
-        <v>74338</v>
+        <v>32178</v>
       </c>
       <c r="M466" s="1" t="inlineStr">
         <is>
@@ -30021,10 +30021,10 @@
         <v>0</v>
       </c>
       <c r="K467" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L467" s="1" t="n">
-        <v>96639</v>
+        <v>41831</v>
       </c>
       <c r="M467" s="1" t="inlineStr">
         <is>
@@ -30084,10 +30084,10 @@
         <v>0</v>
       </c>
       <c r="K468" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L468" s="1" t="n">
-        <v>96639</v>
+        <v>41831</v>
       </c>
       <c r="M468" s="1" t="inlineStr">
         <is>
@@ -30147,10 +30147,10 @@
         <v>0</v>
       </c>
       <c r="K469" s="1" t="n">
-        <v>490000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="L469" s="1" t="n">
-        <v>43987</v>
+        <v>19040</v>
       </c>
       <c r="M469" s="1" t="inlineStr">
         <is>
@@ -30210,10 +30210,10 @@
         <v>0</v>
       </c>
       <c r="K470" s="1" t="n">
-        <v>640000000000</v>
+        <v>290000000000</v>
       </c>
       <c r="L470" s="1" t="n">
-        <v>57183</v>
+        <v>24752</v>
       </c>
       <c r="M470" s="1" t="inlineStr">
         <is>
@@ -30273,10 +30273,10 @@
         <v>0</v>
       </c>
       <c r="K471" s="1" t="n">
-        <v>830000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L471" s="1" t="n">
-        <v>74338</v>
+        <v>32178</v>
       </c>
       <c r="M471" s="1" t="inlineStr">
         <is>
@@ -30336,10 +30336,10 @@
         <v>0</v>
       </c>
       <c r="K472" s="1" t="n">
-        <v>830000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L472" s="1" t="n">
-        <v>74338</v>
+        <v>32178</v>
       </c>
       <c r="M472" s="1" t="inlineStr">
         <is>
@@ -30399,10 +30399,10 @@
         <v>0</v>
       </c>
       <c r="K473" s="1" t="n">
-        <v>830000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L473" s="1" t="n">
-        <v>74338</v>
+        <v>32178</v>
       </c>
       <c r="M473" s="1" t="inlineStr">
         <is>
@@ -30462,10 +30462,10 @@
         <v>0</v>
       </c>
       <c r="K474" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L474" s="1" t="n">
-        <v>96639</v>
+        <v>41831</v>
       </c>
       <c r="M474" s="1" t="inlineStr">
         <is>
@@ -30525,10 +30525,10 @@
         <v>0</v>
       </c>
       <c r="K475" s="1" t="n">
-        <v>1400000000000</v>
+        <v>640000000000</v>
       </c>
       <c r="L475" s="1" t="n">
-        <v>125631</v>
+        <v>54381</v>
       </c>
       <c r="M475" s="1" t="inlineStr">
         <is>
@@ -30588,10 +30588,10 @@
         <v>0</v>
       </c>
       <c r="K476" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L476" s="1" t="n">
-        <v>96639</v>
+        <v>41831</v>
       </c>
       <c r="M476" s="1" t="inlineStr">
         <is>
@@ -30651,10 +30651,10 @@
         <v>0</v>
       </c>
       <c r="K477" s="1" t="n">
-        <v>490000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="L477" s="1" t="n">
-        <v>43987</v>
+        <v>19040</v>
       </c>
       <c r="M477" s="1" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>0</v>
       </c>
       <c r="K478" s="1" t="n">
-        <v>640000000000</v>
+        <v>290000000000</v>
       </c>
       <c r="L478" s="1" t="n">
-        <v>57183</v>
+        <v>24752</v>
       </c>
       <c r="M478" s="1" t="inlineStr">
         <is>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="K479" s="1" t="n">
-        <v>830000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L479" s="1" t="n">
-        <v>74338</v>
+        <v>32178</v>
       </c>
       <c r="M479" s="1" t="inlineStr">
         <is>
@@ -30840,10 +30840,10 @@
         <v>0</v>
       </c>
       <c r="K480" s="1" t="n">
-        <v>830000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L480" s="1" t="n">
-        <v>74338</v>
+        <v>32178</v>
       </c>
       <c r="M480" s="1" t="inlineStr">
         <is>
@@ -30903,10 +30903,10 @@
         <v>0</v>
       </c>
       <c r="K481" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L481" s="1" t="n">
-        <v>96639</v>
+        <v>41831</v>
       </c>
       <c r="M481" s="1" t="inlineStr">
         <is>
@@ -30966,10 +30966,10 @@
         <v>0</v>
       </c>
       <c r="K482" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L482" s="1" t="n">
-        <v>96639</v>
+        <v>41831</v>
       </c>
       <c r="M482" s="1" t="inlineStr">
         <is>
@@ -31029,10 +31029,10 @@
         <v>0</v>
       </c>
       <c r="K483" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L483" s="1" t="n">
-        <v>96639</v>
+        <v>41831</v>
       </c>
       <c r="M483" s="1" t="inlineStr">
         <is>
@@ -31092,10 +31092,10 @@
         <v>0</v>
       </c>
       <c r="K484" s="1" t="n">
-        <v>1400000000000</v>
+        <v>640000000000</v>
       </c>
       <c r="L484" s="1" t="n">
-        <v>125631</v>
+        <v>54381</v>
       </c>
       <c r="M484" s="1" t="inlineStr">
         <is>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="K485" s="1" t="n">
-        <v>490000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="L485" s="1" t="n">
-        <v>43987</v>
+        <v>19040</v>
       </c>
       <c r="M485" s="1" t="inlineStr">
         <is>
@@ -31218,10 +31218,10 @@
         <v>0</v>
       </c>
       <c r="K486" s="1" t="n">
-        <v>640000000000</v>
+        <v>290000000000</v>
       </c>
       <c r="L486" s="1" t="n">
-        <v>57183</v>
+        <v>24752</v>
       </c>
       <c r="M486" s="1" t="inlineStr">
         <is>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="K487" s="1" t="n">
-        <v>830000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L487" s="1" t="n">
-        <v>74338</v>
+        <v>32178</v>
       </c>
       <c r="M487" s="1" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>0</v>
       </c>
       <c r="K488" s="1" t="n">
-        <v>830000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L488" s="1" t="n">
-        <v>74338</v>
+        <v>32178</v>
       </c>
       <c r="M488" s="1" t="inlineStr">
         <is>
@@ -31407,10 +31407,10 @@
         <v>0</v>
       </c>
       <c r="K489" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L489" s="1" t="n">
-        <v>96639</v>
+        <v>41831</v>
       </c>
       <c r="M489" s="1" t="inlineStr">
         <is>
@@ -31470,10 +31470,10 @@
         <v>0</v>
       </c>
       <c r="K490" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L490" s="1" t="n">
-        <v>96639</v>
+        <v>41831</v>
       </c>
       <c r="M490" s="1" t="inlineStr">
         <is>
@@ -31533,10 +31533,10 @@
         <v>0</v>
       </c>
       <c r="K491" s="1" t="n">
-        <v>1400000000000</v>
+        <v>640000000000</v>
       </c>
       <c r="L491" s="1" t="n">
-        <v>125631</v>
+        <v>54381</v>
       </c>
       <c r="M491" s="1" t="inlineStr">
         <is>
@@ -31596,10 +31596,10 @@
         <v>0</v>
       </c>
       <c r="K492" s="1" t="n">
-        <v>1300000000000</v>
+        <v>580000000000</v>
       </c>
       <c r="L492" s="1" t="n">
-        <v>114366</v>
+        <v>49504</v>
       </c>
       <c r="M492" s="1" t="inlineStr">
         <is>
@@ -31659,10 +31659,10 @@
         <v>0</v>
       </c>
       <c r="K493" s="1" t="n">
-        <v>830000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L493" s="1" t="n">
-        <v>74338</v>
+        <v>32178</v>
       </c>
       <c r="M493" s="1" t="inlineStr">
         <is>
@@ -31722,10 +31722,10 @@
         <v>0</v>
       </c>
       <c r="K494" s="1" t="n">
-        <v>2200000000000</v>
+        <v>980000000000</v>
       </c>
       <c r="L494" s="1" t="n">
-        <v>193278</v>
+        <v>83662</v>
       </c>
       <c r="M494" s="1" t="inlineStr">
         <is>
@@ -31785,10 +31785,10 @@
         <v>0</v>
       </c>
       <c r="K495" s="1" t="n">
-        <v>830000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L495" s="1" t="n">
-        <v>74338</v>
+        <v>32178</v>
       </c>
       <c r="M495" s="1" t="inlineStr">
         <is>
@@ -31848,10 +31848,10 @@
         <v>0</v>
       </c>
       <c r="K496" s="1" t="n">
-        <v>1400000000000</v>
+        <v>640000000000</v>
       </c>
       <c r="L496" s="1" t="n">
-        <v>125631</v>
+        <v>54381</v>
       </c>
       <c r="M496" s="1" t="inlineStr">
         <is>
@@ -31911,10 +31911,10 @@
         <v>0</v>
       </c>
       <c r="K497" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L497" s="1" t="n">
-        <v>96639</v>
+        <v>41831</v>
       </c>
       <c r="M497" s="1" t="inlineStr">
         <is>
@@ -32043,10 +32043,10 @@
         <v>0</v>
       </c>
       <c r="K499" s="1" t="n">
-        <v>820000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L499" s="1" t="n">
-        <v>65934</v>
+        <v>28550</v>
       </c>
       <c r="M499" s="1" t="inlineStr">
         <is>
@@ -32106,10 +32106,10 @@
         <v>0</v>
       </c>
       <c r="K500" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L500" s="1" t="n">
-        <v>85714</v>
+        <v>37115</v>
       </c>
       <c r="M500" s="1" t="inlineStr">
         <is>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="K501" s="1" t="n">
-        <v>1400000000000</v>
+        <v>630000000000</v>
       </c>
       <c r="L501" s="1" t="n">
-        <v>111428</v>
+        <v>48250</v>
       </c>
       <c r="M501" s="1" t="inlineStr">
         <is>
@@ -32232,10 +32232,10 @@
         <v>0</v>
       </c>
       <c r="K502" s="1" t="n">
-        <v>1400000000000</v>
+        <v>630000000000</v>
       </c>
       <c r="L502" s="1" t="n">
-        <v>111428</v>
+        <v>48250</v>
       </c>
       <c r="M502" s="1" t="inlineStr">
         <is>
@@ -32295,10 +32295,10 @@
         <v>0</v>
       </c>
       <c r="K503" s="1" t="n">
-        <v>1800000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L503" s="1" t="n">
-        <v>144856</v>
+        <v>62725</v>
       </c>
       <c r="M503" s="1" t="inlineStr">
         <is>
@@ -32358,10 +32358,10 @@
         <v>0</v>
       </c>
       <c r="K504" s="1" t="n">
-        <v>1400000000000</v>
+        <v>630000000000</v>
       </c>
       <c r="L504" s="1" t="n">
-        <v>111428</v>
+        <v>48250</v>
       </c>
       <c r="M504" s="1" t="inlineStr">
         <is>
@@ -32421,10 +32421,10 @@
         <v>0</v>
       </c>
       <c r="K505" s="1" t="n">
-        <v>1800000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L505" s="1" t="n">
-        <v>144856</v>
+        <v>62725</v>
       </c>
       <c r="M505" s="1" t="inlineStr">
         <is>
@@ -32484,10 +32484,10 @@
         <v>0</v>
       </c>
       <c r="K506" s="1" t="n">
-        <v>1800000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L506" s="1" t="n">
-        <v>144856</v>
+        <v>62725</v>
       </c>
       <c r="M506" s="1" t="inlineStr">
         <is>
@@ -32547,10 +32547,10 @@
         <v>0</v>
       </c>
       <c r="K507" s="1" t="n">
-        <v>820000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L507" s="1" t="n">
-        <v>65934</v>
+        <v>28550</v>
       </c>
       <c r="M507" s="1" t="inlineStr">
         <is>
@@ -32610,10 +32610,10 @@
         <v>0</v>
       </c>
       <c r="K508" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L508" s="1" t="n">
-        <v>85714</v>
+        <v>37115</v>
       </c>
       <c r="M508" s="1" t="inlineStr">
         <is>
@@ -32673,10 +32673,10 @@
         <v>0</v>
       </c>
       <c r="K509" s="1" t="n">
-        <v>1400000000000</v>
+        <v>630000000000</v>
       </c>
       <c r="L509" s="1" t="n">
-        <v>111428</v>
+        <v>48250</v>
       </c>
       <c r="M509" s="1" t="inlineStr">
         <is>
@@ -32736,10 +32736,10 @@
         <v>0</v>
       </c>
       <c r="K510" s="1" t="n">
-        <v>1400000000000</v>
+        <v>630000000000</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>111428</v>
+        <v>48250</v>
       </c>
       <c r="M510" s="1" t="inlineStr">
         <is>
@@ -32799,10 +32799,10 @@
         <v>0</v>
       </c>
       <c r="K511" s="1" t="n">
-        <v>1400000000000</v>
+        <v>630000000000</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>111428</v>
+        <v>48250</v>
       </c>
       <c r="M511" s="1" t="inlineStr">
         <is>
@@ -32862,10 +32862,10 @@
         <v>0</v>
       </c>
       <c r="K512" s="1" t="n">
-        <v>1800000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>144856</v>
+        <v>62725</v>
       </c>
       <c r="M512" s="1" t="inlineStr">
         <is>
@@ -32925,10 +32925,10 @@
         <v>0</v>
       </c>
       <c r="K513" s="1" t="n">
-        <v>2400000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>188313</v>
+        <v>81542</v>
       </c>
       <c r="M513" s="1" t="inlineStr">
         <is>
@@ -32988,10 +32988,10 @@
         <v>0</v>
       </c>
       <c r="K514" s="1" t="n">
-        <v>1800000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>144856</v>
+        <v>62725</v>
       </c>
       <c r="M514" s="1" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>0</v>
       </c>
       <c r="K515" s="1" t="n">
-        <v>820000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L515" s="1" t="n">
-        <v>65934</v>
+        <v>28550</v>
       </c>
       <c r="M515" s="1" t="inlineStr">
         <is>
@@ -33114,10 +33114,10 @@
         <v>0</v>
       </c>
       <c r="K516" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L516" s="1" t="n">
-        <v>85714</v>
+        <v>37115</v>
       </c>
       <c r="M516" s="1" t="inlineStr">
         <is>
@@ -33177,10 +33177,10 @@
         <v>0</v>
       </c>
       <c r="K517" s="1" t="n">
-        <v>1400000000000</v>
+        <v>630000000000</v>
       </c>
       <c r="L517" s="1" t="n">
-        <v>111428</v>
+        <v>48250</v>
       </c>
       <c r="M517" s="1" t="inlineStr">
         <is>
@@ -33240,10 +33240,10 @@
         <v>0</v>
       </c>
       <c r="K518" s="1" t="n">
-        <v>1400000000000</v>
+        <v>630000000000</v>
       </c>
       <c r="L518" s="1" t="n">
-        <v>111428</v>
+        <v>48250</v>
       </c>
       <c r="M518" s="1" t="inlineStr">
         <is>
@@ -33303,10 +33303,10 @@
         <v>0</v>
       </c>
       <c r="K519" s="1" t="n">
-        <v>1800000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L519" s="1" t="n">
-        <v>144856</v>
+        <v>62725</v>
       </c>
       <c r="M519" s="1" t="inlineStr">
         <is>
@@ -33366,10 +33366,10 @@
         <v>0</v>
       </c>
       <c r="K520" s="1" t="n">
-        <v>1800000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L520" s="1" t="n">
-        <v>144856</v>
+        <v>62725</v>
       </c>
       <c r="M520" s="1" t="inlineStr">
         <is>
@@ -33429,10 +33429,10 @@
         <v>0</v>
       </c>
       <c r="K521" s="1" t="n">
-        <v>1800000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L521" s="1" t="n">
-        <v>144856</v>
+        <v>62725</v>
       </c>
       <c r="M521" s="1" t="inlineStr">
         <is>
@@ -33492,10 +33492,10 @@
         <v>0</v>
       </c>
       <c r="K522" s="1" t="n">
-        <v>2400000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L522" s="1" t="n">
-        <v>188313</v>
+        <v>81542</v>
       </c>
       <c r="M522" s="1" t="inlineStr">
         <is>
@@ -33555,10 +33555,10 @@
         <v>0</v>
       </c>
       <c r="K523" s="1" t="n">
-        <v>820000000000</v>
+        <v>380000000000</v>
       </c>
       <c r="L523" s="1" t="n">
-        <v>65934</v>
+        <v>28550</v>
       </c>
       <c r="M523" s="1" t="inlineStr">
         <is>
@@ -33618,10 +33618,10 @@
         <v>0</v>
       </c>
       <c r="K524" s="1" t="n">
-        <v>1100000000000</v>
+        <v>490000000000</v>
       </c>
       <c r="L524" s="1" t="n">
-        <v>85714</v>
+        <v>37115</v>
       </c>
       <c r="M524" s="1" t="inlineStr">
         <is>
@@ -33681,10 +33681,10 @@
         <v>0</v>
       </c>
       <c r="K525" s="1" t="n">
-        <v>1400000000000</v>
+        <v>630000000000</v>
       </c>
       <c r="L525" s="1" t="n">
-        <v>111428</v>
+        <v>48250</v>
       </c>
       <c r="M525" s="1" t="inlineStr">
         <is>
@@ -33744,10 +33744,10 @@
         <v>0</v>
       </c>
       <c r="K526" s="1" t="n">
-        <v>1400000000000</v>
+        <v>630000000000</v>
       </c>
       <c r="L526" s="1" t="n">
-        <v>111428</v>
+        <v>48250</v>
       </c>
       <c r="M526" s="1" t="inlineStr">
         <is>
@@ -33807,10 +33807,10 @@
         <v>0</v>
       </c>
       <c r="K527" s="1" t="n">
-        <v>1800000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L527" s="1" t="n">
-        <v>144856</v>
+        <v>62725</v>
       </c>
       <c r="M527" s="1" t="inlineStr">
         <is>
@@ -33870,10 +33870,10 @@
         <v>0</v>
       </c>
       <c r="K528" s="1" t="n">
-        <v>1800000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L528" s="1" t="n">
-        <v>144856</v>
+        <v>62725</v>
       </c>
       <c r="M528" s="1" t="inlineStr">
         <is>
@@ -33933,10 +33933,10 @@
         <v>0</v>
       </c>
       <c r="K529" s="1" t="n">
-        <v>2400000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L529" s="1" t="n">
-        <v>188313</v>
+        <v>81542</v>
       </c>
       <c r="M529" s="1" t="inlineStr">
         <is>
@@ -33996,10 +33996,10 @@
         <v>0</v>
       </c>
       <c r="K530" s="1" t="n">
-        <v>2200000000000</v>
+        <v>970000000000</v>
       </c>
       <c r="L530" s="1" t="n">
-        <v>171427</v>
+        <v>74230</v>
       </c>
       <c r="M530" s="1" t="inlineStr">
         <is>
@@ -34059,10 +34059,10 @@
         <v>0</v>
       </c>
       <c r="K531" s="1" t="n">
-        <v>1400000000000</v>
+        <v>630000000000</v>
       </c>
       <c r="L531" s="1" t="n">
-        <v>111428</v>
+        <v>48250</v>
       </c>
       <c r="M531" s="1" t="inlineStr">
         <is>
@@ -34122,10 +34122,10 @@
         <v>0</v>
       </c>
       <c r="K532" s="1" t="n">
-        <v>3600000000000</v>
+        <v>1700000000000</v>
       </c>
       <c r="L532" s="1" t="n">
-        <v>289711</v>
+        <v>125449</v>
       </c>
       <c r="M532" s="1" t="inlineStr">
         <is>
@@ -34185,10 +34185,10 @@
         <v>0</v>
       </c>
       <c r="K533" s="1" t="n">
-        <v>1400000000000</v>
+        <v>630000000000</v>
       </c>
       <c r="L533" s="1" t="n">
-        <v>111428</v>
+        <v>48250</v>
       </c>
       <c r="M533" s="1" t="inlineStr">
         <is>
@@ -34248,10 +34248,10 @@
         <v>0</v>
       </c>
       <c r="K534" s="1" t="n">
-        <v>2400000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L534" s="1" t="n">
-        <v>188313</v>
+        <v>81542</v>
       </c>
       <c r="M534" s="1" t="inlineStr">
         <is>
@@ -34311,10 +34311,10 @@
         <v>0</v>
       </c>
       <c r="K535" s="1" t="n">
-        <v>1800000000000</v>
+        <v>820000000000</v>
       </c>
       <c r="L535" s="1" t="n">
-        <v>144856</v>
+        <v>62725</v>
       </c>
       <c r="M535" s="1" t="inlineStr">
         <is>
@@ -34443,10 +34443,10 @@
         <v>0</v>
       </c>
       <c r="K537" s="1" t="n">
-        <v>2000000000000</v>
+        <v>690000000000</v>
       </c>
       <c r="L537" s="1" t="n">
-        <v>148720</v>
+        <v>47880</v>
       </c>
       <c r="M537" s="1" t="inlineStr">
         <is>
@@ -34506,10 +34506,10 @@
         <v>0</v>
       </c>
       <c r="K538" s="1" t="n">
-        <v>2600000000000</v>
+        <v>900000000000</v>
       </c>
       <c r="L538" s="1" t="n">
-        <v>193336</v>
+        <v>62244</v>
       </c>
       <c r="M538" s="1" t="inlineStr">
         <is>
@@ -34569,10 +34569,10 @@
         <v>0</v>
       </c>
       <c r="K539" s="1" t="n">
-        <v>3400000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L539" s="1" t="n">
-        <v>251337</v>
+        <v>80918</v>
       </c>
       <c r="M539" s="1" t="inlineStr">
         <is>
@@ -34632,10 +34632,10 @@
         <v>0</v>
       </c>
       <c r="K540" s="1" t="n">
-        <v>3400000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L540" s="1" t="n">
-        <v>251337</v>
+        <v>80918</v>
       </c>
       <c r="M540" s="1" t="inlineStr">
         <is>
@@ -34695,10 +34695,10 @@
         <v>0</v>
       </c>
       <c r="K541" s="1" t="n">
-        <v>4400000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L541" s="1" t="n">
-        <v>326738</v>
+        <v>105193</v>
       </c>
       <c r="M541" s="1" t="inlineStr">
         <is>
@@ -34758,10 +34758,10 @@
         <v>0</v>
       </c>
       <c r="K542" s="1" t="n">
-        <v>3400000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L542" s="1" t="n">
-        <v>251337</v>
+        <v>80918</v>
       </c>
       <c r="M542" s="1" t="inlineStr">
         <is>
@@ -34821,10 +34821,10 @@
         <v>0</v>
       </c>
       <c r="K543" s="1" t="n">
-        <v>4400000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L543" s="1" t="n">
-        <v>326738</v>
+        <v>105193</v>
       </c>
       <c r="M543" s="1" t="inlineStr">
         <is>
@@ -34884,10 +34884,10 @@
         <v>0</v>
       </c>
       <c r="K544" s="1" t="n">
-        <v>4400000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L544" s="1" t="n">
-        <v>326738</v>
+        <v>105193</v>
       </c>
       <c r="M544" s="1" t="inlineStr">
         <is>
@@ -34947,10 +34947,10 @@
         <v>0</v>
       </c>
       <c r="K545" s="1" t="n">
-        <v>2000000000000</v>
+        <v>690000000000</v>
       </c>
       <c r="L545" s="1" t="n">
-        <v>148720</v>
+        <v>47880</v>
       </c>
       <c r="M545" s="1" t="inlineStr">
         <is>
@@ -35010,10 +35010,10 @@
         <v>0</v>
       </c>
       <c r="K546" s="1" t="n">
-        <v>2600000000000</v>
+        <v>900000000000</v>
       </c>
       <c r="L546" s="1" t="n">
-        <v>193336</v>
+        <v>62244</v>
       </c>
       <c r="M546" s="1" t="inlineStr">
         <is>
@@ -35073,10 +35073,10 @@
         <v>0</v>
       </c>
       <c r="K547" s="1" t="n">
-        <v>3400000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L547" s="1" t="n">
-        <v>251337</v>
+        <v>80918</v>
       </c>
       <c r="M547" s="1" t="inlineStr">
         <is>
@@ -35136,10 +35136,10 @@
         <v>0</v>
       </c>
       <c r="K548" s="1" t="n">
-        <v>3400000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L548" s="1" t="n">
-        <v>251337</v>
+        <v>80918</v>
       </c>
       <c r="M548" s="1" t="inlineStr">
         <is>
@@ -35199,10 +35199,10 @@
         <v>0</v>
       </c>
       <c r="K549" s="1" t="n">
-        <v>3400000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L549" s="1" t="n">
-        <v>251337</v>
+        <v>80918</v>
       </c>
       <c r="M549" s="1" t="inlineStr">
         <is>
@@ -35262,10 +35262,10 @@
         <v>0</v>
       </c>
       <c r="K550" s="1" t="n">
-        <v>4400000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L550" s="1" t="n">
-        <v>326738</v>
+        <v>105193</v>
       </c>
       <c r="M550" s="1" t="inlineStr">
         <is>
@@ -35325,10 +35325,10 @@
         <v>0</v>
       </c>
       <c r="K551" s="1" t="n">
-        <v>5700000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="L551" s="1" t="n">
-        <v>424760</v>
+        <v>136751</v>
       </c>
       <c r="M551" s="1" t="inlineStr">
         <is>
@@ -35388,10 +35388,10 @@
         <v>0</v>
       </c>
       <c r="K552" s="1" t="n">
-        <v>4400000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L552" s="1" t="n">
-        <v>326738</v>
+        <v>105193</v>
       </c>
       <c r="M552" s="1" t="inlineStr">
         <is>
@@ -35451,10 +35451,10 @@
         <v>0</v>
       </c>
       <c r="K553" s="1" t="n">
-        <v>2000000000000</v>
+        <v>690000000000</v>
       </c>
       <c r="L553" s="1" t="n">
-        <v>148720</v>
+        <v>47880</v>
       </c>
       <c r="M553" s="1" t="inlineStr">
         <is>
@@ -35514,10 +35514,10 @@
         <v>0</v>
       </c>
       <c r="K554" s="1" t="n">
-        <v>2600000000000</v>
+        <v>900000000000</v>
       </c>
       <c r="L554" s="1" t="n">
-        <v>193336</v>
+        <v>62244</v>
       </c>
       <c r="M554" s="1" t="inlineStr">
         <is>
@@ -35577,10 +35577,10 @@
         <v>0</v>
       </c>
       <c r="K555" s="1" t="n">
-        <v>3400000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L555" s="1" t="n">
-        <v>251337</v>
+        <v>80918</v>
       </c>
       <c r="M555" s="1" t="inlineStr">
         <is>
@@ -35640,10 +35640,10 @@
         <v>0</v>
       </c>
       <c r="K556" s="1" t="n">
-        <v>3400000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L556" s="1" t="n">
-        <v>251337</v>
+        <v>80918</v>
       </c>
       <c r="M556" s="1" t="inlineStr">
         <is>
@@ -35703,10 +35703,10 @@
         <v>0</v>
       </c>
       <c r="K557" s="1" t="n">
-        <v>4400000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L557" s="1" t="n">
-        <v>326738</v>
+        <v>105193</v>
       </c>
       <c r="M557" s="1" t="inlineStr">
         <is>
@@ -35766,10 +35766,10 @@
         <v>0</v>
       </c>
       <c r="K558" s="1" t="n">
-        <v>4400000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L558" s="1" t="n">
-        <v>326738</v>
+        <v>105193</v>
       </c>
       <c r="M558" s="1" t="inlineStr">
         <is>
@@ -35829,10 +35829,10 @@
         <v>0</v>
       </c>
       <c r="K559" s="1" t="n">
-        <v>4400000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L559" s="1" t="n">
-        <v>326738</v>
+        <v>105193</v>
       </c>
       <c r="M559" s="1" t="inlineStr">
         <is>
@@ -35892,10 +35892,10 @@
         <v>0</v>
       </c>
       <c r="K560" s="1" t="n">
-        <v>5700000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="L560" s="1" t="n">
-        <v>424760</v>
+        <v>136751</v>
       </c>
       <c r="M560" s="1" t="inlineStr">
         <is>
@@ -35955,10 +35955,10 @@
         <v>0</v>
       </c>
       <c r="K561" s="1" t="n">
-        <v>2000000000000</v>
+        <v>690000000000</v>
       </c>
       <c r="L561" s="1" t="n">
-        <v>148720</v>
+        <v>47880</v>
       </c>
       <c r="M561" s="1" t="inlineStr">
         <is>
@@ -36018,10 +36018,10 @@
         <v>0</v>
       </c>
       <c r="K562" s="1" t="n">
-        <v>2600000000000</v>
+        <v>900000000000</v>
       </c>
       <c r="L562" s="1" t="n">
-        <v>193336</v>
+        <v>62244</v>
       </c>
       <c r="M562" s="1" t="inlineStr">
         <is>
@@ -36081,10 +36081,10 @@
         <v>0</v>
       </c>
       <c r="K563" s="1" t="n">
-        <v>3400000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L563" s="1" t="n">
-        <v>251337</v>
+        <v>80918</v>
       </c>
       <c r="M563" s="1" t="inlineStr">
         <is>
@@ -36144,10 +36144,10 @@
         <v>0</v>
       </c>
       <c r="K564" s="1" t="n">
-        <v>3400000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L564" s="1" t="n">
-        <v>251337</v>
+        <v>80918</v>
       </c>
       <c r="M564" s="1" t="inlineStr">
         <is>
@@ -36207,10 +36207,10 @@
         <v>0</v>
       </c>
       <c r="K565" s="1" t="n">
-        <v>4400000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L565" s="1" t="n">
-        <v>326738</v>
+        <v>105193</v>
       </c>
       <c r="M565" s="1" t="inlineStr">
         <is>
@@ -36270,10 +36270,10 @@
         <v>0</v>
       </c>
       <c r="K566" s="1" t="n">
-        <v>4400000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L566" s="1" t="n">
-        <v>326738</v>
+        <v>105193</v>
       </c>
       <c r="M566" s="1" t="inlineStr">
         <is>
@@ -36333,10 +36333,10 @@
         <v>0</v>
       </c>
       <c r="K567" s="1" t="n">
-        <v>5700000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="L567" s="1" t="n">
-        <v>424760</v>
+        <v>136751</v>
       </c>
       <c r="M567" s="1" t="inlineStr">
         <is>
@@ -36396,10 +36396,10 @@
         <v>0</v>
       </c>
       <c r="K568" s="1" t="n">
-        <v>5200000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L568" s="1" t="n">
-        <v>386672</v>
+        <v>124488</v>
       </c>
       <c r="M568" s="1" t="inlineStr">
         <is>
@@ -36459,10 +36459,10 @@
         <v>0</v>
       </c>
       <c r="K569" s="1" t="n">
-        <v>3400000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L569" s="1" t="n">
-        <v>251337</v>
+        <v>80918</v>
       </c>
       <c r="M569" s="1" t="inlineStr">
         <is>
@@ -36522,10 +36522,10 @@
         <v>0</v>
       </c>
       <c r="K570" s="1" t="n">
-        <v>8800000000000</v>
+        <v>3100000000000</v>
       </c>
       <c r="L570" s="1" t="n">
-        <v>653476</v>
+        <v>210385</v>
       </c>
       <c r="M570" s="1" t="inlineStr">
         <is>
@@ -36585,10 +36585,10 @@
         <v>0</v>
       </c>
       <c r="K571" s="1" t="n">
-        <v>3400000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L571" s="1" t="n">
-        <v>251337</v>
+        <v>80918</v>
       </c>
       <c r="M571" s="1" t="inlineStr">
         <is>
@@ -36648,10 +36648,10 @@
         <v>0</v>
       </c>
       <c r="K572" s="1" t="n">
-        <v>5700000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="L572" s="1" t="n">
-        <v>424760</v>
+        <v>136751</v>
       </c>
       <c r="M572" s="1" t="inlineStr">
         <is>
@@ -36711,10 +36711,10 @@
         <v>0</v>
       </c>
       <c r="K573" s="1" t="n">
-        <v>4400000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L573" s="1" t="n">
-        <v>326738</v>
+        <v>105193</v>
       </c>
       <c r="M573" s="1" t="inlineStr">
         <is>
@@ -36843,10 +36843,10 @@
         <v>0</v>
       </c>
       <c r="K575" s="1" t="n">
-        <v>5800000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L575" s="1" t="n">
-        <v>371800</v>
+        <v>23940</v>
       </c>
       <c r="M575" s="1" t="inlineStr">
         <is>
@@ -36906,10 +36906,10 @@
         <v>0</v>
       </c>
       <c r="K576" s="1" t="n">
-        <v>7600000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L576" s="1" t="n">
-        <v>483340</v>
+        <v>31122</v>
       </c>
       <c r="M576" s="1" t="inlineStr">
         <is>
@@ -36969,10 +36969,10 @@
         <v>0</v>
       </c>
       <c r="K577" s="1" t="n">
-        <v>9800000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L577" s="1" t="n">
-        <v>628343</v>
+        <v>40459</v>
       </c>
       <c r="M577" s="1" t="inlineStr">
         <is>
@@ -37032,10 +37032,10 @@
         <v>0</v>
       </c>
       <c r="K578" s="1" t="n">
-        <v>9800000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L578" s="1" t="n">
-        <v>628343</v>
+        <v>40459</v>
       </c>
       <c r="M578" s="1" t="inlineStr">
         <is>
@@ -37095,10 +37095,10 @@
         <v>0</v>
       </c>
       <c r="K579" s="1" t="n">
-        <v>13000000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L579" s="1" t="n">
-        <v>816845</v>
+        <v>52597</v>
       </c>
       <c r="M579" s="1" t="inlineStr">
         <is>
@@ -37158,10 +37158,10 @@
         <v>0</v>
       </c>
       <c r="K580" s="1" t="n">
-        <v>9800000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L580" s="1" t="n">
-        <v>628343</v>
+        <v>40459</v>
       </c>
       <c r="M580" s="1" t="inlineStr">
         <is>
@@ -37221,10 +37221,10 @@
         <v>0</v>
       </c>
       <c r="K581" s="1" t="n">
-        <v>13000000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L581" s="1" t="n">
-        <v>816845</v>
+        <v>52597</v>
       </c>
       <c r="M581" s="1" t="inlineStr">
         <is>
@@ -37284,10 +37284,10 @@
         <v>0</v>
       </c>
       <c r="K582" s="1" t="n">
-        <v>13000000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L582" s="1" t="n">
-        <v>816845</v>
+        <v>52597</v>
       </c>
       <c r="M582" s="1" t="inlineStr">
         <is>
@@ -37347,10 +37347,10 @@
         <v>0</v>
       </c>
       <c r="K583" s="1" t="n">
-        <v>5800000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L583" s="1" t="n">
-        <v>371800</v>
+        <v>23940</v>
       </c>
       <c r="M583" s="1" t="inlineStr">
         <is>
@@ -37410,10 +37410,10 @@
         <v>0</v>
       </c>
       <c r="K584" s="1" t="n">
-        <v>7600000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L584" s="1" t="n">
-        <v>483340</v>
+        <v>31122</v>
       </c>
       <c r="M584" s="1" t="inlineStr">
         <is>
@@ -37473,10 +37473,10 @@
         <v>0</v>
       </c>
       <c r="K585" s="1" t="n">
-        <v>9800000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L585" s="1" t="n">
-        <v>628343</v>
+        <v>40459</v>
       </c>
       <c r="M585" s="1" t="inlineStr">
         <is>
@@ -37536,10 +37536,10 @@
         <v>0</v>
       </c>
       <c r="K586" s="1" t="n">
-        <v>9800000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L586" s="1" t="n">
-        <v>628343</v>
+        <v>40459</v>
       </c>
       <c r="M586" s="1" t="inlineStr">
         <is>
@@ -37599,10 +37599,10 @@
         <v>0</v>
       </c>
       <c r="K587" s="1" t="n">
-        <v>9800000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L587" s="1" t="n">
-        <v>628343</v>
+        <v>40459</v>
       </c>
       <c r="M587" s="1" t="inlineStr">
         <is>
@@ -37662,10 +37662,10 @@
         <v>0</v>
       </c>
       <c r="K588" s="1" t="n">
-        <v>13000000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L588" s="1" t="n">
-        <v>816845</v>
+        <v>52597</v>
       </c>
       <c r="M588" s="1" t="inlineStr">
         <is>
@@ -37725,10 +37725,10 @@
         <v>0</v>
       </c>
       <c r="K589" s="1" t="n">
-        <v>17000000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L589" s="1" t="n">
-        <v>1061898</v>
+        <v>68376</v>
       </c>
       <c r="M589" s="1" t="inlineStr">
         <is>
@@ -37788,10 +37788,10 @@
         <v>0</v>
       </c>
       <c r="K590" s="1" t="n">
-        <v>13000000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L590" s="1" t="n">
-        <v>816845</v>
+        <v>52597</v>
       </c>
       <c r="M590" s="1" t="inlineStr">
         <is>
@@ -37851,10 +37851,10 @@
         <v>0</v>
       </c>
       <c r="K591" s="1" t="n">
-        <v>5800000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L591" s="1" t="n">
-        <v>371800</v>
+        <v>23940</v>
       </c>
       <c r="M591" s="1" t="inlineStr">
         <is>
@@ -37914,10 +37914,10 @@
         <v>0</v>
       </c>
       <c r="K592" s="1" t="n">
-        <v>7600000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L592" s="1" t="n">
-        <v>483340</v>
+        <v>31122</v>
       </c>
       <c r="M592" s="1" t="inlineStr">
         <is>
@@ -37977,10 +37977,10 @@
         <v>0</v>
       </c>
       <c r="K593" s="1" t="n">
-        <v>9800000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L593" s="1" t="n">
-        <v>628343</v>
+        <v>40459</v>
       </c>
       <c r="M593" s="1" t="inlineStr">
         <is>
@@ -38040,10 +38040,10 @@
         <v>0</v>
       </c>
       <c r="K594" s="1" t="n">
-        <v>9800000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L594" s="1" t="n">
-        <v>628343</v>
+        <v>40459</v>
       </c>
       <c r="M594" s="1" t="inlineStr">
         <is>
@@ -38103,10 +38103,10 @@
         <v>0</v>
       </c>
       <c r="K595" s="1" t="n">
-        <v>13000000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L595" s="1" t="n">
-        <v>816845</v>
+        <v>52597</v>
       </c>
       <c r="M595" s="1" t="inlineStr">
         <is>
@@ -38166,10 +38166,10 @@
         <v>0</v>
       </c>
       <c r="K596" s="1" t="n">
-        <v>13000000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L596" s="1" t="n">
-        <v>816845</v>
+        <v>52597</v>
       </c>
       <c r="M596" s="1" t="inlineStr">
         <is>
@@ -38229,10 +38229,10 @@
         <v>0</v>
       </c>
       <c r="K597" s="1" t="n">
-        <v>13000000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L597" s="1" t="n">
-        <v>816845</v>
+        <v>52597</v>
       </c>
       <c r="M597" s="1" t="inlineStr">
         <is>
@@ -38292,10 +38292,10 @@
         <v>0</v>
       </c>
       <c r="K598" s="1" t="n">
-        <v>17000000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L598" s="1" t="n">
-        <v>1061898</v>
+        <v>68376</v>
       </c>
       <c r="M598" s="1" t="inlineStr">
         <is>
@@ -38355,10 +38355,10 @@
         <v>0</v>
       </c>
       <c r="K599" s="1" t="n">
-        <v>5800000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L599" s="1" t="n">
-        <v>371800</v>
+        <v>23940</v>
       </c>
       <c r="M599" s="1" t="inlineStr">
         <is>
@@ -38418,10 +38418,10 @@
         <v>0</v>
       </c>
       <c r="K600" s="1" t="n">
-        <v>7600000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L600" s="1" t="n">
-        <v>483340</v>
+        <v>31122</v>
       </c>
       <c r="M600" s="1" t="inlineStr">
         <is>
@@ -38481,10 +38481,10 @@
         <v>0</v>
       </c>
       <c r="K601" s="1" t="n">
-        <v>9800000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L601" s="1" t="n">
-        <v>628343</v>
+        <v>40459</v>
       </c>
       <c r="M601" s="1" t="inlineStr">
         <is>
@@ -38544,10 +38544,10 @@
         <v>0</v>
       </c>
       <c r="K602" s="1" t="n">
-        <v>9800000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L602" s="1" t="n">
-        <v>628343</v>
+        <v>40459</v>
       </c>
       <c r="M602" s="1" t="inlineStr">
         <is>
@@ -38607,10 +38607,10 @@
         <v>0</v>
       </c>
       <c r="K603" s="1" t="n">
-        <v>13000000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L603" s="1" t="n">
-        <v>816845</v>
+        <v>52597</v>
       </c>
       <c r="M603" s="1" t="inlineStr">
         <is>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="K604" s="1" t="n">
-        <v>13000000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L604" s="1" t="n">
-        <v>816845</v>
+        <v>52597</v>
       </c>
       <c r="M604" s="1" t="inlineStr">
         <is>
@@ -38733,10 +38733,10 @@
         <v>0</v>
       </c>
       <c r="K605" s="1" t="n">
-        <v>17000000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L605" s="1" t="n">
-        <v>1061898</v>
+        <v>68376</v>
       </c>
       <c r="M605" s="1" t="inlineStr">
         <is>
@@ -38796,10 +38796,10 @@
         <v>0</v>
       </c>
       <c r="K606" s="1" t="n">
-        <v>16000000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="L606" s="1" t="n">
-        <v>966680</v>
+        <v>62244</v>
       </c>
       <c r="M606" s="1" t="inlineStr">
         <is>
@@ -38859,10 +38859,10 @@
         <v>0</v>
       </c>
       <c r="K607" s="1" t="n">
-        <v>9800000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L607" s="1" t="n">
-        <v>628343</v>
+        <v>40459</v>
       </c>
       <c r="M607" s="1" t="inlineStr">
         <is>
@@ -38922,10 +38922,10 @@
         <v>0</v>
       </c>
       <c r="K608" s="1" t="n">
-        <v>26000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L608" s="1" t="n">
-        <v>1633690</v>
+        <v>105193</v>
       </c>
       <c r="M608" s="1" t="inlineStr">
         <is>
@@ -38985,10 +38985,10 @@
         <v>0</v>
       </c>
       <c r="K609" s="1" t="n">
-        <v>9800000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L609" s="1" t="n">
-        <v>628343</v>
+        <v>40459</v>
       </c>
       <c r="M609" s="1" t="inlineStr">
         <is>
@@ -39048,10 +39048,10 @@
         <v>0</v>
       </c>
       <c r="K610" s="1" t="n">
-        <v>17000000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="L610" s="1" t="n">
-        <v>1061898</v>
+        <v>68376</v>
       </c>
       <c r="M610" s="1" t="inlineStr">
         <is>
@@ -39111,10 +39111,10 @@
         <v>0</v>
       </c>
       <c r="K611" s="1" t="n">
-        <v>26000000000000</v>
+        <v>1800000000000</v>
       </c>
       <c r="L611" s="1" t="n">
-        <v>1633690</v>
+        <v>105193</v>
       </c>
       <c r="M611" s="1" t="inlineStr">
         <is>

--- a/Data_Table/공용 스킬 테이블.xlsx
+++ b/Data_Table/공용 스킬 테이블.xlsx
@@ -2769,11 +2769,11 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +7층</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>2492132</v>
+        <v>2493532</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="N36" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>0</v>
@@ -5169,11 +5169,11 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +1층</t>
+          <t>스테이지 스킵 +2층</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>2492232</v>
+        <v>2492132</v>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="N74" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O74" s="1" t="n">
         <v>0</v>
@@ -5295,11 +5295,11 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +1층</t>
+          <t>스테이지 스킵 +2층</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>2492232</v>
+        <v>2492132</v>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="N76" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O76" s="1" t="n">
         <v>0</v>
@@ -7569,11 +7569,11 @@
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +4층</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>2492332</v>
+        <v>2492732</v>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="N112" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O112" s="1" t="n">
         <v>0</v>
@@ -9969,11 +9969,11 @@
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>2492132</v>
+        <v>2492332</v>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="N150" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O150" s="1" t="n">
         <v>0</v>
@@ -10095,11 +10095,11 @@
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +1층</t>
+          <t>스테이지 스킵 +2층</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>2492232</v>
+        <v>2492132</v>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="N152" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O152" s="1" t="n">
         <v>0</v>
@@ -12369,11 +12369,11 @@
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +5층</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>2492332</v>
+        <v>2493332</v>
       </c>
       <c r="E188" s="1" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="N188" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O188" s="1" t="n">
         <v>0</v>
@@ -12843,10 +12843,10 @@
         <v>0</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>53000000</v>
+        <v>51000000</v>
       </c>
       <c r="L195" s="1" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M195" s="1" t="inlineStr">
         <is>
@@ -12906,10 +12906,10 @@
         <v>0</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>68000000</v>
+        <v>66000000</v>
       </c>
       <c r="L196" s="1" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M196" s="1" t="inlineStr">
         <is>
@@ -12969,10 +12969,10 @@
         <v>0</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>89000000</v>
+        <v>85000000</v>
       </c>
       <c r="L197" s="1" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M197" s="1" t="inlineStr">
         <is>
@@ -13032,10 +13032,10 @@
         <v>0</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>89000000</v>
+        <v>85000000</v>
       </c>
       <c r="L198" s="1" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M198" s="1" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>120000000</v>
       </c>
       <c r="L199" s="1" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M199" s="1" t="inlineStr">
         <is>
@@ -13158,10 +13158,10 @@
         <v>0</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>89000000</v>
+        <v>85000000</v>
       </c>
       <c r="L200" s="1" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M200" s="1" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>120000000</v>
       </c>
       <c r="L201" s="1" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M201" s="1" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>120000000</v>
       </c>
       <c r="L202" s="1" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M202" s="1" t="inlineStr">
         <is>
@@ -13347,10 +13347,10 @@
         <v>0</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>53000000</v>
+        <v>51000000</v>
       </c>
       <c r="L203" s="1" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M203" s="1" t="inlineStr">
         <is>
@@ -13410,10 +13410,10 @@
         <v>0</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>68000000</v>
+        <v>66000000</v>
       </c>
       <c r="L204" s="1" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M204" s="1" t="inlineStr">
         <is>
@@ -13473,10 +13473,10 @@
         <v>0</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>89000000</v>
+        <v>85000000</v>
       </c>
       <c r="L205" s="1" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M205" s="1" t="inlineStr">
         <is>
@@ -13536,10 +13536,10 @@
         <v>0</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>89000000</v>
+        <v>85000000</v>
       </c>
       <c r="L206" s="1" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M206" s="1" t="inlineStr">
         <is>
@@ -13599,10 +13599,10 @@
         <v>0</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>89000000</v>
+        <v>85000000</v>
       </c>
       <c r="L207" s="1" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M207" s="1" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>120000000</v>
       </c>
       <c r="L208" s="1" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M208" s="1" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>150000000</v>
       </c>
       <c r="L209" s="1" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M209" s="1" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>120000000</v>
       </c>
       <c r="L210" s="1" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M210" s="1" t="inlineStr">
         <is>
@@ -13851,10 +13851,10 @@
         <v>0</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>53000000</v>
+        <v>51000000</v>
       </c>
       <c r="L211" s="1" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M211" s="1" t="inlineStr">
         <is>
@@ -13914,10 +13914,10 @@
         <v>0</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>68000000</v>
+        <v>66000000</v>
       </c>
       <c r="L212" s="1" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M212" s="1" t="inlineStr">
         <is>
@@ -13977,10 +13977,10 @@
         <v>0</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>89000000</v>
+        <v>85000000</v>
       </c>
       <c r="L213" s="1" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M213" s="1" t="inlineStr">
         <is>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>89000000</v>
+        <v>85000000</v>
       </c>
       <c r="L214" s="1" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M214" s="1" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>120000000</v>
       </c>
       <c r="L215" s="1" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M215" s="1" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>230000000</v>
       </c>
       <c r="L216" s="1" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="M216" s="1" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>120000000</v>
       </c>
       <c r="L217" s="1" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M217" s="1" t="inlineStr">
         <is>
@@ -14292,10 +14292,10 @@
         <v>0</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>300000000</v>
+        <v>290000000</v>
       </c>
       <c r="L218" s="1" t="n">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="M218" s="1" t="inlineStr">
         <is>
@@ -14355,10 +14355,10 @@
         <v>0</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>53000000</v>
+        <v>51000000</v>
       </c>
       <c r="L219" s="1" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M219" s="1" t="inlineStr">
         <is>
@@ -14418,10 +14418,10 @@
         <v>0</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>68000000</v>
+        <v>66000000</v>
       </c>
       <c r="L220" s="1" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M220" s="1" t="inlineStr">
         <is>
@@ -14481,10 +14481,10 @@
         <v>0</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>89000000</v>
+        <v>85000000</v>
       </c>
       <c r="L221" s="1" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M221" s="1" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>0</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>89000000</v>
+        <v>85000000</v>
       </c>
       <c r="L222" s="1" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M222" s="1" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>120000000</v>
       </c>
       <c r="L223" s="1" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M223" s="1" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>120000000</v>
       </c>
       <c r="L224" s="1" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M224" s="1" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>150000000</v>
       </c>
       <c r="L225" s="1" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M225" s="1" t="inlineStr">
         <is>
@@ -14769,11 +14769,11 @@
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>2492132</v>
+        <v>2492332</v>
       </c>
       <c r="E226" s="1" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>140000000</v>
       </c>
       <c r="L226" s="1" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="M226" s="1" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="N226" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O226" s="1" t="n">
         <v>0</v>
@@ -14859,10 +14859,10 @@
         <v>0</v>
       </c>
       <c r="K227" s="1" t="n">
-        <v>180000000</v>
+        <v>170000000</v>
       </c>
       <c r="L227" s="1" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M227" s="1" t="inlineStr">
         <is>
@@ -14895,11 +14895,11 @@
       </c>
       <c r="C228" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>2492132</v>
+        <v>2492332</v>
       </c>
       <c r="E228" s="1" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>230000000</v>
       </c>
       <c r="L228" s="1" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="M228" s="1" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="N228" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O228" s="1" t="n">
         <v>0</v>
@@ -14985,10 +14985,10 @@
         <v>0</v>
       </c>
       <c r="K229" s="1" t="n">
-        <v>89000000</v>
+        <v>85000000</v>
       </c>
       <c r="L229" s="1" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M229" s="1" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>150000000</v>
       </c>
       <c r="L230" s="1" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M230" s="1" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>120000000</v>
       </c>
       <c r="L231" s="1" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M231" s="1" t="inlineStr">
         <is>
@@ -15243,10 +15243,10 @@
         <v>0</v>
       </c>
       <c r="K233" s="1" t="n">
-        <v>740000000</v>
+        <v>590000000</v>
       </c>
       <c r="L233" s="1" t="n">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="M233" s="1" t="inlineStr">
         <is>
@@ -15306,10 +15306,10 @@
         <v>0</v>
       </c>
       <c r="K234" s="1" t="n">
-        <v>960000000</v>
+        <v>760000000</v>
       </c>
       <c r="L234" s="1" t="n">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="M234" s="1" t="inlineStr">
         <is>
@@ -15369,10 +15369,10 @@
         <v>0</v>
       </c>
       <c r="K235" s="1" t="n">
-        <v>1300000000</v>
+        <v>990000000</v>
       </c>
       <c r="L235" s="1" t="n">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M235" s="1" t="inlineStr">
         <is>
@@ -15432,10 +15432,10 @@
         <v>0</v>
       </c>
       <c r="K236" s="1" t="n">
-        <v>1300000000</v>
+        <v>990000000</v>
       </c>
       <c r="L236" s="1" t="n">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M236" s="1" t="inlineStr">
         <is>
@@ -15495,10 +15495,10 @@
         <v>0</v>
       </c>
       <c r="K237" s="1" t="n">
-        <v>1700000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L237" s="1" t="n">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="M237" s="1" t="inlineStr">
         <is>
@@ -15558,10 +15558,10 @@
         <v>0</v>
       </c>
       <c r="K238" s="1" t="n">
-        <v>1300000000</v>
+        <v>990000000</v>
       </c>
       <c r="L238" s="1" t="n">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M238" s="1" t="inlineStr">
         <is>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="K239" s="1" t="n">
-        <v>1700000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L239" s="1" t="n">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="M239" s="1" t="inlineStr">
         <is>
@@ -15684,10 +15684,10 @@
         <v>0</v>
       </c>
       <c r="K240" s="1" t="n">
-        <v>1700000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L240" s="1" t="n">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="M240" s="1" t="inlineStr">
         <is>
@@ -15747,10 +15747,10 @@
         <v>0</v>
       </c>
       <c r="K241" s="1" t="n">
-        <v>740000000</v>
+        <v>590000000</v>
       </c>
       <c r="L241" s="1" t="n">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="M241" s="1" t="inlineStr">
         <is>
@@ -15810,10 +15810,10 @@
         <v>0</v>
       </c>
       <c r="K242" s="1" t="n">
-        <v>960000000</v>
+        <v>760000000</v>
       </c>
       <c r="L242" s="1" t="n">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="M242" s="1" t="inlineStr">
         <is>
@@ -15873,10 +15873,10 @@
         <v>0</v>
       </c>
       <c r="K243" s="1" t="n">
-        <v>1300000000</v>
+        <v>990000000</v>
       </c>
       <c r="L243" s="1" t="n">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M243" s="1" t="inlineStr">
         <is>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="K244" s="1" t="n">
-        <v>1300000000</v>
+        <v>990000000</v>
       </c>
       <c r="L244" s="1" t="n">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M244" s="1" t="inlineStr">
         <is>
@@ -15999,10 +15999,10 @@
         <v>0</v>
       </c>
       <c r="K245" s="1" t="n">
-        <v>1300000000</v>
+        <v>990000000</v>
       </c>
       <c r="L245" s="1" t="n">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M245" s="1" t="inlineStr">
         <is>
@@ -16062,10 +16062,10 @@
         <v>0</v>
       </c>
       <c r="K246" s="1" t="n">
-        <v>1700000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L246" s="1" t="n">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="M246" s="1" t="inlineStr">
         <is>
@@ -16125,10 +16125,10 @@
         <v>0</v>
       </c>
       <c r="K247" s="1" t="n">
-        <v>2100000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L247" s="1" t="n">
-        <v>612</v>
+        <v>507</v>
       </c>
       <c r="M247" s="1" t="inlineStr">
         <is>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="K248" s="1" t="n">
-        <v>1700000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L248" s="1" t="n">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="M248" s="1" t="inlineStr">
         <is>
@@ -16251,10 +16251,10 @@
         <v>0</v>
       </c>
       <c r="K249" s="1" t="n">
-        <v>740000000</v>
+        <v>590000000</v>
       </c>
       <c r="L249" s="1" t="n">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="M249" s="1" t="inlineStr">
         <is>
@@ -16314,10 +16314,10 @@
         <v>0</v>
       </c>
       <c r="K250" s="1" t="n">
-        <v>960000000</v>
+        <v>760000000</v>
       </c>
       <c r="L250" s="1" t="n">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="M250" s="1" t="inlineStr">
         <is>
@@ -16377,10 +16377,10 @@
         <v>0</v>
       </c>
       <c r="K251" s="1" t="n">
-        <v>1300000000</v>
+        <v>990000000</v>
       </c>
       <c r="L251" s="1" t="n">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M251" s="1" t="inlineStr">
         <is>
@@ -16440,10 +16440,10 @@
         <v>0</v>
       </c>
       <c r="K252" s="1" t="n">
-        <v>1300000000</v>
+        <v>990000000</v>
       </c>
       <c r="L252" s="1" t="n">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M252" s="1" t="inlineStr">
         <is>
@@ -16503,10 +16503,10 @@
         <v>0</v>
       </c>
       <c r="K253" s="1" t="n">
-        <v>1700000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L253" s="1" t="n">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="M253" s="1" t="inlineStr">
         <is>
@@ -16566,10 +16566,10 @@
         <v>0</v>
       </c>
       <c r="K254" s="1" t="n">
-        <v>1700000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L254" s="1" t="n">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="M254" s="1" t="inlineStr">
         <is>
@@ -16629,10 +16629,10 @@
         <v>0</v>
       </c>
       <c r="K255" s="1" t="n">
-        <v>1700000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L255" s="1" t="n">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="M255" s="1" t="inlineStr">
         <is>
@@ -16692,10 +16692,10 @@
         <v>0</v>
       </c>
       <c r="K256" s="1" t="n">
-        <v>4200000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L256" s="1" t="n">
-        <v>1224</v>
+        <v>1014</v>
       </c>
       <c r="M256" s="1" t="inlineStr">
         <is>
@@ -16755,10 +16755,10 @@
         <v>0</v>
       </c>
       <c r="K257" s="1" t="n">
-        <v>740000000</v>
+        <v>590000000</v>
       </c>
       <c r="L257" s="1" t="n">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="M257" s="1" t="inlineStr">
         <is>
@@ -16818,10 +16818,10 @@
         <v>0</v>
       </c>
       <c r="K258" s="1" t="n">
-        <v>960000000</v>
+        <v>760000000</v>
       </c>
       <c r="L258" s="1" t="n">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="M258" s="1" t="inlineStr">
         <is>
@@ -16881,10 +16881,10 @@
         <v>0</v>
       </c>
       <c r="K259" s="1" t="n">
-        <v>1300000000</v>
+        <v>990000000</v>
       </c>
       <c r="L259" s="1" t="n">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M259" s="1" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>0</v>
       </c>
       <c r="K260" s="1" t="n">
-        <v>1300000000</v>
+        <v>990000000</v>
       </c>
       <c r="L260" s="1" t="n">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M260" s="1" t="inlineStr">
         <is>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="K261" s="1" t="n">
-        <v>1700000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L261" s="1" t="n">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="M261" s="1" t="inlineStr">
         <is>
@@ -17070,10 +17070,10 @@
         <v>0</v>
       </c>
       <c r="K262" s="1" t="n">
-        <v>1700000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L262" s="1" t="n">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="M262" s="1" t="inlineStr">
         <is>
@@ -17133,10 +17133,10 @@
         <v>0</v>
       </c>
       <c r="K263" s="1" t="n">
-        <v>2100000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L263" s="1" t="n">
-        <v>612</v>
+        <v>507</v>
       </c>
       <c r="M263" s="1" t="inlineStr">
         <is>
@@ -17169,11 +17169,11 @@
       </c>
       <c r="C264" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +4층</t>
+          <t>스테이지 스킵 +6층</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>2492732</v>
+        <v>2492934</v>
       </c>
       <c r="E264" s="1" t="inlineStr">
         <is>
@@ -17196,10 +17196,10 @@
         <v>0</v>
       </c>
       <c r="K264" s="1" t="n">
-        <v>2000000000</v>
+        <v>1600000000</v>
       </c>
       <c r="L264" s="1" t="n">
-        <v>557</v>
+        <v>462</v>
       </c>
       <c r="M264" s="1" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         </is>
       </c>
       <c r="N264" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O264" s="1" t="n">
         <v>0</v>
@@ -17259,10 +17259,10 @@
         <v>0</v>
       </c>
       <c r="K265" s="1" t="n">
-        <v>1300000000</v>
+        <v>990000000</v>
       </c>
       <c r="L265" s="1" t="n">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M265" s="1" t="inlineStr">
         <is>
@@ -17322,10 +17322,10 @@
         <v>0</v>
       </c>
       <c r="K266" s="1" t="n">
-        <v>1700000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L266" s="1" t="n">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="M266" s="1" t="inlineStr">
         <is>
@@ -17385,10 +17385,10 @@
         <v>0</v>
       </c>
       <c r="K267" s="1" t="n">
-        <v>1300000000</v>
+        <v>990000000</v>
       </c>
       <c r="L267" s="1" t="n">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M267" s="1" t="inlineStr">
         <is>
@@ -17448,10 +17448,10 @@
         <v>0</v>
       </c>
       <c r="K268" s="1" t="n">
-        <v>2100000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L268" s="1" t="n">
-        <v>612</v>
+        <v>507</v>
       </c>
       <c r="M268" s="1" t="inlineStr">
         <is>
@@ -17511,10 +17511,10 @@
         <v>0</v>
       </c>
       <c r="K269" s="1" t="n">
-        <v>1700000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L269" s="1" t="n">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="M269" s="1" t="inlineStr">
         <is>
@@ -17643,10 +17643,10 @@
         <v>0</v>
       </c>
       <c r="K271" s="1" t="n">
-        <v>1400000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L271" s="1" t="n">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
@@ -17706,10 +17706,10 @@
         <v>0</v>
       </c>
       <c r="K272" s="1" t="n">
-        <v>1900000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L272" s="1" t="n">
-        <v>429</v>
+        <v>351</v>
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
@@ -17769,10 +17769,10 @@
         <v>0</v>
       </c>
       <c r="K273" s="1" t="n">
-        <v>2400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L273" s="1" t="n">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
@@ -17832,10 +17832,10 @@
         <v>0</v>
       </c>
       <c r="K274" s="1" t="n">
-        <v>2400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L274" s="1" t="n">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
@@ -17895,10 +17895,10 @@
         <v>0</v>
       </c>
       <c r="K275" s="1" t="n">
-        <v>3100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L275" s="1" t="n">
-        <v>726</v>
+        <v>594</v>
       </c>
       <c r="M275" s="1" t="inlineStr">
         <is>
@@ -17958,10 +17958,10 @@
         <v>0</v>
       </c>
       <c r="K276" s="1" t="n">
-        <v>2400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L276" s="1" t="n">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="M276" s="1" t="inlineStr">
         <is>
@@ -18021,10 +18021,10 @@
         <v>0</v>
       </c>
       <c r="K277" s="1" t="n">
-        <v>3100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L277" s="1" t="n">
-        <v>726</v>
+        <v>594</v>
       </c>
       <c r="M277" s="1" t="inlineStr">
         <is>
@@ -18084,10 +18084,10 @@
         <v>0</v>
       </c>
       <c r="K278" s="1" t="n">
-        <v>3100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L278" s="1" t="n">
-        <v>726</v>
+        <v>594</v>
       </c>
       <c r="M278" s="1" t="inlineStr">
         <is>
@@ -18147,10 +18147,10 @@
         <v>0</v>
       </c>
       <c r="K279" s="1" t="n">
-        <v>1400000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L279" s="1" t="n">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
@@ -18210,10 +18210,10 @@
         <v>0</v>
       </c>
       <c r="K280" s="1" t="n">
-        <v>1900000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L280" s="1" t="n">
-        <v>429</v>
+        <v>351</v>
       </c>
       <c r="M280" s="1" t="inlineStr">
         <is>
@@ -18273,10 +18273,10 @@
         <v>0</v>
       </c>
       <c r="K281" s="1" t="n">
-        <v>2400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L281" s="1" t="n">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="M281" s="1" t="inlineStr">
         <is>
@@ -18336,10 +18336,10 @@
         <v>0</v>
       </c>
       <c r="K282" s="1" t="n">
-        <v>2400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L282" s="1" t="n">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="M282" s="1" t="inlineStr">
         <is>
@@ -18399,10 +18399,10 @@
         <v>0</v>
       </c>
       <c r="K283" s="1" t="n">
-        <v>2400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L283" s="1" t="n">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
@@ -18462,10 +18462,10 @@
         <v>0</v>
       </c>
       <c r="K284" s="1" t="n">
-        <v>3100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L284" s="1" t="n">
-        <v>726</v>
+        <v>594</v>
       </c>
       <c r="M284" s="1" t="inlineStr">
         <is>
@@ -18525,10 +18525,10 @@
         <v>0</v>
       </c>
       <c r="K285" s="1" t="n">
-        <v>4000000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L285" s="1" t="n">
-        <v>943</v>
+        <v>772</v>
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
@@ -18588,10 +18588,10 @@
         <v>0</v>
       </c>
       <c r="K286" s="1" t="n">
-        <v>3100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L286" s="1" t="n">
-        <v>726</v>
+        <v>594</v>
       </c>
       <c r="M286" s="1" t="inlineStr">
         <is>
@@ -18651,10 +18651,10 @@
         <v>0</v>
       </c>
       <c r="K287" s="1" t="n">
-        <v>1400000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L287" s="1" t="n">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="M287" s="1" t="inlineStr">
         <is>
@@ -18714,10 +18714,10 @@
         <v>0</v>
       </c>
       <c r="K288" s="1" t="n">
-        <v>1900000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L288" s="1" t="n">
-        <v>429</v>
+        <v>351</v>
       </c>
       <c r="M288" s="1" t="inlineStr">
         <is>
@@ -18777,10 +18777,10 @@
         <v>0</v>
       </c>
       <c r="K289" s="1" t="n">
-        <v>2400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L289" s="1" t="n">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="M289" s="1" t="inlineStr">
         <is>
@@ -18840,10 +18840,10 @@
         <v>0</v>
       </c>
       <c r="K290" s="1" t="n">
-        <v>2400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L290" s="1" t="n">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
@@ -18903,10 +18903,10 @@
         <v>0</v>
       </c>
       <c r="K291" s="1" t="n">
-        <v>3100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L291" s="1" t="n">
-        <v>726</v>
+        <v>594</v>
       </c>
       <c r="M291" s="1" t="inlineStr">
         <is>
@@ -18966,10 +18966,10 @@
         <v>0</v>
       </c>
       <c r="K292" s="1" t="n">
-        <v>3100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L292" s="1" t="n">
-        <v>726</v>
+        <v>594</v>
       </c>
       <c r="M292" s="1" t="inlineStr">
         <is>
@@ -19029,10 +19029,10 @@
         <v>0</v>
       </c>
       <c r="K293" s="1" t="n">
-        <v>3100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L293" s="1" t="n">
-        <v>726</v>
+        <v>594</v>
       </c>
       <c r="M293" s="1" t="inlineStr">
         <is>
@@ -19092,10 +19092,10 @@
         <v>0</v>
       </c>
       <c r="K294" s="1" t="n">
-        <v>8000000000</v>
+        <v>6200000000</v>
       </c>
       <c r="L294" s="1" t="n">
-        <v>1886</v>
+        <v>1543</v>
       </c>
       <c r="M294" s="1" t="inlineStr">
         <is>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="K295" s="1" t="n">
-        <v>1400000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L295" s="1" t="n">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="M295" s="1" t="inlineStr">
         <is>
@@ -19218,10 +19218,10 @@
         <v>0</v>
       </c>
       <c r="K296" s="1" t="n">
-        <v>1900000000</v>
+        <v>1500000000</v>
       </c>
       <c r="L296" s="1" t="n">
-        <v>429</v>
+        <v>351</v>
       </c>
       <c r="M296" s="1" t="inlineStr">
         <is>
@@ -19281,10 +19281,10 @@
         <v>0</v>
       </c>
       <c r="K297" s="1" t="n">
-        <v>2400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L297" s="1" t="n">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="M297" s="1" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>0</v>
       </c>
       <c r="K298" s="1" t="n">
-        <v>2400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L298" s="1" t="n">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="M298" s="1" t="inlineStr">
         <is>
@@ -19407,10 +19407,10 @@
         <v>0</v>
       </c>
       <c r="K299" s="1" t="n">
-        <v>3100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L299" s="1" t="n">
-        <v>726</v>
+        <v>594</v>
       </c>
       <c r="M299" s="1" t="inlineStr">
         <is>
@@ -19470,10 +19470,10 @@
         <v>0</v>
       </c>
       <c r="K300" s="1" t="n">
-        <v>3100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L300" s="1" t="n">
-        <v>726</v>
+        <v>594</v>
       </c>
       <c r="M300" s="1" t="inlineStr">
         <is>
@@ -19533,10 +19533,10 @@
         <v>0</v>
       </c>
       <c r="K301" s="1" t="n">
-        <v>4000000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L301" s="1" t="n">
-        <v>943</v>
+        <v>772</v>
       </c>
       <c r="M301" s="1" t="inlineStr">
         <is>
@@ -19596,10 +19596,10 @@
         <v>0</v>
       </c>
       <c r="K302" s="1" t="n">
-        <v>3700000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L302" s="1" t="n">
-        <v>858</v>
+        <v>702</v>
       </c>
       <c r="M302" s="1" t="inlineStr">
         <is>
@@ -19659,10 +19659,10 @@
         <v>0</v>
       </c>
       <c r="K303" s="1" t="n">
-        <v>2400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L303" s="1" t="n">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="M303" s="1" t="inlineStr">
         <is>
@@ -19722,10 +19722,10 @@
         <v>0</v>
       </c>
       <c r="K304" s="1" t="n">
-        <v>6200000000</v>
+        <v>4800000000</v>
       </c>
       <c r="L304" s="1" t="n">
-        <v>1451</v>
+        <v>1187</v>
       </c>
       <c r="M304" s="1" t="inlineStr">
         <is>
@@ -19785,10 +19785,10 @@
         <v>0</v>
       </c>
       <c r="K305" s="1" t="n">
-        <v>2400000000</v>
+        <v>1900000000</v>
       </c>
       <c r="L305" s="1" t="n">
-        <v>558</v>
+        <v>457</v>
       </c>
       <c r="M305" s="1" t="inlineStr">
         <is>
@@ -19848,10 +19848,10 @@
         <v>0</v>
       </c>
       <c r="K306" s="1" t="n">
-        <v>4000000000</v>
+        <v>3100000000</v>
       </c>
       <c r="L306" s="1" t="n">
-        <v>943</v>
+        <v>772</v>
       </c>
       <c r="M306" s="1" t="inlineStr">
         <is>
@@ -19911,10 +19911,10 @@
         <v>0</v>
       </c>
       <c r="K307" s="1" t="n">
-        <v>3100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="L307" s="1" t="n">
-        <v>726</v>
+        <v>594</v>
       </c>
       <c r="M307" s="1" t="inlineStr">
         <is>
@@ -20043,10 +20043,10 @@
         <v>0</v>
       </c>
       <c r="K309" s="1" t="n">
-        <v>2600000000</v>
+        <v>2100000000</v>
       </c>
       <c r="L309" s="1" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="M309" s="1" t="inlineStr">
         <is>
@@ -20106,10 +20106,10 @@
         <v>0</v>
       </c>
       <c r="K310" s="1" t="n">
-        <v>3400000000</v>
+        <v>2700000000</v>
       </c>
       <c r="L310" s="1" t="n">
-        <v>715</v>
+        <v>585</v>
       </c>
       <c r="M310" s="1" t="inlineStr">
         <is>
@@ -20169,10 +20169,10 @@
         <v>0</v>
       </c>
       <c r="K311" s="1" t="n">
-        <v>4400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L311" s="1" t="n">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="M311" s="1" t="inlineStr">
         <is>
@@ -20232,10 +20232,10 @@
         <v>0</v>
       </c>
       <c r="K312" s="1" t="n">
-        <v>4400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L312" s="1" t="n">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="M312" s="1" t="inlineStr">
         <is>
@@ -20295,10 +20295,10 @@
         <v>0</v>
       </c>
       <c r="K313" s="1" t="n">
-        <v>5700000000</v>
+        <v>4500000000</v>
       </c>
       <c r="L313" s="1" t="n">
-        <v>1209</v>
+        <v>989</v>
       </c>
       <c r="M313" s="1" t="inlineStr">
         <is>
@@ -20358,10 +20358,10 @@
         <v>0</v>
       </c>
       <c r="K314" s="1" t="n">
-        <v>4400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L314" s="1" t="n">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="M314" s="1" t="inlineStr">
         <is>
@@ -20421,10 +20421,10 @@
         <v>0</v>
       </c>
       <c r="K315" s="1" t="n">
-        <v>5700000000</v>
+        <v>4500000000</v>
       </c>
       <c r="L315" s="1" t="n">
-        <v>1209</v>
+        <v>989</v>
       </c>
       <c r="M315" s="1" t="inlineStr">
         <is>
@@ -20484,10 +20484,10 @@
         <v>0</v>
       </c>
       <c r="K316" s="1" t="n">
-        <v>5700000000</v>
+        <v>4500000000</v>
       </c>
       <c r="L316" s="1" t="n">
-        <v>1209</v>
+        <v>989</v>
       </c>
       <c r="M316" s="1" t="inlineStr">
         <is>
@@ -20547,10 +20547,10 @@
         <v>0</v>
       </c>
       <c r="K317" s="1" t="n">
-        <v>5200000000</v>
+        <v>4100000000</v>
       </c>
       <c r="L317" s="1" t="n">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="M317" s="1" t="inlineStr">
         <is>
@@ -20610,10 +20610,10 @@
         <v>0</v>
       </c>
       <c r="K318" s="1" t="n">
-        <v>3400000000</v>
+        <v>2700000000</v>
       </c>
       <c r="L318" s="1" t="n">
-        <v>715</v>
+        <v>585</v>
       </c>
       <c r="M318" s="1" t="inlineStr">
         <is>
@@ -20673,10 +20673,10 @@
         <v>0</v>
       </c>
       <c r="K319" s="1" t="n">
-        <v>4400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L319" s="1" t="n">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="M319" s="1" t="inlineStr">
         <is>
@@ -20736,10 +20736,10 @@
         <v>0</v>
       </c>
       <c r="K320" s="1" t="n">
-        <v>4400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L320" s="1" t="n">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="M320" s="1" t="inlineStr">
         <is>
@@ -20799,10 +20799,10 @@
         <v>0</v>
       </c>
       <c r="K321" s="1" t="n">
-        <v>4400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L321" s="1" t="n">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="M321" s="1" t="inlineStr">
         <is>
@@ -20862,10 +20862,10 @@
         <v>0</v>
       </c>
       <c r="K322" s="1" t="n">
-        <v>5700000000</v>
+        <v>4500000000</v>
       </c>
       <c r="L322" s="1" t="n">
-        <v>1209</v>
+        <v>989</v>
       </c>
       <c r="M322" s="1" t="inlineStr">
         <is>
@@ -20925,10 +20925,10 @@
         <v>0</v>
       </c>
       <c r="K323" s="1" t="n">
-        <v>7400000000</v>
+        <v>5800000000</v>
       </c>
       <c r="L323" s="1" t="n">
-        <v>1571</v>
+        <v>1286</v>
       </c>
       <c r="M323" s="1" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
         <v>0</v>
       </c>
       <c r="K324" s="1" t="n">
-        <v>5700000000</v>
+        <v>4500000000</v>
       </c>
       <c r="L324" s="1" t="n">
-        <v>1209</v>
+        <v>989</v>
       </c>
       <c r="M324" s="1" t="inlineStr">
         <is>
@@ -21051,10 +21051,10 @@
         <v>0</v>
       </c>
       <c r="K325" s="1" t="n">
-        <v>2600000000</v>
+        <v>2100000000</v>
       </c>
       <c r="L325" s="1" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="M325" s="1" t="inlineStr">
         <is>
@@ -21114,10 +21114,10 @@
         <v>0</v>
       </c>
       <c r="K326" s="1" t="n">
-        <v>3400000000</v>
+        <v>2700000000</v>
       </c>
       <c r="L326" s="1" t="n">
-        <v>715</v>
+        <v>585</v>
       </c>
       <c r="M326" s="1" t="inlineStr">
         <is>
@@ -21177,10 +21177,10 @@
         <v>0</v>
       </c>
       <c r="K327" s="1" t="n">
-        <v>4400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L327" s="1" t="n">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="M327" s="1" t="inlineStr">
         <is>
@@ -21240,10 +21240,10 @@
         <v>0</v>
       </c>
       <c r="K328" s="1" t="n">
-        <v>4400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L328" s="1" t="n">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="M328" s="1" t="inlineStr">
         <is>
@@ -21303,10 +21303,10 @@
         <v>0</v>
       </c>
       <c r="K329" s="1" t="n">
-        <v>5700000000</v>
+        <v>4500000000</v>
       </c>
       <c r="L329" s="1" t="n">
-        <v>1209</v>
+        <v>989</v>
       </c>
       <c r="M329" s="1" t="inlineStr">
         <is>
@@ -21366,10 +21366,10 @@
         <v>0</v>
       </c>
       <c r="K330" s="1" t="n">
-        <v>5700000000</v>
+        <v>4500000000</v>
       </c>
       <c r="L330" s="1" t="n">
-        <v>1209</v>
+        <v>989</v>
       </c>
       <c r="M330" s="1" t="inlineStr">
         <is>
@@ -21429,10 +21429,10 @@
         <v>0</v>
       </c>
       <c r="K331" s="1" t="n">
-        <v>5700000000</v>
+        <v>4500000000</v>
       </c>
       <c r="L331" s="1" t="n">
-        <v>1209</v>
+        <v>989</v>
       </c>
       <c r="M331" s="1" t="inlineStr">
         <is>
@@ -21492,10 +21492,10 @@
         <v>0</v>
       </c>
       <c r="K332" s="1" t="n">
-        <v>7400000000</v>
+        <v>5800000000</v>
       </c>
       <c r="L332" s="1" t="n">
-        <v>1571</v>
+        <v>1286</v>
       </c>
       <c r="M332" s="1" t="inlineStr">
         <is>
@@ -21555,10 +21555,10 @@
         <v>0</v>
       </c>
       <c r="K333" s="1" t="n">
-        <v>2600000000</v>
+        <v>2100000000</v>
       </c>
       <c r="L333" s="1" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="M333" s="1" t="inlineStr">
         <is>
@@ -21618,10 +21618,10 @@
         <v>0</v>
       </c>
       <c r="K334" s="1" t="n">
-        <v>3400000000</v>
+        <v>2700000000</v>
       </c>
       <c r="L334" s="1" t="n">
-        <v>715</v>
+        <v>585</v>
       </c>
       <c r="M334" s="1" t="inlineStr">
         <is>
@@ -21681,10 +21681,10 @@
         <v>0</v>
       </c>
       <c r="K335" s="1" t="n">
-        <v>4400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L335" s="1" t="n">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="M335" s="1" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>0</v>
       </c>
       <c r="K336" s="1" t="n">
-        <v>4400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L336" s="1" t="n">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="M336" s="1" t="inlineStr">
         <is>
@@ -21807,10 +21807,10 @@
         <v>0</v>
       </c>
       <c r="K337" s="1" t="n">
-        <v>5700000000</v>
+        <v>4500000000</v>
       </c>
       <c r="L337" s="1" t="n">
-        <v>1209</v>
+        <v>989</v>
       </c>
       <c r="M337" s="1" t="inlineStr">
         <is>
@@ -21870,10 +21870,10 @@
         <v>0</v>
       </c>
       <c r="K338" s="1" t="n">
-        <v>5700000000</v>
+        <v>4500000000</v>
       </c>
       <c r="L338" s="1" t="n">
-        <v>1209</v>
+        <v>989</v>
       </c>
       <c r="M338" s="1" t="inlineStr">
         <is>
@@ -21933,10 +21933,10 @@
         <v>0</v>
       </c>
       <c r="K339" s="1" t="n">
-        <v>7400000000</v>
+        <v>5800000000</v>
       </c>
       <c r="L339" s="1" t="n">
-        <v>1571</v>
+        <v>1286</v>
       </c>
       <c r="M339" s="1" t="inlineStr">
         <is>
@@ -21969,11 +21969,11 @@
       </c>
       <c r="C340" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +7층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D340" s="1" t="n">
-        <v>2493532</v>
+        <v>2492332</v>
       </c>
       <c r="E340" s="1" t="inlineStr">
         <is>
@@ -21996,10 +21996,10 @@
         <v>0</v>
       </c>
       <c r="K340" s="1" t="n">
-        <v>6700000000</v>
+        <v>5300000000</v>
       </c>
       <c r="L340" s="1" t="n">
-        <v>1430</v>
+        <v>1170</v>
       </c>
       <c r="M340" s="1" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         </is>
       </c>
       <c r="N340" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O340" s="1" t="n">
         <v>0</v>
@@ -22059,10 +22059,10 @@
         <v>0</v>
       </c>
       <c r="K341" s="1" t="n">
-        <v>4400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L341" s="1" t="n">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="M341" s="1" t="inlineStr">
         <is>
@@ -22095,11 +22095,11 @@
       </c>
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +6층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D342" s="1" t="n">
-        <v>2492934</v>
+        <v>2492332</v>
       </c>
       <c r="E342" s="1" t="inlineStr">
         <is>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="K342" s="1" t="n">
-        <v>12000000000</v>
+        <v>8900000000</v>
       </c>
       <c r="L342" s="1" t="n">
-        <v>2417</v>
+        <v>1978</v>
       </c>
       <c r="M342" s="1" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         </is>
       </c>
       <c r="N342" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O342" s="1" t="n">
         <v>0</v>
@@ -22185,10 +22185,10 @@
         <v>0</v>
       </c>
       <c r="K343" s="1" t="n">
-        <v>4400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L343" s="1" t="n">
-        <v>930</v>
+        <v>761</v>
       </c>
       <c r="M343" s="1" t="inlineStr">
         <is>
@@ -22248,10 +22248,10 @@
         <v>0</v>
       </c>
       <c r="K344" s="1" t="n">
-        <v>7400000000</v>
+        <v>5800000000</v>
       </c>
       <c r="L344" s="1" t="n">
-        <v>1571</v>
+        <v>1286</v>
       </c>
       <c r="M344" s="1" t="inlineStr">
         <is>
@@ -22311,10 +22311,10 @@
         <v>0</v>
       </c>
       <c r="K345" s="1" t="n">
-        <v>5700000000</v>
+        <v>4500000000</v>
       </c>
       <c r="L345" s="1" t="n">
-        <v>1209</v>
+        <v>989</v>
       </c>
       <c r="M345" s="1" t="inlineStr">
         <is>
@@ -22443,10 +22443,10 @@
         <v>0</v>
       </c>
       <c r="K347" s="1" t="n">
-        <v>13000000000</v>
+        <v>9900000000</v>
       </c>
       <c r="L347" s="1" t="n">
-        <v>1970</v>
+        <v>1650</v>
       </c>
       <c r="M347" s="1" t="inlineStr">
         <is>
@@ -22506,10 +22506,10 @@
         <v>0</v>
       </c>
       <c r="K348" s="1" t="n">
-        <v>16000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="L348" s="1" t="n">
-        <v>2561</v>
+        <v>2145</v>
       </c>
       <c r="M348" s="1" t="inlineStr">
         <is>
@@ -22569,10 +22569,10 @@
         <v>0</v>
       </c>
       <c r="K349" s="1" t="n">
-        <v>21000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="L349" s="1" t="n">
-        <v>3330</v>
+        <v>2789</v>
       </c>
       <c r="M349" s="1" t="inlineStr">
         <is>
@@ -22632,10 +22632,10 @@
         <v>0</v>
       </c>
       <c r="K350" s="1" t="n">
-        <v>21000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="L350" s="1" t="n">
-        <v>3330</v>
+        <v>2789</v>
       </c>
       <c r="M350" s="1" t="inlineStr">
         <is>
@@ -22695,10 +22695,10 @@
         <v>0</v>
       </c>
       <c r="K351" s="1" t="n">
-        <v>28000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="L351" s="1" t="n">
-        <v>4329</v>
+        <v>3626</v>
       </c>
       <c r="M351" s="1" t="inlineStr">
         <is>
@@ -22758,10 +22758,10 @@
         <v>0</v>
       </c>
       <c r="K352" s="1" t="n">
-        <v>21000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="L352" s="1" t="n">
-        <v>3330</v>
+        <v>2789</v>
       </c>
       <c r="M352" s="1" t="inlineStr">
         <is>
@@ -22821,10 +22821,10 @@
         <v>0</v>
       </c>
       <c r="K353" s="1" t="n">
-        <v>28000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="L353" s="1" t="n">
-        <v>4329</v>
+        <v>3626</v>
       </c>
       <c r="M353" s="1" t="inlineStr">
         <is>
@@ -22884,10 +22884,10 @@
         <v>0</v>
       </c>
       <c r="K354" s="1" t="n">
-        <v>28000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="L354" s="1" t="n">
-        <v>4329</v>
+        <v>3626</v>
       </c>
       <c r="M354" s="1" t="inlineStr">
         <is>
@@ -22947,10 +22947,10 @@
         <v>0</v>
       </c>
       <c r="K355" s="1" t="n">
-        <v>13000000000</v>
+        <v>9900000000</v>
       </c>
       <c r="L355" s="1" t="n">
-        <v>1970</v>
+        <v>1650</v>
       </c>
       <c r="M355" s="1" t="inlineStr">
         <is>
@@ -23010,10 +23010,10 @@
         <v>0</v>
       </c>
       <c r="K356" s="1" t="n">
-        <v>16000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="L356" s="1" t="n">
-        <v>2561</v>
+        <v>2145</v>
       </c>
       <c r="M356" s="1" t="inlineStr">
         <is>
@@ -23073,10 +23073,10 @@
         <v>0</v>
       </c>
       <c r="K357" s="1" t="n">
-        <v>21000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="L357" s="1" t="n">
-        <v>3330</v>
+        <v>2789</v>
       </c>
       <c r="M357" s="1" t="inlineStr">
         <is>
@@ -23136,10 +23136,10 @@
         <v>0</v>
       </c>
       <c r="K358" s="1" t="n">
-        <v>21000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="L358" s="1" t="n">
-        <v>3330</v>
+        <v>2789</v>
       </c>
       <c r="M358" s="1" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         <v>0</v>
       </c>
       <c r="K359" s="1" t="n">
-        <v>21000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="L359" s="1" t="n">
-        <v>3330</v>
+        <v>2789</v>
       </c>
       <c r="M359" s="1" t="inlineStr">
         <is>
@@ -23262,10 +23262,10 @@
         <v>0</v>
       </c>
       <c r="K360" s="1" t="n">
-        <v>28000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="L360" s="1" t="n">
-        <v>4329</v>
+        <v>3626</v>
       </c>
       <c r="M360" s="1" t="inlineStr">
         <is>
@@ -23325,10 +23325,10 @@
         <v>0</v>
       </c>
       <c r="K361" s="1" t="n">
-        <v>36000000000</v>
+        <v>29000000000</v>
       </c>
       <c r="L361" s="1" t="n">
-        <v>5627</v>
+        <v>4713</v>
       </c>
       <c r="M361" s="1" t="inlineStr">
         <is>
@@ -23388,10 +23388,10 @@
         <v>0</v>
       </c>
       <c r="K362" s="1" t="n">
-        <v>28000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="L362" s="1" t="n">
-        <v>4329</v>
+        <v>3626</v>
       </c>
       <c r="M362" s="1" t="inlineStr">
         <is>
@@ -23451,10 +23451,10 @@
         <v>0</v>
       </c>
       <c r="K363" s="1" t="n">
-        <v>13000000000</v>
+        <v>9900000000</v>
       </c>
       <c r="L363" s="1" t="n">
-        <v>1970</v>
+        <v>1650</v>
       </c>
       <c r="M363" s="1" t="inlineStr">
         <is>
@@ -23514,10 +23514,10 @@
         <v>0</v>
       </c>
       <c r="K364" s="1" t="n">
-        <v>16000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="L364" s="1" t="n">
-        <v>2561</v>
+        <v>2145</v>
       </c>
       <c r="M364" s="1" t="inlineStr">
         <is>
@@ -23577,10 +23577,10 @@
         <v>0</v>
       </c>
       <c r="K365" s="1" t="n">
-        <v>21000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="L365" s="1" t="n">
-        <v>3330</v>
+        <v>2789</v>
       </c>
       <c r="M365" s="1" t="inlineStr">
         <is>
@@ -23640,10 +23640,10 @@
         <v>0</v>
       </c>
       <c r="K366" s="1" t="n">
-        <v>21000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="L366" s="1" t="n">
-        <v>3330</v>
+        <v>2789</v>
       </c>
       <c r="M366" s="1" t="inlineStr">
         <is>
@@ -23703,10 +23703,10 @@
         <v>0</v>
       </c>
       <c r="K367" s="1" t="n">
-        <v>28000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="L367" s="1" t="n">
-        <v>4329</v>
+        <v>3626</v>
       </c>
       <c r="M367" s="1" t="inlineStr">
         <is>
@@ -23766,10 +23766,10 @@
         <v>0</v>
       </c>
       <c r="K368" s="1" t="n">
-        <v>28000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="L368" s="1" t="n">
-        <v>4329</v>
+        <v>3626</v>
       </c>
       <c r="M368" s="1" t="inlineStr">
         <is>
@@ -23829,10 +23829,10 @@
         <v>0</v>
       </c>
       <c r="K369" s="1" t="n">
-        <v>28000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="L369" s="1" t="n">
-        <v>4329</v>
+        <v>3626</v>
       </c>
       <c r="M369" s="1" t="inlineStr">
         <is>
@@ -23892,10 +23892,10 @@
         <v>0</v>
       </c>
       <c r="K370" s="1" t="n">
-        <v>36000000000</v>
+        <v>29000000000</v>
       </c>
       <c r="L370" s="1" t="n">
-        <v>5627</v>
+        <v>4713</v>
       </c>
       <c r="M370" s="1" t="inlineStr">
         <is>
@@ -23955,10 +23955,10 @@
         <v>0</v>
       </c>
       <c r="K371" s="1" t="n">
-        <v>13000000000</v>
+        <v>9900000000</v>
       </c>
       <c r="L371" s="1" t="n">
-        <v>1970</v>
+        <v>1650</v>
       </c>
       <c r="M371" s="1" t="inlineStr">
         <is>
@@ -24018,10 +24018,10 @@
         <v>0</v>
       </c>
       <c r="K372" s="1" t="n">
-        <v>16000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="L372" s="1" t="n">
-        <v>2561</v>
+        <v>2145</v>
       </c>
       <c r="M372" s="1" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="K373" s="1" t="n">
-        <v>21000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="L373" s="1" t="n">
-        <v>3330</v>
+        <v>2789</v>
       </c>
       <c r="M373" s="1" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>0</v>
       </c>
       <c r="K374" s="1" t="n">
-        <v>21000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="L374" s="1" t="n">
-        <v>3330</v>
+        <v>2789</v>
       </c>
       <c r="M374" s="1" t="inlineStr">
         <is>
@@ -24207,10 +24207,10 @@
         <v>0</v>
       </c>
       <c r="K375" s="1" t="n">
-        <v>28000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="L375" s="1" t="n">
-        <v>4329</v>
+        <v>3626</v>
       </c>
       <c r="M375" s="1" t="inlineStr">
         <is>
@@ -24270,10 +24270,10 @@
         <v>0</v>
       </c>
       <c r="K376" s="1" t="n">
-        <v>28000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="L376" s="1" t="n">
-        <v>4329</v>
+        <v>3626</v>
       </c>
       <c r="M376" s="1" t="inlineStr">
         <is>
@@ -24333,10 +24333,10 @@
         <v>0</v>
       </c>
       <c r="K377" s="1" t="n">
-        <v>36000000000</v>
+        <v>29000000000</v>
       </c>
       <c r="L377" s="1" t="n">
-        <v>5627</v>
+        <v>4713</v>
       </c>
       <c r="M377" s="1" t="inlineStr">
         <is>
@@ -24369,11 +24369,11 @@
       </c>
       <c r="C378" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D378" s="1" t="n">
-        <v>2493332</v>
+        <v>2492332</v>
       </c>
       <c r="E378" s="1" t="inlineStr">
         <is>
@@ -24396,10 +24396,10 @@
         <v>0</v>
       </c>
       <c r="K378" s="1" t="n">
-        <v>32000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="L378" s="1" t="n">
-        <v>5122</v>
+        <v>4290</v>
       </c>
       <c r="M378" s="1" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         </is>
       </c>
       <c r="N378" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O378" s="1" t="n">
         <v>0</v>
@@ -24459,10 +24459,10 @@
         <v>0</v>
       </c>
       <c r="K379" s="1" t="n">
-        <v>42000000000</v>
+        <v>34000000000</v>
       </c>
       <c r="L379" s="1" t="n">
-        <v>6659</v>
+        <v>5578</v>
       </c>
       <c r="M379" s="1" t="inlineStr">
         <is>
@@ -24495,11 +24495,11 @@
       </c>
       <c r="C380" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D380" s="1" t="n">
-        <v>2493332</v>
+        <v>2492332</v>
       </c>
       <c r="E380" s="1" t="inlineStr">
         <is>
@@ -24522,10 +24522,10 @@
         <v>0</v>
       </c>
       <c r="K380" s="1" t="n">
-        <v>55000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="L380" s="1" t="n">
-        <v>8657</v>
+        <v>7251</v>
       </c>
       <c r="M380" s="1" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         </is>
       </c>
       <c r="N380" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O380" s="1" t="n">
         <v>0</v>
@@ -24585,10 +24585,10 @@
         <v>0</v>
       </c>
       <c r="K381" s="1" t="n">
-        <v>21000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="L381" s="1" t="n">
-        <v>3330</v>
+        <v>2789</v>
       </c>
       <c r="M381" s="1" t="inlineStr">
         <is>
@@ -24648,10 +24648,10 @@
         <v>0</v>
       </c>
       <c r="K382" s="1" t="n">
-        <v>36000000000</v>
+        <v>29000000000</v>
       </c>
       <c r="L382" s="1" t="n">
-        <v>5627</v>
+        <v>4713</v>
       </c>
       <c r="M382" s="1" t="inlineStr">
         <is>
@@ -24711,10 +24711,10 @@
         <v>0</v>
       </c>
       <c r="K383" s="1" t="n">
-        <v>28000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="L383" s="1" t="n">
-        <v>4329</v>
+        <v>3626</v>
       </c>
       <c r="M383" s="1" t="inlineStr">
         <is>
@@ -24843,10 +24843,10 @@
         <v>0</v>
       </c>
       <c r="K385" s="1" t="n">
-        <v>36000000000</v>
+        <v>29000000000</v>
       </c>
       <c r="L385" s="1" t="n">
-        <v>4500</v>
+        <v>3780</v>
       </c>
       <c r="M385" s="1" t="inlineStr">
         <is>
@@ -24906,10 +24906,10 @@
         <v>0</v>
       </c>
       <c r="K386" s="1" t="n">
-        <v>46000000000</v>
+        <v>37000000000</v>
       </c>
       <c r="L386" s="1" t="n">
-        <v>5850</v>
+        <v>4914</v>
       </c>
       <c r="M386" s="1" t="inlineStr">
         <is>
@@ -24969,10 +24969,10 @@
         <v>0</v>
       </c>
       <c r="K387" s="1" t="n">
-        <v>60000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="L387" s="1" t="n">
-        <v>7606</v>
+        <v>6389</v>
       </c>
       <c r="M387" s="1" t="inlineStr">
         <is>
@@ -25032,10 +25032,10 @@
         <v>0</v>
       </c>
       <c r="K388" s="1" t="n">
-        <v>60000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="L388" s="1" t="n">
-        <v>7606</v>
+        <v>6389</v>
       </c>
       <c r="M388" s="1" t="inlineStr">
         <is>
@@ -25095,10 +25095,10 @@
         <v>0</v>
       </c>
       <c r="K389" s="1" t="n">
-        <v>78000000000</v>
+        <v>63000000000</v>
       </c>
       <c r="L389" s="1" t="n">
-        <v>9887</v>
+        <v>8305</v>
       </c>
       <c r="M389" s="1" t="inlineStr">
         <is>
@@ -25158,10 +25158,10 @@
         <v>0</v>
       </c>
       <c r="K390" s="1" t="n">
-        <v>60000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="L390" s="1" t="n">
-        <v>7606</v>
+        <v>6389</v>
       </c>
       <c r="M390" s="1" t="inlineStr">
         <is>
@@ -25221,10 +25221,10 @@
         <v>0</v>
       </c>
       <c r="K391" s="1" t="n">
-        <v>78000000000</v>
+        <v>63000000000</v>
       </c>
       <c r="L391" s="1" t="n">
-        <v>9887</v>
+        <v>8305</v>
       </c>
       <c r="M391" s="1" t="inlineStr">
         <is>
@@ -25284,10 +25284,10 @@
         <v>0</v>
       </c>
       <c r="K392" s="1" t="n">
-        <v>78000000000</v>
+        <v>63000000000</v>
       </c>
       <c r="L392" s="1" t="n">
-        <v>9887</v>
+        <v>8305</v>
       </c>
       <c r="M392" s="1" t="inlineStr">
         <is>
@@ -25347,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="K393" s="1" t="n">
-        <v>36000000000</v>
+        <v>29000000000</v>
       </c>
       <c r="L393" s="1" t="n">
-        <v>4500</v>
+        <v>3780</v>
       </c>
       <c r="M393" s="1" t="inlineStr">
         <is>
@@ -25410,10 +25410,10 @@
         <v>0</v>
       </c>
       <c r="K394" s="1" t="n">
-        <v>46000000000</v>
+        <v>37000000000</v>
       </c>
       <c r="L394" s="1" t="n">
-        <v>5850</v>
+        <v>4914</v>
       </c>
       <c r="M394" s="1" t="inlineStr">
         <is>
@@ -25473,10 +25473,10 @@
         <v>0</v>
       </c>
       <c r="K395" s="1" t="n">
-        <v>60000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="L395" s="1" t="n">
-        <v>7606</v>
+        <v>6389</v>
       </c>
       <c r="M395" s="1" t="inlineStr">
         <is>
@@ -25536,10 +25536,10 @@
         <v>0</v>
       </c>
       <c r="K396" s="1" t="n">
-        <v>60000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="L396" s="1" t="n">
-        <v>7606</v>
+        <v>6389</v>
       </c>
       <c r="M396" s="1" t="inlineStr">
         <is>
@@ -25599,10 +25599,10 @@
         <v>0</v>
       </c>
       <c r="K397" s="1" t="n">
-        <v>60000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="L397" s="1" t="n">
-        <v>7606</v>
+        <v>6389</v>
       </c>
       <c r="M397" s="1" t="inlineStr">
         <is>
@@ -25662,10 +25662,10 @@
         <v>0</v>
       </c>
       <c r="K398" s="1" t="n">
-        <v>78000000000</v>
+        <v>63000000000</v>
       </c>
       <c r="L398" s="1" t="n">
-        <v>9887</v>
+        <v>8305</v>
       </c>
       <c r="M398" s="1" t="inlineStr">
         <is>
@@ -25725,10 +25725,10 @@
         <v>0</v>
       </c>
       <c r="K399" s="1" t="n">
-        <v>110000000000</v>
+        <v>81000000000</v>
       </c>
       <c r="L399" s="1" t="n">
-        <v>12853</v>
+        <v>10797</v>
       </c>
       <c r="M399" s="1" t="inlineStr">
         <is>
@@ -25788,10 +25788,10 @@
         <v>0</v>
       </c>
       <c r="K400" s="1" t="n">
-        <v>78000000000</v>
+        <v>63000000000</v>
       </c>
       <c r="L400" s="1" t="n">
-        <v>9887</v>
+        <v>8305</v>
       </c>
       <c r="M400" s="1" t="inlineStr">
         <is>
@@ -25851,10 +25851,10 @@
         <v>0</v>
       </c>
       <c r="K401" s="1" t="n">
-        <v>36000000000</v>
+        <v>29000000000</v>
       </c>
       <c r="L401" s="1" t="n">
-        <v>4500</v>
+        <v>3780</v>
       </c>
       <c r="M401" s="1" t="inlineStr">
         <is>
@@ -25914,10 +25914,10 @@
         <v>0</v>
       </c>
       <c r="K402" s="1" t="n">
-        <v>46000000000</v>
+        <v>37000000000</v>
       </c>
       <c r="L402" s="1" t="n">
-        <v>5850</v>
+        <v>4914</v>
       </c>
       <c r="M402" s="1" t="inlineStr">
         <is>
@@ -25977,10 +25977,10 @@
         <v>0</v>
       </c>
       <c r="K403" s="1" t="n">
-        <v>60000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="L403" s="1" t="n">
-        <v>7606</v>
+        <v>6389</v>
       </c>
       <c r="M403" s="1" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>0</v>
       </c>
       <c r="K404" s="1" t="n">
-        <v>60000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="L404" s="1" t="n">
-        <v>7606</v>
+        <v>6389</v>
       </c>
       <c r="M404" s="1" t="inlineStr">
         <is>
@@ -26103,10 +26103,10 @@
         <v>0</v>
       </c>
       <c r="K405" s="1" t="n">
-        <v>78000000000</v>
+        <v>63000000000</v>
       </c>
       <c r="L405" s="1" t="n">
-        <v>9887</v>
+        <v>8305</v>
       </c>
       <c r="M405" s="1" t="inlineStr">
         <is>
@@ -26166,10 +26166,10 @@
         <v>0</v>
       </c>
       <c r="K406" s="1" t="n">
-        <v>78000000000</v>
+        <v>63000000000</v>
       </c>
       <c r="L406" s="1" t="n">
-        <v>9887</v>
+        <v>8305</v>
       </c>
       <c r="M406" s="1" t="inlineStr">
         <is>
@@ -26229,10 +26229,10 @@
         <v>0</v>
       </c>
       <c r="K407" s="1" t="n">
-        <v>78000000000</v>
+        <v>63000000000</v>
       </c>
       <c r="L407" s="1" t="n">
-        <v>9887</v>
+        <v>8305</v>
       </c>
       <c r="M407" s="1" t="inlineStr">
         <is>
@@ -26292,10 +26292,10 @@
         <v>0</v>
       </c>
       <c r="K408" s="1" t="n">
-        <v>110000000000</v>
+        <v>81000000000</v>
       </c>
       <c r="L408" s="1" t="n">
-        <v>12853</v>
+        <v>10797</v>
       </c>
       <c r="M408" s="1" t="inlineStr">
         <is>
@@ -26355,10 +26355,10 @@
         <v>0</v>
       </c>
       <c r="K409" s="1" t="n">
-        <v>36000000000</v>
+        <v>29000000000</v>
       </c>
       <c r="L409" s="1" t="n">
-        <v>4500</v>
+        <v>3780</v>
       </c>
       <c r="M409" s="1" t="inlineStr">
         <is>
@@ -26418,10 +26418,10 @@
         <v>0</v>
       </c>
       <c r="K410" s="1" t="n">
-        <v>46000000000</v>
+        <v>37000000000</v>
       </c>
       <c r="L410" s="1" t="n">
-        <v>5850</v>
+        <v>4914</v>
       </c>
       <c r="M410" s="1" t="inlineStr">
         <is>
@@ -26481,10 +26481,10 @@
         <v>0</v>
       </c>
       <c r="K411" s="1" t="n">
-        <v>60000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="L411" s="1" t="n">
-        <v>7606</v>
+        <v>6389</v>
       </c>
       <c r="M411" s="1" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>0</v>
       </c>
       <c r="K412" s="1" t="n">
-        <v>60000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="L412" s="1" t="n">
-        <v>7606</v>
+        <v>6389</v>
       </c>
       <c r="M412" s="1" t="inlineStr">
         <is>
@@ -26607,10 +26607,10 @@
         <v>0</v>
       </c>
       <c r="K413" s="1" t="n">
-        <v>78000000000</v>
+        <v>63000000000</v>
       </c>
       <c r="L413" s="1" t="n">
-        <v>9887</v>
+        <v>8305</v>
       </c>
       <c r="M413" s="1" t="inlineStr">
         <is>
@@ -26670,10 +26670,10 @@
         <v>0</v>
       </c>
       <c r="K414" s="1" t="n">
-        <v>78000000000</v>
+        <v>63000000000</v>
       </c>
       <c r="L414" s="1" t="n">
-        <v>9887</v>
+        <v>8305</v>
       </c>
       <c r="M414" s="1" t="inlineStr">
         <is>
@@ -26733,10 +26733,10 @@
         <v>0</v>
       </c>
       <c r="K415" s="1" t="n">
-        <v>110000000000</v>
+        <v>81000000000</v>
       </c>
       <c r="L415" s="1" t="n">
-        <v>12853</v>
+        <v>10797</v>
       </c>
       <c r="M415" s="1" t="inlineStr">
         <is>
@@ -26769,11 +26769,11 @@
       </c>
       <c r="C416" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D416" s="1" t="n">
-        <v>2493332</v>
+        <v>2492332</v>
       </c>
       <c r="E416" s="1" t="inlineStr">
         <is>
@@ -26796,10 +26796,10 @@
         <v>0</v>
       </c>
       <c r="K416" s="1" t="n">
-        <v>92000000000</v>
+        <v>74000000000</v>
       </c>
       <c r="L416" s="1" t="n">
-        <v>11700</v>
+        <v>9828</v>
       </c>
       <c r="M416" s="1" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         </is>
       </c>
       <c r="N416" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O416" s="1" t="n">
         <v>0</v>
@@ -26859,10 +26859,10 @@
         <v>0</v>
       </c>
       <c r="K417" s="1" t="n">
-        <v>60000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="L417" s="1" t="n">
-        <v>7606</v>
+        <v>6389</v>
       </c>
       <c r="M417" s="1" t="inlineStr">
         <is>
@@ -26895,11 +26895,11 @@
       </c>
       <c r="C418" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D418" s="1" t="n">
-        <v>2493332</v>
+        <v>2492332</v>
       </c>
       <c r="E418" s="1" t="inlineStr">
         <is>
@@ -26922,10 +26922,10 @@
         <v>0</v>
       </c>
       <c r="K418" s="1" t="n">
-        <v>160000000000</v>
+        <v>130000000000</v>
       </c>
       <c r="L418" s="1" t="n">
-        <v>19773</v>
+        <v>16610</v>
       </c>
       <c r="M418" s="1" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         </is>
       </c>
       <c r="N418" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O418" s="1" t="n">
         <v>0</v>
@@ -26985,10 +26985,10 @@
         <v>0</v>
       </c>
       <c r="K419" s="1" t="n">
-        <v>60000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="L419" s="1" t="n">
-        <v>7606</v>
+        <v>6389</v>
       </c>
       <c r="M419" s="1" t="inlineStr">
         <is>
@@ -27048,10 +27048,10 @@
         <v>0</v>
       </c>
       <c r="K420" s="1" t="n">
-        <v>110000000000</v>
+        <v>81000000000</v>
       </c>
       <c r="L420" s="1" t="n">
-        <v>12853</v>
+        <v>10797</v>
       </c>
       <c r="M420" s="1" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         <v>0</v>
       </c>
       <c r="K421" s="1" t="n">
-        <v>78000000000</v>
+        <v>63000000000</v>
       </c>
       <c r="L421" s="1" t="n">
-        <v>9887</v>
+        <v>8305</v>
       </c>
       <c r="M421" s="1" t="inlineStr">
         <is>
@@ -27243,10 +27243,10 @@
         <v>0</v>
       </c>
       <c r="K423" s="1" t="n">
-        <v>130000000000</v>
+        <v>110000000000</v>
       </c>
       <c r="L423" s="1" t="n">
-        <v>12710</v>
+        <v>10760</v>
       </c>
       <c r="M423" s="1" t="inlineStr">
         <is>
@@ -27306,10 +27306,10 @@
         <v>0</v>
       </c>
       <c r="K424" s="1" t="n">
-        <v>170000000000</v>
+        <v>140000000000</v>
       </c>
       <c r="L424" s="1" t="n">
-        <v>16523</v>
+        <v>13988</v>
       </c>
       <c r="M424" s="1" t="inlineStr">
         <is>
@@ -27369,10 +27369,10 @@
         <v>0</v>
       </c>
       <c r="K425" s="1" t="n">
-        <v>220000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L425" s="1" t="n">
-        <v>21480</v>
+        <v>18185</v>
       </c>
       <c r="M425" s="1" t="inlineStr">
         <is>
@@ -27432,10 +27432,10 @@
         <v>0</v>
       </c>
       <c r="K426" s="1" t="n">
-        <v>220000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L426" s="1" t="n">
-        <v>21480</v>
+        <v>18185</v>
       </c>
       <c r="M426" s="1" t="inlineStr">
         <is>
@@ -27495,10 +27495,10 @@
         <v>0</v>
       </c>
       <c r="K427" s="1" t="n">
-        <v>280000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="L427" s="1" t="n">
-        <v>27924</v>
+        <v>23640</v>
       </c>
       <c r="M427" s="1" t="inlineStr">
         <is>
@@ -27558,10 +27558,10 @@
         <v>0</v>
       </c>
       <c r="K428" s="1" t="n">
-        <v>220000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L428" s="1" t="n">
-        <v>21480</v>
+        <v>18185</v>
       </c>
       <c r="M428" s="1" t="inlineStr">
         <is>
@@ -27621,10 +27621,10 @@
         <v>0</v>
       </c>
       <c r="K429" s="1" t="n">
-        <v>280000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="L429" s="1" t="n">
-        <v>27924</v>
+        <v>23640</v>
       </c>
       <c r="M429" s="1" t="inlineStr">
         <is>
@@ -27684,10 +27684,10 @@
         <v>0</v>
       </c>
       <c r="K430" s="1" t="n">
-        <v>280000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="L430" s="1" t="n">
-        <v>27924</v>
+        <v>23640</v>
       </c>
       <c r="M430" s="1" t="inlineStr">
         <is>
@@ -27747,10 +27747,10 @@
         <v>0</v>
       </c>
       <c r="K431" s="1" t="n">
-        <v>130000000000</v>
+        <v>110000000000</v>
       </c>
       <c r="L431" s="1" t="n">
-        <v>12710</v>
+        <v>10760</v>
       </c>
       <c r="M431" s="1" t="inlineStr">
         <is>
@@ -27810,10 +27810,10 @@
         <v>0</v>
       </c>
       <c r="K432" s="1" t="n">
-        <v>170000000000</v>
+        <v>140000000000</v>
       </c>
       <c r="L432" s="1" t="n">
-        <v>16523</v>
+        <v>13988</v>
       </c>
       <c r="M432" s="1" t="inlineStr">
         <is>
@@ -27873,10 +27873,10 @@
         <v>0</v>
       </c>
       <c r="K433" s="1" t="n">
-        <v>220000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L433" s="1" t="n">
-        <v>21480</v>
+        <v>18185</v>
       </c>
       <c r="M433" s="1" t="inlineStr">
         <is>
@@ -27936,10 +27936,10 @@
         <v>0</v>
       </c>
       <c r="K434" s="1" t="n">
-        <v>430000000000</v>
+        <v>350000000000</v>
       </c>
       <c r="L434" s="1" t="n">
-        <v>42960</v>
+        <v>36369</v>
       </c>
       <c r="M434" s="1" t="inlineStr">
         <is>
@@ -27999,10 +27999,10 @@
         <v>0</v>
       </c>
       <c r="K435" s="1" t="n">
-        <v>220000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L435" s="1" t="n">
-        <v>21480</v>
+        <v>18185</v>
       </c>
       <c r="M435" s="1" t="inlineStr">
         <is>
@@ -28062,10 +28062,10 @@
         <v>0</v>
       </c>
       <c r="K436" s="1" t="n">
-        <v>550000000000</v>
+        <v>450000000000</v>
       </c>
       <c r="L436" s="1" t="n">
-        <v>55848</v>
+        <v>47280</v>
       </c>
       <c r="M436" s="1" t="inlineStr">
         <is>
@@ -28125,10 +28125,10 @@
         <v>0</v>
       </c>
       <c r="K437" s="1" t="n">
-        <v>360000000000</v>
+        <v>290000000000</v>
       </c>
       <c r="L437" s="1" t="n">
-        <v>36302</v>
+        <v>30732</v>
       </c>
       <c r="M437" s="1" t="inlineStr">
         <is>
@@ -28188,10 +28188,10 @@
         <v>0</v>
       </c>
       <c r="K438" s="1" t="n">
-        <v>550000000000</v>
+        <v>450000000000</v>
       </c>
       <c r="L438" s="1" t="n">
-        <v>55848</v>
+        <v>47280</v>
       </c>
       <c r="M438" s="1" t="inlineStr">
         <is>
@@ -28251,10 +28251,10 @@
         <v>0</v>
       </c>
       <c r="K439" s="1" t="n">
-        <v>130000000000</v>
+        <v>110000000000</v>
       </c>
       <c r="L439" s="1" t="n">
-        <v>12710</v>
+        <v>10760</v>
       </c>
       <c r="M439" s="1" t="inlineStr">
         <is>
@@ -28314,10 +28314,10 @@
         <v>0</v>
       </c>
       <c r="K440" s="1" t="n">
-        <v>170000000000</v>
+        <v>140000000000</v>
       </c>
       <c r="L440" s="1" t="n">
-        <v>16523</v>
+        <v>13988</v>
       </c>
       <c r="M440" s="1" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>0</v>
       </c>
       <c r="K441" s="1" t="n">
-        <v>220000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L441" s="1" t="n">
-        <v>21480</v>
+        <v>18185</v>
       </c>
       <c r="M441" s="1" t="inlineStr">
         <is>
@@ -28440,10 +28440,10 @@
         <v>0</v>
       </c>
       <c r="K442" s="1" t="n">
-        <v>220000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L442" s="1" t="n">
-        <v>21480</v>
+        <v>18185</v>
       </c>
       <c r="M442" s="1" t="inlineStr">
         <is>
@@ -28503,10 +28503,10 @@
         <v>0</v>
       </c>
       <c r="K443" s="1" t="n">
-        <v>280000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="L443" s="1" t="n">
-        <v>27924</v>
+        <v>23640</v>
       </c>
       <c r="M443" s="1" t="inlineStr">
         <is>
@@ -28566,10 +28566,10 @@
         <v>0</v>
       </c>
       <c r="K444" s="1" t="n">
-        <v>280000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="L444" s="1" t="n">
-        <v>27924</v>
+        <v>23640</v>
       </c>
       <c r="M444" s="1" t="inlineStr">
         <is>
@@ -28629,10 +28629,10 @@
         <v>0</v>
       </c>
       <c r="K445" s="1" t="n">
-        <v>280000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="L445" s="1" t="n">
-        <v>27924</v>
+        <v>23640</v>
       </c>
       <c r="M445" s="1" t="inlineStr">
         <is>
@@ -28692,10 +28692,10 @@
         <v>0</v>
       </c>
       <c r="K446" s="1" t="n">
-        <v>360000000000</v>
+        <v>290000000000</v>
       </c>
       <c r="L446" s="1" t="n">
-        <v>36302</v>
+        <v>30732</v>
       </c>
       <c r="M446" s="1" t="inlineStr">
         <is>
@@ -28755,10 +28755,10 @@
         <v>0</v>
       </c>
       <c r="K447" s="1" t="n">
-        <v>130000000000</v>
+        <v>110000000000</v>
       </c>
       <c r="L447" s="1" t="n">
-        <v>12710</v>
+        <v>10760</v>
       </c>
       <c r="M447" s="1" t="inlineStr">
         <is>
@@ -28818,10 +28818,10 @@
         <v>0</v>
       </c>
       <c r="K448" s="1" t="n">
-        <v>170000000000</v>
+        <v>140000000000</v>
       </c>
       <c r="L448" s="1" t="n">
-        <v>16523</v>
+        <v>13988</v>
       </c>
       <c r="M448" s="1" t="inlineStr">
         <is>
@@ -28881,10 +28881,10 @@
         <v>0</v>
       </c>
       <c r="K449" s="1" t="n">
-        <v>220000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L449" s="1" t="n">
-        <v>21480</v>
+        <v>18185</v>
       </c>
       <c r="M449" s="1" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>0</v>
       </c>
       <c r="K450" s="1" t="n">
-        <v>220000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L450" s="1" t="n">
-        <v>21480</v>
+        <v>18185</v>
       </c>
       <c r="M450" s="1" t="inlineStr">
         <is>
@@ -29007,10 +29007,10 @@
         <v>0</v>
       </c>
       <c r="K451" s="1" t="n">
-        <v>280000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="L451" s="1" t="n">
-        <v>27924</v>
+        <v>23640</v>
       </c>
       <c r="M451" s="1" t="inlineStr">
         <is>
@@ -29070,10 +29070,10 @@
         <v>0</v>
       </c>
       <c r="K452" s="1" t="n">
-        <v>280000000000</v>
+        <v>230000000000</v>
       </c>
       <c r="L452" s="1" t="n">
-        <v>27924</v>
+        <v>23640</v>
       </c>
       <c r="M452" s="1" t="inlineStr">
         <is>
@@ -29133,10 +29133,10 @@
         <v>0</v>
       </c>
       <c r="K453" s="1" t="n">
-        <v>360000000000</v>
+        <v>290000000000</v>
       </c>
       <c r="L453" s="1" t="n">
-        <v>36302</v>
+        <v>30732</v>
       </c>
       <c r="M453" s="1" t="inlineStr">
         <is>
@@ -29169,11 +29169,11 @@
       </c>
       <c r="C454" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D454" s="1" t="n">
-        <v>2493332</v>
+        <v>2492332</v>
       </c>
       <c r="E454" s="1" t="inlineStr">
         <is>
@@ -29196,10 +29196,10 @@
         <v>0</v>
       </c>
       <c r="K454" s="1" t="n">
-        <v>330000000000</v>
+        <v>270000000000</v>
       </c>
       <c r="L454" s="1" t="n">
-        <v>33046</v>
+        <v>27976</v>
       </c>
       <c r="M454" s="1" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         </is>
       </c>
       <c r="N454" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O454" s="1" t="n">
         <v>0</v>
@@ -29259,10 +29259,10 @@
         <v>0</v>
       </c>
       <c r="K455" s="1" t="n">
-        <v>220000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L455" s="1" t="n">
-        <v>21480</v>
+        <v>18185</v>
       </c>
       <c r="M455" s="1" t="inlineStr">
         <is>
@@ -29295,11 +29295,11 @@
       </c>
       <c r="C456" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D456" s="1" t="n">
-        <v>2493332</v>
+        <v>2492332</v>
       </c>
       <c r="E456" s="1" t="inlineStr">
         <is>
@@ -29322,10 +29322,10 @@
         <v>0</v>
       </c>
       <c r="K456" s="1" t="n">
-        <v>550000000000</v>
+        <v>450000000000</v>
       </c>
       <c r="L456" s="1" t="n">
-        <v>55848</v>
+        <v>47280</v>
       </c>
       <c r="M456" s="1" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         </is>
       </c>
       <c r="N456" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O456" s="1" t="n">
         <v>0</v>
@@ -29385,10 +29385,10 @@
         <v>0</v>
       </c>
       <c r="K457" s="1" t="n">
-        <v>220000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L457" s="1" t="n">
-        <v>21480</v>
+        <v>18185</v>
       </c>
       <c r="M457" s="1" t="inlineStr">
         <is>
@@ -29448,10 +29448,10 @@
         <v>0</v>
       </c>
       <c r="K458" s="1" t="n">
-        <v>360000000000</v>
+        <v>290000000000</v>
       </c>
       <c r="L458" s="1" t="n">
-        <v>36302</v>
+        <v>30732</v>
       </c>
       <c r="M458" s="1" t="inlineStr">
         <is>
@@ -29511,10 +29511,10 @@
         <v>0</v>
       </c>
       <c r="K459" s="1" t="n">
-        <v>550000000000</v>
+        <v>450000000000</v>
       </c>
       <c r="L459" s="1" t="n">
-        <v>55848</v>
+        <v>47280</v>
       </c>
       <c r="M459" s="1" t="inlineStr">
         <is>
@@ -29643,10 +29643,10 @@
         <v>0</v>
       </c>
       <c r="K461" s="1" t="n">
-        <v>230000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L461" s="1" t="n">
-        <v>19040</v>
+        <v>16130</v>
       </c>
       <c r="M461" s="1" t="inlineStr">
         <is>
@@ -29706,10 +29706,10 @@
         <v>0</v>
       </c>
       <c r="K462" s="1" t="n">
-        <v>290000000000</v>
+        <v>240000000000</v>
       </c>
       <c r="L462" s="1" t="n">
-        <v>24752</v>
+        <v>20969</v>
       </c>
       <c r="M462" s="1" t="inlineStr">
         <is>
@@ -29769,10 +29769,10 @@
         <v>0</v>
       </c>
       <c r="K463" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L463" s="1" t="n">
-        <v>32178</v>
+        <v>27260</v>
       </c>
       <c r="M463" s="1" t="inlineStr">
         <is>
@@ -29832,10 +29832,10 @@
         <v>0</v>
       </c>
       <c r="K464" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L464" s="1" t="n">
-        <v>32178</v>
+        <v>27260</v>
       </c>
       <c r="M464" s="1" t="inlineStr">
         <is>
@@ -29895,10 +29895,10 @@
         <v>0</v>
       </c>
       <c r="K465" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L465" s="1" t="n">
-        <v>41831</v>
+        <v>35438</v>
       </c>
       <c r="M465" s="1" t="inlineStr">
         <is>
@@ -29958,10 +29958,10 @@
         <v>0</v>
       </c>
       <c r="K466" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L466" s="1" t="n">
-        <v>32178</v>
+        <v>27260</v>
       </c>
       <c r="M466" s="1" t="inlineStr">
         <is>
@@ -30021,10 +30021,10 @@
         <v>0</v>
       </c>
       <c r="K467" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L467" s="1" t="n">
-        <v>41831</v>
+        <v>35438</v>
       </c>
       <c r="M467" s="1" t="inlineStr">
         <is>
@@ -30084,10 +30084,10 @@
         <v>0</v>
       </c>
       <c r="K468" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L468" s="1" t="n">
-        <v>41831</v>
+        <v>35438</v>
       </c>
       <c r="M468" s="1" t="inlineStr">
         <is>
@@ -30147,10 +30147,10 @@
         <v>0</v>
       </c>
       <c r="K469" s="1" t="n">
-        <v>230000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L469" s="1" t="n">
-        <v>19040</v>
+        <v>16130</v>
       </c>
       <c r="M469" s="1" t="inlineStr">
         <is>
@@ -30210,10 +30210,10 @@
         <v>0</v>
       </c>
       <c r="K470" s="1" t="n">
-        <v>290000000000</v>
+        <v>240000000000</v>
       </c>
       <c r="L470" s="1" t="n">
-        <v>24752</v>
+        <v>20969</v>
       </c>
       <c r="M470" s="1" t="inlineStr">
         <is>
@@ -30273,10 +30273,10 @@
         <v>0</v>
       </c>
       <c r="K471" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L471" s="1" t="n">
-        <v>32178</v>
+        <v>27260</v>
       </c>
       <c r="M471" s="1" t="inlineStr">
         <is>
@@ -30336,10 +30336,10 @@
         <v>0</v>
       </c>
       <c r="K472" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L472" s="1" t="n">
-        <v>32178</v>
+        <v>27260</v>
       </c>
       <c r="M472" s="1" t="inlineStr">
         <is>
@@ -30399,10 +30399,10 @@
         <v>0</v>
       </c>
       <c r="K473" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L473" s="1" t="n">
-        <v>32178</v>
+        <v>27260</v>
       </c>
       <c r="M473" s="1" t="inlineStr">
         <is>
@@ -30462,10 +30462,10 @@
         <v>0</v>
       </c>
       <c r="K474" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L474" s="1" t="n">
-        <v>41831</v>
+        <v>35438</v>
       </c>
       <c r="M474" s="1" t="inlineStr">
         <is>
@@ -30525,10 +30525,10 @@
         <v>0</v>
       </c>
       <c r="K475" s="1" t="n">
-        <v>640000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L475" s="1" t="n">
-        <v>54381</v>
+        <v>46069</v>
       </c>
       <c r="M475" s="1" t="inlineStr">
         <is>
@@ -30588,10 +30588,10 @@
         <v>0</v>
       </c>
       <c r="K476" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L476" s="1" t="n">
-        <v>41831</v>
+        <v>35438</v>
       </c>
       <c r="M476" s="1" t="inlineStr">
         <is>
@@ -30651,10 +30651,10 @@
         <v>0</v>
       </c>
       <c r="K477" s="1" t="n">
-        <v>230000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L477" s="1" t="n">
-        <v>19040</v>
+        <v>16130</v>
       </c>
       <c r="M477" s="1" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>0</v>
       </c>
       <c r="K478" s="1" t="n">
-        <v>290000000000</v>
+        <v>240000000000</v>
       </c>
       <c r="L478" s="1" t="n">
-        <v>24752</v>
+        <v>20969</v>
       </c>
       <c r="M478" s="1" t="inlineStr">
         <is>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="K479" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L479" s="1" t="n">
-        <v>32178</v>
+        <v>27260</v>
       </c>
       <c r="M479" s="1" t="inlineStr">
         <is>
@@ -30840,10 +30840,10 @@
         <v>0</v>
       </c>
       <c r="K480" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L480" s="1" t="n">
-        <v>32178</v>
+        <v>27260</v>
       </c>
       <c r="M480" s="1" t="inlineStr">
         <is>
@@ -30903,10 +30903,10 @@
         <v>0</v>
       </c>
       <c r="K481" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L481" s="1" t="n">
-        <v>41831</v>
+        <v>35438</v>
       </c>
       <c r="M481" s="1" t="inlineStr">
         <is>
@@ -30966,10 +30966,10 @@
         <v>0</v>
       </c>
       <c r="K482" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L482" s="1" t="n">
-        <v>41831</v>
+        <v>35438</v>
       </c>
       <c r="M482" s="1" t="inlineStr">
         <is>
@@ -31029,10 +31029,10 @@
         <v>0</v>
       </c>
       <c r="K483" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L483" s="1" t="n">
-        <v>41831</v>
+        <v>35438</v>
       </c>
       <c r="M483" s="1" t="inlineStr">
         <is>
@@ -31092,10 +31092,10 @@
         <v>0</v>
       </c>
       <c r="K484" s="1" t="n">
-        <v>640000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L484" s="1" t="n">
-        <v>54381</v>
+        <v>46069</v>
       </c>
       <c r="M484" s="1" t="inlineStr">
         <is>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="K485" s="1" t="n">
-        <v>230000000000</v>
+        <v>180000000000</v>
       </c>
       <c r="L485" s="1" t="n">
-        <v>19040</v>
+        <v>16130</v>
       </c>
       <c r="M485" s="1" t="inlineStr">
         <is>
@@ -31218,10 +31218,10 @@
         <v>0</v>
       </c>
       <c r="K486" s="1" t="n">
-        <v>290000000000</v>
+        <v>240000000000</v>
       </c>
       <c r="L486" s="1" t="n">
-        <v>24752</v>
+        <v>20969</v>
       </c>
       <c r="M486" s="1" t="inlineStr">
         <is>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="K487" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L487" s="1" t="n">
-        <v>32178</v>
+        <v>27260</v>
       </c>
       <c r="M487" s="1" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>0</v>
       </c>
       <c r="K488" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L488" s="1" t="n">
-        <v>32178</v>
+        <v>27260</v>
       </c>
       <c r="M488" s="1" t="inlineStr">
         <is>
@@ -31407,10 +31407,10 @@
         <v>0</v>
       </c>
       <c r="K489" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L489" s="1" t="n">
-        <v>41831</v>
+        <v>35438</v>
       </c>
       <c r="M489" s="1" t="inlineStr">
         <is>
@@ -31470,10 +31470,10 @@
         <v>0</v>
       </c>
       <c r="K490" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L490" s="1" t="n">
-        <v>41831</v>
+        <v>35438</v>
       </c>
       <c r="M490" s="1" t="inlineStr">
         <is>
@@ -31533,10 +31533,10 @@
         <v>0</v>
       </c>
       <c r="K491" s="1" t="n">
-        <v>640000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L491" s="1" t="n">
-        <v>54381</v>
+        <v>46069</v>
       </c>
       <c r="M491" s="1" t="inlineStr">
         <is>
@@ -31569,11 +31569,11 @@
       </c>
       <c r="C492" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D492" s="1" t="n">
-        <v>2493332</v>
+        <v>2492332</v>
       </c>
       <c r="E492" s="1" t="inlineStr">
         <is>
@@ -31596,10 +31596,10 @@
         <v>0</v>
       </c>
       <c r="K492" s="1" t="n">
-        <v>580000000000</v>
+        <v>470000000000</v>
       </c>
       <c r="L492" s="1" t="n">
-        <v>49504</v>
+        <v>41938</v>
       </c>
       <c r="M492" s="1" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         </is>
       </c>
       <c r="N492" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O492" s="1" t="n">
         <v>0</v>
@@ -31659,10 +31659,10 @@
         <v>0</v>
       </c>
       <c r="K493" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L493" s="1" t="n">
-        <v>32178</v>
+        <v>27260</v>
       </c>
       <c r="M493" s="1" t="inlineStr">
         <is>
@@ -31695,11 +31695,11 @@
       </c>
       <c r="C494" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D494" s="1" t="n">
-        <v>2493332</v>
+        <v>2492332</v>
       </c>
       <c r="E494" s="1" t="inlineStr">
         <is>
@@ -31722,10 +31722,10 @@
         <v>0</v>
       </c>
       <c r="K494" s="1" t="n">
-        <v>980000000000</v>
+        <v>800000000000</v>
       </c>
       <c r="L494" s="1" t="n">
-        <v>83662</v>
+        <v>70876</v>
       </c>
       <c r="M494" s="1" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         </is>
       </c>
       <c r="N494" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O494" s="1" t="n">
         <v>0</v>
@@ -31785,10 +31785,10 @@
         <v>0</v>
       </c>
       <c r="K495" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L495" s="1" t="n">
-        <v>32178</v>
+        <v>27260</v>
       </c>
       <c r="M495" s="1" t="inlineStr">
         <is>
@@ -31848,10 +31848,10 @@
         <v>0</v>
       </c>
       <c r="K496" s="1" t="n">
-        <v>640000000000</v>
+        <v>520000000000</v>
       </c>
       <c r="L496" s="1" t="n">
-        <v>54381</v>
+        <v>46069</v>
       </c>
       <c r="M496" s="1" t="inlineStr">
         <is>
@@ -31911,10 +31911,10 @@
         <v>0</v>
       </c>
       <c r="K497" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L497" s="1" t="n">
-        <v>41831</v>
+        <v>35438</v>
       </c>
       <c r="M497" s="1" t="inlineStr">
         <is>
@@ -32043,10 +32043,10 @@
         <v>0</v>
       </c>
       <c r="K499" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L499" s="1" t="n">
-        <v>28550</v>
+        <v>24160</v>
       </c>
       <c r="M499" s="1" t="inlineStr">
         <is>
@@ -32106,10 +32106,10 @@
         <v>0</v>
       </c>
       <c r="K500" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L500" s="1" t="n">
-        <v>37115</v>
+        <v>31408</v>
       </c>
       <c r="M500" s="1" t="inlineStr">
         <is>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="K501" s="1" t="n">
-        <v>630000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L501" s="1" t="n">
-        <v>48250</v>
+        <v>40831</v>
       </c>
       <c r="M501" s="1" t="inlineStr">
         <is>
@@ -32232,10 +32232,10 @@
         <v>0</v>
       </c>
       <c r="K502" s="1" t="n">
-        <v>630000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L502" s="1" t="n">
-        <v>48250</v>
+        <v>40831</v>
       </c>
       <c r="M502" s="1" t="inlineStr">
         <is>
@@ -32295,10 +32295,10 @@
         <v>0</v>
       </c>
       <c r="K503" s="1" t="n">
-        <v>820000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L503" s="1" t="n">
-        <v>62725</v>
+        <v>53080</v>
       </c>
       <c r="M503" s="1" t="inlineStr">
         <is>
@@ -32358,10 +32358,10 @@
         <v>0</v>
       </c>
       <c r="K504" s="1" t="n">
-        <v>630000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L504" s="1" t="n">
-        <v>48250</v>
+        <v>40831</v>
       </c>
       <c r="M504" s="1" t="inlineStr">
         <is>
@@ -32421,10 +32421,10 @@
         <v>0</v>
       </c>
       <c r="K505" s="1" t="n">
-        <v>820000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L505" s="1" t="n">
-        <v>62725</v>
+        <v>53080</v>
       </c>
       <c r="M505" s="1" t="inlineStr">
         <is>
@@ -32484,10 +32484,10 @@
         <v>0</v>
       </c>
       <c r="K506" s="1" t="n">
-        <v>820000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L506" s="1" t="n">
-        <v>62725</v>
+        <v>53080</v>
       </c>
       <c r="M506" s="1" t="inlineStr">
         <is>
@@ -32547,10 +32547,10 @@
         <v>0</v>
       </c>
       <c r="K507" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L507" s="1" t="n">
-        <v>28550</v>
+        <v>24160</v>
       </c>
       <c r="M507" s="1" t="inlineStr">
         <is>
@@ -32610,10 +32610,10 @@
         <v>0</v>
       </c>
       <c r="K508" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L508" s="1" t="n">
-        <v>37115</v>
+        <v>31408</v>
       </c>
       <c r="M508" s="1" t="inlineStr">
         <is>
@@ -32673,10 +32673,10 @@
         <v>0</v>
       </c>
       <c r="K509" s="1" t="n">
-        <v>630000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L509" s="1" t="n">
-        <v>48250</v>
+        <v>40831</v>
       </c>
       <c r="M509" s="1" t="inlineStr">
         <is>
@@ -32736,10 +32736,10 @@
         <v>0</v>
       </c>
       <c r="K510" s="1" t="n">
-        <v>630000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>48250</v>
+        <v>40831</v>
       </c>
       <c r="M510" s="1" t="inlineStr">
         <is>
@@ -32799,10 +32799,10 @@
         <v>0</v>
       </c>
       <c r="K511" s="1" t="n">
-        <v>630000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>48250</v>
+        <v>40831</v>
       </c>
       <c r="M511" s="1" t="inlineStr">
         <is>
@@ -32862,10 +32862,10 @@
         <v>0</v>
       </c>
       <c r="K512" s="1" t="n">
-        <v>820000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>62725</v>
+        <v>53080</v>
       </c>
       <c r="M512" s="1" t="inlineStr">
         <is>
@@ -32925,10 +32925,10 @@
         <v>0</v>
       </c>
       <c r="K513" s="1" t="n">
-        <v>1100000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>81542</v>
+        <v>69004</v>
       </c>
       <c r="M513" s="1" t="inlineStr">
         <is>
@@ -32988,10 +32988,10 @@
         <v>0</v>
       </c>
       <c r="K514" s="1" t="n">
-        <v>820000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>62725</v>
+        <v>53080</v>
       </c>
       <c r="M514" s="1" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>0</v>
       </c>
       <c r="K515" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L515" s="1" t="n">
-        <v>28550</v>
+        <v>24160</v>
       </c>
       <c r="M515" s="1" t="inlineStr">
         <is>
@@ -33114,10 +33114,10 @@
         <v>0</v>
       </c>
       <c r="K516" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L516" s="1" t="n">
-        <v>37115</v>
+        <v>31408</v>
       </c>
       <c r="M516" s="1" t="inlineStr">
         <is>
@@ -33177,10 +33177,10 @@
         <v>0</v>
       </c>
       <c r="K517" s="1" t="n">
-        <v>630000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L517" s="1" t="n">
-        <v>48250</v>
+        <v>40831</v>
       </c>
       <c r="M517" s="1" t="inlineStr">
         <is>
@@ -33240,10 +33240,10 @@
         <v>0</v>
       </c>
       <c r="K518" s="1" t="n">
-        <v>630000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L518" s="1" t="n">
-        <v>48250</v>
+        <v>40831</v>
       </c>
       <c r="M518" s="1" t="inlineStr">
         <is>
@@ -33303,10 +33303,10 @@
         <v>0</v>
       </c>
       <c r="K519" s="1" t="n">
-        <v>820000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L519" s="1" t="n">
-        <v>62725</v>
+        <v>53080</v>
       </c>
       <c r="M519" s="1" t="inlineStr">
         <is>
@@ -33366,10 +33366,10 @@
         <v>0</v>
       </c>
       <c r="K520" s="1" t="n">
-        <v>820000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L520" s="1" t="n">
-        <v>62725</v>
+        <v>53080</v>
       </c>
       <c r="M520" s="1" t="inlineStr">
         <is>
@@ -33429,10 +33429,10 @@
         <v>0</v>
       </c>
       <c r="K521" s="1" t="n">
-        <v>820000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L521" s="1" t="n">
-        <v>62725</v>
+        <v>53080</v>
       </c>
       <c r="M521" s="1" t="inlineStr">
         <is>
@@ -33492,10 +33492,10 @@
         <v>0</v>
       </c>
       <c r="K522" s="1" t="n">
-        <v>1100000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L522" s="1" t="n">
-        <v>81542</v>
+        <v>69004</v>
       </c>
       <c r="M522" s="1" t="inlineStr">
         <is>
@@ -33555,10 +33555,10 @@
         <v>0</v>
       </c>
       <c r="K523" s="1" t="n">
-        <v>380000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L523" s="1" t="n">
-        <v>28550</v>
+        <v>24160</v>
       </c>
       <c r="M523" s="1" t="inlineStr">
         <is>
@@ -33618,10 +33618,10 @@
         <v>0</v>
       </c>
       <c r="K524" s="1" t="n">
-        <v>490000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L524" s="1" t="n">
-        <v>37115</v>
+        <v>31408</v>
       </c>
       <c r="M524" s="1" t="inlineStr">
         <is>
@@ -33681,10 +33681,10 @@
         <v>0</v>
       </c>
       <c r="K525" s="1" t="n">
-        <v>630000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L525" s="1" t="n">
-        <v>48250</v>
+        <v>40831</v>
       </c>
       <c r="M525" s="1" t="inlineStr">
         <is>
@@ -33744,10 +33744,10 @@
         <v>0</v>
       </c>
       <c r="K526" s="1" t="n">
-        <v>630000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L526" s="1" t="n">
-        <v>48250</v>
+        <v>40831</v>
       </c>
       <c r="M526" s="1" t="inlineStr">
         <is>
@@ -33807,10 +33807,10 @@
         <v>0</v>
       </c>
       <c r="K527" s="1" t="n">
-        <v>820000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L527" s="1" t="n">
-        <v>62725</v>
+        <v>53080</v>
       </c>
       <c r="M527" s="1" t="inlineStr">
         <is>
@@ -33870,10 +33870,10 @@
         <v>0</v>
       </c>
       <c r="K528" s="1" t="n">
-        <v>820000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L528" s="1" t="n">
-        <v>62725</v>
+        <v>53080</v>
       </c>
       <c r="M528" s="1" t="inlineStr">
         <is>
@@ -33933,10 +33933,10 @@
         <v>0</v>
       </c>
       <c r="K529" s="1" t="n">
-        <v>1100000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L529" s="1" t="n">
-        <v>81542</v>
+        <v>69004</v>
       </c>
       <c r="M529" s="1" t="inlineStr">
         <is>
@@ -33969,11 +33969,11 @@
       </c>
       <c r="C530" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +4층</t>
         </is>
       </c>
       <c r="D530" s="1" t="n">
-        <v>2493332</v>
+        <v>2492732</v>
       </c>
       <c r="E530" s="1" t="inlineStr">
         <is>
@@ -33996,10 +33996,10 @@
         <v>0</v>
       </c>
       <c r="K530" s="1" t="n">
-        <v>970000000000</v>
+        <v>790000000000</v>
       </c>
       <c r="L530" s="1" t="n">
-        <v>74230</v>
+        <v>62816</v>
       </c>
       <c r="M530" s="1" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         </is>
       </c>
       <c r="N530" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O530" s="1" t="n">
         <v>0</v>
@@ -34059,10 +34059,10 @@
         <v>0</v>
       </c>
       <c r="K531" s="1" t="n">
-        <v>630000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L531" s="1" t="n">
-        <v>48250</v>
+        <v>40831</v>
       </c>
       <c r="M531" s="1" t="inlineStr">
         <is>
@@ -34095,11 +34095,11 @@
       </c>
       <c r="C532" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D532" s="1" t="n">
-        <v>2493332</v>
+        <v>2492332</v>
       </c>
       <c r="E532" s="1" t="inlineStr">
         <is>
@@ -34122,10 +34122,10 @@
         <v>0</v>
       </c>
       <c r="K532" s="1" t="n">
-        <v>1700000000000</v>
+        <v>1400000000000</v>
       </c>
       <c r="L532" s="1" t="n">
-        <v>125449</v>
+        <v>106160</v>
       </c>
       <c r="M532" s="1" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         </is>
       </c>
       <c r="N532" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O532" s="1" t="n">
         <v>0</v>
@@ -34185,10 +34185,10 @@
         <v>0</v>
       </c>
       <c r="K533" s="1" t="n">
-        <v>630000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L533" s="1" t="n">
-        <v>48250</v>
+        <v>40831</v>
       </c>
       <c r="M533" s="1" t="inlineStr">
         <is>
@@ -34248,10 +34248,10 @@
         <v>0</v>
       </c>
       <c r="K534" s="1" t="n">
-        <v>1100000000000</v>
+        <v>870000000000</v>
       </c>
       <c r="L534" s="1" t="n">
-        <v>81542</v>
+        <v>69004</v>
       </c>
       <c r="M534" s="1" t="inlineStr">
         <is>
@@ -34311,10 +34311,10 @@
         <v>0</v>
       </c>
       <c r="K535" s="1" t="n">
-        <v>820000000000</v>
+        <v>670000000000</v>
       </c>
       <c r="L535" s="1" t="n">
-        <v>62725</v>
+        <v>53080</v>
       </c>
       <c r="M535" s="1" t="inlineStr">
         <is>
@@ -34443,10 +34443,10 @@
         <v>0</v>
       </c>
       <c r="K537" s="1" t="n">
-        <v>690000000000</v>
+        <v>560000000000</v>
       </c>
       <c r="L537" s="1" t="n">
-        <v>47880</v>
+        <v>40320</v>
       </c>
       <c r="M537" s="1" t="inlineStr">
         <is>
@@ -34506,10 +34506,10 @@
         <v>0</v>
       </c>
       <c r="K538" s="1" t="n">
-        <v>900000000000</v>
+        <v>730000000000</v>
       </c>
       <c r="L538" s="1" t="n">
-        <v>62244</v>
+        <v>52416</v>
       </c>
       <c r="M538" s="1" t="inlineStr">
         <is>
@@ -34569,10 +34569,10 @@
         <v>0</v>
       </c>
       <c r="K539" s="1" t="n">
-        <v>1200000000000</v>
+        <v>940000000000</v>
       </c>
       <c r="L539" s="1" t="n">
-        <v>80918</v>
+        <v>68141</v>
       </c>
       <c r="M539" s="1" t="inlineStr">
         <is>
@@ -34632,10 +34632,10 @@
         <v>0</v>
       </c>
       <c r="K540" s="1" t="n">
-        <v>1200000000000</v>
+        <v>940000000000</v>
       </c>
       <c r="L540" s="1" t="n">
-        <v>80918</v>
+        <v>68141</v>
       </c>
       <c r="M540" s="1" t="inlineStr">
         <is>
@@ -34695,10 +34695,10 @@
         <v>0</v>
       </c>
       <c r="K541" s="1" t="n">
-        <v>1600000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="L541" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M541" s="1" t="inlineStr">
         <is>
@@ -34758,10 +34758,10 @@
         <v>0</v>
       </c>
       <c r="K542" s="1" t="n">
-        <v>1200000000000</v>
+        <v>940000000000</v>
       </c>
       <c r="L542" s="1" t="n">
-        <v>80918</v>
+        <v>68141</v>
       </c>
       <c r="M542" s="1" t="inlineStr">
         <is>
@@ -34821,10 +34821,10 @@
         <v>0</v>
       </c>
       <c r="K543" s="1" t="n">
-        <v>1600000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="L543" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M543" s="1" t="inlineStr">
         <is>
@@ -34884,10 +34884,10 @@
         <v>0</v>
       </c>
       <c r="K544" s="1" t="n">
-        <v>1600000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="L544" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M544" s="1" t="inlineStr">
         <is>
@@ -34947,10 +34947,10 @@
         <v>0</v>
       </c>
       <c r="K545" s="1" t="n">
-        <v>690000000000</v>
+        <v>560000000000</v>
       </c>
       <c r="L545" s="1" t="n">
-        <v>47880</v>
+        <v>40320</v>
       </c>
       <c r="M545" s="1" t="inlineStr">
         <is>
@@ -35010,10 +35010,10 @@
         <v>0</v>
       </c>
       <c r="K546" s="1" t="n">
-        <v>900000000000</v>
+        <v>730000000000</v>
       </c>
       <c r="L546" s="1" t="n">
-        <v>62244</v>
+        <v>52416</v>
       </c>
       <c r="M546" s="1" t="inlineStr">
         <is>
@@ -35073,10 +35073,10 @@
         <v>0</v>
       </c>
       <c r="K547" s="1" t="n">
-        <v>1200000000000</v>
+        <v>940000000000</v>
       </c>
       <c r="L547" s="1" t="n">
-        <v>80918</v>
+        <v>68141</v>
       </c>
       <c r="M547" s="1" t="inlineStr">
         <is>
@@ -35136,10 +35136,10 @@
         <v>0</v>
       </c>
       <c r="K548" s="1" t="n">
-        <v>1200000000000</v>
+        <v>940000000000</v>
       </c>
       <c r="L548" s="1" t="n">
-        <v>80918</v>
+        <v>68141</v>
       </c>
       <c r="M548" s="1" t="inlineStr">
         <is>
@@ -35199,10 +35199,10 @@
         <v>0</v>
       </c>
       <c r="K549" s="1" t="n">
-        <v>1200000000000</v>
+        <v>940000000000</v>
       </c>
       <c r="L549" s="1" t="n">
-        <v>80918</v>
+        <v>68141</v>
       </c>
       <c r="M549" s="1" t="inlineStr">
         <is>
@@ -35262,10 +35262,10 @@
         <v>0</v>
       </c>
       <c r="K550" s="1" t="n">
-        <v>1600000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="L550" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M550" s="1" t="inlineStr">
         <is>
@@ -35325,10 +35325,10 @@
         <v>0</v>
       </c>
       <c r="K551" s="1" t="n">
-        <v>2000000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L551" s="1" t="n">
-        <v>136751</v>
+        <v>115158</v>
       </c>
       <c r="M551" s="1" t="inlineStr">
         <is>
@@ -35388,10 +35388,10 @@
         <v>0</v>
       </c>
       <c r="K552" s="1" t="n">
-        <v>1600000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="L552" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M552" s="1" t="inlineStr">
         <is>
@@ -35451,10 +35451,10 @@
         <v>0</v>
       </c>
       <c r="K553" s="1" t="n">
-        <v>690000000000</v>
+        <v>560000000000</v>
       </c>
       <c r="L553" s="1" t="n">
-        <v>47880</v>
+        <v>40320</v>
       </c>
       <c r="M553" s="1" t="inlineStr">
         <is>
@@ -35514,10 +35514,10 @@
         <v>0</v>
       </c>
       <c r="K554" s="1" t="n">
-        <v>900000000000</v>
+        <v>730000000000</v>
       </c>
       <c r="L554" s="1" t="n">
-        <v>62244</v>
+        <v>52416</v>
       </c>
       <c r="M554" s="1" t="inlineStr">
         <is>
@@ -35577,10 +35577,10 @@
         <v>0</v>
       </c>
       <c r="K555" s="1" t="n">
-        <v>1200000000000</v>
+        <v>940000000000</v>
       </c>
       <c r="L555" s="1" t="n">
-        <v>80918</v>
+        <v>68141</v>
       </c>
       <c r="M555" s="1" t="inlineStr">
         <is>
@@ -35640,10 +35640,10 @@
         <v>0</v>
       </c>
       <c r="K556" s="1" t="n">
-        <v>1200000000000</v>
+        <v>940000000000</v>
       </c>
       <c r="L556" s="1" t="n">
-        <v>80918</v>
+        <v>68141</v>
       </c>
       <c r="M556" s="1" t="inlineStr">
         <is>
@@ -35703,10 +35703,10 @@
         <v>0</v>
       </c>
       <c r="K557" s="1" t="n">
-        <v>1600000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="L557" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M557" s="1" t="inlineStr">
         <is>
@@ -35766,10 +35766,10 @@
         <v>0</v>
       </c>
       <c r="K558" s="1" t="n">
-        <v>1600000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="L558" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M558" s="1" t="inlineStr">
         <is>
@@ -35829,10 +35829,10 @@
         <v>0</v>
       </c>
       <c r="K559" s="1" t="n">
-        <v>1600000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="L559" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M559" s="1" t="inlineStr">
         <is>
@@ -35892,10 +35892,10 @@
         <v>0</v>
       </c>
       <c r="K560" s="1" t="n">
-        <v>2000000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L560" s="1" t="n">
-        <v>136751</v>
+        <v>115158</v>
       </c>
       <c r="M560" s="1" t="inlineStr">
         <is>
@@ -35955,10 +35955,10 @@
         <v>0</v>
       </c>
       <c r="K561" s="1" t="n">
-        <v>690000000000</v>
+        <v>560000000000</v>
       </c>
       <c r="L561" s="1" t="n">
-        <v>47880</v>
+        <v>40320</v>
       </c>
       <c r="M561" s="1" t="inlineStr">
         <is>
@@ -36018,10 +36018,10 @@
         <v>0</v>
       </c>
       <c r="K562" s="1" t="n">
-        <v>900000000000</v>
+        <v>730000000000</v>
       </c>
       <c r="L562" s="1" t="n">
-        <v>62244</v>
+        <v>52416</v>
       </c>
       <c r="M562" s="1" t="inlineStr">
         <is>
@@ -36081,10 +36081,10 @@
         <v>0</v>
       </c>
       <c r="K563" s="1" t="n">
-        <v>1200000000000</v>
+        <v>940000000000</v>
       </c>
       <c r="L563" s="1" t="n">
-        <v>80918</v>
+        <v>68141</v>
       </c>
       <c r="M563" s="1" t="inlineStr">
         <is>
@@ -36144,10 +36144,10 @@
         <v>0</v>
       </c>
       <c r="K564" s="1" t="n">
-        <v>1200000000000</v>
+        <v>940000000000</v>
       </c>
       <c r="L564" s="1" t="n">
-        <v>80918</v>
+        <v>68141</v>
       </c>
       <c r="M564" s="1" t="inlineStr">
         <is>
@@ -36207,10 +36207,10 @@
         <v>0</v>
       </c>
       <c r="K565" s="1" t="n">
-        <v>1600000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="L565" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M565" s="1" t="inlineStr">
         <is>
@@ -36270,10 +36270,10 @@
         <v>0</v>
       </c>
       <c r="K566" s="1" t="n">
-        <v>1600000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="L566" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M566" s="1" t="inlineStr">
         <is>
@@ -36333,10 +36333,10 @@
         <v>0</v>
       </c>
       <c r="K567" s="1" t="n">
-        <v>2000000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L567" s="1" t="n">
-        <v>136751</v>
+        <v>115158</v>
       </c>
       <c r="M567" s="1" t="inlineStr">
         <is>
@@ -36369,11 +36369,11 @@
       </c>
       <c r="C568" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +6층</t>
         </is>
       </c>
       <c r="D568" s="1" t="n">
-        <v>2493332</v>
+        <v>2492934</v>
       </c>
       <c r="E568" s="1" t="inlineStr">
         <is>
@@ -36396,10 +36396,10 @@
         <v>0</v>
       </c>
       <c r="K568" s="1" t="n">
-        <v>1800000000000</v>
+        <v>1500000000000</v>
       </c>
       <c r="L568" s="1" t="n">
-        <v>124488</v>
+        <v>104832</v>
       </c>
       <c r="M568" s="1" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         </is>
       </c>
       <c r="N568" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O568" s="1" t="n">
         <v>0</v>
@@ -36459,10 +36459,10 @@
         <v>0</v>
       </c>
       <c r="K569" s="1" t="n">
-        <v>1200000000000</v>
+        <v>940000000000</v>
       </c>
       <c r="L569" s="1" t="n">
-        <v>80918</v>
+        <v>68141</v>
       </c>
       <c r="M569" s="1" t="inlineStr">
         <is>
@@ -36522,10 +36522,10 @@
         <v>0</v>
       </c>
       <c r="K570" s="1" t="n">
-        <v>3100000000000</v>
+        <v>2500000000000</v>
       </c>
       <c r="L570" s="1" t="n">
-        <v>210385</v>
+        <v>177167</v>
       </c>
       <c r="M570" s="1" t="inlineStr">
         <is>
@@ -36585,10 +36585,10 @@
         <v>0</v>
       </c>
       <c r="K571" s="1" t="n">
-        <v>1200000000000</v>
+        <v>940000000000</v>
       </c>
       <c r="L571" s="1" t="n">
-        <v>80918</v>
+        <v>68141</v>
       </c>
       <c r="M571" s="1" t="inlineStr">
         <is>
@@ -36648,10 +36648,10 @@
         <v>0</v>
       </c>
       <c r="K572" s="1" t="n">
-        <v>2000000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="L572" s="1" t="n">
-        <v>136751</v>
+        <v>115158</v>
       </c>
       <c r="M572" s="1" t="inlineStr">
         <is>
@@ -36711,10 +36711,10 @@
         <v>0</v>
       </c>
       <c r="K573" s="1" t="n">
-        <v>1600000000000</v>
+        <v>1300000000000</v>
       </c>
       <c r="L573" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M573" s="1" t="inlineStr">
         <is>
@@ -36843,10 +36843,10 @@
         <v>0</v>
       </c>
       <c r="K575" s="1" t="n">
-        <v>400000000000</v>
+        <v>320000000000</v>
       </c>
       <c r="L575" s="1" t="n">
-        <v>23940</v>
+        <v>20160</v>
       </c>
       <c r="M575" s="1" t="inlineStr">
         <is>
@@ -36906,10 +36906,10 @@
         <v>0</v>
       </c>
       <c r="K576" s="1" t="n">
-        <v>520000000000</v>
+        <v>420000000000</v>
       </c>
       <c r="L576" s="1" t="n">
-        <v>31122</v>
+        <v>26208</v>
       </c>
       <c r="M576" s="1" t="inlineStr">
         <is>
@@ -36969,10 +36969,10 @@
         <v>0</v>
       </c>
       <c r="K577" s="1" t="n">
-        <v>670000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L577" s="1" t="n">
-        <v>40459</v>
+        <v>34071</v>
       </c>
       <c r="M577" s="1" t="inlineStr">
         <is>
@@ -37032,10 +37032,10 @@
         <v>0</v>
       </c>
       <c r="K578" s="1" t="n">
-        <v>670000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L578" s="1" t="n">
-        <v>40459</v>
+        <v>34071</v>
       </c>
       <c r="M578" s="1" t="inlineStr">
         <is>
@@ -37095,10 +37095,10 @@
         <v>0</v>
       </c>
       <c r="K579" s="1" t="n">
-        <v>870000000000</v>
+        <v>710000000000</v>
       </c>
       <c r="L579" s="1" t="n">
-        <v>52597</v>
+        <v>44292</v>
       </c>
       <c r="M579" s="1" t="inlineStr">
         <is>
@@ -37158,10 +37158,10 @@
         <v>0</v>
       </c>
       <c r="K580" s="1" t="n">
-        <v>670000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L580" s="1" t="n">
-        <v>40459</v>
+        <v>34071</v>
       </c>
       <c r="M580" s="1" t="inlineStr">
         <is>
@@ -37221,10 +37221,10 @@
         <v>0</v>
       </c>
       <c r="K581" s="1" t="n">
-        <v>870000000000</v>
+        <v>710000000000</v>
       </c>
       <c r="L581" s="1" t="n">
-        <v>52597</v>
+        <v>44292</v>
       </c>
       <c r="M581" s="1" t="inlineStr">
         <is>
@@ -37284,10 +37284,10 @@
         <v>0</v>
       </c>
       <c r="K582" s="1" t="n">
-        <v>870000000000</v>
+        <v>710000000000</v>
       </c>
       <c r="L582" s="1" t="n">
-        <v>52597</v>
+        <v>44292</v>
       </c>
       <c r="M582" s="1" t="inlineStr">
         <is>
@@ -37347,10 +37347,10 @@
         <v>0</v>
       </c>
       <c r="K583" s="1" t="n">
-        <v>400000000000</v>
+        <v>320000000000</v>
       </c>
       <c r="L583" s="1" t="n">
-        <v>23940</v>
+        <v>20160</v>
       </c>
       <c r="M583" s="1" t="inlineStr">
         <is>
@@ -37410,10 +37410,10 @@
         <v>0</v>
       </c>
       <c r="K584" s="1" t="n">
-        <v>520000000000</v>
+        <v>420000000000</v>
       </c>
       <c r="L584" s="1" t="n">
-        <v>31122</v>
+        <v>26208</v>
       </c>
       <c r="M584" s="1" t="inlineStr">
         <is>
@@ -37473,10 +37473,10 @@
         <v>0</v>
       </c>
       <c r="K585" s="1" t="n">
-        <v>670000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L585" s="1" t="n">
-        <v>40459</v>
+        <v>34071</v>
       </c>
       <c r="M585" s="1" t="inlineStr">
         <is>
@@ -37536,10 +37536,10 @@
         <v>0</v>
       </c>
       <c r="K586" s="1" t="n">
-        <v>670000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L586" s="1" t="n">
-        <v>40459</v>
+        <v>34071</v>
       </c>
       <c r="M586" s="1" t="inlineStr">
         <is>
@@ -37599,10 +37599,10 @@
         <v>0</v>
       </c>
       <c r="K587" s="1" t="n">
-        <v>670000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L587" s="1" t="n">
-        <v>40459</v>
+        <v>34071</v>
       </c>
       <c r="M587" s="1" t="inlineStr">
         <is>
@@ -37662,10 +37662,10 @@
         <v>0</v>
       </c>
       <c r="K588" s="1" t="n">
-        <v>870000000000</v>
+        <v>710000000000</v>
       </c>
       <c r="L588" s="1" t="n">
-        <v>52597</v>
+        <v>44292</v>
       </c>
       <c r="M588" s="1" t="inlineStr">
         <is>
@@ -37725,10 +37725,10 @@
         <v>0</v>
       </c>
       <c r="K589" s="1" t="n">
-        <v>1200000000000</v>
+        <v>920000000000</v>
       </c>
       <c r="L589" s="1" t="n">
-        <v>68376</v>
+        <v>57579</v>
       </c>
       <c r="M589" s="1" t="inlineStr">
         <is>
@@ -37788,10 +37788,10 @@
         <v>0</v>
       </c>
       <c r="K590" s="1" t="n">
-        <v>870000000000</v>
+        <v>710000000000</v>
       </c>
       <c r="L590" s="1" t="n">
-        <v>52597</v>
+        <v>44292</v>
       </c>
       <c r="M590" s="1" t="inlineStr">
         <is>
@@ -37851,10 +37851,10 @@
         <v>0</v>
       </c>
       <c r="K591" s="1" t="n">
-        <v>400000000000</v>
+        <v>320000000000</v>
       </c>
       <c r="L591" s="1" t="n">
-        <v>23940</v>
+        <v>20160</v>
       </c>
       <c r="M591" s="1" t="inlineStr">
         <is>
@@ -37914,10 +37914,10 @@
         <v>0</v>
       </c>
       <c r="K592" s="1" t="n">
-        <v>520000000000</v>
+        <v>420000000000</v>
       </c>
       <c r="L592" s="1" t="n">
-        <v>31122</v>
+        <v>26208</v>
       </c>
       <c r="M592" s="1" t="inlineStr">
         <is>
@@ -37977,10 +37977,10 @@
         <v>0</v>
       </c>
       <c r="K593" s="1" t="n">
-        <v>670000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L593" s="1" t="n">
-        <v>40459</v>
+        <v>34071</v>
       </c>
       <c r="M593" s="1" t="inlineStr">
         <is>
@@ -38040,10 +38040,10 @@
         <v>0</v>
       </c>
       <c r="K594" s="1" t="n">
-        <v>670000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L594" s="1" t="n">
-        <v>40459</v>
+        <v>34071</v>
       </c>
       <c r="M594" s="1" t="inlineStr">
         <is>
@@ -38103,10 +38103,10 @@
         <v>0</v>
       </c>
       <c r="K595" s="1" t="n">
-        <v>870000000000</v>
+        <v>710000000000</v>
       </c>
       <c r="L595" s="1" t="n">
-        <v>52597</v>
+        <v>44292</v>
       </c>
       <c r="M595" s="1" t="inlineStr">
         <is>
@@ -38166,10 +38166,10 @@
         <v>0</v>
       </c>
       <c r="K596" s="1" t="n">
-        <v>870000000000</v>
+        <v>710000000000</v>
       </c>
       <c r="L596" s="1" t="n">
-        <v>52597</v>
+        <v>44292</v>
       </c>
       <c r="M596" s="1" t="inlineStr">
         <is>
@@ -38229,10 +38229,10 @@
         <v>0</v>
       </c>
       <c r="K597" s="1" t="n">
-        <v>870000000000</v>
+        <v>710000000000</v>
       </c>
       <c r="L597" s="1" t="n">
-        <v>52597</v>
+        <v>44292</v>
       </c>
       <c r="M597" s="1" t="inlineStr">
         <is>
@@ -38292,10 +38292,10 @@
         <v>0</v>
       </c>
       <c r="K598" s="1" t="n">
-        <v>1200000000000</v>
+        <v>920000000000</v>
       </c>
       <c r="L598" s="1" t="n">
-        <v>68376</v>
+        <v>57579</v>
       </c>
       <c r="M598" s="1" t="inlineStr">
         <is>
@@ -38355,10 +38355,10 @@
         <v>0</v>
       </c>
       <c r="K599" s="1" t="n">
-        <v>400000000000</v>
+        <v>320000000000</v>
       </c>
       <c r="L599" s="1" t="n">
-        <v>23940</v>
+        <v>20160</v>
       </c>
       <c r="M599" s="1" t="inlineStr">
         <is>
@@ -38418,10 +38418,10 @@
         <v>0</v>
       </c>
       <c r="K600" s="1" t="n">
-        <v>520000000000</v>
+        <v>420000000000</v>
       </c>
       <c r="L600" s="1" t="n">
-        <v>31122</v>
+        <v>26208</v>
       </c>
       <c r="M600" s="1" t="inlineStr">
         <is>
@@ -38481,10 +38481,10 @@
         <v>0</v>
       </c>
       <c r="K601" s="1" t="n">
-        <v>670000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L601" s="1" t="n">
-        <v>40459</v>
+        <v>34071</v>
       </c>
       <c r="M601" s="1" t="inlineStr">
         <is>
@@ -38544,10 +38544,10 @@
         <v>0</v>
       </c>
       <c r="K602" s="1" t="n">
-        <v>670000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L602" s="1" t="n">
-        <v>40459</v>
+        <v>34071</v>
       </c>
       <c r="M602" s="1" t="inlineStr">
         <is>
@@ -38607,10 +38607,10 @@
         <v>0</v>
       </c>
       <c r="K603" s="1" t="n">
-        <v>870000000000</v>
+        <v>710000000000</v>
       </c>
       <c r="L603" s="1" t="n">
-        <v>52597</v>
+        <v>44292</v>
       </c>
       <c r="M603" s="1" t="inlineStr">
         <is>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="K604" s="1" t="n">
-        <v>870000000000</v>
+        <v>710000000000</v>
       </c>
       <c r="L604" s="1" t="n">
-        <v>52597</v>
+        <v>44292</v>
       </c>
       <c r="M604" s="1" t="inlineStr">
         <is>
@@ -38733,10 +38733,10 @@
         <v>0</v>
       </c>
       <c r="K605" s="1" t="n">
-        <v>1200000000000</v>
+        <v>920000000000</v>
       </c>
       <c r="L605" s="1" t="n">
-        <v>68376</v>
+        <v>57579</v>
       </c>
       <c r="M605" s="1" t="inlineStr">
         <is>
@@ -38769,11 +38769,11 @@
       </c>
       <c r="C606" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +4층</t>
         </is>
       </c>
       <c r="D606" s="1" t="n">
-        <v>2493332</v>
+        <v>2492732</v>
       </c>
       <c r="E606" s="1" t="inlineStr">
         <is>
@@ -38796,10 +38796,10 @@
         <v>0</v>
       </c>
       <c r="K606" s="1" t="n">
-        <v>1100000000000</v>
+        <v>840000000000</v>
       </c>
       <c r="L606" s="1" t="n">
-        <v>62244</v>
+        <v>52416</v>
       </c>
       <c r="M606" s="1" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         </is>
       </c>
       <c r="N606" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O606" s="1" t="n">
         <v>0</v>
@@ -38859,10 +38859,10 @@
         <v>0</v>
       </c>
       <c r="K607" s="1" t="n">
-        <v>670000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L607" s="1" t="n">
-        <v>40459</v>
+        <v>34071</v>
       </c>
       <c r="M607" s="1" t="inlineStr">
         <is>
@@ -38895,11 +38895,11 @@
       </c>
       <c r="C608" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +4층</t>
         </is>
       </c>
       <c r="D608" s="1" t="n">
-        <v>2493332</v>
+        <v>2492732</v>
       </c>
       <c r="E608" s="1" t="inlineStr">
         <is>
@@ -38922,10 +38922,10 @@
         <v>0</v>
       </c>
       <c r="K608" s="1" t="n">
-        <v>1800000000000</v>
+        <v>1500000000000</v>
       </c>
       <c r="L608" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M608" s="1" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         </is>
       </c>
       <c r="N608" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O608" s="1" t="n">
         <v>0</v>
@@ -38985,10 +38985,10 @@
         <v>0</v>
       </c>
       <c r="K609" s="1" t="n">
-        <v>670000000000</v>
+        <v>550000000000</v>
       </c>
       <c r="L609" s="1" t="n">
-        <v>40459</v>
+        <v>34071</v>
       </c>
       <c r="M609" s="1" t="inlineStr">
         <is>
@@ -39048,10 +39048,10 @@
         <v>0</v>
       </c>
       <c r="K610" s="1" t="n">
-        <v>1200000000000</v>
+        <v>920000000000</v>
       </c>
       <c r="L610" s="1" t="n">
-        <v>68376</v>
+        <v>57579</v>
       </c>
       <c r="M610" s="1" t="inlineStr">
         <is>
@@ -39111,10 +39111,10 @@
         <v>0</v>
       </c>
       <c r="K611" s="1" t="n">
-        <v>1800000000000</v>
+        <v>1500000000000</v>
       </c>
       <c r="L611" s="1" t="n">
-        <v>105193</v>
+        <v>88584</v>
       </c>
       <c r="M611" s="1" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>증강 장착 슬롯 + 합 (기본 = 증강 테이블 Aug_Config slot_base 5)</t>
+          <t>증강 장착 슬롯 + 합 (기본 = 증강 테이블 Aug_Config slot_base 2, 최대 slot_max 5)</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">

--- a/Data_Table/공용 스킬 테이블.xlsx
+++ b/Data_Table/공용 스킬 테이블.xlsx
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1700</v>
+        <v>3100</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>2400</v>
+        <v>4500</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>0</v>
@@ -969,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>4900</v>
+        <v>9400</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="L10" s="1" t="n">
         <v>0</v>
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>4900</v>
+        <v>9400</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>0</v>
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>4900</v>
+        <v>9400</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1700</v>
+        <v>3100</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>0</v>
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>2400</v>
+        <v>4500</v>
       </c>
       <c r="L14" s="1" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="L15" s="1" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="L16" s="1" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="L17" s="1" t="n">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>4900</v>
+        <v>9400</v>
       </c>
       <c r="L18" s="1" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>7100</v>
+        <v>14000</v>
       </c>
       <c r="L19" s="1" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>4900</v>
+        <v>9400</v>
       </c>
       <c r="L20" s="1" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>1700</v>
+        <v>3100</v>
       </c>
       <c r="L21" s="1" t="n">
         <v>0</v>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>2400</v>
+        <v>4500</v>
       </c>
       <c r="L22" s="1" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="L23" s="1" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="L24" s="1" t="n">
         <v>0</v>
@@ -2103,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>4900</v>
+        <v>9400</v>
       </c>
       <c r="L25" s="1" t="n">
         <v>0</v>
@@ -2166,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>7400</v>
+        <v>14000</v>
       </c>
       <c r="L26" s="1" t="n">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>4900</v>
+        <v>9400</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>11000</v>
+        <v>21000</v>
       </c>
       <c r="L28" s="1" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>2500</v>
+        <v>4600</v>
       </c>
       <c r="L29" s="1" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>2400</v>
+        <v>4500</v>
       </c>
       <c r="L30" s="1" t="n">
         <v>0</v>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="L31" s="1" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="L32" s="1" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>4900</v>
+        <v>9400</v>
       </c>
       <c r="L33" s="1" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>4900</v>
+        <v>9400</v>
       </c>
       <c r="L34" s="1" t="n">
         <v>0</v>
@@ -2733,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>7100</v>
+        <v>14000</v>
       </c>
       <c r="L35" s="1" t="n">
         <v>0</v>
@@ -2769,11 +2769,11 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +7층</t>
+          <t>스테이지 스킵 +8층</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>2493532</v>
+        <v>2400002</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>3500</v>
+        <v>6700</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>0</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="N36" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>0</v>
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>0</v>
@@ -2922,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>4900</v>
+        <v>9400</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>7100</v>
+        <v>14000</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>0</v>
@@ -3111,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>4900</v>
+        <v>9400</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>0</v>
@@ -3243,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>27000</v>
+        <v>76000</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M43" s="1" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         <v>0</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>27000</v>
+        <v>76000</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M44" s="1" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>72000</v>
+        <v>210000</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M45" s="1" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         <v>0</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>36000</v>
+        <v>120000</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M46" s="1" t="inlineStr">
         <is>
@@ -3495,10 +3495,10 @@
         <v>0</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>45000</v>
+        <v>140000</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M47" s="1" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>36000</v>
+        <v>120000</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -3621,10 +3621,10 @@
         <v>0</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>45000</v>
+        <v>140000</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M49" s="1" t="inlineStr">
         <is>
@@ -3684,10 +3684,10 @@
         <v>0</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>45000</v>
+        <v>140000</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M50" s="1" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>27000</v>
+        <v>76000</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M51" s="1" t="inlineStr">
         <is>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>27000</v>
+        <v>76000</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M52" s="1" t="inlineStr">
         <is>
@@ -3873,10 +3873,10 @@
         <v>0</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>36000</v>
+        <v>120000</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M53" s="1" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         <v>0</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>36000</v>
+        <v>120000</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M54" s="1" t="inlineStr">
         <is>
@@ -3999,10 +3999,10 @@
         <v>0</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>36000</v>
+        <v>120000</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M55" s="1" t="inlineStr">
         <is>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>45000</v>
+        <v>140000</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M56" s="1" t="inlineStr">
         <is>
@@ -4125,10 +4125,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>63000</v>
+        <v>180000</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M57" s="1" t="inlineStr">
         <is>
@@ -4188,10 +4188,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>45000</v>
+        <v>140000</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M58" s="1" t="inlineStr">
         <is>
@@ -4251,10 +4251,10 @@
         <v>0</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>27000</v>
+        <v>76000</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M59" s="1" t="inlineStr">
         <is>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>27000</v>
+        <v>76000</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M60" s="1" t="inlineStr">
         <is>
@@ -4377,10 +4377,10 @@
         <v>0</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>36000</v>
+        <v>120000</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M61" s="1" t="inlineStr">
         <is>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>36000</v>
+        <v>120000</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M62" s="1" t="inlineStr">
         <is>
@@ -4503,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>45000</v>
+        <v>140000</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M63" s="1" t="inlineStr">
         <is>
@@ -4566,10 +4566,10 @@
         <v>0</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>90000</v>
+        <v>270000</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M64" s="1" t="inlineStr">
         <is>
@@ -4629,10 +4629,10 @@
         <v>0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>45000</v>
+        <v>140000</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M65" s="1" t="inlineStr">
         <is>
@@ -4692,10 +4692,10 @@
         <v>0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>120000</v>
+        <v>350000</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M66" s="1" t="inlineStr">
         <is>
@@ -4755,10 +4755,10 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>45000</v>
+        <v>140000</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M67" s="1" t="inlineStr">
         <is>
@@ -4818,10 +4818,10 @@
         <v>0</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>27000</v>
+        <v>76000</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M68" s="1" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         <v>0</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>36000</v>
+        <v>120000</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M69" s="1" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>0</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>36000</v>
+        <v>120000</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M70" s="1" t="inlineStr">
         <is>
@@ -5007,10 +5007,10 @@
         <v>0</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>45000</v>
+        <v>140000</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M71" s="1" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
         <v>0</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>45000</v>
+        <v>140000</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M72" s="1" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
         <v>0</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>63000</v>
+        <v>180000</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M73" s="1" t="inlineStr">
         <is>
@@ -5169,11 +5169,11 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>2492132</v>
+        <v>2492332</v>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
@@ -5196,10 +5196,10 @@
         <v>0</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>54000</v>
+        <v>160000</v>
       </c>
       <c r="L74" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M74" s="1" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="N74" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O74" s="1" t="n">
         <v>0</v>
@@ -5259,10 +5259,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>36000</v>
+        <v>120000</v>
       </c>
       <c r="L75" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M75" s="1" t="inlineStr">
         <is>
@@ -5295,11 +5295,11 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>2492132</v>
+        <v>2492332</v>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>90000</v>
+        <v>270000</v>
       </c>
       <c r="L76" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M76" s="1" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="N76" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O76" s="1" t="n">
         <v>0</v>
@@ -5385,10 +5385,10 @@
         <v>0</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>36000</v>
+        <v>120000</v>
       </c>
       <c r="L77" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M77" s="1" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
         <v>0</v>
       </c>
       <c r="K78" s="1" t="n">
-        <v>63000</v>
+        <v>180000</v>
       </c>
       <c r="L78" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M78" s="1" t="inlineStr">
         <is>
@@ -5511,10 +5511,10 @@
         <v>0</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>45000</v>
+        <v>140000</v>
       </c>
       <c r="L79" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M79" s="1" t="inlineStr">
         <is>
@@ -5643,10 +5643,10 @@
         <v>0</v>
       </c>
       <c r="K81" s="1" t="n">
-        <v>130000</v>
+        <v>550000</v>
       </c>
       <c r="L81" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M81" s="1" t="inlineStr">
         <is>
@@ -5706,10 +5706,10 @@
         <v>0</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>160000</v>
+        <v>640000</v>
       </c>
       <c r="L82" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M82" s="1" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
         <v>0</v>
       </c>
       <c r="K83" s="1" t="n">
-        <v>380000</v>
+        <v>1700000</v>
       </c>
       <c r="L83" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M83" s="1" t="inlineStr">
         <is>
@@ -5832,10 +5832,10 @@
         <v>0</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>190000</v>
+        <v>820000</v>
       </c>
       <c r="L84" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M84" s="1" t="inlineStr">
         <is>
@@ -5895,10 +5895,10 @@
         <v>0</v>
       </c>
       <c r="K85" s="1" t="n">
-        <v>260000</v>
+        <v>1100000</v>
       </c>
       <c r="L85" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M85" s="1" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>190000</v>
+        <v>820000</v>
       </c>
       <c r="L86" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M86" s="1" t="inlineStr">
         <is>
@@ -6021,10 +6021,10 @@
         <v>0</v>
       </c>
       <c r="K87" s="1" t="n">
-        <v>260000</v>
+        <v>1100000</v>
       </c>
       <c r="L87" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M87" s="1" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>0</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>260000</v>
+        <v>1100000</v>
       </c>
       <c r="L88" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M88" s="1" t="inlineStr">
         <is>
@@ -6147,10 +6147,10 @@
         <v>0</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>130000</v>
+        <v>550000</v>
       </c>
       <c r="L89" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M89" s="1" t="inlineStr">
         <is>
@@ -6210,10 +6210,10 @@
         <v>0</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>160000</v>
+        <v>640000</v>
       </c>
       <c r="L90" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M90" s="1" t="inlineStr">
         <is>
@@ -6273,10 +6273,10 @@
         <v>0</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>190000</v>
+        <v>820000</v>
       </c>
       <c r="L91" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M91" s="1" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         <v>0</v>
       </c>
       <c r="K92" s="1" t="n">
-        <v>190000</v>
+        <v>820000</v>
       </c>
       <c r="L92" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -6399,10 +6399,10 @@
         <v>0</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>190000</v>
+        <v>820000</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M93" s="1" t="inlineStr">
         <is>
@@ -6462,10 +6462,10 @@
         <v>0</v>
       </c>
       <c r="K94" s="1" t="n">
-        <v>260000</v>
+        <v>1100000</v>
       </c>
       <c r="L94" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M94" s="1" t="inlineStr">
         <is>
@@ -6525,10 +6525,10 @@
         <v>0</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>320000</v>
+        <v>1500000</v>
       </c>
       <c r="L95" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M95" s="1" t="inlineStr">
         <is>
@@ -6588,10 +6588,10 @@
         <v>0</v>
       </c>
       <c r="K96" s="1" t="n">
-        <v>260000</v>
+        <v>1100000</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M96" s="1" t="inlineStr">
         <is>
@@ -6651,10 +6651,10 @@
         <v>0</v>
       </c>
       <c r="K97" s="1" t="n">
-        <v>130000</v>
+        <v>550000</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M97" s="1" t="inlineStr">
         <is>
@@ -6714,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="K98" s="1" t="n">
-        <v>160000</v>
+        <v>640000</v>
       </c>
       <c r="L98" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M98" s="1" t="inlineStr">
         <is>
@@ -6777,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>190000</v>
+        <v>820000</v>
       </c>
       <c r="L99" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M99" s="1" t="inlineStr">
         <is>
@@ -6840,10 +6840,10 @@
         <v>0</v>
       </c>
       <c r="K100" s="1" t="n">
-        <v>190000</v>
+        <v>820000</v>
       </c>
       <c r="L100" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M100" s="1" t="inlineStr">
         <is>
@@ -6903,10 +6903,10 @@
         <v>0</v>
       </c>
       <c r="K101" s="1" t="n">
-        <v>260000</v>
+        <v>1100000</v>
       </c>
       <c r="L101" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M101" s="1" t="inlineStr">
         <is>
@@ -6966,10 +6966,10 @@
         <v>0</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>510000</v>
+        <v>2200000</v>
       </c>
       <c r="L102" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M102" s="1" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>260000</v>
+        <v>1100000</v>
       </c>
       <c r="L103" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M103" s="1" t="inlineStr">
         <is>
@@ -7092,10 +7092,10 @@
         <v>0</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>630000</v>
+        <v>2800000</v>
       </c>
       <c r="L104" s="1" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="M104" s="1" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         <v>0</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>220000</v>
+        <v>1000000</v>
       </c>
       <c r="L105" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M105" s="1" t="inlineStr">
         <is>
@@ -7218,10 +7218,10 @@
         <v>0</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>160000</v>
+        <v>640000</v>
       </c>
       <c r="L106" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M106" s="1" t="inlineStr">
         <is>
@@ -7281,10 +7281,10 @@
         <v>0</v>
       </c>
       <c r="K107" s="1" t="n">
-        <v>190000</v>
+        <v>820000</v>
       </c>
       <c r="L107" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M107" s="1" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>0</v>
       </c>
       <c r="K108" s="1" t="n">
-        <v>190000</v>
+        <v>820000</v>
       </c>
       <c r="L108" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M108" s="1" t="inlineStr">
         <is>
@@ -7407,10 +7407,10 @@
         <v>0</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>260000</v>
+        <v>1100000</v>
       </c>
       <c r="L109" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M109" s="1" t="inlineStr">
         <is>
@@ -7470,10 +7470,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>260000</v>
+        <v>1100000</v>
       </c>
       <c r="L110" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M110" s="1" t="inlineStr">
         <is>
@@ -7533,10 +7533,10 @@
         <v>0</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>320000</v>
+        <v>1500000</v>
       </c>
       <c r="L111" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M111" s="1" t="inlineStr">
         <is>
@@ -7569,11 +7569,11 @@
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +4층</t>
+          <t>스테이지 스킵 +6층</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>2492732</v>
+        <v>2492934</v>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
@@ -7596,10 +7596,10 @@
         <v>0</v>
       </c>
       <c r="K112" s="1" t="n">
-        <v>320000</v>
+        <v>1300000</v>
       </c>
       <c r="L112" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M112" s="1" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="N112" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O112" s="1" t="n">
         <v>0</v>
@@ -7659,10 +7659,10 @@
         <v>0</v>
       </c>
       <c r="K113" s="1" t="n">
-        <v>380000</v>
+        <v>1700000</v>
       </c>
       <c r="L113" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M113" s="1" t="inlineStr">
         <is>
@@ -7722,10 +7722,10 @@
         <v>0</v>
       </c>
       <c r="K114" s="1" t="n">
-        <v>260000</v>
+        <v>1100000</v>
       </c>
       <c r="L114" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M114" s="1" t="inlineStr">
         <is>
@@ -7785,10 +7785,10 @@
         <v>0</v>
       </c>
       <c r="K115" s="1" t="n">
-        <v>190000</v>
+        <v>820000</v>
       </c>
       <c r="L115" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M115" s="1" t="inlineStr">
         <is>
@@ -7848,10 +7848,10 @@
         <v>0</v>
       </c>
       <c r="K116" s="1" t="n">
-        <v>320000</v>
+        <v>1500000</v>
       </c>
       <c r="L116" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M116" s="1" t="inlineStr">
         <is>
@@ -7911,10 +7911,10 @@
         <v>0</v>
       </c>
       <c r="K117" s="1" t="n">
-        <v>260000</v>
+        <v>1100000</v>
       </c>
       <c r="L117" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M117" s="1" t="inlineStr">
         <is>
@@ -8043,10 +8043,10 @@
         <v>0</v>
       </c>
       <c r="K119" s="1" t="n">
-        <v>880000</v>
+        <v>4300000</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M119" s="1" t="inlineStr">
         <is>
@@ -8106,10 +8106,10 @@
         <v>0</v>
       </c>
       <c r="K120" s="1" t="n">
-        <v>1100000</v>
+        <v>5500000</v>
       </c>
       <c r="L120" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M120" s="1" t="inlineStr">
         <is>
@@ -8169,10 +8169,10 @@
         <v>0</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>1500000</v>
+        <v>7400000</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M121" s="1" t="inlineStr">
         <is>
@@ -8232,10 +8232,10 @@
         <v>0</v>
       </c>
       <c r="K122" s="1" t="n">
-        <v>1500000</v>
+        <v>7400000</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M122" s="1" t="inlineStr">
         <is>
@@ -8295,10 +8295,10 @@
         <v>0</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>1800000</v>
+        <v>9300000</v>
       </c>
       <c r="L123" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M123" s="1" t="inlineStr">
         <is>
@@ -8358,10 +8358,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>1500000</v>
+        <v>7400000</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M124" s="1" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>0</v>
       </c>
       <c r="K125" s="1" t="n">
-        <v>1800000</v>
+        <v>9300000</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M125" s="1" t="inlineStr">
         <is>
@@ -8484,10 +8484,10 @@
         <v>0</v>
       </c>
       <c r="K126" s="1" t="n">
-        <v>1800000</v>
+        <v>9300000</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M126" s="1" t="inlineStr">
         <is>
@@ -8547,10 +8547,10 @@
         <v>0</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>880000</v>
+        <v>4300000</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M127" s="1" t="inlineStr">
         <is>
@@ -8610,10 +8610,10 @@
         <v>0</v>
       </c>
       <c r="K128" s="1" t="n">
-        <v>1100000</v>
+        <v>5500000</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M128" s="1" t="inlineStr">
         <is>
@@ -8673,10 +8673,10 @@
         <v>0</v>
       </c>
       <c r="K129" s="1" t="n">
-        <v>1500000</v>
+        <v>7400000</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M129" s="1" t="inlineStr">
         <is>
@@ -8736,10 +8736,10 @@
         <v>0</v>
       </c>
       <c r="K130" s="1" t="n">
-        <v>1500000</v>
+        <v>7400000</v>
       </c>
       <c r="L130" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M130" s="1" t="inlineStr">
         <is>
@@ -8799,10 +8799,10 @@
         <v>0</v>
       </c>
       <c r="K131" s="1" t="n">
-        <v>1500000</v>
+        <v>7400000</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M131" s="1" t="inlineStr">
         <is>
@@ -8862,10 +8862,10 @@
         <v>0</v>
       </c>
       <c r="K132" s="1" t="n">
-        <v>1800000</v>
+        <v>9300000</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M132" s="1" t="inlineStr">
         <is>
@@ -8925,10 +8925,10 @@
         <v>0</v>
       </c>
       <c r="K133" s="1" t="n">
-        <v>2300000</v>
+        <v>13000000</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="M133" s="1" t="inlineStr">
         <is>
@@ -8988,10 +8988,10 @@
         <v>0</v>
       </c>
       <c r="K134" s="1" t="n">
-        <v>1800000</v>
+        <v>9300000</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M134" s="1" t="inlineStr">
         <is>
@@ -9051,10 +9051,10 @@
         <v>0</v>
       </c>
       <c r="K135" s="1" t="n">
-        <v>880000</v>
+        <v>4300000</v>
       </c>
       <c r="L135" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M135" s="1" t="inlineStr">
         <is>
@@ -9114,10 +9114,10 @@
         <v>0</v>
       </c>
       <c r="K136" s="1" t="n">
-        <v>1100000</v>
+        <v>5500000</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M136" s="1" t="inlineStr">
         <is>
@@ -9177,10 +9177,10 @@
         <v>0</v>
       </c>
       <c r="K137" s="1" t="n">
-        <v>1500000</v>
+        <v>7400000</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M137" s="1" t="inlineStr">
         <is>
@@ -9240,10 +9240,10 @@
         <v>0</v>
       </c>
       <c r="K138" s="1" t="n">
-        <v>1500000</v>
+        <v>7400000</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M138" s="1" t="inlineStr">
         <is>
@@ -9303,10 +9303,10 @@
         <v>0</v>
       </c>
       <c r="K139" s="1" t="n">
-        <v>1800000</v>
+        <v>9300000</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M139" s="1" t="inlineStr">
         <is>
@@ -9366,10 +9366,10 @@
         <v>0</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>3500000</v>
+        <v>19000000</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="M140" s="1" t="inlineStr">
         <is>
@@ -9429,10 +9429,10 @@
         <v>0</v>
       </c>
       <c r="K141" s="1" t="n">
-        <v>1800000</v>
+        <v>9300000</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M141" s="1" t="inlineStr">
         <is>
@@ -9492,10 +9492,10 @@
         <v>0</v>
       </c>
       <c r="K142" s="1" t="n">
-        <v>4600000</v>
+        <v>25000000</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="M142" s="1" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         <v>0</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>1700000</v>
+        <v>8600000</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M143" s="1" t="inlineStr">
         <is>
@@ -9618,10 +9618,10 @@
         <v>0</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>1100000</v>
+        <v>5500000</v>
       </c>
       <c r="L144" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M144" s="1" t="inlineStr">
         <is>
@@ -9681,10 +9681,10 @@
         <v>0</v>
       </c>
       <c r="K145" s="1" t="n">
-        <v>1500000</v>
+        <v>7400000</v>
       </c>
       <c r="L145" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M145" s="1" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>0</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>1500000</v>
+        <v>7400000</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M146" s="1" t="inlineStr">
         <is>
@@ -9807,10 +9807,10 @@
         <v>0</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>1800000</v>
+        <v>9300000</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M147" s="1" t="inlineStr">
         <is>
@@ -9870,10 +9870,10 @@
         <v>0</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>1800000</v>
+        <v>9300000</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M148" s="1" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>2300000</v>
+        <v>13000000</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="M149" s="1" t="inlineStr">
         <is>
@@ -9969,11 +9969,11 @@
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +4층</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>2492332</v>
+        <v>2492732</v>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>2100000</v>
+        <v>11000000</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M150" s="1" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="N150" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O150" s="1" t="n">
         <v>0</v>
@@ -10059,10 +10059,10 @@
         <v>0</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>1500000</v>
+        <v>7400000</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M151" s="1" t="inlineStr">
         <is>
@@ -10095,11 +10095,11 @@
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +2층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>2492132</v>
+        <v>2492332</v>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
@@ -10122,10 +10122,10 @@
         <v>0</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>3500000</v>
+        <v>19000000</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="M152" s="1" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="N152" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O152" s="1" t="n">
         <v>0</v>
@@ -10185,10 +10185,10 @@
         <v>0</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>1500000</v>
+        <v>7400000</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M153" s="1" t="inlineStr">
         <is>
@@ -10248,10 +10248,10 @@
         <v>0</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>2300000</v>
+        <v>13000000</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="M154" s="1" t="inlineStr">
         <is>
@@ -10311,10 +10311,10 @@
         <v>0</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>1800000</v>
+        <v>9300000</v>
       </c>
       <c r="L155" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M155" s="1" t="inlineStr">
         <is>
@@ -10443,10 +10443,10 @@
         <v>0</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>6400000</v>
+        <v>45000000</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M157" s="1" t="inlineStr">
         <is>
@@ -10506,10 +10506,10 @@
         <v>0</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>8600000</v>
+        <v>58000000</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M158" s="1" t="inlineStr">
         <is>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>11000000</v>
+        <v>74000000</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M159" s="1" t="inlineStr">
         <is>
@@ -10632,10 +10632,10 @@
         <v>0</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>11000000</v>
+        <v>74000000</v>
       </c>
       <c r="L160" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M160" s="1" t="inlineStr">
         <is>
@@ -10695,10 +10695,10 @@
         <v>0</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>15000000</v>
+        <v>96000000</v>
       </c>
       <c r="L161" s="1" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M161" s="1" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>0</v>
       </c>
       <c r="K162" s="1" t="n">
-        <v>11000000</v>
+        <v>74000000</v>
       </c>
       <c r="L162" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M162" s="1" t="inlineStr">
         <is>
@@ -10821,10 +10821,10 @@
         <v>0</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>15000000</v>
+        <v>96000000</v>
       </c>
       <c r="L163" s="1" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M163" s="1" t="inlineStr">
         <is>
@@ -10884,10 +10884,10 @@
         <v>0</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>15000000</v>
+        <v>96000000</v>
       </c>
       <c r="L164" s="1" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M164" s="1" t="inlineStr">
         <is>
@@ -10947,10 +10947,10 @@
         <v>0</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>6400000</v>
+        <v>45000000</v>
       </c>
       <c r="L165" s="1" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M165" s="1" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         <v>0</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>8600000</v>
+        <v>58000000</v>
       </c>
       <c r="L166" s="1" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M166" s="1" t="inlineStr">
         <is>
@@ -11073,10 +11073,10 @@
         <v>0</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>11000000</v>
+        <v>74000000</v>
       </c>
       <c r="L167" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M167" s="1" t="inlineStr">
         <is>
@@ -11136,10 +11136,10 @@
         <v>0</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>11000000</v>
+        <v>74000000</v>
       </c>
       <c r="L168" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M168" s="1" t="inlineStr">
         <is>
@@ -11199,10 +11199,10 @@
         <v>0</v>
       </c>
       <c r="K169" s="1" t="n">
-        <v>11000000</v>
+        <v>74000000</v>
       </c>
       <c r="L169" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M169" s="1" t="inlineStr">
         <is>
@@ -11262,10 +11262,10 @@
         <v>0</v>
       </c>
       <c r="K170" s="1" t="n">
-        <v>15000000</v>
+        <v>96000000</v>
       </c>
       <c r="L170" s="1" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M170" s="1" t="inlineStr">
         <is>
@@ -11325,10 +11325,10 @@
         <v>0</v>
       </c>
       <c r="K171" s="1" t="n">
-        <v>19000000</v>
+        <v>130000000</v>
       </c>
       <c r="L171" s="1" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="M171" s="1" t="inlineStr">
         <is>
@@ -11388,10 +11388,10 @@
         <v>0</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>15000000</v>
+        <v>96000000</v>
       </c>
       <c r="L172" s="1" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M172" s="1" t="inlineStr">
         <is>
@@ -11451,10 +11451,10 @@
         <v>0</v>
       </c>
       <c r="K173" s="1" t="n">
-        <v>6400000</v>
+        <v>45000000</v>
       </c>
       <c r="L173" s="1" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M173" s="1" t="inlineStr">
         <is>
@@ -11514,10 +11514,10 @@
         <v>0</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>8600000</v>
+        <v>58000000</v>
       </c>
       <c r="L174" s="1" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M174" s="1" t="inlineStr">
         <is>
@@ -11577,10 +11577,10 @@
         <v>0</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>11000000</v>
+        <v>74000000</v>
       </c>
       <c r="L175" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M175" s="1" t="inlineStr">
         <is>
@@ -11640,10 +11640,10 @@
         <v>0</v>
       </c>
       <c r="K176" s="1" t="n">
-        <v>11000000</v>
+        <v>74000000</v>
       </c>
       <c r="L176" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M176" s="1" t="inlineStr">
         <is>
@@ -11703,10 +11703,10 @@
         <v>0</v>
       </c>
       <c r="K177" s="1" t="n">
-        <v>15000000</v>
+        <v>96000000</v>
       </c>
       <c r="L177" s="1" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M177" s="1" t="inlineStr">
         <is>
@@ -11766,10 +11766,10 @@
         <v>0</v>
       </c>
       <c r="K178" s="1" t="n">
-        <v>28000000</v>
+        <v>190000000</v>
       </c>
       <c r="L178" s="1" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="M178" s="1" t="inlineStr">
         <is>
@@ -11829,10 +11829,10 @@
         <v>0</v>
       </c>
       <c r="K179" s="1" t="n">
-        <v>15000000</v>
+        <v>96000000</v>
       </c>
       <c r="L179" s="1" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M179" s="1" t="inlineStr">
         <is>
@@ -11892,10 +11892,10 @@
         <v>0</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>37000000</v>
+        <v>250000000</v>
       </c>
       <c r="L180" s="1" t="n">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="M180" s="1" t="inlineStr">
         <is>
@@ -11955,10 +11955,10 @@
         <v>0</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>13000000</v>
+        <v>88000000</v>
       </c>
       <c r="L181" s="1" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M181" s="1" t="inlineStr">
         <is>
@@ -12018,10 +12018,10 @@
         <v>0</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>8600000</v>
+        <v>58000000</v>
       </c>
       <c r="L182" s="1" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M182" s="1" t="inlineStr">
         <is>
@@ -12081,10 +12081,10 @@
         <v>0</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>11000000</v>
+        <v>74000000</v>
       </c>
       <c r="L183" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M183" s="1" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>0</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>11000000</v>
+        <v>74000000</v>
       </c>
       <c r="L184" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M184" s="1" t="inlineStr">
         <is>
@@ -12207,10 +12207,10 @@
         <v>0</v>
       </c>
       <c r="K185" s="1" t="n">
-        <v>15000000</v>
+        <v>96000000</v>
       </c>
       <c r="L185" s="1" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M185" s="1" t="inlineStr">
         <is>
@@ -12270,10 +12270,10 @@
         <v>0</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>15000000</v>
+        <v>96000000</v>
       </c>
       <c r="L186" s="1" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M186" s="1" t="inlineStr">
         <is>
@@ -12333,10 +12333,10 @@
         <v>0</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>19000000</v>
+        <v>130000000</v>
       </c>
       <c r="L187" s="1" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="M187" s="1" t="inlineStr">
         <is>
@@ -12369,11 +12369,11 @@
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +6층</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>2493332</v>
+        <v>2492934</v>
       </c>
       <c r="E188" s="1" t="inlineStr">
         <is>
@@ -12396,10 +12396,10 @@
         <v>0</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>17000000</v>
+        <v>120000000</v>
       </c>
       <c r="L188" s="1" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="M188" s="1" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="N188" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O188" s="1" t="n">
         <v>0</v>
@@ -12459,10 +12459,10 @@
         <v>0</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>22000000</v>
+        <v>150000000</v>
       </c>
       <c r="L189" s="1" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="M189" s="1" t="inlineStr">
         <is>
@@ -12522,10 +12522,10 @@
         <v>0</v>
       </c>
       <c r="K190" s="1" t="n">
-        <v>15000000</v>
+        <v>96000000</v>
       </c>
       <c r="L190" s="1" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M190" s="1" t="inlineStr">
         <is>
@@ -12585,10 +12585,10 @@
         <v>0</v>
       </c>
       <c r="K191" s="1" t="n">
-        <v>11000000</v>
+        <v>74000000</v>
       </c>
       <c r="L191" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M191" s="1" t="inlineStr">
         <is>
@@ -12648,10 +12648,10 @@
         <v>0</v>
       </c>
       <c r="K192" s="1" t="n">
-        <v>19000000</v>
+        <v>130000000</v>
       </c>
       <c r="L192" s="1" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="M192" s="1" t="inlineStr">
         <is>
@@ -12711,10 +12711,10 @@
         <v>0</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>15000000</v>
+        <v>96000000</v>
       </c>
       <c r="L193" s="1" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M193" s="1" t="inlineStr">
         <is>
@@ -12843,10 +12843,10 @@
         <v>0</v>
       </c>
       <c r="K195" s="1" t="n">
-        <v>51000000</v>
+        <v>200000000</v>
       </c>
       <c r="L195" s="1" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="M195" s="1" t="inlineStr">
         <is>
@@ -12906,10 +12906,10 @@
         <v>0</v>
       </c>
       <c r="K196" s="1" t="n">
-        <v>66000000</v>
+        <v>250000000</v>
       </c>
       <c r="L196" s="1" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="M196" s="1" t="inlineStr">
         <is>
@@ -12969,10 +12969,10 @@
         <v>0</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>85000000</v>
+        <v>320000000</v>
       </c>
       <c r="L197" s="1" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M197" s="1" t="inlineStr">
         <is>
@@ -13032,10 +13032,10 @@
         <v>0</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>85000000</v>
+        <v>320000000</v>
       </c>
       <c r="L198" s="1" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M198" s="1" t="inlineStr">
         <is>
@@ -13095,10 +13095,10 @@
         <v>0</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>120000000</v>
+        <v>420000000</v>
       </c>
       <c r="L199" s="1" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="M199" s="1" t="inlineStr">
         <is>
@@ -13158,10 +13158,10 @@
         <v>0</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>85000000</v>
+        <v>320000000</v>
       </c>
       <c r="L200" s="1" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M200" s="1" t="inlineStr">
         <is>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>120000000</v>
+        <v>420000000</v>
       </c>
       <c r="L201" s="1" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="M201" s="1" t="inlineStr">
         <is>
@@ -13284,10 +13284,10 @@
         <v>0</v>
       </c>
       <c r="K202" s="1" t="n">
-        <v>120000000</v>
+        <v>420000000</v>
       </c>
       <c r="L202" s="1" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="M202" s="1" t="inlineStr">
         <is>
@@ -13347,10 +13347,10 @@
         <v>0</v>
       </c>
       <c r="K203" s="1" t="n">
-        <v>51000000</v>
+        <v>200000000</v>
       </c>
       <c r="L203" s="1" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="M203" s="1" t="inlineStr">
         <is>
@@ -13410,10 +13410,10 @@
         <v>0</v>
       </c>
       <c r="K204" s="1" t="n">
-        <v>66000000</v>
+        <v>250000000</v>
       </c>
       <c r="L204" s="1" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="M204" s="1" t="inlineStr">
         <is>
@@ -13473,10 +13473,10 @@
         <v>0</v>
       </c>
       <c r="K205" s="1" t="n">
-        <v>85000000</v>
+        <v>320000000</v>
       </c>
       <c r="L205" s="1" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M205" s="1" t="inlineStr">
         <is>
@@ -13536,10 +13536,10 @@
         <v>0</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>85000000</v>
+        <v>320000000</v>
       </c>
       <c r="L206" s="1" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M206" s="1" t="inlineStr">
         <is>
@@ -13599,10 +13599,10 @@
         <v>0</v>
       </c>
       <c r="K207" s="1" t="n">
-        <v>85000000</v>
+        <v>320000000</v>
       </c>
       <c r="L207" s="1" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M207" s="1" t="inlineStr">
         <is>
@@ -13662,10 +13662,10 @@
         <v>0</v>
       </c>
       <c r="K208" s="1" t="n">
-        <v>120000000</v>
+        <v>420000000</v>
       </c>
       <c r="L208" s="1" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="M208" s="1" t="inlineStr">
         <is>
@@ -13725,10 +13725,10 @@
         <v>0</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>150000000</v>
+        <v>550000000</v>
       </c>
       <c r="L209" s="1" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="M209" s="1" t="inlineStr">
         <is>
@@ -13788,10 +13788,10 @@
         <v>0</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>120000000</v>
+        <v>420000000</v>
       </c>
       <c r="L210" s="1" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="M210" s="1" t="inlineStr">
         <is>
@@ -13851,10 +13851,10 @@
         <v>0</v>
       </c>
       <c r="K211" s="1" t="n">
-        <v>51000000</v>
+        <v>200000000</v>
       </c>
       <c r="L211" s="1" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="M211" s="1" t="inlineStr">
         <is>
@@ -13914,10 +13914,10 @@
         <v>0</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>66000000</v>
+        <v>250000000</v>
       </c>
       <c r="L212" s="1" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="M212" s="1" t="inlineStr">
         <is>
@@ -13977,10 +13977,10 @@
         <v>0</v>
       </c>
       <c r="K213" s="1" t="n">
-        <v>85000000</v>
+        <v>320000000</v>
       </c>
       <c r="L213" s="1" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M213" s="1" t="inlineStr">
         <is>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="K214" s="1" t="n">
-        <v>85000000</v>
+        <v>320000000</v>
       </c>
       <c r="L214" s="1" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M214" s="1" t="inlineStr">
         <is>
@@ -14103,10 +14103,10 @@
         <v>0</v>
       </c>
       <c r="K215" s="1" t="n">
-        <v>120000000</v>
+        <v>420000000</v>
       </c>
       <c r="L215" s="1" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="M215" s="1" t="inlineStr">
         <is>
@@ -14166,10 +14166,10 @@
         <v>0</v>
       </c>
       <c r="K216" s="1" t="n">
-        <v>230000000</v>
+        <v>840000000</v>
       </c>
       <c r="L216" s="1" t="n">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="M216" s="1" t="inlineStr">
         <is>
@@ -14229,10 +14229,10 @@
         <v>0</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>120000000</v>
+        <v>420000000</v>
       </c>
       <c r="L217" s="1" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="M217" s="1" t="inlineStr">
         <is>
@@ -14292,10 +14292,10 @@
         <v>0</v>
       </c>
       <c r="K218" s="1" t="n">
-        <v>290000000</v>
+        <v>1100000000</v>
       </c>
       <c r="L218" s="1" t="n">
-        <v>233</v>
+        <v>321</v>
       </c>
       <c r="M218" s="1" t="inlineStr">
         <is>
@@ -14355,10 +14355,10 @@
         <v>0</v>
       </c>
       <c r="K219" s="1" t="n">
-        <v>51000000</v>
+        <v>200000000</v>
       </c>
       <c r="L219" s="1" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="M219" s="1" t="inlineStr">
         <is>
@@ -14418,10 +14418,10 @@
         <v>0</v>
       </c>
       <c r="K220" s="1" t="n">
-        <v>66000000</v>
+        <v>250000000</v>
       </c>
       <c r="L220" s="1" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="M220" s="1" t="inlineStr">
         <is>
@@ -14481,10 +14481,10 @@
         <v>0</v>
       </c>
       <c r="K221" s="1" t="n">
-        <v>85000000</v>
+        <v>320000000</v>
       </c>
       <c r="L221" s="1" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M221" s="1" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>0</v>
       </c>
       <c r="K222" s="1" t="n">
-        <v>85000000</v>
+        <v>320000000</v>
       </c>
       <c r="L222" s="1" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M222" s="1" t="inlineStr">
         <is>
@@ -14607,10 +14607,10 @@
         <v>0</v>
       </c>
       <c r="K223" s="1" t="n">
-        <v>120000000</v>
+        <v>420000000</v>
       </c>
       <c r="L223" s="1" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="M223" s="1" t="inlineStr">
         <is>
@@ -14670,10 +14670,10 @@
         <v>0</v>
       </c>
       <c r="K224" s="1" t="n">
-        <v>120000000</v>
+        <v>420000000</v>
       </c>
       <c r="L224" s="1" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="M224" s="1" t="inlineStr">
         <is>
@@ -14733,10 +14733,10 @@
         <v>0</v>
       </c>
       <c r="K225" s="1" t="n">
-        <v>150000000</v>
+        <v>550000000</v>
       </c>
       <c r="L225" s="1" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="M225" s="1" t="inlineStr">
         <is>
@@ -14796,10 +14796,10 @@
         <v>0</v>
       </c>
       <c r="K226" s="1" t="n">
-        <v>140000000</v>
+        <v>500000000</v>
       </c>
       <c r="L226" s="1" t="n">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="M226" s="1" t="inlineStr">
         <is>
@@ -14859,10 +14859,10 @@
         <v>0</v>
       </c>
       <c r="K227" s="1" t="n">
-        <v>170000000</v>
+        <v>640000000</v>
       </c>
       <c r="L227" s="1" t="n">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="M227" s="1" t="inlineStr">
         <is>
@@ -14922,10 +14922,10 @@
         <v>0</v>
       </c>
       <c r="K228" s="1" t="n">
-        <v>230000000</v>
+        <v>840000000</v>
       </c>
       <c r="L228" s="1" t="n">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="M228" s="1" t="inlineStr">
         <is>
@@ -14985,10 +14985,10 @@
         <v>0</v>
       </c>
       <c r="K229" s="1" t="n">
-        <v>85000000</v>
+        <v>320000000</v>
       </c>
       <c r="L229" s="1" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M229" s="1" t="inlineStr">
         <is>
@@ -15048,10 +15048,10 @@
         <v>0</v>
       </c>
       <c r="K230" s="1" t="n">
-        <v>150000000</v>
+        <v>550000000</v>
       </c>
       <c r="L230" s="1" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="M230" s="1" t="inlineStr">
         <is>
@@ -15111,10 +15111,10 @@
         <v>0</v>
       </c>
       <c r="K231" s="1" t="n">
-        <v>120000000</v>
+        <v>420000000</v>
       </c>
       <c r="L231" s="1" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="M231" s="1" t="inlineStr">
         <is>
@@ -15243,10 +15243,10 @@
         <v>0</v>
       </c>
       <c r="K233" s="1" t="n">
-        <v>590000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L233" s="1" t="n">
-        <v>178</v>
+        <v>277</v>
       </c>
       <c r="M233" s="1" t="inlineStr">
         <is>
@@ -15306,10 +15306,10 @@
         <v>0</v>
       </c>
       <c r="K234" s="1" t="n">
-        <v>760000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L234" s="1" t="n">
-        <v>231</v>
+        <v>360</v>
       </c>
       <c r="M234" s="1" t="inlineStr">
         <is>
@@ -15369,10 +15369,10 @@
         <v>0</v>
       </c>
       <c r="K235" s="1" t="n">
-        <v>990000000</v>
+        <v>2200000000</v>
       </c>
       <c r="L235" s="1" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="M235" s="1" t="inlineStr">
         <is>
@@ -15432,10 +15432,10 @@
         <v>0</v>
       </c>
       <c r="K236" s="1" t="n">
-        <v>990000000</v>
+        <v>2200000000</v>
       </c>
       <c r="L236" s="1" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="M236" s="1" t="inlineStr">
         <is>
@@ -15495,10 +15495,10 @@
         <v>0</v>
       </c>
       <c r="K237" s="1" t="n">
-        <v>1300000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L237" s="1" t="n">
-        <v>390</v>
+        <v>609</v>
       </c>
       <c r="M237" s="1" t="inlineStr">
         <is>
@@ -15558,10 +15558,10 @@
         <v>0</v>
       </c>
       <c r="K238" s="1" t="n">
-        <v>990000000</v>
+        <v>2200000000</v>
       </c>
       <c r="L238" s="1" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="M238" s="1" t="inlineStr">
         <is>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="K239" s="1" t="n">
-        <v>1300000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L239" s="1" t="n">
-        <v>390</v>
+        <v>609</v>
       </c>
       <c r="M239" s="1" t="inlineStr">
         <is>
@@ -15684,10 +15684,10 @@
         <v>0</v>
       </c>
       <c r="K240" s="1" t="n">
-        <v>1300000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L240" s="1" t="n">
-        <v>390</v>
+        <v>609</v>
       </c>
       <c r="M240" s="1" t="inlineStr">
         <is>
@@ -15747,10 +15747,10 @@
         <v>0</v>
       </c>
       <c r="K241" s="1" t="n">
-        <v>590000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L241" s="1" t="n">
-        <v>178</v>
+        <v>277</v>
       </c>
       <c r="M241" s="1" t="inlineStr">
         <is>
@@ -15810,10 +15810,10 @@
         <v>0</v>
       </c>
       <c r="K242" s="1" t="n">
-        <v>760000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L242" s="1" t="n">
-        <v>231</v>
+        <v>360</v>
       </c>
       <c r="M242" s="1" t="inlineStr">
         <is>
@@ -15873,10 +15873,10 @@
         <v>0</v>
       </c>
       <c r="K243" s="1" t="n">
-        <v>990000000</v>
+        <v>2200000000</v>
       </c>
       <c r="L243" s="1" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="M243" s="1" t="inlineStr">
         <is>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="K244" s="1" t="n">
-        <v>990000000</v>
+        <v>2200000000</v>
       </c>
       <c r="L244" s="1" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="M244" s="1" t="inlineStr">
         <is>
@@ -15999,10 +15999,10 @@
         <v>0</v>
       </c>
       <c r="K245" s="1" t="n">
-        <v>990000000</v>
+        <v>2200000000</v>
       </c>
       <c r="L245" s="1" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="M245" s="1" t="inlineStr">
         <is>
@@ -16062,10 +16062,10 @@
         <v>0</v>
       </c>
       <c r="K246" s="1" t="n">
-        <v>1300000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L246" s="1" t="n">
-        <v>390</v>
+        <v>609</v>
       </c>
       <c r="M246" s="1" t="inlineStr">
         <is>
@@ -16125,10 +16125,10 @@
         <v>0</v>
       </c>
       <c r="K247" s="1" t="n">
-        <v>1700000000</v>
+        <v>3700000000</v>
       </c>
       <c r="L247" s="1" t="n">
-        <v>507</v>
+        <v>791</v>
       </c>
       <c r="M247" s="1" t="inlineStr">
         <is>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="K248" s="1" t="n">
-        <v>1300000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L248" s="1" t="n">
-        <v>390</v>
+        <v>609</v>
       </c>
       <c r="M248" s="1" t="inlineStr">
         <is>
@@ -16251,10 +16251,10 @@
         <v>0</v>
       </c>
       <c r="K249" s="1" t="n">
-        <v>590000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L249" s="1" t="n">
-        <v>178</v>
+        <v>277</v>
       </c>
       <c r="M249" s="1" t="inlineStr">
         <is>
@@ -16314,10 +16314,10 @@
         <v>0</v>
       </c>
       <c r="K250" s="1" t="n">
-        <v>760000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L250" s="1" t="n">
-        <v>231</v>
+        <v>360</v>
       </c>
       <c r="M250" s="1" t="inlineStr">
         <is>
@@ -16377,10 +16377,10 @@
         <v>0</v>
       </c>
       <c r="K251" s="1" t="n">
-        <v>990000000</v>
+        <v>2200000000</v>
       </c>
       <c r="L251" s="1" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="M251" s="1" t="inlineStr">
         <is>
@@ -16440,10 +16440,10 @@
         <v>0</v>
       </c>
       <c r="K252" s="1" t="n">
-        <v>990000000</v>
+        <v>2200000000</v>
       </c>
       <c r="L252" s="1" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="M252" s="1" t="inlineStr">
         <is>
@@ -16503,10 +16503,10 @@
         <v>0</v>
       </c>
       <c r="K253" s="1" t="n">
-        <v>1300000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L253" s="1" t="n">
-        <v>390</v>
+        <v>609</v>
       </c>
       <c r="M253" s="1" t="inlineStr">
         <is>
@@ -16566,10 +16566,10 @@
         <v>0</v>
       </c>
       <c r="K254" s="1" t="n">
-        <v>1300000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L254" s="1" t="n">
-        <v>390</v>
+        <v>609</v>
       </c>
       <c r="M254" s="1" t="inlineStr">
         <is>
@@ -16629,10 +16629,10 @@
         <v>0</v>
       </c>
       <c r="K255" s="1" t="n">
-        <v>1300000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L255" s="1" t="n">
-        <v>390</v>
+        <v>609</v>
       </c>
       <c r="M255" s="1" t="inlineStr">
         <is>
@@ -16692,10 +16692,10 @@
         <v>0</v>
       </c>
       <c r="K256" s="1" t="n">
-        <v>3400000000</v>
+        <v>7300000000</v>
       </c>
       <c r="L256" s="1" t="n">
-        <v>1014</v>
+        <v>1582</v>
       </c>
       <c r="M256" s="1" t="inlineStr">
         <is>
@@ -16755,10 +16755,10 @@
         <v>0</v>
       </c>
       <c r="K257" s="1" t="n">
-        <v>590000000</v>
+        <v>1300000000</v>
       </c>
       <c r="L257" s="1" t="n">
-        <v>178</v>
+        <v>277</v>
       </c>
       <c r="M257" s="1" t="inlineStr">
         <is>
@@ -16818,10 +16818,10 @@
         <v>0</v>
       </c>
       <c r="K258" s="1" t="n">
-        <v>760000000</v>
+        <v>1700000000</v>
       </c>
       <c r="L258" s="1" t="n">
-        <v>231</v>
+        <v>360</v>
       </c>
       <c r="M258" s="1" t="inlineStr">
         <is>
@@ -16881,10 +16881,10 @@
         <v>0</v>
       </c>
       <c r="K259" s="1" t="n">
-        <v>990000000</v>
+        <v>2200000000</v>
       </c>
       <c r="L259" s="1" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="M259" s="1" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>0</v>
       </c>
       <c r="K260" s="1" t="n">
-        <v>990000000</v>
+        <v>2200000000</v>
       </c>
       <c r="L260" s="1" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="M260" s="1" t="inlineStr">
         <is>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="K261" s="1" t="n">
-        <v>1300000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L261" s="1" t="n">
-        <v>390</v>
+        <v>609</v>
       </c>
       <c r="M261" s="1" t="inlineStr">
         <is>
@@ -17070,10 +17070,10 @@
         <v>0</v>
       </c>
       <c r="K262" s="1" t="n">
-        <v>1300000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L262" s="1" t="n">
-        <v>390</v>
+        <v>609</v>
       </c>
       <c r="M262" s="1" t="inlineStr">
         <is>
@@ -17133,10 +17133,10 @@
         <v>0</v>
       </c>
       <c r="K263" s="1" t="n">
-        <v>1700000000</v>
+        <v>3700000000</v>
       </c>
       <c r="L263" s="1" t="n">
-        <v>507</v>
+        <v>791</v>
       </c>
       <c r="M263" s="1" t="inlineStr">
         <is>
@@ -17169,11 +17169,11 @@
       </c>
       <c r="C264" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +6층</t>
+          <t>스테이지 스킵 +7층</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>2492934</v>
+        <v>2493532</v>
       </c>
       <c r="E264" s="1" t="inlineStr">
         <is>
@@ -17196,10 +17196,10 @@
         <v>0</v>
       </c>
       <c r="K264" s="1" t="n">
-        <v>1600000000</v>
+        <v>3400000000</v>
       </c>
       <c r="L264" s="1" t="n">
-        <v>462</v>
+        <v>720</v>
       </c>
       <c r="M264" s="1" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         </is>
       </c>
       <c r="N264" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O264" s="1" t="n">
         <v>0</v>
@@ -17259,10 +17259,10 @@
         <v>0</v>
       </c>
       <c r="K265" s="1" t="n">
-        <v>990000000</v>
+        <v>2200000000</v>
       </c>
       <c r="L265" s="1" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="M265" s="1" t="inlineStr">
         <is>
@@ -17322,10 +17322,10 @@
         <v>0</v>
       </c>
       <c r="K266" s="1" t="n">
-        <v>1300000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L266" s="1" t="n">
-        <v>390</v>
+        <v>609</v>
       </c>
       <c r="M266" s="1" t="inlineStr">
         <is>
@@ -17385,10 +17385,10 @@
         <v>0</v>
       </c>
       <c r="K267" s="1" t="n">
-        <v>990000000</v>
+        <v>2200000000</v>
       </c>
       <c r="L267" s="1" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="M267" s="1" t="inlineStr">
         <is>
@@ -17448,10 +17448,10 @@
         <v>0</v>
       </c>
       <c r="K268" s="1" t="n">
-        <v>1700000000</v>
+        <v>3700000000</v>
       </c>
       <c r="L268" s="1" t="n">
-        <v>507</v>
+        <v>791</v>
       </c>
       <c r="M268" s="1" t="inlineStr">
         <is>
@@ -17511,10 +17511,10 @@
         <v>0</v>
       </c>
       <c r="K269" s="1" t="n">
-        <v>1300000000</v>
+        <v>2900000000</v>
       </c>
       <c r="L269" s="1" t="n">
-        <v>390</v>
+        <v>609</v>
       </c>
       <c r="M269" s="1" t="inlineStr">
         <is>
@@ -17643,10 +17643,10 @@
         <v>0</v>
       </c>
       <c r="K271" s="1" t="n">
-        <v>1100000000</v>
+        <v>4300000000</v>
       </c>
       <c r="L271" s="1" t="n">
-        <v>270</v>
+        <v>720</v>
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
@@ -17706,10 +17706,10 @@
         <v>0</v>
       </c>
       <c r="K272" s="1" t="n">
-        <v>1500000000</v>
+        <v>5600000000</v>
       </c>
       <c r="L272" s="1" t="n">
-        <v>351</v>
+        <v>936</v>
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
@@ -17769,10 +17769,10 @@
         <v>0</v>
       </c>
       <c r="K273" s="1" t="n">
-        <v>1900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="L273" s="1" t="n">
-        <v>457</v>
+        <v>1216</v>
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
@@ -17832,10 +17832,10 @@
         <v>0</v>
       </c>
       <c r="K274" s="1" t="n">
-        <v>1900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="L274" s="1" t="n">
-        <v>457</v>
+        <v>1216</v>
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
@@ -17895,10 +17895,10 @@
         <v>0</v>
       </c>
       <c r="K275" s="1" t="n">
-        <v>2400000000</v>
+        <v>9300000000</v>
       </c>
       <c r="L275" s="1" t="n">
-        <v>594</v>
+        <v>1581</v>
       </c>
       <c r="M275" s="1" t="inlineStr">
         <is>
@@ -17958,10 +17958,10 @@
         <v>0</v>
       </c>
       <c r="K276" s="1" t="n">
-        <v>1900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="L276" s="1" t="n">
-        <v>457</v>
+        <v>1216</v>
       </c>
       <c r="M276" s="1" t="inlineStr">
         <is>
@@ -18021,10 +18021,10 @@
         <v>0</v>
       </c>
       <c r="K277" s="1" t="n">
-        <v>2400000000</v>
+        <v>9300000000</v>
       </c>
       <c r="L277" s="1" t="n">
-        <v>594</v>
+        <v>1581</v>
       </c>
       <c r="M277" s="1" t="inlineStr">
         <is>
@@ -18084,10 +18084,10 @@
         <v>0</v>
       </c>
       <c r="K278" s="1" t="n">
-        <v>2400000000</v>
+        <v>9300000000</v>
       </c>
       <c r="L278" s="1" t="n">
-        <v>594</v>
+        <v>1581</v>
       </c>
       <c r="M278" s="1" t="inlineStr">
         <is>
@@ -18147,10 +18147,10 @@
         <v>0</v>
       </c>
       <c r="K279" s="1" t="n">
-        <v>1100000000</v>
+        <v>4300000000</v>
       </c>
       <c r="L279" s="1" t="n">
-        <v>270</v>
+        <v>720</v>
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
@@ -18210,10 +18210,10 @@
         <v>0</v>
       </c>
       <c r="K280" s="1" t="n">
-        <v>1500000000</v>
+        <v>5600000000</v>
       </c>
       <c r="L280" s="1" t="n">
-        <v>351</v>
+        <v>936</v>
       </c>
       <c r="M280" s="1" t="inlineStr">
         <is>
@@ -18273,10 +18273,10 @@
         <v>0</v>
       </c>
       <c r="K281" s="1" t="n">
-        <v>1900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="L281" s="1" t="n">
-        <v>457</v>
+        <v>1216</v>
       </c>
       <c r="M281" s="1" t="inlineStr">
         <is>
@@ -18336,10 +18336,10 @@
         <v>0</v>
       </c>
       <c r="K282" s="1" t="n">
-        <v>1900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="L282" s="1" t="n">
-        <v>457</v>
+        <v>1216</v>
       </c>
       <c r="M282" s="1" t="inlineStr">
         <is>
@@ -18399,10 +18399,10 @@
         <v>0</v>
       </c>
       <c r="K283" s="1" t="n">
-        <v>1900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="L283" s="1" t="n">
-        <v>457</v>
+        <v>1216</v>
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
@@ -18462,10 +18462,10 @@
         <v>0</v>
       </c>
       <c r="K284" s="1" t="n">
-        <v>2400000000</v>
+        <v>9300000000</v>
       </c>
       <c r="L284" s="1" t="n">
-        <v>594</v>
+        <v>1581</v>
       </c>
       <c r="M284" s="1" t="inlineStr">
         <is>
@@ -18525,10 +18525,10 @@
         <v>0</v>
       </c>
       <c r="K285" s="1" t="n">
-        <v>3100000000</v>
+        <v>13000000000</v>
       </c>
       <c r="L285" s="1" t="n">
-        <v>772</v>
+        <v>2055</v>
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
@@ -18588,10 +18588,10 @@
         <v>0</v>
       </c>
       <c r="K286" s="1" t="n">
-        <v>2400000000</v>
+        <v>9300000000</v>
       </c>
       <c r="L286" s="1" t="n">
-        <v>594</v>
+        <v>1581</v>
       </c>
       <c r="M286" s="1" t="inlineStr">
         <is>
@@ -18651,10 +18651,10 @@
         <v>0</v>
       </c>
       <c r="K287" s="1" t="n">
-        <v>1100000000</v>
+        <v>4300000000</v>
       </c>
       <c r="L287" s="1" t="n">
-        <v>270</v>
+        <v>720</v>
       </c>
       <c r="M287" s="1" t="inlineStr">
         <is>
@@ -18714,10 +18714,10 @@
         <v>0</v>
       </c>
       <c r="K288" s="1" t="n">
-        <v>1500000000</v>
+        <v>5600000000</v>
       </c>
       <c r="L288" s="1" t="n">
-        <v>351</v>
+        <v>936</v>
       </c>
       <c r="M288" s="1" t="inlineStr">
         <is>
@@ -18777,10 +18777,10 @@
         <v>0</v>
       </c>
       <c r="K289" s="1" t="n">
-        <v>1900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="L289" s="1" t="n">
-        <v>457</v>
+        <v>1216</v>
       </c>
       <c r="M289" s="1" t="inlineStr">
         <is>
@@ -18840,10 +18840,10 @@
         <v>0</v>
       </c>
       <c r="K290" s="1" t="n">
-        <v>1900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="L290" s="1" t="n">
-        <v>457</v>
+        <v>1216</v>
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
@@ -18903,10 +18903,10 @@
         <v>0</v>
       </c>
       <c r="K291" s="1" t="n">
-        <v>2400000000</v>
+        <v>9300000000</v>
       </c>
       <c r="L291" s="1" t="n">
-        <v>594</v>
+        <v>1581</v>
       </c>
       <c r="M291" s="1" t="inlineStr">
         <is>
@@ -18966,10 +18966,10 @@
         <v>0</v>
       </c>
       <c r="K292" s="1" t="n">
-        <v>2400000000</v>
+        <v>9300000000</v>
       </c>
       <c r="L292" s="1" t="n">
-        <v>594</v>
+        <v>1581</v>
       </c>
       <c r="M292" s="1" t="inlineStr">
         <is>
@@ -19029,10 +19029,10 @@
         <v>0</v>
       </c>
       <c r="K293" s="1" t="n">
-        <v>2400000000</v>
+        <v>9300000000</v>
       </c>
       <c r="L293" s="1" t="n">
-        <v>594</v>
+        <v>1581</v>
       </c>
       <c r="M293" s="1" t="inlineStr">
         <is>
@@ -19092,10 +19092,10 @@
         <v>0</v>
       </c>
       <c r="K294" s="1" t="n">
-        <v>6200000000</v>
+        <v>25000000000</v>
       </c>
       <c r="L294" s="1" t="n">
-        <v>1543</v>
+        <v>4110</v>
       </c>
       <c r="M294" s="1" t="inlineStr">
         <is>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="K295" s="1" t="n">
-        <v>1100000000</v>
+        <v>4300000000</v>
       </c>
       <c r="L295" s="1" t="n">
-        <v>270</v>
+        <v>720</v>
       </c>
       <c r="M295" s="1" t="inlineStr">
         <is>
@@ -19218,10 +19218,10 @@
         <v>0</v>
       </c>
       <c r="K296" s="1" t="n">
-        <v>1500000000</v>
+        <v>5600000000</v>
       </c>
       <c r="L296" s="1" t="n">
-        <v>351</v>
+        <v>936</v>
       </c>
       <c r="M296" s="1" t="inlineStr">
         <is>
@@ -19281,10 +19281,10 @@
         <v>0</v>
       </c>
       <c r="K297" s="1" t="n">
-        <v>1900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="L297" s="1" t="n">
-        <v>457</v>
+        <v>1216</v>
       </c>
       <c r="M297" s="1" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>0</v>
       </c>
       <c r="K298" s="1" t="n">
-        <v>1900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="L298" s="1" t="n">
-        <v>457</v>
+        <v>1216</v>
       </c>
       <c r="M298" s="1" t="inlineStr">
         <is>
@@ -19407,10 +19407,10 @@
         <v>0</v>
       </c>
       <c r="K299" s="1" t="n">
-        <v>2400000000</v>
+        <v>9300000000</v>
       </c>
       <c r="L299" s="1" t="n">
-        <v>594</v>
+        <v>1581</v>
       </c>
       <c r="M299" s="1" t="inlineStr">
         <is>
@@ -19470,10 +19470,10 @@
         <v>0</v>
       </c>
       <c r="K300" s="1" t="n">
-        <v>2400000000</v>
+        <v>9300000000</v>
       </c>
       <c r="L300" s="1" t="n">
-        <v>594</v>
+        <v>1581</v>
       </c>
       <c r="M300" s="1" t="inlineStr">
         <is>
@@ -19533,10 +19533,10 @@
         <v>0</v>
       </c>
       <c r="K301" s="1" t="n">
-        <v>3100000000</v>
+        <v>13000000000</v>
       </c>
       <c r="L301" s="1" t="n">
-        <v>772</v>
+        <v>2055</v>
       </c>
       <c r="M301" s="1" t="inlineStr">
         <is>
@@ -19596,10 +19596,10 @@
         <v>0</v>
       </c>
       <c r="K302" s="1" t="n">
-        <v>2900000000</v>
+        <v>11000000000</v>
       </c>
       <c r="L302" s="1" t="n">
-        <v>702</v>
+        <v>1871</v>
       </c>
       <c r="M302" s="1" t="inlineStr">
         <is>
@@ -19659,10 +19659,10 @@
         <v>0</v>
       </c>
       <c r="K303" s="1" t="n">
-        <v>1900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="L303" s="1" t="n">
-        <v>457</v>
+        <v>1216</v>
       </c>
       <c r="M303" s="1" t="inlineStr">
         <is>
@@ -19722,10 +19722,10 @@
         <v>0</v>
       </c>
       <c r="K304" s="1" t="n">
-        <v>4800000000</v>
+        <v>19000000000</v>
       </c>
       <c r="L304" s="1" t="n">
-        <v>1187</v>
+        <v>3161</v>
       </c>
       <c r="M304" s="1" t="inlineStr">
         <is>
@@ -19785,10 +19785,10 @@
         <v>0</v>
       </c>
       <c r="K305" s="1" t="n">
-        <v>1900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="L305" s="1" t="n">
-        <v>457</v>
+        <v>1216</v>
       </c>
       <c r="M305" s="1" t="inlineStr">
         <is>
@@ -19848,10 +19848,10 @@
         <v>0</v>
       </c>
       <c r="K306" s="1" t="n">
-        <v>3100000000</v>
+        <v>13000000000</v>
       </c>
       <c r="L306" s="1" t="n">
-        <v>772</v>
+        <v>2055</v>
       </c>
       <c r="M306" s="1" t="inlineStr">
         <is>
@@ -19911,10 +19911,10 @@
         <v>0</v>
       </c>
       <c r="K307" s="1" t="n">
-        <v>2400000000</v>
+        <v>9300000000</v>
       </c>
       <c r="L307" s="1" t="n">
-        <v>594</v>
+        <v>1581</v>
       </c>
       <c r="M307" s="1" t="inlineStr">
         <is>
@@ -20043,10 +20043,10 @@
         <v>0</v>
       </c>
       <c r="K309" s="1" t="n">
-        <v>2100000000</v>
+        <v>8000000000</v>
       </c>
       <c r="L309" s="1" t="n">
-        <v>450</v>
+        <v>1154</v>
       </c>
       <c r="M309" s="1" t="inlineStr">
         <is>
@@ -20106,10 +20106,10 @@
         <v>0</v>
       </c>
       <c r="K310" s="1" t="n">
-        <v>2700000000</v>
+        <v>11000000000</v>
       </c>
       <c r="L310" s="1" t="n">
-        <v>585</v>
+        <v>1501</v>
       </c>
       <c r="M310" s="1" t="inlineStr">
         <is>
@@ -20169,10 +20169,10 @@
         <v>0</v>
       </c>
       <c r="K311" s="1" t="n">
-        <v>3400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L311" s="1" t="n">
-        <v>761</v>
+        <v>1951</v>
       </c>
       <c r="M311" s="1" t="inlineStr">
         <is>
@@ -20232,10 +20232,10 @@
         <v>0</v>
       </c>
       <c r="K312" s="1" t="n">
-        <v>3400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L312" s="1" t="n">
-        <v>761</v>
+        <v>1951</v>
       </c>
       <c r="M312" s="1" t="inlineStr">
         <is>
@@ -20295,10 +20295,10 @@
         <v>0</v>
       </c>
       <c r="K313" s="1" t="n">
-        <v>4500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="L313" s="1" t="n">
-        <v>989</v>
+        <v>2536</v>
       </c>
       <c r="M313" s="1" t="inlineStr">
         <is>
@@ -20358,10 +20358,10 @@
         <v>0</v>
       </c>
       <c r="K314" s="1" t="n">
-        <v>3400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L314" s="1" t="n">
-        <v>761</v>
+        <v>1951</v>
       </c>
       <c r="M314" s="1" t="inlineStr">
         <is>
@@ -20421,10 +20421,10 @@
         <v>0</v>
       </c>
       <c r="K315" s="1" t="n">
-        <v>4500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="L315" s="1" t="n">
-        <v>989</v>
+        <v>2536</v>
       </c>
       <c r="M315" s="1" t="inlineStr">
         <is>
@@ -20484,10 +20484,10 @@
         <v>0</v>
       </c>
       <c r="K316" s="1" t="n">
-        <v>4500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="L316" s="1" t="n">
-        <v>989</v>
+        <v>2536</v>
       </c>
       <c r="M316" s="1" t="inlineStr">
         <is>
@@ -20547,10 +20547,10 @@
         <v>0</v>
       </c>
       <c r="K317" s="1" t="n">
-        <v>4100000000</v>
+        <v>16000000000</v>
       </c>
       <c r="L317" s="1" t="n">
-        <v>900</v>
+        <v>2308</v>
       </c>
       <c r="M317" s="1" t="inlineStr">
         <is>
@@ -20610,10 +20610,10 @@
         <v>0</v>
       </c>
       <c r="K318" s="1" t="n">
-        <v>2700000000</v>
+        <v>11000000000</v>
       </c>
       <c r="L318" s="1" t="n">
-        <v>585</v>
+        <v>1501</v>
       </c>
       <c r="M318" s="1" t="inlineStr">
         <is>
@@ -20673,10 +20673,10 @@
         <v>0</v>
       </c>
       <c r="K319" s="1" t="n">
-        <v>3400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L319" s="1" t="n">
-        <v>761</v>
+        <v>1951</v>
       </c>
       <c r="M319" s="1" t="inlineStr">
         <is>
@@ -20736,10 +20736,10 @@
         <v>0</v>
       </c>
       <c r="K320" s="1" t="n">
-        <v>3400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L320" s="1" t="n">
-        <v>761</v>
+        <v>1951</v>
       </c>
       <c r="M320" s="1" t="inlineStr">
         <is>
@@ -20799,10 +20799,10 @@
         <v>0</v>
       </c>
       <c r="K321" s="1" t="n">
-        <v>3400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L321" s="1" t="n">
-        <v>761</v>
+        <v>1951</v>
       </c>
       <c r="M321" s="1" t="inlineStr">
         <is>
@@ -20862,10 +20862,10 @@
         <v>0</v>
       </c>
       <c r="K322" s="1" t="n">
-        <v>4500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="L322" s="1" t="n">
-        <v>989</v>
+        <v>2536</v>
       </c>
       <c r="M322" s="1" t="inlineStr">
         <is>
@@ -20925,10 +20925,10 @@
         <v>0</v>
       </c>
       <c r="K323" s="1" t="n">
-        <v>5800000000</v>
+        <v>23000000000</v>
       </c>
       <c r="L323" s="1" t="n">
-        <v>1286</v>
+        <v>3296</v>
       </c>
       <c r="M323" s="1" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
         <v>0</v>
       </c>
       <c r="K324" s="1" t="n">
-        <v>4500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="L324" s="1" t="n">
-        <v>989</v>
+        <v>2536</v>
       </c>
       <c r="M324" s="1" t="inlineStr">
         <is>
@@ -21051,10 +21051,10 @@
         <v>0</v>
       </c>
       <c r="K325" s="1" t="n">
-        <v>2100000000</v>
+        <v>8000000000</v>
       </c>
       <c r="L325" s="1" t="n">
-        <v>450</v>
+        <v>1154</v>
       </c>
       <c r="M325" s="1" t="inlineStr">
         <is>
@@ -21114,10 +21114,10 @@
         <v>0</v>
       </c>
       <c r="K326" s="1" t="n">
-        <v>2700000000</v>
+        <v>11000000000</v>
       </c>
       <c r="L326" s="1" t="n">
-        <v>585</v>
+        <v>1501</v>
       </c>
       <c r="M326" s="1" t="inlineStr">
         <is>
@@ -21177,10 +21177,10 @@
         <v>0</v>
       </c>
       <c r="K327" s="1" t="n">
-        <v>3400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L327" s="1" t="n">
-        <v>761</v>
+        <v>1951</v>
       </c>
       <c r="M327" s="1" t="inlineStr">
         <is>
@@ -21240,10 +21240,10 @@
         <v>0</v>
       </c>
       <c r="K328" s="1" t="n">
-        <v>3400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L328" s="1" t="n">
-        <v>761</v>
+        <v>1951</v>
       </c>
       <c r="M328" s="1" t="inlineStr">
         <is>
@@ -21303,10 +21303,10 @@
         <v>0</v>
       </c>
       <c r="K329" s="1" t="n">
-        <v>4500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="L329" s="1" t="n">
-        <v>989</v>
+        <v>2536</v>
       </c>
       <c r="M329" s="1" t="inlineStr">
         <is>
@@ -21366,10 +21366,10 @@
         <v>0</v>
       </c>
       <c r="K330" s="1" t="n">
-        <v>4500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="L330" s="1" t="n">
-        <v>989</v>
+        <v>2536</v>
       </c>
       <c r="M330" s="1" t="inlineStr">
         <is>
@@ -21429,10 +21429,10 @@
         <v>0</v>
       </c>
       <c r="K331" s="1" t="n">
-        <v>4500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="L331" s="1" t="n">
-        <v>989</v>
+        <v>2536</v>
       </c>
       <c r="M331" s="1" t="inlineStr">
         <is>
@@ -21492,10 +21492,10 @@
         <v>0</v>
       </c>
       <c r="K332" s="1" t="n">
-        <v>5800000000</v>
+        <v>23000000000</v>
       </c>
       <c r="L332" s="1" t="n">
-        <v>1286</v>
+        <v>3296</v>
       </c>
       <c r="M332" s="1" t="inlineStr">
         <is>
@@ -21555,10 +21555,10 @@
         <v>0</v>
       </c>
       <c r="K333" s="1" t="n">
-        <v>2100000000</v>
+        <v>8000000000</v>
       </c>
       <c r="L333" s="1" t="n">
-        <v>450</v>
+        <v>1154</v>
       </c>
       <c r="M333" s="1" t="inlineStr">
         <is>
@@ -21618,10 +21618,10 @@
         <v>0</v>
       </c>
       <c r="K334" s="1" t="n">
-        <v>2700000000</v>
+        <v>11000000000</v>
       </c>
       <c r="L334" s="1" t="n">
-        <v>585</v>
+        <v>1501</v>
       </c>
       <c r="M334" s="1" t="inlineStr">
         <is>
@@ -21681,10 +21681,10 @@
         <v>0</v>
       </c>
       <c r="K335" s="1" t="n">
-        <v>3400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L335" s="1" t="n">
-        <v>761</v>
+        <v>1951</v>
       </c>
       <c r="M335" s="1" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>0</v>
       </c>
       <c r="K336" s="1" t="n">
-        <v>3400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L336" s="1" t="n">
-        <v>761</v>
+        <v>1951</v>
       </c>
       <c r="M336" s="1" t="inlineStr">
         <is>
@@ -21807,10 +21807,10 @@
         <v>0</v>
       </c>
       <c r="K337" s="1" t="n">
-        <v>4500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="L337" s="1" t="n">
-        <v>989</v>
+        <v>2536</v>
       </c>
       <c r="M337" s="1" t="inlineStr">
         <is>
@@ -21870,10 +21870,10 @@
         <v>0</v>
       </c>
       <c r="K338" s="1" t="n">
-        <v>4500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="L338" s="1" t="n">
-        <v>989</v>
+        <v>2536</v>
       </c>
       <c r="M338" s="1" t="inlineStr">
         <is>
@@ -21933,10 +21933,10 @@
         <v>0</v>
       </c>
       <c r="K339" s="1" t="n">
-        <v>5800000000</v>
+        <v>23000000000</v>
       </c>
       <c r="L339" s="1" t="n">
-        <v>1286</v>
+        <v>3296</v>
       </c>
       <c r="M339" s="1" t="inlineStr">
         <is>
@@ -21969,11 +21969,11 @@
       </c>
       <c r="C340" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +4층</t>
         </is>
       </c>
       <c r="D340" s="1" t="n">
-        <v>2492332</v>
+        <v>2492732</v>
       </c>
       <c r="E340" s="1" t="inlineStr">
         <is>
@@ -21996,10 +21996,10 @@
         <v>0</v>
       </c>
       <c r="K340" s="1" t="n">
-        <v>5300000000</v>
+        <v>21000000000</v>
       </c>
       <c r="L340" s="1" t="n">
-        <v>1170</v>
+        <v>3001</v>
       </c>
       <c r="M340" s="1" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         </is>
       </c>
       <c r="N340" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O340" s="1" t="n">
         <v>0</v>
@@ -22059,10 +22059,10 @@
         <v>0</v>
       </c>
       <c r="K341" s="1" t="n">
-        <v>3400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L341" s="1" t="n">
-        <v>761</v>
+        <v>1951</v>
       </c>
       <c r="M341" s="1" t="inlineStr">
         <is>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="K342" s="1" t="n">
-        <v>8900000000</v>
+        <v>36000000000</v>
       </c>
       <c r="L342" s="1" t="n">
-        <v>1978</v>
+        <v>5071</v>
       </c>
       <c r="M342" s="1" t="inlineStr">
         <is>
@@ -22185,10 +22185,10 @@
         <v>0</v>
       </c>
       <c r="K343" s="1" t="n">
-        <v>3400000000</v>
+        <v>14000000000</v>
       </c>
       <c r="L343" s="1" t="n">
-        <v>761</v>
+        <v>1951</v>
       </c>
       <c r="M343" s="1" t="inlineStr">
         <is>
@@ -22248,10 +22248,10 @@
         <v>0</v>
       </c>
       <c r="K344" s="1" t="n">
-        <v>5800000000</v>
+        <v>23000000000</v>
       </c>
       <c r="L344" s="1" t="n">
-        <v>1286</v>
+        <v>3296</v>
       </c>
       <c r="M344" s="1" t="inlineStr">
         <is>
@@ -22311,10 +22311,10 @@
         <v>0</v>
       </c>
       <c r="K345" s="1" t="n">
-        <v>4500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="L345" s="1" t="n">
-        <v>989</v>
+        <v>2536</v>
       </c>
       <c r="M345" s="1" t="inlineStr">
         <is>
@@ -22443,10 +22443,10 @@
         <v>0</v>
       </c>
       <c r="K347" s="1" t="n">
-        <v>9900000000</v>
+        <v>120000000000</v>
       </c>
       <c r="L347" s="1" t="n">
-        <v>1650</v>
+        <v>11810</v>
       </c>
       <c r="M347" s="1" t="inlineStr">
         <is>
@@ -22506,10 +22506,10 @@
         <v>0</v>
       </c>
       <c r="K348" s="1" t="n">
-        <v>13000000000</v>
+        <v>160000000000</v>
       </c>
       <c r="L348" s="1" t="n">
-        <v>2145</v>
+        <v>15353</v>
       </c>
       <c r="M348" s="1" t="inlineStr">
         <is>
@@ -22569,10 +22569,10 @@
         <v>0</v>
       </c>
       <c r="K349" s="1" t="n">
-        <v>17000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="L349" s="1" t="n">
-        <v>2789</v>
+        <v>19959</v>
       </c>
       <c r="M349" s="1" t="inlineStr">
         <is>
@@ -22632,10 +22632,10 @@
         <v>0</v>
       </c>
       <c r="K350" s="1" t="n">
-        <v>17000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="L350" s="1" t="n">
-        <v>2789</v>
+        <v>19959</v>
       </c>
       <c r="M350" s="1" t="inlineStr">
         <is>
@@ -22695,10 +22695,10 @@
         <v>0</v>
       </c>
       <c r="K351" s="1" t="n">
-        <v>22000000000</v>
+        <v>260000000000</v>
       </c>
       <c r="L351" s="1" t="n">
-        <v>3626</v>
+        <v>25946</v>
       </c>
       <c r="M351" s="1" t="inlineStr">
         <is>
@@ -22758,10 +22758,10 @@
         <v>0</v>
       </c>
       <c r="K352" s="1" t="n">
-        <v>17000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="L352" s="1" t="n">
-        <v>2789</v>
+        <v>19959</v>
       </c>
       <c r="M352" s="1" t="inlineStr">
         <is>
@@ -22821,10 +22821,10 @@
         <v>0</v>
       </c>
       <c r="K353" s="1" t="n">
-        <v>22000000000</v>
+        <v>260000000000</v>
       </c>
       <c r="L353" s="1" t="n">
-        <v>3626</v>
+        <v>25946</v>
       </c>
       <c r="M353" s="1" t="inlineStr">
         <is>
@@ -22884,10 +22884,10 @@
         <v>0</v>
       </c>
       <c r="K354" s="1" t="n">
-        <v>22000000000</v>
+        <v>260000000000</v>
       </c>
       <c r="L354" s="1" t="n">
-        <v>3626</v>
+        <v>25946</v>
       </c>
       <c r="M354" s="1" t="inlineStr">
         <is>
@@ -22947,10 +22947,10 @@
         <v>0</v>
       </c>
       <c r="K355" s="1" t="n">
-        <v>9900000000</v>
+        <v>120000000000</v>
       </c>
       <c r="L355" s="1" t="n">
-        <v>1650</v>
+        <v>11810</v>
       </c>
       <c r="M355" s="1" t="inlineStr">
         <is>
@@ -23010,10 +23010,10 @@
         <v>0</v>
       </c>
       <c r="K356" s="1" t="n">
-        <v>13000000000</v>
+        <v>160000000000</v>
       </c>
       <c r="L356" s="1" t="n">
-        <v>2145</v>
+        <v>15353</v>
       </c>
       <c r="M356" s="1" t="inlineStr">
         <is>
@@ -23073,10 +23073,10 @@
         <v>0</v>
       </c>
       <c r="K357" s="1" t="n">
-        <v>17000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="L357" s="1" t="n">
-        <v>2789</v>
+        <v>19959</v>
       </c>
       <c r="M357" s="1" t="inlineStr">
         <is>
@@ -23136,10 +23136,10 @@
         <v>0</v>
       </c>
       <c r="K358" s="1" t="n">
-        <v>17000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="L358" s="1" t="n">
-        <v>2789</v>
+        <v>19959</v>
       </c>
       <c r="M358" s="1" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         <v>0</v>
       </c>
       <c r="K359" s="1" t="n">
-        <v>17000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="L359" s="1" t="n">
-        <v>2789</v>
+        <v>19959</v>
       </c>
       <c r="M359" s="1" t="inlineStr">
         <is>
@@ -23262,10 +23262,10 @@
         <v>0</v>
       </c>
       <c r="K360" s="1" t="n">
-        <v>22000000000</v>
+        <v>260000000000</v>
       </c>
       <c r="L360" s="1" t="n">
-        <v>3626</v>
+        <v>25946</v>
       </c>
       <c r="M360" s="1" t="inlineStr">
         <is>
@@ -23325,10 +23325,10 @@
         <v>0</v>
       </c>
       <c r="K361" s="1" t="n">
-        <v>29000000000</v>
+        <v>340000000000</v>
       </c>
       <c r="L361" s="1" t="n">
-        <v>4713</v>
+        <v>33730</v>
       </c>
       <c r="M361" s="1" t="inlineStr">
         <is>
@@ -23388,10 +23388,10 @@
         <v>0</v>
       </c>
       <c r="K362" s="1" t="n">
-        <v>22000000000</v>
+        <v>260000000000</v>
       </c>
       <c r="L362" s="1" t="n">
-        <v>3626</v>
+        <v>25946</v>
       </c>
       <c r="M362" s="1" t="inlineStr">
         <is>
@@ -23451,10 +23451,10 @@
         <v>0</v>
       </c>
       <c r="K363" s="1" t="n">
-        <v>9900000000</v>
+        <v>120000000000</v>
       </c>
       <c r="L363" s="1" t="n">
-        <v>1650</v>
+        <v>11810</v>
       </c>
       <c r="M363" s="1" t="inlineStr">
         <is>
@@ -23514,10 +23514,10 @@
         <v>0</v>
       </c>
       <c r="K364" s="1" t="n">
-        <v>13000000000</v>
+        <v>160000000000</v>
       </c>
       <c r="L364" s="1" t="n">
-        <v>2145</v>
+        <v>15353</v>
       </c>
       <c r="M364" s="1" t="inlineStr">
         <is>
@@ -23577,10 +23577,10 @@
         <v>0</v>
       </c>
       <c r="K365" s="1" t="n">
-        <v>17000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="L365" s="1" t="n">
-        <v>2789</v>
+        <v>19959</v>
       </c>
       <c r="M365" s="1" t="inlineStr">
         <is>
@@ -23640,10 +23640,10 @@
         <v>0</v>
       </c>
       <c r="K366" s="1" t="n">
-        <v>17000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="L366" s="1" t="n">
-        <v>2789</v>
+        <v>19959</v>
       </c>
       <c r="M366" s="1" t="inlineStr">
         <is>
@@ -23703,10 +23703,10 @@
         <v>0</v>
       </c>
       <c r="K367" s="1" t="n">
-        <v>22000000000</v>
+        <v>260000000000</v>
       </c>
       <c r="L367" s="1" t="n">
-        <v>3626</v>
+        <v>25946</v>
       </c>
       <c r="M367" s="1" t="inlineStr">
         <is>
@@ -23766,10 +23766,10 @@
         <v>0</v>
       </c>
       <c r="K368" s="1" t="n">
-        <v>22000000000</v>
+        <v>260000000000</v>
       </c>
       <c r="L368" s="1" t="n">
-        <v>3626</v>
+        <v>25946</v>
       </c>
       <c r="M368" s="1" t="inlineStr">
         <is>
@@ -23829,10 +23829,10 @@
         <v>0</v>
       </c>
       <c r="K369" s="1" t="n">
-        <v>22000000000</v>
+        <v>260000000000</v>
       </c>
       <c r="L369" s="1" t="n">
-        <v>3626</v>
+        <v>25946</v>
       </c>
       <c r="M369" s="1" t="inlineStr">
         <is>
@@ -23892,10 +23892,10 @@
         <v>0</v>
       </c>
       <c r="K370" s="1" t="n">
-        <v>29000000000</v>
+        <v>340000000000</v>
       </c>
       <c r="L370" s="1" t="n">
-        <v>4713</v>
+        <v>33730</v>
       </c>
       <c r="M370" s="1" t="inlineStr">
         <is>
@@ -23955,10 +23955,10 @@
         <v>0</v>
       </c>
       <c r="K371" s="1" t="n">
-        <v>9900000000</v>
+        <v>120000000000</v>
       </c>
       <c r="L371" s="1" t="n">
-        <v>1650</v>
+        <v>11810</v>
       </c>
       <c r="M371" s="1" t="inlineStr">
         <is>
@@ -24018,10 +24018,10 @@
         <v>0</v>
       </c>
       <c r="K372" s="1" t="n">
-        <v>13000000000</v>
+        <v>160000000000</v>
       </c>
       <c r="L372" s="1" t="n">
-        <v>2145</v>
+        <v>15353</v>
       </c>
       <c r="M372" s="1" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="K373" s="1" t="n">
-        <v>17000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="L373" s="1" t="n">
-        <v>2789</v>
+        <v>19959</v>
       </c>
       <c r="M373" s="1" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>0</v>
       </c>
       <c r="K374" s="1" t="n">
-        <v>17000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="L374" s="1" t="n">
-        <v>2789</v>
+        <v>19959</v>
       </c>
       <c r="M374" s="1" t="inlineStr">
         <is>
@@ -24207,10 +24207,10 @@
         <v>0</v>
       </c>
       <c r="K375" s="1" t="n">
-        <v>22000000000</v>
+        <v>260000000000</v>
       </c>
       <c r="L375" s="1" t="n">
-        <v>3626</v>
+        <v>25946</v>
       </c>
       <c r="M375" s="1" t="inlineStr">
         <is>
@@ -24270,10 +24270,10 @@
         <v>0</v>
       </c>
       <c r="K376" s="1" t="n">
-        <v>22000000000</v>
+        <v>260000000000</v>
       </c>
       <c r="L376" s="1" t="n">
-        <v>3626</v>
+        <v>25946</v>
       </c>
       <c r="M376" s="1" t="inlineStr">
         <is>
@@ -24333,10 +24333,10 @@
         <v>0</v>
       </c>
       <c r="K377" s="1" t="n">
-        <v>29000000000</v>
+        <v>340000000000</v>
       </c>
       <c r="L377" s="1" t="n">
-        <v>4713</v>
+        <v>33730</v>
       </c>
       <c r="M377" s="1" t="inlineStr">
         <is>
@@ -24369,11 +24369,11 @@
       </c>
       <c r="C378" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +4층</t>
         </is>
       </c>
       <c r="D378" s="1" t="n">
-        <v>2492332</v>
+        <v>2492732</v>
       </c>
       <c r="E378" s="1" t="inlineStr">
         <is>
@@ -24396,10 +24396,10 @@
         <v>0</v>
       </c>
       <c r="K378" s="1" t="n">
-        <v>26000000000</v>
+        <v>310000000000</v>
       </c>
       <c r="L378" s="1" t="n">
-        <v>4290</v>
+        <v>30705</v>
       </c>
       <c r="M378" s="1" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         </is>
       </c>
       <c r="N378" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O378" s="1" t="n">
         <v>0</v>
@@ -24459,10 +24459,10 @@
         <v>0</v>
       </c>
       <c r="K379" s="1" t="n">
-        <v>34000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="L379" s="1" t="n">
-        <v>5578</v>
+        <v>39917</v>
       </c>
       <c r="M379" s="1" t="inlineStr">
         <is>
@@ -24522,10 +24522,10 @@
         <v>0</v>
       </c>
       <c r="K380" s="1" t="n">
-        <v>44000000000</v>
+        <v>510000000000</v>
       </c>
       <c r="L380" s="1" t="n">
-        <v>7251</v>
+        <v>51891</v>
       </c>
       <c r="M380" s="1" t="inlineStr">
         <is>
@@ -24585,10 +24585,10 @@
         <v>0</v>
       </c>
       <c r="K381" s="1" t="n">
-        <v>17000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="L381" s="1" t="n">
-        <v>2789</v>
+        <v>19959</v>
       </c>
       <c r="M381" s="1" t="inlineStr">
         <is>
@@ -24648,10 +24648,10 @@
         <v>0</v>
       </c>
       <c r="K382" s="1" t="n">
-        <v>29000000000</v>
+        <v>340000000000</v>
       </c>
       <c r="L382" s="1" t="n">
-        <v>4713</v>
+        <v>33730</v>
       </c>
       <c r="M382" s="1" t="inlineStr">
         <is>
@@ -24711,10 +24711,10 @@
         <v>0</v>
       </c>
       <c r="K383" s="1" t="n">
-        <v>22000000000</v>
+        <v>260000000000</v>
       </c>
       <c r="L383" s="1" t="n">
-        <v>3626</v>
+        <v>25946</v>
       </c>
       <c r="M383" s="1" t="inlineStr">
         <is>
@@ -24843,10 +24843,10 @@
         <v>0</v>
       </c>
       <c r="K385" s="1" t="n">
-        <v>29000000000</v>
+        <v>340000000000</v>
       </c>
       <c r="L385" s="1" t="n">
-        <v>3780</v>
+        <v>25950</v>
       </c>
       <c r="M385" s="1" t="inlineStr">
         <is>
@@ -24906,10 +24906,10 @@
         <v>0</v>
       </c>
       <c r="K386" s="1" t="n">
-        <v>37000000000</v>
+        <v>440000000000</v>
       </c>
       <c r="L386" s="1" t="n">
-        <v>4914</v>
+        <v>33735</v>
       </c>
       <c r="M386" s="1" t="inlineStr">
         <is>
@@ -24969,10 +24969,10 @@
         <v>0</v>
       </c>
       <c r="K387" s="1" t="n">
-        <v>48000000000</v>
+        <v>570000000000</v>
       </c>
       <c r="L387" s="1" t="n">
-        <v>6389</v>
+        <v>43856</v>
       </c>
       <c r="M387" s="1" t="inlineStr">
         <is>
@@ -25032,10 +25032,10 @@
         <v>0</v>
       </c>
       <c r="K388" s="1" t="n">
-        <v>48000000000</v>
+        <v>570000000000</v>
       </c>
       <c r="L388" s="1" t="n">
-        <v>6389</v>
+        <v>43856</v>
       </c>
       <c r="M388" s="1" t="inlineStr">
         <is>
@@ -25095,10 +25095,10 @@
         <v>0</v>
       </c>
       <c r="K389" s="1" t="n">
-        <v>63000000000</v>
+        <v>740000000000</v>
       </c>
       <c r="L389" s="1" t="n">
-        <v>8305</v>
+        <v>57013</v>
       </c>
       <c r="M389" s="1" t="inlineStr">
         <is>
@@ -25158,10 +25158,10 @@
         <v>0</v>
       </c>
       <c r="K390" s="1" t="n">
-        <v>48000000000</v>
+        <v>570000000000</v>
       </c>
       <c r="L390" s="1" t="n">
-        <v>6389</v>
+        <v>43856</v>
       </c>
       <c r="M390" s="1" t="inlineStr">
         <is>
@@ -25221,10 +25221,10 @@
         <v>0</v>
       </c>
       <c r="K391" s="1" t="n">
-        <v>63000000000</v>
+        <v>740000000000</v>
       </c>
       <c r="L391" s="1" t="n">
-        <v>8305</v>
+        <v>57013</v>
       </c>
       <c r="M391" s="1" t="inlineStr">
         <is>
@@ -25284,10 +25284,10 @@
         <v>0</v>
       </c>
       <c r="K392" s="1" t="n">
-        <v>63000000000</v>
+        <v>740000000000</v>
       </c>
       <c r="L392" s="1" t="n">
-        <v>8305</v>
+        <v>57013</v>
       </c>
       <c r="M392" s="1" t="inlineStr">
         <is>
@@ -25347,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="K393" s="1" t="n">
-        <v>29000000000</v>
+        <v>340000000000</v>
       </c>
       <c r="L393" s="1" t="n">
-        <v>3780</v>
+        <v>25950</v>
       </c>
       <c r="M393" s="1" t="inlineStr">
         <is>
@@ -25410,10 +25410,10 @@
         <v>0</v>
       </c>
       <c r="K394" s="1" t="n">
-        <v>37000000000</v>
+        <v>440000000000</v>
       </c>
       <c r="L394" s="1" t="n">
-        <v>4914</v>
+        <v>33735</v>
       </c>
       <c r="M394" s="1" t="inlineStr">
         <is>
@@ -25473,10 +25473,10 @@
         <v>0</v>
       </c>
       <c r="K395" s="1" t="n">
-        <v>48000000000</v>
+        <v>570000000000</v>
       </c>
       <c r="L395" s="1" t="n">
-        <v>6389</v>
+        <v>43856</v>
       </c>
       <c r="M395" s="1" t="inlineStr">
         <is>
@@ -25536,10 +25536,10 @@
         <v>0</v>
       </c>
       <c r="K396" s="1" t="n">
-        <v>48000000000</v>
+        <v>570000000000</v>
       </c>
       <c r="L396" s="1" t="n">
-        <v>6389</v>
+        <v>43856</v>
       </c>
       <c r="M396" s="1" t="inlineStr">
         <is>
@@ -25599,10 +25599,10 @@
         <v>0</v>
       </c>
       <c r="K397" s="1" t="n">
-        <v>48000000000</v>
+        <v>570000000000</v>
       </c>
       <c r="L397" s="1" t="n">
-        <v>6389</v>
+        <v>43856</v>
       </c>
       <c r="M397" s="1" t="inlineStr">
         <is>
@@ -25662,10 +25662,10 @@
         <v>0</v>
       </c>
       <c r="K398" s="1" t="n">
-        <v>63000000000</v>
+        <v>740000000000</v>
       </c>
       <c r="L398" s="1" t="n">
-        <v>8305</v>
+        <v>57013</v>
       </c>
       <c r="M398" s="1" t="inlineStr">
         <is>
@@ -25725,10 +25725,10 @@
         <v>0</v>
       </c>
       <c r="K399" s="1" t="n">
-        <v>81000000000</v>
+        <v>960000000000</v>
       </c>
       <c r="L399" s="1" t="n">
-        <v>10797</v>
+        <v>74116</v>
       </c>
       <c r="M399" s="1" t="inlineStr">
         <is>
@@ -25788,10 +25788,10 @@
         <v>0</v>
       </c>
       <c r="K400" s="1" t="n">
-        <v>63000000000</v>
+        <v>740000000000</v>
       </c>
       <c r="L400" s="1" t="n">
-        <v>8305</v>
+        <v>57013</v>
       </c>
       <c r="M400" s="1" t="inlineStr">
         <is>
@@ -25851,10 +25851,10 @@
         <v>0</v>
       </c>
       <c r="K401" s="1" t="n">
-        <v>29000000000</v>
+        <v>340000000000</v>
       </c>
       <c r="L401" s="1" t="n">
-        <v>3780</v>
+        <v>25950</v>
       </c>
       <c r="M401" s="1" t="inlineStr">
         <is>
@@ -25914,10 +25914,10 @@
         <v>0</v>
       </c>
       <c r="K402" s="1" t="n">
-        <v>37000000000</v>
+        <v>440000000000</v>
       </c>
       <c r="L402" s="1" t="n">
-        <v>4914</v>
+        <v>33735</v>
       </c>
       <c r="M402" s="1" t="inlineStr">
         <is>
@@ -25977,10 +25977,10 @@
         <v>0</v>
       </c>
       <c r="K403" s="1" t="n">
-        <v>48000000000</v>
+        <v>570000000000</v>
       </c>
       <c r="L403" s="1" t="n">
-        <v>6389</v>
+        <v>43856</v>
       </c>
       <c r="M403" s="1" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>0</v>
       </c>
       <c r="K404" s="1" t="n">
-        <v>48000000000</v>
+        <v>570000000000</v>
       </c>
       <c r="L404" s="1" t="n">
-        <v>6389</v>
+        <v>43856</v>
       </c>
       <c r="M404" s="1" t="inlineStr">
         <is>
@@ -26103,10 +26103,10 @@
         <v>0</v>
       </c>
       <c r="K405" s="1" t="n">
-        <v>63000000000</v>
+        <v>740000000000</v>
       </c>
       <c r="L405" s="1" t="n">
-        <v>8305</v>
+        <v>57013</v>
       </c>
       <c r="M405" s="1" t="inlineStr">
         <is>
@@ -26166,10 +26166,10 @@
         <v>0</v>
       </c>
       <c r="K406" s="1" t="n">
-        <v>63000000000</v>
+        <v>740000000000</v>
       </c>
       <c r="L406" s="1" t="n">
-        <v>8305</v>
+        <v>57013</v>
       </c>
       <c r="M406" s="1" t="inlineStr">
         <is>
@@ -26229,10 +26229,10 @@
         <v>0</v>
       </c>
       <c r="K407" s="1" t="n">
-        <v>63000000000</v>
+        <v>740000000000</v>
       </c>
       <c r="L407" s="1" t="n">
-        <v>8305</v>
+        <v>57013</v>
       </c>
       <c r="M407" s="1" t="inlineStr">
         <is>
@@ -26292,10 +26292,10 @@
         <v>0</v>
       </c>
       <c r="K408" s="1" t="n">
-        <v>81000000000</v>
+        <v>960000000000</v>
       </c>
       <c r="L408" s="1" t="n">
-        <v>10797</v>
+        <v>74116</v>
       </c>
       <c r="M408" s="1" t="inlineStr">
         <is>
@@ -26355,10 +26355,10 @@
         <v>0</v>
       </c>
       <c r="K409" s="1" t="n">
-        <v>29000000000</v>
+        <v>340000000000</v>
       </c>
       <c r="L409" s="1" t="n">
-        <v>3780</v>
+        <v>25950</v>
       </c>
       <c r="M409" s="1" t="inlineStr">
         <is>
@@ -26418,10 +26418,10 @@
         <v>0</v>
       </c>
       <c r="K410" s="1" t="n">
-        <v>37000000000</v>
+        <v>440000000000</v>
       </c>
       <c r="L410" s="1" t="n">
-        <v>4914</v>
+        <v>33735</v>
       </c>
       <c r="M410" s="1" t="inlineStr">
         <is>
@@ -26481,10 +26481,10 @@
         <v>0</v>
       </c>
       <c r="K411" s="1" t="n">
-        <v>48000000000</v>
+        <v>570000000000</v>
       </c>
       <c r="L411" s="1" t="n">
-        <v>6389</v>
+        <v>43856</v>
       </c>
       <c r="M411" s="1" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>0</v>
       </c>
       <c r="K412" s="1" t="n">
-        <v>48000000000</v>
+        <v>570000000000</v>
       </c>
       <c r="L412" s="1" t="n">
-        <v>6389</v>
+        <v>43856</v>
       </c>
       <c r="M412" s="1" t="inlineStr">
         <is>
@@ -26607,10 +26607,10 @@
         <v>0</v>
       </c>
       <c r="K413" s="1" t="n">
-        <v>63000000000</v>
+        <v>740000000000</v>
       </c>
       <c r="L413" s="1" t="n">
-        <v>8305</v>
+        <v>57013</v>
       </c>
       <c r="M413" s="1" t="inlineStr">
         <is>
@@ -26670,10 +26670,10 @@
         <v>0</v>
       </c>
       <c r="K414" s="1" t="n">
-        <v>63000000000</v>
+        <v>740000000000</v>
       </c>
       <c r="L414" s="1" t="n">
-        <v>8305</v>
+        <v>57013</v>
       </c>
       <c r="M414" s="1" t="inlineStr">
         <is>
@@ -26733,10 +26733,10 @@
         <v>0</v>
       </c>
       <c r="K415" s="1" t="n">
-        <v>81000000000</v>
+        <v>960000000000</v>
       </c>
       <c r="L415" s="1" t="n">
-        <v>10797</v>
+        <v>74116</v>
       </c>
       <c r="M415" s="1" t="inlineStr">
         <is>
@@ -26796,10 +26796,10 @@
         <v>0</v>
       </c>
       <c r="K416" s="1" t="n">
-        <v>74000000000</v>
+        <v>880000000000</v>
       </c>
       <c r="L416" s="1" t="n">
-        <v>9828</v>
+        <v>67470</v>
       </c>
       <c r="M416" s="1" t="inlineStr">
         <is>
@@ -26859,10 +26859,10 @@
         <v>0</v>
       </c>
       <c r="K417" s="1" t="n">
-        <v>48000000000</v>
+        <v>570000000000</v>
       </c>
       <c r="L417" s="1" t="n">
-        <v>6389</v>
+        <v>43856</v>
       </c>
       <c r="M417" s="1" t="inlineStr">
         <is>
@@ -26922,10 +26922,10 @@
         <v>0</v>
       </c>
       <c r="K418" s="1" t="n">
-        <v>130000000000</v>
+        <v>1500000000000</v>
       </c>
       <c r="L418" s="1" t="n">
-        <v>16610</v>
+        <v>114025</v>
       </c>
       <c r="M418" s="1" t="inlineStr">
         <is>
@@ -26985,10 +26985,10 @@
         <v>0</v>
       </c>
       <c r="K419" s="1" t="n">
-        <v>48000000000</v>
+        <v>570000000000</v>
       </c>
       <c r="L419" s="1" t="n">
-        <v>6389</v>
+        <v>43856</v>
       </c>
       <c r="M419" s="1" t="inlineStr">
         <is>
@@ -27048,10 +27048,10 @@
         <v>0</v>
       </c>
       <c r="K420" s="1" t="n">
-        <v>81000000000</v>
+        <v>960000000000</v>
       </c>
       <c r="L420" s="1" t="n">
-        <v>10797</v>
+        <v>74116</v>
       </c>
       <c r="M420" s="1" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         <v>0</v>
       </c>
       <c r="K421" s="1" t="n">
-        <v>63000000000</v>
+        <v>740000000000</v>
       </c>
       <c r="L421" s="1" t="n">
-        <v>8305</v>
+        <v>57013</v>
       </c>
       <c r="M421" s="1" t="inlineStr">
         <is>
@@ -27243,10 +27243,10 @@
         <v>0</v>
       </c>
       <c r="K423" s="1" t="n">
-        <v>110000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="L423" s="1" t="n">
-        <v>10760</v>
+        <v>111280</v>
       </c>
       <c r="M423" s="1" t="inlineStr">
         <is>
@@ -27306,10 +27306,10 @@
         <v>0</v>
       </c>
       <c r="K424" s="1" t="n">
-        <v>140000000000</v>
+        <v>2500000000000</v>
       </c>
       <c r="L424" s="1" t="n">
-        <v>13988</v>
+        <v>144664</v>
       </c>
       <c r="M424" s="1" t="inlineStr">
         <is>
@@ -27369,10 +27369,10 @@
         <v>0</v>
       </c>
       <c r="K425" s="1" t="n">
-        <v>180000000000</v>
+        <v>3300000000000</v>
       </c>
       <c r="L425" s="1" t="n">
-        <v>18185</v>
+        <v>188064</v>
       </c>
       <c r="M425" s="1" t="inlineStr">
         <is>
@@ -27432,10 +27432,10 @@
         <v>0</v>
       </c>
       <c r="K426" s="1" t="n">
-        <v>180000000000</v>
+        <v>3300000000000</v>
       </c>
       <c r="L426" s="1" t="n">
-        <v>18185</v>
+        <v>188064</v>
       </c>
       <c r="M426" s="1" t="inlineStr">
         <is>
@@ -27495,10 +27495,10 @@
         <v>0</v>
       </c>
       <c r="K427" s="1" t="n">
-        <v>230000000000</v>
+        <v>4300000000000</v>
       </c>
       <c r="L427" s="1" t="n">
-        <v>23640</v>
+        <v>244483</v>
       </c>
       <c r="M427" s="1" t="inlineStr">
         <is>
@@ -27558,10 +27558,10 @@
         <v>0</v>
       </c>
       <c r="K428" s="1" t="n">
-        <v>180000000000</v>
+        <v>3300000000000</v>
       </c>
       <c r="L428" s="1" t="n">
-        <v>18185</v>
+        <v>188064</v>
       </c>
       <c r="M428" s="1" t="inlineStr">
         <is>
@@ -27621,10 +27621,10 @@
         <v>0</v>
       </c>
       <c r="K429" s="1" t="n">
-        <v>230000000000</v>
+        <v>4300000000000</v>
       </c>
       <c r="L429" s="1" t="n">
-        <v>23640</v>
+        <v>244483</v>
       </c>
       <c r="M429" s="1" t="inlineStr">
         <is>
@@ -27684,10 +27684,10 @@
         <v>0</v>
       </c>
       <c r="K430" s="1" t="n">
-        <v>230000000000</v>
+        <v>4300000000000</v>
       </c>
       <c r="L430" s="1" t="n">
-        <v>23640</v>
+        <v>244483</v>
       </c>
       <c r="M430" s="1" t="inlineStr">
         <is>
@@ -27747,10 +27747,10 @@
         <v>0</v>
       </c>
       <c r="K431" s="1" t="n">
-        <v>110000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="L431" s="1" t="n">
-        <v>10760</v>
+        <v>111280</v>
       </c>
       <c r="M431" s="1" t="inlineStr">
         <is>
@@ -27810,10 +27810,10 @@
         <v>0</v>
       </c>
       <c r="K432" s="1" t="n">
-        <v>140000000000</v>
+        <v>2500000000000</v>
       </c>
       <c r="L432" s="1" t="n">
-        <v>13988</v>
+        <v>144664</v>
       </c>
       <c r="M432" s="1" t="inlineStr">
         <is>
@@ -27873,10 +27873,10 @@
         <v>0</v>
       </c>
       <c r="K433" s="1" t="n">
-        <v>180000000000</v>
+        <v>3300000000000</v>
       </c>
       <c r="L433" s="1" t="n">
-        <v>18185</v>
+        <v>188064</v>
       </c>
       <c r="M433" s="1" t="inlineStr">
         <is>
@@ -27936,10 +27936,10 @@
         <v>0</v>
       </c>
       <c r="K434" s="1" t="n">
-        <v>350000000000</v>
+        <v>6500000000000</v>
       </c>
       <c r="L434" s="1" t="n">
-        <v>36369</v>
+        <v>376127</v>
       </c>
       <c r="M434" s="1" t="inlineStr">
         <is>
@@ -27999,10 +27999,10 @@
         <v>0</v>
       </c>
       <c r="K435" s="1" t="n">
-        <v>180000000000</v>
+        <v>3300000000000</v>
       </c>
       <c r="L435" s="1" t="n">
-        <v>18185</v>
+        <v>188064</v>
       </c>
       <c r="M435" s="1" t="inlineStr">
         <is>
@@ -28062,10 +28062,10 @@
         <v>0</v>
       </c>
       <c r="K436" s="1" t="n">
-        <v>450000000000</v>
+        <v>8500000000000</v>
       </c>
       <c r="L436" s="1" t="n">
-        <v>47280</v>
+        <v>488965</v>
       </c>
       <c r="M436" s="1" t="inlineStr">
         <is>
@@ -28125,10 +28125,10 @@
         <v>0</v>
       </c>
       <c r="K437" s="1" t="n">
-        <v>290000000000</v>
+        <v>5500000000000</v>
       </c>
       <c r="L437" s="1" t="n">
-        <v>30732</v>
+        <v>317827</v>
       </c>
       <c r="M437" s="1" t="inlineStr">
         <is>
@@ -28188,10 +28188,10 @@
         <v>0</v>
       </c>
       <c r="K438" s="1" t="n">
-        <v>450000000000</v>
+        <v>8500000000000</v>
       </c>
       <c r="L438" s="1" t="n">
-        <v>47280</v>
+        <v>488965</v>
       </c>
       <c r="M438" s="1" t="inlineStr">
         <is>
@@ -28251,10 +28251,10 @@
         <v>0</v>
       </c>
       <c r="K439" s="1" t="n">
-        <v>110000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="L439" s="1" t="n">
-        <v>10760</v>
+        <v>111280</v>
       </c>
       <c r="M439" s="1" t="inlineStr">
         <is>
@@ -28314,10 +28314,10 @@
         <v>0</v>
       </c>
       <c r="K440" s="1" t="n">
-        <v>140000000000</v>
+        <v>2500000000000</v>
       </c>
       <c r="L440" s="1" t="n">
-        <v>13988</v>
+        <v>144664</v>
       </c>
       <c r="M440" s="1" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>0</v>
       </c>
       <c r="K441" s="1" t="n">
-        <v>180000000000</v>
+        <v>3300000000000</v>
       </c>
       <c r="L441" s="1" t="n">
-        <v>18185</v>
+        <v>188064</v>
       </c>
       <c r="M441" s="1" t="inlineStr">
         <is>
@@ -28440,10 +28440,10 @@
         <v>0</v>
       </c>
       <c r="K442" s="1" t="n">
-        <v>180000000000</v>
+        <v>3300000000000</v>
       </c>
       <c r="L442" s="1" t="n">
-        <v>18185</v>
+        <v>188064</v>
       </c>
       <c r="M442" s="1" t="inlineStr">
         <is>
@@ -28503,10 +28503,10 @@
         <v>0</v>
       </c>
       <c r="K443" s="1" t="n">
-        <v>230000000000</v>
+        <v>4300000000000</v>
       </c>
       <c r="L443" s="1" t="n">
-        <v>23640</v>
+        <v>244483</v>
       </c>
       <c r="M443" s="1" t="inlineStr">
         <is>
@@ -28566,10 +28566,10 @@
         <v>0</v>
       </c>
       <c r="K444" s="1" t="n">
-        <v>230000000000</v>
+        <v>4300000000000</v>
       </c>
       <c r="L444" s="1" t="n">
-        <v>23640</v>
+        <v>244483</v>
       </c>
       <c r="M444" s="1" t="inlineStr">
         <is>
@@ -28629,10 +28629,10 @@
         <v>0</v>
       </c>
       <c r="K445" s="1" t="n">
-        <v>230000000000</v>
+        <v>4300000000000</v>
       </c>
       <c r="L445" s="1" t="n">
-        <v>23640</v>
+        <v>244483</v>
       </c>
       <c r="M445" s="1" t="inlineStr">
         <is>
@@ -28692,10 +28692,10 @@
         <v>0</v>
       </c>
       <c r="K446" s="1" t="n">
-        <v>290000000000</v>
+        <v>5500000000000</v>
       </c>
       <c r="L446" s="1" t="n">
-        <v>30732</v>
+        <v>317827</v>
       </c>
       <c r="M446" s="1" t="inlineStr">
         <is>
@@ -28755,10 +28755,10 @@
         <v>0</v>
       </c>
       <c r="K447" s="1" t="n">
-        <v>110000000000</v>
+        <v>2000000000000</v>
       </c>
       <c r="L447" s="1" t="n">
-        <v>10760</v>
+        <v>111280</v>
       </c>
       <c r="M447" s="1" t="inlineStr">
         <is>
@@ -28818,10 +28818,10 @@
         <v>0</v>
       </c>
       <c r="K448" s="1" t="n">
-        <v>140000000000</v>
+        <v>2500000000000</v>
       </c>
       <c r="L448" s="1" t="n">
-        <v>13988</v>
+        <v>144664</v>
       </c>
       <c r="M448" s="1" t="inlineStr">
         <is>
@@ -28881,10 +28881,10 @@
         <v>0</v>
       </c>
       <c r="K449" s="1" t="n">
-        <v>180000000000</v>
+        <v>3300000000000</v>
       </c>
       <c r="L449" s="1" t="n">
-        <v>18185</v>
+        <v>188064</v>
       </c>
       <c r="M449" s="1" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>0</v>
       </c>
       <c r="K450" s="1" t="n">
-        <v>180000000000</v>
+        <v>3300000000000</v>
       </c>
       <c r="L450" s="1" t="n">
-        <v>18185</v>
+        <v>188064</v>
       </c>
       <c r="M450" s="1" t="inlineStr">
         <is>
@@ -29007,10 +29007,10 @@
         <v>0</v>
       </c>
       <c r="K451" s="1" t="n">
-        <v>230000000000</v>
+        <v>4300000000000</v>
       </c>
       <c r="L451" s="1" t="n">
-        <v>23640</v>
+        <v>244483</v>
       </c>
       <c r="M451" s="1" t="inlineStr">
         <is>
@@ -29070,10 +29070,10 @@
         <v>0</v>
       </c>
       <c r="K452" s="1" t="n">
-        <v>230000000000</v>
+        <v>4300000000000</v>
       </c>
       <c r="L452" s="1" t="n">
-        <v>23640</v>
+        <v>244483</v>
       </c>
       <c r="M452" s="1" t="inlineStr">
         <is>
@@ -29133,10 +29133,10 @@
         <v>0</v>
       </c>
       <c r="K453" s="1" t="n">
-        <v>290000000000</v>
+        <v>5500000000000</v>
       </c>
       <c r="L453" s="1" t="n">
-        <v>30732</v>
+        <v>317827</v>
       </c>
       <c r="M453" s="1" t="inlineStr">
         <is>
@@ -29196,10 +29196,10 @@
         <v>0</v>
       </c>
       <c r="K454" s="1" t="n">
-        <v>270000000000</v>
+        <v>5000000000000</v>
       </c>
       <c r="L454" s="1" t="n">
-        <v>27976</v>
+        <v>289328</v>
       </c>
       <c r="M454" s="1" t="inlineStr">
         <is>
@@ -29259,10 +29259,10 @@
         <v>0</v>
       </c>
       <c r="K455" s="1" t="n">
-        <v>180000000000</v>
+        <v>3300000000000</v>
       </c>
       <c r="L455" s="1" t="n">
-        <v>18185</v>
+        <v>188064</v>
       </c>
       <c r="M455" s="1" t="inlineStr">
         <is>
@@ -29295,11 +29295,11 @@
       </c>
       <c r="C456" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +2층</t>
         </is>
       </c>
       <c r="D456" s="1" t="n">
-        <v>2492332</v>
+        <v>2492132</v>
       </c>
       <c r="E456" s="1" t="inlineStr">
         <is>
@@ -29322,10 +29322,10 @@
         <v>0</v>
       </c>
       <c r="K456" s="1" t="n">
-        <v>450000000000</v>
+        <v>8500000000000</v>
       </c>
       <c r="L456" s="1" t="n">
-        <v>47280</v>
+        <v>488965</v>
       </c>
       <c r="M456" s="1" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         </is>
       </c>
       <c r="N456" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O456" s="1" t="n">
         <v>0</v>
@@ -29385,10 +29385,10 @@
         <v>0</v>
       </c>
       <c r="K457" s="1" t="n">
-        <v>180000000000</v>
+        <v>3300000000000</v>
       </c>
       <c r="L457" s="1" t="n">
-        <v>18185</v>
+        <v>188064</v>
       </c>
       <c r="M457" s="1" t="inlineStr">
         <is>
@@ -29448,10 +29448,10 @@
         <v>0</v>
       </c>
       <c r="K458" s="1" t="n">
-        <v>290000000000</v>
+        <v>5500000000000</v>
       </c>
       <c r="L458" s="1" t="n">
-        <v>30732</v>
+        <v>317827</v>
       </c>
       <c r="M458" s="1" t="inlineStr">
         <is>
@@ -29511,10 +29511,10 @@
         <v>0</v>
       </c>
       <c r="K459" s="1" t="n">
-        <v>450000000000</v>
+        <v>8500000000000</v>
       </c>
       <c r="L459" s="1" t="n">
-        <v>47280</v>
+        <v>488965</v>
       </c>
       <c r="M459" s="1" t="inlineStr">
         <is>
@@ -29643,10 +29643,10 @@
         <v>0</v>
       </c>
       <c r="K461" s="1" t="n">
-        <v>180000000000</v>
+        <v>15000000000000</v>
       </c>
       <c r="L461" s="1" t="n">
-        <v>16130</v>
+        <v>621000</v>
       </c>
       <c r="M461" s="1" t="inlineStr">
         <is>
@@ -29706,10 +29706,10 @@
         <v>0</v>
       </c>
       <c r="K462" s="1" t="n">
-        <v>240000000000</v>
+        <v>20000000000000</v>
       </c>
       <c r="L462" s="1" t="n">
-        <v>20969</v>
+        <v>807300</v>
       </c>
       <c r="M462" s="1" t="inlineStr">
         <is>
@@ -29769,10 +29769,10 @@
         <v>0</v>
       </c>
       <c r="K463" s="1" t="n">
-        <v>310000000000</v>
+        <v>25000000000000</v>
       </c>
       <c r="L463" s="1" t="n">
-        <v>27260</v>
+        <v>1049490</v>
       </c>
       <c r="M463" s="1" t="inlineStr">
         <is>
@@ -29832,10 +29832,10 @@
         <v>0</v>
       </c>
       <c r="K464" s="1" t="n">
-        <v>310000000000</v>
+        <v>25000000000000</v>
       </c>
       <c r="L464" s="1" t="n">
-        <v>27260</v>
+        <v>1049490</v>
       </c>
       <c r="M464" s="1" t="inlineStr">
         <is>
@@ -29895,10 +29895,10 @@
         <v>0</v>
       </c>
       <c r="K465" s="1" t="n">
-        <v>400000000000</v>
+        <v>33000000000000</v>
       </c>
       <c r="L465" s="1" t="n">
-        <v>35438</v>
+        <v>1364337</v>
       </c>
       <c r="M465" s="1" t="inlineStr">
         <is>
@@ -29958,10 +29958,10 @@
         <v>0</v>
       </c>
       <c r="K466" s="1" t="n">
-        <v>310000000000</v>
+        <v>25000000000000</v>
       </c>
       <c r="L466" s="1" t="n">
-        <v>27260</v>
+        <v>1049490</v>
       </c>
       <c r="M466" s="1" t="inlineStr">
         <is>
@@ -30021,10 +30021,10 @@
         <v>0</v>
       </c>
       <c r="K467" s="1" t="n">
-        <v>400000000000</v>
+        <v>33000000000000</v>
       </c>
       <c r="L467" s="1" t="n">
-        <v>35438</v>
+        <v>1364337</v>
       </c>
       <c r="M467" s="1" t="inlineStr">
         <is>
@@ -30084,10 +30084,10 @@
         <v>0</v>
       </c>
       <c r="K468" s="1" t="n">
-        <v>400000000000</v>
+        <v>33000000000000</v>
       </c>
       <c r="L468" s="1" t="n">
-        <v>35438</v>
+        <v>1364337</v>
       </c>
       <c r="M468" s="1" t="inlineStr">
         <is>
@@ -30147,10 +30147,10 @@
         <v>0</v>
       </c>
       <c r="K469" s="1" t="n">
-        <v>180000000000</v>
+        <v>15000000000000</v>
       </c>
       <c r="L469" s="1" t="n">
-        <v>16130</v>
+        <v>621000</v>
       </c>
       <c r="M469" s="1" t="inlineStr">
         <is>
@@ -30210,10 +30210,10 @@
         <v>0</v>
       </c>
       <c r="K470" s="1" t="n">
-        <v>240000000000</v>
+        <v>20000000000000</v>
       </c>
       <c r="L470" s="1" t="n">
-        <v>20969</v>
+        <v>807300</v>
       </c>
       <c r="M470" s="1" t="inlineStr">
         <is>
@@ -30273,10 +30273,10 @@
         <v>0</v>
       </c>
       <c r="K471" s="1" t="n">
-        <v>310000000000</v>
+        <v>25000000000000</v>
       </c>
       <c r="L471" s="1" t="n">
-        <v>27260</v>
+        <v>1049490</v>
       </c>
       <c r="M471" s="1" t="inlineStr">
         <is>
@@ -30336,10 +30336,10 @@
         <v>0</v>
       </c>
       <c r="K472" s="1" t="n">
-        <v>310000000000</v>
+        <v>25000000000000</v>
       </c>
       <c r="L472" s="1" t="n">
-        <v>27260</v>
+        <v>1049490</v>
       </c>
       <c r="M472" s="1" t="inlineStr">
         <is>
@@ -30399,10 +30399,10 @@
         <v>0</v>
       </c>
       <c r="K473" s="1" t="n">
-        <v>310000000000</v>
+        <v>25000000000000</v>
       </c>
       <c r="L473" s="1" t="n">
-        <v>27260</v>
+        <v>1049490</v>
       </c>
       <c r="M473" s="1" t="inlineStr">
         <is>
@@ -30462,10 +30462,10 @@
         <v>0</v>
       </c>
       <c r="K474" s="1" t="n">
-        <v>400000000000</v>
+        <v>33000000000000</v>
       </c>
       <c r="L474" s="1" t="n">
-        <v>35438</v>
+        <v>1364337</v>
       </c>
       <c r="M474" s="1" t="inlineStr">
         <is>
@@ -30525,10 +30525,10 @@
         <v>0</v>
       </c>
       <c r="K475" s="1" t="n">
-        <v>520000000000</v>
+        <v>42000000000000</v>
       </c>
       <c r="L475" s="1" t="n">
-        <v>46069</v>
+        <v>1773639</v>
       </c>
       <c r="M475" s="1" t="inlineStr">
         <is>
@@ -30588,10 +30588,10 @@
         <v>0</v>
       </c>
       <c r="K476" s="1" t="n">
-        <v>400000000000</v>
+        <v>33000000000000</v>
       </c>
       <c r="L476" s="1" t="n">
-        <v>35438</v>
+        <v>1364337</v>
       </c>
       <c r="M476" s="1" t="inlineStr">
         <is>
@@ -30651,10 +30651,10 @@
         <v>0</v>
       </c>
       <c r="K477" s="1" t="n">
-        <v>180000000000</v>
+        <v>15000000000000</v>
       </c>
       <c r="L477" s="1" t="n">
-        <v>16130</v>
+        <v>621000</v>
       </c>
       <c r="M477" s="1" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>0</v>
       </c>
       <c r="K478" s="1" t="n">
-        <v>240000000000</v>
+        <v>20000000000000</v>
       </c>
       <c r="L478" s="1" t="n">
-        <v>20969</v>
+        <v>807300</v>
       </c>
       <c r="M478" s="1" t="inlineStr">
         <is>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="K479" s="1" t="n">
-        <v>310000000000</v>
+        <v>25000000000000</v>
       </c>
       <c r="L479" s="1" t="n">
-        <v>27260</v>
+        <v>1049490</v>
       </c>
       <c r="M479" s="1" t="inlineStr">
         <is>
@@ -30840,10 +30840,10 @@
         <v>0</v>
       </c>
       <c r="K480" s="1" t="n">
-        <v>310000000000</v>
+        <v>25000000000000</v>
       </c>
       <c r="L480" s="1" t="n">
-        <v>27260</v>
+        <v>1049490</v>
       </c>
       <c r="M480" s="1" t="inlineStr">
         <is>
@@ -30903,10 +30903,10 @@
         <v>0</v>
       </c>
       <c r="K481" s="1" t="n">
-        <v>400000000000</v>
+        <v>33000000000000</v>
       </c>
       <c r="L481" s="1" t="n">
-        <v>35438</v>
+        <v>1364337</v>
       </c>
       <c r="M481" s="1" t="inlineStr">
         <is>
@@ -30966,10 +30966,10 @@
         <v>0</v>
       </c>
       <c r="K482" s="1" t="n">
-        <v>400000000000</v>
+        <v>33000000000000</v>
       </c>
       <c r="L482" s="1" t="n">
-        <v>35438</v>
+        <v>1364337</v>
       </c>
       <c r="M482" s="1" t="inlineStr">
         <is>
@@ -31029,10 +31029,10 @@
         <v>0</v>
       </c>
       <c r="K483" s="1" t="n">
-        <v>400000000000</v>
+        <v>33000000000000</v>
       </c>
       <c r="L483" s="1" t="n">
-        <v>35438</v>
+        <v>1364337</v>
       </c>
       <c r="M483" s="1" t="inlineStr">
         <is>
@@ -31092,10 +31092,10 @@
         <v>0</v>
       </c>
       <c r="K484" s="1" t="n">
-        <v>520000000000</v>
+        <v>42000000000000</v>
       </c>
       <c r="L484" s="1" t="n">
-        <v>46069</v>
+        <v>1773639</v>
       </c>
       <c r="M484" s="1" t="inlineStr">
         <is>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="K485" s="1" t="n">
-        <v>180000000000</v>
+        <v>15000000000000</v>
       </c>
       <c r="L485" s="1" t="n">
-        <v>16130</v>
+        <v>621000</v>
       </c>
       <c r="M485" s="1" t="inlineStr">
         <is>
@@ -31218,10 +31218,10 @@
         <v>0</v>
       </c>
       <c r="K486" s="1" t="n">
-        <v>240000000000</v>
+        <v>20000000000000</v>
       </c>
       <c r="L486" s="1" t="n">
-        <v>20969</v>
+        <v>807300</v>
       </c>
       <c r="M486" s="1" t="inlineStr">
         <is>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="K487" s="1" t="n">
-        <v>310000000000</v>
+        <v>25000000000000</v>
       </c>
       <c r="L487" s="1" t="n">
-        <v>27260</v>
+        <v>1049490</v>
       </c>
       <c r="M487" s="1" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>0</v>
       </c>
       <c r="K488" s="1" t="n">
-        <v>310000000000</v>
+        <v>25000000000000</v>
       </c>
       <c r="L488" s="1" t="n">
-        <v>27260</v>
+        <v>1049490</v>
       </c>
       <c r="M488" s="1" t="inlineStr">
         <is>
@@ -31407,10 +31407,10 @@
         <v>0</v>
       </c>
       <c r="K489" s="1" t="n">
-        <v>400000000000</v>
+        <v>33000000000000</v>
       </c>
       <c r="L489" s="1" t="n">
-        <v>35438</v>
+        <v>1364337</v>
       </c>
       <c r="M489" s="1" t="inlineStr">
         <is>
@@ -31470,10 +31470,10 @@
         <v>0</v>
       </c>
       <c r="K490" s="1" t="n">
-        <v>400000000000</v>
+        <v>33000000000000</v>
       </c>
       <c r="L490" s="1" t="n">
-        <v>35438</v>
+        <v>1364337</v>
       </c>
       <c r="M490" s="1" t="inlineStr">
         <is>
@@ -31533,10 +31533,10 @@
         <v>0</v>
       </c>
       <c r="K491" s="1" t="n">
-        <v>520000000000</v>
+        <v>42000000000000</v>
       </c>
       <c r="L491" s="1" t="n">
-        <v>46069</v>
+        <v>1773639</v>
       </c>
       <c r="M491" s="1" t="inlineStr">
         <is>
@@ -31596,10 +31596,10 @@
         <v>0</v>
       </c>
       <c r="K492" s="1" t="n">
-        <v>470000000000</v>
+        <v>39000000000000</v>
       </c>
       <c r="L492" s="1" t="n">
-        <v>41938</v>
+        <v>1614600</v>
       </c>
       <c r="M492" s="1" t="inlineStr">
         <is>
@@ -31659,10 +31659,10 @@
         <v>0</v>
       </c>
       <c r="K493" s="1" t="n">
-        <v>310000000000</v>
+        <v>25000000000000</v>
       </c>
       <c r="L493" s="1" t="n">
-        <v>27260</v>
+        <v>1049490</v>
       </c>
       <c r="M493" s="1" t="inlineStr">
         <is>
@@ -31695,11 +31695,11 @@
       </c>
       <c r="C494" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +2층</t>
         </is>
       </c>
       <c r="D494" s="1" t="n">
-        <v>2492332</v>
+        <v>2492132</v>
       </c>
       <c r="E494" s="1" t="inlineStr">
         <is>
@@ -31722,10 +31722,10 @@
         <v>0</v>
       </c>
       <c r="K494" s="1" t="n">
-        <v>800000000000</v>
+        <v>65000000000000</v>
       </c>
       <c r="L494" s="1" t="n">
-        <v>70876</v>
+        <v>2728674</v>
       </c>
       <c r="M494" s="1" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         </is>
       </c>
       <c r="N494" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O494" s="1" t="n">
         <v>0</v>
@@ -31785,10 +31785,10 @@
         <v>0</v>
       </c>
       <c r="K495" s="1" t="n">
-        <v>310000000000</v>
+        <v>25000000000000</v>
       </c>
       <c r="L495" s="1" t="n">
-        <v>27260</v>
+        <v>1049490</v>
       </c>
       <c r="M495" s="1" t="inlineStr">
         <is>
@@ -31848,10 +31848,10 @@
         <v>0</v>
       </c>
       <c r="K496" s="1" t="n">
-        <v>520000000000</v>
+        <v>42000000000000</v>
       </c>
       <c r="L496" s="1" t="n">
-        <v>46069</v>
+        <v>1773639</v>
       </c>
       <c r="M496" s="1" t="inlineStr">
         <is>
@@ -31911,10 +31911,10 @@
         <v>0</v>
       </c>
       <c r="K497" s="1" t="n">
-        <v>400000000000</v>
+        <v>33000000000000</v>
       </c>
       <c r="L497" s="1" t="n">
-        <v>35438</v>
+        <v>1364337</v>
       </c>
       <c r="M497" s="1" t="inlineStr">
         <is>
@@ -32043,10 +32043,10 @@
         <v>0</v>
       </c>
       <c r="K499" s="1" t="n">
-        <v>310000000000</v>
+        <v>48000000000000</v>
       </c>
       <c r="L499" s="1" t="n">
-        <v>24160</v>
+        <v>1520640</v>
       </c>
       <c r="M499" s="1" t="inlineStr">
         <is>
@@ -32106,10 +32106,10 @@
         <v>0</v>
       </c>
       <c r="K500" s="1" t="n">
-        <v>400000000000</v>
+        <v>62000000000000</v>
       </c>
       <c r="L500" s="1" t="n">
-        <v>31408</v>
+        <v>1976832</v>
       </c>
       <c r="M500" s="1" t="inlineStr">
         <is>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="K501" s="1" t="n">
-        <v>510000000000</v>
+        <v>81000000000000</v>
       </c>
       <c r="L501" s="1" t="n">
-        <v>40831</v>
+        <v>2569882</v>
       </c>
       <c r="M501" s="1" t="inlineStr">
         <is>
@@ -32232,10 +32232,10 @@
         <v>0</v>
       </c>
       <c r="K502" s="1" t="n">
-        <v>510000000000</v>
+        <v>81000000000000</v>
       </c>
       <c r="L502" s="1" t="n">
-        <v>40831</v>
+        <v>2569882</v>
       </c>
       <c r="M502" s="1" t="inlineStr">
         <is>
@@ -32295,10 +32295,10 @@
         <v>0</v>
       </c>
       <c r="K503" s="1" t="n">
-        <v>670000000000</v>
+        <v>110000000000000</v>
       </c>
       <c r="L503" s="1" t="n">
-        <v>53080</v>
+        <v>3340847</v>
       </c>
       <c r="M503" s="1" t="inlineStr">
         <is>
@@ -32358,10 +32358,10 @@
         <v>0</v>
       </c>
       <c r="K504" s="1" t="n">
-        <v>510000000000</v>
+        <v>81000000000000</v>
       </c>
       <c r="L504" s="1" t="n">
-        <v>40831</v>
+        <v>2569882</v>
       </c>
       <c r="M504" s="1" t="inlineStr">
         <is>
@@ -32421,10 +32421,10 @@
         <v>0</v>
       </c>
       <c r="K505" s="1" t="n">
-        <v>670000000000</v>
+        <v>110000000000000</v>
       </c>
       <c r="L505" s="1" t="n">
-        <v>53080</v>
+        <v>3340847</v>
       </c>
       <c r="M505" s="1" t="inlineStr">
         <is>
@@ -32484,10 +32484,10 @@
         <v>0</v>
       </c>
       <c r="K506" s="1" t="n">
-        <v>670000000000</v>
+        <v>110000000000000</v>
       </c>
       <c r="L506" s="1" t="n">
-        <v>53080</v>
+        <v>3340847</v>
       </c>
       <c r="M506" s="1" t="inlineStr">
         <is>
@@ -32547,10 +32547,10 @@
         <v>0</v>
       </c>
       <c r="K507" s="1" t="n">
-        <v>310000000000</v>
+        <v>48000000000000</v>
       </c>
       <c r="L507" s="1" t="n">
-        <v>24160</v>
+        <v>1520640</v>
       </c>
       <c r="M507" s="1" t="inlineStr">
         <is>
@@ -32610,10 +32610,10 @@
         <v>0</v>
       </c>
       <c r="K508" s="1" t="n">
-        <v>400000000000</v>
+        <v>62000000000000</v>
       </c>
       <c r="L508" s="1" t="n">
-        <v>31408</v>
+        <v>1976832</v>
       </c>
       <c r="M508" s="1" t="inlineStr">
         <is>
@@ -32673,10 +32673,10 @@
         <v>0</v>
       </c>
       <c r="K509" s="1" t="n">
-        <v>510000000000</v>
+        <v>81000000000000</v>
       </c>
       <c r="L509" s="1" t="n">
-        <v>40831</v>
+        <v>2569882</v>
       </c>
       <c r="M509" s="1" t="inlineStr">
         <is>
@@ -32736,10 +32736,10 @@
         <v>0</v>
       </c>
       <c r="K510" s="1" t="n">
-        <v>510000000000</v>
+        <v>81000000000000</v>
       </c>
       <c r="L510" s="1" t="n">
-        <v>40831</v>
+        <v>2569882</v>
       </c>
       <c r="M510" s="1" t="inlineStr">
         <is>
@@ -32799,10 +32799,10 @@
         <v>0</v>
       </c>
       <c r="K511" s="1" t="n">
-        <v>510000000000</v>
+        <v>81000000000000</v>
       </c>
       <c r="L511" s="1" t="n">
-        <v>40831</v>
+        <v>2569882</v>
       </c>
       <c r="M511" s="1" t="inlineStr">
         <is>
@@ -32862,10 +32862,10 @@
         <v>0</v>
       </c>
       <c r="K512" s="1" t="n">
-        <v>670000000000</v>
+        <v>110000000000000</v>
       </c>
       <c r="L512" s="1" t="n">
-        <v>53080</v>
+        <v>3340847</v>
       </c>
       <c r="M512" s="1" t="inlineStr">
         <is>
@@ -32925,10 +32925,10 @@
         <v>0</v>
       </c>
       <c r="K513" s="1" t="n">
-        <v>870000000000</v>
+        <v>140000000000000</v>
       </c>
       <c r="L513" s="1" t="n">
-        <v>69004</v>
+        <v>4343100</v>
       </c>
       <c r="M513" s="1" t="inlineStr">
         <is>
@@ -32988,10 +32988,10 @@
         <v>0</v>
       </c>
       <c r="K514" s="1" t="n">
-        <v>670000000000</v>
+        <v>110000000000000</v>
       </c>
       <c r="L514" s="1" t="n">
-        <v>53080</v>
+        <v>3340847</v>
       </c>
       <c r="M514" s="1" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>0</v>
       </c>
       <c r="K515" s="1" t="n">
-        <v>310000000000</v>
+        <v>48000000000000</v>
       </c>
       <c r="L515" s="1" t="n">
-        <v>24160</v>
+        <v>1520640</v>
       </c>
       <c r="M515" s="1" t="inlineStr">
         <is>
@@ -33114,10 +33114,10 @@
         <v>0</v>
       </c>
       <c r="K516" s="1" t="n">
-        <v>400000000000</v>
+        <v>62000000000000</v>
       </c>
       <c r="L516" s="1" t="n">
-        <v>31408</v>
+        <v>1976832</v>
       </c>
       <c r="M516" s="1" t="inlineStr">
         <is>
@@ -33177,10 +33177,10 @@
         <v>0</v>
       </c>
       <c r="K517" s="1" t="n">
-        <v>510000000000</v>
+        <v>81000000000000</v>
       </c>
       <c r="L517" s="1" t="n">
-        <v>40831</v>
+        <v>2569882</v>
       </c>
       <c r="M517" s="1" t="inlineStr">
         <is>
@@ -33240,10 +33240,10 @@
         <v>0</v>
       </c>
       <c r="K518" s="1" t="n">
-        <v>510000000000</v>
+        <v>81000000000000</v>
       </c>
       <c r="L518" s="1" t="n">
-        <v>40831</v>
+        <v>2569882</v>
       </c>
       <c r="M518" s="1" t="inlineStr">
         <is>
@@ -33303,10 +33303,10 @@
         <v>0</v>
       </c>
       <c r="K519" s="1" t="n">
-        <v>670000000000</v>
+        <v>110000000000000</v>
       </c>
       <c r="L519" s="1" t="n">
-        <v>53080</v>
+        <v>3340847</v>
       </c>
       <c r="M519" s="1" t="inlineStr">
         <is>
@@ -33366,10 +33366,10 @@
         <v>0</v>
       </c>
       <c r="K520" s="1" t="n">
-        <v>670000000000</v>
+        <v>110000000000000</v>
       </c>
       <c r="L520" s="1" t="n">
-        <v>53080</v>
+        <v>3340847</v>
       </c>
       <c r="M520" s="1" t="inlineStr">
         <is>
@@ -33429,10 +33429,10 @@
         <v>0</v>
       </c>
       <c r="K521" s="1" t="n">
-        <v>670000000000</v>
+        <v>110000000000000</v>
       </c>
       <c r="L521" s="1" t="n">
-        <v>53080</v>
+        <v>3340847</v>
       </c>
       <c r="M521" s="1" t="inlineStr">
         <is>
@@ -33492,10 +33492,10 @@
         <v>0</v>
       </c>
       <c r="K522" s="1" t="n">
-        <v>870000000000</v>
+        <v>140000000000000</v>
       </c>
       <c r="L522" s="1" t="n">
-        <v>69004</v>
+        <v>4343100</v>
       </c>
       <c r="M522" s="1" t="inlineStr">
         <is>
@@ -33555,10 +33555,10 @@
         <v>0</v>
       </c>
       <c r="K523" s="1" t="n">
-        <v>310000000000</v>
+        <v>48000000000000</v>
       </c>
       <c r="L523" s="1" t="n">
-        <v>24160</v>
+        <v>1520640</v>
       </c>
       <c r="M523" s="1" t="inlineStr">
         <is>
@@ -33618,10 +33618,10 @@
         <v>0</v>
       </c>
       <c r="K524" s="1" t="n">
-        <v>400000000000</v>
+        <v>62000000000000</v>
       </c>
       <c r="L524" s="1" t="n">
-        <v>31408</v>
+        <v>1976832</v>
       </c>
       <c r="M524" s="1" t="inlineStr">
         <is>
@@ -33681,10 +33681,10 @@
         <v>0</v>
       </c>
       <c r="K525" s="1" t="n">
-        <v>510000000000</v>
+        <v>81000000000000</v>
       </c>
       <c r="L525" s="1" t="n">
-        <v>40831</v>
+        <v>2569882</v>
       </c>
       <c r="M525" s="1" t="inlineStr">
         <is>
@@ -33744,10 +33744,10 @@
         <v>0</v>
       </c>
       <c r="K526" s="1" t="n">
-        <v>510000000000</v>
+        <v>81000000000000</v>
       </c>
       <c r="L526" s="1" t="n">
-        <v>40831</v>
+        <v>2569882</v>
       </c>
       <c r="M526" s="1" t="inlineStr">
         <is>
@@ -33807,10 +33807,10 @@
         <v>0</v>
       </c>
       <c r="K527" s="1" t="n">
-        <v>670000000000</v>
+        <v>110000000000000</v>
       </c>
       <c r="L527" s="1" t="n">
-        <v>53080</v>
+        <v>3340847</v>
       </c>
       <c r="M527" s="1" t="inlineStr">
         <is>
@@ -33870,10 +33870,10 @@
         <v>0</v>
       </c>
       <c r="K528" s="1" t="n">
-        <v>670000000000</v>
+        <v>110000000000000</v>
       </c>
       <c r="L528" s="1" t="n">
-        <v>53080</v>
+        <v>3340847</v>
       </c>
       <c r="M528" s="1" t="inlineStr">
         <is>
@@ -33933,10 +33933,10 @@
         <v>0</v>
       </c>
       <c r="K529" s="1" t="n">
-        <v>870000000000</v>
+        <v>140000000000000</v>
       </c>
       <c r="L529" s="1" t="n">
-        <v>69004</v>
+        <v>4343100</v>
       </c>
       <c r="M529" s="1" t="inlineStr">
         <is>
@@ -33969,11 +33969,11 @@
       </c>
       <c r="C530" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +4층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D530" s="1" t="n">
-        <v>2492732</v>
+        <v>2492332</v>
       </c>
       <c r="E530" s="1" t="inlineStr">
         <is>
@@ -33996,10 +33996,10 @@
         <v>0</v>
       </c>
       <c r="K530" s="1" t="n">
-        <v>790000000000</v>
+        <v>130000000000000</v>
       </c>
       <c r="L530" s="1" t="n">
-        <v>62816</v>
+        <v>3953664</v>
       </c>
       <c r="M530" s="1" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         </is>
       </c>
       <c r="N530" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O530" s="1" t="n">
         <v>0</v>
@@ -34059,10 +34059,10 @@
         <v>0</v>
       </c>
       <c r="K531" s="1" t="n">
-        <v>510000000000</v>
+        <v>81000000000000</v>
       </c>
       <c r="L531" s="1" t="n">
-        <v>40831</v>
+        <v>2569882</v>
       </c>
       <c r="M531" s="1" t="inlineStr">
         <is>
@@ -34095,11 +34095,11 @@
       </c>
       <c r="C532" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +3층</t>
+          <t>스테이지 스킵 +2층</t>
         </is>
       </c>
       <c r="D532" s="1" t="n">
-        <v>2492332</v>
+        <v>2492132</v>
       </c>
       <c r="E532" s="1" t="inlineStr">
         <is>
@@ -34122,10 +34122,10 @@
         <v>0</v>
       </c>
       <c r="K532" s="1" t="n">
-        <v>1400000000000</v>
+        <v>210000000000000</v>
       </c>
       <c r="L532" s="1" t="n">
-        <v>106160</v>
+        <v>6681693</v>
       </c>
       <c r="M532" s="1" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         </is>
       </c>
       <c r="N532" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O532" s="1" t="n">
         <v>0</v>
@@ -34185,10 +34185,10 @@
         <v>0</v>
       </c>
       <c r="K533" s="1" t="n">
-        <v>510000000000</v>
+        <v>81000000000000</v>
       </c>
       <c r="L533" s="1" t="n">
-        <v>40831</v>
+        <v>2569882</v>
       </c>
       <c r="M533" s="1" t="inlineStr">
         <is>
@@ -34248,10 +34248,10 @@
         <v>0</v>
       </c>
       <c r="K534" s="1" t="n">
-        <v>870000000000</v>
+        <v>140000000000000</v>
       </c>
       <c r="L534" s="1" t="n">
-        <v>69004</v>
+        <v>4343100</v>
       </c>
       <c r="M534" s="1" t="inlineStr">
         <is>
@@ -34311,10 +34311,10 @@
         <v>0</v>
       </c>
       <c r="K535" s="1" t="n">
-        <v>670000000000</v>
+        <v>110000000000000</v>
       </c>
       <c r="L535" s="1" t="n">
-        <v>53080</v>
+        <v>3340847</v>
       </c>
       <c r="M535" s="1" t="inlineStr">
         <is>
@@ -34443,10 +34443,10 @@
         <v>0</v>
       </c>
       <c r="K537" s="1" t="n">
-        <v>560000000000</v>
+        <v>200000000000000</v>
       </c>
       <c r="L537" s="1" t="n">
-        <v>40320</v>
+        <v>4665600</v>
       </c>
       <c r="M537" s="1" t="inlineStr">
         <is>
@@ -34506,10 +34506,10 @@
         <v>0</v>
       </c>
       <c r="K538" s="1" t="n">
-        <v>730000000000</v>
+        <v>250000000000000</v>
       </c>
       <c r="L538" s="1" t="n">
-        <v>52416</v>
+        <v>6065280</v>
       </c>
       <c r="M538" s="1" t="inlineStr">
         <is>
@@ -34569,10 +34569,10 @@
         <v>0</v>
       </c>
       <c r="K539" s="1" t="n">
-        <v>940000000000</v>
+        <v>330000000000000</v>
       </c>
       <c r="L539" s="1" t="n">
-        <v>68141</v>
+        <v>7884865</v>
       </c>
       <c r="M539" s="1" t="inlineStr">
         <is>
@@ -34632,10 +34632,10 @@
         <v>0</v>
       </c>
       <c r="K540" s="1" t="n">
-        <v>940000000000</v>
+        <v>330000000000000</v>
       </c>
       <c r="L540" s="1" t="n">
-        <v>68141</v>
+        <v>7884865</v>
       </c>
       <c r="M540" s="1" t="inlineStr">
         <is>
@@ -34695,10 +34695,10 @@
         <v>0</v>
       </c>
       <c r="K541" s="1" t="n">
-        <v>1300000000000</v>
+        <v>430000000000000</v>
       </c>
       <c r="L541" s="1" t="n">
-        <v>88584</v>
+        <v>10250324</v>
       </c>
       <c r="M541" s="1" t="inlineStr">
         <is>
@@ -34758,10 +34758,10 @@
         <v>0</v>
       </c>
       <c r="K542" s="1" t="n">
-        <v>940000000000</v>
+        <v>330000000000000</v>
       </c>
       <c r="L542" s="1" t="n">
-        <v>68141</v>
+        <v>7884865</v>
       </c>
       <c r="M542" s="1" t="inlineStr">
         <is>
@@ -34821,10 +34821,10 @@
         <v>0</v>
       </c>
       <c r="K543" s="1" t="n">
-        <v>1300000000000</v>
+        <v>430000000000000</v>
       </c>
       <c r="L543" s="1" t="n">
-        <v>88584</v>
+        <v>10250324</v>
       </c>
       <c r="M543" s="1" t="inlineStr">
         <is>
@@ -34884,10 +34884,10 @@
         <v>0</v>
       </c>
       <c r="K544" s="1" t="n">
-        <v>1300000000000</v>
+        <v>430000000000000</v>
       </c>
       <c r="L544" s="1" t="n">
-        <v>88584</v>
+        <v>10250324</v>
       </c>
       <c r="M544" s="1" t="inlineStr">
         <is>
@@ -34947,10 +34947,10 @@
         <v>0</v>
       </c>
       <c r="K545" s="1" t="n">
-        <v>560000000000</v>
+        <v>200000000000000</v>
       </c>
       <c r="L545" s="1" t="n">
-        <v>40320</v>
+        <v>4665600</v>
       </c>
       <c r="M545" s="1" t="inlineStr">
         <is>
@@ -35010,10 +35010,10 @@
         <v>0</v>
       </c>
       <c r="K546" s="1" t="n">
-        <v>730000000000</v>
+        <v>250000000000000</v>
       </c>
       <c r="L546" s="1" t="n">
-        <v>52416</v>
+        <v>6065280</v>
       </c>
       <c r="M546" s="1" t="inlineStr">
         <is>
@@ -35073,10 +35073,10 @@
         <v>0</v>
       </c>
       <c r="K547" s="1" t="n">
-        <v>940000000000</v>
+        <v>330000000000000</v>
       </c>
       <c r="L547" s="1" t="n">
-        <v>68141</v>
+        <v>7884865</v>
       </c>
       <c r="M547" s="1" t="inlineStr">
         <is>
@@ -35136,10 +35136,10 @@
         <v>0</v>
       </c>
       <c r="K548" s="1" t="n">
-        <v>940000000000</v>
+        <v>330000000000000</v>
       </c>
       <c r="L548" s="1" t="n">
-        <v>68141</v>
+        <v>7884865</v>
       </c>
       <c r="M548" s="1" t="inlineStr">
         <is>
@@ -35199,10 +35199,10 @@
         <v>0</v>
       </c>
       <c r="K549" s="1" t="n">
-        <v>940000000000</v>
+        <v>330000000000000</v>
       </c>
       <c r="L549" s="1" t="n">
-        <v>68141</v>
+        <v>7884865</v>
       </c>
       <c r="M549" s="1" t="inlineStr">
         <is>
@@ -35262,10 +35262,10 @@
         <v>0</v>
       </c>
       <c r="K550" s="1" t="n">
-        <v>1300000000000</v>
+        <v>430000000000000</v>
       </c>
       <c r="L550" s="1" t="n">
-        <v>88584</v>
+        <v>10250324</v>
       </c>
       <c r="M550" s="1" t="inlineStr">
         <is>
@@ -35325,10 +35325,10 @@
         <v>0</v>
       </c>
       <c r="K551" s="1" t="n">
-        <v>1600000000000</v>
+        <v>550000000000000</v>
       </c>
       <c r="L551" s="1" t="n">
-        <v>115158</v>
+        <v>13325421</v>
       </c>
       <c r="M551" s="1" t="inlineStr">
         <is>
@@ -35388,10 +35388,10 @@
         <v>0</v>
       </c>
       <c r="K552" s="1" t="n">
-        <v>1300000000000</v>
+        <v>430000000000000</v>
       </c>
       <c r="L552" s="1" t="n">
-        <v>88584</v>
+        <v>10250324</v>
       </c>
       <c r="M552" s="1" t="inlineStr">
         <is>
@@ -35451,10 +35451,10 @@
         <v>0</v>
       </c>
       <c r="K553" s="1" t="n">
-        <v>560000000000</v>
+        <v>200000000000000</v>
       </c>
       <c r="L553" s="1" t="n">
-        <v>40320</v>
+        <v>4665600</v>
       </c>
       <c r="M553" s="1" t="inlineStr">
         <is>
@@ -35514,10 +35514,10 @@
         <v>0</v>
       </c>
       <c r="K554" s="1" t="n">
-        <v>730000000000</v>
+        <v>250000000000000</v>
       </c>
       <c r="L554" s="1" t="n">
-        <v>52416</v>
+        <v>6065280</v>
       </c>
       <c r="M554" s="1" t="inlineStr">
         <is>
@@ -35577,10 +35577,10 @@
         <v>0</v>
       </c>
       <c r="K555" s="1" t="n">
-        <v>940000000000</v>
+        <v>330000000000000</v>
       </c>
       <c r="L555" s="1" t="n">
-        <v>68141</v>
+        <v>7884865</v>
       </c>
       <c r="M555" s="1" t="inlineStr">
         <is>
@@ -35640,10 +35640,10 @@
         <v>0</v>
       </c>
       <c r="K556" s="1" t="n">
-        <v>940000000000</v>
+        <v>330000000000000</v>
       </c>
       <c r="L556" s="1" t="n">
-        <v>68141</v>
+        <v>7884865</v>
       </c>
       <c r="M556" s="1" t="inlineStr">
         <is>
@@ -35703,10 +35703,10 @@
         <v>0</v>
       </c>
       <c r="K557" s="1" t="n">
-        <v>1300000000000</v>
+        <v>430000000000000</v>
       </c>
       <c r="L557" s="1" t="n">
-        <v>88584</v>
+        <v>10250324</v>
       </c>
       <c r="M557" s="1" t="inlineStr">
         <is>
@@ -35766,10 +35766,10 @@
         <v>0</v>
       </c>
       <c r="K558" s="1" t="n">
-        <v>1300000000000</v>
+        <v>430000000000000</v>
       </c>
       <c r="L558" s="1" t="n">
-        <v>88584</v>
+        <v>10250324</v>
       </c>
       <c r="M558" s="1" t="inlineStr">
         <is>
@@ -35829,10 +35829,10 @@
         <v>0</v>
       </c>
       <c r="K559" s="1" t="n">
-        <v>1300000000000</v>
+        <v>430000000000000</v>
       </c>
       <c r="L559" s="1" t="n">
-        <v>88584</v>
+        <v>10250324</v>
       </c>
       <c r="M559" s="1" t="inlineStr">
         <is>
@@ -35892,10 +35892,10 @@
         <v>0</v>
       </c>
       <c r="K560" s="1" t="n">
-        <v>1600000000000</v>
+        <v>550000000000000</v>
       </c>
       <c r="L560" s="1" t="n">
-        <v>115158</v>
+        <v>13325421</v>
       </c>
       <c r="M560" s="1" t="inlineStr">
         <is>
@@ -35955,10 +35955,10 @@
         <v>0</v>
       </c>
       <c r="K561" s="1" t="n">
-        <v>560000000000</v>
+        <v>200000000000000</v>
       </c>
       <c r="L561" s="1" t="n">
-        <v>40320</v>
+        <v>4665600</v>
       </c>
       <c r="M561" s="1" t="inlineStr">
         <is>
@@ -36018,10 +36018,10 @@
         <v>0</v>
       </c>
       <c r="K562" s="1" t="n">
-        <v>730000000000</v>
+        <v>250000000000000</v>
       </c>
       <c r="L562" s="1" t="n">
-        <v>52416</v>
+        <v>6065280</v>
       </c>
       <c r="M562" s="1" t="inlineStr">
         <is>
@@ -36081,10 +36081,10 @@
         <v>0</v>
       </c>
       <c r="K563" s="1" t="n">
-        <v>940000000000</v>
+        <v>330000000000000</v>
       </c>
       <c r="L563" s="1" t="n">
-        <v>68141</v>
+        <v>7884865</v>
       </c>
       <c r="M563" s="1" t="inlineStr">
         <is>
@@ -36144,10 +36144,10 @@
         <v>0</v>
       </c>
       <c r="K564" s="1" t="n">
-        <v>940000000000</v>
+        <v>330000000000000</v>
       </c>
       <c r="L564" s="1" t="n">
-        <v>68141</v>
+        <v>7884865</v>
       </c>
       <c r="M564" s="1" t="inlineStr">
         <is>
@@ -36207,10 +36207,10 @@
         <v>0</v>
       </c>
       <c r="K565" s="1" t="n">
-        <v>1300000000000</v>
+        <v>430000000000000</v>
       </c>
       <c r="L565" s="1" t="n">
-        <v>88584</v>
+        <v>10250324</v>
       </c>
       <c r="M565" s="1" t="inlineStr">
         <is>
@@ -36270,10 +36270,10 @@
         <v>0</v>
       </c>
       <c r="K566" s="1" t="n">
-        <v>1300000000000</v>
+        <v>430000000000000</v>
       </c>
       <c r="L566" s="1" t="n">
-        <v>88584</v>
+        <v>10250324</v>
       </c>
       <c r="M566" s="1" t="inlineStr">
         <is>
@@ -36333,10 +36333,10 @@
         <v>0</v>
       </c>
       <c r="K567" s="1" t="n">
-        <v>1600000000000</v>
+        <v>550000000000000</v>
       </c>
       <c r="L567" s="1" t="n">
-        <v>115158</v>
+        <v>13325421</v>
       </c>
       <c r="M567" s="1" t="inlineStr">
         <is>
@@ -36369,11 +36369,11 @@
       </c>
       <c r="C568" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +6층</t>
+          <t>스테이지 스킵 +4층</t>
         </is>
       </c>
       <c r="D568" s="1" t="n">
-        <v>2492934</v>
+        <v>2492732</v>
       </c>
       <c r="E568" s="1" t="inlineStr">
         <is>
@@ -36396,10 +36396,10 @@
         <v>0</v>
       </c>
       <c r="K568" s="1" t="n">
-        <v>1500000000000</v>
+        <v>500000000000000</v>
       </c>
       <c r="L568" s="1" t="n">
-        <v>104832</v>
+        <v>12130560</v>
       </c>
       <c r="M568" s="1" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         </is>
       </c>
       <c r="N568" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O568" s="1" t="n">
         <v>0</v>
@@ -36459,10 +36459,10 @@
         <v>0</v>
       </c>
       <c r="K569" s="1" t="n">
-        <v>940000000000</v>
+        <v>330000000000000</v>
       </c>
       <c r="L569" s="1" t="n">
-        <v>68141</v>
+        <v>7884865</v>
       </c>
       <c r="M569" s="1" t="inlineStr">
         <is>
@@ -36495,11 +36495,11 @@
       </c>
       <c r="C570" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +5층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D570" s="1" t="n">
-        <v>2493332</v>
+        <v>2492332</v>
       </c>
       <c r="E570" s="1" t="inlineStr">
         <is>
@@ -36522,10 +36522,10 @@
         <v>0</v>
       </c>
       <c r="K570" s="1" t="n">
-        <v>2500000000000</v>
+        <v>850000000000000</v>
       </c>
       <c r="L570" s="1" t="n">
-        <v>177167</v>
+        <v>20500647</v>
       </c>
       <c r="M570" s="1" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         </is>
       </c>
       <c r="N570" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O570" s="1" t="n">
         <v>0</v>
@@ -36585,10 +36585,10 @@
         <v>0</v>
       </c>
       <c r="K571" s="1" t="n">
-        <v>940000000000</v>
+        <v>330000000000000</v>
       </c>
       <c r="L571" s="1" t="n">
-        <v>68141</v>
+        <v>7884865</v>
       </c>
       <c r="M571" s="1" t="inlineStr">
         <is>
@@ -36648,10 +36648,10 @@
         <v>0</v>
       </c>
       <c r="K572" s="1" t="n">
-        <v>1600000000000</v>
+        <v>550000000000000</v>
       </c>
       <c r="L572" s="1" t="n">
-        <v>115158</v>
+        <v>13325421</v>
       </c>
       <c r="M572" s="1" t="inlineStr">
         <is>
@@ -36711,10 +36711,10 @@
         <v>0</v>
       </c>
       <c r="K573" s="1" t="n">
-        <v>1300000000000</v>
+        <v>430000000000000</v>
       </c>
       <c r="L573" s="1" t="n">
-        <v>88584</v>
+        <v>10250324</v>
       </c>
       <c r="M573" s="1" t="inlineStr">
         <is>
@@ -36843,10 +36843,10 @@
         <v>0</v>
       </c>
       <c r="K575" s="1" t="n">
-        <v>320000000000</v>
+        <v>310000000000000</v>
       </c>
       <c r="L575" s="1" t="n">
-        <v>20160</v>
+        <v>5326560</v>
       </c>
       <c r="M575" s="1" t="inlineStr">
         <is>
@@ -36906,10 +36906,10 @@
         <v>0</v>
       </c>
       <c r="K576" s="1" t="n">
-        <v>420000000000</v>
+        <v>400000000000000</v>
       </c>
       <c r="L576" s="1" t="n">
-        <v>26208</v>
+        <v>6924528</v>
       </c>
       <c r="M576" s="1" t="inlineStr">
         <is>
@@ -36969,10 +36969,10 @@
         <v>0</v>
       </c>
       <c r="K577" s="1" t="n">
-        <v>550000000000</v>
+        <v>520000000000000</v>
       </c>
       <c r="L577" s="1" t="n">
-        <v>34071</v>
+        <v>9001887</v>
       </c>
       <c r="M577" s="1" t="inlineStr">
         <is>
@@ -37032,10 +37032,10 @@
         <v>0</v>
       </c>
       <c r="K578" s="1" t="n">
-        <v>550000000000</v>
+        <v>520000000000000</v>
       </c>
       <c r="L578" s="1" t="n">
-        <v>34071</v>
+        <v>9001887</v>
       </c>
       <c r="M578" s="1" t="inlineStr">
         <is>
@@ -37095,10 +37095,10 @@
         <v>0</v>
       </c>
       <c r="K579" s="1" t="n">
-        <v>710000000000</v>
+        <v>670000000000000</v>
       </c>
       <c r="L579" s="1" t="n">
-        <v>44292</v>
+        <v>11702453</v>
       </c>
       <c r="M579" s="1" t="inlineStr">
         <is>
@@ -37158,10 +37158,10 @@
         <v>0</v>
       </c>
       <c r="K580" s="1" t="n">
-        <v>550000000000</v>
+        <v>520000000000000</v>
       </c>
       <c r="L580" s="1" t="n">
-        <v>34071</v>
+        <v>9001887</v>
       </c>
       <c r="M580" s="1" t="inlineStr">
         <is>
@@ -37221,10 +37221,10 @@
         <v>0</v>
       </c>
       <c r="K581" s="1" t="n">
-        <v>710000000000</v>
+        <v>670000000000000</v>
       </c>
       <c r="L581" s="1" t="n">
-        <v>44292</v>
+        <v>11702453</v>
       </c>
       <c r="M581" s="1" t="inlineStr">
         <is>
@@ -37284,10 +37284,10 @@
         <v>0</v>
       </c>
       <c r="K582" s="1" t="n">
-        <v>710000000000</v>
+        <v>670000000000000</v>
       </c>
       <c r="L582" s="1" t="n">
-        <v>44292</v>
+        <v>11702453</v>
       </c>
       <c r="M582" s="1" t="inlineStr">
         <is>
@@ -37347,10 +37347,10 @@
         <v>0</v>
       </c>
       <c r="K583" s="1" t="n">
-        <v>320000000000</v>
+        <v>310000000000000</v>
       </c>
       <c r="L583" s="1" t="n">
-        <v>20160</v>
+        <v>5326560</v>
       </c>
       <c r="M583" s="1" t="inlineStr">
         <is>
@@ -37410,10 +37410,10 @@
         <v>0</v>
       </c>
       <c r="K584" s="1" t="n">
-        <v>420000000000</v>
+        <v>400000000000000</v>
       </c>
       <c r="L584" s="1" t="n">
-        <v>26208</v>
+        <v>6924528</v>
       </c>
       <c r="M584" s="1" t="inlineStr">
         <is>
@@ -37473,10 +37473,10 @@
         <v>0</v>
       </c>
       <c r="K585" s="1" t="n">
-        <v>550000000000</v>
+        <v>520000000000000</v>
       </c>
       <c r="L585" s="1" t="n">
-        <v>34071</v>
+        <v>9001887</v>
       </c>
       <c r="M585" s="1" t="inlineStr">
         <is>
@@ -37536,10 +37536,10 @@
         <v>0</v>
       </c>
       <c r="K586" s="1" t="n">
-        <v>550000000000</v>
+        <v>520000000000000</v>
       </c>
       <c r="L586" s="1" t="n">
-        <v>34071</v>
+        <v>9001887</v>
       </c>
       <c r="M586" s="1" t="inlineStr">
         <is>
@@ -37599,10 +37599,10 @@
         <v>0</v>
       </c>
       <c r="K587" s="1" t="n">
-        <v>550000000000</v>
+        <v>520000000000000</v>
       </c>
       <c r="L587" s="1" t="n">
-        <v>34071</v>
+        <v>9001887</v>
       </c>
       <c r="M587" s="1" t="inlineStr">
         <is>
@@ -37662,10 +37662,10 @@
         <v>0</v>
       </c>
       <c r="K588" s="1" t="n">
-        <v>710000000000</v>
+        <v>670000000000000</v>
       </c>
       <c r="L588" s="1" t="n">
-        <v>44292</v>
+        <v>11702453</v>
       </c>
       <c r="M588" s="1" t="inlineStr">
         <is>
@@ -37725,10 +37725,10 @@
         <v>0</v>
       </c>
       <c r="K589" s="1" t="n">
-        <v>920000000000</v>
+        <v>870000000000000</v>
       </c>
       <c r="L589" s="1" t="n">
-        <v>57579</v>
+        <v>15213189</v>
       </c>
       <c r="M589" s="1" t="inlineStr">
         <is>
@@ -37788,10 +37788,10 @@
         <v>0</v>
       </c>
       <c r="K590" s="1" t="n">
-        <v>710000000000</v>
+        <v>670000000000000</v>
       </c>
       <c r="L590" s="1" t="n">
-        <v>44292</v>
+        <v>11702453</v>
       </c>
       <c r="M590" s="1" t="inlineStr">
         <is>
@@ -37851,10 +37851,10 @@
         <v>0</v>
       </c>
       <c r="K591" s="1" t="n">
-        <v>320000000000</v>
+        <v>310000000000000</v>
       </c>
       <c r="L591" s="1" t="n">
-        <v>20160</v>
+        <v>5326560</v>
       </c>
       <c r="M591" s="1" t="inlineStr">
         <is>
@@ -37914,10 +37914,10 @@
         <v>0</v>
       </c>
       <c r="K592" s="1" t="n">
-        <v>420000000000</v>
+        <v>400000000000000</v>
       </c>
       <c r="L592" s="1" t="n">
-        <v>26208</v>
+        <v>6924528</v>
       </c>
       <c r="M592" s="1" t="inlineStr">
         <is>
@@ -37977,10 +37977,10 @@
         <v>0</v>
       </c>
       <c r="K593" s="1" t="n">
-        <v>550000000000</v>
+        <v>520000000000000</v>
       </c>
       <c r="L593" s="1" t="n">
-        <v>34071</v>
+        <v>9001887</v>
       </c>
       <c r="M593" s="1" t="inlineStr">
         <is>
@@ -38040,10 +38040,10 @@
         <v>0</v>
       </c>
       <c r="K594" s="1" t="n">
-        <v>550000000000</v>
+        <v>520000000000000</v>
       </c>
       <c r="L594" s="1" t="n">
-        <v>34071</v>
+        <v>9001887</v>
       </c>
       <c r="M594" s="1" t="inlineStr">
         <is>
@@ -38103,10 +38103,10 @@
         <v>0</v>
       </c>
       <c r="K595" s="1" t="n">
-        <v>710000000000</v>
+        <v>670000000000000</v>
       </c>
       <c r="L595" s="1" t="n">
-        <v>44292</v>
+        <v>11702453</v>
       </c>
       <c r="M595" s="1" t="inlineStr">
         <is>
@@ -38166,10 +38166,10 @@
         <v>0</v>
       </c>
       <c r="K596" s="1" t="n">
-        <v>710000000000</v>
+        <v>670000000000000</v>
       </c>
       <c r="L596" s="1" t="n">
-        <v>44292</v>
+        <v>11702453</v>
       </c>
       <c r="M596" s="1" t="inlineStr">
         <is>
@@ -38229,10 +38229,10 @@
         <v>0</v>
       </c>
       <c r="K597" s="1" t="n">
-        <v>710000000000</v>
+        <v>670000000000000</v>
       </c>
       <c r="L597" s="1" t="n">
-        <v>44292</v>
+        <v>11702453</v>
       </c>
       <c r="M597" s="1" t="inlineStr">
         <is>
@@ -38292,10 +38292,10 @@
         <v>0</v>
       </c>
       <c r="K598" s="1" t="n">
-        <v>920000000000</v>
+        <v>870000000000000</v>
       </c>
       <c r="L598" s="1" t="n">
-        <v>57579</v>
+        <v>15213189</v>
       </c>
       <c r="M598" s="1" t="inlineStr">
         <is>
@@ -38355,10 +38355,10 @@
         <v>0</v>
       </c>
       <c r="K599" s="1" t="n">
-        <v>320000000000</v>
+        <v>310000000000000</v>
       </c>
       <c r="L599" s="1" t="n">
-        <v>20160</v>
+        <v>5326560</v>
       </c>
       <c r="M599" s="1" t="inlineStr">
         <is>
@@ -38418,10 +38418,10 @@
         <v>0</v>
       </c>
       <c r="K600" s="1" t="n">
-        <v>420000000000</v>
+        <v>400000000000000</v>
       </c>
       <c r="L600" s="1" t="n">
-        <v>26208</v>
+        <v>6924528</v>
       </c>
       <c r="M600" s="1" t="inlineStr">
         <is>
@@ -38481,10 +38481,10 @@
         <v>0</v>
       </c>
       <c r="K601" s="1" t="n">
-        <v>550000000000</v>
+        <v>520000000000000</v>
       </c>
       <c r="L601" s="1" t="n">
-        <v>34071</v>
+        <v>9001887</v>
       </c>
       <c r="M601" s="1" t="inlineStr">
         <is>
@@ -38544,10 +38544,10 @@
         <v>0</v>
       </c>
       <c r="K602" s="1" t="n">
-        <v>550000000000</v>
+        <v>520000000000000</v>
       </c>
       <c r="L602" s="1" t="n">
-        <v>34071</v>
+        <v>9001887</v>
       </c>
       <c r="M602" s="1" t="inlineStr">
         <is>
@@ -38607,10 +38607,10 @@
         <v>0</v>
       </c>
       <c r="K603" s="1" t="n">
-        <v>710000000000</v>
+        <v>670000000000000</v>
       </c>
       <c r="L603" s="1" t="n">
-        <v>44292</v>
+        <v>11702453</v>
       </c>
       <c r="M603" s="1" t="inlineStr">
         <is>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="K604" s="1" t="n">
-        <v>710000000000</v>
+        <v>670000000000000</v>
       </c>
       <c r="L604" s="1" t="n">
-        <v>44292</v>
+        <v>11702453</v>
       </c>
       <c r="M604" s="1" t="inlineStr">
         <is>
@@ -38733,10 +38733,10 @@
         <v>0</v>
       </c>
       <c r="K605" s="1" t="n">
-        <v>920000000000</v>
+        <v>870000000000000</v>
       </c>
       <c r="L605" s="1" t="n">
-        <v>57579</v>
+        <v>15213189</v>
       </c>
       <c r="M605" s="1" t="inlineStr">
         <is>
@@ -38769,11 +38769,11 @@
       </c>
       <c r="C606" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +4층</t>
+          <t>스테이지 스킵 +3층</t>
         </is>
       </c>
       <c r="D606" s="1" t="n">
-        <v>2492732</v>
+        <v>2492332</v>
       </c>
       <c r="E606" s="1" t="inlineStr">
         <is>
@@ -38796,10 +38796,10 @@
         <v>0</v>
       </c>
       <c r="K606" s="1" t="n">
-        <v>840000000000</v>
+        <v>800000000000000</v>
       </c>
       <c r="L606" s="1" t="n">
-        <v>52416</v>
+        <v>13849056</v>
       </c>
       <c r="M606" s="1" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         </is>
       </c>
       <c r="N606" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O606" s="1" t="n">
         <v>0</v>
@@ -38859,10 +38859,10 @@
         <v>0</v>
       </c>
       <c r="K607" s="1" t="n">
-        <v>550000000000</v>
+        <v>520000000000000</v>
       </c>
       <c r="L607" s="1" t="n">
-        <v>34071</v>
+        <v>9001887</v>
       </c>
       <c r="M607" s="1" t="inlineStr">
         <is>
@@ -38895,11 +38895,11 @@
       </c>
       <c r="C608" s="1" t="inlineStr">
         <is>
-          <t>스테이지 스킵 +4층</t>
+          <t>스테이지 스킵 +2층</t>
         </is>
       </c>
       <c r="D608" s="1" t="n">
-        <v>2492732</v>
+        <v>2492132</v>
       </c>
       <c r="E608" s="1" t="inlineStr">
         <is>
@@ -38922,10 +38922,10 @@
         <v>0</v>
       </c>
       <c r="K608" s="1" t="n">
-        <v>1500000000000</v>
+        <v>1400000000000000</v>
       </c>
       <c r="L608" s="1" t="n">
-        <v>88584</v>
+        <v>23404905</v>
       </c>
       <c r="M608" s="1" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         </is>
       </c>
       <c r="N608" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O608" s="1" t="n">
         <v>0</v>
@@ -38985,10 +38985,10 @@
         <v>0</v>
       </c>
       <c r="K609" s="1" t="n">
-        <v>550000000000</v>
+        <v>520000000000000</v>
       </c>
       <c r="L609" s="1" t="n">
-        <v>34071</v>
+        <v>9001887</v>
       </c>
       <c r="M609" s="1" t="inlineStr">
         <is>
@@ -39048,10 +39048,10 @@
         <v>0</v>
       </c>
       <c r="K610" s="1" t="n">
-        <v>920000000000</v>
+        <v>870000000000000</v>
       </c>
       <c r="L610" s="1" t="n">
-        <v>57579</v>
+        <v>15213189</v>
       </c>
       <c r="M610" s="1" t="inlineStr">
         <is>
@@ -39111,10 +39111,10 @@
         <v>0</v>
       </c>
       <c r="K611" s="1" t="n">
-        <v>1500000000000</v>
+        <v>1400000000000000</v>
       </c>
       <c r="L611" s="1" t="n">
-        <v>88584</v>
+        <v>23404905</v>
       </c>
       <c r="M611" s="1" t="inlineStr">
         <is>
